--- a/Market Fundamentals/Transelectrica_data/Cons_Prod_final/Weekly_Production_2026.xlsx
+++ b/Market Fundamentals/Transelectrica_data/Cons_Prod_final/Weekly_Production_2026.xlsx
@@ -44272,7 +44272,7 @@
         <v>1</v>
       </c>
       <c r="C2498">
-        <v>5076.7</v>
+        <v>6789.2</v>
       </c>
       <c r="D2498" t="s">
         <v>2500</v>
@@ -44286,7 +44286,7 @@
         <v>2</v>
       </c>
       <c r="C2499">
-        <v>5048.7</v>
+        <v>6394.1</v>
       </c>
       <c r="D2499" t="s">
         <v>2501</v>
@@ -44300,7 +44300,7 @@
         <v>3</v>
       </c>
       <c r="C2500">
-        <v>4665.9</v>
+        <v>6682.9</v>
       </c>
       <c r="D2500" t="s">
         <v>2502</v>
@@ -44314,7 +44314,7 @@
         <v>4</v>
       </c>
       <c r="C2501">
-        <v>4483.9</v>
+        <v>6179.3</v>
       </c>
       <c r="D2501" t="s">
         <v>2503</v>
@@ -44328,7 +44328,7 @@
         <v>5</v>
       </c>
       <c r="C2502">
-        <v>5208.5</v>
+        <v>6758.1</v>
       </c>
       <c r="D2502" t="s">
         <v>2504</v>
@@ -44342,7 +44342,7 @@
         <v>6</v>
       </c>
       <c r="C2503">
-        <v>4463</v>
+        <v>6382.7</v>
       </c>
       <c r="D2503" t="s">
         <v>2505</v>
@@ -44356,7 +44356,7 @@
         <v>7</v>
       </c>
       <c r="C2504">
-        <v>4263.4</v>
+        <v>5909.5</v>
       </c>
       <c r="D2504" t="s">
         <v>2506</v>
@@ -44370,7 +44370,7 @@
         <v>8</v>
       </c>
       <c r="C2505">
-        <v>4214.7</v>
+        <v>5819.4</v>
       </c>
       <c r="D2505" t="s">
         <v>2507</v>
@@ -44384,7 +44384,7 @@
         <v>9</v>
       </c>
       <c r="C2506">
-        <v>4234.1</v>
+        <v>5939.2</v>
       </c>
       <c r="D2506" t="s">
         <v>2508</v>
@@ -44398,7 +44398,7 @@
         <v>10</v>
       </c>
       <c r="C2507">
-        <v>4085.3</v>
+        <v>5996.6</v>
       </c>
       <c r="D2507" t="s">
         <v>2509</v>
@@ -44412,7 +44412,7 @@
         <v>11</v>
       </c>
       <c r="C2508">
-        <v>3912.6</v>
+        <v>5747.1</v>
       </c>
       <c r="D2508" t="s">
         <v>2510</v>
@@ -44426,7 +44426,7 @@
         <v>12</v>
       </c>
       <c r="C2509">
-        <v>3527</v>
+        <v>5832</v>
       </c>
       <c r="D2509" t="s">
         <v>2511</v>
@@ -44440,7 +44440,7 @@
         <v>13</v>
       </c>
       <c r="C2510">
-        <v>3495.3</v>
+        <v>6238</v>
       </c>
       <c r="D2510" t="s">
         <v>2512</v>
@@ -44454,7 +44454,7 @@
         <v>14</v>
       </c>
       <c r="C2511">
-        <v>3533.2</v>
+        <v>6119.2</v>
       </c>
       <c r="D2511" t="s">
         <v>2513</v>
@@ -44468,7 +44468,7 @@
         <v>15</v>
       </c>
       <c r="C2512">
-        <v>3517.2</v>
+        <v>6256.7</v>
       </c>
       <c r="D2512" t="s">
         <v>2514</v>
@@ -44482,7 +44482,7 @@
         <v>16</v>
       </c>
       <c r="C2513">
-        <v>3547.9</v>
+        <v>6288.1</v>
       </c>
       <c r="D2513" t="s">
         <v>2515</v>
@@ -44496,7 +44496,7 @@
         <v>17</v>
       </c>
       <c r="C2514">
-        <v>3585.7</v>
+        <v>6161.6</v>
       </c>
       <c r="D2514" t="s">
         <v>2516</v>
@@ -44510,7 +44510,7 @@
         <v>18</v>
       </c>
       <c r="C2515">
-        <v>3536.7</v>
+        <v>5822.9</v>
       </c>
       <c r="D2515" t="s">
         <v>2517</v>
@@ -44524,7 +44524,7 @@
         <v>19</v>
       </c>
       <c r="C2516">
-        <v>3625.3</v>
+        <v>5908.9</v>
       </c>
       <c r="D2516" t="s">
         <v>2518</v>
@@ -44538,7 +44538,7 @@
         <v>20</v>
       </c>
       <c r="C2517">
-        <v>3707</v>
+        <v>6005.4</v>
       </c>
       <c r="D2517" t="s">
         <v>2519</v>
@@ -44552,7 +44552,7 @@
         <v>21</v>
       </c>
       <c r="C2518">
-        <v>3608.2</v>
+        <v>6208.5</v>
       </c>
       <c r="D2518" t="s">
         <v>2520</v>
@@ -44566,7 +44566,7 @@
         <v>22</v>
       </c>
       <c r="C2519">
-        <v>3722.7</v>
+        <v>6187.8</v>
       </c>
       <c r="D2519" t="s">
         <v>2521</v>
@@ -44580,7 +44580,7 @@
         <v>23</v>
       </c>
       <c r="C2520">
-        <v>3842</v>
+        <v>6289.1</v>
       </c>
       <c r="D2520" t="s">
         <v>2522</v>
@@ -44594,7 +44594,7 @@
         <v>24</v>
       </c>
       <c r="C2521">
-        <v>4100.8</v>
+        <v>6255.6</v>
       </c>
       <c r="D2521" t="s">
         <v>2523</v>
@@ -44608,7 +44608,7 @@
         <v>25</v>
       </c>
       <c r="C2522">
-        <v>4625.5</v>
+        <v>6624.3</v>
       </c>
       <c r="D2522" t="s">
         <v>2524</v>
@@ -44622,7 +44622,7 @@
         <v>26</v>
       </c>
       <c r="C2523">
-        <v>4855.4</v>
+        <v>6741.5</v>
       </c>
       <c r="D2523" t="s">
         <v>2525</v>
@@ -44636,7 +44636,7 @@
         <v>27</v>
       </c>
       <c r="C2524">
-        <v>5176</v>
+        <v>6810.4</v>
       </c>
       <c r="D2524" t="s">
         <v>2526</v>
@@ -44650,7 +44650,7 @@
         <v>28</v>
       </c>
       <c r="C2525">
-        <v>5486.6</v>
+        <v>7007.2</v>
       </c>
       <c r="D2525" t="s">
         <v>2527</v>
@@ -44664,7 +44664,7 @@
         <v>29</v>
       </c>
       <c r="C2526">
-        <v>5382.8</v>
+        <v>7608.8</v>
       </c>
       <c r="D2526" t="s">
         <v>2528</v>
@@ -44678,7 +44678,7 @@
         <v>30</v>
       </c>
       <c r="C2527">
-        <v>5952.5</v>
+        <v>7862.7</v>
       </c>
       <c r="D2527" t="s">
         <v>2529</v>
@@ -44692,7 +44692,7 @@
         <v>31</v>
       </c>
       <c r="C2528">
-        <v>6534</v>
+        <v>7951.1</v>
       </c>
       <c r="D2528" t="s">
         <v>2530</v>
@@ -44706,7 +44706,7 @@
         <v>32</v>
       </c>
       <c r="C2529">
-        <v>7158.9</v>
+        <v>8013.9</v>
       </c>
       <c r="D2529" t="s">
         <v>2531</v>
@@ -44720,7 +44720,7 @@
         <v>33</v>
       </c>
       <c r="C2530">
-        <v>7887.1</v>
+        <v>7967.2</v>
       </c>
       <c r="D2530" t="s">
         <v>2532</v>
@@ -44734,7 +44734,7 @@
         <v>34</v>
       </c>
       <c r="C2531">
-        <v>8061</v>
+        <v>7994.7</v>
       </c>
       <c r="D2531" t="s">
         <v>2533</v>
@@ -44748,7 +44748,7 @@
         <v>35</v>
       </c>
       <c r="C2532">
-        <v>8274.5</v>
+        <v>8011.6</v>
       </c>
       <c r="D2532" t="s">
         <v>2534</v>
@@ -44762,7 +44762,7 @@
         <v>36</v>
       </c>
       <c r="C2533">
-        <v>8432.9</v>
+        <v>8015.7</v>
       </c>
       <c r="D2533" t="s">
         <v>2535</v>
@@ -44776,7 +44776,7 @@
         <v>37</v>
       </c>
       <c r="C2534">
-        <v>8187.3</v>
+        <v>7900</v>
       </c>
       <c r="D2534" t="s">
         <v>2536</v>
@@ -44790,7 +44790,7 @@
         <v>38</v>
       </c>
       <c r="C2535">
-        <v>8324</v>
+        <v>7866.7</v>
       </c>
       <c r="D2535" t="s">
         <v>2537</v>
@@ -44804,7 +44804,7 @@
         <v>39</v>
       </c>
       <c r="C2536">
-        <v>8439.4</v>
+        <v>7803.1</v>
       </c>
       <c r="D2536" t="s">
         <v>2538</v>
@@ -44818,7 +44818,7 @@
         <v>40</v>
       </c>
       <c r="C2537">
-        <v>8329.200000000001</v>
+        <v>7738.2</v>
       </c>
       <c r="D2537" t="s">
         <v>2539</v>
@@ -44832,7 +44832,7 @@
         <v>41</v>
       </c>
       <c r="C2538">
-        <v>8196</v>
+        <v>7664.4</v>
       </c>
       <c r="D2538" t="s">
         <v>2540</v>
@@ -44846,7 +44846,7 @@
         <v>42</v>
       </c>
       <c r="C2539">
-        <v>8053</v>
+        <v>7592.9</v>
       </c>
       <c r="D2539" t="s">
         <v>2541</v>
@@ -44860,7 +44860,7 @@
         <v>43</v>
       </c>
       <c r="C2540">
-        <v>7912.4</v>
+        <v>7511.2</v>
       </c>
       <c r="D2540" t="s">
         <v>2542</v>
@@ -44874,7 +44874,7 @@
         <v>44</v>
       </c>
       <c r="C2541">
-        <v>7800.6</v>
+        <v>7443.8</v>
       </c>
       <c r="D2541" t="s">
         <v>2543</v>
@@ -44888,7 +44888,7 @@
         <v>45</v>
       </c>
       <c r="C2542">
-        <v>7714</v>
+        <v>7692.5</v>
       </c>
       <c r="D2542" t="s">
         <v>2544</v>
@@ -44902,7 +44902,7 @@
         <v>46</v>
       </c>
       <c r="C2543">
-        <v>7643.5</v>
+        <v>7492.9</v>
       </c>
       <c r="D2543" t="s">
         <v>2545</v>
@@ -44916,7 +44916,7 @@
         <v>47</v>
       </c>
       <c r="C2544">
-        <v>7584.1</v>
+        <v>7535.9</v>
       </c>
       <c r="D2544" t="s">
         <v>2546</v>
@@ -44930,7 +44930,7 @@
         <v>48</v>
       </c>
       <c r="C2545">
-        <v>7522</v>
+        <v>7324.3</v>
       </c>
       <c r="D2545" t="s">
         <v>2547</v>
@@ -44944,7 +44944,7 @@
         <v>49</v>
       </c>
       <c r="C2546">
-        <v>7541.6</v>
+        <v>7416.1</v>
       </c>
       <c r="D2546" t="s">
         <v>2548</v>
@@ -44958,7 +44958,7 @@
         <v>50</v>
       </c>
       <c r="C2547">
-        <v>7509.2</v>
+        <v>7376.9</v>
       </c>
       <c r="D2547" t="s">
         <v>2549</v>
@@ -44972,7 +44972,7 @@
         <v>51</v>
       </c>
       <c r="C2548">
-        <v>7484</v>
+        <v>7348.1</v>
       </c>
       <c r="D2548" t="s">
         <v>2550</v>
@@ -44986,7 +44986,7 @@
         <v>52</v>
       </c>
       <c r="C2549">
-        <v>7483.8</v>
+        <v>7145.2</v>
       </c>
       <c r="D2549" t="s">
         <v>2551</v>
@@ -45000,7 +45000,7 @@
         <v>53</v>
       </c>
       <c r="C2550">
-        <v>7798</v>
+        <v>6917.1</v>
       </c>
       <c r="D2550" t="s">
         <v>2552</v>
@@ -45014,7 +45014,7 @@
         <v>54</v>
       </c>
       <c r="C2551">
-        <v>7863.6</v>
+        <v>6749.3</v>
       </c>
       <c r="D2551" t="s">
         <v>2553</v>
@@ -45028,7 +45028,7 @@
         <v>55</v>
       </c>
       <c r="C2552">
-        <v>7959.5</v>
+        <v>6778.3</v>
       </c>
       <c r="D2552" t="s">
         <v>2554</v>
@@ -45042,7 +45042,7 @@
         <v>56</v>
       </c>
       <c r="C2553">
-        <v>8048.6</v>
+        <v>6740.5</v>
       </c>
       <c r="D2553" t="s">
         <v>2555</v>
@@ -45056,7 +45056,7 @@
         <v>57</v>
       </c>
       <c r="C2554">
-        <v>7956.3</v>
+        <v>6550.7</v>
       </c>
       <c r="D2554" t="s">
         <v>2556</v>
@@ -45070,7 +45070,7 @@
         <v>58</v>
       </c>
       <c r="C2555">
-        <v>8045.2</v>
+        <v>6520.8</v>
       </c>
       <c r="D2555" t="s">
         <v>2557</v>
@@ -45084,7 +45084,7 @@
         <v>59</v>
       </c>
       <c r="C2556">
-        <v>8122.3</v>
+        <v>6481.4</v>
       </c>
       <c r="D2556" t="s">
         <v>2558</v>
@@ -45098,7 +45098,7 @@
         <v>60</v>
       </c>
       <c r="C2557">
-        <v>8175.7</v>
+        <v>6436.7</v>
       </c>
       <c r="D2557" t="s">
         <v>2559</v>
@@ -45112,7 +45112,7 @@
         <v>61</v>
       </c>
       <c r="C2558">
-        <v>7275.7</v>
+        <v>6710.2</v>
       </c>
       <c r="D2558" t="s">
         <v>2560</v>
@@ -45126,7 +45126,7 @@
         <v>62</v>
       </c>
       <c r="C2559">
-        <v>7312.9</v>
+        <v>6759.1</v>
       </c>
       <c r="D2559" t="s">
         <v>2561</v>
@@ -45140,7 +45140,7 @@
         <v>63</v>
       </c>
       <c r="C2560">
-        <v>7351.1</v>
+        <v>6832.9</v>
       </c>
       <c r="D2560" t="s">
         <v>2562</v>
@@ -45154,7 +45154,7 @@
         <v>64</v>
       </c>
       <c r="C2561">
-        <v>7400.8</v>
+        <v>7164.1</v>
       </c>
       <c r="D2561" t="s">
         <v>2563</v>
@@ -45168,7 +45168,7 @@
         <v>65</v>
       </c>
       <c r="C2562">
-        <v>7812.1</v>
+        <v>6803.7</v>
       </c>
       <c r="D2562" t="s">
         <v>2564</v>
@@ -45182,7 +45182,7 @@
         <v>66</v>
       </c>
       <c r="C2563">
-        <v>7906</v>
+        <v>6801.6</v>
       </c>
       <c r="D2563" t="s">
         <v>2565</v>
@@ -45196,7 +45196,7 @@
         <v>67</v>
       </c>
       <c r="C2564">
-        <v>7944.2</v>
+        <v>6758.6</v>
       </c>
       <c r="D2564" t="s">
         <v>2566</v>
@@ -45210,7 +45210,7 @@
         <v>68</v>
       </c>
       <c r="C2565">
-        <v>7948.3</v>
+        <v>6829.8</v>
       </c>
       <c r="D2565" t="s">
         <v>2567</v>
@@ -45224,7 +45224,7 @@
         <v>69</v>
       </c>
       <c r="C2566">
-        <v>8015.8</v>
+        <v>6166.2</v>
       </c>
       <c r="D2566" t="s">
         <v>2568</v>
@@ -45238,7 +45238,7 @@
         <v>70</v>
       </c>
       <c r="C2567">
-        <v>7952.8</v>
+        <v>6444.5</v>
       </c>
       <c r="D2567" t="s">
         <v>2569</v>
@@ -45252,7 +45252,7 @@
         <v>71</v>
       </c>
       <c r="C2568">
-        <v>8111.1</v>
+        <v>6637.6</v>
       </c>
       <c r="D2568" t="s">
         <v>2570</v>
@@ -45266,7 +45266,7 @@
         <v>72</v>
       </c>
       <c r="C2569">
-        <v>8241.200000000001</v>
+        <v>7124.9</v>
       </c>
       <c r="D2569" t="s">
         <v>2571</v>
@@ -45280,7 +45280,7 @@
         <v>73</v>
       </c>
       <c r="C2570">
-        <v>7976.1</v>
+        <v>7840.7</v>
       </c>
       <c r="D2570" t="s">
         <v>2572</v>
@@ -45294,7 +45294,7 @@
         <v>74</v>
       </c>
       <c r="C2571">
-        <v>7948.5</v>
+        <v>8170</v>
       </c>
       <c r="D2571" t="s">
         <v>2573</v>
@@ -45308,7 +45308,7 @@
         <v>75</v>
       </c>
       <c r="C2572">
-        <v>8111.9</v>
+        <v>8270.299999999999</v>
       </c>
       <c r="D2572" t="s">
         <v>2574</v>
@@ -45322,7 +45322,7 @@
         <v>76</v>
       </c>
       <c r="C2573">
-        <v>8378.299999999999</v>
+        <v>8359.9</v>
       </c>
       <c r="D2573" t="s">
         <v>2575</v>
@@ -45336,7 +45336,7 @@
         <v>77</v>
       </c>
       <c r="C2574">
-        <v>8442.6</v>
+        <v>8513.799999999999</v>
       </c>
       <c r="D2574" t="s">
         <v>2576</v>
@@ -45350,7 +45350,7 @@
         <v>78</v>
       </c>
       <c r="C2575">
-        <v>8511.700000000001</v>
+        <v>8601.299999999999</v>
       </c>
       <c r="D2575" t="s">
         <v>2577</v>
@@ -45364,7 +45364,7 @@
         <v>79</v>
       </c>
       <c r="C2576">
-        <v>8542.4</v>
+        <v>8646.9</v>
       </c>
       <c r="D2576" t="s">
         <v>2578</v>
@@ -45378,7 +45378,7 @@
         <v>80</v>
       </c>
       <c r="C2577">
-        <v>8545.299999999999</v>
+        <v>8681.4</v>
       </c>
       <c r="D2577" t="s">
         <v>2579</v>
@@ -45392,7 +45392,7 @@
         <v>81</v>
       </c>
       <c r="C2578">
-        <v>8604.700000000001</v>
+        <v>8623.4</v>
       </c>
       <c r="D2578" t="s">
         <v>2580</v>
@@ -45406,7 +45406,7 @@
         <v>82</v>
       </c>
       <c r="C2579">
-        <v>8556.700000000001</v>
+        <v>8600.5</v>
       </c>
       <c r="D2579" t="s">
         <v>2581</v>
@@ -45420,7 +45420,7 @@
         <v>83</v>
       </c>
       <c r="C2580">
-        <v>8501.1</v>
+        <v>8537.9</v>
       </c>
       <c r="D2580" t="s">
         <v>2582</v>
@@ -45434,7 +45434,7 @@
         <v>84</v>
       </c>
       <c r="C2581">
-        <v>8409.299999999999</v>
+        <v>8448.299999999999</v>
       </c>
       <c r="D2581" t="s">
         <v>2583</v>
@@ -45448,7 +45448,7 @@
         <v>85</v>
       </c>
       <c r="C2582">
-        <v>8126.9</v>
+        <v>8150.1</v>
       </c>
       <c r="D2582" t="s">
         <v>2584</v>
@@ -45462,7 +45462,7 @@
         <v>86</v>
       </c>
       <c r="C2583">
-        <v>8022.8</v>
+        <v>8042.2</v>
       </c>
       <c r="D2583" t="s">
         <v>2585</v>
@@ -45476,7 +45476,7 @@
         <v>87</v>
       </c>
       <c r="C2584">
-        <v>7921</v>
+        <v>7932.9</v>
       </c>
       <c r="D2584" t="s">
         <v>2586</v>
@@ -45490,7 +45490,7 @@
         <v>88</v>
       </c>
       <c r="C2585">
-        <v>7779.2</v>
+        <v>7443.9</v>
       </c>
       <c r="D2585" t="s">
         <v>2587</v>
@@ -45504,7 +45504,7 @@
         <v>89</v>
       </c>
       <c r="C2586">
-        <v>7636.3</v>
+        <v>7551.7</v>
       </c>
       <c r="D2586" t="s">
         <v>2588</v>
@@ -45518,7 +45518,7 @@
         <v>90</v>
       </c>
       <c r="C2587">
-        <v>7277.5</v>
+        <v>7339.4</v>
       </c>
       <c r="D2587" t="s">
         <v>2589</v>
@@ -45532,7 +45532,7 @@
         <v>91</v>
       </c>
       <c r="C2588">
-        <v>6950.8</v>
+        <v>7045.4</v>
       </c>
       <c r="D2588" t="s">
         <v>2590</v>
@@ -45546,7 +45546,7 @@
         <v>92</v>
       </c>
       <c r="C2589">
-        <v>6599.9</v>
+        <v>6199.9</v>
       </c>
       <c r="D2589" t="s">
         <v>2591</v>
@@ -45560,7 +45560,7 @@
         <v>93</v>
       </c>
       <c r="C2590">
-        <v>6953.5</v>
+        <v>6419.1</v>
       </c>
       <c r="D2590" t="s">
         <v>2592</v>
@@ -45574,7 +45574,7 @@
         <v>94</v>
       </c>
       <c r="C2591">
-        <v>7050.7</v>
+        <v>6196.4</v>
       </c>
       <c r="D2591" t="s">
         <v>2593</v>
@@ -45588,7 +45588,7 @@
         <v>95</v>
       </c>
       <c r="C2592">
-        <v>7041.4</v>
+        <v>6142.5</v>
       </c>
       <c r="D2592" t="s">
         <v>2594</v>
@@ -45602,7 +45602,7 @@
         <v>96</v>
       </c>
       <c r="C2593">
-        <v>7108.7</v>
+        <v>5856.8</v>
       </c>
       <c r="D2593" t="s">
         <v>2595</v>
@@ -45616,7 +45616,7 @@
         <v>1</v>
       </c>
       <c r="C2594">
-        <v>5285.1</v>
+        <v>6969.2</v>
       </c>
       <c r="D2594" t="s">
         <v>2596</v>
@@ -45630,7 +45630,7 @@
         <v>2</v>
       </c>
       <c r="C2595">
-        <v>5268.4</v>
+        <v>6574.1</v>
       </c>
       <c r="D2595" t="s">
         <v>2597</v>
@@ -45644,7 +45644,7 @@
         <v>3</v>
       </c>
       <c r="C2596">
-        <v>5246.3</v>
+        <v>6862.9</v>
       </c>
       <c r="D2596" t="s">
         <v>2598</v>
@@ -45658,7 +45658,7 @@
         <v>4</v>
       </c>
       <c r="C2597">
-        <v>5222.1</v>
+        <v>6349.3</v>
       </c>
       <c r="D2597" t="s">
         <v>2599</v>
@@ -45672,7 +45672,7 @@
         <v>5</v>
       </c>
       <c r="C2598">
-        <v>5106</v>
+        <v>6908.1</v>
       </c>
       <c r="D2598" t="s">
         <v>2600</v>
@@ -45686,7 +45686,7 @@
         <v>6</v>
       </c>
       <c r="C2599">
-        <v>5068.2</v>
+        <v>6532.7</v>
       </c>
       <c r="D2599" t="s">
         <v>2601</v>
@@ -45700,7 +45700,7 @@
         <v>7</v>
       </c>
       <c r="C2600">
-        <v>5068.6</v>
+        <v>6049.5</v>
       </c>
       <c r="D2600" t="s">
         <v>2602</v>
@@ -45714,7 +45714,7 @@
         <v>8</v>
       </c>
       <c r="C2601">
-        <v>5066.8</v>
+        <v>5949.4</v>
       </c>
       <c r="D2601" t="s">
         <v>2603</v>
@@ -45728,7 +45728,7 @@
         <v>9</v>
       </c>
       <c r="C2602">
-        <v>5015.8</v>
+        <v>6049.2</v>
       </c>
       <c r="D2602" t="s">
         <v>2604</v>
@@ -45742,7 +45742,7 @@
         <v>10</v>
       </c>
       <c r="C2603">
-        <v>5017.8</v>
+        <v>6086.6</v>
       </c>
       <c r="D2603" t="s">
         <v>2605</v>
@@ -45756,7 +45756,7 @@
         <v>11</v>
       </c>
       <c r="C2604">
-        <v>5008.7</v>
+        <v>5837.1</v>
       </c>
       <c r="D2604" t="s">
         <v>2606</v>
@@ -45770,7 +45770,7 @@
         <v>12</v>
       </c>
       <c r="C2605">
-        <v>4979.3</v>
+        <v>5902</v>
       </c>
       <c r="D2605" t="s">
         <v>2607</v>
@@ -45784,7 +45784,7 @@
         <v>13</v>
       </c>
       <c r="C2606">
-        <v>4987.9</v>
+        <v>6298</v>
       </c>
       <c r="D2606" t="s">
         <v>2608</v>
@@ -45798,7 +45798,7 @@
         <v>14</v>
       </c>
       <c r="C2607">
-        <v>4962.1</v>
+        <v>6149.2</v>
       </c>
       <c r="D2607" t="s">
         <v>2609</v>
@@ -45812,7 +45812,7 @@
         <v>15</v>
       </c>
       <c r="C2608">
-        <v>4959.7</v>
+        <v>6286.7</v>
       </c>
       <c r="D2608" t="s">
         <v>2610</v>
@@ -45826,7 +45826,7 @@
         <v>16</v>
       </c>
       <c r="C2609">
-        <v>4967.9</v>
+        <v>6308.1</v>
       </c>
       <c r="D2609" t="s">
         <v>2611</v>
@@ -45840,7 +45840,7 @@
         <v>17</v>
       </c>
       <c r="C2610">
-        <v>4916.4</v>
+        <v>6181.6</v>
       </c>
       <c r="D2610" t="s">
         <v>2612</v>
@@ -45854,7 +45854,7 @@
         <v>18</v>
       </c>
       <c r="C2611">
-        <v>4934.7</v>
+        <v>5832.9</v>
       </c>
       <c r="D2611" t="s">
         <v>2613</v>
@@ -45868,7 +45868,7 @@
         <v>19</v>
       </c>
       <c r="C2612">
-        <v>4933.4</v>
+        <v>5918.9</v>
       </c>
       <c r="D2612" t="s">
         <v>2614</v>
@@ -45882,7 +45882,7 @@
         <v>20</v>
       </c>
       <c r="C2613">
-        <v>4926.9</v>
+        <v>5995.4</v>
       </c>
       <c r="D2613" t="s">
         <v>2615</v>
@@ -45896,7 +45896,7 @@
         <v>21</v>
       </c>
       <c r="C2614">
-        <v>4910.4</v>
+        <v>6168.5</v>
       </c>
       <c r="D2614" t="s">
         <v>2616</v>
@@ -45910,7 +45910,7 @@
         <v>22</v>
       </c>
       <c r="C2615">
-        <v>4890.9</v>
+        <v>6097.8</v>
       </c>
       <c r="D2615" t="s">
         <v>2617</v>
@@ -45924,7 +45924,7 @@
         <v>23</v>
       </c>
       <c r="C2616">
-        <v>4838.7</v>
+        <v>6119.1</v>
       </c>
       <c r="D2616" t="s">
         <v>2618</v>
@@ -45938,7 +45938,7 @@
         <v>24</v>
       </c>
       <c r="C2617">
-        <v>4745.1</v>
+        <v>5985.6</v>
       </c>
       <c r="D2617" t="s">
         <v>2619</v>
@@ -45952,7 +45952,7 @@
         <v>25</v>
       </c>
       <c r="C2618">
-        <v>4518.1</v>
+        <v>6234.3</v>
       </c>
       <c r="D2618" t="s">
         <v>2620</v>
@@ -45966,7 +45966,7 @@
         <v>26</v>
       </c>
       <c r="C2619">
-        <v>4431.4</v>
+        <v>6241.5</v>
       </c>
       <c r="D2619" t="s">
         <v>2621</v>
@@ -45980,7 +45980,7 @@
         <v>27</v>
       </c>
       <c r="C2620">
-        <v>4387.6</v>
+        <v>6230.4</v>
       </c>
       <c r="D2620" t="s">
         <v>2622</v>
@@ -45994,7 +45994,7 @@
         <v>28</v>
       </c>
       <c r="C2621">
-        <v>4330.6</v>
+        <v>6357.2</v>
       </c>
       <c r="D2621" t="s">
         <v>2623</v>
@@ -46008,7 +46008,7 @@
         <v>29</v>
       </c>
       <c r="C2622">
-        <v>4464.8</v>
+        <v>6918.8</v>
       </c>
       <c r="D2622" t="s">
         <v>2624</v>
@@ -46022,7 +46022,7 @@
         <v>30</v>
       </c>
       <c r="C2623">
-        <v>4490.8</v>
+        <v>7152.7</v>
       </c>
       <c r="D2623" t="s">
         <v>2625</v>
@@ -46036,7 +46036,7 @@
         <v>31</v>
       </c>
       <c r="C2624">
-        <v>4584.6</v>
+        <v>7231.1</v>
       </c>
       <c r="D2624" t="s">
         <v>2626</v>
@@ -46050,7 +46050,7 @@
         <v>32</v>
       </c>
       <c r="C2625">
-        <v>4681.8</v>
+        <v>7323.9</v>
       </c>
       <c r="D2625" t="s">
         <v>2627</v>
@@ -46064,7 +46064,7 @@
         <v>33</v>
       </c>
       <c r="C2626">
-        <v>4918.8</v>
+        <v>7317.2</v>
       </c>
       <c r="D2626" t="s">
         <v>2628</v>
@@ -46078,7 +46078,7 @@
         <v>34</v>
       </c>
       <c r="C2627">
-        <v>5044.2</v>
+        <v>7404.7</v>
       </c>
       <c r="D2627" t="s">
         <v>2629</v>
@@ -46092,7 +46092,7 @@
         <v>35</v>
       </c>
       <c r="C2628">
-        <v>5263.2</v>
+        <v>7481.6</v>
       </c>
       <c r="D2628" t="s">
         <v>2630</v>
@@ -46106,7 +46106,7 @@
         <v>36</v>
       </c>
       <c r="C2629">
-        <v>5465.1</v>
+        <v>7545.7</v>
       </c>
       <c r="D2629" t="s">
         <v>2631</v>
@@ -46120,7 +46120,7 @@
         <v>37</v>
       </c>
       <c r="C2630">
-        <v>5761.6</v>
+        <v>7510</v>
       </c>
       <c r="D2630" t="s">
         <v>2632</v>
@@ -46134,7 +46134,7 @@
         <v>38</v>
       </c>
       <c r="C2631">
-        <v>5912.6</v>
+        <v>7536.7</v>
       </c>
       <c r="D2631" t="s">
         <v>2633</v>
@@ -46148,7 +46148,7 @@
         <v>39</v>
       </c>
       <c r="C2632">
-        <v>6076.2</v>
+        <v>7543.1</v>
       </c>
       <c r="D2632" t="s">
         <v>2634</v>
@@ -46162,7 +46162,7 @@
         <v>40</v>
       </c>
       <c r="C2633">
-        <v>6263</v>
+        <v>7558.2</v>
       </c>
       <c r="D2633" t="s">
         <v>2635</v>
@@ -46176,7 +46176,7 @@
         <v>41</v>
       </c>
       <c r="C2634">
-        <v>5834.3</v>
+        <v>7564.4</v>
       </c>
       <c r="D2634" t="s">
         <v>2636</v>
@@ -46190,7 +46190,7 @@
         <v>42</v>
       </c>
       <c r="C2635">
-        <v>5937.6</v>
+        <v>7572.9</v>
       </c>
       <c r="D2635" t="s">
         <v>2637</v>
@@ -46204,7 +46204,7 @@
         <v>43</v>
       </c>
       <c r="C2636">
-        <v>6023.4</v>
+        <v>7571.2</v>
       </c>
       <c r="D2636" t="s">
         <v>2638</v>
@@ -46218,7 +46218,7 @@
         <v>44</v>
       </c>
       <c r="C2637">
-        <v>6083.2</v>
+        <v>7563.8</v>
       </c>
       <c r="D2637" t="s">
         <v>2639</v>
@@ -46232,7 +46232,7 @@
         <v>45</v>
       </c>
       <c r="C2638">
-        <v>6211.4</v>
+        <v>7842.5</v>
       </c>
       <c r="D2638" t="s">
         <v>2640</v>
@@ -46246,7 +46246,7 @@
         <v>46</v>
       </c>
       <c r="C2639">
-        <v>6244.7</v>
+        <v>7672.9</v>
       </c>
       <c r="D2639" t="s">
         <v>2641</v>
@@ -46260,7 +46260,7 @@
         <v>47</v>
       </c>
       <c r="C2640">
-        <v>6245.2</v>
+        <v>7735.9</v>
       </c>
       <c r="D2640" t="s">
         <v>2642</v>
@@ -46274,7 +46274,7 @@
         <v>48</v>
       </c>
       <c r="C2641">
-        <v>6244.6</v>
+        <v>7544.3</v>
       </c>
       <c r="D2641" t="s">
         <v>2643</v>
@@ -46288,7 +46288,7 @@
         <v>49</v>
       </c>
       <c r="C2642">
-        <v>6325.8</v>
+        <v>7646.1</v>
       </c>
       <c r="D2642" t="s">
         <v>2644</v>
@@ -46302,7 +46302,7 @@
         <v>50</v>
       </c>
       <c r="C2643">
-        <v>6306.9</v>
+        <v>7606.9</v>
       </c>
       <c r="D2643" t="s">
         <v>2645</v>
@@ -46316,7 +46316,7 @@
         <v>51</v>
       </c>
       <c r="C2644">
-        <v>6257.4</v>
+        <v>7558.1</v>
       </c>
       <c r="D2644" t="s">
         <v>2646</v>
@@ -46330,7 +46330,7 @@
         <v>52</v>
       </c>
       <c r="C2645">
-        <v>6216.2</v>
+        <v>7335.2</v>
       </c>
       <c r="D2645" t="s">
         <v>2647</v>
@@ -46344,7 +46344,7 @@
         <v>53</v>
       </c>
       <c r="C2646">
-        <v>6008.1</v>
+        <v>7077.1</v>
       </c>
       <c r="D2646" t="s">
         <v>2648</v>
@@ -46358,7 +46358,7 @@
         <v>54</v>
       </c>
       <c r="C2647">
-        <v>5965.8</v>
+        <v>6869.3</v>
       </c>
       <c r="D2647" t="s">
         <v>2649</v>
@@ -46372,7 +46372,7 @@
         <v>55</v>
       </c>
       <c r="C2648">
-        <v>5946.4</v>
+        <v>6858.3</v>
       </c>
       <c r="D2648" t="s">
         <v>2650</v>
@@ -46386,7 +46386,7 @@
         <v>56</v>
       </c>
       <c r="C2649">
-        <v>5914.2</v>
+        <v>6780.5</v>
       </c>
       <c r="D2649" t="s">
         <v>2651</v>
@@ -46400,7 +46400,7 @@
         <v>57</v>
       </c>
       <c r="C2650">
-        <v>5970.8</v>
+        <v>6540.7</v>
       </c>
       <c r="D2650" t="s">
         <v>2652</v>
@@ -46414,7 +46414,7 @@
         <v>58</v>
       </c>
       <c r="C2651">
-        <v>5926.4</v>
+        <v>6460.8</v>
       </c>
       <c r="D2651" t="s">
         <v>2653</v>
@@ -46428,7 +46428,7 @@
         <v>59</v>
       </c>
       <c r="C2652">
-        <v>5890.8</v>
+        <v>6381.4</v>
       </c>
       <c r="D2652" t="s">
         <v>2654</v>
@@ -46442,7 +46442,7 @@
         <v>60</v>
       </c>
       <c r="C2653">
-        <v>5848.1</v>
+        <v>6286.7</v>
       </c>
       <c r="D2653" t="s">
         <v>2655</v>
@@ -46456,7 +46456,7 @@
         <v>61</v>
       </c>
       <c r="C2654">
-        <v>6118.4</v>
+        <v>6520.2</v>
       </c>
       <c r="D2654" t="s">
         <v>2656</v>
@@ -46470,7 +46470,7 @@
         <v>62</v>
       </c>
       <c r="C2655">
-        <v>6046.2</v>
+        <v>6539.1</v>
       </c>
       <c r="D2655" t="s">
         <v>2657</v>
@@ -46484,7 +46484,7 @@
         <v>63</v>
       </c>
       <c r="C2656">
-        <v>5998.1</v>
+        <v>6582.9</v>
       </c>
       <c r="D2656" t="s">
         <v>2658</v>
@@ -46498,7 +46498,7 @@
         <v>64</v>
       </c>
       <c r="C2657">
-        <v>5971.4</v>
+        <v>6894.1</v>
       </c>
       <c r="D2657" t="s">
         <v>2659</v>
@@ -46512,7 +46512,7 @@
         <v>65</v>
       </c>
       <c r="C2658">
-        <v>5966.1</v>
+        <v>6533.7</v>
       </c>
       <c r="D2658" t="s">
         <v>2660</v>
@@ -46526,7 +46526,7 @@
         <v>66</v>
       </c>
       <c r="C2659">
-        <v>5914.9</v>
+        <v>6511.6</v>
       </c>
       <c r="D2659" t="s">
         <v>2661</v>
@@ -46540,7 +46540,7 @@
         <v>67</v>
       </c>
       <c r="C2660">
-        <v>5852</v>
+        <v>6468.6</v>
       </c>
       <c r="D2660" t="s">
         <v>2662</v>
@@ -46554,7 +46554,7 @@
         <v>68</v>
       </c>
       <c r="C2661">
-        <v>5827.1</v>
+        <v>6529.8</v>
       </c>
       <c r="D2661" t="s">
         <v>2663</v>
@@ -46568,7 +46568,7 @@
         <v>69</v>
       </c>
       <c r="C2662">
-        <v>5716.4</v>
+        <v>5876.2</v>
       </c>
       <c r="D2662" t="s">
         <v>2664</v>
@@ -46582,7 +46582,7 @@
         <v>70</v>
       </c>
       <c r="C2663">
-        <v>5630.2</v>
+        <v>6144.5</v>
       </c>
       <c r="D2663" t="s">
         <v>2665</v>
@@ -46596,7 +46596,7 @@
         <v>71</v>
       </c>
       <c r="C2664">
-        <v>5557.9</v>
+        <v>6347.6</v>
       </c>
       <c r="D2664" t="s">
         <v>2666</v>
@@ -46610,7 +46610,7 @@
         <v>72</v>
       </c>
       <c r="C2665">
-        <v>5524.4</v>
+        <v>6824.9</v>
       </c>
       <c r="D2665" t="s">
         <v>2667</v>
@@ -46624,7 +46624,7 @@
         <v>73</v>
       </c>
       <c r="C2666">
-        <v>5603</v>
+        <v>7530.7</v>
       </c>
       <c r="D2666" t="s">
         <v>2668</v>
@@ -46638,7 +46638,7 @@
         <v>74</v>
       </c>
       <c r="C2667">
-        <v>5580.2</v>
+        <v>7830</v>
       </c>
       <c r="D2667" t="s">
         <v>2669</v>
@@ -46652,7 +46652,7 @@
         <v>75</v>
       </c>
       <c r="C2668">
-        <v>5571.8</v>
+        <v>7900.3</v>
       </c>
       <c r="D2668" t="s">
         <v>2670</v>
@@ -46666,7 +46666,7 @@
         <v>76</v>
       </c>
       <c r="C2669">
-        <v>5631.1</v>
+        <v>7919.9</v>
       </c>
       <c r="D2669" t="s">
         <v>2671</v>
@@ -46680,7 +46680,7 @@
         <v>77</v>
       </c>
       <c r="C2670">
-        <v>5851.7</v>
+        <v>8073.8</v>
       </c>
       <c r="D2670" t="s">
         <v>2672</v>
@@ -46694,7 +46694,7 @@
         <v>78</v>
       </c>
       <c r="C2671">
-        <v>5953.6</v>
+        <v>8121.3</v>
       </c>
       <c r="D2671" t="s">
         <v>2673</v>
@@ -46708,7 +46708,7 @@
         <v>79</v>
       </c>
       <c r="C2672">
-        <v>5980.8</v>
+        <v>8146.9</v>
       </c>
       <c r="D2672" t="s">
         <v>2674</v>
@@ -46722,7 +46722,7 @@
         <v>80</v>
       </c>
       <c r="C2673">
-        <v>6014.8</v>
+        <v>8191.4</v>
       </c>
       <c r="D2673" t="s">
         <v>2675</v>
@@ -46736,7 +46736,7 @@
         <v>81</v>
       </c>
       <c r="C2674">
-        <v>6030.1</v>
+        <v>8163.4</v>
       </c>
       <c r="D2674" t="s">
         <v>2676</v>
@@ -46750,7 +46750,7 @@
         <v>82</v>
       </c>
       <c r="C2675">
-        <v>5999.8</v>
+        <v>8150.5</v>
       </c>
       <c r="D2675" t="s">
         <v>2677</v>
@@ -46764,7 +46764,7 @@
         <v>83</v>
       </c>
       <c r="C2676">
-        <v>5995</v>
+        <v>8137.9</v>
       </c>
       <c r="D2676" t="s">
         <v>2678</v>
@@ -46778,7 +46778,7 @@
         <v>84</v>
       </c>
       <c r="C2677">
-        <v>5988.8</v>
+        <v>8108.3</v>
       </c>
       <c r="D2677" t="s">
         <v>2679</v>
@@ -46792,7 +46792,7 @@
         <v>85</v>
       </c>
       <c r="C2678">
-        <v>5911.7</v>
+        <v>7810.1</v>
       </c>
       <c r="D2678" t="s">
         <v>2680</v>
@@ -46806,7 +46806,7 @@
         <v>86</v>
       </c>
       <c r="C2679">
-        <v>5883.8</v>
+        <v>7712.2</v>
       </c>
       <c r="D2679" t="s">
         <v>2681</v>
@@ -46820,7 +46820,7 @@
         <v>87</v>
       </c>
       <c r="C2680">
-        <v>5853</v>
+        <v>7612.9</v>
       </c>
       <c r="D2680" t="s">
         <v>2682</v>
@@ -46834,7 +46834,7 @@
         <v>88</v>
       </c>
       <c r="C2681">
-        <v>5797.7</v>
+        <v>7113.9</v>
       </c>
       <c r="D2681" t="s">
         <v>2683</v>
@@ -46848,7 +46848,7 @@
         <v>89</v>
       </c>
       <c r="C2682">
-        <v>5893.8</v>
+        <v>7231.7</v>
       </c>
       <c r="D2682" t="s">
         <v>2684</v>
@@ -46862,7 +46862,7 @@
         <v>90</v>
       </c>
       <c r="C2683">
-        <v>5837.2</v>
+        <v>7039.4</v>
       </c>
       <c r="D2683" t="s">
         <v>2685</v>
@@ -46876,7 +46876,7 @@
         <v>91</v>
       </c>
       <c r="C2684">
-        <v>5784.2</v>
+        <v>6765.4</v>
       </c>
       <c r="D2684" t="s">
         <v>2686</v>
@@ -46890,7 +46890,7 @@
         <v>92</v>
       </c>
       <c r="C2685">
-        <v>5767.9</v>
+        <v>5959.9</v>
       </c>
       <c r="D2685" t="s">
         <v>2687</v>
@@ -46904,7 +46904,7 @@
         <v>93</v>
       </c>
       <c r="C2686">
-        <v>5630.6</v>
+        <v>6189.1</v>
       </c>
       <c r="D2686" t="s">
         <v>2688</v>
@@ -46918,7 +46918,7 @@
         <v>94</v>
       </c>
       <c r="C2687">
-        <v>5607.6</v>
+        <v>5986.4</v>
       </c>
       <c r="D2687" t="s">
         <v>2689</v>
@@ -46932,7 +46932,7 @@
         <v>95</v>
       </c>
       <c r="C2688">
-        <v>5612.5</v>
+        <v>5972.5</v>
       </c>
       <c r="D2688" t="s">
         <v>2690</v>
@@ -46946,7 +46946,7 @@
         <v>96</v>
       </c>
       <c r="C2689">
-        <v>5594.2</v>
+        <v>5686.8</v>
       </c>
       <c r="D2689" t="s">
         <v>2691</v>
@@ -46960,7 +46960,7 @@
         <v>1</v>
       </c>
       <c r="C2690">
-        <v>4985.1</v>
+        <v>5750.6</v>
       </c>
       <c r="D2690" t="s">
         <v>2692</v>
@@ -46974,7 +46974,7 @@
         <v>2</v>
       </c>
       <c r="C2691">
-        <v>4978.4</v>
+        <v>5734.9</v>
       </c>
       <c r="D2691" t="s">
         <v>2693</v>
@@ -46988,7 +46988,7 @@
         <v>3</v>
       </c>
       <c r="C2692">
-        <v>4956.3</v>
+        <v>5745.2</v>
       </c>
       <c r="D2692" t="s">
         <v>2694</v>
@@ -47002,7 +47002,7 @@
         <v>4</v>
       </c>
       <c r="C2693">
-        <v>4922.1</v>
+        <v>5883.3</v>
       </c>
       <c r="D2693" t="s">
         <v>2695</v>
@@ -47016,7 +47016,7 @@
         <v>5</v>
       </c>
       <c r="C2694">
-        <v>4796</v>
+        <v>6354.7</v>
       </c>
       <c r="D2694" t="s">
         <v>2696</v>
@@ -47030,7 +47030,7 @@
         <v>6</v>
       </c>
       <c r="C2695">
-        <v>4738.2</v>
+        <v>6033.6</v>
       </c>
       <c r="D2695" t="s">
         <v>2697</v>
@@ -47044,7 +47044,7 @@
         <v>7</v>
       </c>
       <c r="C2696">
-        <v>4728.6</v>
+        <v>5947.6</v>
       </c>
       <c r="D2696" t="s">
         <v>2698</v>
@@ -47058,7 +47058,7 @@
         <v>8</v>
       </c>
       <c r="C2697">
-        <v>4726.8</v>
+        <v>5682</v>
       </c>
       <c r="D2697" t="s">
         <v>2699</v>
@@ -47072,7 +47072,7 @@
         <v>9</v>
       </c>
       <c r="C2698">
-        <v>4675.8</v>
+        <v>5775.7</v>
       </c>
       <c r="D2698" t="s">
         <v>2700</v>
@@ -47086,7 +47086,7 @@
         <v>10</v>
       </c>
       <c r="C2699">
-        <v>4677.8</v>
+        <v>5666.4</v>
       </c>
       <c r="D2699" t="s">
         <v>2701</v>
@@ -47100,7 +47100,7 @@
         <v>11</v>
       </c>
       <c r="C2700">
-        <v>4668.7</v>
+        <v>5441.4</v>
       </c>
       <c r="D2700" t="s">
         <v>2702</v>
@@ -47114,7 +47114,7 @@
         <v>12</v>
       </c>
       <c r="C2701">
-        <v>4639.3</v>
+        <v>5024.9</v>
       </c>
       <c r="D2701" t="s">
         <v>2703</v>
@@ -47128,7 +47128,7 @@
         <v>17</v>
       </c>
       <c r="C2702">
-        <v>4596.4</v>
+        <v>4799.1</v>
       </c>
       <c r="D2702" t="s">
         <v>2704</v>
@@ -47142,7 +47142,7 @@
         <v>18</v>
       </c>
       <c r="C2703">
-        <v>4594.7</v>
+        <v>4755.7</v>
       </c>
       <c r="D2703" t="s">
         <v>2705</v>
@@ -47156,7 +47156,7 @@
         <v>19</v>
       </c>
       <c r="C2704">
-        <v>4563.4</v>
+        <v>4660.2</v>
       </c>
       <c r="D2704" t="s">
         <v>2706</v>
@@ -47170,7 +47170,7 @@
         <v>20</v>
       </c>
       <c r="C2705">
-        <v>4526.9</v>
+        <v>4607.4</v>
       </c>
       <c r="D2705" t="s">
         <v>2707</v>
@@ -47184,7 +47184,7 @@
         <v>21</v>
       </c>
       <c r="C2706">
-        <v>4490.4</v>
+        <v>4681.7</v>
       </c>
       <c r="D2706" t="s">
         <v>2708</v>
@@ -47198,7 +47198,7 @@
         <v>22</v>
       </c>
       <c r="C2707">
-        <v>4460.9</v>
+        <v>4667.6</v>
       </c>
       <c r="D2707" t="s">
         <v>2709</v>
@@ -47212,7 +47212,7 @@
         <v>23</v>
       </c>
       <c r="C2708">
-        <v>4428.7</v>
+        <v>4587.5</v>
       </c>
       <c r="D2708" t="s">
         <v>2710</v>
@@ -47226,7 +47226,7 @@
         <v>24</v>
       </c>
       <c r="C2709">
-        <v>4365.1</v>
+        <v>4541.4</v>
       </c>
       <c r="D2709" t="s">
         <v>2711</v>
@@ -47240,7 +47240,7 @@
         <v>25</v>
       </c>
       <c r="C2710">
-        <v>4178.1</v>
+        <v>5323</v>
       </c>
       <c r="D2710" t="s">
         <v>2712</v>
@@ -47254,7 +47254,7 @@
         <v>26</v>
       </c>
       <c r="C2711">
-        <v>4101.4</v>
+        <v>5488.5</v>
       </c>
       <c r="D2711" t="s">
         <v>2713</v>
@@ -47268,7 +47268,7 @@
         <v>27</v>
       </c>
       <c r="C2712">
-        <v>4037.6</v>
+        <v>5572.1</v>
       </c>
       <c r="D2712" t="s">
         <v>2714</v>
@@ -47282,7 +47282,7 @@
         <v>28</v>
       </c>
       <c r="C2713">
-        <v>3920.6</v>
+        <v>5864</v>
       </c>
       <c r="D2713" t="s">
         <v>2715</v>
@@ -47296,7 +47296,7 @@
         <v>29</v>
       </c>
       <c r="C2714">
-        <v>3974.8</v>
+        <v>6132.6</v>
       </c>
       <c r="D2714" t="s">
         <v>2716</v>
@@ -47310,7 +47310,7 @@
         <v>30</v>
       </c>
       <c r="C2715">
-        <v>3950.8</v>
+        <v>6297.4</v>
       </c>
       <c r="D2715" t="s">
         <v>2717</v>
@@ -47324,7 +47324,7 @@
         <v>31</v>
       </c>
       <c r="C2716">
-        <v>4034.6</v>
+        <v>6516.9</v>
       </c>
       <c r="D2716" t="s">
         <v>2718</v>
@@ -47338,7 +47338,7 @@
         <v>32</v>
       </c>
       <c r="C2717">
-        <v>4151.8</v>
+        <v>6555.3</v>
       </c>
       <c r="D2717" t="s">
         <v>2719</v>
@@ -47352,7 +47352,7 @@
         <v>33</v>
       </c>
       <c r="C2718">
-        <v>4448.8</v>
+        <v>6637.4</v>
       </c>
       <c r="D2718" t="s">
         <v>2720</v>
@@ -47366,7 +47366,7 @@
         <v>34</v>
       </c>
       <c r="C2719">
-        <v>4624.2</v>
+        <v>6598.8</v>
       </c>
       <c r="D2719" t="s">
         <v>2721</v>
@@ -47380,7 +47380,7 @@
         <v>35</v>
       </c>
       <c r="C2720">
-        <v>4853.2</v>
+        <v>6055.6</v>
       </c>
       <c r="D2720" t="s">
         <v>2722</v>
@@ -47394,7 +47394,7 @@
         <v>36</v>
       </c>
       <c r="C2721">
-        <v>5045.1</v>
+        <v>5281.1</v>
       </c>
       <c r="D2721" t="s">
         <v>2723</v>
@@ -47408,7 +47408,7 @@
         <v>37</v>
       </c>
       <c r="C2722">
-        <v>5301.6</v>
+        <v>5774.7</v>
       </c>
       <c r="D2722" t="s">
         <v>2724</v>
@@ -47422,7 +47422,7 @@
         <v>38</v>
       </c>
       <c r="C2723">
-        <v>5422.6</v>
+        <v>5599.9</v>
       </c>
       <c r="D2723" t="s">
         <v>2725</v>
@@ -47436,7 +47436,7 @@
         <v>39</v>
       </c>
       <c r="C2724">
-        <v>5576.2</v>
+        <v>4732.3</v>
       </c>
       <c r="D2724" t="s">
         <v>2726</v>
@@ -47450,7 +47450,7 @@
         <v>40</v>
       </c>
       <c r="C2725">
-        <v>5753</v>
+        <v>4608.7</v>
       </c>
       <c r="D2725" t="s">
         <v>2727</v>
@@ -47464,7 +47464,7 @@
         <v>41</v>
       </c>
       <c r="C2726">
-        <v>5334.3</v>
+        <v>5200.4</v>
       </c>
       <c r="D2726" t="s">
         <v>2728</v>
@@ -47478,7 +47478,7 @@
         <v>42</v>
       </c>
       <c r="C2727">
-        <v>5447.6</v>
+        <v>5229.6</v>
       </c>
       <c r="D2727" t="s">
         <v>2729</v>
@@ -47492,7 +47492,7 @@
         <v>43</v>
       </c>
       <c r="C2728">
-        <v>5533.4</v>
+        <v>4999.6</v>
       </c>
       <c r="D2728" t="s">
         <v>2730</v>
@@ -47506,7 +47506,7 @@
         <v>44</v>
       </c>
       <c r="C2729">
-        <v>5593.2</v>
+        <v>4526.3</v>
       </c>
       <c r="D2729" t="s">
         <v>2731</v>
@@ -47520,7 +47520,7 @@
         <v>45</v>
       </c>
       <c r="C2730">
-        <v>5711.4</v>
+        <v>5722.1</v>
       </c>
       <c r="D2730" t="s">
         <v>2732</v>
@@ -47534,7 +47534,7 @@
         <v>46</v>
       </c>
       <c r="C2731">
-        <v>5744.7</v>
+        <v>5473.3</v>
       </c>
       <c r="D2731" t="s">
         <v>2733</v>
@@ -47548,7 +47548,7 @@
         <v>47</v>
       </c>
       <c r="C2732">
-        <v>5735.2</v>
+        <v>5039.8</v>
       </c>
       <c r="D2732" t="s">
         <v>2734</v>
@@ -47562,7 +47562,7 @@
         <v>48</v>
       </c>
       <c r="C2733">
-        <v>5734.6</v>
+        <v>4811.6</v>
       </c>
       <c r="D2733" t="s">
         <v>2735</v>
@@ -47576,7 +47576,7 @@
         <v>49</v>
       </c>
       <c r="C2734">
-        <v>5825.8</v>
+        <v>4113.1</v>
       </c>
       <c r="D2734" t="s">
         <v>2736</v>
@@ -47590,7 +47590,7 @@
         <v>50</v>
       </c>
       <c r="C2735">
-        <v>5806.9</v>
+        <v>3864.2</v>
       </c>
       <c r="D2735" t="s">
         <v>2737</v>
@@ -47604,7 +47604,7 @@
         <v>51</v>
       </c>
       <c r="C2736">
-        <v>5757.4</v>
+        <v>3855.7</v>
       </c>
       <c r="D2736" t="s">
         <v>2738</v>
@@ -47618,7 +47618,7 @@
         <v>52</v>
       </c>
       <c r="C2737">
-        <v>5716.2</v>
+        <v>3765.4</v>
       </c>
       <c r="D2737" t="s">
         <v>2739</v>
@@ -47632,7 +47632,7 @@
         <v>53</v>
       </c>
       <c r="C2738">
-        <v>5508.1</v>
+        <v>4020</v>
       </c>
       <c r="D2738" t="s">
         <v>2740</v>
@@ -47646,7 +47646,7 @@
         <v>54</v>
       </c>
       <c r="C2739">
-        <v>5455.8</v>
+        <v>3987.9</v>
       </c>
       <c r="D2739" t="s">
         <v>2741</v>
@@ -47660,7 +47660,7 @@
         <v>55</v>
       </c>
       <c r="C2740">
-        <v>5396.4</v>
+        <v>3873.7</v>
       </c>
       <c r="D2740" t="s">
         <v>2742</v>
@@ -47674,7 +47674,7 @@
         <v>56</v>
       </c>
       <c r="C2741">
-        <v>5314.2</v>
+        <v>3697.1</v>
       </c>
       <c r="D2741" t="s">
         <v>2743</v>
@@ -47688,7 +47688,7 @@
         <v>57</v>
       </c>
       <c r="C2742">
-        <v>5310.8</v>
+        <v>4310.5</v>
       </c>
       <c r="D2742" t="s">
         <v>2744</v>
@@ -47702,7 +47702,7 @@
         <v>58</v>
       </c>
       <c r="C2743">
-        <v>5216.4</v>
+        <v>4077.2</v>
       </c>
       <c r="D2743" t="s">
         <v>2745</v>
@@ -47716,7 +47716,7 @@
         <v>59</v>
       </c>
       <c r="C2744">
-        <v>5140.8</v>
+        <v>4241.8</v>
       </c>
       <c r="D2744" t="s">
         <v>2746</v>
@@ -47730,7 +47730,7 @@
         <v>60</v>
       </c>
       <c r="C2745">
-        <v>5068.1</v>
+        <v>4398.1</v>
       </c>
       <c r="D2745" t="s">
         <v>2747</v>
@@ -47744,7 +47744,7 @@
         <v>61</v>
       </c>
       <c r="C2746">
-        <v>5338.4</v>
+        <v>4934.1</v>
       </c>
       <c r="D2746" t="s">
         <v>2748</v>
@@ -47758,7 +47758,7 @@
         <v>62</v>
       </c>
       <c r="C2747">
-        <v>5256.2</v>
+        <v>5192.7</v>
       </c>
       <c r="D2747" t="s">
         <v>2749</v>
@@ -47772,7 +47772,7 @@
         <v>63</v>
       </c>
       <c r="C2748">
-        <v>5198.1</v>
+        <v>5716</v>
       </c>
       <c r="D2748" t="s">
         <v>2750</v>
@@ -47786,7 +47786,7 @@
         <v>64</v>
       </c>
       <c r="C2749">
-        <v>5161.4</v>
+        <v>6058.5</v>
       </c>
       <c r="D2749" t="s">
         <v>2751</v>
@@ -47800,7 +47800,7 @@
         <v>65</v>
       </c>
       <c r="C2750">
-        <v>5136.1</v>
+        <v>6002.8</v>
       </c>
       <c r="D2750" t="s">
         <v>2752</v>
@@ -47814,7 +47814,7 @@
         <v>66</v>
       </c>
       <c r="C2751">
-        <v>5074.9</v>
+        <v>6309.2</v>
       </c>
       <c r="D2751" t="s">
         <v>2753</v>
@@ -47828,7 +47828,7 @@
         <v>67</v>
       </c>
       <c r="C2752">
-        <v>4992</v>
+        <v>6396.7</v>
       </c>
       <c r="D2752" t="s">
         <v>2754</v>
@@ -47842,7 +47842,7 @@
         <v>68</v>
       </c>
       <c r="C2753">
-        <v>4957.1</v>
+        <v>6290</v>
       </c>
       <c r="D2753" t="s">
         <v>2755</v>
@@ -47856,7 +47856,7 @@
         <v>69</v>
       </c>
       <c r="C2754">
-        <v>4826.4</v>
+        <v>6317.1</v>
       </c>
       <c r="D2754" t="s">
         <v>2756</v>
@@ -47870,7 +47870,7 @@
         <v>70</v>
       </c>
       <c r="C2755">
-        <v>4730.2</v>
+        <v>6442.6</v>
       </c>
       <c r="D2755" t="s">
         <v>2757</v>
@@ -47884,7 +47884,7 @@
         <v>71</v>
       </c>
       <c r="C2756">
-        <v>4677.9</v>
+        <v>6295.6</v>
       </c>
       <c r="D2756" t="s">
         <v>2758</v>
@@ -47898,7 +47898,7 @@
         <v>72</v>
       </c>
       <c r="C2757">
-        <v>4664.4</v>
+        <v>6216.1</v>
       </c>
       <c r="D2757" t="s">
         <v>2759</v>
@@ -47912,7 +47912,7 @@
         <v>73</v>
       </c>
       <c r="C2758">
-        <v>4783</v>
+        <v>6220.5</v>
       </c>
       <c r="D2758" t="s">
         <v>2760</v>
@@ -47926,7 +47926,7 @@
         <v>74</v>
       </c>
       <c r="C2759">
-        <v>4770.2</v>
+        <v>6101.8</v>
       </c>
       <c r="D2759" t="s">
         <v>2761</v>
@@ -47940,7 +47940,7 @@
         <v>75</v>
       </c>
       <c r="C2760">
-        <v>4741.8</v>
+        <v>6456.6</v>
       </c>
       <c r="D2760" t="s">
         <v>2762</v>
@@ -47954,7 +47954,7 @@
         <v>76</v>
       </c>
       <c r="C2761">
-        <v>4741.1</v>
+        <v>6796.3</v>
       </c>
       <c r="D2761" t="s">
         <v>2763</v>
@@ -47968,7 +47968,7 @@
         <v>77</v>
       </c>
       <c r="C2762">
-        <v>4891.7</v>
+        <v>7166.4</v>
       </c>
       <c r="D2762" t="s">
         <v>2764</v>
@@ -47982,7 +47982,7 @@
         <v>78</v>
       </c>
       <c r="C2763">
-        <v>4973.6</v>
+        <v>7325.1</v>
       </c>
       <c r="D2763" t="s">
         <v>2765</v>
@@ -47996,7 +47996,7 @@
         <v>79</v>
       </c>
       <c r="C2764">
-        <v>5060.8</v>
+        <v>7394.8</v>
       </c>
       <c r="D2764" t="s">
         <v>2766</v>
@@ -48010,7 +48010,7 @@
         <v>80</v>
       </c>
       <c r="C2765">
-        <v>5224.8</v>
+        <v>7451.3</v>
       </c>
       <c r="D2765" t="s">
         <v>2767</v>
@@ -48024,7 +48024,7 @@
         <v>81</v>
       </c>
       <c r="C2766">
-        <v>5440.1</v>
+        <v>7519.9</v>
       </c>
       <c r="D2766" t="s">
         <v>2768</v>
@@ -48038,7 +48038,7 @@
         <v>82</v>
       </c>
       <c r="C2767">
-        <v>5559.8</v>
+        <v>7582.2</v>
       </c>
       <c r="D2767" t="s">
         <v>2769</v>
@@ -48052,7 +48052,7 @@
         <v>83</v>
       </c>
       <c r="C2768">
-        <v>5635</v>
+        <v>7642.4</v>
       </c>
       <c r="D2768" t="s">
         <v>2770</v>
@@ -48066,7 +48066,7 @@
         <v>84</v>
       </c>
       <c r="C2769">
-        <v>5648.8</v>
+        <v>7660</v>
       </c>
       <c r="D2769" t="s">
         <v>2771</v>
@@ -48080,7 +48080,7 @@
         <v>85</v>
       </c>
       <c r="C2770">
-        <v>5541.7</v>
+        <v>7076.8</v>
       </c>
       <c r="D2770" t="s">
         <v>2772</v>
@@ -48094,7 +48094,7 @@
         <v>86</v>
       </c>
       <c r="C2771">
-        <v>5503.8</v>
+        <v>6766.3</v>
       </c>
       <c r="D2771" t="s">
         <v>2773</v>
@@ -48108,7 +48108,7 @@
         <v>87</v>
       </c>
       <c r="C2772">
-        <v>5473</v>
+        <v>6470.7</v>
       </c>
       <c r="D2772" t="s">
         <v>2774</v>
@@ -48122,7 +48122,7 @@
         <v>88</v>
       </c>
       <c r="C2773">
-        <v>5457.7</v>
+        <v>6490.2</v>
       </c>
       <c r="D2773" t="s">
         <v>2775</v>
@@ -48136,7 +48136,7 @@
         <v>89</v>
       </c>
       <c r="C2774">
-        <v>5593.8</v>
+        <v>6693.7</v>
       </c>
       <c r="D2774" t="s">
         <v>2776</v>
@@ -48150,7 +48150,7 @@
         <v>90</v>
       </c>
       <c r="C2775">
-        <v>5577.2</v>
+        <v>6665.8</v>
       </c>
       <c r="D2775" t="s">
         <v>2777</v>
@@ -48164,7 +48164,7 @@
         <v>91</v>
       </c>
       <c r="C2776">
-        <v>5554.2</v>
+        <v>6480.2</v>
       </c>
       <c r="D2776" t="s">
         <v>2778</v>
@@ -48178,7 +48178,7 @@
         <v>92</v>
       </c>
       <c r="C2777">
-        <v>5537.9</v>
+        <v>6330.2</v>
       </c>
       <c r="D2777" t="s">
         <v>2779</v>
@@ -48192,7 +48192,7 @@
         <v>93</v>
       </c>
       <c r="C2778">
-        <v>5400.6</v>
+        <v>6368.5</v>
       </c>
       <c r="D2778" t="s">
         <v>2780</v>
@@ -48206,7 +48206,7 @@
         <v>94</v>
       </c>
       <c r="C2779">
-        <v>5377.6</v>
+        <v>6364.1</v>
       </c>
       <c r="D2779" t="s">
         <v>2781</v>
@@ -48220,7 +48220,7 @@
         <v>95</v>
       </c>
       <c r="C2780">
-        <v>5382.5</v>
+        <v>6438.7</v>
       </c>
       <c r="D2780" t="s">
         <v>2782</v>
@@ -48234,7 +48234,7 @@
         <v>96</v>
       </c>
       <c r="C2781">
-        <v>5374.2</v>
+        <v>6099.5</v>
       </c>
       <c r="D2781" t="s">
         <v>2783</v>
@@ -48248,7 +48248,7 @@
         <v>1</v>
       </c>
       <c r="C2782">
-        <v>4755.1</v>
+        <v>5560.6</v>
       </c>
       <c r="D2782" t="s">
         <v>2784</v>
@@ -48262,7 +48262,7 @@
         <v>2</v>
       </c>
       <c r="C2783">
-        <v>4748.4</v>
+        <v>5564.9</v>
       </c>
       <c r="D2783" t="s">
         <v>2785</v>
@@ -48276,7 +48276,7 @@
         <v>3</v>
       </c>
       <c r="C2784">
-        <v>4746.3</v>
+        <v>5585.2</v>
       </c>
       <c r="D2784" t="s">
         <v>2786</v>
@@ -48290,7 +48290,7 @@
         <v>4</v>
       </c>
       <c r="C2785">
-        <v>4722.1</v>
+        <v>5743.3</v>
       </c>
       <c r="D2785" t="s">
         <v>2787</v>
@@ -48304,7 +48304,7 @@
         <v>5</v>
       </c>
       <c r="C2786">
-        <v>4606</v>
+        <v>6224.7</v>
       </c>
       <c r="D2786" t="s">
         <v>2788</v>
@@ -48318,7 +48318,7 @@
         <v>6</v>
       </c>
       <c r="C2787">
-        <v>4568.2</v>
+        <v>5913.6</v>
       </c>
       <c r="D2787" t="s">
         <v>2789</v>
@@ -48332,7 +48332,7 @@
         <v>7</v>
       </c>
       <c r="C2788">
-        <v>4568.6</v>
+        <v>5837.6</v>
       </c>
       <c r="D2788" t="s">
         <v>2790</v>
@@ -48346,7 +48346,7 @@
         <v>8</v>
       </c>
       <c r="C2789">
-        <v>4566.8</v>
+        <v>5582</v>
       </c>
       <c r="D2789" t="s">
         <v>2791</v>
@@ -48360,7 +48360,7 @@
         <v>9</v>
       </c>
       <c r="C2790">
-        <v>4515.8</v>
+        <v>5695.7</v>
       </c>
       <c r="D2790" t="s">
         <v>2792</v>
@@ -48374,7 +48374,7 @@
         <v>10</v>
       </c>
       <c r="C2791">
-        <v>4527.8</v>
+        <v>5636.4</v>
       </c>
       <c r="D2791" t="s">
         <v>2793</v>
@@ -48388,7 +48388,7 @@
         <v>11</v>
       </c>
       <c r="C2792">
-        <v>4538.7</v>
+        <v>5431.4</v>
       </c>
       <c r="D2792" t="s">
         <v>2794</v>
@@ -48402,7 +48402,7 @@
         <v>12</v>
       </c>
       <c r="C2793">
-        <v>4529.3</v>
+        <v>5044.9</v>
       </c>
       <c r="D2793" t="s">
         <v>2795</v>
@@ -48416,7 +48416,7 @@
         <v>13</v>
       </c>
       <c r="C2794">
-        <v>4557.9</v>
+        <v>5528.6</v>
       </c>
       <c r="D2794" t="s">
         <v>2796</v>
@@ -48430,7 +48430,7 @@
         <v>14</v>
       </c>
       <c r="C2795">
-        <v>4562.1</v>
+        <v>5150.2</v>
       </c>
       <c r="D2795" t="s">
         <v>2797</v>
@@ -48444,7 +48444,7 @@
         <v>15</v>
       </c>
       <c r="C2796">
-        <v>4569.7</v>
+        <v>5053.2</v>
       </c>
       <c r="D2796" t="s">
         <v>2798</v>
@@ -48458,7 +48458,7 @@
         <v>16</v>
       </c>
       <c r="C2797">
-        <v>4587.9</v>
+        <v>4799.2</v>
       </c>
       <c r="D2797" t="s">
         <v>2799</v>
@@ -48472,7 +48472,7 @@
         <v>17</v>
       </c>
       <c r="C2798">
-        <v>4536.4</v>
+        <v>4909.1</v>
       </c>
       <c r="D2798" t="s">
         <v>2800</v>
@@ -48486,7 +48486,7 @@
         <v>18</v>
       </c>
       <c r="C2799">
-        <v>4564.7</v>
+        <v>4865.7</v>
       </c>
       <c r="D2799" t="s">
         <v>2801</v>
@@ -48500,7 +48500,7 @@
         <v>19</v>
       </c>
       <c r="C2800">
-        <v>4573.4</v>
+        <v>4760.2</v>
       </c>
       <c r="D2800" t="s">
         <v>2802</v>
@@ -48514,7 +48514,7 @@
         <v>20</v>
       </c>
       <c r="C2801">
-        <v>4566.9</v>
+        <v>4717.4</v>
       </c>
       <c r="D2801" t="s">
         <v>2803</v>
@@ -48528,7 +48528,7 @@
         <v>21</v>
       </c>
       <c r="C2802">
-        <v>4570.4</v>
+        <v>4791.7</v>
       </c>
       <c r="D2802" t="s">
         <v>2804</v>
@@ -48542,7 +48542,7 @@
         <v>22</v>
       </c>
       <c r="C2803">
-        <v>4600.9</v>
+        <v>4827.6</v>
       </c>
       <c r="D2803" t="s">
         <v>2805</v>
@@ -48556,7 +48556,7 @@
         <v>23</v>
       </c>
       <c r="C2804">
-        <v>4648.7</v>
+        <v>4817.5</v>
       </c>
       <c r="D2804" t="s">
         <v>2806</v>
@@ -48570,7 +48570,7 @@
         <v>24</v>
       </c>
       <c r="C2805">
-        <v>4695.1</v>
+        <v>4871.4</v>
       </c>
       <c r="D2805" t="s">
         <v>2807</v>
@@ -48584,7 +48584,7 @@
         <v>25</v>
       </c>
       <c r="C2806">
-        <v>4638.1</v>
+        <v>5783</v>
       </c>
       <c r="D2806" t="s">
         <v>2808</v>
@@ -48598,7 +48598,7 @@
         <v>26</v>
       </c>
       <c r="C2807">
-        <v>4711.4</v>
+        <v>6098.5</v>
       </c>
       <c r="D2807" t="s">
         <v>2809</v>
@@ -48612,7 +48612,7 @@
         <v>27</v>
       </c>
       <c r="C2808">
-        <v>4827.6</v>
+        <v>6352.1</v>
       </c>
       <c r="D2808" t="s">
         <v>2810</v>
@@ -48626,7 +48626,7 @@
         <v>28</v>
       </c>
       <c r="C2809">
-        <v>4910.6</v>
+        <v>6774</v>
       </c>
       <c r="D2809" t="s">
         <v>2811</v>
@@ -48640,7 +48640,7 @@
         <v>29</v>
       </c>
       <c r="C2810">
-        <v>5174.8</v>
+        <v>7212.6</v>
       </c>
       <c r="D2810" t="s">
         <v>2812</v>
@@ -48654,7 +48654,7 @@
         <v>30</v>
       </c>
       <c r="C2811">
-        <v>5340.8</v>
+        <v>7567.4</v>
       </c>
       <c r="D2811" t="s">
         <v>2813</v>
@@ -48668,7 +48668,7 @@
         <v>31</v>
       </c>
       <c r="C2812">
-        <v>5564.6</v>
+        <v>7896.9</v>
       </c>
       <c r="D2812" t="s">
         <v>2814</v>
@@ -48682,7 +48682,7 @@
         <v>32</v>
       </c>
       <c r="C2813">
-        <v>5791.8</v>
+        <v>7975.3</v>
       </c>
       <c r="D2813" t="s">
         <v>2815</v>
@@ -48696,7 +48696,7 @@
         <v>33</v>
       </c>
       <c r="C2814">
-        <v>6158.8</v>
+        <v>8087.4</v>
       </c>
       <c r="D2814" t="s">
         <v>2816</v>
@@ -48710,7 +48710,7 @@
         <v>34</v>
       </c>
       <c r="C2815">
-        <v>6384.2</v>
+        <v>8078.8</v>
       </c>
       <c r="D2815" t="s">
         <v>2817</v>
@@ -48724,7 +48724,7 @@
         <v>35</v>
       </c>
       <c r="C2816">
-        <v>6653.2</v>
+        <v>7565.6</v>
       </c>
       <c r="D2816" t="s">
         <v>2818</v>
@@ -48738,7 +48738,7 @@
         <v>36</v>
       </c>
       <c r="C2817">
-        <v>6865.1</v>
+        <v>6791.1</v>
       </c>
       <c r="D2817" t="s">
         <v>2819</v>
@@ -48752,7 +48752,7 @@
         <v>37</v>
       </c>
       <c r="C2818">
-        <v>7141.6</v>
+        <v>7274.7</v>
       </c>
       <c r="D2818" t="s">
         <v>2820</v>
@@ -48766,7 +48766,7 @@
         <v>38</v>
       </c>
       <c r="C2819">
-        <v>7272.6</v>
+        <v>7079.9</v>
       </c>
       <c r="D2819" t="s">
         <v>2821</v>
@@ -48780,7 +48780,7 @@
         <v>39</v>
       </c>
       <c r="C2820">
-        <v>7416.2</v>
+        <v>6182.3</v>
       </c>
       <c r="D2820" t="s">
         <v>2822</v>
@@ -48794,7 +48794,7 @@
         <v>40</v>
       </c>
       <c r="C2821">
-        <v>7573</v>
+        <v>6058.7</v>
       </c>
       <c r="D2821" t="s">
         <v>2823</v>
@@ -48808,7 +48808,7 @@
         <v>41</v>
       </c>
       <c r="C2822">
-        <v>7124.3</v>
+        <v>6600.4</v>
       </c>
       <c r="D2822" t="s">
         <v>2824</v>
@@ -48822,7 +48822,7 @@
         <v>42</v>
       </c>
       <c r="C2823">
-        <v>7197.6</v>
+        <v>6619.6</v>
       </c>
       <c r="D2823" t="s">
         <v>2825</v>
@@ -48836,7 +48836,7 @@
         <v>43</v>
       </c>
       <c r="C2824">
-        <v>7243.4</v>
+        <v>6379.6</v>
       </c>
       <c r="D2824" t="s">
         <v>2826</v>
@@ -48850,7 +48850,7 @@
         <v>44</v>
       </c>
       <c r="C2825">
-        <v>7263.2</v>
+        <v>5866.3</v>
       </c>
       <c r="D2825" t="s">
         <v>2827</v>
@@ -48864,7 +48864,7 @@
         <v>45</v>
       </c>
       <c r="C2826">
-        <v>7331.4</v>
+        <v>7062.1</v>
       </c>
       <c r="D2826" t="s">
         <v>2828</v>
@@ -48878,7 +48878,7 @@
         <v>46</v>
       </c>
       <c r="C2827">
-        <v>7324.7</v>
+        <v>6753.3</v>
       </c>
       <c r="D2827" t="s">
         <v>2829</v>
@@ -48892,7 +48892,7 @@
         <v>47</v>
       </c>
       <c r="C2828">
-        <v>7275.2</v>
+        <v>6269.8</v>
       </c>
       <c r="D2828" t="s">
         <v>2830</v>
@@ -48906,7 +48906,7 @@
         <v>48</v>
       </c>
       <c r="C2829">
-        <v>7244.6</v>
+        <v>6011.6</v>
       </c>
       <c r="D2829" t="s">
         <v>2831</v>
@@ -48920,7 +48920,7 @@
         <v>49</v>
       </c>
       <c r="C2830">
-        <v>7305.8</v>
+        <v>5273.1</v>
       </c>
       <c r="D2830" t="s">
         <v>2832</v>
@@ -48934,7 +48934,7 @@
         <v>50</v>
       </c>
       <c r="C2831">
-        <v>7266.9</v>
+        <v>5004.2</v>
       </c>
       <c r="D2831" t="s">
         <v>2833</v>
@@ -48948,7 +48948,7 @@
         <v>51</v>
       </c>
       <c r="C2832">
-        <v>7207.4</v>
+        <v>4975.7</v>
       </c>
       <c r="D2832" t="s">
         <v>2834</v>
@@ -48962,7 +48962,7 @@
         <v>52</v>
       </c>
       <c r="C2833">
-        <v>7166.2</v>
+        <v>4865.4</v>
       </c>
       <c r="D2833" t="s">
         <v>2835</v>
@@ -48976,7 +48976,7 @@
         <v>53</v>
       </c>
       <c r="C2834">
-        <v>6958.1</v>
+        <v>5100</v>
       </c>
       <c r="D2834" t="s">
         <v>2836</v>
@@ -48990,7 +48990,7 @@
         <v>54</v>
       </c>
       <c r="C2835">
-        <v>6905.8</v>
+        <v>5047.9</v>
       </c>
       <c r="D2835" t="s">
         <v>2837</v>
@@ -49004,7 +49004,7 @@
         <v>55</v>
       </c>
       <c r="C2836">
-        <v>6836.4</v>
+        <v>4933.7</v>
       </c>
       <c r="D2836" t="s">
         <v>2838</v>
@@ -49018,7 +49018,7 @@
         <v>56</v>
       </c>
       <c r="C2837">
-        <v>6734.2</v>
+        <v>4757.1</v>
       </c>
       <c r="D2837" t="s">
         <v>2839</v>
@@ -49032,7 +49032,7 @@
         <v>57</v>
       </c>
       <c r="C2838">
-        <v>6710.8</v>
+        <v>5380.5</v>
       </c>
       <c r="D2838" t="s">
         <v>2840</v>
@@ -49046,7 +49046,7 @@
         <v>58</v>
       </c>
       <c r="C2839">
-        <v>6606.4</v>
+        <v>5147.2</v>
       </c>
       <c r="D2839" t="s">
         <v>2841</v>
@@ -49060,7 +49060,7 @@
         <v>59</v>
       </c>
       <c r="C2840">
-        <v>6550.8</v>
+        <v>5311.8</v>
       </c>
       <c r="D2840" t="s">
         <v>2842</v>
@@ -49074,7 +49074,7 @@
         <v>60</v>
       </c>
       <c r="C2841">
-        <v>6548.1</v>
+        <v>5468.1</v>
       </c>
       <c r="D2841" t="s">
         <v>2843</v>
@@ -49088,7 +49088,7 @@
         <v>61</v>
       </c>
       <c r="C2842">
-        <v>6878.4</v>
+        <v>5994.1</v>
       </c>
       <c r="D2842" t="s">
         <v>2844</v>
@@ -49102,7 +49102,7 @@
         <v>62</v>
       </c>
       <c r="C2843">
-        <v>6856.2</v>
+        <v>6232.7</v>
       </c>
       <c r="D2843" t="s">
         <v>2845</v>
@@ -49116,7 +49116,7 @@
         <v>63</v>
       </c>
       <c r="C2844">
-        <v>6798.1</v>
+        <v>6736</v>
       </c>
       <c r="D2844" t="s">
         <v>2846</v>
@@ -49130,7 +49130,7 @@
         <v>64</v>
       </c>
       <c r="C2845">
-        <v>6721.4</v>
+        <v>7058.5</v>
       </c>
       <c r="D2845" t="s">
         <v>2847</v>
@@ -49144,7 +49144,7 @@
         <v>65</v>
       </c>
       <c r="C2846">
-        <v>6626.1</v>
+        <v>6962.8</v>
       </c>
       <c r="D2846" t="s">
         <v>2848</v>
@@ -49158,7 +49158,7 @@
         <v>66</v>
       </c>
       <c r="C2847">
-        <v>6504.9</v>
+        <v>7239.2</v>
       </c>
       <c r="D2847" t="s">
         <v>2849</v>
@@ -49172,7 +49172,7 @@
         <v>67</v>
       </c>
       <c r="C2848">
-        <v>6382</v>
+        <v>7306.7</v>
       </c>
       <c r="D2848" t="s">
         <v>2850</v>
@@ -49186,7 +49186,7 @@
         <v>68</v>
       </c>
       <c r="C2849">
-        <v>6317.1</v>
+        <v>7200</v>
       </c>
       <c r="D2849" t="s">
         <v>2851</v>
@@ -49200,7 +49200,7 @@
         <v>69</v>
       </c>
       <c r="C2850">
-        <v>6166.4</v>
+        <v>7227.1</v>
       </c>
       <c r="D2850" t="s">
         <v>2852</v>
@@ -49214,7 +49214,7 @@
         <v>70</v>
       </c>
       <c r="C2851">
-        <v>6060.2</v>
+        <v>7362.6</v>
       </c>
       <c r="D2851" t="s">
         <v>2853</v>
@@ -49228,7 +49228,7 @@
         <v>71</v>
       </c>
       <c r="C2852">
-        <v>5977.9</v>
+        <v>7225.6</v>
       </c>
       <c r="D2852" t="s">
         <v>2854</v>
@@ -49242,7 +49242,7 @@
         <v>72</v>
       </c>
       <c r="C2853">
-        <v>5934.4</v>
+        <v>7146.1</v>
       </c>
       <c r="D2853" t="s">
         <v>2855</v>
@@ -49256,7 +49256,7 @@
         <v>73</v>
       </c>
       <c r="C2854">
-        <v>6003</v>
+        <v>7170.5</v>
       </c>
       <c r="D2854" t="s">
         <v>2856</v>
@@ -49270,7 +49270,7 @@
         <v>74</v>
       </c>
       <c r="C2855">
-        <v>5960.2</v>
+        <v>7051.8</v>
       </c>
       <c r="D2855" t="s">
         <v>2857</v>
@@ -49284,7 +49284,7 @@
         <v>75</v>
       </c>
       <c r="C2856">
-        <v>5901.8</v>
+        <v>7406.6</v>
       </c>
       <c r="D2856" t="s">
         <v>2858</v>
@@ -49298,7 +49298,7 @@
         <v>76</v>
       </c>
       <c r="C2857">
-        <v>5881.1</v>
+        <v>7736.3</v>
       </c>
       <c r="D2857" t="s">
         <v>2859</v>
@@ -49312,7 +49312,7 @@
         <v>77</v>
       </c>
       <c r="C2858">
-        <v>6011.7</v>
+        <v>8086.4</v>
       </c>
       <c r="D2858" t="s">
         <v>2860</v>
@@ -49326,7 +49326,7 @@
         <v>78</v>
       </c>
       <c r="C2859">
-        <v>6083.6</v>
+        <v>8245.1</v>
       </c>
       <c r="D2859" t="s">
         <v>2861</v>
@@ -49340,7 +49340,7 @@
         <v>79</v>
       </c>
       <c r="C2860">
-        <v>6140.8</v>
+        <v>8324.799999999999</v>
       </c>
       <c r="D2860" t="s">
         <v>2862</v>
@@ -49354,7 +49354,7 @@
         <v>80</v>
       </c>
       <c r="C2861">
-        <v>6284.8</v>
+        <v>8431.299999999999</v>
       </c>
       <c r="D2861" t="s">
         <v>2863</v>
@@ -49368,7 +49368,7 @@
         <v>81</v>
       </c>
       <c r="C2862">
-        <v>6460.1</v>
+        <v>8539.9</v>
       </c>
       <c r="D2862" t="s">
         <v>2864</v>
@@ -49382,7 +49382,7 @@
         <v>82</v>
       </c>
       <c r="C2863">
-        <v>6559.8</v>
+        <v>8612.200000000001</v>
       </c>
       <c r="D2863" t="s">
         <v>2865</v>
@@ -49396,7 +49396,7 @@
         <v>83</v>
       </c>
       <c r="C2864">
-        <v>6615</v>
+        <v>8692.4</v>
       </c>
       <c r="D2864" t="s">
         <v>2866</v>
@@ -49410,7 +49410,7 @@
         <v>84</v>
       </c>
       <c r="C2865">
-        <v>6618.8</v>
+        <v>8710</v>
       </c>
       <c r="D2865" t="s">
         <v>2867</v>
@@ -49424,7 +49424,7 @@
         <v>85</v>
       </c>
       <c r="C2866">
-        <v>6491.7</v>
+        <v>8096.8</v>
       </c>
       <c r="D2866" t="s">
         <v>2868</v>
@@ -49438,7 +49438,7 @@
         <v>86</v>
       </c>
       <c r="C2867">
-        <v>6433.8</v>
+        <v>7676.3</v>
       </c>
       <c r="D2867" t="s">
         <v>2869</v>
@@ -49452,7 +49452,7 @@
         <v>87</v>
       </c>
       <c r="C2868">
-        <v>6363</v>
+        <v>7350.7</v>
       </c>
       <c r="D2868" t="s">
         <v>2870</v>
@@ -49466,7 +49466,7 @@
         <v>88</v>
       </c>
       <c r="C2869">
-        <v>6297.7</v>
+        <v>7330.2</v>
       </c>
       <c r="D2869" t="s">
         <v>2871</v>
@@ -49480,7 +49480,7 @@
         <v>89</v>
       </c>
       <c r="C2870">
-        <v>6383.8</v>
+        <v>7483.7</v>
       </c>
       <c r="D2870" t="s">
         <v>2872</v>
@@ -49494,7 +49494,7 @@
         <v>90</v>
       </c>
       <c r="C2871">
-        <v>6317.2</v>
+        <v>7415.8</v>
       </c>
       <c r="D2871" t="s">
         <v>2873</v>
@@ -49508,7 +49508,7 @@
         <v>91</v>
       </c>
       <c r="C2872">
-        <v>6244.2</v>
+        <v>7200.2</v>
       </c>
       <c r="D2872" t="s">
         <v>2874</v>
@@ -49522,7 +49522,7 @@
         <v>92</v>
       </c>
       <c r="C2873">
-        <v>6197.9</v>
+        <v>7000.2</v>
       </c>
       <c r="D2873" t="s">
         <v>2875</v>
@@ -49536,7 +49536,7 @@
         <v>93</v>
       </c>
       <c r="C2874">
-        <v>6030.6</v>
+        <v>6998.5</v>
       </c>
       <c r="D2874" t="s">
         <v>2876</v>
@@ -49550,7 +49550,7 @@
         <v>94</v>
       </c>
       <c r="C2875">
-        <v>5987.6</v>
+        <v>6964.1</v>
       </c>
       <c r="D2875" t="s">
         <v>2877</v>
@@ -49564,7 +49564,7 @@
         <v>95</v>
       </c>
       <c r="C2876">
-        <v>5962.5</v>
+        <v>7008.7</v>
       </c>
       <c r="D2876" t="s">
         <v>2878</v>
@@ -49578,7 +49578,7 @@
         <v>96</v>
       </c>
       <c r="C2877">
-        <v>5934.2</v>
+        <v>6659.5</v>
       </c>
       <c r="D2877" t="s">
         <v>2879</v>
@@ -49592,7 +49592,7 @@
         <v>1</v>
       </c>
       <c r="C2878">
-        <v>5325.1</v>
+        <v>6090.6</v>
       </c>
       <c r="D2878" t="s">
         <v>2880</v>
@@ -49606,7 +49606,7 @@
         <v>2</v>
       </c>
       <c r="C2879">
-        <v>5318.4</v>
+        <v>6084.9</v>
       </c>
       <c r="D2879" t="s">
         <v>2881</v>
@@ -49620,7 +49620,7 @@
         <v>3</v>
       </c>
       <c r="C2880">
-        <v>5306.3</v>
+        <v>6105.2</v>
       </c>
       <c r="D2880" t="s">
         <v>2882</v>
@@ -49634,7 +49634,7 @@
         <v>4</v>
       </c>
       <c r="C2881">
-        <v>5282.1</v>
+        <v>6253.3</v>
       </c>
       <c r="D2881" t="s">
         <v>2883</v>
@@ -49648,7 +49648,7 @@
         <v>5</v>
       </c>
       <c r="C2882">
-        <v>5166</v>
+        <v>6734.7</v>
       </c>
       <c r="D2882" t="s">
         <v>2884</v>
@@ -49662,7 +49662,7 @@
         <v>6</v>
       </c>
       <c r="C2883">
-        <v>5128.2</v>
+        <v>6423.6</v>
       </c>
       <c r="D2883" t="s">
         <v>2885</v>
@@ -49676,7 +49676,7 @@
         <v>7</v>
       </c>
       <c r="C2884">
-        <v>5118.6</v>
+        <v>6337.6</v>
       </c>
       <c r="D2884" t="s">
         <v>2886</v>
@@ -49690,7 +49690,7 @@
         <v>8</v>
       </c>
       <c r="C2885">
-        <v>5116.8</v>
+        <v>6072</v>
       </c>
       <c r="D2885" t="s">
         <v>2887</v>
@@ -49704,7 +49704,7 @@
         <v>9</v>
       </c>
       <c r="C2886">
-        <v>5055.8</v>
+        <v>6175.7</v>
       </c>
       <c r="D2886" t="s">
         <v>2888</v>
@@ -49718,7 +49718,7 @@
         <v>10</v>
       </c>
       <c r="C2887">
-        <v>5057.8</v>
+        <v>6116.4</v>
       </c>
       <c r="D2887" t="s">
         <v>2889</v>
@@ -49732,7 +49732,7 @@
         <v>11</v>
       </c>
       <c r="C2888">
-        <v>5058.7</v>
+        <v>5931.4</v>
       </c>
       <c r="D2888" t="s">
         <v>2890</v>
@@ -49746,7 +49746,7 @@
         <v>12</v>
       </c>
       <c r="C2889">
-        <v>5039.3</v>
+        <v>5564.9</v>
       </c>
       <c r="D2889" t="s">
         <v>2891</v>
@@ -49760,7 +49760,7 @@
         <v>13</v>
       </c>
       <c r="C2890">
-        <v>5067.9</v>
+        <v>6038.6</v>
       </c>
       <c r="D2890" t="s">
         <v>2892</v>
@@ -49774,7 +49774,7 @@
         <v>14</v>
       </c>
       <c r="C2891">
-        <v>5062.1</v>
+        <v>5650.2</v>
       </c>
       <c r="D2891" t="s">
         <v>2893</v>
@@ -49788,7 +49788,7 @@
         <v>15</v>
       </c>
       <c r="C2892">
-        <v>5079.7</v>
+        <v>5553.2</v>
       </c>
       <c r="D2892" t="s">
         <v>2894</v>
@@ -49802,7 +49802,7 @@
         <v>16</v>
       </c>
       <c r="C2893">
-        <v>5097.9</v>
+        <v>5269.2</v>
       </c>
       <c r="D2893" t="s">
         <v>2895</v>
@@ -49816,7 +49816,7 @@
         <v>17</v>
       </c>
       <c r="C2894">
-        <v>5056.4</v>
+        <v>5349.1</v>
       </c>
       <c r="D2894" t="s">
         <v>2896</v>
@@ -49830,7 +49830,7 @@
         <v>18</v>
       </c>
       <c r="C2895">
-        <v>5084.7</v>
+        <v>5325.7</v>
       </c>
       <c r="D2895" t="s">
         <v>2897</v>
@@ -49844,7 +49844,7 @@
         <v>19</v>
       </c>
       <c r="C2896">
-        <v>5083.4</v>
+        <v>5230.2</v>
       </c>
       <c r="D2896" t="s">
         <v>2898</v>
@@ -49858,7 +49858,7 @@
         <v>20</v>
       </c>
       <c r="C2897">
-        <v>5066.9</v>
+        <v>5177.4</v>
       </c>
       <c r="D2897" t="s">
         <v>2899</v>
@@ -49872,7 +49872,7 @@
         <v>21</v>
       </c>
       <c r="C2898">
-        <v>5050.4</v>
+        <v>5251.7</v>
       </c>
       <c r="D2898" t="s">
         <v>2900</v>
@@ -49886,7 +49886,7 @@
         <v>22</v>
       </c>
       <c r="C2899">
-        <v>5050.9</v>
+        <v>5277.6</v>
       </c>
       <c r="D2899" t="s">
         <v>2901</v>
@@ -49900,7 +49900,7 @@
         <v>23</v>
       </c>
       <c r="C2900">
-        <v>5068.7</v>
+        <v>5247.5</v>
       </c>
       <c r="D2900" t="s">
         <v>2902</v>
@@ -49914,7 +49914,7 @@
         <v>24</v>
       </c>
       <c r="C2901">
-        <v>5085.1</v>
+        <v>5261.4</v>
       </c>
       <c r="D2901" t="s">
         <v>2903</v>
@@ -49928,7 +49928,7 @@
         <v>25</v>
       </c>
       <c r="C2902">
-        <v>4988.1</v>
+        <v>6123</v>
       </c>
       <c r="D2902" t="s">
         <v>2904</v>
@@ -49942,7 +49942,7 @@
         <v>26</v>
       </c>
       <c r="C2903">
-        <v>5031.4</v>
+        <v>6388.5</v>
       </c>
       <c r="D2903" t="s">
         <v>2905</v>
@@ -49956,7 +49956,7 @@
         <v>27</v>
       </c>
       <c r="C2904">
-        <v>5127.6</v>
+        <v>6612.1</v>
       </c>
       <c r="D2904" t="s">
         <v>2906</v>
@@ -49970,7 +49970,7 @@
         <v>28</v>
       </c>
       <c r="C2905">
-        <v>5190.6</v>
+        <v>7054</v>
       </c>
       <c r="D2905" t="s">
         <v>2907</v>
@@ -49984,7 +49984,7 @@
         <v>29</v>
       </c>
       <c r="C2906">
-        <v>5434.8</v>
+        <v>7502.6</v>
       </c>
       <c r="D2906" t="s">
         <v>2908</v>
@@ -49998,7 +49998,7 @@
         <v>30</v>
       </c>
       <c r="C2907">
-        <v>5580.8</v>
+        <v>7767.4</v>
       </c>
       <c r="D2907" t="s">
         <v>2909</v>
@@ -50012,7 +50012,7 @@
         <v>31</v>
       </c>
       <c r="C2908">
-        <v>5774.6</v>
+        <v>7976.9</v>
       </c>
       <c r="D2908" t="s">
         <v>2910</v>
@@ -50026,7 +50026,7 @@
         <v>32</v>
       </c>
       <c r="C2909">
-        <v>5971.8</v>
+        <v>8025.3</v>
       </c>
       <c r="D2909" t="s">
         <v>2911</v>
@@ -50040,7 +50040,7 @@
         <v>33</v>
       </c>
       <c r="C2910">
-        <v>6298.8</v>
+        <v>8137.4</v>
       </c>
       <c r="D2910" t="s">
         <v>2912</v>
@@ -50054,7 +50054,7 @@
         <v>34</v>
       </c>
       <c r="C2911">
-        <v>6494.2</v>
+        <v>8128.8</v>
       </c>
       <c r="D2911" t="s">
         <v>2913</v>
@@ -50068,7 +50068,7 @@
         <v>35</v>
       </c>
       <c r="C2912">
-        <v>6753.2</v>
+        <v>7635.6</v>
       </c>
       <c r="D2912" t="s">
         <v>2914</v>
@@ -50082,7 +50082,7 @@
         <v>36</v>
       </c>
       <c r="C2913">
-        <v>6955.1</v>
+        <v>6871.1</v>
       </c>
       <c r="D2913" t="s">
         <v>2915</v>
@@ -50096,7 +50096,7 @@
         <v>37</v>
       </c>
       <c r="C2914">
-        <v>7241.6</v>
+        <v>7374.7</v>
       </c>
       <c r="D2914" t="s">
         <v>2916</v>
@@ -50110,7 +50110,7 @@
         <v>38</v>
       </c>
       <c r="C2915">
-        <v>7362.6</v>
+        <v>7179.9</v>
       </c>
       <c r="D2915" t="s">
         <v>2917</v>
@@ -50124,7 +50124,7 @@
         <v>39</v>
       </c>
       <c r="C2916">
-        <v>7506.2</v>
+        <v>6282.3</v>
       </c>
       <c r="D2916" t="s">
         <v>2918</v>
@@ -50138,7 +50138,7 @@
         <v>40</v>
       </c>
       <c r="C2917">
-        <v>7653</v>
+        <v>6138.7</v>
       </c>
       <c r="D2917" t="s">
         <v>2919</v>
@@ -50152,7 +50152,7 @@
         <v>41</v>
       </c>
       <c r="C2918">
-        <v>7194.3</v>
+        <v>6670.4</v>
       </c>
       <c r="D2918" t="s">
         <v>2920</v>
@@ -50166,7 +50166,7 @@
         <v>42</v>
       </c>
       <c r="C2919">
-        <v>7257.6</v>
+        <v>6629.6</v>
       </c>
       <c r="D2919" t="s">
         <v>2921</v>
@@ -50180,7 +50180,7 @@
         <v>43</v>
       </c>
       <c r="C2920">
-        <v>7303.4</v>
+        <v>6329.6</v>
       </c>
       <c r="D2920" t="s">
         <v>2922</v>
@@ -50194,7 +50194,7 @@
         <v>44</v>
       </c>
       <c r="C2921">
-        <v>7313.2</v>
+        <v>5776.3</v>
       </c>
       <c r="D2921" t="s">
         <v>2923</v>
@@ -50208,7 +50208,7 @@
         <v>45</v>
       </c>
       <c r="C2922">
-        <v>7371.4</v>
+        <v>6882.1</v>
       </c>
       <c r="D2922" t="s">
         <v>2924</v>
@@ -50222,7 +50222,7 @@
         <v>46</v>
       </c>
       <c r="C2923">
-        <v>7364.7</v>
+        <v>6523.3</v>
       </c>
       <c r="D2923" t="s">
         <v>2925</v>
@@ -50236,7 +50236,7 @@
         <v>47</v>
       </c>
       <c r="C2924">
-        <v>7315.2</v>
+        <v>6039.8</v>
       </c>
       <c r="D2924" t="s">
         <v>2926</v>
@@ -50250,7 +50250,7 @@
         <v>48</v>
       </c>
       <c r="C2925">
-        <v>7284.6</v>
+        <v>5781.6</v>
       </c>
       <c r="D2925" t="s">
         <v>2927</v>
@@ -50264,7 +50264,7 @@
         <v>49</v>
       </c>
       <c r="C2926">
-        <v>7345.8</v>
+        <v>5063.1</v>
       </c>
       <c r="D2926" t="s">
         <v>2928</v>
@@ -50278,7 +50278,7 @@
         <v>50</v>
       </c>
       <c r="C2927">
-        <v>7306.9</v>
+        <v>4804.2</v>
       </c>
       <c r="D2927" t="s">
         <v>2929</v>
@@ -50292,7 +50292,7 @@
         <v>51</v>
       </c>
       <c r="C2928">
-        <v>7247.4</v>
+        <v>4785.7</v>
       </c>
       <c r="D2928" t="s">
         <v>2930</v>
@@ -50306,7 +50306,7 @@
         <v>52</v>
       </c>
       <c r="C2929">
-        <v>7196.2</v>
+        <v>4685.4</v>
       </c>
       <c r="D2929" t="s">
         <v>2931</v>
@@ -50320,7 +50320,7 @@
         <v>53</v>
       </c>
       <c r="C2930">
-        <v>6988.1</v>
+        <v>4910</v>
       </c>
       <c r="D2930" t="s">
         <v>2932</v>
@@ -50334,7 +50334,7 @@
         <v>54</v>
       </c>
       <c r="C2931">
-        <v>6925.8</v>
+        <v>4867.9</v>
       </c>
       <c r="D2931" t="s">
         <v>2933</v>
@@ -50348,7 +50348,7 @@
         <v>55</v>
       </c>
       <c r="C2932">
-        <v>6866.4</v>
+        <v>4753.7</v>
       </c>
       <c r="D2932" t="s">
         <v>2934</v>
@@ -50362,7 +50362,7 @@
         <v>56</v>
       </c>
       <c r="C2933">
-        <v>6774.2</v>
+        <v>4577.1</v>
       </c>
       <c r="D2933" t="s">
         <v>2935</v>
@@ -50376,7 +50376,7 @@
         <v>57</v>
       </c>
       <c r="C2934">
-        <v>6760.8</v>
+        <v>5200.5</v>
       </c>
       <c r="D2934" t="s">
         <v>2936</v>
@@ -50390,7 +50390,7 @@
         <v>58</v>
       </c>
       <c r="C2935">
-        <v>6656.4</v>
+        <v>4977.2</v>
       </c>
       <c r="D2935" t="s">
         <v>2937</v>
@@ -50404,7 +50404,7 @@
         <v>59</v>
       </c>
       <c r="C2936">
-        <v>6590.8</v>
+        <v>5131.8</v>
       </c>
       <c r="D2936" t="s">
         <v>2938</v>
@@ -50418,7 +50418,7 @@
         <v>60</v>
       </c>
       <c r="C2937">
-        <v>6558.1</v>
+        <v>5278.1</v>
       </c>
       <c r="D2937" t="s">
         <v>2939</v>
@@ -50432,7 +50432,7 @@
         <v>61</v>
       </c>
       <c r="C2938">
-        <v>6858.4</v>
+        <v>5794.1</v>
       </c>
       <c r="D2938" t="s">
         <v>2940</v>
@@ -50446,7 +50446,7 @@
         <v>62</v>
       </c>
       <c r="C2939">
-        <v>6796.2</v>
+        <v>6032.7</v>
       </c>
       <c r="D2939" t="s">
         <v>2941</v>
@@ -50460,7 +50460,7 @@
         <v>63</v>
       </c>
       <c r="C2940">
-        <v>6728.1</v>
+        <v>6536</v>
       </c>
       <c r="D2940" t="s">
         <v>2942</v>
@@ -50474,7 +50474,7 @@
         <v>64</v>
       </c>
       <c r="C2941">
-        <v>6661.4</v>
+        <v>6868.5</v>
       </c>
       <c r="D2941" t="s">
         <v>2943</v>
@@ -50488,7 +50488,7 @@
         <v>65</v>
       </c>
       <c r="C2942">
-        <v>6576.1</v>
+        <v>6802.8</v>
       </c>
       <c r="D2942" t="s">
         <v>2944</v>
@@ -50502,7 +50502,7 @@
         <v>66</v>
       </c>
       <c r="C2943">
-        <v>6464.9</v>
+        <v>7089.2</v>
       </c>
       <c r="D2943" t="s">
         <v>2945</v>
@@ -50516,7 +50516,7 @@
         <v>67</v>
       </c>
       <c r="C2944">
-        <v>6342</v>
+        <v>7176.7</v>
       </c>
       <c r="D2944" t="s">
         <v>2946</v>
@@ -50530,7 +50530,7 @@
         <v>68</v>
       </c>
       <c r="C2945">
-        <v>6277.1</v>
+        <v>7080</v>
       </c>
       <c r="D2945" t="s">
         <v>2947</v>
@@ -50544,7 +50544,7 @@
         <v>69</v>
       </c>
       <c r="C2946">
-        <v>6136.4</v>
+        <v>7127.1</v>
       </c>
       <c r="D2946" t="s">
         <v>2948</v>
@@ -50558,7 +50558,7 @@
         <v>70</v>
       </c>
       <c r="C2947">
-        <v>6020.2</v>
+        <v>7272.6</v>
       </c>
       <c r="D2947" t="s">
         <v>2949</v>
@@ -50572,7 +50572,7 @@
         <v>71</v>
       </c>
       <c r="C2948">
-        <v>5947.9</v>
+        <v>7145.6</v>
       </c>
       <c r="D2948" t="s">
         <v>2950</v>
@@ -50586,7 +50586,7 @@
         <v>72</v>
       </c>
       <c r="C2949">
-        <v>5904.4</v>
+        <v>7096.1</v>
       </c>
       <c r="D2949" t="s">
         <v>2951</v>
@@ -50600,7 +50600,7 @@
         <v>73</v>
       </c>
       <c r="C2950">
-        <v>5993</v>
+        <v>7130.5</v>
       </c>
       <c r="D2950" t="s">
         <v>2952</v>
@@ -50614,7 +50614,7 @@
         <v>74</v>
       </c>
       <c r="C2951">
-        <v>5950.2</v>
+        <v>7021.8</v>
       </c>
       <c r="D2951" t="s">
         <v>2953</v>
@@ -50628,7 +50628,7 @@
         <v>75</v>
       </c>
       <c r="C2952">
-        <v>5901.8</v>
+        <v>7386.6</v>
       </c>
       <c r="D2952" t="s">
         <v>2954</v>
@@ -50642,7 +50642,7 @@
         <v>76</v>
       </c>
       <c r="C2953">
-        <v>5881.1</v>
+        <v>7716.3</v>
       </c>
       <c r="D2953" t="s">
         <v>2955</v>
@@ -50656,7 +50656,7 @@
         <v>77</v>
       </c>
       <c r="C2954">
-        <v>6021.7</v>
+        <v>8076.4</v>
       </c>
       <c r="D2954" t="s">
         <v>2956</v>
@@ -50670,7 +50670,7 @@
         <v>78</v>
       </c>
       <c r="C2955">
-        <v>6083.6</v>
+        <v>8235.1</v>
       </c>
       <c r="D2955" t="s">
         <v>2957</v>
@@ -50684,7 +50684,7 @@
         <v>79</v>
       </c>
       <c r="C2956">
-        <v>6150.8</v>
+        <v>8334.799999999999</v>
       </c>
       <c r="D2956" t="s">
         <v>2958</v>
@@ -50698,7 +50698,7 @@
         <v>80</v>
       </c>
       <c r="C2957">
-        <v>6294.8</v>
+        <v>8451.299999999999</v>
       </c>
       <c r="D2957" t="s">
         <v>2959</v>
@@ -50712,7 +50712,7 @@
         <v>81</v>
       </c>
       <c r="C2958">
-        <v>6480.1</v>
+        <v>8519.9</v>
       </c>
       <c r="D2958" t="s">
         <v>2960</v>
@@ -50726,7 +50726,7 @@
         <v>82</v>
       </c>
       <c r="C2959">
-        <v>6579.8</v>
+        <v>8642.200000000001</v>
       </c>
       <c r="D2959" t="s">
         <v>2961</v>
@@ -50740,7 +50740,7 @@
         <v>83</v>
       </c>
       <c r="C2960">
-        <v>6635</v>
+        <v>8742.4</v>
       </c>
       <c r="D2960" t="s">
         <v>2962</v>
@@ -50754,7 +50754,7 @@
         <v>84</v>
       </c>
       <c r="C2961">
-        <v>6638.8</v>
+        <v>8760</v>
       </c>
       <c r="D2961" t="s">
         <v>2963</v>
@@ -50768,7 +50768,7 @@
         <v>85</v>
       </c>
       <c r="C2962">
-        <v>6521.7</v>
+        <v>8116.8</v>
       </c>
       <c r="D2962" t="s">
         <v>2964</v>
@@ -50782,7 +50782,7 @@
         <v>86</v>
       </c>
       <c r="C2963">
-        <v>6453.8</v>
+        <v>7746.3</v>
       </c>
       <c r="D2963" t="s">
         <v>2965</v>
@@ -50796,7 +50796,7 @@
         <v>87</v>
       </c>
       <c r="C2964">
-        <v>6393</v>
+        <v>7420.7</v>
       </c>
       <c r="D2964" t="s">
         <v>2966</v>
@@ -50810,7 +50810,7 @@
         <v>88</v>
       </c>
       <c r="C2965">
-        <v>6327.7</v>
+        <v>7390.2</v>
       </c>
       <c r="D2965" t="s">
         <v>2967</v>
@@ -50824,7 +50824,7 @@
         <v>89</v>
       </c>
       <c r="C2966">
-        <v>6413.8</v>
+        <v>7553.7</v>
       </c>
       <c r="D2966" t="s">
         <v>2968</v>
@@ -50838,7 +50838,7 @@
         <v>90</v>
       </c>
       <c r="C2967">
-        <v>6347.2</v>
+        <v>7485.8</v>
       </c>
       <c r="D2967" t="s">
         <v>2969</v>
@@ -50852,7 +50852,7 @@
         <v>91</v>
       </c>
       <c r="C2968">
-        <v>6284.2</v>
+        <v>7270.2</v>
       </c>
       <c r="D2968" t="s">
         <v>2970</v>
@@ -50866,7 +50866,7 @@
         <v>92</v>
       </c>
       <c r="C2969">
-        <v>6237.9</v>
+        <v>7070.2</v>
       </c>
       <c r="D2969" t="s">
         <v>2971</v>
@@ -50880,7 +50880,7 @@
         <v>93</v>
       </c>
       <c r="C2970">
-        <v>6060.6</v>
+        <v>7078.5</v>
       </c>
       <c r="D2970" t="s">
         <v>2972</v>
@@ -50894,7 +50894,7 @@
         <v>94</v>
       </c>
       <c r="C2971">
-        <v>6017.6</v>
+        <v>7034.1</v>
       </c>
       <c r="D2971" t="s">
         <v>2973</v>
@@ -50908,7 +50908,7 @@
         <v>95</v>
       </c>
       <c r="C2972">
-        <v>5992.5</v>
+        <v>7078.7</v>
       </c>
       <c r="D2972" t="s">
         <v>2974</v>
@@ -50922,7 +50922,7 @@
         <v>96</v>
       </c>
       <c r="C2973">
-        <v>5964.2</v>
+        <v>6719.5</v>
       </c>
       <c r="D2973" t="s">
         <v>2975</v>

--- a/Market Fundamentals/Transelectrica_data/Cons_Prod_final/Weekly_Production_2026.xlsx
+++ b/Market Fundamentals/Transelectrica_data/Cons_Prod_final/Weekly_Production_2026.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2692" uniqueCount="2692">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2884" uniqueCount="2884">
   <si>
     <t>Date</t>
   </si>
@@ -8090,6 +8090,582 @@
   </si>
   <si>
     <t>28.04.202696.0</t>
+  </si>
+  <si>
+    <t>29.04.20261.0</t>
+  </si>
+  <si>
+    <t>29.04.20262.0</t>
+  </si>
+  <si>
+    <t>29.04.20263.0</t>
+  </si>
+  <si>
+    <t>29.04.20264.0</t>
+  </si>
+  <si>
+    <t>29.04.20265.0</t>
+  </si>
+  <si>
+    <t>29.04.20266.0</t>
+  </si>
+  <si>
+    <t>29.04.20267.0</t>
+  </si>
+  <si>
+    <t>29.04.20268.0</t>
+  </si>
+  <si>
+    <t>29.04.20269.0</t>
+  </si>
+  <si>
+    <t>29.04.202610.0</t>
+  </si>
+  <si>
+    <t>29.04.202611.0</t>
+  </si>
+  <si>
+    <t>29.04.202612.0</t>
+  </si>
+  <si>
+    <t>29.04.202613.0</t>
+  </si>
+  <si>
+    <t>29.04.202614.0</t>
+  </si>
+  <si>
+    <t>29.04.202615.0</t>
+  </si>
+  <si>
+    <t>29.04.202616.0</t>
+  </si>
+  <si>
+    <t>29.04.202617.0</t>
+  </si>
+  <si>
+    <t>29.04.202618.0</t>
+  </si>
+  <si>
+    <t>29.04.202619.0</t>
+  </si>
+  <si>
+    <t>29.04.202620.0</t>
+  </si>
+  <si>
+    <t>29.04.202621.0</t>
+  </si>
+  <si>
+    <t>29.04.202622.0</t>
+  </si>
+  <si>
+    <t>29.04.202623.0</t>
+  </si>
+  <si>
+    <t>29.04.202624.0</t>
+  </si>
+  <si>
+    <t>29.04.202625.0</t>
+  </si>
+  <si>
+    <t>29.04.202626.0</t>
+  </si>
+  <si>
+    <t>29.04.202627.0</t>
+  </si>
+  <si>
+    <t>29.04.202628.0</t>
+  </si>
+  <si>
+    <t>29.04.202629.0</t>
+  </si>
+  <si>
+    <t>29.04.202630.0</t>
+  </si>
+  <si>
+    <t>29.04.202631.0</t>
+  </si>
+  <si>
+    <t>29.04.202632.0</t>
+  </si>
+  <si>
+    <t>29.04.202633.0</t>
+  </si>
+  <si>
+    <t>29.04.202634.0</t>
+  </si>
+  <si>
+    <t>29.04.202635.0</t>
+  </si>
+  <si>
+    <t>29.04.202636.0</t>
+  </si>
+  <si>
+    <t>29.04.202637.0</t>
+  </si>
+  <si>
+    <t>29.04.202638.0</t>
+  </si>
+  <si>
+    <t>29.04.202639.0</t>
+  </si>
+  <si>
+    <t>29.04.202640.0</t>
+  </si>
+  <si>
+    <t>29.04.202641.0</t>
+  </si>
+  <si>
+    <t>29.04.202642.0</t>
+  </si>
+  <si>
+    <t>29.04.202643.0</t>
+  </si>
+  <si>
+    <t>29.04.202644.0</t>
+  </si>
+  <si>
+    <t>29.04.202645.0</t>
+  </si>
+  <si>
+    <t>29.04.202646.0</t>
+  </si>
+  <si>
+    <t>29.04.202647.0</t>
+  </si>
+  <si>
+    <t>29.04.202648.0</t>
+  </si>
+  <si>
+    <t>29.04.202649.0</t>
+  </si>
+  <si>
+    <t>29.04.202650.0</t>
+  </si>
+  <si>
+    <t>29.04.202651.0</t>
+  </si>
+  <si>
+    <t>29.04.202652.0</t>
+  </si>
+  <si>
+    <t>29.04.202653.0</t>
+  </si>
+  <si>
+    <t>29.04.202654.0</t>
+  </si>
+  <si>
+    <t>29.04.202655.0</t>
+  </si>
+  <si>
+    <t>29.04.202656.0</t>
+  </si>
+  <si>
+    <t>29.04.202657.0</t>
+  </si>
+  <si>
+    <t>29.04.202658.0</t>
+  </si>
+  <si>
+    <t>29.04.202659.0</t>
+  </si>
+  <si>
+    <t>29.04.202660.0</t>
+  </si>
+  <si>
+    <t>29.04.202661.0</t>
+  </si>
+  <si>
+    <t>29.04.202662.0</t>
+  </si>
+  <si>
+    <t>29.04.202663.0</t>
+  </si>
+  <si>
+    <t>29.04.202664.0</t>
+  </si>
+  <si>
+    <t>29.04.202665.0</t>
+  </si>
+  <si>
+    <t>29.04.202666.0</t>
+  </si>
+  <si>
+    <t>29.04.202667.0</t>
+  </si>
+  <si>
+    <t>29.04.202668.0</t>
+  </si>
+  <si>
+    <t>29.04.202669.0</t>
+  </si>
+  <si>
+    <t>29.04.202670.0</t>
+  </si>
+  <si>
+    <t>29.04.202671.0</t>
+  </si>
+  <si>
+    <t>29.04.202672.0</t>
+  </si>
+  <si>
+    <t>29.04.202673.0</t>
+  </si>
+  <si>
+    <t>29.04.202674.0</t>
+  </si>
+  <si>
+    <t>29.04.202675.0</t>
+  </si>
+  <si>
+    <t>29.04.202676.0</t>
+  </si>
+  <si>
+    <t>29.04.202677.0</t>
+  </si>
+  <si>
+    <t>29.04.202678.0</t>
+  </si>
+  <si>
+    <t>29.04.202679.0</t>
+  </si>
+  <si>
+    <t>29.04.202680.0</t>
+  </si>
+  <si>
+    <t>29.04.202681.0</t>
+  </si>
+  <si>
+    <t>29.04.202682.0</t>
+  </si>
+  <si>
+    <t>29.04.202683.0</t>
+  </si>
+  <si>
+    <t>29.04.202684.0</t>
+  </si>
+  <si>
+    <t>29.04.202685.0</t>
+  </si>
+  <si>
+    <t>29.04.202686.0</t>
+  </si>
+  <si>
+    <t>29.04.202687.0</t>
+  </si>
+  <si>
+    <t>29.04.202688.0</t>
+  </si>
+  <si>
+    <t>29.04.202689.0</t>
+  </si>
+  <si>
+    <t>29.04.202690.0</t>
+  </si>
+  <si>
+    <t>29.04.202691.0</t>
+  </si>
+  <si>
+    <t>29.04.202692.0</t>
+  </si>
+  <si>
+    <t>29.04.202693.0</t>
+  </si>
+  <si>
+    <t>29.04.202694.0</t>
+  </si>
+  <si>
+    <t>29.04.202695.0</t>
+  </si>
+  <si>
+    <t>29.04.202696.0</t>
+  </si>
+  <si>
+    <t>30.04.20261.0</t>
+  </si>
+  <si>
+    <t>30.04.20262.0</t>
+  </si>
+  <si>
+    <t>30.04.20263.0</t>
+  </si>
+  <si>
+    <t>30.04.20264.0</t>
+  </si>
+  <si>
+    <t>30.04.20265.0</t>
+  </si>
+  <si>
+    <t>30.04.20266.0</t>
+  </si>
+  <si>
+    <t>30.04.20267.0</t>
+  </si>
+  <si>
+    <t>30.04.20268.0</t>
+  </si>
+  <si>
+    <t>30.04.20269.0</t>
+  </si>
+  <si>
+    <t>30.04.202610.0</t>
+  </si>
+  <si>
+    <t>30.04.202611.0</t>
+  </si>
+  <si>
+    <t>30.04.202612.0</t>
+  </si>
+  <si>
+    <t>30.04.202613.0</t>
+  </si>
+  <si>
+    <t>30.04.202614.0</t>
+  </si>
+  <si>
+    <t>30.04.202615.0</t>
+  </si>
+  <si>
+    <t>30.04.202616.0</t>
+  </si>
+  <si>
+    <t>30.04.202617.0</t>
+  </si>
+  <si>
+    <t>30.04.202618.0</t>
+  </si>
+  <si>
+    <t>30.04.202619.0</t>
+  </si>
+  <si>
+    <t>30.04.202620.0</t>
+  </si>
+  <si>
+    <t>30.04.202621.0</t>
+  </si>
+  <si>
+    <t>30.04.202622.0</t>
+  </si>
+  <si>
+    <t>30.04.202623.0</t>
+  </si>
+  <si>
+    <t>30.04.202624.0</t>
+  </si>
+  <si>
+    <t>30.04.202625.0</t>
+  </si>
+  <si>
+    <t>30.04.202626.0</t>
+  </si>
+  <si>
+    <t>30.04.202627.0</t>
+  </si>
+  <si>
+    <t>30.04.202628.0</t>
+  </si>
+  <si>
+    <t>30.04.202629.0</t>
+  </si>
+  <si>
+    <t>30.04.202630.0</t>
+  </si>
+  <si>
+    <t>30.04.202631.0</t>
+  </si>
+  <si>
+    <t>30.04.202632.0</t>
+  </si>
+  <si>
+    <t>30.04.202633.0</t>
+  </si>
+  <si>
+    <t>30.04.202634.0</t>
+  </si>
+  <si>
+    <t>30.04.202635.0</t>
+  </si>
+  <si>
+    <t>30.04.202636.0</t>
+  </si>
+  <si>
+    <t>30.04.202637.0</t>
+  </si>
+  <si>
+    <t>30.04.202638.0</t>
+  </si>
+  <si>
+    <t>30.04.202639.0</t>
+  </si>
+  <si>
+    <t>30.04.202640.0</t>
+  </si>
+  <si>
+    <t>30.04.202641.0</t>
+  </si>
+  <si>
+    <t>30.04.202642.0</t>
+  </si>
+  <si>
+    <t>30.04.202643.0</t>
+  </si>
+  <si>
+    <t>30.04.202644.0</t>
+  </si>
+  <si>
+    <t>30.04.202645.0</t>
+  </si>
+  <si>
+    <t>30.04.202646.0</t>
+  </si>
+  <si>
+    <t>30.04.202647.0</t>
+  </si>
+  <si>
+    <t>30.04.202648.0</t>
+  </si>
+  <si>
+    <t>30.04.202649.0</t>
+  </si>
+  <si>
+    <t>30.04.202650.0</t>
+  </si>
+  <si>
+    <t>30.04.202651.0</t>
+  </si>
+  <si>
+    <t>30.04.202652.0</t>
+  </si>
+  <si>
+    <t>30.04.202653.0</t>
+  </si>
+  <si>
+    <t>30.04.202654.0</t>
+  </si>
+  <si>
+    <t>30.04.202655.0</t>
+  </si>
+  <si>
+    <t>30.04.202656.0</t>
+  </si>
+  <si>
+    <t>30.04.202657.0</t>
+  </si>
+  <si>
+    <t>30.04.202658.0</t>
+  </si>
+  <si>
+    <t>30.04.202659.0</t>
+  </si>
+  <si>
+    <t>30.04.202660.0</t>
+  </si>
+  <si>
+    <t>30.04.202661.0</t>
+  </si>
+  <si>
+    <t>30.04.202662.0</t>
+  </si>
+  <si>
+    <t>30.04.202663.0</t>
+  </si>
+  <si>
+    <t>30.04.202664.0</t>
+  </si>
+  <si>
+    <t>30.04.202665.0</t>
+  </si>
+  <si>
+    <t>30.04.202666.0</t>
+  </si>
+  <si>
+    <t>30.04.202667.0</t>
+  </si>
+  <si>
+    <t>30.04.202668.0</t>
+  </si>
+  <si>
+    <t>30.04.202669.0</t>
+  </si>
+  <si>
+    <t>30.04.202670.0</t>
+  </si>
+  <si>
+    <t>30.04.202671.0</t>
+  </si>
+  <si>
+    <t>30.04.202672.0</t>
+  </si>
+  <si>
+    <t>30.04.202673.0</t>
+  </si>
+  <si>
+    <t>30.04.202674.0</t>
+  </si>
+  <si>
+    <t>30.04.202675.0</t>
+  </si>
+  <si>
+    <t>30.04.202676.0</t>
+  </si>
+  <si>
+    <t>30.04.202677.0</t>
+  </si>
+  <si>
+    <t>30.04.202678.0</t>
+  </si>
+  <si>
+    <t>30.04.202679.0</t>
+  </si>
+  <si>
+    <t>30.04.202680.0</t>
+  </si>
+  <si>
+    <t>30.04.202681.0</t>
+  </si>
+  <si>
+    <t>30.04.202682.0</t>
+  </si>
+  <si>
+    <t>30.04.202683.0</t>
+  </si>
+  <si>
+    <t>30.04.202684.0</t>
+  </si>
+  <si>
+    <t>30.04.202685.0</t>
+  </si>
+  <si>
+    <t>30.04.202686.0</t>
+  </si>
+  <si>
+    <t>30.04.202687.0</t>
+  </si>
+  <si>
+    <t>30.04.202688.0</t>
+  </si>
+  <si>
+    <t>30.04.202689.0</t>
+  </si>
+  <si>
+    <t>30.04.202690.0</t>
+  </si>
+  <si>
+    <t>30.04.202691.0</t>
+  </si>
+  <si>
+    <t>30.04.202692.0</t>
+  </si>
+  <si>
+    <t>30.04.202693.0</t>
+  </si>
+  <si>
+    <t>30.04.202694.0</t>
+  </si>
+  <si>
+    <t>30.04.202695.0</t>
+  </si>
+  <si>
+    <t>30.04.202696.0</t>
   </si>
 </sst>
 </file>
@@ -8451,7 +9027,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D2689"/>
+  <dimension ref="A1:D2881"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -36700,7 +37276,7 @@
         <v>1</v>
       </c>
       <c r="C2018">
-        <v>5322.7</v>
+        <v>4629.4</v>
       </c>
       <c r="D2018" t="s">
         <v>2020</v>
@@ -36714,7 +37290,7 @@
         <v>2</v>
       </c>
       <c r="C2019">
-        <v>5348.7</v>
+        <v>4634.2</v>
       </c>
       <c r="D2019" t="s">
         <v>2021</v>
@@ -36728,7 +37304,7 @@
         <v>3</v>
       </c>
       <c r="C2020">
-        <v>5374.2</v>
+        <v>4610.5</v>
       </c>
       <c r="D2020" t="s">
         <v>2022</v>
@@ -36742,7 +37318,7 @@
         <v>4</v>
       </c>
       <c r="C2021">
-        <v>5397.3</v>
+        <v>4627.2</v>
       </c>
       <c r="D2021" t="s">
         <v>2023</v>
@@ -36756,7 +37332,7 @@
         <v>5</v>
       </c>
       <c r="C2022">
-        <v>5246.8</v>
+        <v>4477.7</v>
       </c>
       <c r="D2022" t="s">
         <v>2024</v>
@@ -36770,7 +37346,7 @@
         <v>6</v>
       </c>
       <c r="C2023">
-        <v>5255.3</v>
+        <v>4464</v>
       </c>
       <c r="D2023" t="s">
         <v>2025</v>
@@ -36784,7 +37360,7 @@
         <v>7</v>
       </c>
       <c r="C2024">
-        <v>5273.6</v>
+        <v>4465.5</v>
       </c>
       <c r="D2024" t="s">
         <v>2026</v>
@@ -36798,7 +37374,7 @@
         <v>8</v>
       </c>
       <c r="C2025">
-        <v>5301.9</v>
+        <v>4466.7</v>
       </c>
       <c r="D2025" t="s">
         <v>2027</v>
@@ -36812,7 +37388,7 @@
         <v>9</v>
       </c>
       <c r="C2026">
-        <v>5231</v>
+        <v>4315.6</v>
       </c>
       <c r="D2026" t="s">
         <v>2028</v>
@@ -36826,7 +37402,7 @@
         <v>10</v>
       </c>
       <c r="C2027">
-        <v>5251.9</v>
+        <v>4324.2</v>
       </c>
       <c r="D2027" t="s">
         <v>2029</v>
@@ -36840,7 +37416,7 @@
         <v>11</v>
       </c>
       <c r="C2028">
-        <v>5265.6</v>
+        <v>4325.5</v>
       </c>
       <c r="D2028" t="s">
         <v>2030</v>
@@ -36854,7 +37430,7 @@
         <v>12</v>
       </c>
       <c r="C2029">
-        <v>5293.9</v>
+        <v>4325.6</v>
       </c>
       <c r="D2029" t="s">
         <v>2031</v>
@@ -36868,7 +37444,7 @@
         <v>13</v>
       </c>
       <c r="C2030">
-        <v>5318.8</v>
+        <v>4305.6</v>
       </c>
       <c r="D2030" t="s">
         <v>2032</v>
@@ -36882,7 +37458,7 @@
         <v>14</v>
       </c>
       <c r="C2031">
-        <v>5341.4</v>
+        <v>4314</v>
       </c>
       <c r="D2031" t="s">
         <v>2033</v>
@@ -36896,7 +37472,7 @@
         <v>15</v>
       </c>
       <c r="C2032">
-        <v>5378.8</v>
+        <v>4321.9</v>
       </c>
       <c r="D2032" t="s">
         <v>2034</v>
@@ -36910,7 +37486,7 @@
         <v>16</v>
       </c>
       <c r="C2033">
-        <v>5427.2</v>
+        <v>4326.3</v>
       </c>
       <c r="D2033" t="s">
         <v>2035</v>
@@ -36924,7 +37500,7 @@
         <v>17</v>
       </c>
       <c r="C2034">
-        <v>5307.7</v>
+        <v>4213.7</v>
       </c>
       <c r="D2034" t="s">
         <v>2036</v>
@@ -36938,7 +37514,7 @@
         <v>18</v>
       </c>
       <c r="C2035">
-        <v>5342.2</v>
+        <v>4217.4</v>
       </c>
       <c r="D2035" t="s">
         <v>2037</v>
@@ -36952,7 +37528,7 @@
         <v>19</v>
       </c>
       <c r="C2036">
-        <v>5377.4</v>
+        <v>4220.4</v>
       </c>
       <c r="D2036" t="s">
         <v>2038</v>
@@ -36966,7 +37542,7 @@
         <v>20</v>
       </c>
       <c r="C2037">
-        <v>5408.8</v>
+        <v>4220.2</v>
       </c>
       <c r="D2037" t="s">
         <v>2039</v>
@@ -36980,7 +37556,7 @@
         <v>21</v>
       </c>
       <c r="C2038">
-        <v>5450.7</v>
+        <v>4225.3</v>
       </c>
       <c r="D2038" t="s">
         <v>2040</v>
@@ -36994,7 +37570,7 @@
         <v>22</v>
       </c>
       <c r="C2039">
-        <v>5504.6</v>
+        <v>4246.4</v>
       </c>
       <c r="D2039" t="s">
         <v>2041</v>
@@ -37008,7 +37584,7 @@
         <v>23</v>
       </c>
       <c r="C2040">
-        <v>5545.2</v>
+        <v>4262.8</v>
       </c>
       <c r="D2040" t="s">
         <v>2042</v>
@@ -37022,7 +37598,7 @@
         <v>24</v>
       </c>
       <c r="C2041">
-        <v>5601.9</v>
+        <v>4285.1</v>
       </c>
       <c r="D2041" t="s">
         <v>2043</v>
@@ -37036,7 +37612,7 @@
         <v>25</v>
       </c>
       <c r="C2042">
-        <v>5874.8</v>
+        <v>4372.3</v>
       </c>
       <c r="D2042" t="s">
         <v>2044</v>
@@ -37050,7 +37626,7 @@
         <v>26</v>
       </c>
       <c r="C2043">
-        <v>5946.4</v>
+        <v>4435.3</v>
       </c>
       <c r="D2043" t="s">
         <v>2045</v>
@@ -37064,7 +37640,7 @@
         <v>27</v>
       </c>
       <c r="C2044">
-        <v>6017.1</v>
+        <v>4497.4</v>
       </c>
       <c r="D2044" t="s">
         <v>2046</v>
@@ -37078,7 +37654,7 @@
         <v>28</v>
       </c>
       <c r="C2045">
-        <v>6063.4</v>
+        <v>4524.8</v>
       </c>
       <c r="D2045" t="s">
         <v>2047</v>
@@ -37092,7 +37668,7 @@
         <v>29</v>
       </c>
       <c r="C2046">
-        <v>6260.2</v>
+        <v>4841.5</v>
       </c>
       <c r="D2046" t="s">
         <v>2048</v>
@@ -37106,7 +37682,7 @@
         <v>30</v>
       </c>
       <c r="C2047">
-        <v>6293.1</v>
+        <v>4903.3</v>
       </c>
       <c r="D2047" t="s">
         <v>2049</v>
@@ -37120,7 +37696,7 @@
         <v>31</v>
       </c>
       <c r="C2048">
-        <v>6343</v>
+        <v>5004.3</v>
       </c>
       <c r="D2048" t="s">
         <v>2050</v>
@@ -37134,7 +37710,7 @@
         <v>32</v>
       </c>
       <c r="C2049">
-        <v>6408.9</v>
+        <v>5123.6</v>
       </c>
       <c r="D2049" t="s">
         <v>2051</v>
@@ -37148,7 +37724,7 @@
         <v>33</v>
       </c>
       <c r="C2050">
-        <v>6339.7</v>
+        <v>5138.1</v>
       </c>
       <c r="D2050" t="s">
         <v>2052</v>
@@ -37162,7 +37738,7 @@
         <v>34</v>
       </c>
       <c r="C2051">
-        <v>6360.8</v>
+        <v>5230.9</v>
       </c>
       <c r="D2051" t="s">
         <v>2053</v>
@@ -37176,7 +37752,7 @@
         <v>35</v>
       </c>
       <c r="C2052">
-        <v>6395.6</v>
+        <v>5339</v>
       </c>
       <c r="D2052" t="s">
         <v>2054</v>
@@ -37190,7 +37766,7 @@
         <v>36</v>
       </c>
       <c r="C2053">
-        <v>6407.9</v>
+        <v>5422.2</v>
       </c>
       <c r="D2053" t="s">
         <v>2055</v>
@@ -37204,7 +37780,7 @@
         <v>37</v>
       </c>
       <c r="C2054">
-        <v>6055.2</v>
+        <v>5020</v>
       </c>
       <c r="D2054" t="s">
         <v>2056</v>
@@ -37218,7 +37794,7 @@
         <v>38</v>
       </c>
       <c r="C2055">
-        <v>6043.6</v>
+        <v>5065.5</v>
       </c>
       <c r="D2055" t="s">
         <v>2057</v>
@@ -37232,7 +37808,7 @@
         <v>39</v>
       </c>
       <c r="C2056">
-        <v>6029.7</v>
+        <v>5145.2</v>
       </c>
       <c r="D2056" t="s">
         <v>2058</v>
@@ -37246,7 +37822,7 @@
         <v>40</v>
       </c>
       <c r="C2057">
-        <v>6024.1</v>
+        <v>5190.4</v>
       </c>
       <c r="D2057" t="s">
         <v>2059</v>
@@ -37260,7 +37836,7 @@
         <v>41</v>
       </c>
       <c r="C2058">
-        <v>5946.5</v>
+        <v>5208.2</v>
       </c>
       <c r="D2058" t="s">
         <v>2060</v>
@@ -37274,7 +37850,7 @@
         <v>42</v>
       </c>
       <c r="C2059">
-        <v>5949.3</v>
+        <v>5227.1</v>
       </c>
       <c r="D2059" t="s">
         <v>2061</v>
@@ -37288,7 +37864,7 @@
         <v>43</v>
       </c>
       <c r="C2060">
-        <v>5924.5</v>
+        <v>5259.3</v>
       </c>
       <c r="D2060" t="s">
         <v>2062</v>
@@ -37302,7 +37878,7 @@
         <v>44</v>
       </c>
       <c r="C2061">
-        <v>5902.2</v>
+        <v>5286.7</v>
       </c>
       <c r="D2061" t="s">
         <v>2063</v>
@@ -37316,7 +37892,7 @@
         <v>45</v>
       </c>
       <c r="C2062">
-        <v>5795.7</v>
+        <v>5320.3</v>
       </c>
       <c r="D2062" t="s">
         <v>2064</v>
@@ -37330,7 +37906,7 @@
         <v>46</v>
       </c>
       <c r="C2063">
-        <v>5781</v>
+        <v>5335.9</v>
       </c>
       <c r="D2063" t="s">
         <v>2065</v>
@@ -37344,7 +37920,7 @@
         <v>47</v>
       </c>
       <c r="C2064">
-        <v>5750.7</v>
+        <v>5357.7</v>
       </c>
       <c r="D2064" t="s">
         <v>2066</v>
@@ -37358,7 +37934,7 @@
         <v>48</v>
       </c>
       <c r="C2065">
-        <v>5723.1</v>
+        <v>5386.3</v>
       </c>
       <c r="D2065" t="s">
         <v>2067</v>
@@ -37372,7 +37948,7 @@
         <v>49</v>
       </c>
       <c r="C2066">
-        <v>5632.3</v>
+        <v>5312.3</v>
       </c>
       <c r="D2066" t="s">
         <v>2068</v>
@@ -37386,7 +37962,7 @@
         <v>50</v>
       </c>
       <c r="C2067">
-        <v>5602.1</v>
+        <v>5346.7</v>
       </c>
       <c r="D2067" t="s">
         <v>2069</v>
@@ -37400,7 +37976,7 @@
         <v>51</v>
       </c>
       <c r="C2068">
-        <v>5550</v>
+        <v>5345.8</v>
       </c>
       <c r="D2068" t="s">
         <v>2070</v>
@@ -37414,7 +37990,7 @@
         <v>52</v>
       </c>
       <c r="C2069">
-        <v>5500.9</v>
+        <v>5365.2</v>
       </c>
       <c r="D2069" t="s">
         <v>2071</v>
@@ -37428,7 +38004,7 @@
         <v>53</v>
       </c>
       <c r="C2070">
-        <v>5438.5</v>
+        <v>5460.3</v>
       </c>
       <c r="D2070" t="s">
         <v>2072</v>
@@ -37442,7 +38018,7 @@
         <v>54</v>
       </c>
       <c r="C2071">
-        <v>5371.6</v>
+        <v>5443.1</v>
       </c>
       <c r="D2071" t="s">
         <v>2073</v>
@@ -37456,7 +38032,7 @@
         <v>55</v>
       </c>
       <c r="C2072">
-        <v>5323.4</v>
+        <v>5446.8</v>
       </c>
       <c r="D2072" t="s">
         <v>2074</v>
@@ -37470,7 +38046,7 @@
         <v>56</v>
       </c>
       <c r="C2073">
-        <v>5297.1</v>
+        <v>5459.3</v>
       </c>
       <c r="D2073" t="s">
         <v>2075</v>
@@ -37484,7 +38060,7 @@
         <v>57</v>
       </c>
       <c r="C2074">
-        <v>5261.9</v>
+        <v>5531.7</v>
       </c>
       <c r="D2074" t="s">
         <v>2076</v>
@@ -37498,7 +38074,7 @@
         <v>58</v>
       </c>
       <c r="C2075">
-        <v>5225.3</v>
+        <v>5530.1</v>
       </c>
       <c r="D2075" t="s">
         <v>2077</v>
@@ -37512,7 +38088,7 @@
         <v>59</v>
       </c>
       <c r="C2076">
-        <v>5186.1</v>
+        <v>5515.2</v>
       </c>
       <c r="D2076" t="s">
         <v>2078</v>
@@ -37526,7 +38102,7 @@
         <v>60</v>
       </c>
       <c r="C2077">
-        <v>5140.9</v>
+        <v>5516.3</v>
       </c>
       <c r="D2077" t="s">
         <v>2079</v>
@@ -37540,7 +38116,7 @@
         <v>61</v>
       </c>
       <c r="C2078">
-        <v>5078.3</v>
+        <v>5127.2</v>
       </c>
       <c r="D2078" t="s">
         <v>2080</v>
@@ -37554,7 +38130,7 @@
         <v>62</v>
       </c>
       <c r="C2079">
-        <v>5013.9</v>
+        <v>5085.1</v>
       </c>
       <c r="D2079" t="s">
         <v>2081</v>
@@ -37568,7 +38144,7 @@
         <v>63</v>
       </c>
       <c r="C2080">
-        <v>4969.7</v>
+        <v>5047.4</v>
       </c>
       <c r="D2080" t="s">
         <v>2082</v>
@@ -37582,7 +38158,7 @@
         <v>64</v>
       </c>
       <c r="C2081">
-        <v>4900.3</v>
+        <v>5026.1</v>
       </c>
       <c r="D2081" t="s">
         <v>2083</v>
@@ -37596,7 +38172,7 @@
         <v>65</v>
       </c>
       <c r="C2082">
-        <v>4861.4</v>
+        <v>4957.2</v>
       </c>
       <c r="D2082" t="s">
         <v>2084</v>
@@ -37610,7 +38186,7 @@
         <v>66</v>
       </c>
       <c r="C2083">
-        <v>4789.4</v>
+        <v>4908.1</v>
       </c>
       <c r="D2083" t="s">
         <v>2085</v>
@@ -37624,7 +38200,7 @@
         <v>67</v>
       </c>
       <c r="C2084">
-        <v>4714</v>
+        <v>4840.6</v>
       </c>
       <c r="D2084" t="s">
         <v>2086</v>
@@ -37638,7 +38214,7 @@
         <v>68</v>
       </c>
       <c r="C2085">
-        <v>4721.4</v>
+        <v>4825</v>
       </c>
       <c r="D2085" t="s">
         <v>2087</v>
@@ -37652,7 +38228,7 @@
         <v>69</v>
       </c>
       <c r="C2086">
-        <v>4898.8</v>
+        <v>4924.5</v>
       </c>
       <c r="D2086" t="s">
         <v>2088</v>
@@ -37666,7 +38242,7 @@
         <v>70</v>
       </c>
       <c r="C2087">
-        <v>4881.5</v>
+        <v>4832.1</v>
       </c>
       <c r="D2087" t="s">
         <v>2089</v>
@@ -37680,7 +38256,7 @@
         <v>71</v>
       </c>
       <c r="C2088">
-        <v>4813.7</v>
+        <v>4759.4</v>
       </c>
       <c r="D2088" t="s">
         <v>2090</v>
@@ -37694,7 +38270,7 @@
         <v>72</v>
       </c>
       <c r="C2089">
-        <v>4821.2</v>
+        <v>4705</v>
       </c>
       <c r="D2089" t="s">
         <v>2091</v>
@@ -37708,7 +38284,7 @@
         <v>73</v>
       </c>
       <c r="C2090">
-        <v>5142.6</v>
+        <v>5057.7</v>
       </c>
       <c r="D2090" t="s">
         <v>2092</v>
@@ -37722,7 +38298,7 @@
         <v>74</v>
       </c>
       <c r="C2091">
-        <v>5128.8</v>
+        <v>5036.7</v>
       </c>
       <c r="D2091" t="s">
         <v>2093</v>
@@ -37736,7 +38312,7 @@
         <v>75</v>
       </c>
       <c r="C2092">
-        <v>5088</v>
+        <v>4985.7</v>
       </c>
       <c r="D2092" t="s">
         <v>2094</v>
@@ -37750,7 +38326,7 @@
         <v>76</v>
       </c>
       <c r="C2093">
-        <v>5138.3</v>
+        <v>4965.5</v>
       </c>
       <c r="D2093" t="s">
         <v>2095</v>
@@ -37764,7 +38340,7 @@
         <v>77</v>
       </c>
       <c r="C2094">
-        <v>5554.3</v>
+        <v>5105</v>
       </c>
       <c r="D2094" t="s">
         <v>2096</v>
@@ -37778,7 +38354,7 @@
         <v>78</v>
       </c>
       <c r="C2095">
-        <v>5626</v>
+        <v>5109</v>
       </c>
       <c r="D2095" t="s">
         <v>2097</v>
@@ -37792,7 +38368,7 @@
         <v>79</v>
       </c>
       <c r="C2096">
-        <v>5671.5</v>
+        <v>5122.2</v>
       </c>
       <c r="D2096" t="s">
         <v>2098</v>
@@ -37806,7 +38382,7 @@
         <v>80</v>
       </c>
       <c r="C2097">
-        <v>5709</v>
+        <v>5166</v>
       </c>
       <c r="D2097" t="s">
         <v>2099</v>
@@ -37820,7 +38396,7 @@
         <v>81</v>
       </c>
       <c r="C2098">
-        <v>5910.2</v>
+        <v>5365.2</v>
       </c>
       <c r="D2098" t="s">
         <v>2100</v>
@@ -37834,7 +38410,7 @@
         <v>82</v>
       </c>
       <c r="C2099">
-        <v>5904</v>
+        <v>5371.1</v>
       </c>
       <c r="D2099" t="s">
         <v>2101</v>
@@ -37848,7 +38424,7 @@
         <v>83</v>
       </c>
       <c r="C2100">
-        <v>5849.6</v>
+        <v>5348.2</v>
       </c>
       <c r="D2100" t="s">
         <v>2102</v>
@@ -37862,7 +38438,7 @@
         <v>84</v>
       </c>
       <c r="C2101">
-        <v>5858.3</v>
+        <v>5403.3</v>
       </c>
       <c r="D2101" t="s">
         <v>2103</v>
@@ -37876,7 +38452,7 @@
         <v>85</v>
       </c>
       <c r="C2102">
-        <v>5809.9</v>
+        <v>5337.4</v>
       </c>
       <c r="D2102" t="s">
         <v>2104</v>
@@ -37890,7 +38466,7 @@
         <v>86</v>
       </c>
       <c r="C2103">
-        <v>5791</v>
+        <v>5273.4</v>
       </c>
       <c r="D2103" t="s">
         <v>2105</v>
@@ -37904,7 +38480,7 @@
         <v>87</v>
       </c>
       <c r="C2104">
-        <v>5783</v>
+        <v>5253.3</v>
       </c>
       <c r="D2104" t="s">
         <v>2106</v>
@@ -37918,7 +38494,7 @@
         <v>88</v>
       </c>
       <c r="C2105">
-        <v>5749</v>
+        <v>5249.6</v>
       </c>
       <c r="D2105" t="s">
         <v>2107</v>
@@ -37932,7 +38508,7 @@
         <v>89</v>
       </c>
       <c r="C2106">
-        <v>5494.1</v>
+        <v>4814.6</v>
       </c>
       <c r="D2106" t="s">
         <v>2108</v>
@@ -37946,7 +38522,7 @@
         <v>90</v>
       </c>
       <c r="C2107">
-        <v>5476.3</v>
+        <v>4769.4</v>
       </c>
       <c r="D2107" t="s">
         <v>2109</v>
@@ -37960,7 +38536,7 @@
         <v>91</v>
       </c>
       <c r="C2108">
-        <v>5406.5</v>
+        <v>4707.8</v>
       </c>
       <c r="D2108" t="s">
         <v>2110</v>
@@ -37974,7 +38550,7 @@
         <v>92</v>
       </c>
       <c r="C2109">
-        <v>5390.5</v>
+        <v>4659.4</v>
       </c>
       <c r="D2109" t="s">
         <v>2111</v>
@@ -37988,7 +38564,7 @@
         <v>93</v>
       </c>
       <c r="C2110">
-        <v>5043</v>
+        <v>4748.1</v>
       </c>
       <c r="D2110" t="s">
         <v>2112</v>
@@ -38002,7 +38578,7 @@
         <v>94</v>
       </c>
       <c r="C2111">
-        <v>4978.6</v>
+        <v>4684.3</v>
       </c>
       <c r="D2111" t="s">
         <v>2113</v>
@@ -38016,7 +38592,7 @@
         <v>95</v>
       </c>
       <c r="C2112">
-        <v>4930.5</v>
+        <v>4642</v>
       </c>
       <c r="D2112" t="s">
         <v>2114</v>
@@ -38030,7 +38606,7 @@
         <v>96</v>
       </c>
       <c r="C2113">
-        <v>4876.6</v>
+        <v>4594</v>
       </c>
       <c r="D2113" t="s">
         <v>2115</v>
@@ -38044,7 +38620,7 @@
         <v>1</v>
       </c>
       <c r="C2114">
-        <v>4752.1</v>
+        <v>4731.2</v>
       </c>
       <c r="D2114" t="s">
         <v>2116</v>
@@ -38058,7 +38634,7 @@
         <v>2</v>
       </c>
       <c r="C2115">
-        <v>4724.4</v>
+        <v>4747.6</v>
       </c>
       <c r="D2115" t="s">
         <v>2117</v>
@@ -38072,7 +38648,7 @@
         <v>3</v>
       </c>
       <c r="C2116">
-        <v>4667.4</v>
+        <v>4723.2</v>
       </c>
       <c r="D2116" t="s">
         <v>2118</v>
@@ -38086,7 +38662,7 @@
         <v>4</v>
       </c>
       <c r="C2117">
-        <v>4660.4</v>
+        <v>4725.8</v>
       </c>
       <c r="D2117" t="s">
         <v>2119</v>
@@ -38100,7 +38676,7 @@
         <v>5</v>
       </c>
       <c r="C2118">
-        <v>4796.9</v>
+        <v>4503.8</v>
       </c>
       <c r="D2118" t="s">
         <v>2120</v>
@@ -38114,7 +38690,7 @@
         <v>6</v>
       </c>
       <c r="C2119">
-        <v>4749.2</v>
+        <v>4494.6</v>
       </c>
       <c r="D2119" t="s">
         <v>2121</v>
@@ -38128,7 +38704,7 @@
         <v>7</v>
       </c>
       <c r="C2120">
-        <v>4733.7</v>
+        <v>4513</v>
       </c>
       <c r="D2120" t="s">
         <v>2122</v>
@@ -38142,7 +38718,7 @@
         <v>8</v>
       </c>
       <c r="C2121">
-        <v>4724.8</v>
+        <v>4524.9</v>
       </c>
       <c r="D2121" t="s">
         <v>2123</v>
@@ -38156,7 +38732,7 @@
         <v>9</v>
       </c>
       <c r="C2122">
-        <v>4582.5</v>
+        <v>4366.8</v>
       </c>
       <c r="D2122" t="s">
         <v>2124</v>
@@ -38170,7 +38746,7 @@
         <v>10</v>
       </c>
       <c r="C2123">
-        <v>4561.7</v>
+        <v>4383.2</v>
       </c>
       <c r="D2123" t="s">
         <v>2125</v>
@@ -38184,7 +38760,7 @@
         <v>11</v>
       </c>
       <c r="C2124">
-        <v>4547.3</v>
+        <v>4402.3</v>
       </c>
       <c r="D2124" t="s">
         <v>2126</v>
@@ -38198,7 +38774,7 @@
         <v>12</v>
       </c>
       <c r="C2125">
-        <v>4550.6</v>
+        <v>4415.8</v>
       </c>
       <c r="D2125" t="s">
         <v>2127</v>
@@ -38212,7 +38788,7 @@
         <v>13</v>
       </c>
       <c r="C2126">
-        <v>4506.2</v>
+        <v>4429.2</v>
       </c>
       <c r="D2126" t="s">
         <v>2128</v>
@@ -38226,7 +38802,7 @@
         <v>14</v>
       </c>
       <c r="C2127">
-        <v>4502.6</v>
+        <v>4449</v>
       </c>
       <c r="D2127" t="s">
         <v>2129</v>
@@ -38240,7 +38816,7 @@
         <v>15</v>
       </c>
       <c r="C2128">
-        <v>4508</v>
+        <v>4471.2</v>
       </c>
       <c r="D2128" t="s">
         <v>2130</v>
@@ -38254,7 +38830,7 @@
         <v>16</v>
       </c>
       <c r="C2129">
-        <v>4480.7</v>
+        <v>4509.7</v>
       </c>
       <c r="D2129" t="s">
         <v>2131</v>
@@ -38268,7 +38844,7 @@
         <v>17</v>
       </c>
       <c r="C2130">
-        <v>4459.1</v>
+        <v>4524.1</v>
       </c>
       <c r="D2130" t="s">
         <v>2132</v>
@@ -38282,7 +38858,7 @@
         <v>18</v>
       </c>
       <c r="C2131">
-        <v>4468.3</v>
+        <v>4567.1</v>
       </c>
       <c r="D2131" t="s">
         <v>2133</v>
@@ -38296,7 +38872,7 @@
         <v>19</v>
       </c>
       <c r="C2132">
-        <v>4474.4</v>
+        <v>4595.6</v>
       </c>
       <c r="D2132" t="s">
         <v>2134</v>
@@ -38310,7 +38886,7 @@
         <v>20</v>
       </c>
       <c r="C2133">
-        <v>4477.1</v>
+        <v>4625.2</v>
       </c>
       <c r="D2133" t="s">
         <v>2135</v>
@@ -38324,7 +38900,7 @@
         <v>21</v>
       </c>
       <c r="C2134">
-        <v>4467.3</v>
+        <v>4624.3</v>
       </c>
       <c r="D2134" t="s">
         <v>2136</v>
@@ -38338,7 +38914,7 @@
         <v>22</v>
       </c>
       <c r="C2135">
-        <v>4467</v>
+        <v>4645.8</v>
       </c>
       <c r="D2135" t="s">
         <v>2137</v>
@@ -38352,7 +38928,7 @@
         <v>23</v>
       </c>
       <c r="C2136">
-        <v>4482.6</v>
+        <v>4651.8</v>
       </c>
       <c r="D2136" t="s">
         <v>2138</v>
@@ -38366,7 +38942,7 @@
         <v>24</v>
       </c>
       <c r="C2137">
-        <v>4498.9</v>
+        <v>4655.5</v>
       </c>
       <c r="D2137" t="s">
         <v>2139</v>
@@ -38380,7 +38956,7 @@
         <v>25</v>
       </c>
       <c r="C2138">
-        <v>4457</v>
+        <v>4829.9</v>
       </c>
       <c r="D2138" t="s">
         <v>2140</v>
@@ -38394,7 +38970,7 @@
         <v>26</v>
       </c>
       <c r="C2139">
-        <v>4514</v>
+        <v>4882.1</v>
       </c>
       <c r="D2139" t="s">
         <v>2141</v>
@@ -38408,7 +38984,7 @@
         <v>27</v>
       </c>
       <c r="C2140">
-        <v>4559.3</v>
+        <v>4933.2</v>
       </c>
       <c r="D2140" t="s">
         <v>2142</v>
@@ -38422,7 +38998,7 @@
         <v>28</v>
       </c>
       <c r="C2141">
-        <v>4615.6</v>
+        <v>4969.1</v>
       </c>
       <c r="D2141" t="s">
         <v>2143</v>
@@ -38436,7 +39012,7 @@
         <v>29</v>
       </c>
       <c r="C2142">
-        <v>4765.3</v>
+        <v>5313</v>
       </c>
       <c r="D2142" t="s">
         <v>2144</v>
@@ -38450,7 +39026,7 @@
         <v>30</v>
       </c>
       <c r="C2143">
-        <v>4837.1</v>
+        <v>5385.1</v>
       </c>
       <c r="D2143" t="s">
         <v>2145</v>
@@ -38464,7 +39040,7 @@
         <v>31</v>
       </c>
       <c r="C2144">
-        <v>4944.9</v>
+        <v>5485.3</v>
       </c>
       <c r="D2144" t="s">
         <v>2146</v>
@@ -38478,7 +39054,7 @@
         <v>32</v>
       </c>
       <c r="C2145">
-        <v>5066.1</v>
+        <v>5595.9</v>
       </c>
       <c r="D2145" t="s">
         <v>2147</v>
@@ -38492,7 +39068,7 @@
         <v>33</v>
       </c>
       <c r="C2146">
-        <v>5218.5</v>
+        <v>5752.9</v>
       </c>
       <c r="D2146" t="s">
         <v>2148</v>
@@ -38506,7 +39082,7 @@
         <v>34</v>
       </c>
       <c r="C2147">
-        <v>5333.2</v>
+        <v>5851.4</v>
       </c>
       <c r="D2147" t="s">
         <v>2149</v>
@@ -38520,7 +39096,7 @@
         <v>35</v>
       </c>
       <c r="C2148">
-        <v>5515.2</v>
+        <v>5946.6</v>
       </c>
       <c r="D2148" t="s">
         <v>2150</v>
@@ -38534,7 +39110,7 @@
         <v>36</v>
       </c>
       <c r="C2149">
-        <v>5663.3</v>
+        <v>6125.5</v>
       </c>
       <c r="D2149" t="s">
         <v>2151</v>
@@ -38548,7 +39124,7 @@
         <v>37</v>
       </c>
       <c r="C2150">
-        <v>5704.4</v>
+        <v>6078.1</v>
       </c>
       <c r="D2150" t="s">
         <v>2152</v>
@@ -38562,7 +39138,7 @@
         <v>38</v>
       </c>
       <c r="C2151">
-        <v>5808.2</v>
+        <v>6127.8</v>
       </c>
       <c r="D2151" t="s">
         <v>2153</v>
@@ -38576,7 +39152,7 @@
         <v>39</v>
       </c>
       <c r="C2152">
-        <v>5971.9</v>
+        <v>6276.2</v>
       </c>
       <c r="D2152" t="s">
         <v>2154</v>
@@ -38590,7 +39166,7 @@
         <v>40</v>
       </c>
       <c r="C2153">
-        <v>6117.3</v>
+        <v>6388.2</v>
       </c>
       <c r="D2153" t="s">
         <v>2155</v>
@@ -38604,7 +39180,7 @@
         <v>41</v>
       </c>
       <c r="C2154">
-        <v>6146.2</v>
+        <v>6488.3</v>
       </c>
       <c r="D2154" t="s">
         <v>2156</v>
@@ -38618,7 +39194,7 @@
         <v>42</v>
       </c>
       <c r="C2155">
-        <v>6229.7</v>
+        <v>6558.9</v>
       </c>
       <c r="D2155" t="s">
         <v>2157</v>
@@ -38632,7 +39208,7 @@
         <v>43</v>
       </c>
       <c r="C2156">
-        <v>6345.8</v>
+        <v>6673.2</v>
       </c>
       <c r="D2156" t="s">
         <v>2158</v>
@@ -38646,7 +39222,7 @@
         <v>44</v>
       </c>
       <c r="C2157">
-        <v>6418.2</v>
+        <v>6764.2</v>
       </c>
       <c r="D2157" t="s">
         <v>2159</v>
@@ -38660,7 +39236,7 @@
         <v>45</v>
       </c>
       <c r="C2158">
-        <v>6359.3</v>
+        <v>6336.6</v>
       </c>
       <c r="D2158" t="s">
         <v>2160</v>
@@ -38674,7 +39250,7 @@
         <v>46</v>
       </c>
       <c r="C2159">
-        <v>6390</v>
+        <v>6312.4</v>
       </c>
       <c r="D2159" t="s">
         <v>2161</v>
@@ -38688,7 +39264,7 @@
         <v>47</v>
       </c>
       <c r="C2160">
-        <v>6432.7</v>
+        <v>6140.9</v>
       </c>
       <c r="D2160" t="s">
         <v>2162</v>
@@ -38702,7 +39278,7 @@
         <v>48</v>
       </c>
       <c r="C2161">
-        <v>6462.3</v>
+        <v>6274.1</v>
       </c>
       <c r="D2161" t="s">
         <v>2163</v>
@@ -38716,7 +39292,7 @@
         <v>49</v>
       </c>
       <c r="C2162">
-        <v>6409.3</v>
+        <v>5999.6</v>
       </c>
       <c r="D2162" t="s">
         <v>2164</v>
@@ -38730,7 +39306,7 @@
         <v>50</v>
       </c>
       <c r="C2163">
-        <v>6415.7</v>
+        <v>5888.3</v>
       </c>
       <c r="D2163" t="s">
         <v>2165</v>
@@ -38744,7 +39320,7 @@
         <v>51</v>
       </c>
       <c r="C2164">
-        <v>6429.2</v>
+        <v>5837.2</v>
       </c>
       <c r="D2164" t="s">
         <v>2166</v>
@@ -38758,7 +39334,7 @@
         <v>52</v>
       </c>
       <c r="C2165">
-        <v>6470</v>
+        <v>5750</v>
       </c>
       <c r="D2165" t="s">
         <v>2167</v>
@@ -38772,7 +39348,7 @@
         <v>53</v>
       </c>
       <c r="C2166">
-        <v>6448.4</v>
+        <v>5478.1</v>
       </c>
       <c r="D2166" t="s">
         <v>2168</v>
@@ -38786,7 +39362,7 @@
         <v>54</v>
       </c>
       <c r="C2167">
-        <v>6458.4</v>
+        <v>5419.3</v>
       </c>
       <c r="D2167" t="s">
         <v>2169</v>
@@ -38800,7 +39376,7 @@
         <v>55</v>
       </c>
       <c r="C2168">
-        <v>6445.3</v>
+        <v>5420.3</v>
       </c>
       <c r="D2168" t="s">
         <v>2170</v>
@@ -38814,7 +39390,7 @@
         <v>56</v>
       </c>
       <c r="C2169">
-        <v>6413.7</v>
+        <v>5396.4</v>
       </c>
       <c r="D2169" t="s">
         <v>2171</v>
@@ -38828,7 +39404,7 @@
         <v>57</v>
       </c>
       <c r="C2170">
-        <v>6380.2</v>
+        <v>5524.9</v>
       </c>
       <c r="D2170" t="s">
         <v>2172</v>
@@ -38842,7 +39418,7 @@
         <v>58</v>
       </c>
       <c r="C2171">
-        <v>6360.7</v>
+        <v>5521</v>
       </c>
       <c r="D2171" t="s">
         <v>2173</v>
@@ -38856,7 +39432,7 @@
         <v>59</v>
       </c>
       <c r="C2172">
-        <v>6347.3</v>
+        <v>5525.7</v>
       </c>
       <c r="D2172" t="s">
         <v>2174</v>
@@ -38870,7 +39446,7 @@
         <v>60</v>
       </c>
       <c r="C2173">
-        <v>6372.3</v>
+        <v>5540.8</v>
       </c>
       <c r="D2173" t="s">
         <v>2175</v>
@@ -38884,7 +39460,7 @@
         <v>61</v>
       </c>
       <c r="C2174">
-        <v>6317.6</v>
+        <v>5541.1</v>
       </c>
       <c r="D2174" t="s">
         <v>2176</v>
@@ -38898,7 +39474,7 @@
         <v>62</v>
       </c>
       <c r="C2175">
-        <v>6323</v>
+        <v>5537.5</v>
       </c>
       <c r="D2175" t="s">
         <v>2177</v>
@@ -38912,7 +39488,7 @@
         <v>63</v>
       </c>
       <c r="C2176">
-        <v>6273.7</v>
+        <v>5549.5</v>
       </c>
       <c r="D2176" t="s">
         <v>2178</v>
@@ -38926,7 +39502,7 @@
         <v>64</v>
       </c>
       <c r="C2177">
-        <v>6182.7</v>
+        <v>5610.1</v>
       </c>
       <c r="D2177" t="s">
         <v>2179</v>
@@ -38940,7 +39516,7 @@
         <v>65</v>
       </c>
       <c r="C2178">
-        <v>6136.1</v>
+        <v>5843.2</v>
       </c>
       <c r="D2178" t="s">
         <v>2180</v>
@@ -38954,7 +39530,7 @@
         <v>66</v>
       </c>
       <c r="C2179">
-        <v>6055</v>
+        <v>5900.8</v>
       </c>
       <c r="D2179" t="s">
         <v>2181</v>
@@ -38968,7 +39544,7 @@
         <v>67</v>
       </c>
       <c r="C2180">
-        <v>5941.3</v>
+        <v>6037.2</v>
       </c>
       <c r="D2180" t="s">
         <v>2182</v>
@@ -38982,7 +39558,7 @@
         <v>68</v>
       </c>
       <c r="C2181">
-        <v>5871.1</v>
+        <v>6227.7</v>
       </c>
       <c r="D2181" t="s">
         <v>2183</v>
@@ -38996,7 +39572,7 @@
         <v>69</v>
       </c>
       <c r="C2182">
-        <v>5872.7</v>
+        <v>6448.8</v>
       </c>
       <c r="D2182" t="s">
         <v>2184</v>
@@ -39010,7 +39586,7 @@
         <v>70</v>
       </c>
       <c r="C2183">
-        <v>5780.8</v>
+        <v>6402</v>
       </c>
       <c r="D2183" t="s">
         <v>2185</v>
@@ -39024,7 +39600,7 @@
         <v>71</v>
       </c>
       <c r="C2184">
-        <v>5665.6</v>
+        <v>6324.4</v>
       </c>
       <c r="D2184" t="s">
         <v>2186</v>
@@ -39038,7 +39614,7 @@
         <v>72</v>
       </c>
       <c r="C2185">
-        <v>5535.3</v>
+        <v>6239.6</v>
       </c>
       <c r="D2185" t="s">
         <v>2187</v>
@@ -39052,7 +39628,7 @@
         <v>73</v>
       </c>
       <c r="C2186">
-        <v>5897</v>
+        <v>6717.6</v>
       </c>
       <c r="D2186" t="s">
         <v>2188</v>
@@ -39066,7 +39642,7 @@
         <v>74</v>
       </c>
       <c r="C2187">
-        <v>5784.1</v>
+        <v>6640.7</v>
       </c>
       <c r="D2187" t="s">
         <v>2189</v>
@@ -39080,7 +39656,7 @@
         <v>75</v>
       </c>
       <c r="C2188">
-        <v>5648.1</v>
+        <v>6454.8</v>
       </c>
       <c r="D2188" t="s">
         <v>2190</v>
@@ -39094,7 +39670,7 @@
         <v>76</v>
       </c>
       <c r="C2189">
-        <v>5553.7</v>
+        <v>6396.9</v>
       </c>
       <c r="D2189" t="s">
         <v>2191</v>
@@ -39108,7 +39684,7 @@
         <v>77</v>
       </c>
       <c r="C2190">
-        <v>5427.4</v>
+        <v>7096.9</v>
       </c>
       <c r="D2190" t="s">
         <v>2192</v>
@@ -39122,7 +39698,7 @@
         <v>78</v>
       </c>
       <c r="C2191">
-        <v>5381</v>
+        <v>7058.4</v>
       </c>
       <c r="D2191" t="s">
         <v>2193</v>
@@ -39136,7 +39712,7 @@
         <v>79</v>
       </c>
       <c r="C2192">
-        <v>5366.9</v>
+        <v>7017.8</v>
       </c>
       <c r="D2192" t="s">
         <v>2194</v>
@@ -39150,7 +39726,7 @@
         <v>80</v>
       </c>
       <c r="C2193">
-        <v>5371.4</v>
+        <v>6982.7</v>
       </c>
       <c r="D2193" t="s">
         <v>2195</v>
@@ -39164,7 +39740,7 @@
         <v>81</v>
       </c>
       <c r="C2194">
-        <v>5625.5</v>
+        <v>7097.7</v>
       </c>
       <c r="D2194" t="s">
         <v>2196</v>
@@ -39178,7 +39754,7 @@
         <v>82</v>
       </c>
       <c r="C2195">
-        <v>5617.6</v>
+        <v>7068.4</v>
       </c>
       <c r="D2195" t="s">
         <v>2197</v>
@@ -39192,7 +39768,7 @@
         <v>83</v>
       </c>
       <c r="C2196">
-        <v>5643.7</v>
+        <v>6996.4</v>
       </c>
       <c r="D2196" t="s">
         <v>2198</v>
@@ -39206,7 +39782,7 @@
         <v>84</v>
       </c>
       <c r="C2197">
-        <v>5630.3</v>
+        <v>7031.6</v>
       </c>
       <c r="D2197" t="s">
         <v>2199</v>
@@ -39220,7 +39796,7 @@
         <v>85</v>
       </c>
       <c r="C2198">
-        <v>5658</v>
+        <v>6962.7</v>
       </c>
       <c r="D2198" t="s">
         <v>2200</v>
@@ -39234,7 +39810,7 @@
         <v>86</v>
       </c>
       <c r="C2199">
-        <v>5605.3</v>
+        <v>6866.6</v>
       </c>
       <c r="D2199" t="s">
         <v>2201</v>
@@ -39248,7 +39824,7 @@
         <v>87</v>
       </c>
       <c r="C2200">
-        <v>5560.2</v>
+        <v>6764.2</v>
       </c>
       <c r="D2200" t="s">
         <v>2202</v>
@@ -39262,7 +39838,7 @@
         <v>88</v>
       </c>
       <c r="C2201">
-        <v>5534.3</v>
+        <v>6770.6</v>
       </c>
       <c r="D2201" t="s">
         <v>2203</v>
@@ -39276,7 +39852,7 @@
         <v>89</v>
       </c>
       <c r="C2202">
-        <v>5150.1</v>
+        <v>6352.9</v>
       </c>
       <c r="D2202" t="s">
         <v>2204</v>
@@ -39290,7 +39866,7 @@
         <v>90</v>
       </c>
       <c r="C2203">
-        <v>5067.6</v>
+        <v>6303.4</v>
       </c>
       <c r="D2203" t="s">
         <v>2205</v>
@@ -39304,7 +39880,7 @@
         <v>91</v>
       </c>
       <c r="C2204">
-        <v>5028.5</v>
+        <v>6241.3</v>
       </c>
       <c r="D2204" t="s">
         <v>2206</v>
@@ -39318,7 +39894,7 @@
         <v>92</v>
       </c>
       <c r="C2205">
-        <v>5000.2</v>
+        <v>6133.4</v>
       </c>
       <c r="D2205" t="s">
         <v>2207</v>
@@ -39332,7 +39908,7 @@
         <v>93</v>
       </c>
       <c r="C2206">
-        <v>5080.6</v>
+        <v>5697.1</v>
       </c>
       <c r="D2206" t="s">
         <v>2208</v>
@@ -39346,7 +39922,7 @@
         <v>94</v>
       </c>
       <c r="C2207">
-        <v>5027.2</v>
+        <v>5605.2</v>
       </c>
       <c r="D2207" t="s">
         <v>2209</v>
@@ -39360,7 +39936,7 @@
         <v>95</v>
       </c>
       <c r="C2208">
-        <v>4982.7</v>
+        <v>5498.5</v>
       </c>
       <c r="D2208" t="s">
         <v>2210</v>
@@ -39374,7 +39950,7 @@
         <v>96</v>
       </c>
       <c r="C2209">
-        <v>4961.6</v>
+        <v>5399.2</v>
       </c>
       <c r="D2209" t="s">
         <v>2211</v>
@@ -39388,7 +39964,7 @@
         <v>1</v>
       </c>
       <c r="C2210">
-        <v>4772.1</v>
+        <v>5155.9</v>
       </c>
       <c r="D2210" t="s">
         <v>2212</v>
@@ -39402,7 +39978,7 @@
         <v>2</v>
       </c>
       <c r="C2211">
-        <v>4754.4</v>
+        <v>5118.6</v>
       </c>
       <c r="D2211" t="s">
         <v>2213</v>
@@ -39416,7 +39992,7 @@
         <v>3</v>
       </c>
       <c r="C2212">
-        <v>4697.4</v>
+        <v>5090.7</v>
       </c>
       <c r="D2212" t="s">
         <v>2214</v>
@@ -39430,7 +40006,7 @@
         <v>4</v>
       </c>
       <c r="C2213">
-        <v>4680.4</v>
+        <v>5052.8</v>
       </c>
       <c r="D2213" t="s">
         <v>2215</v>
@@ -39444,7 +40020,7 @@
         <v>5</v>
       </c>
       <c r="C2214">
-        <v>4826.9</v>
+        <v>4937.9</v>
       </c>
       <c r="D2214" t="s">
         <v>2216</v>
@@ -39458,7 +40034,7 @@
         <v>6</v>
       </c>
       <c r="C2215">
-        <v>4769.2</v>
+        <v>4922.8</v>
       </c>
       <c r="D2215" t="s">
         <v>2217</v>
@@ -39472,7 +40048,7 @@
         <v>7</v>
       </c>
       <c r="C2216">
-        <v>4753.7</v>
+        <v>4922.6</v>
       </c>
       <c r="D2216" t="s">
         <v>2218</v>
@@ -39486,7 +40062,7 @@
         <v>8</v>
       </c>
       <c r="C2217">
-        <v>4754.8</v>
+        <v>4910.6</v>
       </c>
       <c r="D2217" t="s">
         <v>2219</v>
@@ -39500,7 +40076,7 @@
         <v>9</v>
       </c>
       <c r="C2218">
-        <v>4622.5</v>
+        <v>4720.5</v>
       </c>
       <c r="D2218" t="s">
         <v>2220</v>
@@ -39514,7 +40090,7 @@
         <v>10</v>
       </c>
       <c r="C2219">
-        <v>4601.7</v>
+        <v>4701.3</v>
       </c>
       <c r="D2219" t="s">
         <v>2221</v>
@@ -39528,7 +40104,7 @@
         <v>11</v>
       </c>
       <c r="C2220">
-        <v>4587.3</v>
+        <v>4686.4</v>
       </c>
       <c r="D2220" t="s">
         <v>2222</v>
@@ -39542,7 +40118,7 @@
         <v>12</v>
       </c>
       <c r="C2221">
-        <v>4590.6</v>
+        <v>4674.4</v>
       </c>
       <c r="D2221" t="s">
         <v>2223</v>
@@ -39556,7 +40132,7 @@
         <v>13</v>
       </c>
       <c r="C2222">
-        <v>4546.2</v>
+        <v>4552.2</v>
       </c>
       <c r="D2222" t="s">
         <v>2224</v>
@@ -39570,7 +40146,7 @@
         <v>14</v>
       </c>
       <c r="C2223">
-        <v>4542.6</v>
+        <v>4541</v>
       </c>
       <c r="D2223" t="s">
         <v>2225</v>
@@ -39584,7 +40160,7 @@
         <v>15</v>
       </c>
       <c r="C2224">
-        <v>4548</v>
+        <v>4524.9</v>
       </c>
       <c r="D2224" t="s">
         <v>2226</v>
@@ -39598,7 +40174,7 @@
         <v>16</v>
       </c>
       <c r="C2225">
-        <v>4520.7</v>
+        <v>4541.7</v>
       </c>
       <c r="D2225" t="s">
         <v>2227</v>
@@ -39612,7 +40188,7 @@
         <v>17</v>
       </c>
       <c r="C2226">
-        <v>4499.1</v>
+        <v>4459.8</v>
       </c>
       <c r="D2226" t="s">
         <v>2228</v>
@@ -39626,7 +40202,7 @@
         <v>18</v>
       </c>
       <c r="C2227">
-        <v>4508.3</v>
+        <v>4452.9</v>
       </c>
       <c r="D2227" t="s">
         <v>2229</v>
@@ -39640,7 +40216,7 @@
         <v>19</v>
       </c>
       <c r="C2228">
-        <v>4504.4</v>
+        <v>4435.7</v>
       </c>
       <c r="D2228" t="s">
         <v>2230</v>
@@ -39654,7 +40230,7 @@
         <v>20</v>
       </c>
       <c r="C2229">
-        <v>4507.1</v>
+        <v>4438.2</v>
       </c>
       <c r="D2229" t="s">
         <v>2231</v>
@@ -39668,7 +40244,7 @@
         <v>21</v>
       </c>
       <c r="C2230">
-        <v>4497.3</v>
+        <v>4549</v>
       </c>
       <c r="D2230" t="s">
         <v>2232</v>
@@ -39682,7 +40258,7 @@
         <v>22</v>
       </c>
       <c r="C2231">
-        <v>4487</v>
+        <v>4556.9</v>
       </c>
       <c r="D2231" t="s">
         <v>2233</v>
@@ -39696,7 +40272,7 @@
         <v>23</v>
       </c>
       <c r="C2232">
-        <v>4502.6</v>
+        <v>4584.9</v>
       </c>
       <c r="D2232" t="s">
         <v>2234</v>
@@ -39710,7 +40286,7 @@
         <v>24</v>
       </c>
       <c r="C2233">
-        <v>4538.9</v>
+        <v>4613.8</v>
       </c>
       <c r="D2233" t="s">
         <v>2235</v>
@@ -39724,7 +40300,7 @@
         <v>25</v>
       </c>
       <c r="C2234">
-        <v>4507</v>
+        <v>4767.7</v>
       </c>
       <c r="D2234" t="s">
         <v>2236</v>
@@ -39738,7 +40314,7 @@
         <v>26</v>
       </c>
       <c r="C2235">
-        <v>4574</v>
+        <v>4803</v>
       </c>
       <c r="D2235" t="s">
         <v>2237</v>
@@ -39752,7 +40328,7 @@
         <v>27</v>
       </c>
       <c r="C2236">
-        <v>4609.3</v>
+        <v>4845.9</v>
       </c>
       <c r="D2236" t="s">
         <v>2238</v>
@@ -39766,7 +40342,7 @@
         <v>28</v>
       </c>
       <c r="C2237">
-        <v>4645.6</v>
+        <v>4869</v>
       </c>
       <c r="D2237" t="s">
         <v>2239</v>
@@ -39780,7 +40356,7 @@
         <v>29</v>
       </c>
       <c r="C2238">
-        <v>4765.3</v>
+        <v>5016.9</v>
       </c>
       <c r="D2238" t="s">
         <v>2240</v>
@@ -39794,7 +40370,7 @@
         <v>30</v>
       </c>
       <c r="C2239">
-        <v>4817.1</v>
+        <v>5106.2</v>
       </c>
       <c r="D2239" t="s">
         <v>2241</v>
@@ -39808,7 +40384,7 @@
         <v>31</v>
       </c>
       <c r="C2240">
-        <v>4914.9</v>
+        <v>5200</v>
       </c>
       <c r="D2240" t="s">
         <v>2242</v>
@@ -39822,7 +40398,7 @@
         <v>32</v>
       </c>
       <c r="C2241">
-        <v>5026.1</v>
+        <v>5294</v>
       </c>
       <c r="D2241" t="s">
         <v>2243</v>
@@ -39836,7 +40412,7 @@
         <v>33</v>
       </c>
       <c r="C2242">
-        <v>5178.5</v>
+        <v>5179.3</v>
       </c>
       <c r="D2242" t="s">
         <v>2244</v>
@@ -39850,7 +40426,7 @@
         <v>34</v>
       </c>
       <c r="C2243">
-        <v>5283.2</v>
+        <v>5273.5</v>
       </c>
       <c r="D2243" t="s">
         <v>2245</v>
@@ -39864,7 +40440,7 @@
         <v>35</v>
       </c>
       <c r="C2244">
-        <v>5435.2</v>
+        <v>5337</v>
       </c>
       <c r="D2244" t="s">
         <v>2246</v>
@@ -39878,7 +40454,7 @@
         <v>36</v>
       </c>
       <c r="C2245">
-        <v>5563.3</v>
+        <v>5437.2</v>
       </c>
       <c r="D2245" t="s">
         <v>2247</v>
@@ -39892,7 +40468,7 @@
         <v>37</v>
       </c>
       <c r="C2246">
-        <v>5564.4</v>
+        <v>5290.8</v>
       </c>
       <c r="D2246" t="s">
         <v>2248</v>
@@ -39906,7 +40482,7 @@
         <v>38</v>
       </c>
       <c r="C2247">
-        <v>5648.2</v>
+        <v>5312.2</v>
       </c>
       <c r="D2247" t="s">
         <v>2249</v>
@@ -39920,7 +40496,7 @@
         <v>39</v>
       </c>
       <c r="C2248">
-        <v>5791.9</v>
+        <v>5381</v>
       </c>
       <c r="D2248" t="s">
         <v>2250</v>
@@ -39934,7 +40510,7 @@
         <v>40</v>
       </c>
       <c r="C2249">
-        <v>5927.3</v>
+        <v>5399.1</v>
       </c>
       <c r="D2249" t="s">
         <v>2251</v>
@@ -39948,7 +40524,7 @@
         <v>41</v>
       </c>
       <c r="C2250">
-        <v>5946.2</v>
+        <v>5630.6</v>
       </c>
       <c r="D2250" t="s">
         <v>2252</v>
@@ -39962,7 +40538,7 @@
         <v>42</v>
       </c>
       <c r="C2251">
-        <v>6029.7</v>
+        <v>5652.8</v>
       </c>
       <c r="D2251" t="s">
         <v>2253</v>
@@ -39976,7 +40552,7 @@
         <v>43</v>
       </c>
       <c r="C2252">
-        <v>6145.8</v>
+        <v>5667.8</v>
       </c>
       <c r="D2252" t="s">
         <v>2254</v>
@@ -39990,7 +40566,7 @@
         <v>44</v>
       </c>
       <c r="C2253">
-        <v>6208.2</v>
+        <v>5696</v>
       </c>
       <c r="D2253" t="s">
         <v>2255</v>
@@ -40004,7 +40580,7 @@
         <v>45</v>
       </c>
       <c r="C2254">
-        <v>6139.3</v>
+        <v>5347.5</v>
       </c>
       <c r="D2254" t="s">
         <v>2256</v>
@@ -40018,7 +40594,7 @@
         <v>46</v>
       </c>
       <c r="C2255">
-        <v>6150</v>
+        <v>5388.3</v>
       </c>
       <c r="D2255" t="s">
         <v>2257</v>
@@ -40032,7 +40608,7 @@
         <v>47</v>
       </c>
       <c r="C2256">
-        <v>6202.7</v>
+        <v>5412.3</v>
       </c>
       <c r="D2256" t="s">
         <v>2258</v>
@@ -40046,7 +40622,7 @@
         <v>48</v>
       </c>
       <c r="C2257">
-        <v>6222.3</v>
+        <v>5058.1</v>
       </c>
       <c r="D2257" t="s">
         <v>2259</v>
@@ -40060,7 +40636,7 @@
         <v>49</v>
       </c>
       <c r="C2258">
-        <v>6179.3</v>
+        <v>5266.6</v>
       </c>
       <c r="D2258" t="s">
         <v>2260</v>
@@ -40074,7 +40650,7 @@
         <v>50</v>
       </c>
       <c r="C2259">
-        <v>6175.7</v>
+        <v>4674.3</v>
       </c>
       <c r="D2259" t="s">
         <v>2261</v>
@@ -40088,7 +40664,7 @@
         <v>51</v>
       </c>
       <c r="C2260">
-        <v>6189.2</v>
+        <v>4685.9</v>
       </c>
       <c r="D2260" t="s">
         <v>2262</v>
@@ -40102,7 +40678,7 @@
         <v>52</v>
       </c>
       <c r="C2261">
-        <v>6220</v>
+        <v>4750.1</v>
       </c>
       <c r="D2261" t="s">
         <v>2263</v>
@@ -40116,7 +40692,7 @@
         <v>53</v>
       </c>
       <c r="C2262">
-        <v>6188.4</v>
+        <v>4549.4</v>
       </c>
       <c r="D2262" t="s">
         <v>2264</v>
@@ -40130,7 +40706,7 @@
         <v>54</v>
       </c>
       <c r="C2263">
-        <v>6198.4</v>
+        <v>4395.8</v>
       </c>
       <c r="D2263" t="s">
         <v>2265</v>
@@ -40144,7 +40720,7 @@
         <v>55</v>
       </c>
       <c r="C2264">
-        <v>6175.3</v>
+        <v>4410.3</v>
       </c>
       <c r="D2264" t="s">
         <v>2266</v>
@@ -40158,7 +40734,7 @@
         <v>56</v>
       </c>
       <c r="C2265">
-        <v>6143.7</v>
+        <v>4251.8</v>
       </c>
       <c r="D2265" t="s">
         <v>2267</v>
@@ -40172,7 +40748,7 @@
         <v>57</v>
       </c>
       <c r="C2266">
-        <v>6120.2</v>
+        <v>4206</v>
       </c>
       <c r="D2266" t="s">
         <v>2268</v>
@@ -40186,7 +40762,7 @@
         <v>58</v>
       </c>
       <c r="C2267">
-        <v>6090.7</v>
+        <v>4246</v>
       </c>
       <c r="D2267" t="s">
         <v>2269</v>
@@ -40200,7 +40776,7 @@
         <v>59</v>
       </c>
       <c r="C2268">
-        <v>6077.3</v>
+        <v>4252.6</v>
       </c>
       <c r="D2268" t="s">
         <v>2270</v>
@@ -40214,7 +40790,7 @@
         <v>60</v>
       </c>
       <c r="C2269">
-        <v>6112.3</v>
+        <v>4279.6</v>
       </c>
       <c r="D2269" t="s">
         <v>2271</v>
@@ -40228,7 +40804,7 @@
         <v>61</v>
       </c>
       <c r="C2270">
-        <v>6057.6</v>
+        <v>4236.1</v>
       </c>
       <c r="D2270" t="s">
         <v>2272</v>
@@ -40242,7 +40818,7 @@
         <v>62</v>
       </c>
       <c r="C2271">
-        <v>6063</v>
+        <v>4244.1</v>
       </c>
       <c r="D2271" t="s">
         <v>2273</v>
@@ -40256,7 +40832,7 @@
         <v>63</v>
       </c>
       <c r="C2272">
-        <v>6013.7</v>
+        <v>4287.9</v>
       </c>
       <c r="D2272" t="s">
         <v>2274</v>
@@ -40270,7 +40846,7 @@
         <v>64</v>
       </c>
       <c r="C2273">
-        <v>5932.7</v>
+        <v>4209</v>
       </c>
       <c r="D2273" t="s">
         <v>2275</v>
@@ -40284,7 +40860,7 @@
         <v>65</v>
       </c>
       <c r="C2274">
-        <v>5886.1</v>
+        <v>4177.3</v>
       </c>
       <c r="D2274" t="s">
         <v>2276</v>
@@ -40298,7 +40874,7 @@
         <v>66</v>
       </c>
       <c r="C2275">
-        <v>5815</v>
+        <v>4039.4</v>
       </c>
       <c r="D2275" t="s">
         <v>2277</v>
@@ -40312,7 +40888,7 @@
         <v>67</v>
       </c>
       <c r="C2276">
-        <v>5701.3</v>
+        <v>4060.3</v>
       </c>
       <c r="D2276" t="s">
         <v>2278</v>
@@ -40326,7 +40902,7 @@
         <v>68</v>
       </c>
       <c r="C2277">
-        <v>5631.1</v>
+        <v>4198.5</v>
       </c>
       <c r="D2277" t="s">
         <v>2279</v>
@@ -40340,7 +40916,7 @@
         <v>69</v>
       </c>
       <c r="C2278">
-        <v>5642.7</v>
+        <v>4336.4</v>
       </c>
       <c r="D2278" t="s">
         <v>2280</v>
@@ -40354,7 +40930,7 @@
         <v>70</v>
       </c>
       <c r="C2279">
-        <v>5560.8</v>
+        <v>4383.5</v>
       </c>
       <c r="D2279" t="s">
         <v>2281</v>
@@ -40368,7 +40944,7 @@
         <v>71</v>
       </c>
       <c r="C2280">
-        <v>5455.6</v>
+        <v>4536.7</v>
       </c>
       <c r="D2280" t="s">
         <v>2282</v>
@@ -40382,7 +40958,7 @@
         <v>72</v>
       </c>
       <c r="C2281">
-        <v>5345.3</v>
+        <v>4535</v>
       </c>
       <c r="D2281" t="s">
         <v>2283</v>
@@ -40396,7 +40972,7 @@
         <v>73</v>
       </c>
       <c r="C2282">
-        <v>5727</v>
+        <v>4982.3</v>
       </c>
       <c r="D2282" t="s">
         <v>2284</v>
@@ -40410,7 +40986,7 @@
         <v>74</v>
       </c>
       <c r="C2283">
-        <v>5634.1</v>
+        <v>5024.2</v>
       </c>
       <c r="D2283" t="s">
         <v>2285</v>
@@ -40424,7 +41000,7 @@
         <v>75</v>
       </c>
       <c r="C2284">
-        <v>5508.1</v>
+        <v>4943.6</v>
       </c>
       <c r="D2284" t="s">
         <v>2286</v>
@@ -40438,7 +41014,7 @@
         <v>76</v>
       </c>
       <c r="C2285">
-        <v>5433.7</v>
+        <v>4956.1</v>
       </c>
       <c r="D2285" t="s">
         <v>2287</v>
@@ -40452,7 +41028,7 @@
         <v>77</v>
       </c>
       <c r="C2286">
-        <v>5307.4</v>
+        <v>5619.2</v>
       </c>
       <c r="D2286" t="s">
         <v>2288</v>
@@ -40466,7 +41042,7 @@
         <v>78</v>
       </c>
       <c r="C2287">
-        <v>5261</v>
+        <v>5586</v>
       </c>
       <c r="D2287" t="s">
         <v>2289</v>
@@ -40480,7 +41056,7 @@
         <v>79</v>
       </c>
       <c r="C2288">
-        <v>5256.9</v>
+        <v>5590.3</v>
       </c>
       <c r="D2288" t="s">
         <v>2290</v>
@@ -40494,7 +41070,7 @@
         <v>80</v>
       </c>
       <c r="C2289">
-        <v>5271.4</v>
+        <v>5594.5</v>
       </c>
       <c r="D2289" t="s">
         <v>2291</v>
@@ -40508,7 +41084,7 @@
         <v>81</v>
       </c>
       <c r="C2290">
-        <v>5525.5</v>
+        <v>5971.1</v>
       </c>
       <c r="D2290" t="s">
         <v>2292</v>
@@ -40522,7 +41098,7 @@
         <v>82</v>
       </c>
       <c r="C2291">
-        <v>5517.6</v>
+        <v>5998.2</v>
       </c>
       <c r="D2291" t="s">
         <v>2293</v>
@@ -40536,7 +41112,7 @@
         <v>83</v>
       </c>
       <c r="C2292">
-        <v>5563.7</v>
+        <v>5963.9</v>
       </c>
       <c r="D2292" t="s">
         <v>2294</v>
@@ -40550,7 +41126,7 @@
         <v>84</v>
       </c>
       <c r="C2293">
-        <v>5550.3</v>
+        <v>6049.7</v>
       </c>
       <c r="D2293" t="s">
         <v>2295</v>
@@ -40564,7 +41140,7 @@
         <v>85</v>
       </c>
       <c r="C2294">
-        <v>5578</v>
+        <v>5982</v>
       </c>
       <c r="D2294" t="s">
         <v>2296</v>
@@ -40578,7 +41154,7 @@
         <v>86</v>
       </c>
       <c r="C2295">
-        <v>5525.3</v>
+        <v>5974</v>
       </c>
       <c r="D2295" t="s">
         <v>2297</v>
@@ -40592,7 +41168,7 @@
         <v>87</v>
       </c>
       <c r="C2296">
-        <v>5500.2</v>
+        <v>5967.9</v>
       </c>
       <c r="D2296" t="s">
         <v>2298</v>
@@ -40606,7 +41182,7 @@
         <v>88</v>
       </c>
       <c r="C2297">
-        <v>5484.3</v>
+        <v>5997.6</v>
       </c>
       <c r="D2297" t="s">
         <v>2299</v>
@@ -40620,7 +41196,7 @@
         <v>89</v>
       </c>
       <c r="C2298">
-        <v>5120.1</v>
+        <v>5578.3</v>
       </c>
       <c r="D2298" t="s">
         <v>2300</v>
@@ -40634,7 +41210,7 @@
         <v>90</v>
       </c>
       <c r="C2299">
-        <v>5047.6</v>
+        <v>5540.3</v>
       </c>
       <c r="D2299" t="s">
         <v>2301</v>
@@ -40648,7 +41224,7 @@
         <v>91</v>
       </c>
       <c r="C2300">
-        <v>5018.5</v>
+        <v>5572.7</v>
       </c>
       <c r="D2300" t="s">
         <v>2302</v>
@@ -40662,7 +41238,7 @@
         <v>92</v>
       </c>
       <c r="C2301">
-        <v>5000.2</v>
+        <v>5464.9</v>
       </c>
       <c r="D2301" t="s">
         <v>2303</v>
@@ -40676,7 +41252,7 @@
         <v>93</v>
       </c>
       <c r="C2302">
-        <v>5090.6</v>
+        <v>5218.7</v>
       </c>
       <c r="D2302" t="s">
         <v>2304</v>
@@ -40690,7 +41266,7 @@
         <v>94</v>
       </c>
       <c r="C2303">
-        <v>5037.2</v>
+        <v>5159.4</v>
       </c>
       <c r="D2303" t="s">
         <v>2305</v>
@@ -40704,7 +41280,7 @@
         <v>95</v>
       </c>
       <c r="C2304">
-        <v>4992.7</v>
+        <v>5119.6</v>
       </c>
       <c r="D2304" t="s">
         <v>2306</v>
@@ -40718,7 +41294,7 @@
         <v>96</v>
       </c>
       <c r="C2305">
-        <v>4961.6</v>
+        <v>5086.8</v>
       </c>
       <c r="D2305" t="s">
         <v>2307</v>
@@ -40732,7 +41308,7 @@
         <v>1</v>
       </c>
       <c r="C2306">
-        <v>4702.1</v>
+        <v>5115.9</v>
       </c>
       <c r="D2306" t="s">
         <v>2308</v>
@@ -40746,7 +41322,7 @@
         <v>2</v>
       </c>
       <c r="C2307">
-        <v>4674.4</v>
+        <v>5108.6</v>
       </c>
       <c r="D2307" t="s">
         <v>2309</v>
@@ -40760,7 +41336,7 @@
         <v>3</v>
       </c>
       <c r="C2308">
-        <v>4607.4</v>
+        <v>5060.7</v>
       </c>
       <c r="D2308" t="s">
         <v>2310</v>
@@ -40774,7 +41350,7 @@
         <v>4</v>
       </c>
       <c r="C2309">
-        <v>4590.4</v>
+        <v>5002.8</v>
       </c>
       <c r="D2309" t="s">
         <v>2311</v>
@@ -40788,7 +41364,7 @@
         <v>5</v>
       </c>
       <c r="C2310">
-        <v>4726.9</v>
+        <v>4857.9</v>
       </c>
       <c r="D2310" t="s">
         <v>2312</v>
@@ -40802,7 +41378,7 @@
         <v>6</v>
       </c>
       <c r="C2311">
-        <v>4669.2</v>
+        <v>4832.8</v>
       </c>
       <c r="D2311" t="s">
         <v>2313</v>
@@ -40816,7 +41392,7 @@
         <v>7</v>
       </c>
       <c r="C2312">
-        <v>4653.7</v>
+        <v>4842.6</v>
       </c>
       <c r="D2312" t="s">
         <v>2314</v>
@@ -40830,7 +41406,7 @@
         <v>8</v>
       </c>
       <c r="C2313">
-        <v>4644.8</v>
+        <v>4840.6</v>
       </c>
       <c r="D2313" t="s">
         <v>2315</v>
@@ -40844,7 +41420,7 @@
         <v>9</v>
       </c>
       <c r="C2314">
-        <v>4502.5</v>
+        <v>4650.5</v>
       </c>
       <c r="D2314" t="s">
         <v>2316</v>
@@ -40858,7 +41434,7 @@
         <v>10</v>
       </c>
       <c r="C2315">
-        <v>4481.7</v>
+        <v>4641.3</v>
       </c>
       <c r="D2315" t="s">
         <v>2317</v>
@@ -40872,7 +41448,7 @@
         <v>11</v>
       </c>
       <c r="C2316">
-        <v>4457.3</v>
+        <v>4626.4</v>
       </c>
       <c r="D2316" t="s">
         <v>2318</v>
@@ -40886,7 +41462,7 @@
         <v>12</v>
       </c>
       <c r="C2317">
-        <v>4450.6</v>
+        <v>4624.4</v>
       </c>
       <c r="D2317" t="s">
         <v>2319</v>
@@ -40900,7 +41476,7 @@
         <v>13</v>
       </c>
       <c r="C2318">
-        <v>4386.2</v>
+        <v>4502.2</v>
       </c>
       <c r="D2318" t="s">
         <v>2320</v>
@@ -40914,7 +41490,7 @@
         <v>14</v>
       </c>
       <c r="C2319">
-        <v>4372.6</v>
+        <v>4491</v>
       </c>
       <c r="D2319" t="s">
         <v>2321</v>
@@ -40928,7 +41504,7 @@
         <v>15</v>
       </c>
       <c r="C2320">
-        <v>4368</v>
+        <v>4464.9</v>
       </c>
       <c r="D2320" t="s">
         <v>2322</v>
@@ -40942,7 +41518,7 @@
         <v>16</v>
       </c>
       <c r="C2321">
-        <v>4340.7</v>
+        <v>4471.7</v>
       </c>
       <c r="D2321" t="s">
         <v>2323</v>
@@ -40956,7 +41532,7 @@
         <v>17</v>
       </c>
       <c r="C2322">
-        <v>4309.1</v>
+        <v>4399.8</v>
       </c>
       <c r="D2322" t="s">
         <v>2324</v>
@@ -40970,7 +41546,7 @@
         <v>18</v>
       </c>
       <c r="C2323">
-        <v>4318.3</v>
+        <v>4392.9</v>
       </c>
       <c r="D2323" t="s">
         <v>2325</v>
@@ -40984,7 +41560,7 @@
         <v>19</v>
       </c>
       <c r="C2324">
-        <v>4314.4</v>
+        <v>4375.7</v>
       </c>
       <c r="D2324" t="s">
         <v>2326</v>
@@ -40998,7 +41574,7 @@
         <v>20</v>
       </c>
       <c r="C2325">
-        <v>4307.1</v>
+        <v>4378.2</v>
       </c>
       <c r="D2325" t="s">
         <v>2327</v>
@@ -41012,7 +41588,7 @@
         <v>21</v>
       </c>
       <c r="C2326">
-        <v>4287.3</v>
+        <v>4449</v>
       </c>
       <c r="D2326" t="s">
         <v>2328</v>
@@ -41026,7 +41602,7 @@
         <v>22</v>
       </c>
       <c r="C2327">
-        <v>4237</v>
+        <v>4416.9</v>
       </c>
       <c r="D2327" t="s">
         <v>2329</v>
@@ -41040,7 +41616,7 @@
         <v>23</v>
       </c>
       <c r="C2328">
-        <v>4202.6</v>
+        <v>4374.9</v>
       </c>
       <c r="D2328" t="s">
         <v>2330</v>
@@ -41054,7 +41630,7 @@
         <v>24</v>
       </c>
       <c r="C2329">
-        <v>4138.9</v>
+        <v>4323.8</v>
       </c>
       <c r="D2329" t="s">
         <v>2331</v>
@@ -41068,7 +41644,7 @@
         <v>25</v>
       </c>
       <c r="C2330">
-        <v>3997</v>
+        <v>4367.7</v>
       </c>
       <c r="D2330" t="s">
         <v>2332</v>
@@ -41082,7 +41658,7 @@
         <v>26</v>
       </c>
       <c r="C2331">
-        <v>3954</v>
+        <v>4283</v>
       </c>
       <c r="D2331" t="s">
         <v>2333</v>
@@ -41096,7 +41672,7 @@
         <v>27</v>
       </c>
       <c r="C2332">
-        <v>3879.3</v>
+        <v>4175.9</v>
       </c>
       <c r="D2332" t="s">
         <v>2334</v>
@@ -41110,7 +41686,7 @@
         <v>28</v>
       </c>
       <c r="C2333">
-        <v>3835.6</v>
+        <v>4109</v>
       </c>
       <c r="D2333" t="s">
         <v>2335</v>
@@ -41124,7 +41700,7 @@
         <v>29</v>
       </c>
       <c r="C2334">
-        <v>3875.3</v>
+        <v>4196.9</v>
       </c>
       <c r="D2334" t="s">
         <v>2336</v>
@@ -41138,7 +41714,7 @@
         <v>30</v>
       </c>
       <c r="C2335">
-        <v>3847.1</v>
+        <v>4236.2</v>
       </c>
       <c r="D2335" t="s">
         <v>2337</v>
@@ -41152,7 +41728,7 @@
         <v>31</v>
       </c>
       <c r="C2336">
-        <v>3894.9</v>
+        <v>4300</v>
       </c>
       <c r="D2336" t="s">
         <v>2338</v>
@@ -41166,7 +41742,7 @@
         <v>32</v>
       </c>
       <c r="C2337">
-        <v>3976.1</v>
+        <v>4384</v>
       </c>
       <c r="D2337" t="s">
         <v>2339</v>
@@ -41180,7 +41756,7 @@
         <v>33</v>
       </c>
       <c r="C2338">
-        <v>4108.5</v>
+        <v>4279.3</v>
       </c>
       <c r="D2338" t="s">
         <v>2340</v>
@@ -41194,7 +41770,7 @@
         <v>34</v>
       </c>
       <c r="C2339">
-        <v>4203.2</v>
+        <v>4383.5</v>
       </c>
       <c r="D2339" t="s">
         <v>2341</v>
@@ -41208,7 +41784,7 @@
         <v>35</v>
       </c>
       <c r="C2340">
-        <v>4355.2</v>
+        <v>4457</v>
       </c>
       <c r="D2340" t="s">
         <v>2342</v>
@@ -41222,7 +41798,7 @@
         <v>36</v>
       </c>
       <c r="C2341">
-        <v>4473.3</v>
+        <v>4557.2</v>
       </c>
       <c r="D2341" t="s">
         <v>2343</v>
@@ -41236,7 +41812,7 @@
         <v>37</v>
       </c>
       <c r="C2342">
-        <v>4474.4</v>
+        <v>4390.8</v>
       </c>
       <c r="D2342" t="s">
         <v>2344</v>
@@ -41250,7 +41826,7 @@
         <v>38</v>
       </c>
       <c r="C2343">
-        <v>4558.2</v>
+        <v>4452.2</v>
       </c>
       <c r="D2343" t="s">
         <v>2345</v>
@@ -41264,7 +41840,7 @@
         <v>39</v>
       </c>
       <c r="C2344">
-        <v>4711.9</v>
+        <v>4581</v>
       </c>
       <c r="D2344" t="s">
         <v>2346</v>
@@ -41278,7 +41854,7 @@
         <v>40</v>
       </c>
       <c r="C2345">
-        <v>4867.3</v>
+        <v>4689.1</v>
       </c>
       <c r="D2345" t="s">
         <v>2347</v>
@@ -41292,7 +41868,7 @@
         <v>41</v>
       </c>
       <c r="C2346">
-        <v>4916.2</v>
+        <v>5030.6</v>
       </c>
       <c r="D2346" t="s">
         <v>2348</v>
@@ -41306,7 +41882,7 @@
         <v>42</v>
       </c>
       <c r="C2347">
-        <v>5029.7</v>
+        <v>5122.8</v>
       </c>
       <c r="D2347" t="s">
         <v>2349</v>
@@ -41320,7 +41896,7 @@
         <v>43</v>
       </c>
       <c r="C2348">
-        <v>5165.8</v>
+        <v>5177.8</v>
       </c>
       <c r="D2348" t="s">
         <v>2350</v>
@@ -41334,7 +41910,7 @@
         <v>44</v>
       </c>
       <c r="C2349">
-        <v>5258.2</v>
+        <v>5196</v>
       </c>
       <c r="D2349" t="s">
         <v>2351</v>
@@ -41348,7 +41924,7 @@
         <v>45</v>
       </c>
       <c r="C2350">
-        <v>5209.3</v>
+        <v>4797.5</v>
       </c>
       <c r="D2350" t="s">
         <v>2352</v>
@@ -41362,7 +41938,7 @@
         <v>46</v>
       </c>
       <c r="C2351">
-        <v>5250</v>
+        <v>4808.3</v>
       </c>
       <c r="D2351" t="s">
         <v>2353</v>
@@ -41376,7 +41952,7 @@
         <v>47</v>
       </c>
       <c r="C2352">
-        <v>5322.7</v>
+        <v>4842.3</v>
       </c>
       <c r="D2352" t="s">
         <v>2354</v>
@@ -41390,7 +41966,7 @@
         <v>48</v>
       </c>
       <c r="C2353">
-        <v>5362.3</v>
+        <v>4538.1</v>
       </c>
       <c r="D2353" t="s">
         <v>2355</v>
@@ -41404,7 +41980,7 @@
         <v>49</v>
       </c>
       <c r="C2354">
-        <v>5319.3</v>
+        <v>4826.6</v>
       </c>
       <c r="D2354" t="s">
         <v>2356</v>
@@ -41418,7 +41994,7 @@
         <v>50</v>
       </c>
       <c r="C2355">
-        <v>5325.7</v>
+        <v>4274.3</v>
       </c>
       <c r="D2355" t="s">
         <v>2357</v>
@@ -41432,7 +42008,7 @@
         <v>51</v>
       </c>
       <c r="C2356">
-        <v>5329.2</v>
+        <v>4305.9</v>
       </c>
       <c r="D2356" t="s">
         <v>2358</v>
@@ -41446,7 +42022,7 @@
         <v>52</v>
       </c>
       <c r="C2357">
-        <v>5350</v>
+        <v>4320.1</v>
       </c>
       <c r="D2357" t="s">
         <v>2359</v>
@@ -41460,7 +42036,7 @@
         <v>53</v>
       </c>
       <c r="C2358">
-        <v>5308.4</v>
+        <v>4069.4</v>
       </c>
       <c r="D2358" t="s">
         <v>2360</v>
@@ -41474,7 +42050,7 @@
         <v>54</v>
       </c>
       <c r="C2359">
-        <v>5298.4</v>
+        <v>3835.8</v>
       </c>
       <c r="D2359" t="s">
         <v>2361</v>
@@ -41488,7 +42064,7 @@
         <v>55</v>
       </c>
       <c r="C2360">
-        <v>5275.3</v>
+        <v>3780.3</v>
       </c>
       <c r="D2360" t="s">
         <v>2362</v>
@@ -41502,7 +42078,7 @@
         <v>56</v>
       </c>
       <c r="C2361">
-        <v>5243.7</v>
+        <v>3561.8</v>
       </c>
       <c r="D2361" t="s">
         <v>2363</v>
@@ -41516,7 +42092,7 @@
         <v>57</v>
       </c>
       <c r="C2362">
-        <v>5220.2</v>
+        <v>3456</v>
       </c>
       <c r="D2362" t="s">
         <v>2364</v>
@@ -41530,7 +42106,7 @@
         <v>58</v>
       </c>
       <c r="C2363">
-        <v>5210.7</v>
+        <v>3466</v>
       </c>
       <c r="D2363" t="s">
         <v>2365</v>
@@ -41544,7 +42120,7 @@
         <v>59</v>
       </c>
       <c r="C2364">
-        <v>5197.3</v>
+        <v>3462.6</v>
       </c>
       <c r="D2364" t="s">
         <v>2366</v>
@@ -41558,7 +42134,7 @@
         <v>60</v>
       </c>
       <c r="C2365">
-        <v>5232.3</v>
+        <v>3519.6</v>
       </c>
       <c r="D2365" t="s">
         <v>2367</v>
@@ -41572,7 +42148,7 @@
         <v>61</v>
       </c>
       <c r="C2366">
-        <v>5187.6</v>
+        <v>3516.1</v>
       </c>
       <c r="D2366" t="s">
         <v>2368</v>
@@ -41586,7 +42162,7 @@
         <v>62</v>
       </c>
       <c r="C2367">
-        <v>5203</v>
+        <v>3564.1</v>
       </c>
       <c r="D2367" t="s">
         <v>2369</v>
@@ -41600,7 +42176,7 @@
         <v>63</v>
       </c>
       <c r="C2368">
-        <v>5163.7</v>
+        <v>3637.9</v>
       </c>
       <c r="D2368" t="s">
         <v>2370</v>
@@ -41614,7 +42190,7 @@
         <v>64</v>
       </c>
       <c r="C2369">
-        <v>5092.7</v>
+        <v>3589</v>
       </c>
       <c r="D2369" t="s">
         <v>2371</v>
@@ -41628,7 +42204,7 @@
         <v>65</v>
       </c>
       <c r="C2370">
-        <v>5066.1</v>
+        <v>3547.3</v>
       </c>
       <c r="D2370" t="s">
         <v>2372</v>
@@ -41642,7 +42218,7 @@
         <v>66</v>
       </c>
       <c r="C2371">
-        <v>5015</v>
+        <v>3399.4</v>
       </c>
       <c r="D2371" t="s">
         <v>2373</v>
@@ -41656,7 +42232,7 @@
         <v>67</v>
       </c>
       <c r="C2372">
-        <v>4921.3</v>
+        <v>3420.3</v>
       </c>
       <c r="D2372" t="s">
         <v>2374</v>
@@ -41670,7 +42246,7 @@
         <v>68</v>
       </c>
       <c r="C2373">
-        <v>4861.1</v>
+        <v>3548.5</v>
       </c>
       <c r="D2373" t="s">
         <v>2375</v>
@@ -41684,7 +42260,7 @@
         <v>69</v>
       </c>
       <c r="C2374">
-        <v>4892.7</v>
+        <v>3696.4</v>
       </c>
       <c r="D2374" t="s">
         <v>2376</v>
@@ -41698,7 +42274,7 @@
         <v>70</v>
       </c>
       <c r="C2375">
-        <v>4810.8</v>
+        <v>3753.5</v>
       </c>
       <c r="D2375" t="s">
         <v>2377</v>
@@ -41712,7 +42288,7 @@
         <v>71</v>
       </c>
       <c r="C2376">
-        <v>4725.6</v>
+        <v>3926.7</v>
       </c>
       <c r="D2376" t="s">
         <v>2378</v>
@@ -41726,7 +42302,7 @@
         <v>72</v>
       </c>
       <c r="C2377">
-        <v>4615.3</v>
+        <v>3945</v>
       </c>
       <c r="D2377" t="s">
         <v>2379</v>
@@ -41740,7 +42316,7 @@
         <v>73</v>
       </c>
       <c r="C2378">
-        <v>4997</v>
+        <v>4412.3</v>
       </c>
       <c r="D2378" t="s">
         <v>2380</v>
@@ -41754,7 +42330,7 @@
         <v>74</v>
       </c>
       <c r="C2379">
-        <v>4914.1</v>
+        <v>4464.2</v>
       </c>
       <c r="D2379" t="s">
         <v>2381</v>
@@ -41768,7 +42344,7 @@
         <v>75</v>
       </c>
       <c r="C2380">
-        <v>4808.1</v>
+        <v>4383.6</v>
       </c>
       <c r="D2380" t="s">
         <v>2382</v>
@@ -41782,7 +42358,7 @@
         <v>76</v>
       </c>
       <c r="C2381">
-        <v>4733.7</v>
+        <v>4366.1</v>
       </c>
       <c r="D2381" t="s">
         <v>2383</v>
@@ -41796,7 +42372,7 @@
         <v>77</v>
       </c>
       <c r="C2382">
-        <v>4627.4</v>
+        <v>4979.2</v>
       </c>
       <c r="D2382" t="s">
         <v>2384</v>
@@ -41810,7 +42386,7 @@
         <v>78</v>
       </c>
       <c r="C2383">
-        <v>4591</v>
+        <v>4906</v>
       </c>
       <c r="D2383" t="s">
         <v>2385</v>
@@ -41824,7 +42400,7 @@
         <v>79</v>
       </c>
       <c r="C2384">
-        <v>4606.9</v>
+        <v>4910.3</v>
       </c>
       <c r="D2384" t="s">
         <v>2386</v>
@@ -41838,7 +42414,7 @@
         <v>80</v>
       </c>
       <c r="C2385">
-        <v>4621.4</v>
+        <v>4934.5</v>
       </c>
       <c r="D2385" t="s">
         <v>2387</v>
@@ -41852,7 +42428,7 @@
         <v>81</v>
       </c>
       <c r="C2386">
-        <v>4885.5</v>
+        <v>5341.1</v>
       </c>
       <c r="D2386" t="s">
         <v>2388</v>
@@ -41866,7 +42442,7 @@
         <v>82</v>
       </c>
       <c r="C2387">
-        <v>4897.6</v>
+        <v>5388.2</v>
       </c>
       <c r="D2387" t="s">
         <v>2389</v>
@@ -41880,7 +42456,7 @@
         <v>83</v>
       </c>
       <c r="C2388">
-        <v>4943.7</v>
+        <v>5373.9</v>
       </c>
       <c r="D2388" t="s">
         <v>2390</v>
@@ -41894,7 +42470,7 @@
         <v>84</v>
       </c>
       <c r="C2389">
-        <v>4940.3</v>
+        <v>5469.7</v>
       </c>
       <c r="D2389" t="s">
         <v>2391</v>
@@ -41908,7 +42484,7 @@
         <v>85</v>
       </c>
       <c r="C2390">
-        <v>4988</v>
+        <v>5432</v>
       </c>
       <c r="D2390" t="s">
         <v>2392</v>
@@ -41922,7 +42498,7 @@
         <v>86</v>
       </c>
       <c r="C2391">
-        <v>4945.3</v>
+        <v>5464</v>
       </c>
       <c r="D2391" t="s">
         <v>2393</v>
@@ -41936,7 +42512,7 @@
         <v>87</v>
       </c>
       <c r="C2392">
-        <v>4930.2</v>
+        <v>5477.9</v>
       </c>
       <c r="D2392" t="s">
         <v>2394</v>
@@ -41950,7 +42526,7 @@
         <v>88</v>
       </c>
       <c r="C2393">
-        <v>4934.3</v>
+        <v>5527.6</v>
       </c>
       <c r="D2393" t="s">
         <v>2395</v>
@@ -41964,7 +42540,7 @@
         <v>89</v>
       </c>
       <c r="C2394">
-        <v>4580.1</v>
+        <v>5128.3</v>
       </c>
       <c r="D2394" t="s">
         <v>2396</v>
@@ -41978,7 +42554,7 @@
         <v>90</v>
       </c>
       <c r="C2395">
-        <v>4537.6</v>
+        <v>5100.3</v>
       </c>
       <c r="D2395" t="s">
         <v>2397</v>
@@ -41992,7 +42568,7 @@
         <v>91</v>
       </c>
       <c r="C2396">
-        <v>4538.5</v>
+        <v>5162.7</v>
       </c>
       <c r="D2396" t="s">
         <v>2398</v>
@@ -42006,7 +42582,7 @@
         <v>92</v>
       </c>
       <c r="C2397">
-        <v>4550.2</v>
+        <v>5104.9</v>
       </c>
       <c r="D2397" t="s">
         <v>2399</v>
@@ -42020,7 +42596,7 @@
         <v>93</v>
       </c>
       <c r="C2398">
-        <v>4660.6</v>
+        <v>4908.7</v>
       </c>
       <c r="D2398" t="s">
         <v>2400</v>
@@ -42034,7 +42610,7 @@
         <v>94</v>
       </c>
       <c r="C2399">
-        <v>4627.2</v>
+        <v>4879.4</v>
       </c>
       <c r="D2399" t="s">
         <v>2401</v>
@@ -42048,7 +42624,7 @@
         <v>95</v>
       </c>
       <c r="C2400">
-        <v>4592.7</v>
+        <v>4849.6</v>
       </c>
       <c r="D2400" t="s">
         <v>2402</v>
@@ -42062,7 +42638,7 @@
         <v>96</v>
       </c>
       <c r="C2401">
-        <v>4561.6</v>
+        <v>4826.8</v>
       </c>
       <c r="D2401" t="s">
         <v>2403</v>
@@ -42076,7 +42652,7 @@
         <v>1</v>
       </c>
       <c r="C2402">
-        <v>4352.1</v>
+        <v>4261.2</v>
       </c>
       <c r="D2402" t="s">
         <v>2404</v>
@@ -42090,7 +42666,7 @@
         <v>2</v>
       </c>
       <c r="C2403">
-        <v>4304.4</v>
+        <v>4247.6</v>
       </c>
       <c r="D2403" t="s">
         <v>2405</v>
@@ -42104,7 +42680,7 @@
         <v>3</v>
       </c>
       <c r="C2404">
-        <v>4237.4</v>
+        <v>4203.2</v>
       </c>
       <c r="D2404" t="s">
         <v>2406</v>
@@ -42118,7 +42694,7 @@
         <v>4</v>
       </c>
       <c r="C2405">
-        <v>4220.4</v>
+        <v>4195.8</v>
       </c>
       <c r="D2405" t="s">
         <v>2407</v>
@@ -42132,7 +42708,7 @@
         <v>5</v>
       </c>
       <c r="C2406">
-        <v>4356.9</v>
+        <v>3973.8</v>
       </c>
       <c r="D2406" t="s">
         <v>2408</v>
@@ -42146,7 +42722,7 @@
         <v>6</v>
       </c>
       <c r="C2407">
-        <v>4299.2</v>
+        <v>3964.6</v>
       </c>
       <c r="D2407" t="s">
         <v>2409</v>
@@ -42160,7 +42736,7 @@
         <v>7</v>
       </c>
       <c r="C2408">
-        <v>4283.7</v>
+        <v>3983</v>
       </c>
       <c r="D2408" t="s">
         <v>2410</v>
@@ -42174,7 +42750,7 @@
         <v>8</v>
       </c>
       <c r="C2409">
-        <v>4264.8</v>
+        <v>4004.9</v>
       </c>
       <c r="D2409" t="s">
         <v>2411</v>
@@ -42188,7 +42764,7 @@
         <v>9</v>
       </c>
       <c r="C2410">
-        <v>4122.5</v>
+        <v>3856.8</v>
       </c>
       <c r="D2410" t="s">
         <v>2412</v>
@@ -42202,7 +42778,7 @@
         <v>10</v>
       </c>
       <c r="C2411">
-        <v>4091.7</v>
+        <v>3853.2</v>
       </c>
       <c r="D2411" t="s">
         <v>2413</v>
@@ -42216,7 +42792,7 @@
         <v>11</v>
       </c>
       <c r="C2412">
-        <v>4067.3</v>
+        <v>3872.3</v>
       </c>
       <c r="D2412" t="s">
         <v>2414</v>
@@ -42230,7 +42806,7 @@
         <v>12</v>
       </c>
       <c r="C2413">
-        <v>4050.6</v>
+        <v>3895.8</v>
       </c>
       <c r="D2413" t="s">
         <v>2415</v>
@@ -42244,7 +42820,7 @@
         <v>13</v>
       </c>
       <c r="C2414">
-        <v>3996.2</v>
+        <v>3919.2</v>
       </c>
       <c r="D2414" t="s">
         <v>2416</v>
@@ -42258,7 +42834,7 @@
         <v>14</v>
       </c>
       <c r="C2415">
-        <v>3972.6</v>
+        <v>3939</v>
       </c>
       <c r="D2415" t="s">
         <v>2417</v>
@@ -42272,7 +42848,7 @@
         <v>15</v>
       </c>
       <c r="C2416">
-        <v>3968</v>
+        <v>3961.2</v>
       </c>
       <c r="D2416" t="s">
         <v>2418</v>
@@ -42286,7 +42862,7 @@
         <v>16</v>
       </c>
       <c r="C2417">
-        <v>3940.7</v>
+        <v>3979.7</v>
       </c>
       <c r="D2417" t="s">
         <v>2419</v>
@@ -42300,7 +42876,7 @@
         <v>17</v>
       </c>
       <c r="C2418">
-        <v>3909.1</v>
+        <v>3954.1</v>
       </c>
       <c r="D2418" t="s">
         <v>2420</v>
@@ -42314,7 +42890,7 @@
         <v>18</v>
       </c>
       <c r="C2419">
-        <v>3918.3</v>
+        <v>3957.1</v>
       </c>
       <c r="D2419" t="s">
         <v>2421</v>
@@ -42328,7 +42904,7 @@
         <v>19</v>
       </c>
       <c r="C2420">
-        <v>3904.4</v>
+        <v>3935.6</v>
       </c>
       <c r="D2420" t="s">
         <v>2422</v>
@@ -42342,7 +42918,7 @@
         <v>20</v>
       </c>
       <c r="C2421">
-        <v>3897.1</v>
+        <v>3955.2</v>
       </c>
       <c r="D2421" t="s">
         <v>2423</v>
@@ -42356,7 +42932,7 @@
         <v>21</v>
       </c>
       <c r="C2422">
-        <v>3867.3</v>
+        <v>3934.3</v>
       </c>
       <c r="D2422" t="s">
         <v>2424</v>
@@ -42370,7 +42946,7 @@
         <v>22</v>
       </c>
       <c r="C2423">
-        <v>3817</v>
+        <v>3905.8</v>
       </c>
       <c r="D2423" t="s">
         <v>2425</v>
@@ -42384,7 +42960,7 @@
         <v>23</v>
       </c>
       <c r="C2424">
-        <v>3762.6</v>
+        <v>3841.8</v>
       </c>
       <c r="D2424" t="s">
         <v>2426</v>
@@ -42398,7 +42974,7 @@
         <v>24</v>
       </c>
       <c r="C2425">
-        <v>3678.9</v>
+        <v>3745.5</v>
       </c>
       <c r="D2425" t="s">
         <v>2427</v>
@@ -42412,7 +42988,7 @@
         <v>25</v>
       </c>
       <c r="C2426">
-        <v>3527</v>
+        <v>3769.9</v>
       </c>
       <c r="D2426" t="s">
         <v>2428</v>
@@ -42426,7 +43002,7 @@
         <v>26</v>
       </c>
       <c r="C2427">
-        <v>3454</v>
+        <v>3652.1</v>
       </c>
       <c r="D2427" t="s">
         <v>2429</v>
@@ -42440,7 +43016,7 @@
         <v>27</v>
       </c>
       <c r="C2428">
-        <v>3349.3</v>
+        <v>3583.2</v>
       </c>
       <c r="D2428" t="s">
         <v>2430</v>
@@ -42454,7 +43030,7 @@
         <v>28</v>
       </c>
       <c r="C2429">
-        <v>3245.6</v>
+        <v>3509.1</v>
       </c>
       <c r="D2429" t="s">
         <v>2431</v>
@@ -42468,7 +43044,7 @@
         <v>29</v>
       </c>
       <c r="C2430">
-        <v>3235.3</v>
+        <v>3723</v>
       </c>
       <c r="D2430" t="s">
         <v>2432</v>
@@ -42482,7 +43058,7 @@
         <v>30</v>
       </c>
       <c r="C2431">
-        <v>3167.1</v>
+        <v>3715.1</v>
       </c>
       <c r="D2431" t="s">
         <v>2433</v>
@@ -42496,7 +43072,7 @@
         <v>31</v>
       </c>
       <c r="C2432">
-        <v>3164.9</v>
+        <v>3765.3</v>
       </c>
       <c r="D2432" t="s">
         <v>2434</v>
@@ -42510,7 +43086,7 @@
         <v>32</v>
       </c>
       <c r="C2433">
-        <v>3206.1</v>
+        <v>3845.9</v>
       </c>
       <c r="D2433" t="s">
         <v>2435</v>
@@ -42524,7 +43100,7 @@
         <v>33</v>
       </c>
       <c r="C2434">
-        <v>3308.5</v>
+        <v>3912.9</v>
       </c>
       <c r="D2434" t="s">
         <v>2436</v>
@@ -42538,7 +43114,7 @@
         <v>34</v>
       </c>
       <c r="C2435">
-        <v>3383.2</v>
+        <v>3961.4</v>
       </c>
       <c r="D2435" t="s">
         <v>2437</v>
@@ -42552,7 +43128,7 @@
         <v>35</v>
       </c>
       <c r="C2436">
-        <v>3515.2</v>
+        <v>4036.6</v>
       </c>
       <c r="D2436" t="s">
         <v>2438</v>
@@ -42566,7 +43142,7 @@
         <v>36</v>
       </c>
       <c r="C2437">
-        <v>3633.3</v>
+        <v>4185.5</v>
       </c>
       <c r="D2437" t="s">
         <v>2439</v>
@@ -42580,7 +43156,7 @@
         <v>37</v>
       </c>
       <c r="C2438">
-        <v>3634.4</v>
+        <v>4138.1</v>
       </c>
       <c r="D2438" t="s">
         <v>2440</v>
@@ -42594,7 +43170,7 @@
         <v>38</v>
       </c>
       <c r="C2439">
-        <v>3718.2</v>
+        <v>4207.8</v>
       </c>
       <c r="D2439" t="s">
         <v>2441</v>
@@ -42608,7 +43184,7 @@
         <v>39</v>
       </c>
       <c r="C2440">
-        <v>3871.9</v>
+        <v>4386.2</v>
       </c>
       <c r="D2440" t="s">
         <v>2442</v>
@@ -42622,7 +43198,7 @@
         <v>40</v>
       </c>
       <c r="C2441">
-        <v>4017.3</v>
+        <v>4548.2</v>
       </c>
       <c r="D2441" t="s">
         <v>2443</v>
@@ -42636,7 +43212,7 @@
         <v>41</v>
       </c>
       <c r="C2442">
-        <v>4056.2</v>
+        <v>4688.3</v>
       </c>
       <c r="D2442" t="s">
         <v>2444</v>
@@ -42650,7 +43226,7 @@
         <v>42</v>
       </c>
       <c r="C2443">
-        <v>4159.7</v>
+        <v>4788.9</v>
       </c>
       <c r="D2443" t="s">
         <v>2445</v>
@@ -42664,7 +43240,7 @@
         <v>43</v>
       </c>
       <c r="C2444">
-        <v>4295.8</v>
+        <v>4923.2</v>
       </c>
       <c r="D2444" t="s">
         <v>2446</v>
@@ -42678,7 +43254,7 @@
         <v>44</v>
       </c>
       <c r="C2445">
-        <v>4408.2</v>
+        <v>5014.2</v>
       </c>
       <c r="D2445" t="s">
         <v>2447</v>
@@ -42692,7 +43268,7 @@
         <v>45</v>
       </c>
       <c r="C2446">
-        <v>4379.3</v>
+        <v>4586.6</v>
       </c>
       <c r="D2446" t="s">
         <v>2448</v>
@@ -42706,7 +43282,7 @@
         <v>46</v>
       </c>
       <c r="C2447">
-        <v>4430</v>
+        <v>4562.4</v>
       </c>
       <c r="D2447" t="s">
         <v>2449</v>
@@ -42720,7 +43296,7 @@
         <v>47</v>
       </c>
       <c r="C2448">
-        <v>4502.7</v>
+        <v>4410.9</v>
       </c>
       <c r="D2448" t="s">
         <v>2450</v>
@@ -42734,7 +43310,7 @@
         <v>48</v>
       </c>
       <c r="C2449">
-        <v>4552.3</v>
+        <v>4574.1</v>
       </c>
       <c r="D2449" t="s">
         <v>2451</v>
@@ -42748,7 +43324,7 @@
         <v>49</v>
       </c>
       <c r="C2450">
-        <v>4519.3</v>
+        <v>4349.6</v>
       </c>
       <c r="D2450" t="s">
         <v>2452</v>
@@ -42762,7 +43338,7 @@
         <v>50</v>
       </c>
       <c r="C2451">
-        <v>4535.7</v>
+        <v>4288.3</v>
       </c>
       <c r="D2451" t="s">
         <v>2453</v>
@@ -42776,7 +43352,7 @@
         <v>51</v>
       </c>
       <c r="C2452">
-        <v>4549.2</v>
+        <v>4247.2</v>
       </c>
       <c r="D2452" t="s">
         <v>2454</v>
@@ -42790,7 +43366,7 @@
         <v>52</v>
       </c>
       <c r="C2453">
-        <v>4590</v>
+        <v>4160</v>
       </c>
       <c r="D2453" t="s">
         <v>2455</v>
@@ -42804,7 +43380,7 @@
         <v>53</v>
       </c>
       <c r="C2454">
-        <v>4568.4</v>
+        <v>3878.1</v>
       </c>
       <c r="D2454" t="s">
         <v>2456</v>
@@ -42818,7 +43394,7 @@
         <v>54</v>
       </c>
       <c r="C2455">
-        <v>4578.4</v>
+        <v>3799.3</v>
       </c>
       <c r="D2455" t="s">
         <v>2457</v>
@@ -42832,7 +43408,7 @@
         <v>55</v>
       </c>
       <c r="C2456">
-        <v>4575.3</v>
+        <v>3770.3</v>
       </c>
       <c r="D2456" t="s">
         <v>2458</v>
@@ -42846,7 +43422,7 @@
         <v>56</v>
       </c>
       <c r="C2457">
-        <v>4553.7</v>
+        <v>3736.4</v>
       </c>
       <c r="D2457" t="s">
         <v>2459</v>
@@ -42860,7 +43436,7 @@
         <v>57</v>
       </c>
       <c r="C2458">
-        <v>4530.2</v>
+        <v>3844.9</v>
       </c>
       <c r="D2458" t="s">
         <v>2460</v>
@@ -42874,7 +43450,7 @@
         <v>58</v>
       </c>
       <c r="C2459">
-        <v>4520.7</v>
+        <v>3841</v>
       </c>
       <c r="D2459" t="s">
         <v>2461</v>
@@ -42888,7 +43464,7 @@
         <v>59</v>
       </c>
       <c r="C2460">
-        <v>4517.3</v>
+        <v>3845.7</v>
       </c>
       <c r="D2460" t="s">
         <v>2462</v>
@@ -42902,7 +43478,7 @@
         <v>60</v>
       </c>
       <c r="C2461">
-        <v>4552.3</v>
+        <v>3870.8</v>
       </c>
       <c r="D2461" t="s">
         <v>2463</v>
@@ -42916,7 +43492,7 @@
         <v>61</v>
       </c>
       <c r="C2462">
-        <v>4497.6</v>
+        <v>3891.1</v>
       </c>
       <c r="D2462" t="s">
         <v>2464</v>
@@ -42930,7 +43506,7 @@
         <v>62</v>
       </c>
       <c r="C2463">
-        <v>4513</v>
+        <v>3917.5</v>
       </c>
       <c r="D2463" t="s">
         <v>2465</v>
@@ -42944,7 +43520,7 @@
         <v>63</v>
       </c>
       <c r="C2464">
-        <v>4483.7</v>
+        <v>3949.5</v>
       </c>
       <c r="D2464" t="s">
         <v>2466</v>
@@ -42958,7 +43534,7 @@
         <v>64</v>
       </c>
       <c r="C2465">
-        <v>4422.7</v>
+        <v>4020.1</v>
       </c>
       <c r="D2465" t="s">
         <v>2467</v>
@@ -42972,7 +43548,7 @@
         <v>65</v>
       </c>
       <c r="C2466">
-        <v>4406.1</v>
+        <v>4263.2</v>
       </c>
       <c r="D2466" t="s">
         <v>2468</v>
@@ -42986,7 +43562,7 @@
         <v>66</v>
       </c>
       <c r="C2467">
-        <v>4365</v>
+        <v>4320.8</v>
       </c>
       <c r="D2467" t="s">
         <v>2469</v>
@@ -43000,7 +43576,7 @@
         <v>67</v>
       </c>
       <c r="C2468">
-        <v>4281.3</v>
+        <v>4477.2</v>
       </c>
       <c r="D2468" t="s">
         <v>2470</v>
@@ -43014,7 +43590,7 @@
         <v>68</v>
       </c>
       <c r="C2469">
-        <v>4231.1</v>
+        <v>4687.7</v>
       </c>
       <c r="D2469" t="s">
         <v>2471</v>
@@ -43028,7 +43604,7 @@
         <v>69</v>
       </c>
       <c r="C2470">
-        <v>4262.7</v>
+        <v>4948.8</v>
       </c>
       <c r="D2470" t="s">
         <v>2472</v>
@@ -43042,7 +43618,7 @@
         <v>70</v>
       </c>
       <c r="C2471">
-        <v>4190.8</v>
+        <v>4932</v>
       </c>
       <c r="D2471" t="s">
         <v>2473</v>
@@ -43056,7 +43632,7 @@
         <v>71</v>
       </c>
       <c r="C2472">
-        <v>4105.6</v>
+        <v>4904.4</v>
       </c>
       <c r="D2472" t="s">
         <v>2474</v>
@@ -43070,7 +43646,7 @@
         <v>72</v>
       </c>
       <c r="C2473">
-        <v>4015.3</v>
+        <v>4869.6</v>
       </c>
       <c r="D2473" t="s">
         <v>2475</v>
@@ -43084,7 +43660,7 @@
         <v>73</v>
       </c>
       <c r="C2474">
-        <v>4397</v>
+        <v>5417.6</v>
       </c>
       <c r="D2474" t="s">
         <v>2476</v>
@@ -43098,7 +43674,7 @@
         <v>74</v>
       </c>
       <c r="C2475">
-        <v>4324.1</v>
+        <v>5380.7</v>
       </c>
       <c r="D2475" t="s">
         <v>2477</v>
@@ -43112,7 +43688,7 @@
         <v>75</v>
       </c>
       <c r="C2476">
-        <v>4218.1</v>
+        <v>5254.8</v>
       </c>
       <c r="D2476" t="s">
         <v>2478</v>
@@ -43126,7 +43702,7 @@
         <v>76</v>
       </c>
       <c r="C2477">
-        <v>4163.7</v>
+        <v>5216.9</v>
       </c>
       <c r="D2477" t="s">
         <v>2479</v>
@@ -43140,7 +43716,7 @@
         <v>77</v>
       </c>
       <c r="C2478">
-        <v>4067.4</v>
+        <v>5936.9</v>
       </c>
       <c r="D2478" t="s">
         <v>2480</v>
@@ -43154,7 +43730,7 @@
         <v>78</v>
       </c>
       <c r="C2479">
-        <v>4051</v>
+        <v>5898.4</v>
       </c>
       <c r="D2479" t="s">
         <v>2481</v>
@@ -43168,7 +43744,7 @@
         <v>79</v>
       </c>
       <c r="C2480">
-        <v>4056.9</v>
+        <v>5857.8</v>
       </c>
       <c r="D2480" t="s">
         <v>2482</v>
@@ -43182,7 +43758,7 @@
         <v>80</v>
       </c>
       <c r="C2481">
-        <v>4071.4</v>
+        <v>5822.7</v>
       </c>
       <c r="D2481" t="s">
         <v>2483</v>
@@ -43196,7 +43772,7 @@
         <v>81</v>
       </c>
       <c r="C2482">
-        <v>4335.5</v>
+        <v>5967.7</v>
       </c>
       <c r="D2482" t="s">
         <v>2484</v>
@@ -43210,7 +43786,7 @@
         <v>82</v>
       </c>
       <c r="C2483">
-        <v>4337.6</v>
+        <v>5948.4</v>
       </c>
       <c r="D2483" t="s">
         <v>2485</v>
@@ -43224,7 +43800,7 @@
         <v>83</v>
       </c>
       <c r="C2484">
-        <v>4403.7</v>
+        <v>5926.4</v>
       </c>
       <c r="D2484" t="s">
         <v>2486</v>
@@ -43238,7 +43814,7 @@
         <v>84</v>
       </c>
       <c r="C2485">
-        <v>4430.3</v>
+        <v>6001.6</v>
       </c>
       <c r="D2485" t="s">
         <v>2487</v>
@@ -43252,7 +43828,7 @@
         <v>85</v>
       </c>
       <c r="C2486">
-        <v>4518</v>
+        <v>5972.7</v>
       </c>
       <c r="D2486" t="s">
         <v>2488</v>
@@ -43266,7 +43842,7 @@
         <v>86</v>
       </c>
       <c r="C2487">
-        <v>4515.3</v>
+        <v>5926.6</v>
       </c>
       <c r="D2487" t="s">
         <v>2489</v>
@@ -43280,7 +43856,7 @@
         <v>87</v>
       </c>
       <c r="C2488">
-        <v>4530.2</v>
+        <v>5904.2</v>
       </c>
       <c r="D2488" t="s">
         <v>2490</v>
@@ -43294,7 +43870,7 @@
         <v>88</v>
       </c>
       <c r="C2489">
-        <v>4544.3</v>
+        <v>5990.6</v>
       </c>
       <c r="D2489" t="s">
         <v>2491</v>
@@ -43308,7 +43884,7 @@
         <v>89</v>
       </c>
       <c r="C2490">
-        <v>4210.1</v>
+        <v>5602.9</v>
       </c>
       <c r="D2490" t="s">
         <v>2492</v>
@@ -43322,7 +43898,7 @@
         <v>90</v>
       </c>
       <c r="C2491">
-        <v>4167.6</v>
+        <v>5543.4</v>
       </c>
       <c r="D2491" t="s">
         <v>2493</v>
@@ -43336,7 +43912,7 @@
         <v>91</v>
       </c>
       <c r="C2492">
-        <v>4178.5</v>
+        <v>5511.3</v>
       </c>
       <c r="D2492" t="s">
         <v>2494</v>
@@ -43350,7 +43926,7 @@
         <v>92</v>
       </c>
       <c r="C2493">
-        <v>4190.2</v>
+        <v>5443.4</v>
       </c>
       <c r="D2493" t="s">
         <v>2495</v>
@@ -43364,7 +43940,7 @@
         <v>93</v>
       </c>
       <c r="C2494">
-        <v>4310.6</v>
+        <v>5057.1</v>
       </c>
       <c r="D2494" t="s">
         <v>2496</v>
@@ -43378,7 +43954,7 @@
         <v>94</v>
       </c>
       <c r="C2495">
-        <v>4287.2</v>
+        <v>4995.2</v>
       </c>
       <c r="D2495" t="s">
         <v>2497</v>
@@ -43392,7 +43968,7 @@
         <v>95</v>
       </c>
       <c r="C2496">
-        <v>4262.7</v>
+        <v>4938.5</v>
       </c>
       <c r="D2496" t="s">
         <v>2498</v>
@@ -43406,7 +43982,7 @@
         <v>96</v>
       </c>
       <c r="C2497">
-        <v>4251.6</v>
+        <v>4889.2</v>
       </c>
       <c r="D2497" t="s">
         <v>2499</v>
@@ -43420,7 +43996,7 @@
         <v>1</v>
       </c>
       <c r="C2498">
-        <v>4132.1</v>
+        <v>4101.2</v>
       </c>
       <c r="D2498" t="s">
         <v>2500</v>
@@ -43434,7 +44010,7 @@
         <v>2</v>
       </c>
       <c r="C2499">
-        <v>4114.4</v>
+        <v>4107.6</v>
       </c>
       <c r="D2499" t="s">
         <v>2501</v>
@@ -43448,7 +44024,7 @@
         <v>3</v>
       </c>
       <c r="C2500">
-        <v>4067.4</v>
+        <v>4073.2</v>
       </c>
       <c r="D2500" t="s">
         <v>2502</v>
@@ -43462,7 +44038,7 @@
         <v>4</v>
       </c>
       <c r="C2501">
-        <v>4060.4</v>
+        <v>4075.8</v>
       </c>
       <c r="D2501" t="s">
         <v>2503</v>
@@ -43476,7 +44052,7 @@
         <v>5</v>
       </c>
       <c r="C2502">
-        <v>4196.9</v>
+        <v>3843.8</v>
       </c>
       <c r="D2502" t="s">
         <v>2504</v>
@@ -43490,7 +44066,7 @@
         <v>6</v>
       </c>
       <c r="C2503">
-        <v>4149.2</v>
+        <v>3844.6</v>
       </c>
       <c r="D2503" t="s">
         <v>2505</v>
@@ -43504,7 +44080,7 @@
         <v>7</v>
       </c>
       <c r="C2504">
-        <v>4143.7</v>
+        <v>3863</v>
       </c>
       <c r="D2504" t="s">
         <v>2506</v>
@@ -43518,7 +44094,7 @@
         <v>8</v>
       </c>
       <c r="C2505">
-        <v>4134.8</v>
+        <v>3884.9</v>
       </c>
       <c r="D2505" t="s">
         <v>2507</v>
@@ -43532,7 +44108,7 @@
         <v>9</v>
       </c>
       <c r="C2506">
-        <v>4002.5</v>
+        <v>3756.8</v>
       </c>
       <c r="D2506" t="s">
         <v>2508</v>
@@ -43546,7 +44122,7 @@
         <v>10</v>
       </c>
       <c r="C2507">
-        <v>3991.7</v>
+        <v>3793.2</v>
       </c>
       <c r="D2507" t="s">
         <v>2509</v>
@@ -43560,7 +44136,7 @@
         <v>11</v>
       </c>
       <c r="C2508">
-        <v>3977.3</v>
+        <v>3822.3</v>
       </c>
       <c r="D2508" t="s">
         <v>2510</v>
@@ -43574,7 +44150,7 @@
         <v>12</v>
       </c>
       <c r="C2509">
-        <v>3990.6</v>
+        <v>3845.8</v>
       </c>
       <c r="D2509" t="s">
         <v>2511</v>
@@ -43588,7 +44164,7 @@
         <v>13</v>
       </c>
       <c r="C2510">
-        <v>3946.2</v>
+        <v>3869.2</v>
       </c>
       <c r="D2510" t="s">
         <v>2512</v>
@@ -43602,7 +44178,7 @@
         <v>14</v>
       </c>
       <c r="C2511">
-        <v>3952.6</v>
+        <v>3889</v>
       </c>
       <c r="D2511" t="s">
         <v>2513</v>
@@ -43616,7 +44192,7 @@
         <v>15</v>
       </c>
       <c r="C2512">
-        <v>3958</v>
+        <v>3911.2</v>
       </c>
       <c r="D2512" t="s">
         <v>2514</v>
@@ -43630,7 +44206,7 @@
         <v>16</v>
       </c>
       <c r="C2513">
-        <v>3940.7</v>
+        <v>3929.7</v>
       </c>
       <c r="D2513" t="s">
         <v>2515</v>
@@ -43644,7 +44220,7 @@
         <v>17</v>
       </c>
       <c r="C2514">
-        <v>3929.1</v>
+        <v>3934.1</v>
       </c>
       <c r="D2514" t="s">
         <v>2516</v>
@@ -43658,7 +44234,7 @@
         <v>18</v>
       </c>
       <c r="C2515">
-        <v>3948.3</v>
+        <v>3967.1</v>
       </c>
       <c r="D2515" t="s">
         <v>2517</v>
@@ -43672,7 +44248,7 @@
         <v>19</v>
       </c>
       <c r="C2516">
-        <v>3944.4</v>
+        <v>3995.6</v>
       </c>
       <c r="D2516" t="s">
         <v>2518</v>
@@ -43686,7 +44262,7 @@
         <v>20</v>
       </c>
       <c r="C2517">
-        <v>3947.1</v>
+        <v>4035.2</v>
       </c>
       <c r="D2517" t="s">
         <v>2519</v>
@@ -43700,7 +44276,7 @@
         <v>21</v>
       </c>
       <c r="C2518">
-        <v>3937.3</v>
+        <v>4044.3</v>
       </c>
       <c r="D2518" t="s">
         <v>2520</v>
@@ -43714,7 +44290,7 @@
         <v>22</v>
       </c>
       <c r="C2519">
-        <v>3937</v>
+        <v>4085.8</v>
       </c>
       <c r="D2519" t="s">
         <v>2521</v>
@@ -43728,7 +44304,7 @@
         <v>23</v>
       </c>
       <c r="C2520">
-        <v>3972.6</v>
+        <v>4101.8</v>
       </c>
       <c r="D2520" t="s">
         <v>2522</v>
@@ -43742,7 +44318,7 @@
         <v>24</v>
       </c>
       <c r="C2521">
-        <v>4018.9</v>
+        <v>4115.5</v>
       </c>
       <c r="D2521" t="s">
         <v>2523</v>
@@ -43756,7 +44332,7 @@
         <v>25</v>
       </c>
       <c r="C2522">
-        <v>4017</v>
+        <v>4299.9</v>
       </c>
       <c r="D2522" t="s">
         <v>2524</v>
@@ -43770,7 +44346,7 @@
         <v>26</v>
       </c>
       <c r="C2523">
-        <v>4114</v>
+        <v>4382.1</v>
       </c>
       <c r="D2523" t="s">
         <v>2525</v>
@@ -43784,7 +44360,7 @@
         <v>27</v>
       </c>
       <c r="C2524">
-        <v>4169.3</v>
+        <v>4463.2</v>
       </c>
       <c r="D2524" t="s">
         <v>2526</v>
@@ -43798,7 +44374,7 @@
         <v>28</v>
       </c>
       <c r="C2525">
-        <v>4245.6</v>
+        <v>4539.1</v>
       </c>
       <c r="D2525" t="s">
         <v>2527</v>
@@ -43812,7 +44388,7 @@
         <v>29</v>
       </c>
       <c r="C2526">
-        <v>4395.3</v>
+        <v>4943</v>
       </c>
       <c r="D2526" t="s">
         <v>2528</v>
@@ -43826,7 +44402,7 @@
         <v>30</v>
       </c>
       <c r="C2527">
-        <v>4467.1</v>
+        <v>5055.1</v>
       </c>
       <c r="D2527" t="s">
         <v>2529</v>
@@ -43840,7 +44416,7 @@
         <v>31</v>
       </c>
       <c r="C2528">
-        <v>4574.9</v>
+        <v>5195.3</v>
       </c>
       <c r="D2528" t="s">
         <v>2530</v>
@@ -43854,7 +44430,7 @@
         <v>32</v>
       </c>
       <c r="C2529">
-        <v>4676.1</v>
+        <v>5385.9</v>
       </c>
       <c r="D2529" t="s">
         <v>2531</v>
@@ -43868,7 +44444,7 @@
         <v>33</v>
       </c>
       <c r="C2530">
-        <v>4818.5</v>
+        <v>5632.9</v>
       </c>
       <c r="D2530" t="s">
         <v>2532</v>
@@ -43882,7 +44458,7 @@
         <v>34</v>
       </c>
       <c r="C2531">
-        <v>4913.2</v>
+        <v>5831.4</v>
       </c>
       <c r="D2531" t="s">
         <v>2533</v>
@@ -43896,7 +44472,7 @@
         <v>35</v>
       </c>
       <c r="C2532">
-        <v>5055.2</v>
+        <v>6056.6</v>
       </c>
       <c r="D2532" t="s">
         <v>2534</v>
@@ -43910,7 +44486,7 @@
         <v>36</v>
       </c>
       <c r="C2533">
-        <v>5183.3</v>
+        <v>6225.5</v>
       </c>
       <c r="D2533" t="s">
         <v>2535</v>
@@ -43924,7 +44500,7 @@
         <v>37</v>
       </c>
       <c r="C2534">
-        <v>5174.4</v>
+        <v>6098.1</v>
       </c>
       <c r="D2534" t="s">
         <v>2536</v>
@@ -43938,7 +44514,7 @@
         <v>38</v>
       </c>
       <c r="C2535">
-        <v>5248.2</v>
+        <v>5977.8</v>
       </c>
       <c r="D2535" t="s">
         <v>2537</v>
@@ -43952,7 +44528,7 @@
         <v>39</v>
       </c>
       <c r="C2536">
-        <v>5381.9</v>
+        <v>6166.2</v>
       </c>
       <c r="D2536" t="s">
         <v>2538</v>
@@ -43966,7 +44542,7 @@
         <v>40</v>
       </c>
       <c r="C2537">
-        <v>5487.3</v>
+        <v>6218.2</v>
       </c>
       <c r="D2537" t="s">
         <v>2539</v>
@@ -43980,7 +44556,7 @@
         <v>41</v>
       </c>
       <c r="C2538">
-        <v>5486.2</v>
+        <v>6248.3</v>
       </c>
       <c r="D2538" t="s">
         <v>2540</v>
@@ -43994,7 +44570,7 @@
         <v>42</v>
       </c>
       <c r="C2539">
-        <v>5549.7</v>
+        <v>6308.9</v>
       </c>
       <c r="D2539" t="s">
         <v>2541</v>
@@ -44008,7 +44584,7 @@
         <v>43</v>
       </c>
       <c r="C2540">
-        <v>5645.8</v>
+        <v>6393.2</v>
       </c>
       <c r="D2540" t="s">
         <v>2542</v>
@@ -44022,7 +44598,7 @@
         <v>44</v>
       </c>
       <c r="C2541">
-        <v>5698.2</v>
+        <v>6454.2</v>
       </c>
       <c r="D2541" t="s">
         <v>2543</v>
@@ -44036,7 +44612,7 @@
         <v>45</v>
       </c>
       <c r="C2542">
-        <v>5629.3</v>
+        <v>5976.6</v>
       </c>
       <c r="D2542" t="s">
         <v>2544</v>
@@ -44050,7 +44626,7 @@
         <v>46</v>
       </c>
       <c r="C2543">
-        <v>5650</v>
+        <v>5912.4</v>
       </c>
       <c r="D2543" t="s">
         <v>2545</v>
@@ -44064,7 +44640,7 @@
         <v>47</v>
       </c>
       <c r="C2544">
-        <v>5692.7</v>
+        <v>5720.9</v>
       </c>
       <c r="D2544" t="s">
         <v>2546</v>
@@ -44078,7 +44654,7 @@
         <v>48</v>
       </c>
       <c r="C2545">
-        <v>5732.3</v>
+        <v>5854.1</v>
       </c>
       <c r="D2545" t="s">
         <v>2547</v>
@@ -44092,7 +44668,7 @@
         <v>49</v>
       </c>
       <c r="C2546">
-        <v>5689.3</v>
+        <v>5589.6</v>
       </c>
       <c r="D2546" t="s">
         <v>2548</v>
@@ -44106,7 +44682,7 @@
         <v>50</v>
       </c>
       <c r="C2547">
-        <v>5695.7</v>
+        <v>5498.3</v>
       </c>
       <c r="D2547" t="s">
         <v>2549</v>
@@ -44120,7 +44696,7 @@
         <v>51</v>
       </c>
       <c r="C2548">
-        <v>5719.2</v>
+        <v>5447.2</v>
       </c>
       <c r="D2548" t="s">
         <v>2550</v>
@@ -44134,7 +44710,7 @@
         <v>52</v>
       </c>
       <c r="C2549">
-        <v>5750</v>
+        <v>5350</v>
       </c>
       <c r="D2549" t="s">
         <v>2551</v>
@@ -44148,7 +44724,7 @@
         <v>53</v>
       </c>
       <c r="C2550">
-        <v>5728.4</v>
+        <v>5078.1</v>
       </c>
       <c r="D2550" t="s">
         <v>2552</v>
@@ -44162,7 +44738,7 @@
         <v>54</v>
       </c>
       <c r="C2551">
-        <v>5738.4</v>
+        <v>4989.3</v>
       </c>
       <c r="D2551" t="s">
         <v>2553</v>
@@ -44176,7 +44752,7 @@
         <v>55</v>
       </c>
       <c r="C2552">
-        <v>5725.3</v>
+        <v>4960.3</v>
       </c>
       <c r="D2552" t="s">
         <v>2554</v>
@@ -44190,7 +44766,7 @@
         <v>56</v>
       </c>
       <c r="C2553">
-        <v>5703.7</v>
+        <v>4896.4</v>
       </c>
       <c r="D2553" t="s">
         <v>2555</v>
@@ -44204,7 +44780,7 @@
         <v>57</v>
       </c>
       <c r="C2554">
-        <v>5680.2</v>
+        <v>4984.9</v>
       </c>
       <c r="D2554" t="s">
         <v>2556</v>
@@ -44218,7 +44794,7 @@
         <v>58</v>
       </c>
       <c r="C2555">
-        <v>5680.7</v>
+        <v>4961</v>
       </c>
       <c r="D2555" t="s">
         <v>2557</v>
@@ -44232,7 +44808,7 @@
         <v>59</v>
       </c>
       <c r="C2556">
-        <v>5677.3</v>
+        <v>4965.7</v>
       </c>
       <c r="D2556" t="s">
         <v>2558</v>
@@ -44246,7 +44822,7 @@
         <v>60</v>
       </c>
       <c r="C2557">
-        <v>5742.3</v>
+        <v>5000.8</v>
       </c>
       <c r="D2557" t="s">
         <v>2559</v>
@@ -44260,7 +44836,7 @@
         <v>61</v>
       </c>
       <c r="C2558">
-        <v>5727.6</v>
+        <v>5041.1</v>
       </c>
       <c r="D2558" t="s">
         <v>2560</v>
@@ -44274,7 +44850,7 @@
         <v>62</v>
       </c>
       <c r="C2559">
-        <v>5763</v>
+        <v>5067.5</v>
       </c>
       <c r="D2559" t="s">
         <v>2561</v>
@@ -44288,7 +44864,7 @@
         <v>63</v>
       </c>
       <c r="C2560">
-        <v>5743.7</v>
+        <v>5109.5</v>
       </c>
       <c r="D2560" t="s">
         <v>2562</v>
@@ -44302,7 +44878,7 @@
         <v>64</v>
       </c>
       <c r="C2561">
-        <v>5662.7</v>
+        <v>5170.1</v>
       </c>
       <c r="D2561" t="s">
         <v>2563</v>
@@ -44316,7 +44892,7 @@
         <v>65</v>
       </c>
       <c r="C2562">
-        <v>5626.1</v>
+        <v>5393.2</v>
       </c>
       <c r="D2562" t="s">
         <v>2564</v>
@@ -44330,7 +44906,7 @@
         <v>66</v>
       </c>
       <c r="C2563">
-        <v>5545</v>
+        <v>5440.8</v>
       </c>
       <c r="D2563" t="s">
         <v>2565</v>
@@ -44344,7 +44920,7 @@
         <v>67</v>
       </c>
       <c r="C2564">
-        <v>5441.3</v>
+        <v>5557.2</v>
       </c>
       <c r="D2564" t="s">
         <v>2566</v>
@@ -44358,7 +44934,7 @@
         <v>68</v>
       </c>
       <c r="C2565">
-        <v>5371.1</v>
+        <v>5737.7</v>
       </c>
       <c r="D2565" t="s">
         <v>2567</v>
@@ -44372,7 +44948,7 @@
         <v>69</v>
       </c>
       <c r="C2566">
-        <v>5382.7</v>
+        <v>5958.8</v>
       </c>
       <c r="D2566" t="s">
         <v>2568</v>
@@ -44386,7 +44962,7 @@
         <v>70</v>
       </c>
       <c r="C2567">
-        <v>5300.8</v>
+        <v>5932</v>
       </c>
       <c r="D2567" t="s">
         <v>2569</v>
@@ -44400,7 +44976,7 @@
         <v>71</v>
       </c>
       <c r="C2568">
-        <v>5195.6</v>
+        <v>5904.4</v>
       </c>
       <c r="D2568" t="s">
         <v>2570</v>
@@ -44414,7 +44990,7 @@
         <v>72</v>
       </c>
       <c r="C2569">
-        <v>5085.3</v>
+        <v>5879.6</v>
       </c>
       <c r="D2569" t="s">
         <v>2571</v>
@@ -44428,7 +45004,7 @@
         <v>73</v>
       </c>
       <c r="C2570">
-        <v>5467</v>
+        <v>6457.6</v>
       </c>
       <c r="D2570" t="s">
         <v>2572</v>
@@ -44442,7 +45018,7 @@
         <v>74</v>
       </c>
       <c r="C2571">
-        <v>5374.1</v>
+        <v>6450.7</v>
       </c>
       <c r="D2571" t="s">
         <v>2573</v>
@@ -44456,7 +45032,7 @@
         <v>75</v>
       </c>
       <c r="C2572">
-        <v>5258.1</v>
+        <v>6324.8</v>
       </c>
       <c r="D2572" t="s">
         <v>2574</v>
@@ -44470,7 +45046,7 @@
         <v>76</v>
       </c>
       <c r="C2573">
-        <v>5193.7</v>
+        <v>6276.9</v>
       </c>
       <c r="D2573" t="s">
         <v>2575</v>
@@ -44484,7 +45060,7 @@
         <v>77</v>
       </c>
       <c r="C2574">
-        <v>5077.4</v>
+        <v>6976.9</v>
       </c>
       <c r="D2574" t="s">
         <v>2576</v>
@@ -44498,7 +45074,7 @@
         <v>78</v>
       </c>
       <c r="C2575">
-        <v>5051</v>
+        <v>6918.4</v>
       </c>
       <c r="D2575" t="s">
         <v>2577</v>
@@ -44512,7 +45088,7 @@
         <v>79</v>
       </c>
       <c r="C2576">
-        <v>5056.9</v>
+        <v>6867.8</v>
       </c>
       <c r="D2576" t="s">
         <v>2578</v>
@@ -44526,7 +45102,7 @@
         <v>80</v>
       </c>
       <c r="C2577">
-        <v>5081.4</v>
+        <v>6822.7</v>
       </c>
       <c r="D2577" t="s">
         <v>2579</v>
@@ -44540,7 +45116,7 @@
         <v>81</v>
       </c>
       <c r="C2578">
-        <v>5345.5</v>
+        <v>6957.7</v>
       </c>
       <c r="D2578" t="s">
         <v>2580</v>
@@ -44554,7 +45130,7 @@
         <v>82</v>
       </c>
       <c r="C2579">
-        <v>5347.6</v>
+        <v>6928.4</v>
       </c>
       <c r="D2579" t="s">
         <v>2581</v>
@@ -44568,7 +45144,7 @@
         <v>83</v>
       </c>
       <c r="C2580">
-        <v>5403.7</v>
+        <v>6886.4</v>
       </c>
       <c r="D2580" t="s">
         <v>2582</v>
@@ -44582,7 +45158,7 @@
         <v>84</v>
       </c>
       <c r="C2581">
-        <v>5420.3</v>
+        <v>6951.6</v>
       </c>
       <c r="D2581" t="s">
         <v>2583</v>
@@ -44596,7 +45172,7 @@
         <v>85</v>
       </c>
       <c r="C2582">
-        <v>5478</v>
+        <v>6972.7</v>
       </c>
       <c r="D2582" t="s">
         <v>2584</v>
@@ -44610,7 +45186,7 @@
         <v>86</v>
       </c>
       <c r="C2583">
-        <v>5445.3</v>
+        <v>6896.6</v>
       </c>
       <c r="D2583" t="s">
         <v>2585</v>
@@ -44624,7 +45200,7 @@
         <v>87</v>
       </c>
       <c r="C2584">
-        <v>5420.2</v>
+        <v>6804.2</v>
       </c>
       <c r="D2584" t="s">
         <v>2586</v>
@@ -44638,7 +45214,7 @@
         <v>88</v>
       </c>
       <c r="C2585">
-        <v>5404.3</v>
+        <v>6800.6</v>
       </c>
       <c r="D2585" t="s">
         <v>2587</v>
@@ -44652,7 +45228,7 @@
         <v>89</v>
       </c>
       <c r="C2586">
-        <v>5030.1</v>
+        <v>6372.9</v>
       </c>
       <c r="D2586" t="s">
         <v>2588</v>
@@ -44666,7 +45242,7 @@
         <v>90</v>
       </c>
       <c r="C2587">
-        <v>4947.6</v>
+        <v>6283.4</v>
       </c>
       <c r="D2587" t="s">
         <v>2589</v>
@@ -44680,7 +45256,7 @@
         <v>91</v>
       </c>
       <c r="C2588">
-        <v>4898.5</v>
+        <v>6221.3</v>
       </c>
       <c r="D2588" t="s">
         <v>2590</v>
@@ -44694,7 +45270,7 @@
         <v>92</v>
       </c>
       <c r="C2589">
-        <v>4870.2</v>
+        <v>6113.4</v>
       </c>
       <c r="D2589" t="s">
         <v>2591</v>
@@ -44708,7 +45284,7 @@
         <v>93</v>
       </c>
       <c r="C2590">
-        <v>4940.6</v>
+        <v>5707.1</v>
       </c>
       <c r="D2590" t="s">
         <v>2592</v>
@@ -44722,7 +45298,7 @@
         <v>94</v>
       </c>
       <c r="C2591">
-        <v>4877.2</v>
+        <v>5615.2</v>
       </c>
       <c r="D2591" t="s">
         <v>2593</v>
@@ -44736,7 +45312,7 @@
         <v>95</v>
       </c>
       <c r="C2592">
-        <v>4822.7</v>
+        <v>5528.5</v>
       </c>
       <c r="D2592" t="s">
         <v>2594</v>
@@ -44750,7 +45326,7 @@
         <v>96</v>
       </c>
       <c r="C2593">
-        <v>4791.6</v>
+        <v>5449.2</v>
       </c>
       <c r="D2593" t="s">
         <v>2595</v>
@@ -44764,7 +45340,7 @@
         <v>1</v>
       </c>
       <c r="C2594">
-        <v>4592.1</v>
+        <v>4631.2</v>
       </c>
       <c r="D2594" t="s">
         <v>2596</v>
@@ -44778,7 +45354,7 @@
         <v>2</v>
       </c>
       <c r="C2595">
-        <v>4564.4</v>
+        <v>4627.6</v>
       </c>
       <c r="D2595" t="s">
         <v>2597</v>
@@ -44792,7 +45368,7 @@
         <v>3</v>
       </c>
       <c r="C2596">
-        <v>4507.4</v>
+        <v>4583.2</v>
       </c>
       <c r="D2596" t="s">
         <v>2598</v>
@@ -44806,7 +45382,7 @@
         <v>4</v>
       </c>
       <c r="C2597">
-        <v>4490.4</v>
+        <v>4575.8</v>
       </c>
       <c r="D2597" t="s">
         <v>2599</v>
@@ -44820,7 +45396,7 @@
         <v>5</v>
       </c>
       <c r="C2598">
-        <v>4626.9</v>
+        <v>4353.8</v>
       </c>
       <c r="D2598" t="s">
         <v>2600</v>
@@ -44834,7 +45410,7 @@
         <v>6</v>
       </c>
       <c r="C2599">
-        <v>4579.2</v>
+        <v>4354.6</v>
       </c>
       <c r="D2599" t="s">
         <v>2601</v>
@@ -44848,7 +45424,7 @@
         <v>7</v>
       </c>
       <c r="C2600">
-        <v>4563.7</v>
+        <v>4373</v>
       </c>
       <c r="D2600" t="s">
         <v>2602</v>
@@ -44862,7 +45438,7 @@
         <v>8</v>
       </c>
       <c r="C2601">
-        <v>4554.8</v>
+        <v>4394.9</v>
       </c>
       <c r="D2601" t="s">
         <v>2603</v>
@@ -44876,7 +45452,7 @@
         <v>9</v>
       </c>
       <c r="C2602">
-        <v>4412.5</v>
+        <v>4256.8</v>
       </c>
       <c r="D2602" t="s">
         <v>2604</v>
@@ -44890,7 +45466,7 @@
         <v>10</v>
       </c>
       <c r="C2603">
-        <v>4401.7</v>
+        <v>4293.2</v>
       </c>
       <c r="D2603" t="s">
         <v>2605</v>
@@ -44904,7 +45480,7 @@
         <v>11</v>
       </c>
       <c r="C2604">
-        <v>4377.3</v>
+        <v>4322.3</v>
       </c>
       <c r="D2604" t="s">
         <v>2606</v>
@@ -44918,7 +45494,7 @@
         <v>12</v>
       </c>
       <c r="C2605">
-        <v>4380.6</v>
+        <v>4345.8</v>
       </c>
       <c r="D2605" t="s">
         <v>2607</v>
@@ -44932,7 +45508,7 @@
         <v>13</v>
       </c>
       <c r="C2606">
-        <v>4336.2</v>
+        <v>4369.2</v>
       </c>
       <c r="D2606" t="s">
         <v>2608</v>
@@ -44946,7 +45522,7 @@
         <v>14</v>
       </c>
       <c r="C2607">
-        <v>4332.6</v>
+        <v>4389</v>
       </c>
       <c r="D2607" t="s">
         <v>2609</v>
@@ -44960,7 +45536,7 @@
         <v>15</v>
       </c>
       <c r="C2608">
-        <v>4338</v>
+        <v>4421.2</v>
       </c>
       <c r="D2608" t="s">
         <v>2610</v>
@@ -44974,7 +45550,7 @@
         <v>16</v>
       </c>
       <c r="C2609">
-        <v>4310.7</v>
+        <v>4449.7</v>
       </c>
       <c r="D2609" t="s">
         <v>2611</v>
@@ -44988,7 +45564,7 @@
         <v>17</v>
       </c>
       <c r="C2610">
-        <v>4289.1</v>
+        <v>4454.1</v>
       </c>
       <c r="D2610" t="s">
         <v>2612</v>
@@ -45002,7 +45578,7 @@
         <v>18</v>
       </c>
       <c r="C2611">
-        <v>4308.3</v>
+        <v>4487.1</v>
       </c>
       <c r="D2611" t="s">
         <v>2613</v>
@@ -45016,7 +45592,7 @@
         <v>19</v>
       </c>
       <c r="C2612">
-        <v>4304.4</v>
+        <v>4495.6</v>
       </c>
       <c r="D2612" t="s">
         <v>2614</v>
@@ -45030,7 +45606,7 @@
         <v>20</v>
       </c>
       <c r="C2613">
-        <v>4307.1</v>
+        <v>4485.2</v>
       </c>
       <c r="D2613" t="s">
         <v>2615</v>
@@ -45044,7 +45620,7 @@
         <v>21</v>
       </c>
       <c r="C2614">
-        <v>4297.3</v>
+        <v>4464.3</v>
       </c>
       <c r="D2614" t="s">
         <v>2616</v>
@@ -45058,7 +45634,7 @@
         <v>22</v>
       </c>
       <c r="C2615">
-        <v>4277</v>
+        <v>4475.8</v>
       </c>
       <c r="D2615" t="s">
         <v>2617</v>
@@ -45072,7 +45648,7 @@
         <v>23</v>
       </c>
       <c r="C2616">
-        <v>4292.6</v>
+        <v>4471.8</v>
       </c>
       <c r="D2616" t="s">
         <v>2618</v>
@@ -45086,7 +45662,7 @@
         <v>24</v>
       </c>
       <c r="C2617">
-        <v>4298.9</v>
+        <v>4465.5</v>
       </c>
       <c r="D2617" t="s">
         <v>2619</v>
@@ -45100,7 +45676,7 @@
         <v>25</v>
       </c>
       <c r="C2618">
-        <v>4247</v>
+        <v>4619.9</v>
       </c>
       <c r="D2618" t="s">
         <v>2620</v>
@@ -45114,7 +45690,7 @@
         <v>26</v>
       </c>
       <c r="C2619">
-        <v>4294</v>
+        <v>4672.1</v>
       </c>
       <c r="D2619" t="s">
         <v>2621</v>
@@ -45128,7 +45704,7 @@
         <v>27</v>
       </c>
       <c r="C2620">
-        <v>4319.3</v>
+        <v>4733.2</v>
       </c>
       <c r="D2620" t="s">
         <v>2622</v>
@@ -45142,7 +45718,7 @@
         <v>28</v>
       </c>
       <c r="C2621">
-        <v>4375.6</v>
+        <v>4799.1</v>
       </c>
       <c r="D2621" t="s">
         <v>2623</v>
@@ -45156,7 +45732,7 @@
         <v>29</v>
       </c>
       <c r="C2622">
-        <v>4515.3</v>
+        <v>5193</v>
       </c>
       <c r="D2622" t="s">
         <v>2624</v>
@@ -45170,7 +45746,7 @@
         <v>30</v>
       </c>
       <c r="C2623">
-        <v>4577.1</v>
+        <v>5285.1</v>
       </c>
       <c r="D2623" t="s">
         <v>2625</v>
@@ -45184,7 +45760,7 @@
         <v>31</v>
       </c>
       <c r="C2624">
-        <v>4664.9</v>
+        <v>5405.3</v>
       </c>
       <c r="D2624" t="s">
         <v>2626</v>
@@ -45198,7 +45774,7 @@
         <v>32</v>
       </c>
       <c r="C2625">
-        <v>4756.1</v>
+        <v>5525.9</v>
       </c>
       <c r="D2625" t="s">
         <v>2627</v>
@@ -45212,7 +45788,7 @@
         <v>33</v>
       </c>
       <c r="C2626">
-        <v>4878.5</v>
+        <v>5752.9</v>
       </c>
       <c r="D2626" t="s">
         <v>2628</v>
@@ -45226,7 +45802,7 @@
         <v>34</v>
       </c>
       <c r="C2627">
-        <v>4953.2</v>
+        <v>5931.4</v>
       </c>
       <c r="D2627" t="s">
         <v>2629</v>
@@ -45240,7 +45816,7 @@
         <v>35</v>
       </c>
       <c r="C2628">
-        <v>5085.2</v>
+        <v>6156.6</v>
       </c>
       <c r="D2628" t="s">
         <v>2630</v>
@@ -45254,7 +45830,7 @@
         <v>36</v>
       </c>
       <c r="C2629">
-        <v>5203.3</v>
+        <v>6325.5</v>
       </c>
       <c r="D2629" t="s">
         <v>2631</v>
@@ -45268,7 +45844,7 @@
         <v>37</v>
       </c>
       <c r="C2630">
-        <v>5204.4</v>
+        <v>6348.1</v>
       </c>
       <c r="D2630" t="s">
         <v>2632</v>
@@ -45282,7 +45858,7 @@
         <v>38</v>
       </c>
       <c r="C2631">
-        <v>5278.2</v>
+        <v>6377.8</v>
       </c>
       <c r="D2631" t="s">
         <v>2633</v>
@@ -45296,7 +45872,7 @@
         <v>39</v>
       </c>
       <c r="C2632">
-        <v>5421.9</v>
+        <v>6366.2</v>
       </c>
       <c r="D2632" t="s">
         <v>2634</v>
@@ -45310,7 +45886,7 @@
         <v>40</v>
       </c>
       <c r="C2633">
-        <v>5537.3</v>
+        <v>6378.2</v>
       </c>
       <c r="D2633" t="s">
         <v>2635</v>
@@ -45324,7 +45900,7 @@
         <v>41</v>
       </c>
       <c r="C2634">
-        <v>5546.2</v>
+        <v>6498.3</v>
       </c>
       <c r="D2634" t="s">
         <v>2636</v>
@@ -45338,7 +45914,7 @@
         <v>42</v>
       </c>
       <c r="C2635">
-        <v>5609.7</v>
+        <v>6568.9</v>
       </c>
       <c r="D2635" t="s">
         <v>2637</v>
@@ -45352,7 +45928,7 @@
         <v>43</v>
       </c>
       <c r="C2636">
-        <v>5705.8</v>
+        <v>6653.2</v>
       </c>
       <c r="D2636" t="s">
         <v>2638</v>
@@ -45366,7 +45942,7 @@
         <v>44</v>
       </c>
       <c r="C2637">
-        <v>5768.2</v>
+        <v>6694.2</v>
       </c>
       <c r="D2637" t="s">
         <v>2639</v>
@@ -45380,7 +45956,7 @@
         <v>45</v>
       </c>
       <c r="C2638">
-        <v>5689.3</v>
+        <v>6206.6</v>
       </c>
       <c r="D2638" t="s">
         <v>2640</v>
@@ -45394,7 +45970,7 @@
         <v>46</v>
       </c>
       <c r="C2639">
-        <v>5710</v>
+        <v>6112.4</v>
       </c>
       <c r="D2639" t="s">
         <v>2641</v>
@@ -45408,7 +45984,7 @@
         <v>47</v>
       </c>
       <c r="C2640">
-        <v>5752.7</v>
+        <v>5900.9</v>
       </c>
       <c r="D2640" t="s">
         <v>2642</v>
@@ -45422,7 +45998,7 @@
         <v>48</v>
       </c>
       <c r="C2641">
-        <v>5792.3</v>
+        <v>6004.1</v>
       </c>
       <c r="D2641" t="s">
         <v>2643</v>
@@ -45436,7 +46012,7 @@
         <v>49</v>
       </c>
       <c r="C2642">
-        <v>5749.3</v>
+        <v>5719.6</v>
       </c>
       <c r="D2642" t="s">
         <v>2644</v>
@@ -45450,7 +46026,7 @@
         <v>50</v>
       </c>
       <c r="C2643">
-        <v>5755.7</v>
+        <v>5608.3</v>
       </c>
       <c r="D2643" t="s">
         <v>2645</v>
@@ -45464,7 +46040,7 @@
         <v>51</v>
       </c>
       <c r="C2644">
-        <v>5779.2</v>
+        <v>5557.2</v>
       </c>
       <c r="D2644" t="s">
         <v>2646</v>
@@ -45478,7 +46054,7 @@
         <v>52</v>
       </c>
       <c r="C2645">
-        <v>5810</v>
+        <v>5470</v>
       </c>
       <c r="D2645" t="s">
         <v>2647</v>
@@ -45492,7 +46068,7 @@
         <v>53</v>
       </c>
       <c r="C2646">
-        <v>5788.4</v>
+        <v>5208.1</v>
       </c>
       <c r="D2646" t="s">
         <v>2648</v>
@@ -45506,7 +46082,7 @@
         <v>54</v>
       </c>
       <c r="C2647">
-        <v>5798.4</v>
+        <v>5129.3</v>
       </c>
       <c r="D2647" t="s">
         <v>2649</v>
@@ -45520,7 +46096,7 @@
         <v>55</v>
       </c>
       <c r="C2648">
-        <v>5785.3</v>
+        <v>5090.3</v>
       </c>
       <c r="D2648" t="s">
         <v>2650</v>
@@ -45534,7 +46110,7 @@
         <v>56</v>
       </c>
       <c r="C2649">
-        <v>5763.7</v>
+        <v>5016.4</v>
       </c>
       <c r="D2649" t="s">
         <v>2651</v>
@@ -45548,7 +46124,7 @@
         <v>57</v>
       </c>
       <c r="C2650">
-        <v>5740.2</v>
+        <v>5074.9</v>
       </c>
       <c r="D2650" t="s">
         <v>2652</v>
@@ -45562,7 +46138,7 @@
         <v>58</v>
       </c>
       <c r="C2651">
-        <v>5730.7</v>
+        <v>5051</v>
       </c>
       <c r="D2651" t="s">
         <v>2653</v>
@@ -45576,7 +46152,7 @@
         <v>59</v>
       </c>
       <c r="C2652">
-        <v>5727.3</v>
+        <v>5085.7</v>
       </c>
       <c r="D2652" t="s">
         <v>2654</v>
@@ -45590,7 +46166,7 @@
         <v>60</v>
       </c>
       <c r="C2653">
-        <v>5782.3</v>
+        <v>5170.8</v>
       </c>
       <c r="D2653" t="s">
         <v>2655</v>
@@ -45604,7 +46180,7 @@
         <v>61</v>
       </c>
       <c r="C2654">
-        <v>5747.6</v>
+        <v>5291.1</v>
       </c>
       <c r="D2654" t="s">
         <v>2656</v>
@@ -45618,7 +46194,7 @@
         <v>62</v>
       </c>
       <c r="C2655">
-        <v>5773</v>
+        <v>5377.5</v>
       </c>
       <c r="D2655" t="s">
         <v>2657</v>
@@ -45632,7 +46208,7 @@
         <v>63</v>
       </c>
       <c r="C2656">
-        <v>5743.7</v>
+        <v>5439.5</v>
       </c>
       <c r="D2656" t="s">
         <v>2658</v>
@@ -45646,7 +46222,7 @@
         <v>64</v>
       </c>
       <c r="C2657">
-        <v>5662.7</v>
+        <v>5510.1</v>
       </c>
       <c r="D2657" t="s">
         <v>2659</v>
@@ -45660,7 +46236,7 @@
         <v>65</v>
       </c>
       <c r="C2658">
-        <v>5626.1</v>
+        <v>5713.2</v>
       </c>
       <c r="D2658" t="s">
         <v>2660</v>
@@ -45674,7 +46250,7 @@
         <v>66</v>
       </c>
       <c r="C2659">
-        <v>5555</v>
+        <v>5740.8</v>
       </c>
       <c r="D2659" t="s">
         <v>2661</v>
@@ -45688,7 +46264,7 @@
         <v>67</v>
       </c>
       <c r="C2660">
-        <v>5461.3</v>
+        <v>5857.2</v>
       </c>
       <c r="D2660" t="s">
         <v>2662</v>
@@ -45702,7 +46278,7 @@
         <v>68</v>
       </c>
       <c r="C2661">
-        <v>5401.1</v>
+        <v>6027.7</v>
       </c>
       <c r="D2661" t="s">
         <v>2663</v>
@@ -45716,7 +46292,7 @@
         <v>69</v>
       </c>
       <c r="C2662">
-        <v>5422.7</v>
+        <v>6248.8</v>
       </c>
       <c r="D2662" t="s">
         <v>2664</v>
@@ -45730,7 +46306,7 @@
         <v>70</v>
       </c>
       <c r="C2663">
-        <v>5350.8</v>
+        <v>6212</v>
       </c>
       <c r="D2663" t="s">
         <v>2665</v>
@@ -45744,7 +46320,7 @@
         <v>71</v>
       </c>
       <c r="C2664">
-        <v>5255.6</v>
+        <v>6154.4</v>
       </c>
       <c r="D2664" t="s">
         <v>2666</v>
@@ -45758,7 +46334,7 @@
         <v>72</v>
       </c>
       <c r="C2665">
-        <v>5135.3</v>
+        <v>6089.6</v>
       </c>
       <c r="D2665" t="s">
         <v>2667</v>
@@ -45772,7 +46348,7 @@
         <v>73</v>
       </c>
       <c r="C2666">
-        <v>5507</v>
+        <v>6607.6</v>
       </c>
       <c r="D2666" t="s">
         <v>2668</v>
@@ -45786,7 +46362,7 @@
         <v>74</v>
       </c>
       <c r="C2667">
-        <v>5414.1</v>
+        <v>6550.7</v>
       </c>
       <c r="D2667" t="s">
         <v>2669</v>
@@ -45800,7 +46376,7 @@
         <v>75</v>
       </c>
       <c r="C2668">
-        <v>5288.1</v>
+        <v>6404.8</v>
       </c>
       <c r="D2668" t="s">
         <v>2670</v>
@@ -45814,7 +46390,7 @@
         <v>76</v>
       </c>
       <c r="C2669">
-        <v>5213.7</v>
+        <v>6346.9</v>
       </c>
       <c r="D2669" t="s">
         <v>2671</v>
@@ -45828,7 +46404,7 @@
         <v>77</v>
       </c>
       <c r="C2670">
-        <v>5097.4</v>
+        <v>7046.9</v>
       </c>
       <c r="D2670" t="s">
         <v>2672</v>
@@ -45842,7 +46418,7 @@
         <v>78</v>
       </c>
       <c r="C2671">
-        <v>5071</v>
+        <v>6988.4</v>
       </c>
       <c r="D2671" t="s">
         <v>2673</v>
@@ -45856,7 +46432,7 @@
         <v>79</v>
       </c>
       <c r="C2672">
-        <v>5066.9</v>
+        <v>6937.8</v>
       </c>
       <c r="D2672" t="s">
         <v>2674</v>
@@ -45870,7 +46446,7 @@
         <v>80</v>
       </c>
       <c r="C2673">
-        <v>5081.4</v>
+        <v>6892.7</v>
       </c>
       <c r="D2673" t="s">
         <v>2675</v>
@@ -45884,7 +46460,7 @@
         <v>81</v>
       </c>
       <c r="C2674">
-        <v>5325.5</v>
+        <v>7027.7</v>
       </c>
       <c r="D2674" t="s">
         <v>2676</v>
@@ -45898,7 +46474,7 @@
         <v>82</v>
       </c>
       <c r="C2675">
-        <v>5327.6</v>
+        <v>6988.4</v>
       </c>
       <c r="D2675" t="s">
         <v>2677</v>
@@ -45912,7 +46488,7 @@
         <v>83</v>
       </c>
       <c r="C2676">
-        <v>5383.7</v>
+        <v>6946.4</v>
       </c>
       <c r="D2676" t="s">
         <v>2678</v>
@@ -45926,7 +46502,7 @@
         <v>84</v>
       </c>
       <c r="C2677">
-        <v>5400.3</v>
+        <v>7061.6</v>
       </c>
       <c r="D2677" t="s">
         <v>2679</v>
@@ -45940,7 +46516,7 @@
         <v>85</v>
       </c>
       <c r="C2678">
-        <v>5458</v>
+        <v>7052.7</v>
       </c>
       <c r="D2678" t="s">
         <v>2680</v>
@@ -45954,7 +46530,7 @@
         <v>86</v>
       </c>
       <c r="C2679">
-        <v>5435.3</v>
+        <v>7026.6</v>
       </c>
       <c r="D2679" t="s">
         <v>2681</v>
@@ -45968,7 +46544,7 @@
         <v>87</v>
       </c>
       <c r="C2680">
-        <v>5420.2</v>
+        <v>6854.2</v>
       </c>
       <c r="D2680" t="s">
         <v>2682</v>
@@ -45982,7 +46558,7 @@
         <v>88</v>
       </c>
       <c r="C2681">
-        <v>5404.3</v>
+        <v>6850.6</v>
       </c>
       <c r="D2681" t="s">
         <v>2683</v>
@@ -45996,7 +46572,7 @@
         <v>89</v>
       </c>
       <c r="C2682">
-        <v>5030.1</v>
+        <v>6422.9</v>
       </c>
       <c r="D2682" t="s">
         <v>2684</v>
@@ -46010,7 +46586,7 @@
         <v>90</v>
       </c>
       <c r="C2683">
-        <v>4947.6</v>
+        <v>6323.4</v>
       </c>
       <c r="D2683" t="s">
         <v>2685</v>
@@ -46024,7 +46600,7 @@
         <v>91</v>
       </c>
       <c r="C2684">
-        <v>4908.5</v>
+        <v>6261.3</v>
       </c>
       <c r="D2684" t="s">
         <v>2686</v>
@@ -46038,7 +46614,7 @@
         <v>92</v>
       </c>
       <c r="C2685">
-        <v>4880.2</v>
+        <v>6153.4</v>
       </c>
       <c r="D2685" t="s">
         <v>2687</v>
@@ -46052,7 +46628,7 @@
         <v>93</v>
       </c>
       <c r="C2686">
-        <v>4950.6</v>
+        <v>5737.1</v>
       </c>
       <c r="D2686" t="s">
         <v>2688</v>
@@ -46066,7 +46642,7 @@
         <v>94</v>
       </c>
       <c r="C2687">
-        <v>4887.2</v>
+        <v>5645.2</v>
       </c>
       <c r="D2687" t="s">
         <v>2689</v>
@@ -46080,7 +46656,7 @@
         <v>95</v>
       </c>
       <c r="C2688">
-        <v>4832.7</v>
+        <v>5558.5</v>
       </c>
       <c r="D2688" t="s">
         <v>2690</v>
@@ -46094,10 +46670,2698 @@
         <v>96</v>
       </c>
       <c r="C2689">
-        <v>4801.6</v>
+        <v>5479.2</v>
       </c>
       <c r="D2689" t="s">
         <v>2691</v>
+      </c>
+    </row>
+    <row r="2690" spans="1:4">
+      <c r="A2690" s="2">
+        <v>46141</v>
+      </c>
+      <c r="B2690">
+        <v>1</v>
+      </c>
+      <c r="C2690">
+        <v>4531.2</v>
+      </c>
+      <c r="D2690" t="s">
+        <v>2692</v>
+      </c>
+    </row>
+    <row r="2691" spans="1:4">
+      <c r="A2691" s="2">
+        <v>46141</v>
+      </c>
+      <c r="B2691">
+        <v>2</v>
+      </c>
+      <c r="C2691">
+        <v>4577.6</v>
+      </c>
+      <c r="D2691" t="s">
+        <v>2693</v>
+      </c>
+    </row>
+    <row r="2692" spans="1:4">
+      <c r="A2692" s="2">
+        <v>46141</v>
+      </c>
+      <c r="B2692">
+        <v>3</v>
+      </c>
+      <c r="C2692">
+        <v>4533.2</v>
+      </c>
+      <c r="D2692" t="s">
+        <v>2694</v>
+      </c>
+    </row>
+    <row r="2693" spans="1:4">
+      <c r="A2693" s="2">
+        <v>46141</v>
+      </c>
+      <c r="B2693">
+        <v>4</v>
+      </c>
+      <c r="C2693">
+        <v>4515.8</v>
+      </c>
+      <c r="D2693" t="s">
+        <v>2695</v>
+      </c>
+    </row>
+    <row r="2694" spans="1:4">
+      <c r="A2694" s="2">
+        <v>46141</v>
+      </c>
+      <c r="B2694">
+        <v>5</v>
+      </c>
+      <c r="C2694">
+        <v>4283.8</v>
+      </c>
+      <c r="D2694" t="s">
+        <v>2696</v>
+      </c>
+    </row>
+    <row r="2695" spans="1:4">
+      <c r="A2695" s="2">
+        <v>46141</v>
+      </c>
+      <c r="B2695">
+        <v>6</v>
+      </c>
+      <c r="C2695">
+        <v>4274.6</v>
+      </c>
+      <c r="D2695" t="s">
+        <v>2697</v>
+      </c>
+    </row>
+    <row r="2696" spans="1:4">
+      <c r="A2696" s="2">
+        <v>46141</v>
+      </c>
+      <c r="B2696">
+        <v>7</v>
+      </c>
+      <c r="C2696">
+        <v>4293</v>
+      </c>
+      <c r="D2696" t="s">
+        <v>2698</v>
+      </c>
+    </row>
+    <row r="2697" spans="1:4">
+      <c r="A2697" s="2">
+        <v>46141</v>
+      </c>
+      <c r="B2697">
+        <v>8</v>
+      </c>
+      <c r="C2697">
+        <v>4284.9</v>
+      </c>
+      <c r="D2697" t="s">
+        <v>2699</v>
+      </c>
+    </row>
+    <row r="2698" spans="1:4">
+      <c r="A2698" s="2">
+        <v>46141</v>
+      </c>
+      <c r="B2698">
+        <v>9</v>
+      </c>
+      <c r="C2698">
+        <v>4116.8</v>
+      </c>
+      <c r="D2698" t="s">
+        <v>2700</v>
+      </c>
+    </row>
+    <row r="2699" spans="1:4">
+      <c r="A2699" s="2">
+        <v>46141</v>
+      </c>
+      <c r="B2699">
+        <v>10</v>
+      </c>
+      <c r="C2699">
+        <v>4113.2</v>
+      </c>
+      <c r="D2699" t="s">
+        <v>2701</v>
+      </c>
+    </row>
+    <row r="2700" spans="1:4">
+      <c r="A2700" s="2">
+        <v>46141</v>
+      </c>
+      <c r="B2700">
+        <v>11</v>
+      </c>
+      <c r="C2700">
+        <v>4122.3</v>
+      </c>
+      <c r="D2700" t="s">
+        <v>2702</v>
+      </c>
+    </row>
+    <row r="2701" spans="1:4">
+      <c r="A2701" s="2">
+        <v>46141</v>
+      </c>
+      <c r="B2701">
+        <v>12</v>
+      </c>
+      <c r="C2701">
+        <v>4145.8</v>
+      </c>
+      <c r="D2701" t="s">
+        <v>2703</v>
+      </c>
+    </row>
+    <row r="2702" spans="1:4">
+      <c r="A2702" s="2">
+        <v>46141</v>
+      </c>
+      <c r="B2702">
+        <v>13</v>
+      </c>
+      <c r="C2702">
+        <v>4179.2</v>
+      </c>
+      <c r="D2702" t="s">
+        <v>2704</v>
+      </c>
+    </row>
+    <row r="2703" spans="1:4">
+      <c r="A2703" s="2">
+        <v>46141</v>
+      </c>
+      <c r="B2703">
+        <v>14</v>
+      </c>
+      <c r="C2703">
+        <v>4209</v>
+      </c>
+      <c r="D2703" t="s">
+        <v>2705</v>
+      </c>
+    </row>
+    <row r="2704" spans="1:4">
+      <c r="A2704" s="2">
+        <v>46141</v>
+      </c>
+      <c r="B2704">
+        <v>15</v>
+      </c>
+      <c r="C2704">
+        <v>4241.2</v>
+      </c>
+      <c r="D2704" t="s">
+        <v>2706</v>
+      </c>
+    </row>
+    <row r="2705" spans="1:4">
+      <c r="A2705" s="2">
+        <v>46141</v>
+      </c>
+      <c r="B2705">
+        <v>16</v>
+      </c>
+      <c r="C2705">
+        <v>4269.7</v>
+      </c>
+      <c r="D2705" t="s">
+        <v>2707</v>
+      </c>
+    </row>
+    <row r="2706" spans="1:4">
+      <c r="A2706" s="2">
+        <v>46141</v>
+      </c>
+      <c r="B2706">
+        <v>17</v>
+      </c>
+      <c r="C2706">
+        <v>4264.1</v>
+      </c>
+      <c r="D2706" t="s">
+        <v>2708</v>
+      </c>
+    </row>
+    <row r="2707" spans="1:4">
+      <c r="A2707" s="2">
+        <v>46141</v>
+      </c>
+      <c r="B2707">
+        <v>18</v>
+      </c>
+      <c r="C2707">
+        <v>4277.1</v>
+      </c>
+      <c r="D2707" t="s">
+        <v>2709</v>
+      </c>
+    </row>
+    <row r="2708" spans="1:4">
+      <c r="A2708" s="2">
+        <v>46141</v>
+      </c>
+      <c r="B2708">
+        <v>19</v>
+      </c>
+      <c r="C2708">
+        <v>4275.6</v>
+      </c>
+      <c r="D2708" t="s">
+        <v>2710</v>
+      </c>
+    </row>
+    <row r="2709" spans="1:4">
+      <c r="A2709" s="2">
+        <v>46141</v>
+      </c>
+      <c r="B2709">
+        <v>20</v>
+      </c>
+      <c r="C2709">
+        <v>4285.2</v>
+      </c>
+      <c r="D2709" t="s">
+        <v>2711</v>
+      </c>
+    </row>
+    <row r="2710" spans="1:4">
+      <c r="A2710" s="2">
+        <v>46141</v>
+      </c>
+      <c r="B2710">
+        <v>21</v>
+      </c>
+      <c r="C2710">
+        <v>4254.3</v>
+      </c>
+      <c r="D2710" t="s">
+        <v>2712</v>
+      </c>
+    </row>
+    <row r="2711" spans="1:4">
+      <c r="A2711" s="2">
+        <v>46141</v>
+      </c>
+      <c r="B2711">
+        <v>22</v>
+      </c>
+      <c r="C2711">
+        <v>4265.8</v>
+      </c>
+      <c r="D2711" t="s">
+        <v>2713</v>
+      </c>
+    </row>
+    <row r="2712" spans="1:4">
+      <c r="A2712" s="2">
+        <v>46141</v>
+      </c>
+      <c r="B2712">
+        <v>23</v>
+      </c>
+      <c r="C2712">
+        <v>4261.8</v>
+      </c>
+      <c r="D2712" t="s">
+        <v>2714</v>
+      </c>
+    </row>
+    <row r="2713" spans="1:4">
+      <c r="A2713" s="2">
+        <v>46141</v>
+      </c>
+      <c r="B2713">
+        <v>24</v>
+      </c>
+      <c r="C2713">
+        <v>4265.5</v>
+      </c>
+      <c r="D2713" t="s">
+        <v>2715</v>
+      </c>
+    </row>
+    <row r="2714" spans="1:4">
+      <c r="A2714" s="2">
+        <v>46141</v>
+      </c>
+      <c r="B2714">
+        <v>25</v>
+      </c>
+      <c r="C2714">
+        <v>4439.9</v>
+      </c>
+      <c r="D2714" t="s">
+        <v>2716</v>
+      </c>
+    </row>
+    <row r="2715" spans="1:4">
+      <c r="A2715" s="2">
+        <v>46141</v>
+      </c>
+      <c r="B2715">
+        <v>26</v>
+      </c>
+      <c r="C2715">
+        <v>4522.1</v>
+      </c>
+      <c r="D2715" t="s">
+        <v>2717</v>
+      </c>
+    </row>
+    <row r="2716" spans="1:4">
+      <c r="A2716" s="2">
+        <v>46141</v>
+      </c>
+      <c r="B2716">
+        <v>27</v>
+      </c>
+      <c r="C2716">
+        <v>4603.2</v>
+      </c>
+      <c r="D2716" t="s">
+        <v>2718</v>
+      </c>
+    </row>
+    <row r="2717" spans="1:4">
+      <c r="A2717" s="2">
+        <v>46141</v>
+      </c>
+      <c r="B2717">
+        <v>28</v>
+      </c>
+      <c r="C2717">
+        <v>4659.1</v>
+      </c>
+      <c r="D2717" t="s">
+        <v>2719</v>
+      </c>
+    </row>
+    <row r="2718" spans="1:4">
+      <c r="A2718" s="2">
+        <v>46141</v>
+      </c>
+      <c r="B2718">
+        <v>29</v>
+      </c>
+      <c r="C2718">
+        <v>5033</v>
+      </c>
+      <c r="D2718" t="s">
+        <v>2720</v>
+      </c>
+    </row>
+    <row r="2719" spans="1:4">
+      <c r="A2719" s="2">
+        <v>46141</v>
+      </c>
+      <c r="B2719">
+        <v>30</v>
+      </c>
+      <c r="C2719">
+        <v>5135.1</v>
+      </c>
+      <c r="D2719" t="s">
+        <v>2721</v>
+      </c>
+    </row>
+    <row r="2720" spans="1:4">
+      <c r="A2720" s="2">
+        <v>46141</v>
+      </c>
+      <c r="B2720">
+        <v>31</v>
+      </c>
+      <c r="C2720">
+        <v>5265.3</v>
+      </c>
+      <c r="D2720" t="s">
+        <v>2722</v>
+      </c>
+    </row>
+    <row r="2721" spans="1:4">
+      <c r="A2721" s="2">
+        <v>46141</v>
+      </c>
+      <c r="B2721">
+        <v>32</v>
+      </c>
+      <c r="C2721">
+        <v>5395.9</v>
+      </c>
+      <c r="D2721" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="2722" spans="1:4">
+      <c r="A2722" s="2">
+        <v>46141</v>
+      </c>
+      <c r="B2722">
+        <v>33</v>
+      </c>
+      <c r="C2722">
+        <v>5562.9</v>
+      </c>
+      <c r="D2722" t="s">
+        <v>2724</v>
+      </c>
+    </row>
+    <row r="2723" spans="1:4">
+      <c r="A2723" s="2">
+        <v>46141</v>
+      </c>
+      <c r="B2723">
+        <v>34</v>
+      </c>
+      <c r="C2723">
+        <v>5681.4</v>
+      </c>
+      <c r="D2723" t="s">
+        <v>2725</v>
+      </c>
+    </row>
+    <row r="2724" spans="1:4">
+      <c r="A2724" s="2">
+        <v>46141</v>
+      </c>
+      <c r="B2724">
+        <v>35</v>
+      </c>
+      <c r="C2724">
+        <v>5796.6</v>
+      </c>
+      <c r="D2724" t="s">
+        <v>2726</v>
+      </c>
+    </row>
+    <row r="2725" spans="1:4">
+      <c r="A2725" s="2">
+        <v>46141</v>
+      </c>
+      <c r="B2725">
+        <v>36</v>
+      </c>
+      <c r="C2725">
+        <v>5975.5</v>
+      </c>
+      <c r="D2725" t="s">
+        <v>2727</v>
+      </c>
+    </row>
+    <row r="2726" spans="1:4">
+      <c r="A2726" s="2">
+        <v>46141</v>
+      </c>
+      <c r="B2726">
+        <v>37</v>
+      </c>
+      <c r="C2726">
+        <v>5938.1</v>
+      </c>
+      <c r="D2726" t="s">
+        <v>2728</v>
+      </c>
+    </row>
+    <row r="2727" spans="1:4">
+      <c r="A2727" s="2">
+        <v>46141</v>
+      </c>
+      <c r="B2727">
+        <v>38</v>
+      </c>
+      <c r="C2727">
+        <v>5987.8</v>
+      </c>
+      <c r="D2727" t="s">
+        <v>2729</v>
+      </c>
+    </row>
+    <row r="2728" spans="1:4">
+      <c r="A2728" s="2">
+        <v>46141</v>
+      </c>
+      <c r="B2728">
+        <v>39</v>
+      </c>
+      <c r="C2728">
+        <v>6146.2</v>
+      </c>
+      <c r="D2728" t="s">
+        <v>2730</v>
+      </c>
+    </row>
+    <row r="2729" spans="1:4">
+      <c r="A2729" s="2">
+        <v>46141</v>
+      </c>
+      <c r="B2729">
+        <v>40</v>
+      </c>
+      <c r="C2729">
+        <v>6268.2</v>
+      </c>
+      <c r="D2729" t="s">
+        <v>2731</v>
+      </c>
+    </row>
+    <row r="2730" spans="1:4">
+      <c r="A2730" s="2">
+        <v>46141</v>
+      </c>
+      <c r="B2730">
+        <v>41</v>
+      </c>
+      <c r="C2730">
+        <v>6378.3</v>
+      </c>
+      <c r="D2730" t="s">
+        <v>2732</v>
+      </c>
+    </row>
+    <row r="2731" spans="1:4">
+      <c r="A2731" s="2">
+        <v>46141</v>
+      </c>
+      <c r="B2731">
+        <v>42</v>
+      </c>
+      <c r="C2731">
+        <v>6448.9</v>
+      </c>
+      <c r="D2731" t="s">
+        <v>2733</v>
+      </c>
+    </row>
+    <row r="2732" spans="1:4">
+      <c r="A2732" s="2">
+        <v>46141</v>
+      </c>
+      <c r="B2732">
+        <v>43</v>
+      </c>
+      <c r="C2732">
+        <v>6563.2</v>
+      </c>
+      <c r="D2732" t="s">
+        <v>2734</v>
+      </c>
+    </row>
+    <row r="2733" spans="1:4">
+      <c r="A2733" s="2">
+        <v>46141</v>
+      </c>
+      <c r="B2733">
+        <v>44</v>
+      </c>
+      <c r="C2733">
+        <v>6654.2</v>
+      </c>
+      <c r="D2733" t="s">
+        <v>2735</v>
+      </c>
+    </row>
+    <row r="2734" spans="1:4">
+      <c r="A2734" s="2">
+        <v>46141</v>
+      </c>
+      <c r="B2734">
+        <v>45</v>
+      </c>
+      <c r="C2734">
+        <v>6226.6</v>
+      </c>
+      <c r="D2734" t="s">
+        <v>2736</v>
+      </c>
+    </row>
+    <row r="2735" spans="1:4">
+      <c r="A2735" s="2">
+        <v>46141</v>
+      </c>
+      <c r="B2735">
+        <v>46</v>
+      </c>
+      <c r="C2735">
+        <v>6202.4</v>
+      </c>
+      <c r="D2735" t="s">
+        <v>2737</v>
+      </c>
+    </row>
+    <row r="2736" spans="1:4">
+      <c r="A2736" s="2">
+        <v>46141</v>
+      </c>
+      <c r="B2736">
+        <v>47</v>
+      </c>
+      <c r="C2736">
+        <v>6020.9</v>
+      </c>
+      <c r="D2736" t="s">
+        <v>2738</v>
+      </c>
+    </row>
+    <row r="2737" spans="1:4">
+      <c r="A2737" s="2">
+        <v>46141</v>
+      </c>
+      <c r="B2737">
+        <v>48</v>
+      </c>
+      <c r="C2737">
+        <v>6154.1</v>
+      </c>
+      <c r="D2737" t="s">
+        <v>2739</v>
+      </c>
+    </row>
+    <row r="2738" spans="1:4">
+      <c r="A2738" s="2">
+        <v>46141</v>
+      </c>
+      <c r="B2738">
+        <v>49</v>
+      </c>
+      <c r="C2738">
+        <v>5879.6</v>
+      </c>
+      <c r="D2738" t="s">
+        <v>2740</v>
+      </c>
+    </row>
+    <row r="2739" spans="1:4">
+      <c r="A2739" s="2">
+        <v>46141</v>
+      </c>
+      <c r="B2739">
+        <v>50</v>
+      </c>
+      <c r="C2739">
+        <v>5768.3</v>
+      </c>
+      <c r="D2739" t="s">
+        <v>2741</v>
+      </c>
+    </row>
+    <row r="2740" spans="1:4">
+      <c r="A2740" s="2">
+        <v>46141</v>
+      </c>
+      <c r="B2740">
+        <v>51</v>
+      </c>
+      <c r="C2740">
+        <v>5697.2</v>
+      </c>
+      <c r="D2740" t="s">
+        <v>2742</v>
+      </c>
+    </row>
+    <row r="2741" spans="1:4">
+      <c r="A2741" s="2">
+        <v>46141</v>
+      </c>
+      <c r="B2741">
+        <v>52</v>
+      </c>
+      <c r="C2741">
+        <v>5600</v>
+      </c>
+      <c r="D2741" t="s">
+        <v>2743</v>
+      </c>
+    </row>
+    <row r="2742" spans="1:4">
+      <c r="A2742" s="2">
+        <v>46141</v>
+      </c>
+      <c r="B2742">
+        <v>53</v>
+      </c>
+      <c r="C2742">
+        <v>5328.1</v>
+      </c>
+      <c r="D2742" t="s">
+        <v>2744</v>
+      </c>
+    </row>
+    <row r="2743" spans="1:4">
+      <c r="A2743" s="2">
+        <v>46141</v>
+      </c>
+      <c r="B2743">
+        <v>54</v>
+      </c>
+      <c r="C2743">
+        <v>5239.3</v>
+      </c>
+      <c r="D2743" t="s">
+        <v>2745</v>
+      </c>
+    </row>
+    <row r="2744" spans="1:4">
+      <c r="A2744" s="2">
+        <v>46141</v>
+      </c>
+      <c r="B2744">
+        <v>55</v>
+      </c>
+      <c r="C2744">
+        <v>5220.3</v>
+      </c>
+      <c r="D2744" t="s">
+        <v>2746</v>
+      </c>
+    </row>
+    <row r="2745" spans="1:4">
+      <c r="A2745" s="2">
+        <v>46141</v>
+      </c>
+      <c r="B2745">
+        <v>56</v>
+      </c>
+      <c r="C2745">
+        <v>5186.4</v>
+      </c>
+      <c r="D2745" t="s">
+        <v>2747</v>
+      </c>
+    </row>
+    <row r="2746" spans="1:4">
+      <c r="A2746" s="2">
+        <v>46141</v>
+      </c>
+      <c r="B2746">
+        <v>57</v>
+      </c>
+      <c r="C2746">
+        <v>5294.9</v>
+      </c>
+      <c r="D2746" t="s">
+        <v>2748</v>
+      </c>
+    </row>
+    <row r="2747" spans="1:4">
+      <c r="A2747" s="2">
+        <v>46141</v>
+      </c>
+      <c r="B2747">
+        <v>58</v>
+      </c>
+      <c r="C2747">
+        <v>5271</v>
+      </c>
+      <c r="D2747" t="s">
+        <v>2749</v>
+      </c>
+    </row>
+    <row r="2748" spans="1:4">
+      <c r="A2748" s="2">
+        <v>46141</v>
+      </c>
+      <c r="B2748">
+        <v>59</v>
+      </c>
+      <c r="C2748">
+        <v>5255.7</v>
+      </c>
+      <c r="D2748" t="s">
+        <v>2750</v>
+      </c>
+    </row>
+    <row r="2749" spans="1:4">
+      <c r="A2749" s="2">
+        <v>46141</v>
+      </c>
+      <c r="B2749">
+        <v>60</v>
+      </c>
+      <c r="C2749">
+        <v>5260.8</v>
+      </c>
+      <c r="D2749" t="s">
+        <v>2751</v>
+      </c>
+    </row>
+    <row r="2750" spans="1:4">
+      <c r="A2750" s="2">
+        <v>46141</v>
+      </c>
+      <c r="B2750">
+        <v>61</v>
+      </c>
+      <c r="C2750">
+        <v>5241.1</v>
+      </c>
+      <c r="D2750" t="s">
+        <v>2752</v>
+      </c>
+    </row>
+    <row r="2751" spans="1:4">
+      <c r="A2751" s="2">
+        <v>46141</v>
+      </c>
+      <c r="B2751">
+        <v>62</v>
+      </c>
+      <c r="C2751">
+        <v>5227.5</v>
+      </c>
+      <c r="D2751" t="s">
+        <v>2753</v>
+      </c>
+    </row>
+    <row r="2752" spans="1:4">
+      <c r="A2752" s="2">
+        <v>46141</v>
+      </c>
+      <c r="B2752">
+        <v>63</v>
+      </c>
+      <c r="C2752">
+        <v>5219.5</v>
+      </c>
+      <c r="D2752" t="s">
+        <v>2754</v>
+      </c>
+    </row>
+    <row r="2753" spans="1:4">
+      <c r="A2753" s="2">
+        <v>46141</v>
+      </c>
+      <c r="B2753">
+        <v>64</v>
+      </c>
+      <c r="C2753">
+        <v>5270.1</v>
+      </c>
+      <c r="D2753" t="s">
+        <v>2755</v>
+      </c>
+    </row>
+    <row r="2754" spans="1:4">
+      <c r="A2754" s="2">
+        <v>46141</v>
+      </c>
+      <c r="B2754">
+        <v>65</v>
+      </c>
+      <c r="C2754">
+        <v>5493.2</v>
+      </c>
+      <c r="D2754" t="s">
+        <v>2756</v>
+      </c>
+    </row>
+    <row r="2755" spans="1:4">
+      <c r="A2755" s="2">
+        <v>46141</v>
+      </c>
+      <c r="B2755">
+        <v>66</v>
+      </c>
+      <c r="C2755">
+        <v>5540.8</v>
+      </c>
+      <c r="D2755" t="s">
+        <v>2757</v>
+      </c>
+    </row>
+    <row r="2756" spans="1:4">
+      <c r="A2756" s="2">
+        <v>46141</v>
+      </c>
+      <c r="B2756">
+        <v>67</v>
+      </c>
+      <c r="C2756">
+        <v>5667.2</v>
+      </c>
+      <c r="D2756" t="s">
+        <v>2758</v>
+      </c>
+    </row>
+    <row r="2757" spans="1:4">
+      <c r="A2757" s="2">
+        <v>46141</v>
+      </c>
+      <c r="B2757">
+        <v>68</v>
+      </c>
+      <c r="C2757">
+        <v>5867.7</v>
+      </c>
+      <c r="D2757" t="s">
+        <v>2759</v>
+      </c>
+    </row>
+    <row r="2758" spans="1:4">
+      <c r="A2758" s="2">
+        <v>46141</v>
+      </c>
+      <c r="B2758">
+        <v>69</v>
+      </c>
+      <c r="C2758">
+        <v>6088.8</v>
+      </c>
+      <c r="D2758" t="s">
+        <v>2760</v>
+      </c>
+    </row>
+    <row r="2759" spans="1:4">
+      <c r="A2759" s="2">
+        <v>46141</v>
+      </c>
+      <c r="B2759">
+        <v>70</v>
+      </c>
+      <c r="C2759">
+        <v>6052</v>
+      </c>
+      <c r="D2759" t="s">
+        <v>2761</v>
+      </c>
+    </row>
+    <row r="2760" spans="1:4">
+      <c r="A2760" s="2">
+        <v>46141</v>
+      </c>
+      <c r="B2760">
+        <v>71</v>
+      </c>
+      <c r="C2760">
+        <v>5984.4</v>
+      </c>
+      <c r="D2760" t="s">
+        <v>2762</v>
+      </c>
+    </row>
+    <row r="2761" spans="1:4">
+      <c r="A2761" s="2">
+        <v>46141</v>
+      </c>
+      <c r="B2761">
+        <v>72</v>
+      </c>
+      <c r="C2761">
+        <v>5899.6</v>
+      </c>
+      <c r="D2761" t="s">
+        <v>2763</v>
+      </c>
+    </row>
+    <row r="2762" spans="1:4">
+      <c r="A2762" s="2">
+        <v>46141</v>
+      </c>
+      <c r="B2762">
+        <v>73</v>
+      </c>
+      <c r="C2762">
+        <v>6407.6</v>
+      </c>
+      <c r="D2762" t="s">
+        <v>2764</v>
+      </c>
+    </row>
+    <row r="2763" spans="1:4">
+      <c r="A2763" s="2">
+        <v>46141</v>
+      </c>
+      <c r="B2763">
+        <v>74</v>
+      </c>
+      <c r="C2763">
+        <v>6340.7</v>
+      </c>
+      <c r="D2763" t="s">
+        <v>2765</v>
+      </c>
+    </row>
+    <row r="2764" spans="1:4">
+      <c r="A2764" s="2">
+        <v>46141</v>
+      </c>
+      <c r="B2764">
+        <v>75</v>
+      </c>
+      <c r="C2764">
+        <v>6184.8</v>
+      </c>
+      <c r="D2764" t="s">
+        <v>2766</v>
+      </c>
+    </row>
+    <row r="2765" spans="1:4">
+      <c r="A2765" s="2">
+        <v>46141</v>
+      </c>
+      <c r="B2765">
+        <v>76</v>
+      </c>
+      <c r="C2765">
+        <v>6156.9</v>
+      </c>
+      <c r="D2765" t="s">
+        <v>2767</v>
+      </c>
+    </row>
+    <row r="2766" spans="1:4">
+      <c r="A2766" s="2">
+        <v>46141</v>
+      </c>
+      <c r="B2766">
+        <v>77</v>
+      </c>
+      <c r="C2766">
+        <v>6886.9</v>
+      </c>
+      <c r="D2766" t="s">
+        <v>2768</v>
+      </c>
+    </row>
+    <row r="2767" spans="1:4">
+      <c r="A2767" s="2">
+        <v>46141</v>
+      </c>
+      <c r="B2767">
+        <v>78</v>
+      </c>
+      <c r="C2767">
+        <v>6888.4</v>
+      </c>
+      <c r="D2767" t="s">
+        <v>2769</v>
+      </c>
+    </row>
+    <row r="2768" spans="1:4">
+      <c r="A2768" s="2">
+        <v>46141</v>
+      </c>
+      <c r="B2768">
+        <v>79</v>
+      </c>
+      <c r="C2768">
+        <v>6877.8</v>
+      </c>
+      <c r="D2768" t="s">
+        <v>2770</v>
+      </c>
+    </row>
+    <row r="2769" spans="1:4">
+      <c r="A2769" s="2">
+        <v>46141</v>
+      </c>
+      <c r="B2769">
+        <v>80</v>
+      </c>
+      <c r="C2769">
+        <v>6862.7</v>
+      </c>
+      <c r="D2769" t="s">
+        <v>2771</v>
+      </c>
+    </row>
+    <row r="2770" spans="1:4">
+      <c r="A2770" s="2">
+        <v>46141</v>
+      </c>
+      <c r="B2770">
+        <v>81</v>
+      </c>
+      <c r="C2770">
+        <v>7027.7</v>
+      </c>
+      <c r="D2770" t="s">
+        <v>2772</v>
+      </c>
+    </row>
+    <row r="2771" spans="1:4">
+      <c r="A2771" s="2">
+        <v>46141</v>
+      </c>
+      <c r="B2771">
+        <v>82</v>
+      </c>
+      <c r="C2771">
+        <v>7048.4</v>
+      </c>
+      <c r="D2771" t="s">
+        <v>2773</v>
+      </c>
+    </row>
+    <row r="2772" spans="1:4">
+      <c r="A2772" s="2">
+        <v>46141</v>
+      </c>
+      <c r="B2772">
+        <v>83</v>
+      </c>
+      <c r="C2772">
+        <v>7006.4</v>
+      </c>
+      <c r="D2772" t="s">
+        <v>2774</v>
+      </c>
+    </row>
+    <row r="2773" spans="1:4">
+      <c r="A2773" s="2">
+        <v>46141</v>
+      </c>
+      <c r="B2773">
+        <v>84</v>
+      </c>
+      <c r="C2773">
+        <v>7071.6</v>
+      </c>
+      <c r="D2773" t="s">
+        <v>2775</v>
+      </c>
+    </row>
+    <row r="2774" spans="1:4">
+      <c r="A2774" s="2">
+        <v>46141</v>
+      </c>
+      <c r="B2774">
+        <v>85</v>
+      </c>
+      <c r="C2774">
+        <v>7012.7</v>
+      </c>
+      <c r="D2774" t="s">
+        <v>2776</v>
+      </c>
+    </row>
+    <row r="2775" spans="1:4">
+      <c r="A2775" s="2">
+        <v>46141</v>
+      </c>
+      <c r="B2775">
+        <v>86</v>
+      </c>
+      <c r="C2775">
+        <v>6886.6</v>
+      </c>
+      <c r="D2775" t="s">
+        <v>2777</v>
+      </c>
+    </row>
+    <row r="2776" spans="1:4">
+      <c r="A2776" s="2">
+        <v>46141</v>
+      </c>
+      <c r="B2776">
+        <v>87</v>
+      </c>
+      <c r="C2776">
+        <v>6804.2</v>
+      </c>
+      <c r="D2776" t="s">
+        <v>2778</v>
+      </c>
+    </row>
+    <row r="2777" spans="1:4">
+      <c r="A2777" s="2">
+        <v>46141</v>
+      </c>
+      <c r="B2777">
+        <v>88</v>
+      </c>
+      <c r="C2777">
+        <v>6850.6</v>
+      </c>
+      <c r="D2777" t="s">
+        <v>2779</v>
+      </c>
+    </row>
+    <row r="2778" spans="1:4">
+      <c r="A2778" s="2">
+        <v>46141</v>
+      </c>
+      <c r="B2778">
+        <v>89</v>
+      </c>
+      <c r="C2778">
+        <v>6482.9</v>
+      </c>
+      <c r="D2778" t="s">
+        <v>2780</v>
+      </c>
+    </row>
+    <row r="2779" spans="1:4">
+      <c r="A2779" s="2">
+        <v>46141</v>
+      </c>
+      <c r="B2779">
+        <v>90</v>
+      </c>
+      <c r="C2779">
+        <v>6473.4</v>
+      </c>
+      <c r="D2779" t="s">
+        <v>2781</v>
+      </c>
+    </row>
+    <row r="2780" spans="1:4">
+      <c r="A2780" s="2">
+        <v>46141</v>
+      </c>
+      <c r="B2780">
+        <v>91</v>
+      </c>
+      <c r="C2780">
+        <v>6401.3</v>
+      </c>
+      <c r="D2780" t="s">
+        <v>2782</v>
+      </c>
+    </row>
+    <row r="2781" spans="1:4">
+      <c r="A2781" s="2">
+        <v>46141</v>
+      </c>
+      <c r="B2781">
+        <v>92</v>
+      </c>
+      <c r="C2781">
+        <v>6253.4</v>
+      </c>
+      <c r="D2781" t="s">
+        <v>2783</v>
+      </c>
+    </row>
+    <row r="2782" spans="1:4">
+      <c r="A2782" s="2">
+        <v>46141</v>
+      </c>
+      <c r="B2782">
+        <v>93</v>
+      </c>
+      <c r="C2782">
+        <v>5737.1</v>
+      </c>
+      <c r="D2782" t="s">
+        <v>2784</v>
+      </c>
+    </row>
+    <row r="2783" spans="1:4">
+      <c r="A2783" s="2">
+        <v>46141</v>
+      </c>
+      <c r="B2783">
+        <v>94</v>
+      </c>
+      <c r="C2783">
+        <v>5555.2</v>
+      </c>
+      <c r="D2783" t="s">
+        <v>2785</v>
+      </c>
+    </row>
+    <row r="2784" spans="1:4">
+      <c r="A2784" s="2">
+        <v>46141</v>
+      </c>
+      <c r="B2784">
+        <v>95</v>
+      </c>
+      <c r="C2784">
+        <v>5528.5</v>
+      </c>
+      <c r="D2784" t="s">
+        <v>2786</v>
+      </c>
+    </row>
+    <row r="2785" spans="1:4">
+      <c r="A2785" s="2">
+        <v>46141</v>
+      </c>
+      <c r="B2785">
+        <v>96</v>
+      </c>
+      <c r="C2785">
+        <v>5459.2</v>
+      </c>
+      <c r="D2785" t="s">
+        <v>2787</v>
+      </c>
+    </row>
+    <row r="2786" spans="1:4">
+      <c r="A2786" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2786">
+        <v>1</v>
+      </c>
+      <c r="C2786">
+        <v>4571.2</v>
+      </c>
+      <c r="D2786" t="s">
+        <v>2788</v>
+      </c>
+    </row>
+    <row r="2787" spans="1:4">
+      <c r="A2787" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2787">
+        <v>2</v>
+      </c>
+      <c r="C2787">
+        <v>4617.6</v>
+      </c>
+      <c r="D2787" t="s">
+        <v>2789</v>
+      </c>
+    </row>
+    <row r="2788" spans="1:4">
+      <c r="A2788" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2788">
+        <v>3</v>
+      </c>
+      <c r="C2788">
+        <v>4593.2</v>
+      </c>
+      <c r="D2788" t="s">
+        <v>2790</v>
+      </c>
+    </row>
+    <row r="2789" spans="1:4">
+      <c r="A2789" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2789">
+        <v>4</v>
+      </c>
+      <c r="C2789">
+        <v>4575.8</v>
+      </c>
+      <c r="D2789" t="s">
+        <v>2791</v>
+      </c>
+    </row>
+    <row r="2790" spans="1:4">
+      <c r="A2790" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2790">
+        <v>5</v>
+      </c>
+      <c r="C2790">
+        <v>4333.8</v>
+      </c>
+      <c r="D2790" t="s">
+        <v>2792</v>
+      </c>
+    </row>
+    <row r="2791" spans="1:4">
+      <c r="A2791" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2791">
+        <v>6</v>
+      </c>
+      <c r="C2791">
+        <v>4324.6</v>
+      </c>
+      <c r="D2791" t="s">
+        <v>2793</v>
+      </c>
+    </row>
+    <row r="2792" spans="1:4">
+      <c r="A2792" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2792">
+        <v>7</v>
+      </c>
+      <c r="C2792">
+        <v>4333</v>
+      </c>
+      <c r="D2792" t="s">
+        <v>2794</v>
+      </c>
+    </row>
+    <row r="2793" spans="1:4">
+      <c r="A2793" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2793">
+        <v>8</v>
+      </c>
+      <c r="C2793">
+        <v>4334.9</v>
+      </c>
+      <c r="D2793" t="s">
+        <v>2795</v>
+      </c>
+    </row>
+    <row r="2794" spans="1:4">
+      <c r="A2794" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2794">
+        <v>9</v>
+      </c>
+      <c r="C2794">
+        <v>4166.8</v>
+      </c>
+      <c r="D2794" t="s">
+        <v>2796</v>
+      </c>
+    </row>
+    <row r="2795" spans="1:4">
+      <c r="A2795" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2795">
+        <v>10</v>
+      </c>
+      <c r="C2795">
+        <v>4173.2</v>
+      </c>
+      <c r="D2795" t="s">
+        <v>2797</v>
+      </c>
+    </row>
+    <row r="2796" spans="1:4">
+      <c r="A2796" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2796">
+        <v>11</v>
+      </c>
+      <c r="C2796">
+        <v>4182.3</v>
+      </c>
+      <c r="D2796" t="s">
+        <v>2798</v>
+      </c>
+    </row>
+    <row r="2797" spans="1:4">
+      <c r="A2797" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2797">
+        <v>12</v>
+      </c>
+      <c r="C2797">
+        <v>4195.8</v>
+      </c>
+      <c r="D2797" t="s">
+        <v>2799</v>
+      </c>
+    </row>
+    <row r="2798" spans="1:4">
+      <c r="A2798" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2798">
+        <v>13</v>
+      </c>
+      <c r="C2798">
+        <v>4229.2</v>
+      </c>
+      <c r="D2798" t="s">
+        <v>2800</v>
+      </c>
+    </row>
+    <row r="2799" spans="1:4">
+      <c r="A2799" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2799">
+        <v>14</v>
+      </c>
+      <c r="C2799">
+        <v>4249</v>
+      </c>
+      <c r="D2799" t="s">
+        <v>2801</v>
+      </c>
+    </row>
+    <row r="2800" spans="1:4">
+      <c r="A2800" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2800">
+        <v>15</v>
+      </c>
+      <c r="C2800">
+        <v>4281.2</v>
+      </c>
+      <c r="D2800" t="s">
+        <v>2802</v>
+      </c>
+    </row>
+    <row r="2801" spans="1:4">
+      <c r="A2801" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2801">
+        <v>16</v>
+      </c>
+      <c r="C2801">
+        <v>4309.7</v>
+      </c>
+      <c r="D2801" t="s">
+        <v>2803</v>
+      </c>
+    </row>
+    <row r="2802" spans="1:4">
+      <c r="A2802" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2802">
+        <v>17</v>
+      </c>
+      <c r="C2802">
+        <v>4304.1</v>
+      </c>
+      <c r="D2802" t="s">
+        <v>2804</v>
+      </c>
+    </row>
+    <row r="2803" spans="1:4">
+      <c r="A2803" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2803">
+        <v>18</v>
+      </c>
+      <c r="C2803">
+        <v>4317.1</v>
+      </c>
+      <c r="D2803" t="s">
+        <v>2805</v>
+      </c>
+    </row>
+    <row r="2804" spans="1:4">
+      <c r="A2804" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2804">
+        <v>19</v>
+      </c>
+      <c r="C2804">
+        <v>4315.6</v>
+      </c>
+      <c r="D2804" t="s">
+        <v>2806</v>
+      </c>
+    </row>
+    <row r="2805" spans="1:4">
+      <c r="A2805" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2805">
+        <v>20</v>
+      </c>
+      <c r="C2805">
+        <v>4325.2</v>
+      </c>
+      <c r="D2805" t="s">
+        <v>2807</v>
+      </c>
+    </row>
+    <row r="2806" spans="1:4">
+      <c r="A2806" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2806">
+        <v>21</v>
+      </c>
+      <c r="C2806">
+        <v>4304.3</v>
+      </c>
+      <c r="D2806" t="s">
+        <v>2808</v>
+      </c>
+    </row>
+    <row r="2807" spans="1:4">
+      <c r="A2807" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2807">
+        <v>22</v>
+      </c>
+      <c r="C2807">
+        <v>4315.8</v>
+      </c>
+      <c r="D2807" t="s">
+        <v>2809</v>
+      </c>
+    </row>
+    <row r="2808" spans="1:4">
+      <c r="A2808" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2808">
+        <v>23</v>
+      </c>
+      <c r="C2808">
+        <v>4321.8</v>
+      </c>
+      <c r="D2808" t="s">
+        <v>2810</v>
+      </c>
+    </row>
+    <row r="2809" spans="1:4">
+      <c r="A2809" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2809">
+        <v>24</v>
+      </c>
+      <c r="C2809">
+        <v>4325.5</v>
+      </c>
+      <c r="D2809" t="s">
+        <v>2811</v>
+      </c>
+    </row>
+    <row r="2810" spans="1:4">
+      <c r="A2810" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2810">
+        <v>25</v>
+      </c>
+      <c r="C2810">
+        <v>4509.9</v>
+      </c>
+      <c r="D2810" t="s">
+        <v>2812</v>
+      </c>
+    </row>
+    <row r="2811" spans="1:4">
+      <c r="A2811" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2811">
+        <v>26</v>
+      </c>
+      <c r="C2811">
+        <v>4592.1</v>
+      </c>
+      <c r="D2811" t="s">
+        <v>2813</v>
+      </c>
+    </row>
+    <row r="2812" spans="1:4">
+      <c r="A2812" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2812">
+        <v>27</v>
+      </c>
+      <c r="C2812">
+        <v>4683.2</v>
+      </c>
+      <c r="D2812" t="s">
+        <v>2814</v>
+      </c>
+    </row>
+    <row r="2813" spans="1:4">
+      <c r="A2813" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2813">
+        <v>28</v>
+      </c>
+      <c r="C2813">
+        <v>4749.1</v>
+      </c>
+      <c r="D2813" t="s">
+        <v>2815</v>
+      </c>
+    </row>
+    <row r="2814" spans="1:4">
+      <c r="A2814" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2814">
+        <v>29</v>
+      </c>
+      <c r="C2814">
+        <v>5133</v>
+      </c>
+      <c r="D2814" t="s">
+        <v>2816</v>
+      </c>
+    </row>
+    <row r="2815" spans="1:4">
+      <c r="A2815" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2815">
+        <v>30</v>
+      </c>
+      <c r="C2815">
+        <v>5245.1</v>
+      </c>
+      <c r="D2815" t="s">
+        <v>2817</v>
+      </c>
+    </row>
+    <row r="2816" spans="1:4">
+      <c r="A2816" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2816">
+        <v>31</v>
+      </c>
+      <c r="C2816">
+        <v>5385.3</v>
+      </c>
+      <c r="D2816" t="s">
+        <v>2818</v>
+      </c>
+    </row>
+    <row r="2817" spans="1:4">
+      <c r="A2817" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2817">
+        <v>32</v>
+      </c>
+      <c r="C2817">
+        <v>5545.9</v>
+      </c>
+      <c r="D2817" t="s">
+        <v>2819</v>
+      </c>
+    </row>
+    <row r="2818" spans="1:4">
+      <c r="A2818" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2818">
+        <v>33</v>
+      </c>
+      <c r="C2818">
+        <v>5722.9</v>
+      </c>
+      <c r="D2818" t="s">
+        <v>2820</v>
+      </c>
+    </row>
+    <row r="2819" spans="1:4">
+      <c r="A2819" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2819">
+        <v>34</v>
+      </c>
+      <c r="C2819">
+        <v>5861.4</v>
+      </c>
+      <c r="D2819" t="s">
+        <v>2821</v>
+      </c>
+    </row>
+    <row r="2820" spans="1:4">
+      <c r="A2820" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2820">
+        <v>35</v>
+      </c>
+      <c r="C2820">
+        <v>5986.6</v>
+      </c>
+      <c r="D2820" t="s">
+        <v>2822</v>
+      </c>
+    </row>
+    <row r="2821" spans="1:4">
+      <c r="A2821" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2821">
+        <v>36</v>
+      </c>
+      <c r="C2821">
+        <v>6175.5</v>
+      </c>
+      <c r="D2821" t="s">
+        <v>2823</v>
+      </c>
+    </row>
+    <row r="2822" spans="1:4">
+      <c r="A2822" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2822">
+        <v>37</v>
+      </c>
+      <c r="C2822">
+        <v>6148.1</v>
+      </c>
+      <c r="D2822" t="s">
+        <v>2824</v>
+      </c>
+    </row>
+    <row r="2823" spans="1:4">
+      <c r="A2823" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2823">
+        <v>38</v>
+      </c>
+      <c r="C2823">
+        <v>6207.8</v>
+      </c>
+      <c r="D2823" t="s">
+        <v>2825</v>
+      </c>
+    </row>
+    <row r="2824" spans="1:4">
+      <c r="A2824" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2824">
+        <v>39</v>
+      </c>
+      <c r="C2824">
+        <v>6366.2</v>
+      </c>
+      <c r="D2824" t="s">
+        <v>2826</v>
+      </c>
+    </row>
+    <row r="2825" spans="1:4">
+      <c r="A2825" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2825">
+        <v>40</v>
+      </c>
+      <c r="C2825">
+        <v>6488.2</v>
+      </c>
+      <c r="D2825" t="s">
+        <v>2827</v>
+      </c>
+    </row>
+    <row r="2826" spans="1:4">
+      <c r="A2826" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2826">
+        <v>41</v>
+      </c>
+      <c r="C2826">
+        <v>6598.3</v>
+      </c>
+      <c r="D2826" t="s">
+        <v>2828</v>
+      </c>
+    </row>
+    <row r="2827" spans="1:4">
+      <c r="A2827" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2827">
+        <v>42</v>
+      </c>
+      <c r="C2827">
+        <v>6678.9</v>
+      </c>
+      <c r="D2827" t="s">
+        <v>2829</v>
+      </c>
+    </row>
+    <row r="2828" spans="1:4">
+      <c r="A2828" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2828">
+        <v>43</v>
+      </c>
+      <c r="C2828">
+        <v>6783.2</v>
+      </c>
+      <c r="D2828" t="s">
+        <v>2830</v>
+      </c>
+    </row>
+    <row r="2829" spans="1:4">
+      <c r="A2829" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2829">
+        <v>44</v>
+      </c>
+      <c r="C2829">
+        <v>6884.2</v>
+      </c>
+      <c r="D2829" t="s">
+        <v>2831</v>
+      </c>
+    </row>
+    <row r="2830" spans="1:4">
+      <c r="A2830" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2830">
+        <v>45</v>
+      </c>
+      <c r="C2830">
+        <v>6456.6</v>
+      </c>
+      <c r="D2830" t="s">
+        <v>2832</v>
+      </c>
+    </row>
+    <row r="2831" spans="1:4">
+      <c r="A2831" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2831">
+        <v>46</v>
+      </c>
+      <c r="C2831">
+        <v>6432.4</v>
+      </c>
+      <c r="D2831" t="s">
+        <v>2833</v>
+      </c>
+    </row>
+    <row r="2832" spans="1:4">
+      <c r="A2832" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2832">
+        <v>47</v>
+      </c>
+      <c r="C2832">
+        <v>6250.9</v>
+      </c>
+      <c r="D2832" t="s">
+        <v>2834</v>
+      </c>
+    </row>
+    <row r="2833" spans="1:4">
+      <c r="A2833" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2833">
+        <v>48</v>
+      </c>
+      <c r="C2833">
+        <v>6384.1</v>
+      </c>
+      <c r="D2833" t="s">
+        <v>2835</v>
+      </c>
+    </row>
+    <row r="2834" spans="1:4">
+      <c r="A2834" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2834">
+        <v>49</v>
+      </c>
+      <c r="C2834">
+        <v>6099.6</v>
+      </c>
+      <c r="D2834" t="s">
+        <v>2836</v>
+      </c>
+    </row>
+    <row r="2835" spans="1:4">
+      <c r="A2835" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2835">
+        <v>50</v>
+      </c>
+      <c r="C2835">
+        <v>5978.3</v>
+      </c>
+      <c r="D2835" t="s">
+        <v>2837</v>
+      </c>
+    </row>
+    <row r="2836" spans="1:4">
+      <c r="A2836" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2836">
+        <v>51</v>
+      </c>
+      <c r="C2836">
+        <v>5907.2</v>
+      </c>
+      <c r="D2836" t="s">
+        <v>2838</v>
+      </c>
+    </row>
+    <row r="2837" spans="1:4">
+      <c r="A2837" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2837">
+        <v>52</v>
+      </c>
+      <c r="C2837">
+        <v>5810</v>
+      </c>
+      <c r="D2837" t="s">
+        <v>2839</v>
+      </c>
+    </row>
+    <row r="2838" spans="1:4">
+      <c r="A2838" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2838">
+        <v>53</v>
+      </c>
+      <c r="C2838">
+        <v>5528.1</v>
+      </c>
+      <c r="D2838" t="s">
+        <v>2840</v>
+      </c>
+    </row>
+    <row r="2839" spans="1:4">
+      <c r="A2839" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2839">
+        <v>54</v>
+      </c>
+      <c r="C2839">
+        <v>5439.3</v>
+      </c>
+      <c r="D2839" t="s">
+        <v>2841</v>
+      </c>
+    </row>
+    <row r="2840" spans="1:4">
+      <c r="A2840" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2840">
+        <v>55</v>
+      </c>
+      <c r="C2840">
+        <v>5420.3</v>
+      </c>
+      <c r="D2840" t="s">
+        <v>2842</v>
+      </c>
+    </row>
+    <row r="2841" spans="1:4">
+      <c r="A2841" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2841">
+        <v>56</v>
+      </c>
+      <c r="C2841">
+        <v>5376.4</v>
+      </c>
+      <c r="D2841" t="s">
+        <v>2843</v>
+      </c>
+    </row>
+    <row r="2842" spans="1:4">
+      <c r="A2842" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2842">
+        <v>57</v>
+      </c>
+      <c r="C2842">
+        <v>5484.9</v>
+      </c>
+      <c r="D2842" t="s">
+        <v>2844</v>
+      </c>
+    </row>
+    <row r="2843" spans="1:4">
+      <c r="A2843" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2843">
+        <v>58</v>
+      </c>
+      <c r="C2843">
+        <v>5471</v>
+      </c>
+      <c r="D2843" t="s">
+        <v>2845</v>
+      </c>
+    </row>
+    <row r="2844" spans="1:4">
+      <c r="A2844" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2844">
+        <v>59</v>
+      </c>
+      <c r="C2844">
+        <v>5455.7</v>
+      </c>
+      <c r="D2844" t="s">
+        <v>2846</v>
+      </c>
+    </row>
+    <row r="2845" spans="1:4">
+      <c r="A2845" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2845">
+        <v>60</v>
+      </c>
+      <c r="C2845">
+        <v>5460.8</v>
+      </c>
+      <c r="D2845" t="s">
+        <v>2847</v>
+      </c>
+    </row>
+    <row r="2846" spans="1:4">
+      <c r="A2846" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2846">
+        <v>61</v>
+      </c>
+      <c r="C2846">
+        <v>5451.1</v>
+      </c>
+      <c r="D2846" t="s">
+        <v>2848</v>
+      </c>
+    </row>
+    <row r="2847" spans="1:4">
+      <c r="A2847" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2847">
+        <v>62</v>
+      </c>
+      <c r="C2847">
+        <v>5427.5</v>
+      </c>
+      <c r="D2847" t="s">
+        <v>2849</v>
+      </c>
+    </row>
+    <row r="2848" spans="1:4">
+      <c r="A2848" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2848">
+        <v>63</v>
+      </c>
+      <c r="C2848">
+        <v>5429.5</v>
+      </c>
+      <c r="D2848" t="s">
+        <v>2850</v>
+      </c>
+    </row>
+    <row r="2849" spans="1:4">
+      <c r="A2849" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2849">
+        <v>64</v>
+      </c>
+      <c r="C2849">
+        <v>5470.1</v>
+      </c>
+      <c r="D2849" t="s">
+        <v>2851</v>
+      </c>
+    </row>
+    <row r="2850" spans="1:4">
+      <c r="A2850" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2850">
+        <v>65</v>
+      </c>
+      <c r="C2850">
+        <v>5693.2</v>
+      </c>
+      <c r="D2850" t="s">
+        <v>2852</v>
+      </c>
+    </row>
+    <row r="2851" spans="1:4">
+      <c r="A2851" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2851">
+        <v>66</v>
+      </c>
+      <c r="C2851">
+        <v>5730.8</v>
+      </c>
+      <c r="D2851" t="s">
+        <v>2853</v>
+      </c>
+    </row>
+    <row r="2852" spans="1:4">
+      <c r="A2852" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2852">
+        <v>67</v>
+      </c>
+      <c r="C2852">
+        <v>5857.2</v>
+      </c>
+      <c r="D2852" t="s">
+        <v>2854</v>
+      </c>
+    </row>
+    <row r="2853" spans="1:4">
+      <c r="A2853" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2853">
+        <v>68</v>
+      </c>
+      <c r="C2853">
+        <v>6047.7</v>
+      </c>
+      <c r="D2853" t="s">
+        <v>2855</v>
+      </c>
+    </row>
+    <row r="2854" spans="1:4">
+      <c r="A2854" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2854">
+        <v>69</v>
+      </c>
+      <c r="C2854">
+        <v>6258.8</v>
+      </c>
+      <c r="D2854" t="s">
+        <v>2856</v>
+      </c>
+    </row>
+    <row r="2855" spans="1:4">
+      <c r="A2855" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2855">
+        <v>70</v>
+      </c>
+      <c r="C2855">
+        <v>6212</v>
+      </c>
+      <c r="D2855" t="s">
+        <v>2857</v>
+      </c>
+    </row>
+    <row r="2856" spans="1:4">
+      <c r="A2856" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2856">
+        <v>71</v>
+      </c>
+      <c r="C2856">
+        <v>6134.4</v>
+      </c>
+      <c r="D2856" t="s">
+        <v>2858</v>
+      </c>
+    </row>
+    <row r="2857" spans="1:4">
+      <c r="A2857" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2857">
+        <v>72</v>
+      </c>
+      <c r="C2857">
+        <v>6049.6</v>
+      </c>
+      <c r="D2857" t="s">
+        <v>2859</v>
+      </c>
+    </row>
+    <row r="2858" spans="1:4">
+      <c r="A2858" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2858">
+        <v>73</v>
+      </c>
+      <c r="C2858">
+        <v>6547.6</v>
+      </c>
+      <c r="D2858" t="s">
+        <v>2860</v>
+      </c>
+    </row>
+    <row r="2859" spans="1:4">
+      <c r="A2859" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2859">
+        <v>74</v>
+      </c>
+      <c r="C2859">
+        <v>6480.7</v>
+      </c>
+      <c r="D2859" t="s">
+        <v>2861</v>
+      </c>
+    </row>
+    <row r="2860" spans="1:4">
+      <c r="A2860" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2860">
+        <v>75</v>
+      </c>
+      <c r="C2860">
+        <v>6334.8</v>
+      </c>
+      <c r="D2860" t="s">
+        <v>2862</v>
+      </c>
+    </row>
+    <row r="2861" spans="1:4">
+      <c r="A2861" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2861">
+        <v>76</v>
+      </c>
+      <c r="C2861">
+        <v>6306.9</v>
+      </c>
+      <c r="D2861" t="s">
+        <v>2863</v>
+      </c>
+    </row>
+    <row r="2862" spans="1:4">
+      <c r="A2862" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2862">
+        <v>77</v>
+      </c>
+      <c r="C2862">
+        <v>7046.9</v>
+      </c>
+      <c r="D2862" t="s">
+        <v>2864</v>
+      </c>
+    </row>
+    <row r="2863" spans="1:4">
+      <c r="A2863" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2863">
+        <v>78</v>
+      </c>
+      <c r="C2863">
+        <v>7038.4</v>
+      </c>
+      <c r="D2863" t="s">
+        <v>2865</v>
+      </c>
+    </row>
+    <row r="2864" spans="1:4">
+      <c r="A2864" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2864">
+        <v>79</v>
+      </c>
+      <c r="C2864">
+        <v>7027.8</v>
+      </c>
+      <c r="D2864" t="s">
+        <v>2866</v>
+      </c>
+    </row>
+    <row r="2865" spans="1:4">
+      <c r="A2865" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2865">
+        <v>80</v>
+      </c>
+      <c r="C2865">
+        <v>7012.7</v>
+      </c>
+      <c r="D2865" t="s">
+        <v>2867</v>
+      </c>
+    </row>
+    <row r="2866" spans="1:4">
+      <c r="A2866" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2866">
+        <v>81</v>
+      </c>
+      <c r="C2866">
+        <v>7177.7</v>
+      </c>
+      <c r="D2866" t="s">
+        <v>2868</v>
+      </c>
+    </row>
+    <row r="2867" spans="1:4">
+      <c r="A2867" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2867">
+        <v>82</v>
+      </c>
+      <c r="C2867">
+        <v>7188.4</v>
+      </c>
+      <c r="D2867" t="s">
+        <v>2869</v>
+      </c>
+    </row>
+    <row r="2868" spans="1:4">
+      <c r="A2868" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2868">
+        <v>83</v>
+      </c>
+      <c r="C2868">
+        <v>7156.4</v>
+      </c>
+      <c r="D2868" t="s">
+        <v>2870</v>
+      </c>
+    </row>
+    <row r="2869" spans="1:4">
+      <c r="A2869" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2869">
+        <v>84</v>
+      </c>
+      <c r="C2869">
+        <v>7221.6</v>
+      </c>
+      <c r="D2869" t="s">
+        <v>2871</v>
+      </c>
+    </row>
+    <row r="2870" spans="1:4">
+      <c r="A2870" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2870">
+        <v>85</v>
+      </c>
+      <c r="C2870">
+        <v>7162.7</v>
+      </c>
+      <c r="D2870" t="s">
+        <v>2872</v>
+      </c>
+    </row>
+    <row r="2871" spans="1:4">
+      <c r="A2871" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2871">
+        <v>86</v>
+      </c>
+      <c r="C2871">
+        <v>7036.6</v>
+      </c>
+      <c r="D2871" t="s">
+        <v>2873</v>
+      </c>
+    </row>
+    <row r="2872" spans="1:4">
+      <c r="A2872" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2872">
+        <v>87</v>
+      </c>
+      <c r="C2872">
+        <v>6954.2</v>
+      </c>
+      <c r="D2872" t="s">
+        <v>2874</v>
+      </c>
+    </row>
+    <row r="2873" spans="1:4">
+      <c r="A2873" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2873">
+        <v>88</v>
+      </c>
+      <c r="C2873">
+        <v>7000.6</v>
+      </c>
+      <c r="D2873" t="s">
+        <v>2875</v>
+      </c>
+    </row>
+    <row r="2874" spans="1:4">
+      <c r="A2874" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2874">
+        <v>89</v>
+      </c>
+      <c r="C2874">
+        <v>6632.9</v>
+      </c>
+      <c r="D2874" t="s">
+        <v>2876</v>
+      </c>
+    </row>
+    <row r="2875" spans="1:4">
+      <c r="A2875" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2875">
+        <v>90</v>
+      </c>
+      <c r="C2875">
+        <v>6623.4</v>
+      </c>
+      <c r="D2875" t="s">
+        <v>2877</v>
+      </c>
+    </row>
+    <row r="2876" spans="1:4">
+      <c r="A2876" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2876">
+        <v>91</v>
+      </c>
+      <c r="C2876">
+        <v>6551.3</v>
+      </c>
+      <c r="D2876" t="s">
+        <v>2878</v>
+      </c>
+    </row>
+    <row r="2877" spans="1:4">
+      <c r="A2877" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2877">
+        <v>92</v>
+      </c>
+      <c r="C2877">
+        <v>6403.4</v>
+      </c>
+      <c r="D2877" t="s">
+        <v>2879</v>
+      </c>
+    </row>
+    <row r="2878" spans="1:4">
+      <c r="A2878" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2878">
+        <v>93</v>
+      </c>
+      <c r="C2878">
+        <v>5887.1</v>
+      </c>
+      <c r="D2878" t="s">
+        <v>2880</v>
+      </c>
+    </row>
+    <row r="2879" spans="1:4">
+      <c r="A2879" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2879">
+        <v>94</v>
+      </c>
+      <c r="C2879">
+        <v>5705.2</v>
+      </c>
+      <c r="D2879" t="s">
+        <v>2881</v>
+      </c>
+    </row>
+    <row r="2880" spans="1:4">
+      <c r="A2880" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2880">
+        <v>95</v>
+      </c>
+      <c r="C2880">
+        <v>5678.5</v>
+      </c>
+      <c r="D2880" t="s">
+        <v>2882</v>
+      </c>
+    </row>
+    <row r="2881" spans="1:4">
+      <c r="A2881" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2881">
+        <v>96</v>
+      </c>
+      <c r="C2881">
+        <v>5609.2</v>
+      </c>
+      <c r="D2881" t="s">
+        <v>2883</v>
       </c>
     </row>
   </sheetData>

--- a/Market Fundamentals/Transelectrica_data/Cons_Prod_final/Weekly_Production_2026.xlsx
+++ b/Market Fundamentals/Transelectrica_data/Cons_Prod_final/Weekly_Production_2026.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1828" uniqueCount="1828">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1924" uniqueCount="1924">
   <si>
     <t>Date</t>
   </si>
@@ -5498,6 +5498,294 @@
   </si>
   <si>
     <t>19.05.202696.0</t>
+  </si>
+  <si>
+    <t>20.05.20261.0</t>
+  </si>
+  <si>
+    <t>20.05.20262.0</t>
+  </si>
+  <si>
+    <t>20.05.20263.0</t>
+  </si>
+  <si>
+    <t>20.05.20264.0</t>
+  </si>
+  <si>
+    <t>20.05.20265.0</t>
+  </si>
+  <si>
+    <t>20.05.20266.0</t>
+  </si>
+  <si>
+    <t>20.05.20267.0</t>
+  </si>
+  <si>
+    <t>20.05.20268.0</t>
+  </si>
+  <si>
+    <t>20.05.20269.0</t>
+  </si>
+  <si>
+    <t>20.05.202610.0</t>
+  </si>
+  <si>
+    <t>20.05.202611.0</t>
+  </si>
+  <si>
+    <t>20.05.202612.0</t>
+  </si>
+  <si>
+    <t>20.05.202613.0</t>
+  </si>
+  <si>
+    <t>20.05.202614.0</t>
+  </si>
+  <si>
+    <t>20.05.202615.0</t>
+  </si>
+  <si>
+    <t>20.05.202616.0</t>
+  </si>
+  <si>
+    <t>20.05.202617.0</t>
+  </si>
+  <si>
+    <t>20.05.202618.0</t>
+  </si>
+  <si>
+    <t>20.05.202619.0</t>
+  </si>
+  <si>
+    <t>20.05.202620.0</t>
+  </si>
+  <si>
+    <t>20.05.202621.0</t>
+  </si>
+  <si>
+    <t>20.05.202622.0</t>
+  </si>
+  <si>
+    <t>20.05.202623.0</t>
+  </si>
+  <si>
+    <t>20.05.202624.0</t>
+  </si>
+  <si>
+    <t>20.05.202625.0</t>
+  </si>
+  <si>
+    <t>20.05.202626.0</t>
+  </si>
+  <si>
+    <t>20.05.202627.0</t>
+  </si>
+  <si>
+    <t>20.05.202628.0</t>
+  </si>
+  <si>
+    <t>20.05.202629.0</t>
+  </si>
+  <si>
+    <t>20.05.202630.0</t>
+  </si>
+  <si>
+    <t>20.05.202631.0</t>
+  </si>
+  <si>
+    <t>20.05.202632.0</t>
+  </si>
+  <si>
+    <t>20.05.202633.0</t>
+  </si>
+  <si>
+    <t>20.05.202634.0</t>
+  </si>
+  <si>
+    <t>20.05.202635.0</t>
+  </si>
+  <si>
+    <t>20.05.202636.0</t>
+  </si>
+  <si>
+    <t>20.05.202637.0</t>
+  </si>
+  <si>
+    <t>20.05.202638.0</t>
+  </si>
+  <si>
+    <t>20.05.202639.0</t>
+  </si>
+  <si>
+    <t>20.05.202640.0</t>
+  </si>
+  <si>
+    <t>20.05.202641.0</t>
+  </si>
+  <si>
+    <t>20.05.202642.0</t>
+  </si>
+  <si>
+    <t>20.05.202643.0</t>
+  </si>
+  <si>
+    <t>20.05.202644.0</t>
+  </si>
+  <si>
+    <t>20.05.202645.0</t>
+  </si>
+  <si>
+    <t>20.05.202646.0</t>
+  </si>
+  <si>
+    <t>20.05.202647.0</t>
+  </si>
+  <si>
+    <t>20.05.202648.0</t>
+  </si>
+  <si>
+    <t>20.05.202649.0</t>
+  </si>
+  <si>
+    <t>20.05.202650.0</t>
+  </si>
+  <si>
+    <t>20.05.202651.0</t>
+  </si>
+  <si>
+    <t>20.05.202652.0</t>
+  </si>
+  <si>
+    <t>20.05.202653.0</t>
+  </si>
+  <si>
+    <t>20.05.202654.0</t>
+  </si>
+  <si>
+    <t>20.05.202655.0</t>
+  </si>
+  <si>
+    <t>20.05.202656.0</t>
+  </si>
+  <si>
+    <t>20.05.202657.0</t>
+  </si>
+  <si>
+    <t>20.05.202658.0</t>
+  </si>
+  <si>
+    <t>20.05.202659.0</t>
+  </si>
+  <si>
+    <t>20.05.202660.0</t>
+  </si>
+  <si>
+    <t>20.05.202661.0</t>
+  </si>
+  <si>
+    <t>20.05.202662.0</t>
+  </si>
+  <si>
+    <t>20.05.202663.0</t>
+  </si>
+  <si>
+    <t>20.05.202664.0</t>
+  </si>
+  <si>
+    <t>20.05.202665.0</t>
+  </si>
+  <si>
+    <t>20.05.202666.0</t>
+  </si>
+  <si>
+    <t>20.05.202667.0</t>
+  </si>
+  <si>
+    <t>20.05.202668.0</t>
+  </si>
+  <si>
+    <t>20.05.202669.0</t>
+  </si>
+  <si>
+    <t>20.05.202670.0</t>
+  </si>
+  <si>
+    <t>20.05.202671.0</t>
+  </si>
+  <si>
+    <t>20.05.202672.0</t>
+  </si>
+  <si>
+    <t>20.05.202673.0</t>
+  </si>
+  <si>
+    <t>20.05.202674.0</t>
+  </si>
+  <si>
+    <t>20.05.202675.0</t>
+  </si>
+  <si>
+    <t>20.05.202676.0</t>
+  </si>
+  <si>
+    <t>20.05.202677.0</t>
+  </si>
+  <si>
+    <t>20.05.202678.0</t>
+  </si>
+  <si>
+    <t>20.05.202679.0</t>
+  </si>
+  <si>
+    <t>20.05.202680.0</t>
+  </si>
+  <si>
+    <t>20.05.202681.0</t>
+  </si>
+  <si>
+    <t>20.05.202682.0</t>
+  </si>
+  <si>
+    <t>20.05.202683.0</t>
+  </si>
+  <si>
+    <t>20.05.202684.0</t>
+  </si>
+  <si>
+    <t>20.05.202685.0</t>
+  </si>
+  <si>
+    <t>20.05.202686.0</t>
+  </si>
+  <si>
+    <t>20.05.202687.0</t>
+  </si>
+  <si>
+    <t>20.05.202688.0</t>
+  </si>
+  <si>
+    <t>20.05.202689.0</t>
+  </si>
+  <si>
+    <t>20.05.202690.0</t>
+  </si>
+  <si>
+    <t>20.05.202691.0</t>
+  </si>
+  <si>
+    <t>20.05.202692.0</t>
+  </si>
+  <si>
+    <t>20.05.202693.0</t>
+  </si>
+  <si>
+    <t>20.05.202694.0</t>
+  </si>
+  <si>
+    <t>20.05.202695.0</t>
+  </si>
+  <si>
+    <t>20.05.202696.0</t>
   </si>
 </sst>
 </file>
@@ -5859,7 +6147,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1825"/>
+  <dimension ref="A1:D1921"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -22012,7 +22300,7 @@
         <v>1</v>
       </c>
       <c r="C1154">
-        <v>5616</v>
+        <v>4319.2</v>
       </c>
       <c r="D1154" t="s">
         <v>1156</v>
@@ -22026,7 +22314,7 @@
         <v>2</v>
       </c>
       <c r="C1155">
-        <v>5596.2</v>
+        <v>4295.4</v>
       </c>
       <c r="D1155" t="s">
         <v>1157</v>
@@ -22040,7 +22328,7 @@
         <v>3</v>
       </c>
       <c r="C1156">
-        <v>5489.7</v>
+        <v>4308.8</v>
       </c>
       <c r="D1156" t="s">
         <v>1158</v>
@@ -22054,7 +22342,7 @@
         <v>4</v>
       </c>
       <c r="C1157">
-        <v>5367.7</v>
+        <v>4322.6</v>
       </c>
       <c r="D1157" t="s">
         <v>1159</v>
@@ -22068,7 +22356,7 @@
         <v>5</v>
       </c>
       <c r="C1158">
-        <v>4913.4</v>
+        <v>4963</v>
       </c>
       <c r="D1158" t="s">
         <v>1160</v>
@@ -22082,7 +22370,7 @@
         <v>6</v>
       </c>
       <c r="C1159">
-        <v>4878.2</v>
+        <v>4933</v>
       </c>
       <c r="D1159" t="s">
         <v>1161</v>
@@ -22096,7 +22384,7 @@
         <v>7</v>
       </c>
       <c r="C1160">
-        <v>4819.8</v>
+        <v>4913</v>
       </c>
       <c r="D1160" t="s">
         <v>1162</v>
@@ -22110,7 +22398,7 @@
         <v>8</v>
       </c>
       <c r="C1161">
-        <v>4774.3</v>
+        <v>4893</v>
       </c>
       <c r="D1161" t="s">
         <v>1163</v>
@@ -22124,7 +22412,7 @@
         <v>9</v>
       </c>
       <c r="C1162">
-        <v>4485.1</v>
+        <v>4784</v>
       </c>
       <c r="D1162" t="s">
         <v>1164</v>
@@ -22138,7 +22426,7 @@
         <v>10</v>
       </c>
       <c r="C1163">
-        <v>4454.8</v>
+        <v>4774</v>
       </c>
       <c r="D1163" t="s">
         <v>1165</v>
@@ -22152,7 +22440,7 @@
         <v>11</v>
       </c>
       <c r="C1164">
-        <v>4430.6</v>
+        <v>4774</v>
       </c>
       <c r="D1164" t="s">
         <v>1166</v>
@@ -22166,7 +22454,7 @@
         <v>12</v>
       </c>
       <c r="C1165">
-        <v>4421.4</v>
+        <v>4774</v>
       </c>
       <c r="D1165" t="s">
         <v>1167</v>
@@ -22180,7 +22468,7 @@
         <v>13</v>
       </c>
       <c r="C1166">
-        <v>4434</v>
+        <v>4763</v>
       </c>
       <c r="D1166" t="s">
         <v>1168</v>
@@ -22194,7 +22482,7 @@
         <v>14</v>
       </c>
       <c r="C1167">
-        <v>4411.1</v>
+        <v>4763</v>
       </c>
       <c r="D1167" t="s">
         <v>1169</v>
@@ -22208,7 +22496,7 @@
         <v>15</v>
       </c>
       <c r="C1168">
-        <v>4385.4</v>
+        <v>4763</v>
       </c>
       <c r="D1168" t="s">
         <v>1170</v>
@@ -22222,7 +22510,7 @@
         <v>16</v>
       </c>
       <c r="C1169">
-        <v>4365.9</v>
+        <v>4773</v>
       </c>
       <c r="D1169" t="s">
         <v>1171</v>
@@ -22236,7 +22524,7 @@
         <v>17</v>
       </c>
       <c r="C1170">
-        <v>4345.9</v>
+        <v>4833</v>
       </c>
       <c r="D1170" t="s">
         <v>1172</v>
@@ -22250,7 +22538,7 @@
         <v>18</v>
       </c>
       <c r="C1171">
-        <v>4309.2</v>
+        <v>4833</v>
       </c>
       <c r="D1171" t="s">
         <v>1173</v>
@@ -22264,7 +22552,7 @@
         <v>19</v>
       </c>
       <c r="C1172">
-        <v>4267.8</v>
+        <v>4833</v>
       </c>
       <c r="D1172" t="s">
         <v>1174</v>
@@ -22278,7 +22566,7 @@
         <v>20</v>
       </c>
       <c r="C1173">
-        <v>4253.5</v>
+        <v>4833</v>
       </c>
       <c r="D1173" t="s">
         <v>1175</v>
@@ -22292,7 +22580,7 @@
         <v>21</v>
       </c>
       <c r="C1174">
-        <v>4295.6</v>
+        <v>4881</v>
       </c>
       <c r="D1174" t="s">
         <v>1176</v>
@@ -22306,7 +22594,7 @@
         <v>22</v>
       </c>
       <c r="C1175">
-        <v>4295.6</v>
+        <v>4911</v>
       </c>
       <c r="D1175" t="s">
         <v>1177</v>
@@ -22320,7 +22608,7 @@
         <v>23</v>
       </c>
       <c r="C1176">
-        <v>4283.4</v>
+        <v>4951</v>
       </c>
       <c r="D1176" t="s">
         <v>1178</v>
@@ -22334,7 +22622,7 @@
         <v>24</v>
       </c>
       <c r="C1177">
-        <v>4256.6</v>
+        <v>5021</v>
       </c>
       <c r="D1177" t="s">
         <v>1179</v>
@@ -22348,7 +22636,7 @@
         <v>25</v>
       </c>
       <c r="C1178">
-        <v>4296.8</v>
+        <v>5128</v>
       </c>
       <c r="D1178" t="s">
         <v>1180</v>
@@ -22362,7 +22650,7 @@
         <v>26</v>
       </c>
       <c r="C1179">
-        <v>4311.3</v>
+        <v>5228</v>
       </c>
       <c r="D1179" t="s">
         <v>1181</v>
@@ -22376,7 +22664,7 @@
         <v>27</v>
       </c>
       <c r="C1180">
-        <v>4333.1</v>
+        <v>5328</v>
       </c>
       <c r="D1180" t="s">
         <v>1182</v>
@@ -22390,7 +22678,7 @@
         <v>28</v>
       </c>
       <c r="C1181">
-        <v>4326.4</v>
+        <v>5438</v>
       </c>
       <c r="D1181" t="s">
         <v>1183</v>
@@ -22404,7 +22692,7 @@
         <v>29</v>
       </c>
       <c r="C1182">
-        <v>4340.9</v>
+        <v>5874</v>
       </c>
       <c r="D1182" t="s">
         <v>1184</v>
@@ -22418,7 +22706,7 @@
         <v>30</v>
       </c>
       <c r="C1183">
-        <v>4336.5</v>
+        <v>6004</v>
       </c>
       <c r="D1183" t="s">
         <v>1185</v>
@@ -22432,7 +22720,7 @@
         <v>31</v>
       </c>
       <c r="C1184">
-        <v>4432.3</v>
+        <v>6084</v>
       </c>
       <c r="D1184" t="s">
         <v>1186</v>
@@ -22446,7 +22734,7 @@
         <v>32</v>
       </c>
       <c r="C1185">
-        <v>4539.7</v>
+        <v>6134</v>
       </c>
       <c r="D1185" t="s">
         <v>1187</v>
@@ -22460,7 +22748,7 @@
         <v>33</v>
       </c>
       <c r="C1186">
-        <v>4461.3</v>
+        <v>6119</v>
       </c>
       <c r="D1186" t="s">
         <v>1188</v>
@@ -22474,7 +22762,7 @@
         <v>34</v>
       </c>
       <c r="C1187">
-        <v>4573</v>
+        <v>6109</v>
       </c>
       <c r="D1187" t="s">
         <v>1189</v>
@@ -22488,7 +22776,7 @@
         <v>35</v>
       </c>
       <c r="C1188">
-        <v>4669.6</v>
+        <v>6109</v>
       </c>
       <c r="D1188" t="s">
         <v>1190</v>
@@ -22502,7 +22790,7 @@
         <v>36</v>
       </c>
       <c r="C1189">
-        <v>4844.8</v>
+        <v>6099</v>
       </c>
       <c r="D1189" t="s">
         <v>1191</v>
@@ -22516,7 +22804,7 @@
         <v>37</v>
       </c>
       <c r="C1190">
-        <v>4736.5</v>
+        <v>6146</v>
       </c>
       <c r="D1190" t="s">
         <v>1192</v>
@@ -22530,7 +22818,7 @@
         <v>38</v>
       </c>
       <c r="C1191">
-        <v>4769.5</v>
+        <v>6106</v>
       </c>
       <c r="D1191" t="s">
         <v>1193</v>
@@ -22544,7 +22832,7 @@
         <v>39</v>
       </c>
       <c r="C1192">
-        <v>4836.2</v>
+        <v>6076</v>
       </c>
       <c r="D1192" t="s">
         <v>1194</v>
@@ -22558,7 +22846,7 @@
         <v>40</v>
       </c>
       <c r="C1193">
-        <v>4904.8</v>
+        <v>5996</v>
       </c>
       <c r="D1193" t="s">
         <v>1195</v>
@@ -22572,7 +22860,7 @@
         <v>41</v>
       </c>
       <c r="C1194">
-        <v>5070.7</v>
+        <v>6027</v>
       </c>
       <c r="D1194" t="s">
         <v>1196</v>
@@ -22586,7 +22874,7 @@
         <v>42</v>
       </c>
       <c r="C1195">
-        <v>5069.9</v>
+        <v>5937</v>
       </c>
       <c r="D1195" t="s">
         <v>1197</v>
@@ -22600,7 +22888,7 @@
         <v>43</v>
       </c>
       <c r="C1196">
-        <v>5078.3</v>
+        <v>5847</v>
       </c>
       <c r="D1196" t="s">
         <v>1198</v>
@@ -22614,7 +22902,7 @@
         <v>44</v>
       </c>
       <c r="C1197">
-        <v>5107.5</v>
+        <v>5767</v>
       </c>
       <c r="D1197" t="s">
         <v>1199</v>
@@ -22628,7 +22916,7 @@
         <v>45</v>
       </c>
       <c r="C1198">
-        <v>5118</v>
+        <v>5728</v>
       </c>
       <c r="D1198" t="s">
         <v>1200</v>
@@ -22642,7 +22930,7 @@
         <v>46</v>
       </c>
       <c r="C1199">
-        <v>5123.3</v>
+        <v>5668</v>
       </c>
       <c r="D1199" t="s">
         <v>1201</v>
@@ -22656,7 +22944,7 @@
         <v>47</v>
       </c>
       <c r="C1200">
-        <v>5114.1</v>
+        <v>5618</v>
       </c>
       <c r="D1200" t="s">
         <v>1202</v>
@@ -22670,7 +22958,7 @@
         <v>48</v>
       </c>
       <c r="C1201">
-        <v>5150.1</v>
+        <v>5578</v>
       </c>
       <c r="D1201" t="s">
         <v>1203</v>
@@ -22684,7 +22972,7 @@
         <v>49</v>
       </c>
       <c r="C1202">
-        <v>4956.1</v>
+        <v>5513</v>
       </c>
       <c r="D1202" t="s">
         <v>1204</v>
@@ -22698,7 +22986,7 @@
         <v>50</v>
       </c>
       <c r="C1203">
-        <v>4938.2</v>
+        <v>5493</v>
       </c>
       <c r="D1203" t="s">
         <v>1205</v>
@@ -22712,7 +23000,7 @@
         <v>51</v>
       </c>
       <c r="C1204">
-        <v>4925.5</v>
+        <v>5473</v>
       </c>
       <c r="D1204" t="s">
         <v>1206</v>
@@ -22726,7 +23014,7 @@
         <v>52</v>
       </c>
       <c r="C1205">
-        <v>4920</v>
+        <v>5473</v>
       </c>
       <c r="D1205" t="s">
         <v>1207</v>
@@ -22740,7 +23028,7 @@
         <v>53</v>
       </c>
       <c r="C1206">
-        <v>4887.1</v>
+        <v>5471</v>
       </c>
       <c r="D1206" t="s">
         <v>1208</v>
@@ -22754,7 +23042,7 @@
         <v>54</v>
       </c>
       <c r="C1207">
-        <v>4868.4</v>
+        <v>5471</v>
       </c>
       <c r="D1207" t="s">
         <v>1209</v>
@@ -22768,7 +23056,7 @@
         <v>55</v>
       </c>
       <c r="C1208">
-        <v>4883.8</v>
+        <v>5471</v>
       </c>
       <c r="D1208" t="s">
         <v>1210</v>
@@ -22782,7 +23070,7 @@
         <v>56</v>
       </c>
       <c r="C1209">
-        <v>4898.2</v>
+        <v>5461</v>
       </c>
       <c r="D1209" t="s">
         <v>1211</v>
@@ -22796,7 +23084,7 @@
         <v>57</v>
       </c>
       <c r="C1210">
-        <v>4960.2</v>
+        <v>5512</v>
       </c>
       <c r="D1210" t="s">
         <v>1212</v>
@@ -22810,7 +23098,7 @@
         <v>58</v>
       </c>
       <c r="C1211">
-        <v>4957</v>
+        <v>5502</v>
       </c>
       <c r="D1211" t="s">
         <v>1213</v>
@@ -22824,7 +23112,7 @@
         <v>59</v>
       </c>
       <c r="C1212">
-        <v>4958</v>
+        <v>5502</v>
       </c>
       <c r="D1212" t="s">
         <v>1214</v>
@@ -22838,7 +23126,7 @@
         <v>60</v>
       </c>
       <c r="C1213">
-        <v>4995.1</v>
+        <v>5512</v>
       </c>
       <c r="D1213" t="s">
         <v>1215</v>
@@ -22852,7 +23140,7 @@
         <v>61</v>
       </c>
       <c r="C1214">
-        <v>5031.2</v>
+        <v>5569</v>
       </c>
       <c r="D1214" t="s">
         <v>1216</v>
@@ -22866,7 +23154,7 @@
         <v>62</v>
       </c>
       <c r="C1215">
-        <v>4966.4</v>
+        <v>5589</v>
       </c>
       <c r="D1215" t="s">
         <v>1217</v>
@@ -22880,7 +23168,7 @@
         <v>63</v>
       </c>
       <c r="C1216">
-        <v>4911.2</v>
+        <v>5609</v>
       </c>
       <c r="D1216" t="s">
         <v>1218</v>
@@ -22894,7 +23182,7 @@
         <v>64</v>
       </c>
       <c r="C1217">
-        <v>4900.3</v>
+        <v>5639</v>
       </c>
       <c r="D1217" t="s">
         <v>1219</v>
@@ -22908,7 +23196,7 @@
         <v>65</v>
       </c>
       <c r="C1218">
-        <v>4899.1</v>
+        <v>5752</v>
       </c>
       <c r="D1218" t="s">
         <v>1220</v>
@@ -22922,7 +23210,7 @@
         <v>66</v>
       </c>
       <c r="C1219">
-        <v>4820.3</v>
+        <v>5812</v>
       </c>
       <c r="D1219" t="s">
         <v>1221</v>
@@ -22936,7 +23224,7 @@
         <v>67</v>
       </c>
       <c r="C1220">
-        <v>4799.2</v>
+        <v>5882</v>
       </c>
       <c r="D1220" t="s">
         <v>1222</v>
@@ -22950,7 +23238,7 @@
         <v>68</v>
       </c>
       <c r="C1221">
-        <v>4740.9</v>
+        <v>5952</v>
       </c>
       <c r="D1221" t="s">
         <v>1223</v>
@@ -22964,7 +23252,7 @@
         <v>69</v>
       </c>
       <c r="C1222">
-        <v>4633.4</v>
+        <v>5921</v>
       </c>
       <c r="D1222" t="s">
         <v>1224</v>
@@ -22978,7 +23266,7 @@
         <v>70</v>
       </c>
       <c r="C1223">
-        <v>4568.8</v>
+        <v>6001</v>
       </c>
       <c r="D1223" t="s">
         <v>1225</v>
@@ -22992,7 +23280,7 @@
         <v>71</v>
       </c>
       <c r="C1224">
-        <v>4524.3</v>
+        <v>6071</v>
       </c>
       <c r="D1224" t="s">
         <v>1226</v>
@@ -23006,7 +23294,7 @@
         <v>72</v>
       </c>
       <c r="C1225">
-        <v>4458.9</v>
+        <v>6161</v>
       </c>
       <c r="D1225" t="s">
         <v>1227</v>
@@ -23020,7 +23308,7 @@
         <v>73</v>
       </c>
       <c r="C1226">
-        <v>5024.8</v>
+        <v>5868</v>
       </c>
       <c r="D1226" t="s">
         <v>1228</v>
@@ -23034,7 +23322,7 @@
         <v>74</v>
       </c>
       <c r="C1227">
-        <v>4935</v>
+        <v>5958</v>
       </c>
       <c r="D1227" t="s">
         <v>1229</v>
@@ -23048,7 +23336,7 @@
         <v>75</v>
       </c>
       <c r="C1228">
-        <v>4876.5</v>
+        <v>6048</v>
       </c>
       <c r="D1228" t="s">
         <v>1230</v>
@@ -23062,7 +23350,7 @@
         <v>76</v>
       </c>
       <c r="C1229">
-        <v>4845.9</v>
+        <v>6158</v>
       </c>
       <c r="D1229" t="s">
         <v>1231</v>
@@ -23076,7 +23364,7 @@
         <v>77</v>
       </c>
       <c r="C1230">
-        <v>4761.2</v>
+        <v>6256</v>
       </c>
       <c r="D1230" t="s">
         <v>1232</v>
@@ -23090,7 +23378,7 @@
         <v>78</v>
       </c>
       <c r="C1231">
-        <v>4789.7</v>
+        <v>6376</v>
       </c>
       <c r="D1231" t="s">
         <v>1233</v>
@@ -23104,7 +23392,7 @@
         <v>79</v>
       </c>
       <c r="C1232">
-        <v>4736.6</v>
+        <v>6476</v>
       </c>
       <c r="D1232" t="s">
         <v>1234</v>
@@ -23118,7 +23406,7 @@
         <v>80</v>
       </c>
       <c r="C1233">
-        <v>4729.2</v>
+        <v>6556</v>
       </c>
       <c r="D1233" t="s">
         <v>1235</v>
@@ -23132,7 +23420,7 @@
         <v>81</v>
       </c>
       <c r="C1234">
-        <v>4815.1</v>
+        <v>6608</v>
       </c>
       <c r="D1234" t="s">
         <v>1236</v>
@@ -23146,7 +23434,7 @@
         <v>82</v>
       </c>
       <c r="C1235">
-        <v>4876.2</v>
+        <v>6688</v>
       </c>
       <c r="D1235" t="s">
         <v>1237</v>
@@ -23160,7 +23448,7 @@
         <v>83</v>
       </c>
       <c r="C1236">
-        <v>4918.5</v>
+        <v>6738</v>
       </c>
       <c r="D1236" t="s">
         <v>1238</v>
@@ -23174,7 +23462,7 @@
         <v>84</v>
       </c>
       <c r="C1237">
-        <v>4930.7</v>
+        <v>6798</v>
       </c>
       <c r="D1237" t="s">
         <v>1239</v>
@@ -23188,7 +23476,7 @@
         <v>85</v>
       </c>
       <c r="C1238">
-        <v>4974.6</v>
+        <v>6859</v>
       </c>
       <c r="D1238" t="s">
         <v>1240</v>
@@ -23202,7 +23490,7 @@
         <v>86</v>
       </c>
       <c r="C1239">
-        <v>4962.3</v>
+        <v>6829</v>
       </c>
       <c r="D1239" t="s">
         <v>1241</v>
@@ -23216,7 +23504,7 @@
         <v>87</v>
       </c>
       <c r="C1240">
-        <v>5014.8</v>
+        <v>6769</v>
       </c>
       <c r="D1240" t="s">
         <v>1242</v>
@@ -23230,7 +23518,7 @@
         <v>88</v>
       </c>
       <c r="C1241">
-        <v>5013.5</v>
+        <v>6659</v>
       </c>
       <c r="D1241" t="s">
         <v>1243</v>
@@ -23244,7 +23532,7 @@
         <v>89</v>
       </c>
       <c r="C1242">
-        <v>4841.9</v>
+        <v>6509</v>
       </c>
       <c r="D1242" t="s">
         <v>1244</v>
@@ -23258,7 +23546,7 @@
         <v>90</v>
       </c>
       <c r="C1243">
-        <v>4823.7</v>
+        <v>6359</v>
       </c>
       <c r="D1243" t="s">
         <v>1245</v>
@@ -23272,7 +23560,7 @@
         <v>91</v>
       </c>
       <c r="C1244">
-        <v>4760.4</v>
+        <v>6209</v>
       </c>
       <c r="D1244" t="s">
         <v>1246</v>
@@ -23286,7 +23574,7 @@
         <v>92</v>
       </c>
       <c r="C1245">
-        <v>4753.1</v>
+        <v>6049</v>
       </c>
       <c r="D1245" t="s">
         <v>1247</v>
@@ -23300,7 +23588,7 @@
         <v>93</v>
       </c>
       <c r="C1246">
-        <v>4639.7</v>
+        <v>5794</v>
       </c>
       <c r="D1246" t="s">
         <v>1248</v>
@@ -23314,7 +23602,7 @@
         <v>94</v>
       </c>
       <c r="C1247">
-        <v>4555.6</v>
+        <v>5634</v>
       </c>
       <c r="D1247" t="s">
         <v>1249</v>
@@ -23328,7 +23616,7 @@
         <v>95</v>
       </c>
       <c r="C1248">
-        <v>4530.6</v>
+        <v>5524</v>
       </c>
       <c r="D1248" t="s">
         <v>1250</v>
@@ -23342,7 +23630,7 @@
         <v>96</v>
       </c>
       <c r="C1249">
-        <v>4532.5</v>
+        <v>5414</v>
       </c>
       <c r="D1249" t="s">
         <v>1251</v>
@@ -23356,7 +23644,7 @@
         <v>1</v>
       </c>
       <c r="C1250">
-        <v>5360.8</v>
+        <v>5074</v>
       </c>
       <c r="D1250" t="s">
         <v>1252</v>
@@ -23370,7 +23658,7 @@
         <v>2</v>
       </c>
       <c r="C1251">
-        <v>5340</v>
+        <v>4974</v>
       </c>
       <c r="D1251" t="s">
         <v>1253</v>
@@ -23384,7 +23672,7 @@
         <v>3</v>
       </c>
       <c r="C1252">
-        <v>5306.7</v>
+        <v>4904</v>
       </c>
       <c r="D1252" t="s">
         <v>1254</v>
@@ -23398,7 +23686,7 @@
         <v>4</v>
       </c>
       <c r="C1253">
-        <v>5305.8</v>
+        <v>4844</v>
       </c>
       <c r="D1253" t="s">
         <v>1255</v>
@@ -23412,7 +23700,7 @@
         <v>5</v>
       </c>
       <c r="C1254">
-        <v>4527.2</v>
+        <v>4089</v>
       </c>
       <c r="D1254" t="s">
         <v>1256</v>
@@ -23426,7 +23714,7 @@
         <v>6</v>
       </c>
       <c r="C1255">
-        <v>4505.1</v>
+        <v>4061.3</v>
       </c>
       <c r="D1255" t="s">
         <v>1257</v>
@@ -23440,7 +23728,7 @@
         <v>7</v>
       </c>
       <c r="C1256">
-        <v>4482.3</v>
+        <v>4063.1</v>
       </c>
       <c r="D1256" t="s">
         <v>1258</v>
@@ -23454,7 +23742,7 @@
         <v>8</v>
       </c>
       <c r="C1257">
-        <v>4454.1</v>
+        <v>4015.6</v>
       </c>
       <c r="D1257" t="s">
         <v>1259</v>
@@ -23468,7 +23756,7 @@
         <v>9</v>
       </c>
       <c r="C1258">
-        <v>4209.9</v>
+        <v>3881.6</v>
       </c>
       <c r="D1258" t="s">
         <v>1260</v>
@@ -23482,7 +23770,7 @@
         <v>10</v>
       </c>
       <c r="C1259">
-        <v>4160.2</v>
+        <v>3860.1</v>
       </c>
       <c r="D1259" t="s">
         <v>1261</v>
@@ -23496,7 +23784,7 @@
         <v>11</v>
       </c>
       <c r="C1260">
-        <v>4132.8</v>
+        <v>3867.5</v>
       </c>
       <c r="D1260" t="s">
         <v>1262</v>
@@ -23510,7 +23798,7 @@
         <v>12</v>
       </c>
       <c r="C1261">
-        <v>4133</v>
+        <v>3894.2</v>
       </c>
       <c r="D1261" t="s">
         <v>1263</v>
@@ -23524,7 +23812,7 @@
         <v>13</v>
       </c>
       <c r="C1262">
-        <v>4070.6</v>
+        <v>3965.5</v>
       </c>
       <c r="D1262" t="s">
         <v>1264</v>
@@ -23538,7 +23826,7 @@
         <v>14</v>
       </c>
       <c r="C1263">
-        <v>4066.1</v>
+        <v>3925.3</v>
       </c>
       <c r="D1263" t="s">
         <v>1265</v>
@@ -23552,7 +23840,7 @@
         <v>15</v>
       </c>
       <c r="C1264">
-        <v>4051.2</v>
+        <v>3923.1</v>
       </c>
       <c r="D1264" t="s">
         <v>1266</v>
@@ -23566,7 +23854,7 @@
         <v>16</v>
       </c>
       <c r="C1265">
-        <v>4044.2</v>
+        <v>3936.9</v>
       </c>
       <c r="D1265" t="s">
         <v>1267</v>
@@ -23580,7 +23868,7 @@
         <v>17</v>
       </c>
       <c r="C1266">
-        <v>4035.2</v>
+        <v>3939.9</v>
       </c>
       <c r="D1266" t="s">
         <v>1268</v>
@@ -23594,7 +23882,7 @@
         <v>18</v>
       </c>
       <c r="C1267">
-        <v>4021.4</v>
+        <v>3940.4</v>
       </c>
       <c r="D1267" t="s">
         <v>1269</v>
@@ -23608,7 +23896,7 @@
         <v>19</v>
       </c>
       <c r="C1268">
-        <v>4010</v>
+        <v>3914.2</v>
       </c>
       <c r="D1268" t="s">
         <v>1270</v>
@@ -23622,7 +23910,7 @@
         <v>20</v>
       </c>
       <c r="C1269">
-        <v>4001.8</v>
+        <v>3926.6</v>
       </c>
       <c r="D1269" t="s">
         <v>1271</v>
@@ -23636,7 +23924,7 @@
         <v>21</v>
       </c>
       <c r="C1270">
-        <v>3956</v>
+        <v>3979.6</v>
       </c>
       <c r="D1270" t="s">
         <v>1272</v>
@@ -23650,7 +23938,7 @@
         <v>22</v>
       </c>
       <c r="C1271">
-        <v>3957.5</v>
+        <v>3940.5</v>
       </c>
       <c r="D1271" t="s">
         <v>1273</v>
@@ -23664,7 +23952,7 @@
         <v>23</v>
       </c>
       <c r="C1272">
-        <v>4009.4</v>
+        <v>3952.8</v>
       </c>
       <c r="D1272" t="s">
         <v>1274</v>
@@ -23678,7 +23966,7 @@
         <v>24</v>
       </c>
       <c r="C1273">
-        <v>4046</v>
+        <v>3973.9</v>
       </c>
       <c r="D1273" t="s">
         <v>1275</v>
@@ -23692,7 +23980,7 @@
         <v>25</v>
       </c>
       <c r="C1274">
-        <v>4137.6</v>
+        <v>4154.4</v>
       </c>
       <c r="D1274" t="s">
         <v>1276</v>
@@ -23706,7 +23994,7 @@
         <v>26</v>
       </c>
       <c r="C1275">
-        <v>4176.7</v>
+        <v>4201.4</v>
       </c>
       <c r="D1275" t="s">
         <v>1277</v>
@@ -23720,7 +24008,7 @@
         <v>27</v>
       </c>
       <c r="C1276">
-        <v>4240.5</v>
+        <v>4253.7</v>
       </c>
       <c r="D1276" t="s">
         <v>1278</v>
@@ -23734,7 +24022,7 @@
         <v>28</v>
       </c>
       <c r="C1277">
-        <v>4283.9</v>
+        <v>4330.7</v>
       </c>
       <c r="D1277" t="s">
         <v>1279</v>
@@ -23748,7 +24036,7 @@
         <v>29</v>
       </c>
       <c r="C1278">
-        <v>4521.7</v>
+        <v>4277.2</v>
       </c>
       <c r="D1278" t="s">
         <v>1280</v>
@@ -23762,7 +24050,7 @@
         <v>30</v>
       </c>
       <c r="C1279">
-        <v>4612.8</v>
+        <v>4349.3</v>
       </c>
       <c r="D1279" t="s">
         <v>1281</v>
@@ -23776,7 +24064,7 @@
         <v>31</v>
       </c>
       <c r="C1280">
-        <v>4765.2</v>
+        <v>4466.7</v>
       </c>
       <c r="D1280" t="s">
         <v>1282</v>
@@ -23790,7 +24078,7 @@
         <v>32</v>
       </c>
       <c r="C1281">
-        <v>4915.3</v>
+        <v>4559.8</v>
       </c>
       <c r="D1281" t="s">
         <v>1283</v>
@@ -23804,7 +24092,7 @@
         <v>33</v>
       </c>
       <c r="C1282">
-        <v>5048</v>
+        <v>4454.8</v>
       </c>
       <c r="D1282" t="s">
         <v>1284</v>
@@ -23818,7 +24106,7 @@
         <v>34</v>
       </c>
       <c r="C1283">
-        <v>5211.3</v>
+        <v>4559.1</v>
       </c>
       <c r="D1283" t="s">
         <v>1285</v>
@@ -23832,7 +24120,7 @@
         <v>35</v>
       </c>
       <c r="C1284">
-        <v>5415.2</v>
+        <v>4634.5</v>
       </c>
       <c r="D1284" t="s">
         <v>1286</v>
@@ -23846,7 +24134,7 @@
         <v>36</v>
       </c>
       <c r="C1285">
-        <v>5624.8</v>
+        <v>4699.1</v>
       </c>
       <c r="D1285" t="s">
         <v>1287</v>
@@ -23860,7 +24148,7 @@
         <v>37</v>
       </c>
       <c r="C1286">
-        <v>5598.9</v>
+        <v>4678.2</v>
       </c>
       <c r="D1286" t="s">
         <v>1288</v>
@@ -23874,7 +24162,7 @@
         <v>38</v>
       </c>
       <c r="C1287">
-        <v>5605.2</v>
+        <v>4715.1</v>
       </c>
       <c r="D1287" t="s">
         <v>1289</v>
@@ -23888,7 +24176,7 @@
         <v>39</v>
       </c>
       <c r="C1288">
-        <v>5700.3</v>
+        <v>4770.3</v>
       </c>
       <c r="D1288" t="s">
         <v>1290</v>
@@ -23902,7 +24190,7 @@
         <v>40</v>
       </c>
       <c r="C1289">
-        <v>5778.8</v>
+        <v>4848.9</v>
       </c>
       <c r="D1289" t="s">
         <v>1291</v>
@@ -23916,7 +24204,7 @@
         <v>41</v>
       </c>
       <c r="C1290">
-        <v>5763.6</v>
+        <v>4909.4</v>
       </c>
       <c r="D1290" t="s">
         <v>1292</v>
@@ -23930,7 +24218,7 @@
         <v>42</v>
       </c>
       <c r="C1291">
-        <v>5859.8</v>
+        <v>4946.4</v>
       </c>
       <c r="D1291" t="s">
         <v>1293</v>
@@ -23944,7 +24232,7 @@
         <v>43</v>
       </c>
       <c r="C1292">
-        <v>5923.2</v>
+        <v>4984.6</v>
       </c>
       <c r="D1292" t="s">
         <v>1294</v>
@@ -23958,7 +24246,7 @@
         <v>44</v>
       </c>
       <c r="C1293">
-        <v>6002.4</v>
+        <v>5016.4</v>
       </c>
       <c r="D1293" t="s">
         <v>1295</v>
@@ -23972,7 +24260,7 @@
         <v>45</v>
       </c>
       <c r="C1294">
-        <v>6063.1</v>
+        <v>5114.6</v>
       </c>
       <c r="D1294" t="s">
         <v>1296</v>
@@ -23986,7 +24274,7 @@
         <v>46</v>
       </c>
       <c r="C1295">
-        <v>6121.7</v>
+        <v>5118.2</v>
       </c>
       <c r="D1295" t="s">
         <v>1297</v>
@@ -24000,7 +24288,7 @@
         <v>47</v>
       </c>
       <c r="C1296">
-        <v>6198.4</v>
+        <v>5104.9</v>
       </c>
       <c r="D1296" t="s">
         <v>1298</v>
@@ -24014,7 +24302,7 @@
         <v>48</v>
       </c>
       <c r="C1297">
-        <v>6264</v>
+        <v>5111.8</v>
       </c>
       <c r="D1297" t="s">
         <v>1299</v>
@@ -24028,7 +24316,7 @@
         <v>49</v>
       </c>
       <c r="C1298">
-        <v>6220.7</v>
+        <v>4809</v>
       </c>
       <c r="D1298" t="s">
         <v>1300</v>
@@ -24042,7 +24330,7 @@
         <v>50</v>
       </c>
       <c r="C1299">
-        <v>6257.8</v>
+        <v>4790</v>
       </c>
       <c r="D1299" t="s">
         <v>1301</v>
@@ -24056,7 +24344,7 @@
         <v>51</v>
       </c>
       <c r="C1300">
-        <v>6277.6</v>
+        <v>4745.6</v>
       </c>
       <c r="D1300" t="s">
         <v>1302</v>
@@ -24070,7 +24358,7 @@
         <v>52</v>
       </c>
       <c r="C1301">
-        <v>6300.2</v>
+        <v>4720</v>
       </c>
       <c r="D1301" t="s">
         <v>1303</v>
@@ -24084,7 +24372,7 @@
         <v>53</v>
       </c>
       <c r="C1302">
-        <v>6259.8</v>
+        <v>4486.5</v>
       </c>
       <c r="D1302" t="s">
         <v>1304</v>
@@ -24098,7 +24386,7 @@
         <v>54</v>
       </c>
       <c r="C1303">
-        <v>6287.4</v>
+        <v>4456.6</v>
       </c>
       <c r="D1303" t="s">
         <v>1305</v>
@@ -24112,7 +24400,7 @@
         <v>55</v>
       </c>
       <c r="C1304">
-        <v>6280.6</v>
+        <v>4473.2</v>
       </c>
       <c r="D1304" t="s">
         <v>1306</v>
@@ -24126,7 +24414,7 @@
         <v>56</v>
       </c>
       <c r="C1305">
-        <v>6312.3</v>
+        <v>4477.2</v>
       </c>
       <c r="D1305" t="s">
         <v>1307</v>
@@ -24140,7 +24428,7 @@
         <v>57</v>
       </c>
       <c r="C1306">
-        <v>6355.8</v>
+        <v>4516.7</v>
       </c>
       <c r="D1306" t="s">
         <v>1308</v>
@@ -24154,7 +24442,7 @@
         <v>58</v>
       </c>
       <c r="C1307">
-        <v>6362</v>
+        <v>4499.9</v>
       </c>
       <c r="D1307" t="s">
         <v>1309</v>
@@ -24168,7 +24456,7 @@
         <v>59</v>
       </c>
       <c r="C1308">
-        <v>6363.3</v>
+        <v>4488.4</v>
       </c>
       <c r="D1308" t="s">
         <v>1310</v>
@@ -24182,7 +24470,7 @@
         <v>60</v>
       </c>
       <c r="C1309">
-        <v>6362.9</v>
+        <v>4496</v>
       </c>
       <c r="D1309" t="s">
         <v>1311</v>
@@ -24196,7 +24484,7 @@
         <v>61</v>
       </c>
       <c r="C1310">
-        <v>6281.5</v>
+        <v>4472.8</v>
       </c>
       <c r="D1310" t="s">
         <v>1312</v>
@@ -24210,7 +24498,7 @@
         <v>62</v>
       </c>
       <c r="C1311">
-        <v>6240.1</v>
+        <v>4460.4</v>
       </c>
       <c r="D1311" t="s">
         <v>1313</v>
@@ -24224,7 +24512,7 @@
         <v>63</v>
       </c>
       <c r="C1312">
-        <v>6195.8</v>
+        <v>4441.3</v>
       </c>
       <c r="D1312" t="s">
         <v>1314</v>
@@ -24238,7 +24526,7 @@
         <v>64</v>
       </c>
       <c r="C1313">
-        <v>6172.4</v>
+        <v>4431.8</v>
       </c>
       <c r="D1313" t="s">
         <v>1315</v>
@@ -24252,7 +24540,7 @@
         <v>65</v>
       </c>
       <c r="C1314">
-        <v>6361.3</v>
+        <v>4493.4</v>
       </c>
       <c r="D1314" t="s">
         <v>1316</v>
@@ -24266,7 +24554,7 @@
         <v>66</v>
       </c>
       <c r="C1315">
-        <v>6289.8</v>
+        <v>4444.7</v>
       </c>
       <c r="D1315" t="s">
         <v>1317</v>
@@ -24280,7 +24568,7 @@
         <v>67</v>
       </c>
       <c r="C1316">
-        <v>6241.4</v>
+        <v>4415.2</v>
       </c>
       <c r="D1316" t="s">
         <v>1318</v>
@@ -24294,7 +24582,7 @@
         <v>68</v>
       </c>
       <c r="C1317">
-        <v>6182.2</v>
+        <v>4370.7</v>
       </c>
       <c r="D1317" t="s">
         <v>1319</v>
@@ -24308,7 +24596,7 @@
         <v>69</v>
       </c>
       <c r="C1318">
-        <v>6263.8</v>
+        <v>4614.6</v>
       </c>
       <c r="D1318" t="s">
         <v>1320</v>
@@ -24322,7 +24610,7 @@
         <v>70</v>
       </c>
       <c r="C1319">
-        <v>6164.8</v>
+        <v>4506.9</v>
       </c>
       <c r="D1319" t="s">
         <v>1321</v>
@@ -24336,7 +24624,7 @@
         <v>71</v>
       </c>
       <c r="C1320">
-        <v>6041.9</v>
+        <v>4430.8</v>
       </c>
       <c r="D1320" t="s">
         <v>1322</v>
@@ -24350,7 +24638,7 @@
         <v>72</v>
       </c>
       <c r="C1321">
-        <v>5923</v>
+        <v>4358.5</v>
       </c>
       <c r="D1321" t="s">
         <v>1323</v>
@@ -24364,7 +24652,7 @@
         <v>73</v>
       </c>
       <c r="C1322">
-        <v>6228.4</v>
+        <v>4591.9</v>
       </c>
       <c r="D1322" t="s">
         <v>1324</v>
@@ -24378,7 +24666,7 @@
         <v>74</v>
       </c>
       <c r="C1323">
-        <v>6113.5</v>
+        <v>4510.2</v>
       </c>
       <c r="D1323" t="s">
         <v>1325</v>
@@ -24392,7 +24680,7 @@
         <v>75</v>
       </c>
       <c r="C1324">
-        <v>5979.6</v>
+        <v>4434.6</v>
       </c>
       <c r="D1324" t="s">
         <v>1326</v>
@@ -24406,7 +24694,7 @@
         <v>76</v>
       </c>
       <c r="C1325">
-        <v>5852.3</v>
+        <v>4347.8</v>
       </c>
       <c r="D1325" t="s">
         <v>1327</v>
@@ -24420,7 +24708,7 @@
         <v>77</v>
       </c>
       <c r="C1326">
-        <v>5684.4</v>
+        <v>4405.7</v>
       </c>
       <c r="D1326" t="s">
         <v>1328</v>
@@ -24434,7 +24722,7 @@
         <v>78</v>
       </c>
       <c r="C1327">
-        <v>5623.7</v>
+        <v>4384.3</v>
       </c>
       <c r="D1327" t="s">
         <v>1329</v>
@@ -24448,7 +24736,7 @@
         <v>79</v>
       </c>
       <c r="C1328">
-        <v>5568</v>
+        <v>4335</v>
       </c>
       <c r="D1328" t="s">
         <v>1330</v>
@@ -24462,7 +24750,7 @@
         <v>80</v>
       </c>
       <c r="C1329">
-        <v>5511.4</v>
+        <v>4330.2</v>
       </c>
       <c r="D1329" t="s">
         <v>1331</v>
@@ -24476,7 +24764,7 @@
         <v>81</v>
       </c>
       <c r="C1330">
-        <v>5839.2</v>
+        <v>4474.3</v>
       </c>
       <c r="D1330" t="s">
         <v>1332</v>
@@ -24490,7 +24778,7 @@
         <v>82</v>
       </c>
       <c r="C1331">
-        <v>5855.4</v>
+        <v>4496.2</v>
       </c>
       <c r="D1331" t="s">
         <v>1333</v>
@@ -24504,7 +24792,7 @@
         <v>83</v>
       </c>
       <c r="C1332">
-        <v>5835.5</v>
+        <v>4496.7</v>
       </c>
       <c r="D1332" t="s">
         <v>1334</v>
@@ -24518,7 +24806,7 @@
         <v>84</v>
       </c>
       <c r="C1333">
-        <v>5900.6</v>
+        <v>4545.1</v>
       </c>
       <c r="D1333" t="s">
         <v>1335</v>
@@ -24532,7 +24820,7 @@
         <v>85</v>
       </c>
       <c r="C1334">
-        <v>5967.6</v>
+        <v>4642</v>
       </c>
       <c r="D1334" t="s">
         <v>1336</v>
@@ -24546,7 +24834,7 @@
         <v>86</v>
       </c>
       <c r="C1335">
-        <v>5950.9</v>
+        <v>4624.5</v>
       </c>
       <c r="D1335" t="s">
         <v>1337</v>
@@ -24560,7 +24848,7 @@
         <v>87</v>
       </c>
       <c r="C1336">
-        <v>5967.6</v>
+        <v>4667.7</v>
       </c>
       <c r="D1336" t="s">
         <v>1338</v>
@@ -24574,7 +24862,7 @@
         <v>88</v>
       </c>
       <c r="C1337">
-        <v>5913.5</v>
+        <v>4692.2</v>
       </c>
       <c r="D1337" t="s">
         <v>1339</v>
@@ -24588,7 +24876,7 @@
         <v>89</v>
       </c>
       <c r="C1338">
-        <v>5619</v>
+        <v>4675.6</v>
       </c>
       <c r="D1338" t="s">
         <v>1340</v>
@@ -24602,7 +24890,7 @@
         <v>90</v>
       </c>
       <c r="C1339">
-        <v>5590.2</v>
+        <v>4568.7</v>
       </c>
       <c r="D1339" t="s">
         <v>1341</v>
@@ -24616,7 +24904,7 @@
         <v>91</v>
       </c>
       <c r="C1340">
-        <v>5602.3</v>
+        <v>4483.4</v>
       </c>
       <c r="D1340" t="s">
         <v>1342</v>
@@ -24630,7 +24918,7 @@
         <v>92</v>
       </c>
       <c r="C1341">
-        <v>5519.6</v>
+        <v>4439.4</v>
       </c>
       <c r="D1341" t="s">
         <v>1343</v>
@@ -24644,7 +24932,7 @@
         <v>93</v>
       </c>
       <c r="C1342">
-        <v>5423.6</v>
+        <v>3967.4</v>
       </c>
       <c r="D1342" t="s">
         <v>1344</v>
@@ -24658,7 +24946,7 @@
         <v>94</v>
       </c>
       <c r="C1343">
-        <v>5355.8</v>
+        <v>3894.4</v>
       </c>
       <c r="D1343" t="s">
         <v>1345</v>
@@ -24672,7 +24960,7 @@
         <v>95</v>
       </c>
       <c r="C1344">
-        <v>5354.5</v>
+        <v>3847</v>
       </c>
       <c r="D1344" t="s">
         <v>1346</v>
@@ -24686,7 +24974,7 @@
         <v>96</v>
       </c>
       <c r="C1345">
-        <v>5309.3</v>
+        <v>3856.4</v>
       </c>
       <c r="D1345" t="s">
         <v>1347</v>
@@ -24700,7 +24988,7 @@
         <v>1</v>
       </c>
       <c r="C1346">
-        <v>5350.8</v>
+        <v>5104</v>
       </c>
       <c r="D1346" t="s">
         <v>1348</v>
@@ -24714,7 +25002,7 @@
         <v>2</v>
       </c>
       <c r="C1347">
-        <v>5340</v>
+        <v>5064</v>
       </c>
       <c r="D1347" t="s">
         <v>1349</v>
@@ -24728,7 +25016,7 @@
         <v>3</v>
       </c>
       <c r="C1348">
-        <v>5296.7</v>
+        <v>5004</v>
       </c>
       <c r="D1348" t="s">
         <v>1350</v>
@@ -24742,7 +25030,7 @@
         <v>4</v>
       </c>
       <c r="C1349">
-        <v>5285.8</v>
+        <v>4934</v>
       </c>
       <c r="D1349" t="s">
         <v>1351</v>
@@ -24756,7 +25044,7 @@
         <v>5</v>
       </c>
       <c r="C1350">
-        <v>4517.2</v>
+        <v>4179</v>
       </c>
       <c r="D1350" t="s">
         <v>1352</v>
@@ -24770,7 +25058,7 @@
         <v>6</v>
       </c>
       <c r="C1351">
-        <v>4485.1</v>
+        <v>4151.3</v>
       </c>
       <c r="D1351" t="s">
         <v>1353</v>
@@ -24784,7 +25072,7 @@
         <v>7</v>
       </c>
       <c r="C1352">
-        <v>4462.3</v>
+        <v>4113.1</v>
       </c>
       <c r="D1352" t="s">
         <v>1354</v>
@@ -24798,7 +25086,7 @@
         <v>8</v>
       </c>
       <c r="C1353">
-        <v>4444.1</v>
+        <v>4055.6</v>
       </c>
       <c r="D1353" t="s">
         <v>1355</v>
@@ -24812,7 +25100,7 @@
         <v>9</v>
       </c>
       <c r="C1354">
-        <v>4199.9</v>
+        <v>3891.6</v>
       </c>
       <c r="D1354" t="s">
         <v>1356</v>
@@ -24826,7 +25114,7 @@
         <v>10</v>
       </c>
       <c r="C1355">
-        <v>4160.2</v>
+        <v>3850.1</v>
       </c>
       <c r="D1355" t="s">
         <v>1357</v>
@@ -24840,7 +25128,7 @@
         <v>11</v>
       </c>
       <c r="C1356">
-        <v>4142.8</v>
+        <v>3837.5</v>
       </c>
       <c r="D1356" t="s">
         <v>1358</v>
@@ -24854,7 +25142,7 @@
         <v>12</v>
       </c>
       <c r="C1357">
-        <v>4143</v>
+        <v>3864.2</v>
       </c>
       <c r="D1357" t="s">
         <v>1359</v>
@@ -24868,7 +25156,7 @@
         <v>13</v>
       </c>
       <c r="C1358">
-        <v>4080.6</v>
+        <v>3935.5</v>
       </c>
       <c r="D1358" t="s">
         <v>1360</v>
@@ -24882,7 +25170,7 @@
         <v>14</v>
       </c>
       <c r="C1359">
-        <v>4066.1</v>
+        <v>3925.3</v>
       </c>
       <c r="D1359" t="s">
         <v>1361</v>
@@ -24896,7 +25184,7 @@
         <v>15</v>
       </c>
       <c r="C1360">
-        <v>4051.2</v>
+        <v>3933.1</v>
       </c>
       <c r="D1360" t="s">
         <v>1362</v>
@@ -24910,7 +25198,7 @@
         <v>16</v>
       </c>
       <c r="C1361">
-        <v>4034.2</v>
+        <v>3936.9</v>
       </c>
       <c r="D1361" t="s">
         <v>1363</v>
@@ -24924,7 +25212,7 @@
         <v>17</v>
       </c>
       <c r="C1362">
-        <v>4035.2</v>
+        <v>3919.9</v>
       </c>
       <c r="D1362" t="s">
         <v>1364</v>
@@ -24938,7 +25226,7 @@
         <v>18</v>
       </c>
       <c r="C1363">
-        <v>4011.4</v>
+        <v>3920.4</v>
       </c>
       <c r="D1363" t="s">
         <v>1365</v>
@@ -24952,7 +25240,7 @@
         <v>19</v>
       </c>
       <c r="C1364">
-        <v>4010</v>
+        <v>3914.2</v>
       </c>
       <c r="D1364" t="s">
         <v>1366</v>
@@ -24966,7 +25254,7 @@
         <v>20</v>
       </c>
       <c r="C1365">
-        <v>4001.8</v>
+        <v>3916.6</v>
       </c>
       <c r="D1365" t="s">
         <v>1367</v>
@@ -24980,7 +25268,7 @@
         <v>21</v>
       </c>
       <c r="C1366">
-        <v>3966</v>
+        <v>3999.6</v>
       </c>
       <c r="D1366" t="s">
         <v>1368</v>
@@ -24994,7 +25282,7 @@
         <v>22</v>
       </c>
       <c r="C1367">
-        <v>3967.5</v>
+        <v>4000.5</v>
       </c>
       <c r="D1367" t="s">
         <v>1369</v>
@@ -25008,7 +25296,7 @@
         <v>23</v>
       </c>
       <c r="C1368">
-        <v>4009.4</v>
+        <v>4052.8</v>
       </c>
       <c r="D1368" t="s">
         <v>1370</v>
@@ -25022,7 +25310,7 @@
         <v>24</v>
       </c>
       <c r="C1369">
-        <v>4026</v>
+        <v>4093.9</v>
       </c>
       <c r="D1369" t="s">
         <v>1371</v>
@@ -25036,7 +25324,7 @@
         <v>25</v>
       </c>
       <c r="C1370">
-        <v>4097.6</v>
+        <v>4274.4</v>
       </c>
       <c r="D1370" t="s">
         <v>1372</v>
@@ -25050,7 +25338,7 @@
         <v>26</v>
       </c>
       <c r="C1371">
-        <v>4116.7</v>
+        <v>4341.4</v>
       </c>
       <c r="D1371" t="s">
         <v>1373</v>
@@ -25064,7 +25352,7 @@
         <v>27</v>
       </c>
       <c r="C1372">
-        <v>4150.5</v>
+        <v>4373.7</v>
       </c>
       <c r="D1372" t="s">
         <v>1374</v>
@@ -25078,7 +25366,7 @@
         <v>28</v>
       </c>
       <c r="C1373">
-        <v>4173.9</v>
+        <v>4400.7</v>
       </c>
       <c r="D1373" t="s">
         <v>1375</v>
@@ -25092,7 +25380,7 @@
         <v>29</v>
       </c>
       <c r="C1374">
-        <v>4391.7</v>
+        <v>4267.2</v>
       </c>
       <c r="D1374" t="s">
         <v>1376</v>
@@ -25106,7 +25394,7 @@
         <v>30</v>
       </c>
       <c r="C1375">
-        <v>4462.8</v>
+        <v>4269.3</v>
       </c>
       <c r="D1375" t="s">
         <v>1377</v>
@@ -25120,7 +25408,7 @@
         <v>31</v>
       </c>
       <c r="C1376">
-        <v>4605.2</v>
+        <v>4346.7</v>
       </c>
       <c r="D1376" t="s">
         <v>1378</v>
@@ -25134,7 +25422,7 @@
         <v>32</v>
       </c>
       <c r="C1377">
-        <v>4735.3</v>
+        <v>4439.8</v>
       </c>
       <c r="D1377" t="s">
         <v>1379</v>
@@ -25148,7 +25436,7 @@
         <v>33</v>
       </c>
       <c r="C1378">
-        <v>4868</v>
+        <v>4284.8</v>
       </c>
       <c r="D1378" t="s">
         <v>1380</v>
@@ -25162,7 +25450,7 @@
         <v>34</v>
       </c>
       <c r="C1379">
-        <v>5031.3</v>
+        <v>4359.1</v>
       </c>
       <c r="D1379" t="s">
         <v>1381</v>
@@ -25176,7 +25464,7 @@
         <v>35</v>
       </c>
       <c r="C1380">
-        <v>5225.2</v>
+        <v>4424.5</v>
       </c>
       <c r="D1380" t="s">
         <v>1382</v>
@@ -25190,7 +25478,7 @@
         <v>36</v>
       </c>
       <c r="C1381">
-        <v>5444.8</v>
+        <v>4519.1</v>
       </c>
       <c r="D1381" t="s">
         <v>1383</v>
@@ -25204,7 +25492,7 @@
         <v>37</v>
       </c>
       <c r="C1382">
-        <v>5418.9</v>
+        <v>4528.2</v>
       </c>
       <c r="D1382" t="s">
         <v>1384</v>
@@ -25218,7 +25506,7 @@
         <v>38</v>
       </c>
       <c r="C1383">
-        <v>5425.2</v>
+        <v>4575.1</v>
       </c>
       <c r="D1383" t="s">
         <v>1385</v>
@@ -25232,7 +25520,7 @@
         <v>39</v>
       </c>
       <c r="C1384">
-        <v>5520.3</v>
+        <v>4660.3</v>
       </c>
       <c r="D1384" t="s">
         <v>1386</v>
@@ -25246,7 +25534,7 @@
         <v>40</v>
       </c>
       <c r="C1385">
-        <v>5598.8</v>
+        <v>4788.9</v>
       </c>
       <c r="D1385" t="s">
         <v>1387</v>
@@ -25260,7 +25548,7 @@
         <v>41</v>
       </c>
       <c r="C1386">
-        <v>5583.6</v>
+        <v>4869.4</v>
       </c>
       <c r="D1386" t="s">
         <v>1388</v>
@@ -25274,7 +25562,7 @@
         <v>42</v>
       </c>
       <c r="C1387">
-        <v>5669.8</v>
+        <v>4936.4</v>
       </c>
       <c r="D1387" t="s">
         <v>1389</v>
@@ -25288,7 +25576,7 @@
         <v>43</v>
       </c>
       <c r="C1388">
-        <v>5743.2</v>
+        <v>5004.6</v>
       </c>
       <c r="D1388" t="s">
         <v>1390</v>
@@ -25302,7 +25590,7 @@
         <v>44</v>
       </c>
       <c r="C1389">
-        <v>5822.4</v>
+        <v>5076.4</v>
       </c>
       <c r="D1389" t="s">
         <v>1391</v>
@@ -25316,7 +25604,7 @@
         <v>45</v>
       </c>
       <c r="C1390">
-        <v>5893.1</v>
+        <v>5224.6</v>
       </c>
       <c r="D1390" t="s">
         <v>1392</v>
@@ -25330,7 +25618,7 @@
         <v>46</v>
       </c>
       <c r="C1391">
-        <v>5961.7</v>
+        <v>5248.2</v>
       </c>
       <c r="D1391" t="s">
         <v>1393</v>
@@ -25344,7 +25632,7 @@
         <v>47</v>
       </c>
       <c r="C1392">
-        <v>6048.4</v>
+        <v>5234.9</v>
       </c>
       <c r="D1392" t="s">
         <v>1394</v>
@@ -25358,7 +25646,7 @@
         <v>48</v>
       </c>
       <c r="C1393">
-        <v>6124</v>
+        <v>5241.8</v>
       </c>
       <c r="D1393" t="s">
         <v>1395</v>
@@ -25372,7 +25660,7 @@
         <v>49</v>
       </c>
       <c r="C1394">
-        <v>6080.7</v>
+        <v>4959</v>
       </c>
       <c r="D1394" t="s">
         <v>1396</v>
@@ -25386,7 +25674,7 @@
         <v>50</v>
       </c>
       <c r="C1395">
-        <v>6117.8</v>
+        <v>4930</v>
       </c>
       <c r="D1395" t="s">
         <v>1397</v>
@@ -25400,7 +25688,7 @@
         <v>51</v>
       </c>
       <c r="C1396">
-        <v>6127.6</v>
+        <v>4865.6</v>
       </c>
       <c r="D1396" t="s">
         <v>1398</v>
@@ -25414,7 +25702,7 @@
         <v>52</v>
       </c>
       <c r="C1397">
-        <v>6140.2</v>
+        <v>4820</v>
       </c>
       <c r="D1397" t="s">
         <v>1399</v>
@@ -25428,7 +25716,7 @@
         <v>53</v>
       </c>
       <c r="C1398">
-        <v>6079.8</v>
+        <v>4546.5</v>
       </c>
       <c r="D1398" t="s">
         <v>1400</v>
@@ -25442,7 +25730,7 @@
         <v>54</v>
       </c>
       <c r="C1399">
-        <v>6077.4</v>
+        <v>4496.6</v>
       </c>
       <c r="D1399" t="s">
         <v>1401</v>
@@ -25456,7 +25744,7 @@
         <v>55</v>
       </c>
       <c r="C1400">
-        <v>6060.6</v>
+        <v>4493.2</v>
       </c>
       <c r="D1400" t="s">
         <v>1402</v>
@@ -25470,7 +25758,7 @@
         <v>56</v>
       </c>
       <c r="C1401">
-        <v>6072.3</v>
+        <v>4497.2</v>
       </c>
       <c r="D1401" t="s">
         <v>1403</v>
@@ -25484,7 +25772,7 @@
         <v>57</v>
       </c>
       <c r="C1402">
-        <v>6095.8</v>
+        <v>4526.7</v>
       </c>
       <c r="D1402" t="s">
         <v>1404</v>
@@ -25498,7 +25786,7 @@
         <v>58</v>
       </c>
       <c r="C1403">
-        <v>6092</v>
+        <v>4519.9</v>
       </c>
       <c r="D1403" t="s">
         <v>1405</v>
@@ -25512,7 +25800,7 @@
         <v>59</v>
       </c>
       <c r="C1404">
-        <v>6093.3</v>
+        <v>4528.4</v>
       </c>
       <c r="D1404" t="s">
         <v>1406</v>
@@ -25526,7 +25814,7 @@
         <v>60</v>
       </c>
       <c r="C1405">
-        <v>6112.9</v>
+        <v>4556</v>
       </c>
       <c r="D1405" t="s">
         <v>1407</v>
@@ -25540,7 +25828,7 @@
         <v>61</v>
       </c>
       <c r="C1406">
-        <v>6041.5</v>
+        <v>4532.8</v>
       </c>
       <c r="D1406" t="s">
         <v>1408</v>
@@ -25554,7 +25842,7 @@
         <v>62</v>
       </c>
       <c r="C1407">
-        <v>6030.1</v>
+        <v>4530.4</v>
       </c>
       <c r="D1407" t="s">
         <v>1409</v>
@@ -25568,7 +25856,7 @@
         <v>63</v>
       </c>
       <c r="C1408">
-        <v>6015.8</v>
+        <v>4531.3</v>
       </c>
       <c r="D1408" t="s">
         <v>1410</v>
@@ -25582,7 +25870,7 @@
         <v>64</v>
       </c>
       <c r="C1409">
-        <v>6002.4</v>
+        <v>4531.8</v>
       </c>
       <c r="D1409" t="s">
         <v>1411</v>
@@ -25596,7 +25884,7 @@
         <v>65</v>
       </c>
       <c r="C1410">
-        <v>6211.3</v>
+        <v>4603.4</v>
       </c>
       <c r="D1410" t="s">
         <v>1412</v>
@@ -25610,7 +25898,7 @@
         <v>66</v>
       </c>
       <c r="C1411">
-        <v>6149.8</v>
+        <v>4564.7</v>
       </c>
       <c r="D1411" t="s">
         <v>1413</v>
@@ -25624,7 +25912,7 @@
         <v>67</v>
       </c>
       <c r="C1412">
-        <v>6111.4</v>
+        <v>4525.2</v>
       </c>
       <c r="D1412" t="s">
         <v>1414</v>
@@ -25638,7 +25926,7 @@
         <v>68</v>
       </c>
       <c r="C1413">
-        <v>6062.2</v>
+        <v>4500.7</v>
       </c>
       <c r="D1413" t="s">
         <v>1415</v>
@@ -25652,7 +25940,7 @@
         <v>69</v>
       </c>
       <c r="C1414">
-        <v>6153.8</v>
+        <v>4754.6</v>
       </c>
       <c r="D1414" t="s">
         <v>1416</v>
@@ -25666,7 +25954,7 @@
         <v>70</v>
       </c>
       <c r="C1415">
-        <v>6054.8</v>
+        <v>4666.9</v>
       </c>
       <c r="D1415" t="s">
         <v>1417</v>
@@ -25680,7 +25968,7 @@
         <v>71</v>
       </c>
       <c r="C1416">
-        <v>5921.9</v>
+        <v>4590.8</v>
       </c>
       <c r="D1416" t="s">
         <v>1418</v>
@@ -25694,7 +25982,7 @@
         <v>72</v>
       </c>
       <c r="C1417">
-        <v>5793</v>
+        <v>4498.5</v>
       </c>
       <c r="D1417" t="s">
         <v>1419</v>
@@ -25708,7 +25996,7 @@
         <v>73</v>
       </c>
       <c r="C1418">
-        <v>6098.4</v>
+        <v>4701.9</v>
       </c>
       <c r="D1418" t="s">
         <v>1420</v>
@@ -25722,7 +26010,7 @@
         <v>74</v>
       </c>
       <c r="C1419">
-        <v>5983.5</v>
+        <v>4580.2</v>
       </c>
       <c r="D1419" t="s">
         <v>1421</v>
@@ -25736,7 +26024,7 @@
         <v>75</v>
       </c>
       <c r="C1420">
-        <v>5859.6</v>
+        <v>4484.6</v>
       </c>
       <c r="D1420" t="s">
         <v>1422</v>
@@ -25750,7 +26038,7 @@
         <v>76</v>
       </c>
       <c r="C1421">
-        <v>5732.3</v>
+        <v>4387.8</v>
       </c>
       <c r="D1421" t="s">
         <v>1423</v>
@@ -25764,7 +26052,7 @@
         <v>77</v>
       </c>
       <c r="C1422">
-        <v>5574.4</v>
+        <v>4425.7</v>
       </c>
       <c r="D1422" t="s">
         <v>1424</v>
@@ -25778,7 +26066,7 @@
         <v>78</v>
       </c>
       <c r="C1423">
-        <v>5523.7</v>
+        <v>4394.3</v>
       </c>
       <c r="D1423" t="s">
         <v>1425</v>
@@ -25792,7 +26080,7 @@
         <v>79</v>
       </c>
       <c r="C1424">
-        <v>5468</v>
+        <v>4335</v>
       </c>
       <c r="D1424" t="s">
         <v>1426</v>
@@ -25806,7 +26094,7 @@
         <v>80</v>
       </c>
       <c r="C1425">
-        <v>5411.4</v>
+        <v>4290.2</v>
       </c>
       <c r="D1425" t="s">
         <v>1427</v>
@@ -25820,7 +26108,7 @@
         <v>81</v>
       </c>
       <c r="C1426">
-        <v>5749.2</v>
+        <v>4444.3</v>
       </c>
       <c r="D1426" t="s">
         <v>1428</v>
@@ -25834,7 +26122,7 @@
         <v>82</v>
       </c>
       <c r="C1427">
-        <v>5755.4</v>
+        <v>4436.2</v>
       </c>
       <c r="D1427" t="s">
         <v>1429</v>
@@ -25848,7 +26136,7 @@
         <v>83</v>
       </c>
       <c r="C1428">
-        <v>5735.5</v>
+        <v>4426.7</v>
       </c>
       <c r="D1428" t="s">
         <v>1430</v>
@@ -25862,7 +26150,7 @@
         <v>84</v>
       </c>
       <c r="C1429">
-        <v>5800.6</v>
+        <v>4415.1</v>
       </c>
       <c r="D1429" t="s">
         <v>1431</v>
@@ -25876,7 +26164,7 @@
         <v>85</v>
       </c>
       <c r="C1430">
-        <v>5867.6</v>
+        <v>4452</v>
       </c>
       <c r="D1430" t="s">
         <v>1432</v>
@@ -25890,7 +26178,7 @@
         <v>86</v>
       </c>
       <c r="C1431">
-        <v>5850.9</v>
+        <v>4434.5</v>
       </c>
       <c r="D1431" t="s">
         <v>1433</v>
@@ -25904,7 +26192,7 @@
         <v>87</v>
       </c>
       <c r="C1432">
-        <v>5867.6</v>
+        <v>4457.7</v>
       </c>
       <c r="D1432" t="s">
         <v>1434</v>
@@ -25918,7 +26206,7 @@
         <v>88</v>
       </c>
       <c r="C1433">
-        <v>5813.5</v>
+        <v>4472.2</v>
       </c>
       <c r="D1433" t="s">
         <v>1435</v>
@@ -25932,7 +26220,7 @@
         <v>89</v>
       </c>
       <c r="C1434">
-        <v>5519</v>
+        <v>4475.6</v>
       </c>
       <c r="D1434" t="s">
         <v>1436</v>
@@ -25946,7 +26234,7 @@
         <v>90</v>
       </c>
       <c r="C1435">
-        <v>5490.2</v>
+        <v>4478.7</v>
       </c>
       <c r="D1435" t="s">
         <v>1437</v>
@@ -25960,7 +26248,7 @@
         <v>91</v>
       </c>
       <c r="C1436">
-        <v>5502.3</v>
+        <v>4403.4</v>
       </c>
       <c r="D1436" t="s">
         <v>1438</v>
@@ -25974,7 +26262,7 @@
         <v>92</v>
       </c>
       <c r="C1437">
-        <v>5429.6</v>
+        <v>4409.4</v>
       </c>
       <c r="D1437" t="s">
         <v>1439</v>
@@ -25988,7 +26276,7 @@
         <v>93</v>
       </c>
       <c r="C1438">
-        <v>5333.6</v>
+        <v>3917.4</v>
       </c>
       <c r="D1438" t="s">
         <v>1440</v>
@@ -26002,7 +26290,7 @@
         <v>94</v>
       </c>
       <c r="C1439">
-        <v>5265.8</v>
+        <v>3824.4</v>
       </c>
       <c r="D1439" t="s">
         <v>1441</v>
@@ -26016,7 +26304,7 @@
         <v>95</v>
       </c>
       <c r="C1440">
-        <v>5254.5</v>
+        <v>3797</v>
       </c>
       <c r="D1440" t="s">
         <v>1442</v>
@@ -26030,7 +26318,7 @@
         <v>96</v>
       </c>
       <c r="C1441">
-        <v>5209.3</v>
+        <v>3816.4</v>
       </c>
       <c r="D1441" t="s">
         <v>1443</v>
@@ -31410,6 +31698,1350 @@
       </c>
       <c r="D1825" t="s">
         <v>1827</v>
+      </c>
+    </row>
+    <row r="1826" spans="1:4">
+      <c r="A1826" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1826">
+        <v>1</v>
+      </c>
+      <c r="C1826">
+        <v>5736</v>
+      </c>
+      <c r="D1826" t="s">
+        <v>1828</v>
+      </c>
+    </row>
+    <row r="1827" spans="1:4">
+      <c r="A1827" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1827">
+        <v>2</v>
+      </c>
+      <c r="C1827">
+        <v>5726.2</v>
+      </c>
+      <c r="D1827" t="s">
+        <v>1829</v>
+      </c>
+    </row>
+    <row r="1828" spans="1:4">
+      <c r="A1828" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1828">
+        <v>3</v>
+      </c>
+      <c r="C1828">
+        <v>5619.7</v>
+      </c>
+      <c r="D1828" t="s">
+        <v>1830</v>
+      </c>
+    </row>
+    <row r="1829" spans="1:4">
+      <c r="A1829" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1829">
+        <v>4</v>
+      </c>
+      <c r="C1829">
+        <v>5487.7</v>
+      </c>
+      <c r="D1829" t="s">
+        <v>1831</v>
+      </c>
+    </row>
+    <row r="1830" spans="1:4">
+      <c r="A1830" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1830">
+        <v>5</v>
+      </c>
+      <c r="C1830">
+        <v>5023.4</v>
+      </c>
+      <c r="D1830" t="s">
+        <v>1832</v>
+      </c>
+    </row>
+    <row r="1831" spans="1:4">
+      <c r="A1831" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1831">
+        <v>6</v>
+      </c>
+      <c r="C1831">
+        <v>4978.2</v>
+      </c>
+      <c r="D1831" t="s">
+        <v>1833</v>
+      </c>
+    </row>
+    <row r="1832" spans="1:4">
+      <c r="A1832" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1832">
+        <v>7</v>
+      </c>
+      <c r="C1832">
+        <v>4929.8</v>
+      </c>
+      <c r="D1832" t="s">
+        <v>1834</v>
+      </c>
+    </row>
+    <row r="1833" spans="1:4">
+      <c r="A1833" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1833">
+        <v>8</v>
+      </c>
+      <c r="C1833">
+        <v>4884.3</v>
+      </c>
+      <c r="D1833" t="s">
+        <v>1835</v>
+      </c>
+    </row>
+    <row r="1834" spans="1:4">
+      <c r="A1834" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1834">
+        <v>9</v>
+      </c>
+      <c r="C1834">
+        <v>4595.1</v>
+      </c>
+      <c r="D1834" t="s">
+        <v>1836</v>
+      </c>
+    </row>
+    <row r="1835" spans="1:4">
+      <c r="A1835" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1835">
+        <v>10</v>
+      </c>
+      <c r="C1835">
+        <v>4564.8</v>
+      </c>
+      <c r="D1835" t="s">
+        <v>1837</v>
+      </c>
+    </row>
+    <row r="1836" spans="1:4">
+      <c r="A1836" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1836">
+        <v>11</v>
+      </c>
+      <c r="C1836">
+        <v>4530.6</v>
+      </c>
+      <c r="D1836" t="s">
+        <v>1838</v>
+      </c>
+    </row>
+    <row r="1837" spans="1:4">
+      <c r="A1837" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1837">
+        <v>12</v>
+      </c>
+      <c r="C1837">
+        <v>4511.4</v>
+      </c>
+      <c r="D1837" t="s">
+        <v>1839</v>
+      </c>
+    </row>
+    <row r="1838" spans="1:4">
+      <c r="A1838" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1838">
+        <v>13</v>
+      </c>
+      <c r="C1838">
+        <v>4534</v>
+      </c>
+      <c r="D1838" t="s">
+        <v>1840</v>
+      </c>
+    </row>
+    <row r="1839" spans="1:4">
+      <c r="A1839" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1839">
+        <v>14</v>
+      </c>
+      <c r="C1839">
+        <v>4511.1</v>
+      </c>
+      <c r="D1839" t="s">
+        <v>1841</v>
+      </c>
+    </row>
+    <row r="1840" spans="1:4">
+      <c r="A1840" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1840">
+        <v>15</v>
+      </c>
+      <c r="C1840">
+        <v>4485.4</v>
+      </c>
+      <c r="D1840" t="s">
+        <v>1842</v>
+      </c>
+    </row>
+    <row r="1841" spans="1:4">
+      <c r="A1841" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1841">
+        <v>16</v>
+      </c>
+      <c r="C1841">
+        <v>4465.9</v>
+      </c>
+      <c r="D1841" t="s">
+        <v>1843</v>
+      </c>
+    </row>
+    <row r="1842" spans="1:4">
+      <c r="A1842" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1842">
+        <v>17</v>
+      </c>
+      <c r="C1842">
+        <v>4435.9</v>
+      </c>
+      <c r="D1842" t="s">
+        <v>1844</v>
+      </c>
+    </row>
+    <row r="1843" spans="1:4">
+      <c r="A1843" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1843">
+        <v>18</v>
+      </c>
+      <c r="C1843">
+        <v>4389.2</v>
+      </c>
+      <c r="D1843" t="s">
+        <v>1845</v>
+      </c>
+    </row>
+    <row r="1844" spans="1:4">
+      <c r="A1844" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1844">
+        <v>19</v>
+      </c>
+      <c r="C1844">
+        <v>4347.8</v>
+      </c>
+      <c r="D1844" t="s">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="1845" spans="1:4">
+      <c r="A1845" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1845">
+        <v>20</v>
+      </c>
+      <c r="C1845">
+        <v>4313.5</v>
+      </c>
+      <c r="D1845" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="1846" spans="1:4">
+      <c r="A1846" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1846">
+        <v>21</v>
+      </c>
+      <c r="C1846">
+        <v>4345.6</v>
+      </c>
+      <c r="D1846" t="s">
+        <v>1848</v>
+      </c>
+    </row>
+    <row r="1847" spans="1:4">
+      <c r="A1847" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1847">
+        <v>22</v>
+      </c>
+      <c r="C1847">
+        <v>4325.6</v>
+      </c>
+      <c r="D1847" t="s">
+        <v>1849</v>
+      </c>
+    </row>
+    <row r="1848" spans="1:4">
+      <c r="A1848" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1848">
+        <v>23</v>
+      </c>
+      <c r="C1848">
+        <v>4313.4</v>
+      </c>
+      <c r="D1848" t="s">
+        <v>1850</v>
+      </c>
+    </row>
+    <row r="1849" spans="1:4">
+      <c r="A1849" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1849">
+        <v>24</v>
+      </c>
+      <c r="C1849">
+        <v>4296.6</v>
+      </c>
+      <c r="D1849" t="s">
+        <v>1851</v>
+      </c>
+    </row>
+    <row r="1850" spans="1:4">
+      <c r="A1850" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1850">
+        <v>25</v>
+      </c>
+      <c r="C1850">
+        <v>4356.8</v>
+      </c>
+      <c r="D1850" t="s">
+        <v>1852</v>
+      </c>
+    </row>
+    <row r="1851" spans="1:4">
+      <c r="A1851" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1851">
+        <v>26</v>
+      </c>
+      <c r="C1851">
+        <v>4401.3</v>
+      </c>
+      <c r="D1851" t="s">
+        <v>1853</v>
+      </c>
+    </row>
+    <row r="1852" spans="1:4">
+      <c r="A1852" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1852">
+        <v>27</v>
+      </c>
+      <c r="C1852">
+        <v>4453.1</v>
+      </c>
+      <c r="D1852" t="s">
+        <v>1854</v>
+      </c>
+    </row>
+    <row r="1853" spans="1:4">
+      <c r="A1853" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1853">
+        <v>28</v>
+      </c>
+      <c r="C1853">
+        <v>4486.4</v>
+      </c>
+      <c r="D1853" t="s">
+        <v>1855</v>
+      </c>
+    </row>
+    <row r="1854" spans="1:4">
+      <c r="A1854" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1854">
+        <v>29</v>
+      </c>
+      <c r="C1854">
+        <v>4530.9</v>
+      </c>
+      <c r="D1854" t="s">
+        <v>1856</v>
+      </c>
+    </row>
+    <row r="1855" spans="1:4">
+      <c r="A1855" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1855">
+        <v>30</v>
+      </c>
+      <c r="C1855">
+        <v>4556.5</v>
+      </c>
+      <c r="D1855" t="s">
+        <v>1857</v>
+      </c>
+    </row>
+    <row r="1856" spans="1:4">
+      <c r="A1856" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1856">
+        <v>31</v>
+      </c>
+      <c r="C1856">
+        <v>4652.3</v>
+      </c>
+      <c r="D1856" t="s">
+        <v>1858</v>
+      </c>
+    </row>
+    <row r="1857" spans="1:4">
+      <c r="A1857" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1857">
+        <v>32</v>
+      </c>
+      <c r="C1857">
+        <v>4739.7</v>
+      </c>
+      <c r="D1857" t="s">
+        <v>1859</v>
+      </c>
+    </row>
+    <row r="1858" spans="1:4">
+      <c r="A1858" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1858">
+        <v>33</v>
+      </c>
+      <c r="C1858">
+        <v>4631.3</v>
+      </c>
+      <c r="D1858" t="s">
+        <v>1860</v>
+      </c>
+    </row>
+    <row r="1859" spans="1:4">
+      <c r="A1859" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1859">
+        <v>34</v>
+      </c>
+      <c r="C1859">
+        <v>4683</v>
+      </c>
+      <c r="D1859" t="s">
+        <v>1861</v>
+      </c>
+    </row>
+    <row r="1860" spans="1:4">
+      <c r="A1860" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1860">
+        <v>35</v>
+      </c>
+      <c r="C1860">
+        <v>4719.6</v>
+      </c>
+      <c r="D1860" t="s">
+        <v>1862</v>
+      </c>
+    </row>
+    <row r="1861" spans="1:4">
+      <c r="A1861" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1861">
+        <v>36</v>
+      </c>
+      <c r="C1861">
+        <v>4834.8</v>
+      </c>
+      <c r="D1861" t="s">
+        <v>1863</v>
+      </c>
+    </row>
+    <row r="1862" spans="1:4">
+      <c r="A1862" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1862">
+        <v>37</v>
+      </c>
+      <c r="C1862">
+        <v>4656.5</v>
+      </c>
+      <c r="D1862" t="s">
+        <v>1864</v>
+      </c>
+    </row>
+    <row r="1863" spans="1:4">
+      <c r="A1863" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1863">
+        <v>38</v>
+      </c>
+      <c r="C1863">
+        <v>4619.5</v>
+      </c>
+      <c r="D1863" t="s">
+        <v>1865</v>
+      </c>
+    </row>
+    <row r="1864" spans="1:4">
+      <c r="A1864" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1864">
+        <v>39</v>
+      </c>
+      <c r="C1864">
+        <v>4636.2</v>
+      </c>
+      <c r="D1864" t="s">
+        <v>1866</v>
+      </c>
+    </row>
+    <row r="1865" spans="1:4">
+      <c r="A1865" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1865">
+        <v>40</v>
+      </c>
+      <c r="C1865">
+        <v>4654.8</v>
+      </c>
+      <c r="D1865" t="s">
+        <v>1867</v>
+      </c>
+    </row>
+    <row r="1866" spans="1:4">
+      <c r="A1866" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1866">
+        <v>41</v>
+      </c>
+      <c r="C1866">
+        <v>4790.7</v>
+      </c>
+      <c r="D1866" t="s">
+        <v>1868</v>
+      </c>
+    </row>
+    <row r="1867" spans="1:4">
+      <c r="A1867" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1867">
+        <v>42</v>
+      </c>
+      <c r="C1867">
+        <v>4769.9</v>
+      </c>
+      <c r="D1867" t="s">
+        <v>1869</v>
+      </c>
+    </row>
+    <row r="1868" spans="1:4">
+      <c r="A1868" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1868">
+        <v>43</v>
+      </c>
+      <c r="C1868">
+        <v>4768.3</v>
+      </c>
+      <c r="D1868" t="s">
+        <v>1870</v>
+      </c>
+    </row>
+    <row r="1869" spans="1:4">
+      <c r="A1869" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1869">
+        <v>44</v>
+      </c>
+      <c r="C1869">
+        <v>4787.5</v>
+      </c>
+      <c r="D1869" t="s">
+        <v>1871</v>
+      </c>
+    </row>
+    <row r="1870" spans="1:4">
+      <c r="A1870" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1870">
+        <v>45</v>
+      </c>
+      <c r="C1870">
+        <v>4778</v>
+      </c>
+      <c r="D1870" t="s">
+        <v>1872</v>
+      </c>
+    </row>
+    <row r="1871" spans="1:4">
+      <c r="A1871" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1871">
+        <v>46</v>
+      </c>
+      <c r="C1871">
+        <v>4773.3</v>
+      </c>
+      <c r="D1871" t="s">
+        <v>1873</v>
+      </c>
+    </row>
+    <row r="1872" spans="1:4">
+      <c r="A1872" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1872">
+        <v>47</v>
+      </c>
+      <c r="C1872">
+        <v>4754.1</v>
+      </c>
+      <c r="D1872" t="s">
+        <v>1874</v>
+      </c>
+    </row>
+    <row r="1873" spans="1:4">
+      <c r="A1873" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1873">
+        <v>48</v>
+      </c>
+      <c r="C1873">
+        <v>4770.1</v>
+      </c>
+      <c r="D1873" t="s">
+        <v>1875</v>
+      </c>
+    </row>
+    <row r="1874" spans="1:4">
+      <c r="A1874" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1874">
+        <v>49</v>
+      </c>
+      <c r="C1874">
+        <v>4566.1</v>
+      </c>
+      <c r="D1874" t="s">
+        <v>1876</v>
+      </c>
+    </row>
+    <row r="1875" spans="1:4">
+      <c r="A1875" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1875">
+        <v>50</v>
+      </c>
+      <c r="C1875">
+        <v>4528.2</v>
+      </c>
+      <c r="D1875" t="s">
+        <v>1877</v>
+      </c>
+    </row>
+    <row r="1876" spans="1:4">
+      <c r="A1876" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1876">
+        <v>51</v>
+      </c>
+      <c r="C1876">
+        <v>4505.5</v>
+      </c>
+      <c r="D1876" t="s">
+        <v>1878</v>
+      </c>
+    </row>
+    <row r="1877" spans="1:4">
+      <c r="A1877" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1877">
+        <v>52</v>
+      </c>
+      <c r="C1877">
+        <v>4500</v>
+      </c>
+      <c r="D1877" t="s">
+        <v>1879</v>
+      </c>
+    </row>
+    <row r="1878" spans="1:4">
+      <c r="A1878" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1878">
+        <v>53</v>
+      </c>
+      <c r="C1878">
+        <v>4467.1</v>
+      </c>
+      <c r="D1878" t="s">
+        <v>1880</v>
+      </c>
+    </row>
+    <row r="1879" spans="1:4">
+      <c r="A1879" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1879">
+        <v>54</v>
+      </c>
+      <c r="C1879">
+        <v>4448.4</v>
+      </c>
+      <c r="D1879" t="s">
+        <v>1881</v>
+      </c>
+    </row>
+    <row r="1880" spans="1:4">
+      <c r="A1880" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1880">
+        <v>55</v>
+      </c>
+      <c r="C1880">
+        <v>4473.8</v>
+      </c>
+      <c r="D1880" t="s">
+        <v>1882</v>
+      </c>
+    </row>
+    <row r="1881" spans="1:4">
+      <c r="A1881" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1881">
+        <v>56</v>
+      </c>
+      <c r="C1881">
+        <v>4498.2</v>
+      </c>
+      <c r="D1881" t="s">
+        <v>1883</v>
+      </c>
+    </row>
+    <row r="1882" spans="1:4">
+      <c r="A1882" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1882">
+        <v>57</v>
+      </c>
+      <c r="C1882">
+        <v>4570.2</v>
+      </c>
+      <c r="D1882" t="s">
+        <v>1884</v>
+      </c>
+    </row>
+    <row r="1883" spans="1:4">
+      <c r="A1883" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1883">
+        <v>58</v>
+      </c>
+      <c r="C1883">
+        <v>4567</v>
+      </c>
+      <c r="D1883" t="s">
+        <v>1885</v>
+      </c>
+    </row>
+    <row r="1884" spans="1:4">
+      <c r="A1884" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1884">
+        <v>59</v>
+      </c>
+      <c r="C1884">
+        <v>4588</v>
+      </c>
+      <c r="D1884" t="s">
+        <v>1886</v>
+      </c>
+    </row>
+    <row r="1885" spans="1:4">
+      <c r="A1885" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1885">
+        <v>60</v>
+      </c>
+      <c r="C1885">
+        <v>4635.1</v>
+      </c>
+      <c r="D1885" t="s">
+        <v>1887</v>
+      </c>
+    </row>
+    <row r="1886" spans="1:4">
+      <c r="A1886" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1886">
+        <v>61</v>
+      </c>
+      <c r="C1886">
+        <v>4691.2</v>
+      </c>
+      <c r="D1886" t="s">
+        <v>1888</v>
+      </c>
+    </row>
+    <row r="1887" spans="1:4">
+      <c r="A1887" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1887">
+        <v>62</v>
+      </c>
+      <c r="C1887">
+        <v>4666.4</v>
+      </c>
+      <c r="D1887" t="s">
+        <v>1889</v>
+      </c>
+    </row>
+    <row r="1888" spans="1:4">
+      <c r="A1888" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1888">
+        <v>63</v>
+      </c>
+      <c r="C1888">
+        <v>4651.2</v>
+      </c>
+      <c r="D1888" t="s">
+        <v>1890</v>
+      </c>
+    </row>
+    <row r="1889" spans="1:4">
+      <c r="A1889" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1889">
+        <v>64</v>
+      </c>
+      <c r="C1889">
+        <v>4680.3</v>
+      </c>
+      <c r="D1889" t="s">
+        <v>1891</v>
+      </c>
+    </row>
+    <row r="1890" spans="1:4">
+      <c r="A1890" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1890">
+        <v>65</v>
+      </c>
+      <c r="C1890">
+        <v>4729.1</v>
+      </c>
+      <c r="D1890" t="s">
+        <v>1892</v>
+      </c>
+    </row>
+    <row r="1891" spans="1:4">
+      <c r="A1891" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1891">
+        <v>66</v>
+      </c>
+      <c r="C1891">
+        <v>4690.3</v>
+      </c>
+      <c r="D1891" t="s">
+        <v>1893</v>
+      </c>
+    </row>
+    <row r="1892" spans="1:4">
+      <c r="A1892" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1892">
+        <v>67</v>
+      </c>
+      <c r="C1892">
+        <v>4689.2</v>
+      </c>
+      <c r="D1892" t="s">
+        <v>1894</v>
+      </c>
+    </row>
+    <row r="1893" spans="1:4">
+      <c r="A1893" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1893">
+        <v>68</v>
+      </c>
+      <c r="C1893">
+        <v>4650.9</v>
+      </c>
+      <c r="D1893" t="s">
+        <v>1895</v>
+      </c>
+    </row>
+    <row r="1894" spans="1:4">
+      <c r="A1894" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1894">
+        <v>69</v>
+      </c>
+      <c r="C1894">
+        <v>4533.4</v>
+      </c>
+      <c r="D1894" t="s">
+        <v>1896</v>
+      </c>
+    </row>
+    <row r="1895" spans="1:4">
+      <c r="A1895" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1895">
+        <v>70</v>
+      </c>
+      <c r="C1895">
+        <v>4448.8</v>
+      </c>
+      <c r="D1895" t="s">
+        <v>1897</v>
+      </c>
+    </row>
+    <row r="1896" spans="1:4">
+      <c r="A1896" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1896">
+        <v>71</v>
+      </c>
+      <c r="C1896">
+        <v>4394.3</v>
+      </c>
+      <c r="D1896" t="s">
+        <v>1898</v>
+      </c>
+    </row>
+    <row r="1897" spans="1:4">
+      <c r="A1897" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1897">
+        <v>72</v>
+      </c>
+      <c r="C1897">
+        <v>4328.9</v>
+      </c>
+      <c r="D1897" t="s">
+        <v>1899</v>
+      </c>
+    </row>
+    <row r="1898" spans="1:4">
+      <c r="A1898" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1898">
+        <v>73</v>
+      </c>
+      <c r="C1898">
+        <v>4914.8</v>
+      </c>
+      <c r="D1898" t="s">
+        <v>1900</v>
+      </c>
+    </row>
+    <row r="1899" spans="1:4">
+      <c r="A1899" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1899">
+        <v>74</v>
+      </c>
+      <c r="C1899">
+        <v>4845</v>
+      </c>
+      <c r="D1899" t="s">
+        <v>1901</v>
+      </c>
+    </row>
+    <row r="1900" spans="1:4">
+      <c r="A1900" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1900">
+        <v>75</v>
+      </c>
+      <c r="C1900">
+        <v>4816.5</v>
+      </c>
+      <c r="D1900" t="s">
+        <v>1902</v>
+      </c>
+    </row>
+    <row r="1901" spans="1:4">
+      <c r="A1901" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1901">
+        <v>76</v>
+      </c>
+      <c r="C1901">
+        <v>4815.9</v>
+      </c>
+      <c r="D1901" t="s">
+        <v>1903</v>
+      </c>
+    </row>
+    <row r="1902" spans="1:4">
+      <c r="A1902" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1902">
+        <v>77</v>
+      </c>
+      <c r="C1902">
+        <v>4761.2</v>
+      </c>
+      <c r="D1902" t="s">
+        <v>1904</v>
+      </c>
+    </row>
+    <row r="1903" spans="1:4">
+      <c r="A1903" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1903">
+        <v>78</v>
+      </c>
+      <c r="C1903">
+        <v>4809.7</v>
+      </c>
+      <c r="D1903" t="s">
+        <v>1905</v>
+      </c>
+    </row>
+    <row r="1904" spans="1:4">
+      <c r="A1904" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1904">
+        <v>79</v>
+      </c>
+      <c r="C1904">
+        <v>4756.6</v>
+      </c>
+      <c r="D1904" t="s">
+        <v>1906</v>
+      </c>
+    </row>
+    <row r="1905" spans="1:4">
+      <c r="A1905" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1905">
+        <v>80</v>
+      </c>
+      <c r="C1905">
+        <v>4759.2</v>
+      </c>
+      <c r="D1905" t="s">
+        <v>1907</v>
+      </c>
+    </row>
+    <row r="1906" spans="1:4">
+      <c r="A1906" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1906">
+        <v>81</v>
+      </c>
+      <c r="C1906">
+        <v>4855.1</v>
+      </c>
+      <c r="D1906" t="s">
+        <v>1908</v>
+      </c>
+    </row>
+    <row r="1907" spans="1:4">
+      <c r="A1907" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1907">
+        <v>82</v>
+      </c>
+      <c r="C1907">
+        <v>4916.2</v>
+      </c>
+      <c r="D1907" t="s">
+        <v>1909</v>
+      </c>
+    </row>
+    <row r="1908" spans="1:4">
+      <c r="A1908" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1908">
+        <v>83</v>
+      </c>
+      <c r="C1908">
+        <v>4968.5</v>
+      </c>
+      <c r="D1908" t="s">
+        <v>1910</v>
+      </c>
+    </row>
+    <row r="1909" spans="1:4">
+      <c r="A1909" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1909">
+        <v>84</v>
+      </c>
+      <c r="C1909">
+        <v>4990.7</v>
+      </c>
+      <c r="D1909" t="s">
+        <v>1911</v>
+      </c>
+    </row>
+    <row r="1910" spans="1:4">
+      <c r="A1910" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1910">
+        <v>85</v>
+      </c>
+      <c r="C1910">
+        <v>5004.6</v>
+      </c>
+      <c r="D1910" t="s">
+        <v>1912</v>
+      </c>
+    </row>
+    <row r="1911" spans="1:4">
+      <c r="A1911" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1911">
+        <v>86</v>
+      </c>
+      <c r="C1911">
+        <v>4932.3</v>
+      </c>
+      <c r="D1911" t="s">
+        <v>1913</v>
+      </c>
+    </row>
+    <row r="1912" spans="1:4">
+      <c r="A1912" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1912">
+        <v>87</v>
+      </c>
+      <c r="C1912">
+        <v>4984.8</v>
+      </c>
+      <c r="D1912" t="s">
+        <v>1914</v>
+      </c>
+    </row>
+    <row r="1913" spans="1:4">
+      <c r="A1913" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1913">
+        <v>88</v>
+      </c>
+      <c r="C1913">
+        <v>4993.5</v>
+      </c>
+      <c r="D1913" t="s">
+        <v>1915</v>
+      </c>
+    </row>
+    <row r="1914" spans="1:4">
+      <c r="A1914" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1914">
+        <v>89</v>
+      </c>
+      <c r="C1914">
+        <v>4871.9</v>
+      </c>
+      <c r="D1914" t="s">
+        <v>1916</v>
+      </c>
+    </row>
+    <row r="1915" spans="1:4">
+      <c r="A1915" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1915">
+        <v>90</v>
+      </c>
+      <c r="C1915">
+        <v>4933.7</v>
+      </c>
+      <c r="D1915" t="s">
+        <v>1917</v>
+      </c>
+    </row>
+    <row r="1916" spans="1:4">
+      <c r="A1916" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1916">
+        <v>91</v>
+      </c>
+      <c r="C1916">
+        <v>4900.4</v>
+      </c>
+      <c r="D1916" t="s">
+        <v>1918</v>
+      </c>
+    </row>
+    <row r="1917" spans="1:4">
+      <c r="A1917" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1917">
+        <v>92</v>
+      </c>
+      <c r="C1917">
+        <v>4893.1</v>
+      </c>
+      <c r="D1917" t="s">
+        <v>1919</v>
+      </c>
+    </row>
+    <row r="1918" spans="1:4">
+      <c r="A1918" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1918">
+        <v>93</v>
+      </c>
+      <c r="C1918">
+        <v>4739.7</v>
+      </c>
+      <c r="D1918" t="s">
+        <v>1920</v>
+      </c>
+    </row>
+    <row r="1919" spans="1:4">
+      <c r="A1919" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1919">
+        <v>94</v>
+      </c>
+      <c r="C1919">
+        <v>4625.6</v>
+      </c>
+      <c r="D1919" t="s">
+        <v>1921</v>
+      </c>
+    </row>
+    <row r="1920" spans="1:4">
+      <c r="A1920" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1920">
+        <v>95</v>
+      </c>
+      <c r="C1920">
+        <v>4660.6</v>
+      </c>
+      <c r="D1920" t="s">
+        <v>1922</v>
+      </c>
+    </row>
+    <row r="1921" spans="1:4">
+      <c r="A1921" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1921">
+        <v>96</v>
+      </c>
+      <c r="C1921">
+        <v>4692.5</v>
+      </c>
+      <c r="D1921" t="s">
+        <v>1923</v>
       </c>
     </row>
   </sheetData>

--- a/Market Fundamentals/Transelectrica_data/Cons_Prod_final/Weekly_Production_2026.xlsx
+++ b/Market Fundamentals/Transelectrica_data/Cons_Prod_final/Weekly_Production_2026.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1924" uniqueCount="1924">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2116" uniqueCount="2116">
   <si>
     <t>Date</t>
   </si>
@@ -5786,6 +5786,582 @@
   </si>
   <si>
     <t>20.05.202696.0</t>
+  </si>
+  <si>
+    <t>21.05.20261.0</t>
+  </si>
+  <si>
+    <t>21.05.20262.0</t>
+  </si>
+  <si>
+    <t>21.05.20263.0</t>
+  </si>
+  <si>
+    <t>21.05.20264.0</t>
+  </si>
+  <si>
+    <t>21.05.20265.0</t>
+  </si>
+  <si>
+    <t>21.05.20266.0</t>
+  </si>
+  <si>
+    <t>21.05.20267.0</t>
+  </si>
+  <si>
+    <t>21.05.20268.0</t>
+  </si>
+  <si>
+    <t>21.05.20269.0</t>
+  </si>
+  <si>
+    <t>21.05.202610.0</t>
+  </si>
+  <si>
+    <t>21.05.202611.0</t>
+  </si>
+  <si>
+    <t>21.05.202612.0</t>
+  </si>
+  <si>
+    <t>21.05.202613.0</t>
+  </si>
+  <si>
+    <t>21.05.202614.0</t>
+  </si>
+  <si>
+    <t>21.05.202615.0</t>
+  </si>
+  <si>
+    <t>21.05.202616.0</t>
+  </si>
+  <si>
+    <t>21.05.202617.0</t>
+  </si>
+  <si>
+    <t>21.05.202618.0</t>
+  </si>
+  <si>
+    <t>21.05.202619.0</t>
+  </si>
+  <si>
+    <t>21.05.202620.0</t>
+  </si>
+  <si>
+    <t>21.05.202621.0</t>
+  </si>
+  <si>
+    <t>21.05.202622.0</t>
+  </si>
+  <si>
+    <t>21.05.202623.0</t>
+  </si>
+  <si>
+    <t>21.05.202624.0</t>
+  </si>
+  <si>
+    <t>21.05.202625.0</t>
+  </si>
+  <si>
+    <t>21.05.202626.0</t>
+  </si>
+  <si>
+    <t>21.05.202627.0</t>
+  </si>
+  <si>
+    <t>21.05.202628.0</t>
+  </si>
+  <si>
+    <t>21.05.202629.0</t>
+  </si>
+  <si>
+    <t>21.05.202630.0</t>
+  </si>
+  <si>
+    <t>21.05.202631.0</t>
+  </si>
+  <si>
+    <t>21.05.202632.0</t>
+  </si>
+  <si>
+    <t>21.05.202633.0</t>
+  </si>
+  <si>
+    <t>21.05.202634.0</t>
+  </si>
+  <si>
+    <t>21.05.202635.0</t>
+  </si>
+  <si>
+    <t>21.05.202636.0</t>
+  </si>
+  <si>
+    <t>21.05.202637.0</t>
+  </si>
+  <si>
+    <t>21.05.202638.0</t>
+  </si>
+  <si>
+    <t>21.05.202639.0</t>
+  </si>
+  <si>
+    <t>21.05.202640.0</t>
+  </si>
+  <si>
+    <t>21.05.202641.0</t>
+  </si>
+  <si>
+    <t>21.05.202642.0</t>
+  </si>
+  <si>
+    <t>21.05.202643.0</t>
+  </si>
+  <si>
+    <t>21.05.202644.0</t>
+  </si>
+  <si>
+    <t>21.05.202645.0</t>
+  </si>
+  <si>
+    <t>21.05.202646.0</t>
+  </si>
+  <si>
+    <t>21.05.202647.0</t>
+  </si>
+  <si>
+    <t>21.05.202648.0</t>
+  </si>
+  <si>
+    <t>21.05.202649.0</t>
+  </si>
+  <si>
+    <t>21.05.202650.0</t>
+  </si>
+  <si>
+    <t>21.05.202651.0</t>
+  </si>
+  <si>
+    <t>21.05.202652.0</t>
+  </si>
+  <si>
+    <t>21.05.202653.0</t>
+  </si>
+  <si>
+    <t>21.05.202654.0</t>
+  </si>
+  <si>
+    <t>21.05.202655.0</t>
+  </si>
+  <si>
+    <t>21.05.202656.0</t>
+  </si>
+  <si>
+    <t>21.05.202657.0</t>
+  </si>
+  <si>
+    <t>21.05.202658.0</t>
+  </si>
+  <si>
+    <t>21.05.202659.0</t>
+  </si>
+  <si>
+    <t>21.05.202660.0</t>
+  </si>
+  <si>
+    <t>21.05.202661.0</t>
+  </si>
+  <si>
+    <t>21.05.202662.0</t>
+  </si>
+  <si>
+    <t>21.05.202663.0</t>
+  </si>
+  <si>
+    <t>21.05.202664.0</t>
+  </si>
+  <si>
+    <t>21.05.202665.0</t>
+  </si>
+  <si>
+    <t>21.05.202666.0</t>
+  </si>
+  <si>
+    <t>21.05.202667.0</t>
+  </si>
+  <si>
+    <t>21.05.202668.0</t>
+  </si>
+  <si>
+    <t>21.05.202669.0</t>
+  </si>
+  <si>
+    <t>21.05.202670.0</t>
+  </si>
+  <si>
+    <t>21.05.202671.0</t>
+  </si>
+  <si>
+    <t>21.05.202672.0</t>
+  </si>
+  <si>
+    <t>21.05.202673.0</t>
+  </si>
+  <si>
+    <t>21.05.202674.0</t>
+  </si>
+  <si>
+    <t>21.05.202675.0</t>
+  </si>
+  <si>
+    <t>21.05.202676.0</t>
+  </si>
+  <si>
+    <t>21.05.202677.0</t>
+  </si>
+  <si>
+    <t>21.05.202678.0</t>
+  </si>
+  <si>
+    <t>21.05.202679.0</t>
+  </si>
+  <si>
+    <t>21.05.202680.0</t>
+  </si>
+  <si>
+    <t>21.05.202681.0</t>
+  </si>
+  <si>
+    <t>21.05.202682.0</t>
+  </si>
+  <si>
+    <t>21.05.202683.0</t>
+  </si>
+  <si>
+    <t>21.05.202684.0</t>
+  </si>
+  <si>
+    <t>21.05.202685.0</t>
+  </si>
+  <si>
+    <t>21.05.202686.0</t>
+  </si>
+  <si>
+    <t>21.05.202687.0</t>
+  </si>
+  <si>
+    <t>21.05.202688.0</t>
+  </si>
+  <si>
+    <t>21.05.202689.0</t>
+  </si>
+  <si>
+    <t>21.05.202690.0</t>
+  </si>
+  <si>
+    <t>21.05.202691.0</t>
+  </si>
+  <si>
+    <t>21.05.202692.0</t>
+  </si>
+  <si>
+    <t>21.05.202693.0</t>
+  </si>
+  <si>
+    <t>21.05.202694.0</t>
+  </si>
+  <si>
+    <t>21.05.202695.0</t>
+  </si>
+  <si>
+    <t>21.05.202696.0</t>
+  </si>
+  <si>
+    <t>22.05.20261.0</t>
+  </si>
+  <si>
+    <t>22.05.20262.0</t>
+  </si>
+  <si>
+    <t>22.05.20263.0</t>
+  </si>
+  <si>
+    <t>22.05.20264.0</t>
+  </si>
+  <si>
+    <t>22.05.20265.0</t>
+  </si>
+  <si>
+    <t>22.05.20266.0</t>
+  </si>
+  <si>
+    <t>22.05.20267.0</t>
+  </si>
+  <si>
+    <t>22.05.20268.0</t>
+  </si>
+  <si>
+    <t>22.05.20269.0</t>
+  </si>
+  <si>
+    <t>22.05.202610.0</t>
+  </si>
+  <si>
+    <t>22.05.202611.0</t>
+  </si>
+  <si>
+    <t>22.05.202612.0</t>
+  </si>
+  <si>
+    <t>22.05.202613.0</t>
+  </si>
+  <si>
+    <t>22.05.202614.0</t>
+  </si>
+  <si>
+    <t>22.05.202615.0</t>
+  </si>
+  <si>
+    <t>22.05.202616.0</t>
+  </si>
+  <si>
+    <t>22.05.202617.0</t>
+  </si>
+  <si>
+    <t>22.05.202618.0</t>
+  </si>
+  <si>
+    <t>22.05.202619.0</t>
+  </si>
+  <si>
+    <t>22.05.202620.0</t>
+  </si>
+  <si>
+    <t>22.05.202621.0</t>
+  </si>
+  <si>
+    <t>22.05.202622.0</t>
+  </si>
+  <si>
+    <t>22.05.202623.0</t>
+  </si>
+  <si>
+    <t>22.05.202624.0</t>
+  </si>
+  <si>
+    <t>22.05.202625.0</t>
+  </si>
+  <si>
+    <t>22.05.202626.0</t>
+  </si>
+  <si>
+    <t>22.05.202627.0</t>
+  </si>
+  <si>
+    <t>22.05.202628.0</t>
+  </si>
+  <si>
+    <t>22.05.202629.0</t>
+  </si>
+  <si>
+    <t>22.05.202630.0</t>
+  </si>
+  <si>
+    <t>22.05.202631.0</t>
+  </si>
+  <si>
+    <t>22.05.202632.0</t>
+  </si>
+  <si>
+    <t>22.05.202633.0</t>
+  </si>
+  <si>
+    <t>22.05.202634.0</t>
+  </si>
+  <si>
+    <t>22.05.202635.0</t>
+  </si>
+  <si>
+    <t>22.05.202636.0</t>
+  </si>
+  <si>
+    <t>22.05.202637.0</t>
+  </si>
+  <si>
+    <t>22.05.202638.0</t>
+  </si>
+  <si>
+    <t>22.05.202639.0</t>
+  </si>
+  <si>
+    <t>22.05.202640.0</t>
+  </si>
+  <si>
+    <t>22.05.202641.0</t>
+  </si>
+  <si>
+    <t>22.05.202642.0</t>
+  </si>
+  <si>
+    <t>22.05.202643.0</t>
+  </si>
+  <si>
+    <t>22.05.202644.0</t>
+  </si>
+  <si>
+    <t>22.05.202645.0</t>
+  </si>
+  <si>
+    <t>22.05.202646.0</t>
+  </si>
+  <si>
+    <t>22.05.202647.0</t>
+  </si>
+  <si>
+    <t>22.05.202648.0</t>
+  </si>
+  <si>
+    <t>22.05.202649.0</t>
+  </si>
+  <si>
+    <t>22.05.202650.0</t>
+  </si>
+  <si>
+    <t>22.05.202651.0</t>
+  </si>
+  <si>
+    <t>22.05.202652.0</t>
+  </si>
+  <si>
+    <t>22.05.202653.0</t>
+  </si>
+  <si>
+    <t>22.05.202654.0</t>
+  </si>
+  <si>
+    <t>22.05.202655.0</t>
+  </si>
+  <si>
+    <t>22.05.202656.0</t>
+  </si>
+  <si>
+    <t>22.05.202657.0</t>
+  </si>
+  <si>
+    <t>22.05.202658.0</t>
+  </si>
+  <si>
+    <t>22.05.202659.0</t>
+  </si>
+  <si>
+    <t>22.05.202660.0</t>
+  </si>
+  <si>
+    <t>22.05.202661.0</t>
+  </si>
+  <si>
+    <t>22.05.202662.0</t>
+  </si>
+  <si>
+    <t>22.05.202663.0</t>
+  </si>
+  <si>
+    <t>22.05.202664.0</t>
+  </si>
+  <si>
+    <t>22.05.202665.0</t>
+  </si>
+  <si>
+    <t>22.05.202666.0</t>
+  </si>
+  <si>
+    <t>22.05.202667.0</t>
+  </si>
+  <si>
+    <t>22.05.202668.0</t>
+  </si>
+  <si>
+    <t>22.05.202669.0</t>
+  </si>
+  <si>
+    <t>22.05.202670.0</t>
+  </si>
+  <si>
+    <t>22.05.202671.0</t>
+  </si>
+  <si>
+    <t>22.05.202672.0</t>
+  </si>
+  <si>
+    <t>22.05.202673.0</t>
+  </si>
+  <si>
+    <t>22.05.202674.0</t>
+  </si>
+  <si>
+    <t>22.05.202675.0</t>
+  </si>
+  <si>
+    <t>22.05.202676.0</t>
+  </si>
+  <si>
+    <t>22.05.202677.0</t>
+  </si>
+  <si>
+    <t>22.05.202678.0</t>
+  </si>
+  <si>
+    <t>22.05.202679.0</t>
+  </si>
+  <si>
+    <t>22.05.202680.0</t>
+  </si>
+  <si>
+    <t>22.05.202681.0</t>
+  </si>
+  <si>
+    <t>22.05.202682.0</t>
+  </si>
+  <si>
+    <t>22.05.202683.0</t>
+  </si>
+  <si>
+    <t>22.05.202684.0</t>
+  </si>
+  <si>
+    <t>22.05.202685.0</t>
+  </si>
+  <si>
+    <t>22.05.202686.0</t>
+  </si>
+  <si>
+    <t>22.05.202687.0</t>
+  </si>
+  <si>
+    <t>22.05.202688.0</t>
+  </si>
+  <si>
+    <t>22.05.202689.0</t>
+  </si>
+  <si>
+    <t>22.05.202690.0</t>
+  </si>
+  <si>
+    <t>22.05.202691.0</t>
+  </si>
+  <si>
+    <t>22.05.202692.0</t>
+  </si>
+  <si>
+    <t>22.05.202693.0</t>
+  </si>
+  <si>
+    <t>22.05.202694.0</t>
+  </si>
+  <si>
+    <t>22.05.202695.0</t>
+  </si>
+  <si>
+    <t>22.05.202696.0</t>
   </si>
 </sst>
 </file>
@@ -6147,7 +6723,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1921"/>
+  <dimension ref="A1:D2113"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -24988,7 +25564,7 @@
         <v>1</v>
       </c>
       <c r="C1346">
-        <v>5104</v>
+        <v>3664</v>
       </c>
       <c r="D1346" t="s">
         <v>1348</v>
@@ -25002,7 +25578,7 @@
         <v>2</v>
       </c>
       <c r="C1347">
-        <v>5064</v>
+        <v>3629.3</v>
       </c>
       <c r="D1347" t="s">
         <v>1349</v>
@@ -25016,7 +25592,7 @@
         <v>3</v>
       </c>
       <c r="C1348">
-        <v>5004</v>
+        <v>3628</v>
       </c>
       <c r="D1348" t="s">
         <v>1350</v>
@@ -25030,7 +25606,7 @@
         <v>4</v>
       </c>
       <c r="C1349">
-        <v>4934</v>
+        <v>3606</v>
       </c>
       <c r="D1349" t="s">
         <v>1351</v>
@@ -25044,7 +25620,7 @@
         <v>5</v>
       </c>
       <c r="C1350">
-        <v>4179</v>
+        <v>3592</v>
       </c>
       <c r="D1350" t="s">
         <v>1352</v>
@@ -25058,7 +25634,7 @@
         <v>6</v>
       </c>
       <c r="C1351">
-        <v>4151.3</v>
+        <v>3585.8</v>
       </c>
       <c r="D1351" t="s">
         <v>1353</v>
@@ -25072,7 +25648,7 @@
         <v>7</v>
       </c>
       <c r="C1352">
-        <v>4113.1</v>
+        <v>3577.6</v>
       </c>
       <c r="D1352" t="s">
         <v>1354</v>
@@ -25086,7 +25662,7 @@
         <v>8</v>
       </c>
       <c r="C1353">
-        <v>4055.6</v>
+        <v>3614.3</v>
       </c>
       <c r="D1353" t="s">
         <v>1355</v>
@@ -25100,7 +25676,7 @@
         <v>9</v>
       </c>
       <c r="C1354">
-        <v>3891.6</v>
+        <v>3479.6</v>
       </c>
       <c r="D1354" t="s">
         <v>1356</v>
@@ -25114,7 +25690,7 @@
         <v>10</v>
       </c>
       <c r="C1355">
-        <v>3850.1</v>
+        <v>3499.5</v>
       </c>
       <c r="D1355" t="s">
         <v>1357</v>
@@ -25128,7 +25704,7 @@
         <v>11</v>
       </c>
       <c r="C1356">
-        <v>3837.5</v>
+        <v>3517.1</v>
       </c>
       <c r="D1356" t="s">
         <v>1358</v>
@@ -25142,7 +25718,7 @@
         <v>12</v>
       </c>
       <c r="C1357">
-        <v>3864.2</v>
+        <v>3551.4</v>
       </c>
       <c r="D1357" t="s">
         <v>1359</v>
@@ -25156,7 +25732,7 @@
         <v>13</v>
       </c>
       <c r="C1358">
-        <v>3935.5</v>
+        <v>3627.7</v>
       </c>
       <c r="D1358" t="s">
         <v>1360</v>
@@ -25170,7 +25746,7 @@
         <v>14</v>
       </c>
       <c r="C1359">
-        <v>3925.3</v>
+        <v>3634.4</v>
       </c>
       <c r="D1359" t="s">
         <v>1361</v>
@@ -25184,7 +25760,7 @@
         <v>15</v>
       </c>
       <c r="C1360">
-        <v>3933.1</v>
+        <v>3642.9</v>
       </c>
       <c r="D1360" t="s">
         <v>1362</v>
@@ -25198,7 +25774,7 @@
         <v>16</v>
       </c>
       <c r="C1361">
-        <v>3936.9</v>
+        <v>3663.2</v>
       </c>
       <c r="D1361" t="s">
         <v>1363</v>
@@ -25212,7 +25788,7 @@
         <v>17</v>
       </c>
       <c r="C1362">
-        <v>3919.9</v>
+        <v>3627.3</v>
       </c>
       <c r="D1362" t="s">
         <v>1364</v>
@@ -25226,7 +25802,7 @@
         <v>18</v>
       </c>
       <c r="C1363">
-        <v>3920.4</v>
+        <v>3631.4</v>
       </c>
       <c r="D1363" t="s">
         <v>1365</v>
@@ -25240,7 +25816,7 @@
         <v>19</v>
       </c>
       <c r="C1364">
-        <v>3914.2</v>
+        <v>3631.6</v>
       </c>
       <c r="D1364" t="s">
         <v>1366</v>
@@ -25254,7 +25830,7 @@
         <v>20</v>
       </c>
       <c r="C1365">
-        <v>3916.6</v>
+        <v>3643.2</v>
       </c>
       <c r="D1365" t="s">
         <v>1367</v>
@@ -25268,7 +25844,7 @@
         <v>21</v>
       </c>
       <c r="C1366">
-        <v>3999.6</v>
+        <v>3694.8</v>
       </c>
       <c r="D1366" t="s">
         <v>1368</v>
@@ -25282,7 +25858,7 @@
         <v>22</v>
       </c>
       <c r="C1367">
-        <v>4000.5</v>
+        <v>3678.5</v>
       </c>
       <c r="D1367" t="s">
         <v>1369</v>
@@ -25296,7 +25872,7 @@
         <v>23</v>
       </c>
       <c r="C1368">
-        <v>4052.8</v>
+        <v>3721.9</v>
       </c>
       <c r="D1368" t="s">
         <v>1370</v>
@@ -25310,7 +25886,7 @@
         <v>24</v>
       </c>
       <c r="C1369">
-        <v>4093.9</v>
+        <v>3780.3</v>
       </c>
       <c r="D1369" t="s">
         <v>1371</v>
@@ -25324,7 +25900,7 @@
         <v>25</v>
       </c>
       <c r="C1370">
-        <v>4274.4</v>
+        <v>4023</v>
       </c>
       <c r="D1370" t="s">
         <v>1372</v>
@@ -25338,7 +25914,7 @@
         <v>26</v>
       </c>
       <c r="C1371">
-        <v>4341.4</v>
+        <v>4060.3</v>
       </c>
       <c r="D1371" t="s">
         <v>1373</v>
@@ -25352,7 +25928,7 @@
         <v>27</v>
       </c>
       <c r="C1372">
-        <v>4373.7</v>
+        <v>4099.6</v>
       </c>
       <c r="D1372" t="s">
         <v>1374</v>
@@ -25366,7 +25942,7 @@
         <v>28</v>
       </c>
       <c r="C1373">
-        <v>4400.7</v>
+        <v>4131.4</v>
       </c>
       <c r="D1373" t="s">
         <v>1375</v>
@@ -25380,7 +25956,7 @@
         <v>29</v>
       </c>
       <c r="C1374">
-        <v>4267.2</v>
+        <v>4210.4</v>
       </c>
       <c r="D1374" t="s">
         <v>1376</v>
@@ -25394,7 +25970,7 @@
         <v>30</v>
       </c>
       <c r="C1375">
-        <v>4269.3</v>
+        <v>4262.5</v>
       </c>
       <c r="D1375" t="s">
         <v>1377</v>
@@ -25408,7 +25984,7 @@
         <v>31</v>
       </c>
       <c r="C1376">
-        <v>4346.7</v>
+        <v>4346.2</v>
       </c>
       <c r="D1376" t="s">
         <v>1378</v>
@@ -25422,7 +25998,7 @@
         <v>32</v>
       </c>
       <c r="C1377">
-        <v>4439.8</v>
+        <v>4428.5</v>
       </c>
       <c r="D1377" t="s">
         <v>1379</v>
@@ -25436,7 +26012,7 @@
         <v>33</v>
       </c>
       <c r="C1378">
-        <v>4284.8</v>
+        <v>4339.1</v>
       </c>
       <c r="D1378" t="s">
         <v>1380</v>
@@ -25450,7 +26026,7 @@
         <v>34</v>
       </c>
       <c r="C1379">
-        <v>4359.1</v>
+        <v>4373.8</v>
       </c>
       <c r="D1379" t="s">
         <v>1381</v>
@@ -25464,7 +26040,7 @@
         <v>35</v>
       </c>
       <c r="C1380">
-        <v>4424.5</v>
+        <v>4459.7</v>
       </c>
       <c r="D1380" t="s">
         <v>1382</v>
@@ -25478,7 +26054,7 @@
         <v>36</v>
       </c>
       <c r="C1381">
-        <v>4519.1</v>
+        <v>4533</v>
       </c>
       <c r="D1381" t="s">
         <v>1383</v>
@@ -25492,7 +26068,7 @@
         <v>37</v>
       </c>
       <c r="C1382">
-        <v>4528.2</v>
+        <v>4676</v>
       </c>
       <c r="D1382" t="s">
         <v>1384</v>
@@ -25506,7 +26082,7 @@
         <v>38</v>
       </c>
       <c r="C1383">
-        <v>4575.1</v>
+        <v>4705.1</v>
       </c>
       <c r="D1383" t="s">
         <v>1385</v>
@@ -25520,7 +26096,7 @@
         <v>39</v>
       </c>
       <c r="C1384">
-        <v>4660.3</v>
+        <v>4743.3</v>
       </c>
       <c r="D1384" t="s">
         <v>1386</v>
@@ -25534,7 +26110,7 @@
         <v>40</v>
       </c>
       <c r="C1385">
-        <v>4788.9</v>
+        <v>4797.3</v>
       </c>
       <c r="D1385" t="s">
         <v>1387</v>
@@ -25548,7 +26124,7 @@
         <v>41</v>
       </c>
       <c r="C1386">
-        <v>4869.4</v>
+        <v>5110.7</v>
       </c>
       <c r="D1386" t="s">
         <v>1388</v>
@@ -25562,7 +26138,7 @@
         <v>42</v>
       </c>
       <c r="C1387">
-        <v>4936.4</v>
+        <v>5178.9</v>
       </c>
       <c r="D1387" t="s">
         <v>1389</v>
@@ -25576,7 +26152,7 @@
         <v>43</v>
       </c>
       <c r="C1388">
-        <v>5004.6</v>
+        <v>5165.7</v>
       </c>
       <c r="D1388" t="s">
         <v>1390</v>
@@ -25590,7 +26166,7 @@
         <v>44</v>
       </c>
       <c r="C1389">
-        <v>5076.4</v>
+        <v>5216</v>
       </c>
       <c r="D1389" t="s">
         <v>1391</v>
@@ -25604,7 +26180,7 @@
         <v>45</v>
       </c>
       <c r="C1390">
-        <v>5224.6</v>
+        <v>5009.9</v>
       </c>
       <c r="D1390" t="s">
         <v>1392</v>
@@ -25618,7 +26194,7 @@
         <v>46</v>
       </c>
       <c r="C1391">
-        <v>5248.2</v>
+        <v>5005.4</v>
       </c>
       <c r="D1391" t="s">
         <v>1393</v>
@@ -25632,7 +26208,7 @@
         <v>47</v>
       </c>
       <c r="C1392">
-        <v>5234.9</v>
+        <v>5035.9</v>
       </c>
       <c r="D1392" t="s">
         <v>1394</v>
@@ -25646,7 +26222,7 @@
         <v>48</v>
       </c>
       <c r="C1393">
-        <v>5241.8</v>
+        <v>5106.1</v>
       </c>
       <c r="D1393" t="s">
         <v>1395</v>
@@ -25660,7 +26236,7 @@
         <v>49</v>
       </c>
       <c r="C1394">
-        <v>4959</v>
+        <v>5089.4</v>
       </c>
       <c r="D1394" t="s">
         <v>1396</v>
@@ -25674,7 +26250,7 @@
         <v>50</v>
       </c>
       <c r="C1395">
-        <v>4930</v>
+        <v>5133.9</v>
       </c>
       <c r="D1395" t="s">
         <v>1397</v>
@@ -25688,7 +26264,7 @@
         <v>51</v>
       </c>
       <c r="C1396">
-        <v>4865.6</v>
+        <v>5159.4</v>
       </c>
       <c r="D1396" t="s">
         <v>1398</v>
@@ -25702,7 +26278,7 @@
         <v>52</v>
       </c>
       <c r="C1397">
-        <v>4820</v>
+        <v>5209</v>
       </c>
       <c r="D1397" t="s">
         <v>1399</v>
@@ -25716,7 +26292,7 @@
         <v>53</v>
       </c>
       <c r="C1398">
-        <v>4546.5</v>
+        <v>5105.9</v>
       </c>
       <c r="D1398" t="s">
         <v>1400</v>
@@ -25730,7 +26306,7 @@
         <v>54</v>
       </c>
       <c r="C1399">
-        <v>4496.6</v>
+        <v>5145</v>
       </c>
       <c r="D1399" t="s">
         <v>1401</v>
@@ -25744,7 +26320,7 @@
         <v>55</v>
       </c>
       <c r="C1400">
-        <v>4493.2</v>
+        <v>5200.4</v>
       </c>
       <c r="D1400" t="s">
         <v>1402</v>
@@ -25758,7 +26334,7 @@
         <v>56</v>
       </c>
       <c r="C1401">
-        <v>4497.2</v>
+        <v>5226.9</v>
       </c>
       <c r="D1401" t="s">
         <v>1403</v>
@@ -25772,7 +26348,7 @@
         <v>57</v>
       </c>
       <c r="C1402">
-        <v>4526.7</v>
+        <v>5289.3</v>
       </c>
       <c r="D1402" t="s">
         <v>1404</v>
@@ -25786,7 +26362,7 @@
         <v>58</v>
       </c>
       <c r="C1403">
-        <v>4519.9</v>
+        <v>5314.7</v>
       </c>
       <c r="D1403" t="s">
         <v>1405</v>
@@ -25800,7 +26376,7 @@
         <v>59</v>
       </c>
       <c r="C1404">
-        <v>4528.4</v>
+        <v>5358.2</v>
       </c>
       <c r="D1404" t="s">
         <v>1406</v>
@@ -25814,7 +26390,7 @@
         <v>60</v>
       </c>
       <c r="C1405">
-        <v>4556</v>
+        <v>5394.4</v>
       </c>
       <c r="D1405" t="s">
         <v>1407</v>
@@ -25828,7 +26404,7 @@
         <v>61</v>
       </c>
       <c r="C1406">
-        <v>4532.8</v>
+        <v>5402.5</v>
       </c>
       <c r="D1406" t="s">
         <v>1408</v>
@@ -25842,7 +26418,7 @@
         <v>62</v>
       </c>
       <c r="C1407">
-        <v>4530.4</v>
+        <v>5436.9</v>
       </c>
       <c r="D1407" t="s">
         <v>1409</v>
@@ -25856,7 +26432,7 @@
         <v>63</v>
       </c>
       <c r="C1408">
-        <v>4531.3</v>
+        <v>5462.6</v>
       </c>
       <c r="D1408" t="s">
         <v>1410</v>
@@ -25870,7 +26446,7 @@
         <v>64</v>
       </c>
       <c r="C1409">
-        <v>4531.8</v>
+        <v>5488</v>
       </c>
       <c r="D1409" t="s">
         <v>1411</v>
@@ -25884,7 +26460,7 @@
         <v>65</v>
       </c>
       <c r="C1410">
-        <v>4603.4</v>
+        <v>5549.6</v>
       </c>
       <c r="D1410" t="s">
         <v>1412</v>
@@ -25898,7 +26474,7 @@
         <v>66</v>
       </c>
       <c r="C1411">
-        <v>4564.7</v>
+        <v>5518</v>
       </c>
       <c r="D1411" t="s">
         <v>1413</v>
@@ -25912,7 +26488,7 @@
         <v>67</v>
       </c>
       <c r="C1412">
-        <v>4525.2</v>
+        <v>5511.9</v>
       </c>
       <c r="D1412" t="s">
         <v>1414</v>
@@ -25926,7 +26502,7 @@
         <v>68</v>
       </c>
       <c r="C1413">
-        <v>4500.7</v>
+        <v>5482.4</v>
       </c>
       <c r="D1413" t="s">
         <v>1415</v>
@@ -25940,7 +26516,7 @@
         <v>69</v>
       </c>
       <c r="C1414">
-        <v>4754.6</v>
+        <v>5538.5</v>
       </c>
       <c r="D1414" t="s">
         <v>1416</v>
@@ -25954,7 +26530,7 @@
         <v>70</v>
       </c>
       <c r="C1415">
-        <v>4666.9</v>
+        <v>5469.8</v>
       </c>
       <c r="D1415" t="s">
         <v>1417</v>
@@ -25968,7 +26544,7 @@
         <v>71</v>
       </c>
       <c r="C1416">
-        <v>4590.8</v>
+        <v>5413.7</v>
       </c>
       <c r="D1416" t="s">
         <v>1418</v>
@@ -25982,7 +26558,7 @@
         <v>72</v>
       </c>
       <c r="C1417">
-        <v>4498.5</v>
+        <v>5400.3</v>
       </c>
       <c r="D1417" t="s">
         <v>1419</v>
@@ -25996,7 +26572,7 @@
         <v>73</v>
       </c>
       <c r="C1418">
-        <v>4701.9</v>
+        <v>5610.4</v>
       </c>
       <c r="D1418" t="s">
         <v>1420</v>
@@ -26010,7 +26586,7 @@
         <v>74</v>
       </c>
       <c r="C1419">
-        <v>4580.2</v>
+        <v>5548.3</v>
       </c>
       <c r="D1419" t="s">
         <v>1421</v>
@@ -26024,7 +26600,7 @@
         <v>75</v>
       </c>
       <c r="C1420">
-        <v>4484.6</v>
+        <v>5538.7</v>
       </c>
       <c r="D1420" t="s">
         <v>1422</v>
@@ -26038,7 +26614,7 @@
         <v>76</v>
       </c>
       <c r="C1421">
-        <v>4387.8</v>
+        <v>5521.3</v>
       </c>
       <c r="D1421" t="s">
         <v>1423</v>
@@ -26052,7 +26628,7 @@
         <v>77</v>
       </c>
       <c r="C1422">
-        <v>4425.7</v>
+        <v>5693</v>
       </c>
       <c r="D1422" t="s">
         <v>1424</v>
@@ -26066,7 +26642,7 @@
         <v>78</v>
       </c>
       <c r="C1423">
-        <v>4394.3</v>
+        <v>5700.3</v>
       </c>
       <c r="D1423" t="s">
         <v>1425</v>
@@ -26080,7 +26656,7 @@
         <v>79</v>
       </c>
       <c r="C1424">
-        <v>4335</v>
+        <v>5683</v>
       </c>
       <c r="D1424" t="s">
         <v>1426</v>
@@ -26094,7 +26670,7 @@
         <v>80</v>
       </c>
       <c r="C1425">
-        <v>4290.2</v>
+        <v>5684.9</v>
       </c>
       <c r="D1425" t="s">
         <v>1427</v>
@@ -26108,7 +26684,7 @@
         <v>81</v>
       </c>
       <c r="C1426">
-        <v>4444.3</v>
+        <v>5681.5</v>
       </c>
       <c r="D1426" t="s">
         <v>1428</v>
@@ -26122,7 +26698,7 @@
         <v>82</v>
       </c>
       <c r="C1427">
-        <v>4436.2</v>
+        <v>5695.5</v>
       </c>
       <c r="D1427" t="s">
         <v>1429</v>
@@ -26136,7 +26712,7 @@
         <v>83</v>
       </c>
       <c r="C1428">
-        <v>4426.7</v>
+        <v>5721</v>
       </c>
       <c r="D1428" t="s">
         <v>1430</v>
@@ -26150,7 +26726,7 @@
         <v>84</v>
       </c>
       <c r="C1429">
-        <v>4415.1</v>
+        <v>5753.7</v>
       </c>
       <c r="D1429" t="s">
         <v>1431</v>
@@ -26164,7 +26740,7 @@
         <v>85</v>
       </c>
       <c r="C1430">
-        <v>4452</v>
+        <v>5978.2</v>
       </c>
       <c r="D1430" t="s">
         <v>1432</v>
@@ -26178,7 +26754,7 @@
         <v>86</v>
       </c>
       <c r="C1431">
-        <v>4434.5</v>
+        <v>5969.5</v>
       </c>
       <c r="D1431" t="s">
         <v>1433</v>
@@ -26192,7 +26768,7 @@
         <v>87</v>
       </c>
       <c r="C1432">
-        <v>4457.7</v>
+        <v>5990.8</v>
       </c>
       <c r="D1432" t="s">
         <v>1434</v>
@@ -26206,7 +26782,7 @@
         <v>88</v>
       </c>
       <c r="C1433">
-        <v>4472.2</v>
+        <v>6008.5</v>
       </c>
       <c r="D1433" t="s">
         <v>1435</v>
@@ -26220,7 +26796,7 @@
         <v>89</v>
       </c>
       <c r="C1434">
-        <v>4475.6</v>
+        <v>5958.3</v>
       </c>
       <c r="D1434" t="s">
         <v>1436</v>
@@ -26234,7 +26810,7 @@
         <v>90</v>
       </c>
       <c r="C1435">
-        <v>4478.7</v>
+        <v>5935.8</v>
       </c>
       <c r="D1435" t="s">
         <v>1437</v>
@@ -26248,7 +26824,7 @@
         <v>91</v>
       </c>
       <c r="C1436">
-        <v>4403.4</v>
+        <v>5880.4</v>
       </c>
       <c r="D1436" t="s">
         <v>1438</v>
@@ -26262,7 +26838,7 @@
         <v>92</v>
       </c>
       <c r="C1437">
-        <v>4409.4</v>
+        <v>5858.1</v>
       </c>
       <c r="D1437" t="s">
         <v>1439</v>
@@ -26276,7 +26852,7 @@
         <v>93</v>
       </c>
       <c r="C1438">
-        <v>3917.4</v>
+        <v>5552.2</v>
       </c>
       <c r="D1438" t="s">
         <v>1440</v>
@@ -26290,7 +26866,7 @@
         <v>94</v>
       </c>
       <c r="C1439">
-        <v>3824.4</v>
+        <v>5515</v>
       </c>
       <c r="D1439" t="s">
         <v>1441</v>
@@ -26304,7 +26880,7 @@
         <v>95</v>
       </c>
       <c r="C1440">
-        <v>3797</v>
+        <v>5484.1</v>
       </c>
       <c r="D1440" t="s">
         <v>1442</v>
@@ -26318,7 +26894,7 @@
         <v>96</v>
       </c>
       <c r="C1441">
-        <v>3816.4</v>
+        <v>5447.6</v>
       </c>
       <c r="D1441" t="s">
         <v>1443</v>
@@ -26332,7 +26908,7 @@
         <v>1</v>
       </c>
       <c r="C1442">
-        <v>4579.6</v>
+        <v>3654</v>
       </c>
       <c r="D1442" t="s">
         <v>1444</v>
@@ -26346,7 +26922,7 @@
         <v>2</v>
       </c>
       <c r="C1443">
-        <v>4453.2</v>
+        <v>3639.3</v>
       </c>
       <c r="D1443" t="s">
         <v>1445</v>
@@ -26360,7 +26936,7 @@
         <v>3</v>
       </c>
       <c r="C1444">
-        <v>4414.8</v>
+        <v>3638</v>
       </c>
       <c r="D1444" t="s">
         <v>1446</v>
@@ -26374,7 +26950,7 @@
         <v>4</v>
       </c>
       <c r="C1445">
-        <v>4385.1</v>
+        <v>3596</v>
       </c>
       <c r="D1445" t="s">
         <v>1447</v>
@@ -26388,7 +26964,7 @@
         <v>5</v>
       </c>
       <c r="C1446">
-        <v>3960.2</v>
+        <v>3602</v>
       </c>
       <c r="D1446" t="s">
         <v>1448</v>
@@ -26402,7 +26978,7 @@
         <v>6</v>
       </c>
       <c r="C1447">
-        <v>3951.1</v>
+        <v>3595.8</v>
       </c>
       <c r="D1447" t="s">
         <v>1449</v>
@@ -26416,7 +26992,7 @@
         <v>7</v>
       </c>
       <c r="C1448">
-        <v>3932.1</v>
+        <v>3567.6</v>
       </c>
       <c r="D1448" t="s">
         <v>1450</v>
@@ -26430,7 +27006,7 @@
         <v>8</v>
       </c>
       <c r="C1449">
-        <v>3943.1</v>
+        <v>3584.3</v>
       </c>
       <c r="D1449" t="s">
         <v>1451</v>
@@ -26444,7 +27020,7 @@
         <v>9</v>
       </c>
       <c r="C1450">
-        <v>4017.8</v>
+        <v>3429.6</v>
       </c>
       <c r="D1450" t="s">
         <v>1452</v>
@@ -26458,7 +27034,7 @@
         <v>10</v>
       </c>
       <c r="C1451">
-        <v>4023.3</v>
+        <v>3429.5</v>
       </c>
       <c r="D1451" t="s">
         <v>1453</v>
@@ -26472,7 +27048,7 @@
         <v>11</v>
       </c>
       <c r="C1452">
-        <v>4030.3</v>
+        <v>3417.1</v>
       </c>
       <c r="D1452" t="s">
         <v>1454</v>
@@ -26486,7 +27062,7 @@
         <v>12</v>
       </c>
       <c r="C1453">
-        <v>4056.4</v>
+        <v>3451.4</v>
       </c>
       <c r="D1453" t="s">
         <v>1455</v>
@@ -26500,7 +27076,7 @@
         <v>13</v>
       </c>
       <c r="C1454">
-        <v>4139.7</v>
+        <v>3527.7</v>
       </c>
       <c r="D1454" t="s">
         <v>1456</v>
@@ -26514,7 +27090,7 @@
         <v>14</v>
       </c>
       <c r="C1455">
-        <v>4154.8</v>
+        <v>3524.4</v>
       </c>
       <c r="D1455" t="s">
         <v>1457</v>
@@ -26528,7 +27104,7 @@
         <v>15</v>
       </c>
       <c r="C1456">
-        <v>4197.3</v>
+        <v>3532.9</v>
       </c>
       <c r="D1456" t="s">
         <v>1458</v>
@@ -26542,7 +27118,7 @@
         <v>16</v>
       </c>
       <c r="C1457">
-        <v>4209.2</v>
+        <v>3533.2</v>
       </c>
       <c r="D1457" t="s">
         <v>1459</v>
@@ -26556,7 +27132,7 @@
         <v>17</v>
       </c>
       <c r="C1458">
-        <v>4070.8</v>
+        <v>3487.3</v>
       </c>
       <c r="D1458" t="s">
         <v>1460</v>
@@ -26570,7 +27146,7 @@
         <v>18</v>
       </c>
       <c r="C1459">
-        <v>4098.7</v>
+        <v>3471.4</v>
       </c>
       <c r="D1459" t="s">
         <v>1461</v>
@@ -26584,7 +27160,7 @@
         <v>19</v>
       </c>
       <c r="C1460">
-        <v>4130.4</v>
+        <v>3461.6</v>
       </c>
       <c r="D1460" t="s">
         <v>1462</v>
@@ -26598,7 +27174,7 @@
         <v>20</v>
       </c>
       <c r="C1461">
-        <v>4164.3</v>
+        <v>3453.2</v>
       </c>
       <c r="D1461" t="s">
         <v>1463</v>
@@ -26612,7 +27188,7 @@
         <v>21</v>
       </c>
       <c r="C1462">
-        <v>4173.9</v>
+        <v>3484.8</v>
       </c>
       <c r="D1462" t="s">
         <v>1464</v>
@@ -26626,7 +27202,7 @@
         <v>22</v>
       </c>
       <c r="C1463">
-        <v>4199.3</v>
+        <v>3428.5</v>
       </c>
       <c r="D1463" t="s">
         <v>1465</v>
@@ -26640,7 +27216,7 @@
         <v>23</v>
       </c>
       <c r="C1464">
-        <v>4206.5</v>
+        <v>3421.9</v>
       </c>
       <c r="D1464" t="s">
         <v>1466</v>
@@ -26654,7 +27230,7 @@
         <v>24</v>
       </c>
       <c r="C1465">
-        <v>4209.6</v>
+        <v>3430.3</v>
       </c>
       <c r="D1465" t="s">
         <v>1467</v>
@@ -26668,7 +27244,7 @@
         <v>25</v>
       </c>
       <c r="C1466">
-        <v>4194.7</v>
+        <v>3623</v>
       </c>
       <c r="D1466" t="s">
         <v>1468</v>
@@ -26682,7 +27258,7 @@
         <v>26</v>
       </c>
       <c r="C1467">
-        <v>4173.8</v>
+        <v>3580.3</v>
       </c>
       <c r="D1467" t="s">
         <v>1469</v>
@@ -26696,7 +27272,7 @@
         <v>27</v>
       </c>
       <c r="C1468">
-        <v>4171.5</v>
+        <v>3559.6</v>
       </c>
       <c r="D1468" t="s">
         <v>1470</v>
@@ -26710,7 +27286,7 @@
         <v>28</v>
       </c>
       <c r="C1469">
-        <v>4196.3</v>
+        <v>3501.4</v>
       </c>
       <c r="D1469" t="s">
         <v>1471</v>
@@ -26724,7 +27300,7 @@
         <v>29</v>
       </c>
       <c r="C1470">
-        <v>4119.7</v>
+        <v>3420.4</v>
       </c>
       <c r="D1470" t="s">
         <v>1472</v>
@@ -26738,7 +27314,7 @@
         <v>30</v>
       </c>
       <c r="C1471">
-        <v>4179.8</v>
+        <v>3412.5</v>
       </c>
       <c r="D1471" t="s">
         <v>1473</v>
@@ -26752,7 +27328,7 @@
         <v>31</v>
       </c>
       <c r="C1472">
-        <v>4249.2</v>
+        <v>3456.2</v>
       </c>
       <c r="D1472" t="s">
         <v>1474</v>
@@ -26766,7 +27342,7 @@
         <v>32</v>
       </c>
       <c r="C1473">
-        <v>4341.1</v>
+        <v>3538.5</v>
       </c>
       <c r="D1473" t="s">
         <v>1475</v>
@@ -26780,7 +27356,7 @@
         <v>33</v>
       </c>
       <c r="C1474">
-        <v>4389.7</v>
+        <v>3469.1</v>
       </c>
       <c r="D1474" t="s">
         <v>1476</v>
@@ -26794,7 +27370,7 @@
         <v>34</v>
       </c>
       <c r="C1475">
-        <v>4465.5</v>
+        <v>3513.8</v>
       </c>
       <c r="D1475" t="s">
         <v>1477</v>
@@ -26808,7 +27384,7 @@
         <v>35</v>
       </c>
       <c r="C1476">
-        <v>4497.9</v>
+        <v>3609.7</v>
       </c>
       <c r="D1476" t="s">
         <v>1478</v>
@@ -26822,7 +27398,7 @@
         <v>36</v>
       </c>
       <c r="C1477">
-        <v>4578.7</v>
+        <v>3703</v>
       </c>
       <c r="D1477" t="s">
         <v>1479</v>
@@ -26836,7 +27412,7 @@
         <v>37</v>
       </c>
       <c r="C1478">
-        <v>4112.8</v>
+        <v>3916</v>
       </c>
       <c r="D1478" t="s">
         <v>1480</v>
@@ -26850,7 +27426,7 @@
         <v>38</v>
       </c>
       <c r="C1479">
-        <v>4189.2</v>
+        <v>3995.1</v>
       </c>
       <c r="D1479" t="s">
         <v>1481</v>
@@ -26864,7 +27440,7 @@
         <v>39</v>
       </c>
       <c r="C1480">
-        <v>4270.8</v>
+        <v>4083.3</v>
       </c>
       <c r="D1480" t="s">
         <v>1482</v>
@@ -26878,7 +27454,7 @@
         <v>40</v>
       </c>
       <c r="C1481">
-        <v>4345.9</v>
+        <v>4177.3</v>
       </c>
       <c r="D1481" t="s">
         <v>1483</v>
@@ -26892,7 +27468,7 @@
         <v>41</v>
       </c>
       <c r="C1482">
-        <v>4243.8</v>
+        <v>4520.7</v>
       </c>
       <c r="D1482" t="s">
         <v>1484</v>
@@ -26906,7 +27482,7 @@
         <v>42</v>
       </c>
       <c r="C1483">
-        <v>4158.5</v>
+        <v>4638.9</v>
       </c>
       <c r="D1483" t="s">
         <v>1485</v>
@@ -26920,7 +27496,7 @@
         <v>43</v>
       </c>
       <c r="C1484">
-        <v>3998.6</v>
+        <v>4675.7</v>
       </c>
       <c r="D1484" t="s">
         <v>1486</v>
@@ -26934,7 +27510,7 @@
         <v>44</v>
       </c>
       <c r="C1485">
-        <v>3900</v>
+        <v>4776</v>
       </c>
       <c r="D1485" t="s">
         <v>1487</v>
@@ -26948,7 +27524,7 @@
         <v>45</v>
       </c>
       <c r="C1486">
-        <v>3968.2</v>
+        <v>4669.9</v>
       </c>
       <c r="D1486" t="s">
         <v>1488</v>
@@ -26962,7 +27538,7 @@
         <v>46</v>
       </c>
       <c r="C1487">
-        <v>4061.4</v>
+        <v>4725.4</v>
       </c>
       <c r="D1487" t="s">
         <v>1489</v>
@@ -26976,7 +27552,7 @@
         <v>47</v>
       </c>
       <c r="C1488">
-        <v>4091.7</v>
+        <v>4765.9</v>
       </c>
       <c r="D1488" t="s">
         <v>1490</v>
@@ -26990,7 +27566,7 @@
         <v>48</v>
       </c>
       <c r="C1489">
-        <v>4089.4</v>
+        <v>4826.1</v>
       </c>
       <c r="D1489" t="s">
         <v>1491</v>
@@ -27004,7 +27580,7 @@
         <v>49</v>
       </c>
       <c r="C1490">
-        <v>4014.3</v>
+        <v>4809.4</v>
       </c>
       <c r="D1490" t="s">
         <v>1492</v>
@@ -27018,7 +27594,7 @@
         <v>50</v>
       </c>
       <c r="C1491">
-        <v>4018.4</v>
+        <v>4843.9</v>
       </c>
       <c r="D1491" t="s">
         <v>1493</v>
@@ -27032,7 +27608,7 @@
         <v>51</v>
       </c>
       <c r="C1492">
-        <v>4192.4</v>
+        <v>4849.4</v>
       </c>
       <c r="D1492" t="s">
         <v>1494</v>
@@ -27046,7 +27622,7 @@
         <v>52</v>
       </c>
       <c r="C1493">
-        <v>4303.2</v>
+        <v>4899</v>
       </c>
       <c r="D1493" t="s">
         <v>1495</v>
@@ -27060,7 +27636,7 @@
         <v>53</v>
       </c>
       <c r="C1494">
-        <v>4265.4</v>
+        <v>4785.9</v>
       </c>
       <c r="D1494" t="s">
         <v>1496</v>
@@ -27074,7 +27650,7 @@
         <v>54</v>
       </c>
       <c r="C1495">
-        <v>4275.2</v>
+        <v>4805</v>
       </c>
       <c r="D1495" t="s">
         <v>1497</v>
@@ -27088,7 +27664,7 @@
         <v>55</v>
       </c>
       <c r="C1496">
-        <v>4256.1</v>
+        <v>4860.4</v>
       </c>
       <c r="D1496" t="s">
         <v>1498</v>
@@ -27102,7 +27678,7 @@
         <v>56</v>
       </c>
       <c r="C1497">
-        <v>4244.5</v>
+        <v>4896.9</v>
       </c>
       <c r="D1497" t="s">
         <v>1499</v>
@@ -27116,7 +27692,7 @@
         <v>57</v>
       </c>
       <c r="C1498">
-        <v>4092.4</v>
+        <v>4989.3</v>
       </c>
       <c r="D1498" t="s">
         <v>1500</v>
@@ -27130,7 +27706,7 @@
         <v>58</v>
       </c>
       <c r="C1499">
-        <v>4211.3</v>
+        <v>5024.7</v>
       </c>
       <c r="D1499" t="s">
         <v>1501</v>
@@ -27144,7 +27720,7 @@
         <v>59</v>
       </c>
       <c r="C1500">
-        <v>4241.3</v>
+        <v>5108.2</v>
       </c>
       <c r="D1500" t="s">
         <v>1502</v>
@@ -27158,7 +27734,7 @@
         <v>60</v>
       </c>
       <c r="C1501">
-        <v>4289.7</v>
+        <v>5174.4</v>
       </c>
       <c r="D1501" t="s">
         <v>1503</v>
@@ -27172,7 +27748,7 @@
         <v>61</v>
       </c>
       <c r="C1502">
-        <v>4390.4</v>
+        <v>5182.5</v>
       </c>
       <c r="D1502" t="s">
         <v>1504</v>
@@ -27186,7 +27762,7 @@
         <v>62</v>
       </c>
       <c r="C1503">
-        <v>4470.5</v>
+        <v>5236.9</v>
       </c>
       <c r="D1503" t="s">
         <v>1505</v>
@@ -27200,7 +27776,7 @@
         <v>63</v>
       </c>
       <c r="C1504">
-        <v>4543.1</v>
+        <v>5282.6</v>
       </c>
       <c r="D1504" t="s">
         <v>1506</v>
@@ -27214,7 +27790,7 @@
         <v>64</v>
       </c>
       <c r="C1505">
-        <v>4520.2</v>
+        <v>5338</v>
       </c>
       <c r="D1505" t="s">
         <v>1507</v>
@@ -27228,7 +27804,7 @@
         <v>65</v>
       </c>
       <c r="C1506">
-        <v>4665.2</v>
+        <v>5419.6</v>
       </c>
       <c r="D1506" t="s">
         <v>1508</v>
@@ -27242,7 +27818,7 @@
         <v>66</v>
       </c>
       <c r="C1507">
-        <v>4670.1</v>
+        <v>5408</v>
       </c>
       <c r="D1507" t="s">
         <v>1509</v>
@@ -27256,7 +27832,7 @@
         <v>67</v>
       </c>
       <c r="C1508">
-        <v>4641.2</v>
+        <v>5401.9</v>
       </c>
       <c r="D1508" t="s">
         <v>1510</v>
@@ -27270,7 +27846,7 @@
         <v>68</v>
       </c>
       <c r="C1509">
-        <v>4661.1</v>
+        <v>5392.4</v>
       </c>
       <c r="D1509" t="s">
         <v>1511</v>
@@ -27284,7 +27860,7 @@
         <v>69</v>
       </c>
       <c r="C1510">
-        <v>4613</v>
+        <v>5468.5</v>
       </c>
       <c r="D1510" t="s">
         <v>1512</v>
@@ -27298,7 +27874,7 @@
         <v>70</v>
       </c>
       <c r="C1511">
-        <v>4552.6</v>
+        <v>5409.8</v>
       </c>
       <c r="D1511" t="s">
         <v>1513</v>
@@ -27312,7 +27888,7 @@
         <v>71</v>
       </c>
       <c r="C1512">
-        <v>4481.9</v>
+        <v>5353.7</v>
       </c>
       <c r="D1512" t="s">
         <v>1514</v>
@@ -27326,7 +27902,7 @@
         <v>72</v>
       </c>
       <c r="C1513">
-        <v>4436.9</v>
+        <v>5330.3</v>
       </c>
       <c r="D1513" t="s">
         <v>1515</v>
@@ -27340,7 +27916,7 @@
         <v>73</v>
       </c>
       <c r="C1514">
-        <v>4515.2</v>
+        <v>5480.4</v>
       </c>
       <c r="D1514" t="s">
         <v>1516</v>
@@ -27354,7 +27930,7 @@
         <v>74</v>
       </c>
       <c r="C1515">
-        <v>4451.3</v>
+        <v>5388.3</v>
       </c>
       <c r="D1515" t="s">
         <v>1517</v>
@@ -27368,7 +27944,7 @@
         <v>75</v>
       </c>
       <c r="C1516">
-        <v>4355.1</v>
+        <v>5338.7</v>
       </c>
       <c r="D1516" t="s">
         <v>1518</v>
@@ -27382,7 +27958,7 @@
         <v>76</v>
       </c>
       <c r="C1517">
-        <v>4294.1</v>
+        <v>5301.3</v>
       </c>
       <c r="D1517" t="s">
         <v>1519</v>
@@ -27396,7 +27972,7 @@
         <v>77</v>
       </c>
       <c r="C1518">
-        <v>4902.8</v>
+        <v>5443</v>
       </c>
       <c r="D1518" t="s">
         <v>1520</v>
@@ -27410,7 +27986,7 @@
         <v>78</v>
       </c>
       <c r="C1519">
-        <v>4852.1</v>
+        <v>5440.3</v>
       </c>
       <c r="D1519" t="s">
         <v>1521</v>
@@ -27424,7 +28000,7 @@
         <v>79</v>
       </c>
       <c r="C1520">
-        <v>4782.8</v>
+        <v>5433</v>
       </c>
       <c r="D1520" t="s">
         <v>1522</v>
@@ -27438,7 +28014,7 @@
         <v>80</v>
       </c>
       <c r="C1521">
-        <v>4736.2</v>
+        <v>5434.9</v>
       </c>
       <c r="D1521" t="s">
         <v>1523</v>
@@ -27452,7 +28028,7 @@
         <v>81</v>
       </c>
       <c r="C1522">
-        <v>4998.6</v>
+        <v>5451.5</v>
       </c>
       <c r="D1522" t="s">
         <v>1524</v>
@@ -27466,7 +28042,7 @@
         <v>82</v>
       </c>
       <c r="C1523">
-        <v>5001</v>
+        <v>5485.5</v>
       </c>
       <c r="D1523" t="s">
         <v>1525</v>
@@ -27480,7 +28056,7 @@
         <v>83</v>
       </c>
       <c r="C1524">
-        <v>4972.9</v>
+        <v>5491</v>
       </c>
       <c r="D1524" t="s">
         <v>1526</v>
@@ -27494,7 +28070,7 @@
         <v>84</v>
       </c>
       <c r="C1525">
-        <v>4966.8</v>
+        <v>5453.7</v>
       </c>
       <c r="D1525" t="s">
         <v>1527</v>
@@ -27508,7 +28084,7 @@
         <v>85</v>
       </c>
       <c r="C1526">
-        <v>5062.1</v>
+        <v>5618.2</v>
       </c>
       <c r="D1526" t="s">
         <v>1528</v>
@@ -27522,7 +28098,7 @@
         <v>86</v>
       </c>
       <c r="C1527">
-        <v>5095.1</v>
+        <v>5609.5</v>
       </c>
       <c r="D1527" t="s">
         <v>1529</v>
@@ -27536,7 +28112,7 @@
         <v>87</v>
       </c>
       <c r="C1528">
-        <v>5094.2</v>
+        <v>5620.8</v>
       </c>
       <c r="D1528" t="s">
         <v>1530</v>
@@ -27550,7 +28126,7 @@
         <v>88</v>
       </c>
       <c r="C1529">
-        <v>5055.7</v>
+        <v>5638.5</v>
       </c>
       <c r="D1529" t="s">
         <v>1531</v>
@@ -27564,7 +28140,7 @@
         <v>89</v>
       </c>
       <c r="C1530">
-        <v>4825.8</v>
+        <v>5638.3</v>
       </c>
       <c r="D1530" t="s">
         <v>1532</v>
@@ -27578,7 +28154,7 @@
         <v>90</v>
       </c>
       <c r="C1531">
-        <v>4765.2</v>
+        <v>5635.8</v>
       </c>
       <c r="D1531" t="s">
         <v>1533</v>
@@ -27592,7 +28168,7 @@
         <v>91</v>
       </c>
       <c r="C1532">
-        <v>4734.7</v>
+        <v>5580.4</v>
       </c>
       <c r="D1532" t="s">
         <v>1534</v>
@@ -27606,7 +28182,7 @@
         <v>92</v>
       </c>
       <c r="C1533">
-        <v>4706.5</v>
+        <v>5578.1</v>
       </c>
       <c r="D1533" t="s">
         <v>1535</v>
@@ -27620,7 +28196,7 @@
         <v>93</v>
       </c>
       <c r="C1534">
-        <v>4480.9</v>
+        <v>5292.2</v>
       </c>
       <c r="D1534" t="s">
         <v>1536</v>
@@ -27634,7 +28210,7 @@
         <v>94</v>
       </c>
       <c r="C1535">
-        <v>4445.2</v>
+        <v>5245</v>
       </c>
       <c r="D1535" t="s">
         <v>1537</v>
@@ -27648,7 +28224,7 @@
         <v>95</v>
       </c>
       <c r="C1536">
-        <v>4442.2</v>
+        <v>5234.1</v>
       </c>
       <c r="D1536" t="s">
         <v>1538</v>
@@ -27662,7 +28238,7 @@
         <v>96</v>
       </c>
       <c r="C1537">
-        <v>4446.2</v>
+        <v>5197.6</v>
       </c>
       <c r="D1537" t="s">
         <v>1539</v>
@@ -27676,7 +28252,7 @@
         <v>1</v>
       </c>
       <c r="C1538">
-        <v>4463</v>
+        <v>5326</v>
       </c>
       <c r="D1538" t="s">
         <v>1540</v>
@@ -27690,7 +28266,7 @@
         <v>2</v>
       </c>
       <c r="C1539">
-        <v>4467</v>
+        <v>5286.2</v>
       </c>
       <c r="D1539" t="s">
         <v>1541</v>
@@ -27704,7 +28280,7 @@
         <v>3</v>
       </c>
       <c r="C1540">
-        <v>4473.4</v>
+        <v>5209.7</v>
       </c>
       <c r="D1540" t="s">
         <v>1542</v>
@@ -27718,7 +28294,7 @@
         <v>4</v>
       </c>
       <c r="C1541">
-        <v>4470.3</v>
+        <v>5087.7</v>
       </c>
       <c r="D1541" t="s">
         <v>1543</v>
@@ -27732,7 +28308,7 @@
         <v>5</v>
       </c>
       <c r="C1542">
-        <v>5045.6</v>
+        <v>4613.4</v>
       </c>
       <c r="D1542" t="s">
         <v>1544</v>
@@ -27746,7 +28322,7 @@
         <v>6</v>
       </c>
       <c r="C1543">
-        <v>5050.1</v>
+        <v>4558.2</v>
       </c>
       <c r="D1543" t="s">
         <v>1545</v>
@@ -27760,7 +28336,7 @@
         <v>7</v>
       </c>
       <c r="C1544">
-        <v>5069.5</v>
+        <v>4499.8</v>
       </c>
       <c r="D1544" t="s">
         <v>1546</v>
@@ -27774,7 +28350,7 @@
         <v>8</v>
       </c>
       <c r="C1545">
-        <v>5130</v>
+        <v>4454.3</v>
       </c>
       <c r="D1545" t="s">
         <v>1547</v>
@@ -27788,7 +28364,7 @@
         <v>9</v>
       </c>
       <c r="C1546">
-        <v>5154.4</v>
+        <v>4175.1</v>
       </c>
       <c r="D1546" t="s">
         <v>1548</v>
@@ -27802,7 +28378,7 @@
         <v>10</v>
       </c>
       <c r="C1547">
-        <v>5196.7</v>
+        <v>4144.8</v>
       </c>
       <c r="D1547" t="s">
         <v>1549</v>
@@ -27816,7 +28392,7 @@
         <v>11</v>
       </c>
       <c r="C1548">
-        <v>5246</v>
+        <v>4120.6</v>
       </c>
       <c r="D1548" t="s">
         <v>1550</v>
@@ -27830,7 +28406,7 @@
         <v>12</v>
       </c>
       <c r="C1549">
-        <v>5293.5</v>
+        <v>4101.4</v>
       </c>
       <c r="D1549" t="s">
         <v>1551</v>
@@ -27844,7 +28420,7 @@
         <v>13</v>
       </c>
       <c r="C1550">
-        <v>5281</v>
+        <v>4114</v>
       </c>
       <c r="D1550" t="s">
         <v>1552</v>
@@ -27858,7 +28434,7 @@
         <v>14</v>
       </c>
       <c r="C1551">
-        <v>5327.2</v>
+        <v>4071.1</v>
       </c>
       <c r="D1551" t="s">
         <v>1553</v>
@@ -27872,7 +28448,7 @@
         <v>15</v>
       </c>
       <c r="C1552">
-        <v>5377.2</v>
+        <v>4025.4</v>
       </c>
       <c r="D1552" t="s">
         <v>1554</v>
@@ -27886,7 +28462,7 @@
         <v>16</v>
       </c>
       <c r="C1553">
-        <v>5389.4</v>
+        <v>3985.9</v>
       </c>
       <c r="D1553" t="s">
         <v>1555</v>
@@ -27900,7 +28476,7 @@
         <v>17</v>
       </c>
       <c r="C1554">
-        <v>5467.4</v>
+        <v>3945.9</v>
       </c>
       <c r="D1554" t="s">
         <v>1556</v>
@@ -27914,7 +28490,7 @@
         <v>18</v>
       </c>
       <c r="C1555">
-        <v>5499.6</v>
+        <v>3889.2</v>
       </c>
       <c r="D1555" t="s">
         <v>1557</v>
@@ -27928,7 +28504,7 @@
         <v>19</v>
       </c>
       <c r="C1556">
-        <v>5491.6</v>
+        <v>3827.8</v>
       </c>
       <c r="D1556" t="s">
         <v>1558</v>
@@ -27942,7 +28518,7 @@
         <v>20</v>
       </c>
       <c r="C1557">
-        <v>5391.1</v>
+        <v>3783.5</v>
       </c>
       <c r="D1557" t="s">
         <v>1559</v>
@@ -27956,7 +28532,7 @@
         <v>21</v>
       </c>
       <c r="C1558">
-        <v>5401.9</v>
+        <v>3785.6</v>
       </c>
       <c r="D1558" t="s">
         <v>1560</v>
@@ -27970,7 +28546,7 @@
         <v>22</v>
       </c>
       <c r="C1559">
-        <v>5416.1</v>
+        <v>3735.6</v>
       </c>
       <c r="D1559" t="s">
         <v>1561</v>
@@ -27984,7 +28560,7 @@
         <v>23</v>
       </c>
       <c r="C1560">
-        <v>5418.5</v>
+        <v>3653.4</v>
       </c>
       <c r="D1560" t="s">
         <v>1562</v>
@@ -27998,7 +28574,7 @@
         <v>24</v>
       </c>
       <c r="C1561">
-        <v>5415.4</v>
+        <v>3556.6</v>
       </c>
       <c r="D1561" t="s">
         <v>1563</v>
@@ -28012,7 +28588,7 @@
         <v>25</v>
       </c>
       <c r="C1562">
-        <v>5328.4</v>
+        <v>3506.8</v>
       </c>
       <c r="D1562" t="s">
         <v>1564</v>
@@ -28026,7 +28602,7 @@
         <v>26</v>
       </c>
       <c r="C1563">
-        <v>5492.1</v>
+        <v>3441.3</v>
       </c>
       <c r="D1563" t="s">
         <v>1565</v>
@@ -28040,7 +28616,7 @@
         <v>27</v>
       </c>
       <c r="C1564">
-        <v>5421.7</v>
+        <v>3373.1</v>
       </c>
       <c r="D1564" t="s">
         <v>1566</v>
@@ -28054,7 +28630,7 @@
         <v>28</v>
       </c>
       <c r="C1565">
-        <v>5306.8</v>
+        <v>3296.4</v>
       </c>
       <c r="D1565" t="s">
         <v>1567</v>
@@ -28068,7 +28644,7 @@
         <v>29</v>
       </c>
       <c r="C1566">
-        <v>5303.4</v>
+        <v>3230.9</v>
       </c>
       <c r="D1566" t="s">
         <v>1568</v>
@@ -28082,7 +28658,7 @@
         <v>30</v>
       </c>
       <c r="C1567">
-        <v>5409.2</v>
+        <v>3176.5</v>
       </c>
       <c r="D1567" t="s">
         <v>1569</v>
@@ -28096,7 +28672,7 @@
         <v>31</v>
       </c>
       <c r="C1568">
-        <v>5615.6</v>
+        <v>3222.3</v>
       </c>
       <c r="D1568" t="s">
         <v>1570</v>
@@ -28110,7 +28686,7 @@
         <v>32</v>
       </c>
       <c r="C1569">
-        <v>5792.9</v>
+        <v>3299.7</v>
       </c>
       <c r="D1569" t="s">
         <v>1571</v>
@@ -28124,7 +28700,7 @@
         <v>33</v>
       </c>
       <c r="C1570">
-        <v>6257.1</v>
+        <v>3191.3</v>
       </c>
       <c r="D1570" t="s">
         <v>1572</v>
@@ -28138,7 +28714,7 @@
         <v>34</v>
       </c>
       <c r="C1571">
-        <v>6835.5</v>
+        <v>3313</v>
       </c>
       <c r="D1571" t="s">
         <v>1573</v>
@@ -28152,7 +28728,7 @@
         <v>35</v>
       </c>
       <c r="C1572">
-        <v>7183.7</v>
+        <v>3419.6</v>
       </c>
       <c r="D1572" t="s">
         <v>1574</v>
@@ -28166,7 +28742,7 @@
         <v>36</v>
       </c>
       <c r="C1573">
-        <v>7333.8</v>
+        <v>3584.8</v>
       </c>
       <c r="D1573" t="s">
         <v>1575</v>
@@ -28180,7 +28756,7 @@
         <v>37</v>
       </c>
       <c r="C1574">
-        <v>7079.6</v>
+        <v>3476.5</v>
       </c>
       <c r="D1574" t="s">
         <v>1576</v>
@@ -28194,7 +28770,7 @@
         <v>38</v>
       </c>
       <c r="C1575">
-        <v>7373.5</v>
+        <v>3529.5</v>
       </c>
       <c r="D1575" t="s">
         <v>1577</v>
@@ -28208,7 +28784,7 @@
         <v>39</v>
       </c>
       <c r="C1576">
-        <v>7142</v>
+        <v>3616.2</v>
       </c>
       <c r="D1576" t="s">
         <v>1578</v>
@@ -28222,7 +28798,7 @@
         <v>40</v>
       </c>
       <c r="C1577">
-        <v>6746.9</v>
+        <v>3704.8</v>
       </c>
       <c r="D1577" t="s">
         <v>1579</v>
@@ -28236,7 +28812,7 @@
         <v>41</v>
       </c>
       <c r="C1578">
-        <v>7646.5</v>
+        <v>3900.7</v>
       </c>
       <c r="D1578" t="s">
         <v>1580</v>
@@ -28250,7 +28826,7 @@
         <v>42</v>
       </c>
       <c r="C1579">
-        <v>7576.5</v>
+        <v>3929.9</v>
       </c>
       <c r="D1579" t="s">
         <v>1581</v>
@@ -28264,7 +28840,7 @@
         <v>43</v>
       </c>
       <c r="C1580">
-        <v>7456.9</v>
+        <v>3968.3</v>
       </c>
       <c r="D1580" t="s">
         <v>1582</v>
@@ -28278,7 +28854,7 @@
         <v>44</v>
       </c>
       <c r="C1581">
-        <v>7296.4</v>
+        <v>4027.5</v>
       </c>
       <c r="D1581" t="s">
         <v>1583</v>
@@ -28292,7 +28868,7 @@
         <v>45</v>
       </c>
       <c r="C1582">
-        <v>6748.3</v>
+        <v>4058</v>
       </c>
       <c r="D1582" t="s">
         <v>1584</v>
@@ -28306,7 +28882,7 @@
         <v>46</v>
       </c>
       <c r="C1583">
-        <v>6783.9</v>
+        <v>4083.3</v>
       </c>
       <c r="D1583" t="s">
         <v>1585</v>
@@ -28320,7 +28896,7 @@
         <v>47</v>
       </c>
       <c r="C1584">
-        <v>6036.5</v>
+        <v>4094.1</v>
       </c>
       <c r="D1584" t="s">
         <v>1586</v>
@@ -28334,7 +28910,7 @@
         <v>48</v>
       </c>
       <c r="C1585">
-        <v>4224.7</v>
+        <v>4140.1</v>
       </c>
       <c r="D1585" t="s">
         <v>1587</v>
@@ -28348,7 +28924,7 @@
         <v>49</v>
       </c>
       <c r="C1586">
-        <v>5921.1</v>
+        <v>3966.1</v>
       </c>
       <c r="D1586" t="s">
         <v>1588</v>
@@ -28362,7 +28938,7 @@
         <v>50</v>
       </c>
       <c r="C1587">
-        <v>4454</v>
+        <v>3958.2</v>
       </c>
       <c r="D1587" t="s">
         <v>1589</v>
@@ -28376,7 +28952,7 @@
         <v>51</v>
       </c>
       <c r="C1588">
-        <v>4419.4</v>
+        <v>3945.5</v>
       </c>
       <c r="D1588" t="s">
         <v>1590</v>
@@ -28390,7 +28966,7 @@
         <v>52</v>
       </c>
       <c r="C1589">
-        <v>3471.1</v>
+        <v>3950</v>
       </c>
       <c r="D1589" t="s">
         <v>1591</v>
@@ -28404,7 +28980,7 @@
         <v>53</v>
       </c>
       <c r="C1590">
-        <v>3171.7</v>
+        <v>3917.1</v>
       </c>
       <c r="D1590" t="s">
         <v>1592</v>
@@ -28418,7 +28994,7 @@
         <v>54</v>
       </c>
       <c r="C1591">
-        <v>3051</v>
+        <v>3888.4</v>
       </c>
       <c r="D1591" t="s">
         <v>1593</v>
@@ -28432,7 +29008,7 @@
         <v>55</v>
       </c>
       <c r="C1592">
-        <v>3149.3</v>
+        <v>3903.8</v>
       </c>
       <c r="D1592" t="s">
         <v>1594</v>
@@ -28446,7 +29022,7 @@
         <v>56</v>
       </c>
       <c r="C1593">
-        <v>3098.9</v>
+        <v>3918.2</v>
       </c>
       <c r="D1593" t="s">
         <v>1595</v>
@@ -28460,7 +29036,7 @@
         <v>57</v>
       </c>
       <c r="C1594">
-        <v>2825</v>
+        <v>3960.2</v>
       </c>
       <c r="D1594" t="s">
         <v>1596</v>
@@ -28474,7 +29050,7 @@
         <v>58</v>
       </c>
       <c r="C1595">
-        <v>2832.1</v>
+        <v>3937</v>
       </c>
       <c r="D1595" t="s">
         <v>1597</v>
@@ -28488,7 +29064,7 @@
         <v>59</v>
       </c>
       <c r="C1596">
-        <v>2864.6</v>
+        <v>3928</v>
       </c>
       <c r="D1596" t="s">
         <v>1598</v>
@@ -28502,7 +29078,7 @@
         <v>60</v>
       </c>
       <c r="C1597">
-        <v>2899.3</v>
+        <v>3955.1</v>
       </c>
       <c r="D1597" t="s">
         <v>1599</v>
@@ -28516,7 +29092,7 @@
         <v>61</v>
       </c>
       <c r="C1598">
-        <v>3475</v>
+        <v>3981.2</v>
       </c>
       <c r="D1598" t="s">
         <v>1600</v>
@@ -28530,7 +29106,7 @@
         <v>62</v>
       </c>
       <c r="C1599">
-        <v>3711.1</v>
+        <v>3916.4</v>
       </c>
       <c r="D1599" t="s">
         <v>1601</v>
@@ -28544,7 +29120,7 @@
         <v>63</v>
       </c>
       <c r="C1600">
-        <v>3646.4</v>
+        <v>3871.2</v>
       </c>
       <c r="D1600" t="s">
         <v>1602</v>
@@ -28558,7 +29134,7 @@
         <v>64</v>
       </c>
       <c r="C1601">
-        <v>3878.3</v>
+        <v>3880.3</v>
       </c>
       <c r="D1601" t="s">
         <v>1603</v>
@@ -28572,7 +29148,7 @@
         <v>65</v>
       </c>
       <c r="C1602">
-        <v>4089.6</v>
+        <v>3899.1</v>
       </c>
       <c r="D1602" t="s">
         <v>1604</v>
@@ -28586,7 +29162,7 @@
         <v>66</v>
       </c>
       <c r="C1603">
-        <v>4287.5</v>
+        <v>3860.3</v>
       </c>
       <c r="D1603" t="s">
         <v>1605</v>
@@ -28600,7 +29176,7 @@
         <v>67</v>
       </c>
       <c r="C1604">
-        <v>4433.9</v>
+        <v>3869.2</v>
       </c>
       <c r="D1604" t="s">
         <v>1606</v>
@@ -28614,7 +29190,7 @@
         <v>68</v>
       </c>
       <c r="C1605">
-        <v>4593.6</v>
+        <v>3850.9</v>
       </c>
       <c r="D1605" t="s">
         <v>1607</v>
@@ -28628,7 +29204,7 @@
         <v>69</v>
       </c>
       <c r="C1606">
-        <v>2990.4</v>
+        <v>3763.4</v>
       </c>
       <c r="D1606" t="s">
         <v>1608</v>
@@ -28642,7 +29218,7 @@
         <v>70</v>
       </c>
       <c r="C1607">
-        <v>5548.8</v>
+        <v>3698.8</v>
       </c>
       <c r="D1607" t="s">
         <v>1609</v>
@@ -28656,7 +29232,7 @@
         <v>71</v>
       </c>
       <c r="C1608">
-        <v>5750.7</v>
+        <v>3654.3</v>
       </c>
       <c r="D1608" t="s">
         <v>1610</v>
@@ -28670,7 +29246,7 @@
         <v>72</v>
       </c>
       <c r="C1609">
-        <v>6107.3</v>
+        <v>3578.9</v>
       </c>
       <c r="D1609" t="s">
         <v>1611</v>
@@ -28684,7 +29260,7 @@
         <v>73</v>
       </c>
       <c r="C1610">
-        <v>6382.7</v>
+        <v>4134.8</v>
       </c>
       <c r="D1610" t="s">
         <v>1612</v>
@@ -28698,7 +29274,7 @@
         <v>74</v>
       </c>
       <c r="C1611">
-        <v>6024.3</v>
+        <v>4035</v>
       </c>
       <c r="D1611" t="s">
         <v>1613</v>
@@ -28712,7 +29288,7 @@
         <v>75</v>
       </c>
       <c r="C1612">
-        <v>5885.2</v>
+        <v>3966.5</v>
       </c>
       <c r="D1612" t="s">
         <v>1614</v>
@@ -28726,7 +29302,7 @@
         <v>76</v>
       </c>
       <c r="C1613">
-        <v>5711.8</v>
+        <v>3935.9</v>
       </c>
       <c r="D1613" t="s">
         <v>1615</v>
@@ -28740,7 +29316,7 @@
         <v>77</v>
       </c>
       <c r="C1614">
-        <v>6118.9</v>
+        <v>3861.2</v>
       </c>
       <c r="D1614" t="s">
         <v>1616</v>
@@ -28754,7 +29330,7 @@
         <v>78</v>
       </c>
       <c r="C1615">
-        <v>6174.3</v>
+        <v>3889.7</v>
       </c>
       <c r="D1615" t="s">
         <v>1617</v>
@@ -28768,7 +29344,7 @@
         <v>79</v>
       </c>
       <c r="C1616">
-        <v>6476.5</v>
+        <v>3836.6</v>
       </c>
       <c r="D1616" t="s">
         <v>1618</v>
@@ -28782,7 +29358,7 @@
         <v>80</v>
       </c>
       <c r="C1617">
-        <v>6624.4</v>
+        <v>3819.2</v>
       </c>
       <c r="D1617" t="s">
         <v>1619</v>
@@ -28796,7 +29372,7 @@
         <v>81</v>
       </c>
       <c r="C1618">
-        <v>6294.8</v>
+        <v>3875.1</v>
       </c>
       <c r="D1618" t="s">
         <v>1620</v>
@@ -28810,7 +29386,7 @@
         <v>82</v>
       </c>
       <c r="C1619">
-        <v>6544.4</v>
+        <v>3906.2</v>
       </c>
       <c r="D1619" t="s">
         <v>1621</v>
@@ -28824,7 +29400,7 @@
         <v>83</v>
       </c>
       <c r="C1620">
-        <v>6770</v>
+        <v>3908.5</v>
       </c>
       <c r="D1620" t="s">
         <v>1622</v>
@@ -28838,7 +29414,7 @@
         <v>84</v>
       </c>
       <c r="C1621">
-        <v>6990.7</v>
+        <v>3900.7</v>
       </c>
       <c r="D1621" t="s">
         <v>1623</v>
@@ -28852,7 +29428,7 @@
         <v>85</v>
       </c>
       <c r="C1622">
-        <v>7027.2</v>
+        <v>3924.6</v>
       </c>
       <c r="D1622" t="s">
         <v>1624</v>
@@ -28866,7 +29442,7 @@
         <v>86</v>
       </c>
       <c r="C1623">
-        <v>7074.6</v>
+        <v>3902.3</v>
       </c>
       <c r="D1623" t="s">
         <v>1625</v>
@@ -28880,7 +29456,7 @@
         <v>87</v>
       </c>
       <c r="C1624">
-        <v>7022.4</v>
+        <v>3964.8</v>
       </c>
       <c r="D1624" t="s">
         <v>1626</v>
@@ -28894,7 +29470,7 @@
         <v>88</v>
       </c>
       <c r="C1625">
-        <v>6921.1</v>
+        <v>3963.5</v>
       </c>
       <c r="D1625" t="s">
         <v>1627</v>
@@ -28908,7 +29484,7 @@
         <v>89</v>
       </c>
       <c r="C1626">
-        <v>6564.7</v>
+        <v>3791.9</v>
       </c>
       <c r="D1626" t="s">
         <v>1628</v>
@@ -28922,7 +29498,7 @@
         <v>90</v>
       </c>
       <c r="C1627">
-        <v>6502.2</v>
+        <v>3823.7</v>
       </c>
       <c r="D1627" t="s">
         <v>1629</v>
@@ -28936,7 +29512,7 @@
         <v>91</v>
       </c>
       <c r="C1628">
-        <v>6382.8</v>
+        <v>3810.4</v>
       </c>
       <c r="D1628" t="s">
         <v>1630</v>
@@ -28950,7 +29526,7 @@
         <v>92</v>
       </c>
       <c r="C1629">
-        <v>6197.7</v>
+        <v>3873.1</v>
       </c>
       <c r="D1629" t="s">
         <v>1631</v>
@@ -28964,7 +29540,7 @@
         <v>93</v>
       </c>
       <c r="C1630">
-        <v>6055.4</v>
+        <v>3789.7</v>
       </c>
       <c r="D1630" t="s">
         <v>1632</v>
@@ -28978,7 +29554,7 @@
         <v>94</v>
       </c>
       <c r="C1631">
-        <v>5830.9</v>
+        <v>3765.6</v>
       </c>
       <c r="D1631" t="s">
         <v>1633</v>
@@ -28992,7 +29568,7 @@
         <v>95</v>
       </c>
       <c r="C1632">
-        <v>5577.8</v>
+        <v>3760.6</v>
       </c>
       <c r="D1632" t="s">
         <v>1634</v>
@@ -29006,7 +29582,7 @@
         <v>96</v>
       </c>
       <c r="C1633">
-        <v>5511</v>
+        <v>3802.5</v>
       </c>
       <c r="D1633" t="s">
         <v>1635</v>
@@ -29020,7 +29596,7 @@
         <v>1</v>
       </c>
       <c r="C1634">
-        <v>5983.6</v>
+        <v>5106</v>
       </c>
       <c r="D1634" t="s">
         <v>1636</v>
@@ -29034,7 +29610,7 @@
         <v>2</v>
       </c>
       <c r="C1635">
-        <v>5898.9</v>
+        <v>5096.2</v>
       </c>
       <c r="D1635" t="s">
         <v>1637</v>
@@ -29048,7 +29624,7 @@
         <v>3</v>
       </c>
       <c r="C1636">
-        <v>5798.4</v>
+        <v>4989.7</v>
       </c>
       <c r="D1636" t="s">
         <v>1638</v>
@@ -29062,7 +29638,7 @@
         <v>4</v>
       </c>
       <c r="C1637">
-        <v>5722.5</v>
+        <v>4867.7</v>
       </c>
       <c r="D1637" t="s">
         <v>1639</v>
@@ -29076,7 +29652,7 @@
         <v>5</v>
       </c>
       <c r="C1638">
-        <v>5150.7</v>
+        <v>4423.4</v>
       </c>
       <c r="D1638" t="s">
         <v>1640</v>
@@ -29090,7 +29666,7 @@
         <v>6</v>
       </c>
       <c r="C1639">
-        <v>5088.9</v>
+        <v>4388.2</v>
       </c>
       <c r="D1639" t="s">
         <v>1641</v>
@@ -29104,7 +29680,7 @@
         <v>7</v>
       </c>
       <c r="C1640">
-        <v>5064.6</v>
+        <v>4339.8</v>
       </c>
       <c r="D1640" t="s">
         <v>1642</v>
@@ -29118,7 +29694,7 @@
         <v>8</v>
       </c>
       <c r="C1641">
-        <v>4998.4</v>
+        <v>4304.3</v>
       </c>
       <c r="D1641" t="s">
         <v>1643</v>
@@ -29132,7 +29708,7 @@
         <v>9</v>
       </c>
       <c r="C1642">
-        <v>4854.2</v>
+        <v>4015.1</v>
       </c>
       <c r="D1642" t="s">
         <v>1644</v>
@@ -29146,7 +29722,7 @@
         <v>10</v>
       </c>
       <c r="C1643">
-        <v>4857.7</v>
+        <v>3994.8</v>
       </c>
       <c r="D1643" t="s">
         <v>1645</v>
@@ -29160,7 +29736,7 @@
         <v>11</v>
       </c>
       <c r="C1644">
-        <v>4829.9</v>
+        <v>3960.6</v>
       </c>
       <c r="D1644" t="s">
         <v>1646</v>
@@ -29174,7 +29750,7 @@
         <v>12</v>
       </c>
       <c r="C1645">
-        <v>4795.7</v>
+        <v>3961.4</v>
       </c>
       <c r="D1645" t="s">
         <v>1647</v>
@@ -29188,7 +29764,7 @@
         <v>13</v>
       </c>
       <c r="C1646">
-        <v>4687.3</v>
+        <v>3984</v>
       </c>
       <c r="D1646" t="s">
         <v>1648</v>
@@ -29202,7 +29778,7 @@
         <v>14</v>
       </c>
       <c r="C1647">
-        <v>4674.6</v>
+        <v>3971.1</v>
       </c>
       <c r="D1647" t="s">
         <v>1649</v>
@@ -29216,7 +29792,7 @@
         <v>15</v>
       </c>
       <c r="C1648">
-        <v>4724.8</v>
+        <v>3955.4</v>
       </c>
       <c r="D1648" t="s">
         <v>1650</v>
@@ -29230,7 +29806,7 @@
         <v>16</v>
       </c>
       <c r="C1649">
-        <v>4681.7</v>
+        <v>3935.9</v>
       </c>
       <c r="D1649" t="s">
         <v>1651</v>
@@ -29244,7 +29820,7 @@
         <v>17</v>
       </c>
       <c r="C1650">
-        <v>4643.5</v>
+        <v>3905.9</v>
       </c>
       <c r="D1650" t="s">
         <v>1652</v>
@@ -29258,7 +29834,7 @@
         <v>18</v>
       </c>
       <c r="C1651">
-        <v>4604.5</v>
+        <v>3869.2</v>
       </c>
       <c r="D1651" t="s">
         <v>1653</v>
@@ -29272,7 +29848,7 @@
         <v>19</v>
       </c>
       <c r="C1652">
-        <v>4554.1</v>
+        <v>3827.8</v>
       </c>
       <c r="D1652" t="s">
         <v>1654</v>
@@ -29286,7 +29862,7 @@
         <v>20</v>
       </c>
       <c r="C1653">
-        <v>4553.4</v>
+        <v>3803.5</v>
       </c>
       <c r="D1653" t="s">
         <v>1655</v>
@@ -29300,7 +29876,7 @@
         <v>21</v>
       </c>
       <c r="C1654">
-        <v>4537.1</v>
+        <v>3855.6</v>
       </c>
       <c r="D1654" t="s">
         <v>1656</v>
@@ -29314,7 +29890,7 @@
         <v>22</v>
       </c>
       <c r="C1655">
-        <v>4556.9</v>
+        <v>3875.6</v>
       </c>
       <c r="D1655" t="s">
         <v>1657</v>
@@ -29328,7 +29904,7 @@
         <v>23</v>
       </c>
       <c r="C1656">
-        <v>4571.2</v>
+        <v>3883.4</v>
       </c>
       <c r="D1656" t="s">
         <v>1658</v>
@@ -29342,7 +29918,7 @@
         <v>24</v>
       </c>
       <c r="C1657">
-        <v>4548.2</v>
+        <v>3896.6</v>
       </c>
       <c r="D1657" t="s">
         <v>1659</v>
@@ -29356,7 +29932,7 @@
         <v>25</v>
       </c>
       <c r="C1658">
-        <v>4702.6</v>
+        <v>3966.8</v>
       </c>
       <c r="D1658" t="s">
         <v>1660</v>
@@ -29370,7 +29946,7 @@
         <v>26</v>
       </c>
       <c r="C1659">
-        <v>4722.2</v>
+        <v>4031.3</v>
       </c>
       <c r="D1659" t="s">
         <v>1661</v>
@@ -29384,7 +29960,7 @@
         <v>27</v>
       </c>
       <c r="C1660">
-        <v>4748</v>
+        <v>4103.1</v>
       </c>
       <c r="D1660" t="s">
         <v>1662</v>
@@ -29398,7 +29974,7 @@
         <v>28</v>
       </c>
       <c r="C1661">
-        <v>4781.3</v>
+        <v>4146.4</v>
       </c>
       <c r="D1661" t="s">
         <v>1663</v>
@@ -29412,7 +29988,7 @@
         <v>29</v>
       </c>
       <c r="C1662">
-        <v>4777.3</v>
+        <v>4200.9</v>
       </c>
       <c r="D1662" t="s">
         <v>1664</v>
@@ -29426,7 +30002,7 @@
         <v>30</v>
       </c>
       <c r="C1663">
-        <v>4866.1</v>
+        <v>4236.5</v>
       </c>
       <c r="D1663" t="s">
         <v>1665</v>
@@ -29440,7 +30016,7 @@
         <v>31</v>
       </c>
       <c r="C1664">
-        <v>5024.3</v>
+        <v>4362.3</v>
       </c>
       <c r="D1664" t="s">
         <v>1666</v>
@@ -29454,7 +30030,7 @@
         <v>32</v>
       </c>
       <c r="C1665">
-        <v>5159.7</v>
+        <v>4489.7</v>
       </c>
       <c r="D1665" t="s">
         <v>1667</v>
@@ -29468,7 +30044,7 @@
         <v>33</v>
       </c>
       <c r="C1666">
-        <v>5087.8</v>
+        <v>4421.3</v>
       </c>
       <c r="D1666" t="s">
         <v>1668</v>
@@ -29482,7 +30058,7 @@
         <v>34</v>
       </c>
       <c r="C1667">
-        <v>5266.6</v>
+        <v>4523</v>
       </c>
       <c r="D1667" t="s">
         <v>1669</v>
@@ -29496,7 +30072,7 @@
         <v>35</v>
       </c>
       <c r="C1668">
-        <v>5407</v>
+        <v>4619.6</v>
       </c>
       <c r="D1668" t="s">
         <v>1670</v>
@@ -29510,7 +30086,7 @@
         <v>36</v>
       </c>
       <c r="C1669">
-        <v>5632.8</v>
+        <v>4794.8</v>
       </c>
       <c r="D1669" t="s">
         <v>1671</v>
@@ -29524,7 +30100,7 @@
         <v>37</v>
       </c>
       <c r="C1670">
-        <v>5618.9</v>
+        <v>4696.5</v>
       </c>
       <c r="D1670" t="s">
         <v>1672</v>
@@ -29538,7 +30114,7 @@
         <v>38</v>
       </c>
       <c r="C1671">
-        <v>5667.8</v>
+        <v>4729.5</v>
       </c>
       <c r="D1671" t="s">
         <v>1673</v>
@@ -29552,7 +30128,7 @@
         <v>39</v>
       </c>
       <c r="C1672">
-        <v>5780.8</v>
+        <v>4796.2</v>
       </c>
       <c r="D1672" t="s">
         <v>1674</v>
@@ -29566,7 +30142,7 @@
         <v>40</v>
       </c>
       <c r="C1673">
-        <v>5863.6</v>
+        <v>4864.8</v>
       </c>
       <c r="D1673" t="s">
         <v>1675</v>
@@ -29580,7 +30156,7 @@
         <v>41</v>
       </c>
       <c r="C1674">
-        <v>5687.9</v>
+        <v>5030.7</v>
       </c>
       <c r="D1674" t="s">
         <v>1676</v>
@@ -29594,7 +30170,7 @@
         <v>42</v>
       </c>
       <c r="C1675">
-        <v>5700.8</v>
+        <v>5019.9</v>
       </c>
       <c r="D1675" t="s">
         <v>1677</v>
@@ -29608,7 +30184,7 @@
         <v>43</v>
       </c>
       <c r="C1676">
-        <v>5753.5</v>
+        <v>5018.3</v>
       </c>
       <c r="D1676" t="s">
         <v>1678</v>
@@ -29622,7 +30198,7 @@
         <v>44</v>
       </c>
       <c r="C1677">
-        <v>5823.7</v>
+        <v>5017.5</v>
       </c>
       <c r="D1677" t="s">
         <v>1679</v>
@@ -29636,7 +30212,7 @@
         <v>45</v>
       </c>
       <c r="C1678">
-        <v>5459.9</v>
+        <v>4998</v>
       </c>
       <c r="D1678" t="s">
         <v>1680</v>
@@ -29650,7 +30226,7 @@
         <v>46</v>
       </c>
       <c r="C1679">
-        <v>5552.5</v>
+        <v>4973.3</v>
       </c>
       <c r="D1679" t="s">
         <v>1681</v>
@@ -29664,7 +30240,7 @@
         <v>47</v>
       </c>
       <c r="C1680">
-        <v>5611.6</v>
+        <v>4924.1</v>
       </c>
       <c r="D1680" t="s">
         <v>1682</v>
@@ -29678,7 +30254,7 @@
         <v>48</v>
       </c>
       <c r="C1681">
-        <v>5609.1</v>
+        <v>4910.1</v>
       </c>
       <c r="D1681" t="s">
         <v>1683</v>
@@ -29692,7 +30268,7 @@
         <v>49</v>
       </c>
       <c r="C1682">
-        <v>5464</v>
+        <v>4686.1</v>
       </c>
       <c r="D1682" t="s">
         <v>1684</v>
@@ -29706,7 +30282,7 @@
         <v>50</v>
       </c>
       <c r="C1683">
-        <v>5238.7</v>
+        <v>4628.2</v>
       </c>
       <c r="D1683" t="s">
         <v>1685</v>
@@ -29720,7 +30296,7 @@
         <v>51</v>
       </c>
       <c r="C1684">
-        <v>4660.3</v>
+        <v>4585.5</v>
       </c>
       <c r="D1684" t="s">
         <v>1686</v>
@@ -29734,7 +30310,7 @@
         <v>52</v>
       </c>
       <c r="C1685">
-        <v>4661.4</v>
+        <v>4570</v>
       </c>
       <c r="D1685" t="s">
         <v>1687</v>
@@ -29748,7 +30324,7 @@
         <v>53</v>
       </c>
       <c r="C1686">
-        <v>4597.4</v>
+        <v>4517.1</v>
       </c>
       <c r="D1686" t="s">
         <v>1688</v>
@@ -29762,7 +30338,7 @@
         <v>54</v>
       </c>
       <c r="C1687">
-        <v>4564.2</v>
+        <v>4488.4</v>
       </c>
       <c r="D1687" t="s">
         <v>1689</v>
@@ -29776,7 +30352,7 @@
         <v>55</v>
       </c>
       <c r="C1688">
-        <v>4582.1</v>
+        <v>4513.8</v>
       </c>
       <c r="D1688" t="s">
         <v>1690</v>
@@ -29790,7 +30366,7 @@
         <v>56</v>
       </c>
       <c r="C1689">
-        <v>4524.6</v>
+        <v>4528.2</v>
       </c>
       <c r="D1689" t="s">
         <v>1691</v>
@@ -29804,7 +30380,7 @@
         <v>57</v>
       </c>
       <c r="C1690">
-        <v>4573.6</v>
+        <v>4590.2</v>
       </c>
       <c r="D1690" t="s">
         <v>1692</v>
@@ -29818,7 +30394,7 @@
         <v>58</v>
       </c>
       <c r="C1691">
-        <v>4632.5</v>
+        <v>4587</v>
       </c>
       <c r="D1691" t="s">
         <v>1693</v>
@@ -29832,7 +30408,7 @@
         <v>59</v>
       </c>
       <c r="C1692">
-        <v>4634.2</v>
+        <v>4588</v>
       </c>
       <c r="D1692" t="s">
         <v>1694</v>
@@ -29846,7 +30422,7 @@
         <v>60</v>
       </c>
       <c r="C1693">
-        <v>4650.3</v>
+        <v>4625.1</v>
       </c>
       <c r="D1693" t="s">
         <v>1695</v>
@@ -29860,7 +30436,7 @@
         <v>61</v>
       </c>
       <c r="C1694">
-        <v>4664.6</v>
+        <v>4661.2</v>
       </c>
       <c r="D1694" t="s">
         <v>1696</v>
@@ -29874,7 +30450,7 @@
         <v>62</v>
       </c>
       <c r="C1695">
-        <v>4756.9</v>
+        <v>4616.4</v>
       </c>
       <c r="D1695" t="s">
         <v>1697</v>
@@ -29888,7 +30464,7 @@
         <v>63</v>
       </c>
       <c r="C1696">
-        <v>4780.7</v>
+        <v>4571.2</v>
       </c>
       <c r="D1696" t="s">
         <v>1698</v>
@@ -29902,7 +30478,7 @@
         <v>64</v>
       </c>
       <c r="C1697">
-        <v>4792.3</v>
+        <v>4580.3</v>
       </c>
       <c r="D1697" t="s">
         <v>1699</v>
@@ -29916,7 +30492,7 @@
         <v>65</v>
       </c>
       <c r="C1698">
-        <v>4845.5</v>
+        <v>4609.1</v>
       </c>
       <c r="D1698" t="s">
         <v>1700</v>
@@ -29930,7 +30506,7 @@
         <v>66</v>
       </c>
       <c r="C1699">
-        <v>4852.8</v>
+        <v>4560.3</v>
       </c>
       <c r="D1699" t="s">
         <v>1701</v>
@@ -29944,7 +30520,7 @@
         <v>67</v>
       </c>
       <c r="C1700">
-        <v>5311.7</v>
+        <v>4549.2</v>
       </c>
       <c r="D1700" t="s">
         <v>1702</v>
@@ -29958,7 +30534,7 @@
         <v>68</v>
       </c>
       <c r="C1701">
-        <v>5453.2</v>
+        <v>4510.9</v>
       </c>
       <c r="D1701" t="s">
         <v>1703</v>
@@ -29972,7 +30548,7 @@
         <v>69</v>
       </c>
       <c r="C1702">
-        <v>5809.2</v>
+        <v>4413.4</v>
       </c>
       <c r="D1702" t="s">
         <v>1704</v>
@@ -29986,7 +30562,7 @@
         <v>70</v>
       </c>
       <c r="C1703">
-        <v>5715.5</v>
+        <v>4338.8</v>
       </c>
       <c r="D1703" t="s">
         <v>1705</v>
@@ -30000,7 +30576,7 @@
         <v>71</v>
       </c>
       <c r="C1704">
-        <v>5569.7</v>
+        <v>4294.3</v>
       </c>
       <c r="D1704" t="s">
         <v>1706</v>
@@ -30014,7 +30590,7 @@
         <v>72</v>
       </c>
       <c r="C1705">
-        <v>5370.9</v>
+        <v>4238.9</v>
       </c>
       <c r="D1705" t="s">
         <v>1707</v>
@@ -30028,7 +30604,7 @@
         <v>73</v>
       </c>
       <c r="C1706">
-        <v>5730.7</v>
+        <v>4814.8</v>
       </c>
       <c r="D1706" t="s">
         <v>1708</v>
@@ -30042,7 +30618,7 @@
         <v>74</v>
       </c>
       <c r="C1707">
-        <v>5565</v>
+        <v>4745</v>
       </c>
       <c r="D1707" t="s">
         <v>1709</v>
@@ -30056,7 +30632,7 @@
         <v>75</v>
       </c>
       <c r="C1708">
-        <v>5513.9</v>
+        <v>4716.5</v>
       </c>
       <c r="D1708" t="s">
         <v>1710</v>
@@ -30070,7 +30646,7 @@
         <v>76</v>
       </c>
       <c r="C1709">
-        <v>5370.7</v>
+        <v>4715.9</v>
       </c>
       <c r="D1709" t="s">
         <v>1711</v>
@@ -30084,7 +30660,7 @@
         <v>77</v>
       </c>
       <c r="C1710">
-        <v>5854.6</v>
+        <v>4651.2</v>
       </c>
       <c r="D1710" t="s">
         <v>1712</v>
@@ -30098,7 +30674,7 @@
         <v>78</v>
       </c>
       <c r="C1711">
-        <v>5806.1</v>
+        <v>4689.7</v>
       </c>
       <c r="D1711" t="s">
         <v>1713</v>
@@ -30112,7 +30688,7 @@
         <v>79</v>
       </c>
       <c r="C1712">
-        <v>5815.1</v>
+        <v>4636.6</v>
       </c>
       <c r="D1712" t="s">
         <v>1714</v>
@@ -30126,7 +30702,7 @@
         <v>80</v>
       </c>
       <c r="C1713">
-        <v>5814.1</v>
+        <v>4609.2</v>
       </c>
       <c r="D1713" t="s">
         <v>1715</v>
@@ -30140,7 +30716,7 @@
         <v>81</v>
       </c>
       <c r="C1714">
-        <v>6083</v>
+        <v>4675.1</v>
       </c>
       <c r="D1714" t="s">
         <v>1716</v>
@@ -30154,7 +30730,7 @@
         <v>82</v>
       </c>
       <c r="C1715">
-        <v>6104.8</v>
+        <v>4716.2</v>
       </c>
       <c r="D1715" t="s">
         <v>1717</v>
@@ -30168,7 +30744,7 @@
         <v>83</v>
       </c>
       <c r="C1716">
-        <v>6162.7</v>
+        <v>4758.5</v>
       </c>
       <c r="D1716" t="s">
         <v>1718</v>
@@ -30182,7 +30758,7 @@
         <v>84</v>
       </c>
       <c r="C1717">
-        <v>6266.4</v>
+        <v>4800.7</v>
       </c>
       <c r="D1717" t="s">
         <v>1719</v>
@@ -30196,7 +30772,7 @@
         <v>85</v>
       </c>
       <c r="C1718">
-        <v>6621.1</v>
+        <v>4824.6</v>
       </c>
       <c r="D1718" t="s">
         <v>1720</v>
@@ -30210,7 +30786,7 @@
         <v>86</v>
       </c>
       <c r="C1719">
-        <v>6628.2</v>
+        <v>4812.3</v>
       </c>
       <c r="D1719" t="s">
         <v>1721</v>
@@ -30224,7 +30800,7 @@
         <v>87</v>
       </c>
       <c r="C1720">
-        <v>6677.8</v>
+        <v>4864.8</v>
       </c>
       <c r="D1720" t="s">
         <v>1722</v>
@@ -30238,7 +30814,7 @@
         <v>88</v>
       </c>
       <c r="C1721">
-        <v>6658.2</v>
+        <v>4803.5</v>
       </c>
       <c r="D1721" t="s">
         <v>1723</v>
@@ -30252,7 +30828,7 @@
         <v>89</v>
       </c>
       <c r="C1722">
-        <v>6429.5</v>
+        <v>4581.9</v>
       </c>
       <c r="D1722" t="s">
         <v>1724</v>
@@ -30266,7 +30842,7 @@
         <v>90</v>
       </c>
       <c r="C1723">
-        <v>6399</v>
+        <v>4573.7</v>
       </c>
       <c r="D1723" t="s">
         <v>1725</v>
@@ -30280,7 +30856,7 @@
         <v>91</v>
       </c>
       <c r="C1724">
-        <v>6367.6</v>
+        <v>4540.4</v>
       </c>
       <c r="D1724" t="s">
         <v>1726</v>
@@ -30294,7 +30870,7 @@
         <v>92</v>
       </c>
       <c r="C1725">
-        <v>6297.5</v>
+        <v>4563.1</v>
       </c>
       <c r="D1725" t="s">
         <v>1727</v>
@@ -30308,7 +30884,7 @@
         <v>93</v>
       </c>
       <c r="C1726">
-        <v>6268.1</v>
+        <v>4399.7</v>
       </c>
       <c r="D1726" t="s">
         <v>1728</v>
@@ -30322,7 +30898,7 @@
         <v>94</v>
       </c>
       <c r="C1727">
-        <v>6196.9</v>
+        <v>4295.6</v>
       </c>
       <c r="D1727" t="s">
         <v>1729</v>
@@ -30336,7 +30912,7 @@
         <v>95</v>
       </c>
       <c r="C1728">
-        <v>6153.6</v>
+        <v>4330.6</v>
       </c>
       <c r="D1728" t="s">
         <v>1730</v>
@@ -30350,7 +30926,7 @@
         <v>96</v>
       </c>
       <c r="C1729">
-        <v>6077</v>
+        <v>4362.5</v>
       </c>
       <c r="D1729" t="s">
         <v>1731</v>
@@ -30364,7 +30940,7 @@
         <v>1</v>
       </c>
       <c r="C1730">
-        <v>6523.6</v>
+        <v>5566</v>
       </c>
       <c r="D1730" t="s">
         <v>1732</v>
@@ -30378,7 +30954,7 @@
         <v>2</v>
       </c>
       <c r="C1731">
-        <v>6478.9</v>
+        <v>5556.2</v>
       </c>
       <c r="D1731" t="s">
         <v>1733</v>
@@ -30392,7 +30968,7 @@
         <v>3</v>
       </c>
       <c r="C1732">
-        <v>6368.4</v>
+        <v>5449.7</v>
       </c>
       <c r="D1732" t="s">
         <v>1734</v>
@@ -30406,7 +30982,7 @@
         <v>4</v>
       </c>
       <c r="C1733">
-        <v>6252.5</v>
+        <v>5327.7</v>
       </c>
       <c r="D1733" t="s">
         <v>1735</v>
@@ -30420,7 +30996,7 @@
         <v>5</v>
       </c>
       <c r="C1734">
-        <v>5670.7</v>
+        <v>4883.4</v>
       </c>
       <c r="D1734" t="s">
         <v>1736</v>
@@ -30434,7 +31010,7 @@
         <v>6</v>
       </c>
       <c r="C1735">
-        <v>5598.9</v>
+        <v>4848.2</v>
       </c>
       <c r="D1735" t="s">
         <v>1737</v>
@@ -30448,7 +31024,7 @@
         <v>7</v>
       </c>
       <c r="C1736">
-        <v>5564.6</v>
+        <v>4799.8</v>
       </c>
       <c r="D1736" t="s">
         <v>1738</v>
@@ -30462,7 +31038,7 @@
         <v>8</v>
       </c>
       <c r="C1737">
-        <v>5478.4</v>
+        <v>4754.3</v>
       </c>
       <c r="D1737" t="s">
         <v>1739</v>
@@ -30476,7 +31052,7 @@
         <v>9</v>
       </c>
       <c r="C1738">
-        <v>5324.2</v>
+        <v>4465.1</v>
       </c>
       <c r="D1738" t="s">
         <v>1740</v>
@@ -30490,7 +31066,7 @@
         <v>10</v>
       </c>
       <c r="C1739">
-        <v>5317.7</v>
+        <v>4434.8</v>
       </c>
       <c r="D1739" t="s">
         <v>1741</v>
@@ -30504,7 +31080,7 @@
         <v>11</v>
       </c>
       <c r="C1740">
-        <v>5289.9</v>
+        <v>4410.6</v>
       </c>
       <c r="D1740" t="s">
         <v>1742</v>
@@ -30518,7 +31094,7 @@
         <v>12</v>
       </c>
       <c r="C1741">
-        <v>5245.7</v>
+        <v>4411.4</v>
       </c>
       <c r="D1741" t="s">
         <v>1743</v>
@@ -30532,7 +31108,7 @@
         <v>13</v>
       </c>
       <c r="C1742">
-        <v>5147.3</v>
+        <v>4434</v>
       </c>
       <c r="D1742" t="s">
         <v>1744</v>
@@ -30546,7 +31122,7 @@
         <v>14</v>
       </c>
       <c r="C1743">
-        <v>5124.6</v>
+        <v>4421.1</v>
       </c>
       <c r="D1743" t="s">
         <v>1745</v>
@@ -30560,7 +31136,7 @@
         <v>15</v>
       </c>
       <c r="C1744">
-        <v>5184.8</v>
+        <v>4405.4</v>
       </c>
       <c r="D1744" t="s">
         <v>1746</v>
@@ -30574,7 +31150,7 @@
         <v>16</v>
       </c>
       <c r="C1745">
-        <v>5121.7</v>
+        <v>4375.9</v>
       </c>
       <c r="D1745" t="s">
         <v>1747</v>
@@ -30588,7 +31164,7 @@
         <v>17</v>
       </c>
       <c r="C1746">
-        <v>5083.5</v>
+        <v>4345.9</v>
       </c>
       <c r="D1746" t="s">
         <v>1748</v>
@@ -30602,7 +31178,7 @@
         <v>18</v>
       </c>
       <c r="C1747">
-        <v>5024.5</v>
+        <v>4299.2</v>
       </c>
       <c r="D1747" t="s">
         <v>1749</v>
@@ -30616,7 +31192,7 @@
         <v>19</v>
       </c>
       <c r="C1748">
-        <v>4964.1</v>
+        <v>4247.8</v>
       </c>
       <c r="D1748" t="s">
         <v>1750</v>
@@ -30630,7 +31206,7 @@
         <v>20</v>
       </c>
       <c r="C1749">
-        <v>4943.4</v>
+        <v>4213.5</v>
       </c>
       <c r="D1749" t="s">
         <v>1751</v>
@@ -30644,7 +31220,7 @@
         <v>21</v>
       </c>
       <c r="C1750">
-        <v>4907.1</v>
+        <v>4245.6</v>
       </c>
       <c r="D1750" t="s">
         <v>1752</v>
@@ -30658,7 +31234,7 @@
         <v>22</v>
       </c>
       <c r="C1751">
-        <v>4896.9</v>
+        <v>4235.6</v>
       </c>
       <c r="D1751" t="s">
         <v>1753</v>
@@ -30672,7 +31248,7 @@
         <v>23</v>
       </c>
       <c r="C1752">
-        <v>4891.2</v>
+        <v>4213.4</v>
       </c>
       <c r="D1752" t="s">
         <v>1754</v>
@@ -30686,7 +31262,7 @@
         <v>24</v>
       </c>
       <c r="C1753">
-        <v>4848.2</v>
+        <v>4196.6</v>
       </c>
       <c r="D1753" t="s">
         <v>1755</v>
@@ -30700,7 +31276,7 @@
         <v>25</v>
       </c>
       <c r="C1754">
-        <v>4982.6</v>
+        <v>4236.8</v>
       </c>
       <c r="D1754" t="s">
         <v>1756</v>
@@ -30714,7 +31290,7 @@
         <v>26</v>
       </c>
       <c r="C1755">
-        <v>4992.2</v>
+        <v>4271.3</v>
       </c>
       <c r="D1755" t="s">
         <v>1757</v>
@@ -30728,7 +31304,7 @@
         <v>27</v>
       </c>
       <c r="C1756">
-        <v>4998</v>
+        <v>4313.1</v>
       </c>
       <c r="D1756" t="s">
         <v>1758</v>
@@ -30742,7 +31318,7 @@
         <v>28</v>
       </c>
       <c r="C1757">
-        <v>5011.3</v>
+        <v>4326.4</v>
       </c>
       <c r="D1757" t="s">
         <v>1759</v>
@@ -30756,7 +31332,7 @@
         <v>29</v>
       </c>
       <c r="C1758">
-        <v>4997.3</v>
+        <v>4360.9</v>
       </c>
       <c r="D1758" t="s">
         <v>1760</v>
@@ -30770,7 +31346,7 @@
         <v>30</v>
       </c>
       <c r="C1759">
-        <v>5076.1</v>
+        <v>4376.5</v>
       </c>
       <c r="D1759" t="s">
         <v>1761</v>
@@ -30784,7 +31360,7 @@
         <v>31</v>
       </c>
       <c r="C1760">
-        <v>5224.3</v>
+        <v>4482.3</v>
       </c>
       <c r="D1760" t="s">
         <v>1762</v>
@@ -30798,7 +31374,7 @@
         <v>32</v>
       </c>
       <c r="C1761">
-        <v>5359.7</v>
+        <v>4589.7</v>
       </c>
       <c r="D1761" t="s">
         <v>1763</v>
@@ -30812,7 +31388,7 @@
         <v>33</v>
       </c>
       <c r="C1762">
-        <v>5287.8</v>
+        <v>4501.3</v>
       </c>
       <c r="D1762" t="s">
         <v>1764</v>
@@ -30826,7 +31402,7 @@
         <v>34</v>
       </c>
       <c r="C1763">
-        <v>5466.6</v>
+        <v>4593</v>
       </c>
       <c r="D1763" t="s">
         <v>1765</v>
@@ -30840,7 +31416,7 @@
         <v>35</v>
       </c>
       <c r="C1764">
-        <v>5627</v>
+        <v>4669.6</v>
       </c>
       <c r="D1764" t="s">
         <v>1766</v>
@@ -30854,7 +31430,7 @@
         <v>36</v>
       </c>
       <c r="C1765">
-        <v>5872.8</v>
+        <v>4824.8</v>
       </c>
       <c r="D1765" t="s">
         <v>1767</v>
@@ -30868,7 +31444,7 @@
         <v>37</v>
       </c>
       <c r="C1766">
-        <v>5878.9</v>
+        <v>4686.5</v>
       </c>
       <c r="D1766" t="s">
         <v>1768</v>
@@ -30882,7 +31458,7 @@
         <v>38</v>
       </c>
       <c r="C1767">
-        <v>5947.8</v>
+        <v>4689.5</v>
       </c>
       <c r="D1767" t="s">
         <v>1769</v>
@@ -30896,7 +31472,7 @@
         <v>39</v>
       </c>
       <c r="C1768">
-        <v>6080.8</v>
+        <v>4726.2</v>
       </c>
       <c r="D1768" t="s">
         <v>1770</v>
@@ -30910,7 +31486,7 @@
         <v>40</v>
       </c>
       <c r="C1769">
-        <v>6183.6</v>
+        <v>4764.8</v>
       </c>
       <c r="D1769" t="s">
         <v>1771</v>
@@ -30924,7 +31500,7 @@
         <v>41</v>
       </c>
       <c r="C1770">
-        <v>6017.9</v>
+        <v>4920.7</v>
       </c>
       <c r="D1770" t="s">
         <v>1772</v>
@@ -30938,7 +31514,7 @@
         <v>42</v>
       </c>
       <c r="C1771">
-        <v>6040.8</v>
+        <v>4889.9</v>
       </c>
       <c r="D1771" t="s">
         <v>1773</v>
@@ -30952,7 +31528,7 @@
         <v>43</v>
       </c>
       <c r="C1772">
-        <v>6083.5</v>
+        <v>4888.3</v>
       </c>
       <c r="D1772" t="s">
         <v>1774</v>
@@ -30966,7 +31542,7 @@
         <v>44</v>
       </c>
       <c r="C1773">
-        <v>6133.7</v>
+        <v>4907.5</v>
       </c>
       <c r="D1773" t="s">
         <v>1775</v>
@@ -30980,7 +31556,7 @@
         <v>45</v>
       </c>
       <c r="C1774">
-        <v>5749.9</v>
+        <v>4898</v>
       </c>
       <c r="D1774" t="s">
         <v>1776</v>
@@ -30994,7 +31570,7 @@
         <v>46</v>
       </c>
       <c r="C1775">
-        <v>5822.5</v>
+        <v>4883.3</v>
       </c>
       <c r="D1775" t="s">
         <v>1777</v>
@@ -31008,7 +31584,7 @@
         <v>47</v>
       </c>
       <c r="C1776">
-        <v>5861.6</v>
+        <v>4864.1</v>
       </c>
       <c r="D1776" t="s">
         <v>1778</v>
@@ -31022,7 +31598,7 @@
         <v>48</v>
       </c>
       <c r="C1777">
-        <v>5839.1</v>
+        <v>4880.1</v>
       </c>
       <c r="D1777" t="s">
         <v>1779</v>
@@ -31036,7 +31612,7 @@
         <v>49</v>
       </c>
       <c r="C1778">
-        <v>5674</v>
+        <v>4686.1</v>
       </c>
       <c r="D1778" t="s">
         <v>1780</v>
@@ -31050,7 +31626,7 @@
         <v>50</v>
       </c>
       <c r="C1779">
-        <v>5448.7</v>
+        <v>4658.2</v>
       </c>
       <c r="D1779" t="s">
         <v>1781</v>
@@ -31064,7 +31640,7 @@
         <v>51</v>
       </c>
       <c r="C1780">
-        <v>4870.3</v>
+        <v>4625.5</v>
       </c>
       <c r="D1780" t="s">
         <v>1782</v>
@@ -31078,7 +31654,7 @@
         <v>52</v>
       </c>
       <c r="C1781">
-        <v>4881.4</v>
+        <v>4630</v>
       </c>
       <c r="D1781" t="s">
         <v>1783</v>
@@ -31092,7 +31668,7 @@
         <v>53</v>
       </c>
       <c r="C1782">
-        <v>4827.4</v>
+        <v>4587.1</v>
       </c>
       <c r="D1782" t="s">
         <v>1784</v>
@@ -31106,7 +31682,7 @@
         <v>54</v>
       </c>
       <c r="C1783">
-        <v>4804.2</v>
+        <v>4568.4</v>
       </c>
       <c r="D1783" t="s">
         <v>1785</v>
@@ -31120,7 +31696,7 @@
         <v>55</v>
       </c>
       <c r="C1784">
-        <v>4832.1</v>
+        <v>4583.8</v>
       </c>
       <c r="D1784" t="s">
         <v>1786</v>
@@ -31134,7 +31710,7 @@
         <v>56</v>
       </c>
       <c r="C1785">
-        <v>4774.6</v>
+        <v>4598.2</v>
       </c>
       <c r="D1785" t="s">
         <v>1787</v>
@@ -31148,7 +31724,7 @@
         <v>57</v>
       </c>
       <c r="C1786">
-        <v>4813.6</v>
+        <v>4650.2</v>
       </c>
       <c r="D1786" t="s">
         <v>1788</v>
@@ -31162,7 +31738,7 @@
         <v>58</v>
       </c>
       <c r="C1787">
-        <v>4862.5</v>
+        <v>4647</v>
       </c>
       <c r="D1787" t="s">
         <v>1789</v>
@@ -31176,7 +31752,7 @@
         <v>59</v>
       </c>
       <c r="C1788">
-        <v>4844.2</v>
+        <v>4658</v>
       </c>
       <c r="D1788" t="s">
         <v>1790</v>
@@ -31190,7 +31766,7 @@
         <v>60</v>
       </c>
       <c r="C1789">
-        <v>4850.3</v>
+        <v>4695.1</v>
       </c>
       <c r="D1789" t="s">
         <v>1791</v>
@@ -31204,7 +31780,7 @@
         <v>61</v>
       </c>
       <c r="C1790">
-        <v>4844.6</v>
+        <v>4741.2</v>
       </c>
       <c r="D1790" t="s">
         <v>1792</v>
@@ -31218,7 +31794,7 @@
         <v>62</v>
       </c>
       <c r="C1791">
-        <v>4926.9</v>
+        <v>4696.4</v>
       </c>
       <c r="D1791" t="s">
         <v>1793</v>
@@ -31232,7 +31808,7 @@
         <v>63</v>
       </c>
       <c r="C1792">
-        <v>4940.7</v>
+        <v>4661.2</v>
       </c>
       <c r="D1792" t="s">
         <v>1794</v>
@@ -31246,7 +31822,7 @@
         <v>64</v>
       </c>
       <c r="C1793">
-        <v>4942.3</v>
+        <v>4680.3</v>
       </c>
       <c r="D1793" t="s">
         <v>1795</v>
@@ -31260,7 +31836,7 @@
         <v>65</v>
       </c>
       <c r="C1794">
-        <v>4985.5</v>
+        <v>4709.1</v>
       </c>
       <c r="D1794" t="s">
         <v>1796</v>
@@ -31274,7 +31850,7 @@
         <v>66</v>
       </c>
       <c r="C1795">
-        <v>4982.8</v>
+        <v>4670.3</v>
       </c>
       <c r="D1795" t="s">
         <v>1797</v>
@@ -31288,7 +31864,7 @@
         <v>67</v>
       </c>
       <c r="C1796">
-        <v>5411.7</v>
+        <v>4659.2</v>
       </c>
       <c r="D1796" t="s">
         <v>1798</v>
@@ -31302,7 +31878,7 @@
         <v>68</v>
       </c>
       <c r="C1797">
-        <v>5543.2</v>
+        <v>4620.9</v>
       </c>
       <c r="D1797" t="s">
         <v>1799</v>
@@ -31316,7 +31892,7 @@
         <v>69</v>
       </c>
       <c r="C1798">
-        <v>5869.2</v>
+        <v>4523.4</v>
       </c>
       <c r="D1798" t="s">
         <v>1800</v>
@@ -31330,7 +31906,7 @@
         <v>70</v>
       </c>
       <c r="C1799">
-        <v>5745.5</v>
+        <v>4448.8</v>
       </c>
       <c r="D1799" t="s">
         <v>1801</v>
@@ -31344,7 +31920,7 @@
         <v>71</v>
       </c>
       <c r="C1800">
-        <v>5579.7</v>
+        <v>4394.3</v>
       </c>
       <c r="D1800" t="s">
         <v>1802</v>
@@ -31358,7 +31934,7 @@
         <v>72</v>
       </c>
       <c r="C1801">
-        <v>5360.9</v>
+        <v>4328.9</v>
       </c>
       <c r="D1801" t="s">
         <v>1803</v>
@@ -31372,7 +31948,7 @@
         <v>73</v>
       </c>
       <c r="C1802">
-        <v>5720.7</v>
+        <v>4904.8</v>
       </c>
       <c r="D1802" t="s">
         <v>1804</v>
@@ -31386,7 +31962,7 @@
         <v>74</v>
       </c>
       <c r="C1803">
-        <v>5565</v>
+        <v>4825</v>
       </c>
       <c r="D1803" t="s">
         <v>1805</v>
@@ -31400,7 +31976,7 @@
         <v>75</v>
       </c>
       <c r="C1804">
-        <v>5523.9</v>
+        <v>4786.5</v>
       </c>
       <c r="D1804" t="s">
         <v>1806</v>
@@ -31414,7 +31990,7 @@
         <v>76</v>
       </c>
       <c r="C1805">
-        <v>5390.7</v>
+        <v>4775.9</v>
       </c>
       <c r="D1805" t="s">
         <v>1807</v>
@@ -31428,7 +32004,7 @@
         <v>77</v>
       </c>
       <c r="C1806">
-        <v>5894.6</v>
+        <v>4711.2</v>
       </c>
       <c r="D1806" t="s">
         <v>1808</v>
@@ -31442,7 +32018,7 @@
         <v>78</v>
       </c>
       <c r="C1807">
-        <v>5866.1</v>
+        <v>4739.7</v>
       </c>
       <c r="D1807" t="s">
         <v>1809</v>
@@ -31456,7 +32032,7 @@
         <v>79</v>
       </c>
       <c r="C1808">
-        <v>5885.1</v>
+        <v>4676.6</v>
       </c>
       <c r="D1808" t="s">
         <v>1810</v>
@@ -31470,7 +32046,7 @@
         <v>80</v>
       </c>
       <c r="C1809">
-        <v>5904.1</v>
+        <v>4639.2</v>
       </c>
       <c r="D1809" t="s">
         <v>1811</v>
@@ -31484,7 +32060,7 @@
         <v>81</v>
       </c>
       <c r="C1810">
-        <v>6193</v>
+        <v>4695.1</v>
       </c>
       <c r="D1810" t="s">
         <v>1812</v>
@@ -31498,7 +32074,7 @@
         <v>82</v>
       </c>
       <c r="C1811">
-        <v>6234.8</v>
+        <v>4726.2</v>
       </c>
       <c r="D1811" t="s">
         <v>1813</v>
@@ -31512,7 +32088,7 @@
         <v>83</v>
       </c>
       <c r="C1812">
-        <v>6302.7</v>
+        <v>4758.5</v>
       </c>
       <c r="D1812" t="s">
         <v>1814</v>
@@ -31526,7 +32102,7 @@
         <v>84</v>
       </c>
       <c r="C1813">
-        <v>6406.4</v>
+        <v>4800.7</v>
       </c>
       <c r="D1813" t="s">
         <v>1815</v>
@@ -31540,7 +32116,7 @@
         <v>85</v>
       </c>
       <c r="C1814">
-        <v>6761.1</v>
+        <v>4824.6</v>
       </c>
       <c r="D1814" t="s">
         <v>1816</v>
@@ -31554,7 +32130,7 @@
         <v>86</v>
       </c>
       <c r="C1815">
-        <v>6768.2</v>
+        <v>4812.3</v>
       </c>
       <c r="D1815" t="s">
         <v>1817</v>
@@ -31568,7 +32144,7 @@
         <v>87</v>
       </c>
       <c r="C1816">
-        <v>6817.8</v>
+        <v>4864.8</v>
       </c>
       <c r="D1816" t="s">
         <v>1818</v>
@@ -31582,7 +32158,7 @@
         <v>88</v>
       </c>
       <c r="C1817">
-        <v>6818.2</v>
+        <v>4813.5</v>
       </c>
       <c r="D1817" t="s">
         <v>1819</v>
@@ -31596,7 +32172,7 @@
         <v>89</v>
       </c>
       <c r="C1818">
-        <v>6619.5</v>
+        <v>4591.9</v>
       </c>
       <c r="D1818" t="s">
         <v>1820</v>
@@ -31610,7 +32186,7 @@
         <v>90</v>
       </c>
       <c r="C1819">
-        <v>6629</v>
+        <v>4583.7</v>
       </c>
       <c r="D1819" t="s">
         <v>1821</v>
@@ -31624,7 +32200,7 @@
         <v>91</v>
       </c>
       <c r="C1820">
-        <v>6617.6</v>
+        <v>4560.4</v>
       </c>
       <c r="D1820" t="s">
         <v>1822</v>
@@ -31638,7 +32214,7 @@
         <v>92</v>
       </c>
       <c r="C1821">
-        <v>6567.5</v>
+        <v>4583.1</v>
       </c>
       <c r="D1821" t="s">
         <v>1823</v>
@@ -31652,7 +32228,7 @@
         <v>93</v>
       </c>
       <c r="C1822">
-        <v>6468.1</v>
+        <v>4429.7</v>
       </c>
       <c r="D1822" t="s">
         <v>1824</v>
@@ -31666,7 +32242,7 @@
         <v>94</v>
       </c>
       <c r="C1823">
-        <v>6366.9</v>
+        <v>4325.6</v>
       </c>
       <c r="D1823" t="s">
         <v>1825</v>
@@ -31680,7 +32256,7 @@
         <v>95</v>
       </c>
       <c r="C1824">
-        <v>6373.6</v>
+        <v>4360.6</v>
       </c>
       <c r="D1824" t="s">
         <v>1826</v>
@@ -31694,7 +32270,7 @@
         <v>96</v>
       </c>
       <c r="C1825">
-        <v>6327</v>
+        <v>4392.5</v>
       </c>
       <c r="D1825" t="s">
         <v>1827</v>
@@ -31708,7 +32284,7 @@
         <v>1</v>
       </c>
       <c r="C1826">
-        <v>5736</v>
+        <v>5636</v>
       </c>
       <c r="D1826" t="s">
         <v>1828</v>
@@ -31722,7 +32298,7 @@
         <v>2</v>
       </c>
       <c r="C1827">
-        <v>5726.2</v>
+        <v>5586.2</v>
       </c>
       <c r="D1827" t="s">
         <v>1829</v>
@@ -31736,7 +32312,7 @@
         <v>3</v>
       </c>
       <c r="C1828">
-        <v>5619.7</v>
+        <v>5459.7</v>
       </c>
       <c r="D1828" t="s">
         <v>1830</v>
@@ -31750,7 +32326,7 @@
         <v>4</v>
       </c>
       <c r="C1829">
-        <v>5487.7</v>
+        <v>5347.7</v>
       </c>
       <c r="D1829" t="s">
         <v>1831</v>
@@ -31764,7 +32340,7 @@
         <v>5</v>
       </c>
       <c r="C1830">
-        <v>5023.4</v>
+        <v>4903.4</v>
       </c>
       <c r="D1830" t="s">
         <v>1832</v>
@@ -31778,7 +32354,7 @@
         <v>6</v>
       </c>
       <c r="C1831">
-        <v>4978.2</v>
+        <v>4868.2</v>
       </c>
       <c r="D1831" t="s">
         <v>1833</v>
@@ -31792,7 +32368,7 @@
         <v>7</v>
       </c>
       <c r="C1832">
-        <v>4929.8</v>
+        <v>4819.8</v>
       </c>
       <c r="D1832" t="s">
         <v>1834</v>
@@ -31806,7 +32382,7 @@
         <v>8</v>
       </c>
       <c r="C1833">
-        <v>4884.3</v>
+        <v>4784.3</v>
       </c>
       <c r="D1833" t="s">
         <v>1835</v>
@@ -31820,7 +32396,7 @@
         <v>9</v>
       </c>
       <c r="C1834">
-        <v>4595.1</v>
+        <v>4495.1</v>
       </c>
       <c r="D1834" t="s">
         <v>1836</v>
@@ -31834,7 +32410,7 @@
         <v>10</v>
       </c>
       <c r="C1835">
-        <v>4564.8</v>
+        <v>4464.8</v>
       </c>
       <c r="D1835" t="s">
         <v>1837</v>
@@ -31848,7 +32424,7 @@
         <v>11</v>
       </c>
       <c r="C1836">
-        <v>4530.6</v>
+        <v>4430.6</v>
       </c>
       <c r="D1836" t="s">
         <v>1838</v>
@@ -31862,7 +32438,7 @@
         <v>12</v>
       </c>
       <c r="C1837">
-        <v>4511.4</v>
+        <v>4431.4</v>
       </c>
       <c r="D1837" t="s">
         <v>1839</v>
@@ -31876,7 +32452,7 @@
         <v>13</v>
       </c>
       <c r="C1838">
-        <v>4534</v>
+        <v>4444</v>
       </c>
       <c r="D1838" t="s">
         <v>1840</v>
@@ -31890,7 +32466,7 @@
         <v>14</v>
       </c>
       <c r="C1839">
-        <v>4511.1</v>
+        <v>4421.1</v>
       </c>
       <c r="D1839" t="s">
         <v>1841</v>
@@ -31904,7 +32480,7 @@
         <v>15</v>
       </c>
       <c r="C1840">
-        <v>4485.4</v>
+        <v>4395.4</v>
       </c>
       <c r="D1840" t="s">
         <v>1842</v>
@@ -31918,7 +32494,7 @@
         <v>16</v>
       </c>
       <c r="C1841">
-        <v>4465.9</v>
+        <v>4365.9</v>
       </c>
       <c r="D1841" t="s">
         <v>1843</v>
@@ -31932,7 +32508,7 @@
         <v>17</v>
       </c>
       <c r="C1842">
-        <v>4435.9</v>
+        <v>4345.9</v>
       </c>
       <c r="D1842" t="s">
         <v>1844</v>
@@ -31946,7 +32522,7 @@
         <v>18</v>
       </c>
       <c r="C1843">
-        <v>4389.2</v>
+        <v>4299.2</v>
       </c>
       <c r="D1843" t="s">
         <v>1845</v>
@@ -31960,7 +32536,7 @@
         <v>19</v>
       </c>
       <c r="C1844">
-        <v>4347.8</v>
+        <v>4267.8</v>
       </c>
       <c r="D1844" t="s">
         <v>1846</v>
@@ -31974,7 +32550,7 @@
         <v>20</v>
       </c>
       <c r="C1845">
-        <v>4313.5</v>
+        <v>4243.5</v>
       </c>
       <c r="D1845" t="s">
         <v>1847</v>
@@ -31988,7 +32564,7 @@
         <v>21</v>
       </c>
       <c r="C1846">
-        <v>4345.6</v>
+        <v>4285.6</v>
       </c>
       <c r="D1846" t="s">
         <v>1848</v>
@@ -32002,7 +32578,7 @@
         <v>22</v>
       </c>
       <c r="C1847">
-        <v>4325.6</v>
+        <v>4265.6</v>
       </c>
       <c r="D1847" t="s">
         <v>1849</v>
@@ -32016,7 +32592,7 @@
         <v>23</v>
       </c>
       <c r="C1848">
-        <v>4313.4</v>
+        <v>4243.4</v>
       </c>
       <c r="D1848" t="s">
         <v>1850</v>
@@ -32030,7 +32606,7 @@
         <v>24</v>
       </c>
       <c r="C1849">
-        <v>4296.6</v>
+        <v>4216.6</v>
       </c>
       <c r="D1849" t="s">
         <v>1851</v>
@@ -32044,7 +32620,7 @@
         <v>25</v>
       </c>
       <c r="C1850">
-        <v>4356.8</v>
+        <v>4246.8</v>
       </c>
       <c r="D1850" t="s">
         <v>1852</v>
@@ -32058,7 +32634,7 @@
         <v>26</v>
       </c>
       <c r="C1851">
-        <v>4401.3</v>
+        <v>4271.3</v>
       </c>
       <c r="D1851" t="s">
         <v>1853</v>
@@ -32072,7 +32648,7 @@
         <v>27</v>
       </c>
       <c r="C1852">
-        <v>4453.1</v>
+        <v>4313.1</v>
       </c>
       <c r="D1852" t="s">
         <v>1854</v>
@@ -32086,7 +32662,7 @@
         <v>28</v>
       </c>
       <c r="C1853">
-        <v>4486.4</v>
+        <v>4346.4</v>
       </c>
       <c r="D1853" t="s">
         <v>1855</v>
@@ -32100,7 +32676,7 @@
         <v>29</v>
       </c>
       <c r="C1854">
-        <v>4530.9</v>
+        <v>4400.9</v>
       </c>
       <c r="D1854" t="s">
         <v>1856</v>
@@ -32114,7 +32690,7 @@
         <v>30</v>
       </c>
       <c r="C1855">
-        <v>4556.5</v>
+        <v>4426.5</v>
       </c>
       <c r="D1855" t="s">
         <v>1857</v>
@@ -32128,7 +32704,7 @@
         <v>31</v>
       </c>
       <c r="C1856">
-        <v>4652.3</v>
+        <v>4542.3</v>
       </c>
       <c r="D1856" t="s">
         <v>1858</v>
@@ -32142,7 +32718,7 @@
         <v>32</v>
       </c>
       <c r="C1857">
-        <v>4739.7</v>
+        <v>4649.7</v>
       </c>
       <c r="D1857" t="s">
         <v>1859</v>
@@ -32156,7 +32732,7 @@
         <v>33</v>
       </c>
       <c r="C1858">
-        <v>4631.3</v>
+        <v>4561.3</v>
       </c>
       <c r="D1858" t="s">
         <v>1860</v>
@@ -32170,7 +32746,7 @@
         <v>34</v>
       </c>
       <c r="C1859">
-        <v>4683</v>
+        <v>4643</v>
       </c>
       <c r="D1859" t="s">
         <v>1861</v>
@@ -32184,7 +32760,7 @@
         <v>35</v>
       </c>
       <c r="C1860">
-        <v>4719.6</v>
+        <v>4709.6</v>
       </c>
       <c r="D1860" t="s">
         <v>1862</v>
@@ -32198,7 +32774,7 @@
         <v>36</v>
       </c>
       <c r="C1861">
-        <v>4834.8</v>
+        <v>4854.8</v>
       </c>
       <c r="D1861" t="s">
         <v>1863</v>
@@ -32212,7 +32788,7 @@
         <v>37</v>
       </c>
       <c r="C1862">
-        <v>4656.5</v>
+        <v>4686.5</v>
       </c>
       <c r="D1862" t="s">
         <v>1864</v>
@@ -32226,7 +32802,7 @@
         <v>38</v>
       </c>
       <c r="C1863">
-        <v>4619.5</v>
+        <v>4689.5</v>
       </c>
       <c r="D1863" t="s">
         <v>1865</v>
@@ -32240,7 +32816,7 @@
         <v>39</v>
       </c>
       <c r="C1864">
-        <v>4636.2</v>
+        <v>4746.2</v>
       </c>
       <c r="D1864" t="s">
         <v>1866</v>
@@ -32254,7 +32830,7 @@
         <v>40</v>
       </c>
       <c r="C1865">
-        <v>4654.8</v>
+        <v>4824.8</v>
       </c>
       <c r="D1865" t="s">
         <v>1867</v>
@@ -32268,7 +32844,7 @@
         <v>41</v>
       </c>
       <c r="C1866">
-        <v>4790.7</v>
+        <v>5020.7</v>
       </c>
       <c r="D1866" t="s">
         <v>1868</v>
@@ -32282,7 +32858,7 @@
         <v>42</v>
       </c>
       <c r="C1867">
-        <v>4769.9</v>
+        <v>5019.9</v>
       </c>
       <c r="D1867" t="s">
         <v>1869</v>
@@ -32296,7 +32872,7 @@
         <v>43</v>
       </c>
       <c r="C1868">
-        <v>4768.3</v>
+        <v>5028.3</v>
       </c>
       <c r="D1868" t="s">
         <v>1870</v>
@@ -32310,7 +32886,7 @@
         <v>44</v>
       </c>
       <c r="C1869">
-        <v>4787.5</v>
+        <v>5027.5</v>
       </c>
       <c r="D1869" t="s">
         <v>1871</v>
@@ -32324,7 +32900,7 @@
         <v>45</v>
       </c>
       <c r="C1870">
-        <v>4778</v>
+        <v>4978</v>
       </c>
       <c r="D1870" t="s">
         <v>1872</v>
@@ -32338,7 +32914,7 @@
         <v>46</v>
       </c>
       <c r="C1871">
-        <v>4773.3</v>
+        <v>4933.3</v>
       </c>
       <c r="D1871" t="s">
         <v>1873</v>
@@ -32352,7 +32928,7 @@
         <v>47</v>
       </c>
       <c r="C1872">
-        <v>4754.1</v>
+        <v>4894.1</v>
       </c>
       <c r="D1872" t="s">
         <v>1874</v>
@@ -32366,7 +32942,7 @@
         <v>48</v>
       </c>
       <c r="C1873">
-        <v>4770.1</v>
+        <v>4910.1</v>
       </c>
       <c r="D1873" t="s">
         <v>1875</v>
@@ -32380,7 +32956,7 @@
         <v>49</v>
       </c>
       <c r="C1874">
-        <v>4566.1</v>
+        <v>4716.1</v>
       </c>
       <c r="D1874" t="s">
         <v>1876</v>
@@ -32394,7 +32970,7 @@
         <v>50</v>
       </c>
       <c r="C1875">
-        <v>4528.2</v>
+        <v>4698.2</v>
       </c>
       <c r="D1875" t="s">
         <v>1877</v>
@@ -32408,7 +32984,7 @@
         <v>51</v>
       </c>
       <c r="C1876">
-        <v>4505.5</v>
+        <v>4685.5</v>
       </c>
       <c r="D1876" t="s">
         <v>1878</v>
@@ -32422,7 +32998,7 @@
         <v>52</v>
       </c>
       <c r="C1877">
-        <v>4500</v>
+        <v>4700</v>
       </c>
       <c r="D1877" t="s">
         <v>1879</v>
@@ -32436,7 +33012,7 @@
         <v>53</v>
       </c>
       <c r="C1878">
-        <v>4467.1</v>
+        <v>4687.1</v>
       </c>
       <c r="D1878" t="s">
         <v>1880</v>
@@ -32450,7 +33026,7 @@
         <v>54</v>
       </c>
       <c r="C1879">
-        <v>4448.4</v>
+        <v>4668.4</v>
       </c>
       <c r="D1879" t="s">
         <v>1881</v>
@@ -32464,7 +33040,7 @@
         <v>55</v>
       </c>
       <c r="C1880">
-        <v>4473.8</v>
+        <v>4693.8</v>
       </c>
       <c r="D1880" t="s">
         <v>1882</v>
@@ -32478,7 +33054,7 @@
         <v>56</v>
       </c>
       <c r="C1881">
-        <v>4498.2</v>
+        <v>4698.2</v>
       </c>
       <c r="D1881" t="s">
         <v>1883</v>
@@ -32492,7 +33068,7 @@
         <v>57</v>
       </c>
       <c r="C1882">
-        <v>4570.2</v>
+        <v>4740.2</v>
       </c>
       <c r="D1882" t="s">
         <v>1884</v>
@@ -32506,7 +33082,7 @@
         <v>58</v>
       </c>
       <c r="C1883">
-        <v>4567</v>
+        <v>4717</v>
       </c>
       <c r="D1883" t="s">
         <v>1885</v>
@@ -32520,7 +33096,7 @@
         <v>59</v>
       </c>
       <c r="C1884">
-        <v>4588</v>
+        <v>4708</v>
       </c>
       <c r="D1884" t="s">
         <v>1886</v>
@@ -32534,7 +33110,7 @@
         <v>60</v>
       </c>
       <c r="C1885">
-        <v>4635.1</v>
+        <v>4735.1</v>
       </c>
       <c r="D1885" t="s">
         <v>1887</v>
@@ -32548,7 +33124,7 @@
         <v>61</v>
       </c>
       <c r="C1886">
-        <v>4691.2</v>
+        <v>4771.2</v>
       </c>
       <c r="D1886" t="s">
         <v>1888</v>
@@ -32562,7 +33138,7 @@
         <v>62</v>
       </c>
       <c r="C1887">
-        <v>4666.4</v>
+        <v>4726.4</v>
       </c>
       <c r="D1887" t="s">
         <v>1889</v>
@@ -32576,7 +33152,7 @@
         <v>63</v>
       </c>
       <c r="C1888">
-        <v>4651.2</v>
+        <v>4701.2</v>
       </c>
       <c r="D1888" t="s">
         <v>1890</v>
@@ -32590,7 +33166,7 @@
         <v>64</v>
       </c>
       <c r="C1889">
-        <v>4680.3</v>
+        <v>4720.3</v>
       </c>
       <c r="D1889" t="s">
         <v>1891</v>
@@ -32604,7 +33180,7 @@
         <v>65</v>
       </c>
       <c r="C1890">
-        <v>4729.1</v>
+        <v>4749.1</v>
       </c>
       <c r="D1890" t="s">
         <v>1892</v>
@@ -32618,7 +33194,7 @@
         <v>66</v>
       </c>
       <c r="C1891">
-        <v>4690.3</v>
+        <v>4700.3</v>
       </c>
       <c r="D1891" t="s">
         <v>1893</v>
@@ -32632,7 +33208,7 @@
         <v>67</v>
       </c>
       <c r="C1892">
-        <v>4689.2</v>
+        <v>4679.2</v>
       </c>
       <c r="D1892" t="s">
         <v>1894</v>
@@ -32646,7 +33222,7 @@
         <v>68</v>
       </c>
       <c r="C1893">
-        <v>4650.9</v>
+        <v>4620.9</v>
       </c>
       <c r="D1893" t="s">
         <v>1895</v>
@@ -32660,7 +33236,7 @@
         <v>69</v>
       </c>
       <c r="C1894">
-        <v>4533.4</v>
+        <v>4503.4</v>
       </c>
       <c r="D1894" t="s">
         <v>1896</v>
@@ -32674,7 +33250,7 @@
         <v>70</v>
       </c>
       <c r="C1895">
-        <v>4448.8</v>
+        <v>4418.8</v>
       </c>
       <c r="D1895" t="s">
         <v>1897</v>
@@ -32688,7 +33264,7 @@
         <v>71</v>
       </c>
       <c r="C1896">
-        <v>4394.3</v>
+        <v>4364.3</v>
       </c>
       <c r="D1896" t="s">
         <v>1898</v>
@@ -32702,7 +33278,7 @@
         <v>72</v>
       </c>
       <c r="C1897">
-        <v>4328.9</v>
+        <v>4308.9</v>
       </c>
       <c r="D1897" t="s">
         <v>1899</v>
@@ -32716,7 +33292,7 @@
         <v>73</v>
       </c>
       <c r="C1898">
-        <v>4914.8</v>
+        <v>4884.8</v>
       </c>
       <c r="D1898" t="s">
         <v>1900</v>
@@ -32730,7 +33306,7 @@
         <v>74</v>
       </c>
       <c r="C1899">
-        <v>4845</v>
+        <v>4805</v>
       </c>
       <c r="D1899" t="s">
         <v>1901</v>
@@ -32744,7 +33320,7 @@
         <v>75</v>
       </c>
       <c r="C1900">
-        <v>4816.5</v>
+        <v>4766.5</v>
       </c>
       <c r="D1900" t="s">
         <v>1902</v>
@@ -32758,7 +33334,7 @@
         <v>76</v>
       </c>
       <c r="C1901">
-        <v>4815.9</v>
+        <v>4745.9</v>
       </c>
       <c r="D1901" t="s">
         <v>1903</v>
@@ -32772,7 +33348,7 @@
         <v>77</v>
       </c>
       <c r="C1902">
-        <v>4761.2</v>
+        <v>4671.2</v>
       </c>
       <c r="D1902" t="s">
         <v>1904</v>
@@ -32786,7 +33362,7 @@
         <v>78</v>
       </c>
       <c r="C1903">
-        <v>4809.7</v>
+        <v>4679.7</v>
       </c>
       <c r="D1903" t="s">
         <v>1905</v>
@@ -32800,7 +33376,7 @@
         <v>79</v>
       </c>
       <c r="C1904">
-        <v>4756.6</v>
+        <v>4606.6</v>
       </c>
       <c r="D1904" t="s">
         <v>1906</v>
@@ -32814,7 +33390,7 @@
         <v>80</v>
       </c>
       <c r="C1905">
-        <v>4759.2</v>
+        <v>4589.2</v>
       </c>
       <c r="D1905" t="s">
         <v>1907</v>
@@ -32828,7 +33404,7 @@
         <v>81</v>
       </c>
       <c r="C1906">
-        <v>4855.1</v>
+        <v>4645.1</v>
       </c>
       <c r="D1906" t="s">
         <v>1908</v>
@@ -32842,7 +33418,7 @@
         <v>82</v>
       </c>
       <c r="C1907">
-        <v>4916.2</v>
+        <v>4666.2</v>
       </c>
       <c r="D1907" t="s">
         <v>1909</v>
@@ -32856,7 +33432,7 @@
         <v>83</v>
       </c>
       <c r="C1908">
-        <v>4968.5</v>
+        <v>4698.5</v>
       </c>
       <c r="D1908" t="s">
         <v>1910</v>
@@ -32870,7 +33446,7 @@
         <v>84</v>
       </c>
       <c r="C1909">
-        <v>4990.7</v>
+        <v>4730.7</v>
       </c>
       <c r="D1909" t="s">
         <v>1911</v>
@@ -32884,7 +33460,7 @@
         <v>85</v>
       </c>
       <c r="C1910">
-        <v>5004.6</v>
+        <v>4804.6</v>
       </c>
       <c r="D1910" t="s">
         <v>1912</v>
@@ -32898,7 +33474,7 @@
         <v>86</v>
       </c>
       <c r="C1911">
-        <v>4932.3</v>
+        <v>4802.3</v>
       </c>
       <c r="D1911" t="s">
         <v>1913</v>
@@ -32912,7 +33488,7 @@
         <v>87</v>
       </c>
       <c r="C1912">
-        <v>4984.8</v>
+        <v>4834.8</v>
       </c>
       <c r="D1912" t="s">
         <v>1914</v>
@@ -32926,7 +33502,7 @@
         <v>88</v>
       </c>
       <c r="C1913">
-        <v>4993.5</v>
+        <v>4783.5</v>
       </c>
       <c r="D1913" t="s">
         <v>1915</v>
@@ -32940,7 +33516,7 @@
         <v>89</v>
       </c>
       <c r="C1914">
-        <v>4871.9</v>
+        <v>4581.9</v>
       </c>
       <c r="D1914" t="s">
         <v>1916</v>
@@ -32954,7 +33530,7 @@
         <v>90</v>
       </c>
       <c r="C1915">
-        <v>4933.7</v>
+        <v>4543.7</v>
       </c>
       <c r="D1915" t="s">
         <v>1917</v>
@@ -32968,7 +33544,7 @@
         <v>91</v>
       </c>
       <c r="C1916">
-        <v>4900.4</v>
+        <v>4500.4</v>
       </c>
       <c r="D1916" t="s">
         <v>1918</v>
@@ -32982,7 +33558,7 @@
         <v>92</v>
       </c>
       <c r="C1917">
-        <v>4893.1</v>
+        <v>4533.1</v>
       </c>
       <c r="D1917" t="s">
         <v>1919</v>
@@ -32996,7 +33572,7 @@
         <v>93</v>
       </c>
       <c r="C1918">
-        <v>4739.7</v>
+        <v>4449.7</v>
       </c>
       <c r="D1918" t="s">
         <v>1920</v>
@@ -33010,7 +33586,7 @@
         <v>94</v>
       </c>
       <c r="C1919">
-        <v>4625.6</v>
+        <v>4385.6</v>
       </c>
       <c r="D1919" t="s">
         <v>1921</v>
@@ -33024,7 +33600,7 @@
         <v>95</v>
       </c>
       <c r="C1920">
-        <v>4660.6</v>
+        <v>4380.6</v>
       </c>
       <c r="D1920" t="s">
         <v>1922</v>
@@ -33038,10 +33614,2698 @@
         <v>96</v>
       </c>
       <c r="C1921">
-        <v>4692.5</v>
+        <v>4412.5</v>
       </c>
       <c r="D1921" t="s">
         <v>1923</v>
+      </c>
+    </row>
+    <row r="1922" spans="1:4">
+      <c r="A1922" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1922">
+        <v>1</v>
+      </c>
+      <c r="C1922">
+        <v>5646</v>
+      </c>
+      <c r="D1922" t="s">
+        <v>1924</v>
+      </c>
+    </row>
+    <row r="1923" spans="1:4">
+      <c r="A1923" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1923">
+        <v>2</v>
+      </c>
+      <c r="C1923">
+        <v>5586.2</v>
+      </c>
+      <c r="D1923" t="s">
+        <v>1925</v>
+      </c>
+    </row>
+    <row r="1924" spans="1:4">
+      <c r="A1924" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1924">
+        <v>3</v>
+      </c>
+      <c r="C1924">
+        <v>5469.7</v>
+      </c>
+      <c r="D1924" t="s">
+        <v>1926</v>
+      </c>
+    </row>
+    <row r="1925" spans="1:4">
+      <c r="A1925" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1925">
+        <v>4</v>
+      </c>
+      <c r="C1925">
+        <v>5357.7</v>
+      </c>
+      <c r="D1925" t="s">
+        <v>1927</v>
+      </c>
+    </row>
+    <row r="1926" spans="1:4">
+      <c r="A1926" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1926">
+        <v>5</v>
+      </c>
+      <c r="C1926">
+        <v>4913.4</v>
+      </c>
+      <c r="D1926" t="s">
+        <v>1928</v>
+      </c>
+    </row>
+    <row r="1927" spans="1:4">
+      <c r="A1927" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1927">
+        <v>6</v>
+      </c>
+      <c r="C1927">
+        <v>4868.2</v>
+      </c>
+      <c r="D1927" t="s">
+        <v>1929</v>
+      </c>
+    </row>
+    <row r="1928" spans="1:4">
+      <c r="A1928" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1928">
+        <v>7</v>
+      </c>
+      <c r="C1928">
+        <v>4819.8</v>
+      </c>
+      <c r="D1928" t="s">
+        <v>1930</v>
+      </c>
+    </row>
+    <row r="1929" spans="1:4">
+      <c r="A1929" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1929">
+        <v>8</v>
+      </c>
+      <c r="C1929">
+        <v>4784.3</v>
+      </c>
+      <c r="D1929" t="s">
+        <v>1931</v>
+      </c>
+    </row>
+    <row r="1930" spans="1:4">
+      <c r="A1930" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1930">
+        <v>9</v>
+      </c>
+      <c r="C1930">
+        <v>4495.1</v>
+      </c>
+      <c r="D1930" t="s">
+        <v>1932</v>
+      </c>
+    </row>
+    <row r="1931" spans="1:4">
+      <c r="A1931" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1931">
+        <v>10</v>
+      </c>
+      <c r="C1931">
+        <v>4464.8</v>
+      </c>
+      <c r="D1931" t="s">
+        <v>1933</v>
+      </c>
+    </row>
+    <row r="1932" spans="1:4">
+      <c r="A1932" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1932">
+        <v>11</v>
+      </c>
+      <c r="C1932">
+        <v>4440.6</v>
+      </c>
+      <c r="D1932" t="s">
+        <v>1934</v>
+      </c>
+    </row>
+    <row r="1933" spans="1:4">
+      <c r="A1933" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1933">
+        <v>12</v>
+      </c>
+      <c r="C1933">
+        <v>4431.4</v>
+      </c>
+      <c r="D1933" t="s">
+        <v>1935</v>
+      </c>
+    </row>
+    <row r="1934" spans="1:4">
+      <c r="A1934" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1934">
+        <v>13</v>
+      </c>
+      <c r="C1934">
+        <v>4444</v>
+      </c>
+      <c r="D1934" t="s">
+        <v>1936</v>
+      </c>
+    </row>
+    <row r="1935" spans="1:4">
+      <c r="A1935" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1935">
+        <v>14</v>
+      </c>
+      <c r="C1935">
+        <v>4421.1</v>
+      </c>
+      <c r="D1935" t="s">
+        <v>1937</v>
+      </c>
+    </row>
+    <row r="1936" spans="1:4">
+      <c r="A1936" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1936">
+        <v>15</v>
+      </c>
+      <c r="C1936">
+        <v>4395.4</v>
+      </c>
+      <c r="D1936" t="s">
+        <v>1938</v>
+      </c>
+    </row>
+    <row r="1937" spans="1:4">
+      <c r="A1937" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1937">
+        <v>16</v>
+      </c>
+      <c r="C1937">
+        <v>4365.9</v>
+      </c>
+      <c r="D1937" t="s">
+        <v>1939</v>
+      </c>
+    </row>
+    <row r="1938" spans="1:4">
+      <c r="A1938" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1938">
+        <v>17</v>
+      </c>
+      <c r="C1938">
+        <v>4335.9</v>
+      </c>
+      <c r="D1938" t="s">
+        <v>1940</v>
+      </c>
+    </row>
+    <row r="1939" spans="1:4">
+      <c r="A1939" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1939">
+        <v>18</v>
+      </c>
+      <c r="C1939">
+        <v>4289.2</v>
+      </c>
+      <c r="D1939" t="s">
+        <v>1941</v>
+      </c>
+    </row>
+    <row r="1940" spans="1:4">
+      <c r="A1940" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1940">
+        <v>19</v>
+      </c>
+      <c r="C1940">
+        <v>4247.8</v>
+      </c>
+      <c r="D1940" t="s">
+        <v>1942</v>
+      </c>
+    </row>
+    <row r="1941" spans="1:4">
+      <c r="A1941" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1941">
+        <v>20</v>
+      </c>
+      <c r="C1941">
+        <v>4213.5</v>
+      </c>
+      <c r="D1941" t="s">
+        <v>1943</v>
+      </c>
+    </row>
+    <row r="1942" spans="1:4">
+      <c r="A1942" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1942">
+        <v>21</v>
+      </c>
+      <c r="C1942">
+        <v>4235.6</v>
+      </c>
+      <c r="D1942" t="s">
+        <v>1944</v>
+      </c>
+    </row>
+    <row r="1943" spans="1:4">
+      <c r="A1943" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1943">
+        <v>22</v>
+      </c>
+      <c r="C1943">
+        <v>4215.6</v>
+      </c>
+      <c r="D1943" t="s">
+        <v>1945</v>
+      </c>
+    </row>
+    <row r="1944" spans="1:4">
+      <c r="A1944" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1944">
+        <v>23</v>
+      </c>
+      <c r="C1944">
+        <v>4203.4</v>
+      </c>
+      <c r="D1944" t="s">
+        <v>1946</v>
+      </c>
+    </row>
+    <row r="1945" spans="1:4">
+      <c r="A1945" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1945">
+        <v>24</v>
+      </c>
+      <c r="C1945">
+        <v>4176.6</v>
+      </c>
+      <c r="D1945" t="s">
+        <v>1947</v>
+      </c>
+    </row>
+    <row r="1946" spans="1:4">
+      <c r="A1946" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1946">
+        <v>25</v>
+      </c>
+      <c r="C1946">
+        <v>4226.8</v>
+      </c>
+      <c r="D1946" t="s">
+        <v>1948</v>
+      </c>
+    </row>
+    <row r="1947" spans="1:4">
+      <c r="A1947" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1947">
+        <v>26</v>
+      </c>
+      <c r="C1947">
+        <v>4251.3</v>
+      </c>
+      <c r="D1947" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="1948" spans="1:4">
+      <c r="A1948" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1948">
+        <v>27</v>
+      </c>
+      <c r="C1948">
+        <v>4273.1</v>
+      </c>
+      <c r="D1948" t="s">
+        <v>1950</v>
+      </c>
+    </row>
+    <row r="1949" spans="1:4">
+      <c r="A1949" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1949">
+        <v>28</v>
+      </c>
+      <c r="C1949">
+        <v>4286.4</v>
+      </c>
+      <c r="D1949" t="s">
+        <v>1951</v>
+      </c>
+    </row>
+    <row r="1950" spans="1:4">
+      <c r="A1950" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1950">
+        <v>29</v>
+      </c>
+      <c r="C1950">
+        <v>4300.9</v>
+      </c>
+      <c r="D1950" t="s">
+        <v>1952</v>
+      </c>
+    </row>
+    <row r="1951" spans="1:4">
+      <c r="A1951" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1951">
+        <v>30</v>
+      </c>
+      <c r="C1951">
+        <v>4306.5</v>
+      </c>
+      <c r="D1951" t="s">
+        <v>1953</v>
+      </c>
+    </row>
+    <row r="1952" spans="1:4">
+      <c r="A1952" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1952">
+        <v>31</v>
+      </c>
+      <c r="C1952">
+        <v>4392.3</v>
+      </c>
+      <c r="D1952" t="s">
+        <v>1954</v>
+      </c>
+    </row>
+    <row r="1953" spans="1:4">
+      <c r="A1953" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1953">
+        <v>32</v>
+      </c>
+      <c r="C1953">
+        <v>4499.7</v>
+      </c>
+      <c r="D1953" t="s">
+        <v>1955</v>
+      </c>
+    </row>
+    <row r="1954" spans="1:4">
+      <c r="A1954" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1954">
+        <v>33</v>
+      </c>
+      <c r="C1954">
+        <v>4411.3</v>
+      </c>
+      <c r="D1954" t="s">
+        <v>1956</v>
+      </c>
+    </row>
+    <row r="1955" spans="1:4">
+      <c r="A1955" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1955">
+        <v>34</v>
+      </c>
+      <c r="C1955">
+        <v>4483</v>
+      </c>
+      <c r="D1955" t="s">
+        <v>1957</v>
+      </c>
+    </row>
+    <row r="1956" spans="1:4">
+      <c r="A1956" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1956">
+        <v>35</v>
+      </c>
+      <c r="C1956">
+        <v>4539.6</v>
+      </c>
+      <c r="D1956" t="s">
+        <v>1958</v>
+      </c>
+    </row>
+    <row r="1957" spans="1:4">
+      <c r="A1957" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1957">
+        <v>36</v>
+      </c>
+      <c r="C1957">
+        <v>4664.8</v>
+      </c>
+      <c r="D1957" t="s">
+        <v>1959</v>
+      </c>
+    </row>
+    <row r="1958" spans="1:4">
+      <c r="A1958" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1958">
+        <v>37</v>
+      </c>
+      <c r="C1958">
+        <v>4476.5</v>
+      </c>
+      <c r="D1958" t="s">
+        <v>1960</v>
+      </c>
+    </row>
+    <row r="1959" spans="1:4">
+      <c r="A1959" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1959">
+        <v>38</v>
+      </c>
+      <c r="C1959">
+        <v>4459.5</v>
+      </c>
+      <c r="D1959" t="s">
+        <v>1961</v>
+      </c>
+    </row>
+    <row r="1960" spans="1:4">
+      <c r="A1960" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1960">
+        <v>39</v>
+      </c>
+      <c r="C1960">
+        <v>4496.2</v>
+      </c>
+      <c r="D1960" t="s">
+        <v>1962</v>
+      </c>
+    </row>
+    <row r="1961" spans="1:4">
+      <c r="A1961" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1961">
+        <v>40</v>
+      </c>
+      <c r="C1961">
+        <v>4544.8</v>
+      </c>
+      <c r="D1961" t="s">
+        <v>1963</v>
+      </c>
+    </row>
+    <row r="1962" spans="1:4">
+      <c r="A1962" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1962">
+        <v>41</v>
+      </c>
+      <c r="C1962">
+        <v>4720.7</v>
+      </c>
+      <c r="D1962" t="s">
+        <v>1964</v>
+      </c>
+    </row>
+    <row r="1963" spans="1:4">
+      <c r="A1963" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1963">
+        <v>42</v>
+      </c>
+      <c r="C1963">
+        <v>4699.9</v>
+      </c>
+      <c r="D1963" t="s">
+        <v>1965</v>
+      </c>
+    </row>
+    <row r="1964" spans="1:4">
+      <c r="A1964" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1964">
+        <v>43</v>
+      </c>
+      <c r="C1964">
+        <v>4688.3</v>
+      </c>
+      <c r="D1964" t="s">
+        <v>1966</v>
+      </c>
+    </row>
+    <row r="1965" spans="1:4">
+      <c r="A1965" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1965">
+        <v>44</v>
+      </c>
+      <c r="C1965">
+        <v>4677.5</v>
+      </c>
+      <c r="D1965" t="s">
+        <v>1967</v>
+      </c>
+    </row>
+    <row r="1966" spans="1:4">
+      <c r="A1966" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1966">
+        <v>45</v>
+      </c>
+      <c r="C1966">
+        <v>4618</v>
+      </c>
+      <c r="D1966" t="s">
+        <v>1968</v>
+      </c>
+    </row>
+    <row r="1967" spans="1:4">
+      <c r="A1967" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1967">
+        <v>46</v>
+      </c>
+      <c r="C1967">
+        <v>4573.3</v>
+      </c>
+      <c r="D1967" t="s">
+        <v>1969</v>
+      </c>
+    </row>
+    <row r="1968" spans="1:4">
+      <c r="A1968" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1968">
+        <v>47</v>
+      </c>
+      <c r="C1968">
+        <v>4534.1</v>
+      </c>
+      <c r="D1968" t="s">
+        <v>1970</v>
+      </c>
+    </row>
+    <row r="1969" spans="1:4">
+      <c r="A1969" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1969">
+        <v>48</v>
+      </c>
+      <c r="C1969">
+        <v>4550.1</v>
+      </c>
+      <c r="D1969" t="s">
+        <v>1971</v>
+      </c>
+    </row>
+    <row r="1970" spans="1:4">
+      <c r="A1970" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1970">
+        <v>49</v>
+      </c>
+      <c r="C1970">
+        <v>4366.1</v>
+      </c>
+      <c r="D1970" t="s">
+        <v>1972</v>
+      </c>
+    </row>
+    <row r="1971" spans="1:4">
+      <c r="A1971" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1971">
+        <v>50</v>
+      </c>
+      <c r="C1971">
+        <v>4358.2</v>
+      </c>
+      <c r="D1971" t="s">
+        <v>1973</v>
+      </c>
+    </row>
+    <row r="1972" spans="1:4">
+      <c r="A1972" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1972">
+        <v>51</v>
+      </c>
+      <c r="C1972">
+        <v>4345.5</v>
+      </c>
+      <c r="D1972" t="s">
+        <v>1974</v>
+      </c>
+    </row>
+    <row r="1973" spans="1:4">
+      <c r="A1973" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1973">
+        <v>52</v>
+      </c>
+      <c r="C1973">
+        <v>4360</v>
+      </c>
+      <c r="D1973" t="s">
+        <v>1975</v>
+      </c>
+    </row>
+    <row r="1974" spans="1:4">
+      <c r="A1974" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1974">
+        <v>53</v>
+      </c>
+      <c r="C1974">
+        <v>4337.1</v>
+      </c>
+      <c r="D1974" t="s">
+        <v>1976</v>
+      </c>
+    </row>
+    <row r="1975" spans="1:4">
+      <c r="A1975" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1975">
+        <v>54</v>
+      </c>
+      <c r="C1975">
+        <v>4318.4</v>
+      </c>
+      <c r="D1975" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="1976" spans="1:4">
+      <c r="A1976" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1976">
+        <v>55</v>
+      </c>
+      <c r="C1976">
+        <v>4343.8</v>
+      </c>
+      <c r="D1976" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="1977" spans="1:4">
+      <c r="A1977" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1977">
+        <v>56</v>
+      </c>
+      <c r="C1977">
+        <v>4348.2</v>
+      </c>
+      <c r="D1977" t="s">
+        <v>1979</v>
+      </c>
+    </row>
+    <row r="1978" spans="1:4">
+      <c r="A1978" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1978">
+        <v>57</v>
+      </c>
+      <c r="C1978">
+        <v>4390.2</v>
+      </c>
+      <c r="D1978" t="s">
+        <v>1980</v>
+      </c>
+    </row>
+    <row r="1979" spans="1:4">
+      <c r="A1979" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1979">
+        <v>58</v>
+      </c>
+      <c r="C1979">
+        <v>4377</v>
+      </c>
+      <c r="D1979" t="s">
+        <v>1981</v>
+      </c>
+    </row>
+    <row r="1980" spans="1:4">
+      <c r="A1980" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1980">
+        <v>59</v>
+      </c>
+      <c r="C1980">
+        <v>4388</v>
+      </c>
+      <c r="D1980" t="s">
+        <v>1982</v>
+      </c>
+    </row>
+    <row r="1981" spans="1:4">
+      <c r="A1981" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1981">
+        <v>60</v>
+      </c>
+      <c r="C1981">
+        <v>4425.1</v>
+      </c>
+      <c r="D1981" t="s">
+        <v>1983</v>
+      </c>
+    </row>
+    <row r="1982" spans="1:4">
+      <c r="A1982" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1982">
+        <v>61</v>
+      </c>
+      <c r="C1982">
+        <v>4471.2</v>
+      </c>
+      <c r="D1982" t="s">
+        <v>1984</v>
+      </c>
+    </row>
+    <row r="1983" spans="1:4">
+      <c r="A1983" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1983">
+        <v>62</v>
+      </c>
+      <c r="C1983">
+        <v>4446.4</v>
+      </c>
+      <c r="D1983" t="s">
+        <v>1985</v>
+      </c>
+    </row>
+    <row r="1984" spans="1:4">
+      <c r="A1984" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1984">
+        <v>63</v>
+      </c>
+      <c r="C1984">
+        <v>4421.2</v>
+      </c>
+      <c r="D1984" t="s">
+        <v>1986</v>
+      </c>
+    </row>
+    <row r="1985" spans="1:4">
+      <c r="A1985" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1985">
+        <v>64</v>
+      </c>
+      <c r="C1985">
+        <v>4440.3</v>
+      </c>
+      <c r="D1985" t="s">
+        <v>1987</v>
+      </c>
+    </row>
+    <row r="1986" spans="1:4">
+      <c r="A1986" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1986">
+        <v>65</v>
+      </c>
+      <c r="C1986">
+        <v>4469.1</v>
+      </c>
+      <c r="D1986" t="s">
+        <v>1988</v>
+      </c>
+    </row>
+    <row r="1987" spans="1:4">
+      <c r="A1987" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1987">
+        <v>66</v>
+      </c>
+      <c r="C1987">
+        <v>4420.3</v>
+      </c>
+      <c r="D1987" t="s">
+        <v>1989</v>
+      </c>
+    </row>
+    <row r="1988" spans="1:4">
+      <c r="A1988" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1988">
+        <v>67</v>
+      </c>
+      <c r="C1988">
+        <v>4409.2</v>
+      </c>
+      <c r="D1988" t="s">
+        <v>1990</v>
+      </c>
+    </row>
+    <row r="1989" spans="1:4">
+      <c r="A1989" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1989">
+        <v>68</v>
+      </c>
+      <c r="C1989">
+        <v>4370.9</v>
+      </c>
+      <c r="D1989" t="s">
+        <v>1991</v>
+      </c>
+    </row>
+    <row r="1990" spans="1:4">
+      <c r="A1990" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1990">
+        <v>69</v>
+      </c>
+      <c r="C1990">
+        <v>4273.4</v>
+      </c>
+      <c r="D1990" t="s">
+        <v>1992</v>
+      </c>
+    </row>
+    <row r="1991" spans="1:4">
+      <c r="A1991" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1991">
+        <v>70</v>
+      </c>
+      <c r="C1991">
+        <v>4208.8</v>
+      </c>
+      <c r="D1991" t="s">
+        <v>1993</v>
+      </c>
+    </row>
+    <row r="1992" spans="1:4">
+      <c r="A1992" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1992">
+        <v>71</v>
+      </c>
+      <c r="C1992">
+        <v>4174.3</v>
+      </c>
+      <c r="D1992" t="s">
+        <v>1994</v>
+      </c>
+    </row>
+    <row r="1993" spans="1:4">
+      <c r="A1993" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1993">
+        <v>72</v>
+      </c>
+      <c r="C1993">
+        <v>4118.9</v>
+      </c>
+      <c r="D1993" t="s">
+        <v>1995</v>
+      </c>
+    </row>
+    <row r="1994" spans="1:4">
+      <c r="A1994" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1994">
+        <v>73</v>
+      </c>
+      <c r="C1994">
+        <v>4704.8</v>
+      </c>
+      <c r="D1994" t="s">
+        <v>1996</v>
+      </c>
+    </row>
+    <row r="1995" spans="1:4">
+      <c r="A1995" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1995">
+        <v>74</v>
+      </c>
+      <c r="C1995">
+        <v>4635</v>
+      </c>
+      <c r="D1995" t="s">
+        <v>1997</v>
+      </c>
+    </row>
+    <row r="1996" spans="1:4">
+      <c r="A1996" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1996">
+        <v>75</v>
+      </c>
+      <c r="C1996">
+        <v>4606.5</v>
+      </c>
+      <c r="D1996" t="s">
+        <v>1998</v>
+      </c>
+    </row>
+    <row r="1997" spans="1:4">
+      <c r="A1997" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1997">
+        <v>76</v>
+      </c>
+      <c r="C1997">
+        <v>4605.9</v>
+      </c>
+      <c r="D1997" t="s">
+        <v>1999</v>
+      </c>
+    </row>
+    <row r="1998" spans="1:4">
+      <c r="A1998" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1998">
+        <v>77</v>
+      </c>
+      <c r="C1998">
+        <v>4541.2</v>
+      </c>
+      <c r="D1998" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="1999" spans="1:4">
+      <c r="A1999" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1999">
+        <v>78</v>
+      </c>
+      <c r="C1999">
+        <v>4559.7</v>
+      </c>
+      <c r="D1999" t="s">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="2000" spans="1:4">
+      <c r="A2000" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B2000">
+        <v>79</v>
+      </c>
+      <c r="C2000">
+        <v>4496.6</v>
+      </c>
+      <c r="D2000" t="s">
+        <v>2002</v>
+      </c>
+    </row>
+    <row r="2001" spans="1:4">
+      <c r="A2001" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B2001">
+        <v>80</v>
+      </c>
+      <c r="C2001">
+        <v>4479.2</v>
+      </c>
+      <c r="D2001" t="s">
+        <v>2003</v>
+      </c>
+    </row>
+    <row r="2002" spans="1:4">
+      <c r="A2002" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B2002">
+        <v>81</v>
+      </c>
+      <c r="C2002">
+        <v>4525.1</v>
+      </c>
+      <c r="D2002" t="s">
+        <v>2004</v>
+      </c>
+    </row>
+    <row r="2003" spans="1:4">
+      <c r="A2003" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B2003">
+        <v>82</v>
+      </c>
+      <c r="C2003">
+        <v>4546.2</v>
+      </c>
+      <c r="D2003" t="s">
+        <v>2005</v>
+      </c>
+    </row>
+    <row r="2004" spans="1:4">
+      <c r="A2004" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B2004">
+        <v>83</v>
+      </c>
+      <c r="C2004">
+        <v>4578.5</v>
+      </c>
+      <c r="D2004" t="s">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="2005" spans="1:4">
+      <c r="A2005" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B2005">
+        <v>84</v>
+      </c>
+      <c r="C2005">
+        <v>4620.7</v>
+      </c>
+      <c r="D2005" t="s">
+        <v>2007</v>
+      </c>
+    </row>
+    <row r="2006" spans="1:4">
+      <c r="A2006" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B2006">
+        <v>85</v>
+      </c>
+      <c r="C2006">
+        <v>4714.6</v>
+      </c>
+      <c r="D2006" t="s">
+        <v>2008</v>
+      </c>
+    </row>
+    <row r="2007" spans="1:4">
+      <c r="A2007" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B2007">
+        <v>86</v>
+      </c>
+      <c r="C2007">
+        <v>4732.3</v>
+      </c>
+      <c r="D2007" t="s">
+        <v>2009</v>
+      </c>
+    </row>
+    <row r="2008" spans="1:4">
+      <c r="A2008" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B2008">
+        <v>87</v>
+      </c>
+      <c r="C2008">
+        <v>4774.8</v>
+      </c>
+      <c r="D2008" t="s">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="2009" spans="1:4">
+      <c r="A2009" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B2009">
+        <v>88</v>
+      </c>
+      <c r="C2009">
+        <v>4733.5</v>
+      </c>
+      <c r="D2009" t="s">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="2010" spans="1:4">
+      <c r="A2010" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B2010">
+        <v>89</v>
+      </c>
+      <c r="C2010">
+        <v>4541.9</v>
+      </c>
+      <c r="D2010" t="s">
+        <v>2012</v>
+      </c>
+    </row>
+    <row r="2011" spans="1:4">
+      <c r="A2011" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B2011">
+        <v>90</v>
+      </c>
+      <c r="C2011">
+        <v>4503.7</v>
+      </c>
+      <c r="D2011" t="s">
+        <v>2013</v>
+      </c>
+    </row>
+    <row r="2012" spans="1:4">
+      <c r="A2012" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B2012">
+        <v>91</v>
+      </c>
+      <c r="C2012">
+        <v>4460.4</v>
+      </c>
+      <c r="D2012" t="s">
+        <v>2014</v>
+      </c>
+    </row>
+    <row r="2013" spans="1:4">
+      <c r="A2013" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B2013">
+        <v>92</v>
+      </c>
+      <c r="C2013">
+        <v>4493.1</v>
+      </c>
+      <c r="D2013" t="s">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="2014" spans="1:4">
+      <c r="A2014" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B2014">
+        <v>93</v>
+      </c>
+      <c r="C2014">
+        <v>4409.7</v>
+      </c>
+      <c r="D2014" t="s">
+        <v>2016</v>
+      </c>
+    </row>
+    <row r="2015" spans="1:4">
+      <c r="A2015" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B2015">
+        <v>94</v>
+      </c>
+      <c r="C2015">
+        <v>4345.6</v>
+      </c>
+      <c r="D2015" t="s">
+        <v>2017</v>
+      </c>
+    </row>
+    <row r="2016" spans="1:4">
+      <c r="A2016" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B2016">
+        <v>95</v>
+      </c>
+      <c r="C2016">
+        <v>4340.6</v>
+      </c>
+      <c r="D2016" t="s">
+        <v>2018</v>
+      </c>
+    </row>
+    <row r="2017" spans="1:4">
+      <c r="A2017" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B2017">
+        <v>96</v>
+      </c>
+      <c r="C2017">
+        <v>4372.5</v>
+      </c>
+      <c r="D2017" t="s">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="2018" spans="1:4">
+      <c r="A2018" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2018">
+        <v>1</v>
+      </c>
+      <c r="C2018">
+        <v>5606</v>
+      </c>
+      <c r="D2018" t="s">
+        <v>2020</v>
+      </c>
+    </row>
+    <row r="2019" spans="1:4">
+      <c r="A2019" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2019">
+        <v>2</v>
+      </c>
+      <c r="C2019">
+        <v>5556.2</v>
+      </c>
+      <c r="D2019" t="s">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="2020" spans="1:4">
+      <c r="A2020" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2020">
+        <v>3</v>
+      </c>
+      <c r="C2020">
+        <v>5439.7</v>
+      </c>
+      <c r="D2020" t="s">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="2021" spans="1:4">
+      <c r="A2021" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2021">
+        <v>4</v>
+      </c>
+      <c r="C2021">
+        <v>5317.7</v>
+      </c>
+      <c r="D2021" t="s">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="2022" spans="1:4">
+      <c r="A2022" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2022">
+        <v>5</v>
+      </c>
+      <c r="C2022">
+        <v>4873.4</v>
+      </c>
+      <c r="D2022" t="s">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="2023" spans="1:4">
+      <c r="A2023" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2023">
+        <v>6</v>
+      </c>
+      <c r="C2023">
+        <v>4828.2</v>
+      </c>
+      <c r="D2023" t="s">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="2024" spans="1:4">
+      <c r="A2024" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2024">
+        <v>7</v>
+      </c>
+      <c r="C2024">
+        <v>4779.8</v>
+      </c>
+      <c r="D2024" t="s">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2025" spans="1:4">
+      <c r="A2025" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2025">
+        <v>8</v>
+      </c>
+      <c r="C2025">
+        <v>4744.3</v>
+      </c>
+      <c r="D2025" t="s">
+        <v>2027</v>
+      </c>
+    </row>
+    <row r="2026" spans="1:4">
+      <c r="A2026" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2026">
+        <v>9</v>
+      </c>
+      <c r="C2026">
+        <v>4465.1</v>
+      </c>
+      <c r="D2026" t="s">
+        <v>2028</v>
+      </c>
+    </row>
+    <row r="2027" spans="1:4">
+      <c r="A2027" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2027">
+        <v>10</v>
+      </c>
+      <c r="C2027">
+        <v>4434.8</v>
+      </c>
+      <c r="D2027" t="s">
+        <v>2029</v>
+      </c>
+    </row>
+    <row r="2028" spans="1:4">
+      <c r="A2028" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2028">
+        <v>11</v>
+      </c>
+      <c r="C2028">
+        <v>4410.6</v>
+      </c>
+      <c r="D2028" t="s">
+        <v>2030</v>
+      </c>
+    </row>
+    <row r="2029" spans="1:4">
+      <c r="A2029" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2029">
+        <v>12</v>
+      </c>
+      <c r="C2029">
+        <v>4401.4</v>
+      </c>
+      <c r="D2029" t="s">
+        <v>2031</v>
+      </c>
+    </row>
+    <row r="2030" spans="1:4">
+      <c r="A2030" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2030">
+        <v>13</v>
+      </c>
+      <c r="C2030">
+        <v>4424</v>
+      </c>
+      <c r="D2030" t="s">
+        <v>2032</v>
+      </c>
+    </row>
+    <row r="2031" spans="1:4">
+      <c r="A2031" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2031">
+        <v>14</v>
+      </c>
+      <c r="C2031">
+        <v>4391.1</v>
+      </c>
+      <c r="D2031" t="s">
+        <v>2033</v>
+      </c>
+    </row>
+    <row r="2032" spans="1:4">
+      <c r="A2032" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2032">
+        <v>15</v>
+      </c>
+      <c r="C2032">
+        <v>4365.4</v>
+      </c>
+      <c r="D2032" t="s">
+        <v>2034</v>
+      </c>
+    </row>
+    <row r="2033" spans="1:4">
+      <c r="A2033" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2033">
+        <v>16</v>
+      </c>
+      <c r="C2033">
+        <v>4335.9</v>
+      </c>
+      <c r="D2033" t="s">
+        <v>2035</v>
+      </c>
+    </row>
+    <row r="2034" spans="1:4">
+      <c r="A2034" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2034">
+        <v>17</v>
+      </c>
+      <c r="C2034">
+        <v>4315.9</v>
+      </c>
+      <c r="D2034" t="s">
+        <v>2036</v>
+      </c>
+    </row>
+    <row r="2035" spans="1:4">
+      <c r="A2035" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2035">
+        <v>18</v>
+      </c>
+      <c r="C2035">
+        <v>4279.2</v>
+      </c>
+      <c r="D2035" t="s">
+        <v>2037</v>
+      </c>
+    </row>
+    <row r="2036" spans="1:4">
+      <c r="A2036" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2036">
+        <v>19</v>
+      </c>
+      <c r="C2036">
+        <v>4227.8</v>
+      </c>
+      <c r="D2036" t="s">
+        <v>2038</v>
+      </c>
+    </row>
+    <row r="2037" spans="1:4">
+      <c r="A2037" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2037">
+        <v>20</v>
+      </c>
+      <c r="C2037">
+        <v>4193.5</v>
+      </c>
+      <c r="D2037" t="s">
+        <v>2039</v>
+      </c>
+    </row>
+    <row r="2038" spans="1:4">
+      <c r="A2038" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2038">
+        <v>21</v>
+      </c>
+      <c r="C2038">
+        <v>4215.6</v>
+      </c>
+      <c r="D2038" t="s">
+        <v>2040</v>
+      </c>
+    </row>
+    <row r="2039" spans="1:4">
+      <c r="A2039" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2039">
+        <v>22</v>
+      </c>
+      <c r="C2039">
+        <v>4195.6</v>
+      </c>
+      <c r="D2039" t="s">
+        <v>2041</v>
+      </c>
+    </row>
+    <row r="2040" spans="1:4">
+      <c r="A2040" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2040">
+        <v>23</v>
+      </c>
+      <c r="C2040">
+        <v>4173.4</v>
+      </c>
+      <c r="D2040" t="s">
+        <v>2042</v>
+      </c>
+    </row>
+    <row r="2041" spans="1:4">
+      <c r="A2041" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2041">
+        <v>24</v>
+      </c>
+      <c r="C2041">
+        <v>4146.6</v>
+      </c>
+      <c r="D2041" t="s">
+        <v>2043</v>
+      </c>
+    </row>
+    <row r="2042" spans="1:4">
+      <c r="A2042" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2042">
+        <v>25</v>
+      </c>
+      <c r="C2042">
+        <v>4196.8</v>
+      </c>
+      <c r="D2042" t="s">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="2043" spans="1:4">
+      <c r="A2043" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2043">
+        <v>26</v>
+      </c>
+      <c r="C2043">
+        <v>4221.3</v>
+      </c>
+      <c r="D2043" t="s">
+        <v>2045</v>
+      </c>
+    </row>
+    <row r="2044" spans="1:4">
+      <c r="A2044" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2044">
+        <v>27</v>
+      </c>
+      <c r="C2044">
+        <v>4243.1</v>
+      </c>
+      <c r="D2044" t="s">
+        <v>2046</v>
+      </c>
+    </row>
+    <row r="2045" spans="1:4">
+      <c r="A2045" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2045">
+        <v>28</v>
+      </c>
+      <c r="C2045">
+        <v>4256.4</v>
+      </c>
+      <c r="D2045" t="s">
+        <v>2047</v>
+      </c>
+    </row>
+    <row r="2046" spans="1:4">
+      <c r="A2046" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2046">
+        <v>29</v>
+      </c>
+      <c r="C2046">
+        <v>4280.9</v>
+      </c>
+      <c r="D2046" t="s">
+        <v>2048</v>
+      </c>
+    </row>
+    <row r="2047" spans="1:4">
+      <c r="A2047" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2047">
+        <v>30</v>
+      </c>
+      <c r="C2047">
+        <v>4286.5</v>
+      </c>
+      <c r="D2047" t="s">
+        <v>2049</v>
+      </c>
+    </row>
+    <row r="2048" spans="1:4">
+      <c r="A2048" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2048">
+        <v>31</v>
+      </c>
+      <c r="C2048">
+        <v>4372.3</v>
+      </c>
+      <c r="D2048" t="s">
+        <v>2050</v>
+      </c>
+    </row>
+    <row r="2049" spans="1:4">
+      <c r="A2049" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2049">
+        <v>32</v>
+      </c>
+      <c r="C2049">
+        <v>4469.7</v>
+      </c>
+      <c r="D2049" t="s">
+        <v>2051</v>
+      </c>
+    </row>
+    <row r="2050" spans="1:4">
+      <c r="A2050" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2050">
+        <v>33</v>
+      </c>
+      <c r="C2050">
+        <v>4361.3</v>
+      </c>
+      <c r="D2050" t="s">
+        <v>2052</v>
+      </c>
+    </row>
+    <row r="2051" spans="1:4">
+      <c r="A2051" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2051">
+        <v>34</v>
+      </c>
+      <c r="C2051">
+        <v>4433</v>
+      </c>
+      <c r="D2051" t="s">
+        <v>2053</v>
+      </c>
+    </row>
+    <row r="2052" spans="1:4">
+      <c r="A2052" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2052">
+        <v>35</v>
+      </c>
+      <c r="C2052">
+        <v>4479.6</v>
+      </c>
+      <c r="D2052" t="s">
+        <v>2054</v>
+      </c>
+    </row>
+    <row r="2053" spans="1:4">
+      <c r="A2053" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2053">
+        <v>36</v>
+      </c>
+      <c r="C2053">
+        <v>4584.8</v>
+      </c>
+      <c r="D2053" t="s">
+        <v>2055</v>
+      </c>
+    </row>
+    <row r="2054" spans="1:4">
+      <c r="A2054" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2054">
+        <v>37</v>
+      </c>
+      <c r="C2054">
+        <v>4396.5</v>
+      </c>
+      <c r="D2054" t="s">
+        <v>2056</v>
+      </c>
+    </row>
+    <row r="2055" spans="1:4">
+      <c r="A2055" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2055">
+        <v>38</v>
+      </c>
+      <c r="C2055">
+        <v>4369.5</v>
+      </c>
+      <c r="D2055" t="s">
+        <v>2057</v>
+      </c>
+    </row>
+    <row r="2056" spans="1:4">
+      <c r="A2056" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2056">
+        <v>39</v>
+      </c>
+      <c r="C2056">
+        <v>4406.2</v>
+      </c>
+      <c r="D2056" t="s">
+        <v>2058</v>
+      </c>
+    </row>
+    <row r="2057" spans="1:4">
+      <c r="A2057" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2057">
+        <v>40</v>
+      </c>
+      <c r="C2057">
+        <v>4444.8</v>
+      </c>
+      <c r="D2057" t="s">
+        <v>2059</v>
+      </c>
+    </row>
+    <row r="2058" spans="1:4">
+      <c r="A2058" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2058">
+        <v>41</v>
+      </c>
+      <c r="C2058">
+        <v>4610.7</v>
+      </c>
+      <c r="D2058" t="s">
+        <v>2060</v>
+      </c>
+    </row>
+    <row r="2059" spans="1:4">
+      <c r="A2059" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2059">
+        <v>42</v>
+      </c>
+      <c r="C2059">
+        <v>4589.9</v>
+      </c>
+      <c r="D2059" t="s">
+        <v>2061</v>
+      </c>
+    </row>
+    <row r="2060" spans="1:4">
+      <c r="A2060" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2060">
+        <v>43</v>
+      </c>
+      <c r="C2060">
+        <v>4588.3</v>
+      </c>
+      <c r="D2060" t="s">
+        <v>2062</v>
+      </c>
+    </row>
+    <row r="2061" spans="1:4">
+      <c r="A2061" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2061">
+        <v>44</v>
+      </c>
+      <c r="C2061">
+        <v>4577.5</v>
+      </c>
+      <c r="D2061" t="s">
+        <v>2063</v>
+      </c>
+    </row>
+    <row r="2062" spans="1:4">
+      <c r="A2062" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2062">
+        <v>45</v>
+      </c>
+      <c r="C2062">
+        <v>4528</v>
+      </c>
+      <c r="D2062" t="s">
+        <v>2064</v>
+      </c>
+    </row>
+    <row r="2063" spans="1:4">
+      <c r="A2063" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2063">
+        <v>46</v>
+      </c>
+      <c r="C2063">
+        <v>4493.3</v>
+      </c>
+      <c r="D2063" t="s">
+        <v>2065</v>
+      </c>
+    </row>
+    <row r="2064" spans="1:4">
+      <c r="A2064" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2064">
+        <v>47</v>
+      </c>
+      <c r="C2064">
+        <v>4444.1</v>
+      </c>
+      <c r="D2064" t="s">
+        <v>2066</v>
+      </c>
+    </row>
+    <row r="2065" spans="1:4">
+      <c r="A2065" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2065">
+        <v>48</v>
+      </c>
+      <c r="C2065">
+        <v>4460.1</v>
+      </c>
+      <c r="D2065" t="s">
+        <v>2067</v>
+      </c>
+    </row>
+    <row r="2066" spans="1:4">
+      <c r="A2066" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2066">
+        <v>49</v>
+      </c>
+      <c r="C2066">
+        <v>4266.1</v>
+      </c>
+      <c r="D2066" t="s">
+        <v>2068</v>
+      </c>
+    </row>
+    <row r="2067" spans="1:4">
+      <c r="A2067" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2067">
+        <v>50</v>
+      </c>
+      <c r="C2067">
+        <v>4248.2</v>
+      </c>
+      <c r="D2067" t="s">
+        <v>2069</v>
+      </c>
+    </row>
+    <row r="2068" spans="1:4">
+      <c r="A2068" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2068">
+        <v>51</v>
+      </c>
+      <c r="C2068">
+        <v>4235.5</v>
+      </c>
+      <c r="D2068" t="s">
+        <v>2070</v>
+      </c>
+    </row>
+    <row r="2069" spans="1:4">
+      <c r="A2069" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2069">
+        <v>52</v>
+      </c>
+      <c r="C2069">
+        <v>4250</v>
+      </c>
+      <c r="D2069" t="s">
+        <v>2071</v>
+      </c>
+    </row>
+    <row r="2070" spans="1:4">
+      <c r="A2070" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2070">
+        <v>53</v>
+      </c>
+      <c r="C2070">
+        <v>4237.1</v>
+      </c>
+      <c r="D2070" t="s">
+        <v>2072</v>
+      </c>
+    </row>
+    <row r="2071" spans="1:4">
+      <c r="A2071" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2071">
+        <v>54</v>
+      </c>
+      <c r="C2071">
+        <v>4218.4</v>
+      </c>
+      <c r="D2071" t="s">
+        <v>2073</v>
+      </c>
+    </row>
+    <row r="2072" spans="1:4">
+      <c r="A2072" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2072">
+        <v>55</v>
+      </c>
+      <c r="C2072">
+        <v>4233.8</v>
+      </c>
+      <c r="D2072" t="s">
+        <v>2074</v>
+      </c>
+    </row>
+    <row r="2073" spans="1:4">
+      <c r="A2073" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2073">
+        <v>56</v>
+      </c>
+      <c r="C2073">
+        <v>4248.2</v>
+      </c>
+      <c r="D2073" t="s">
+        <v>2075</v>
+      </c>
+    </row>
+    <row r="2074" spans="1:4">
+      <c r="A2074" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2074">
+        <v>57</v>
+      </c>
+      <c r="C2074">
+        <v>4280.2</v>
+      </c>
+      <c r="D2074" t="s">
+        <v>2076</v>
+      </c>
+    </row>
+    <row r="2075" spans="1:4">
+      <c r="A2075" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2075">
+        <v>58</v>
+      </c>
+      <c r="C2075">
+        <v>4267</v>
+      </c>
+      <c r="D2075" t="s">
+        <v>2077</v>
+      </c>
+    </row>
+    <row r="2076" spans="1:4">
+      <c r="A2076" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2076">
+        <v>59</v>
+      </c>
+      <c r="C2076">
+        <v>4288</v>
+      </c>
+      <c r="D2076" t="s">
+        <v>2078</v>
+      </c>
+    </row>
+    <row r="2077" spans="1:4">
+      <c r="A2077" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2077">
+        <v>60</v>
+      </c>
+      <c r="C2077">
+        <v>4335.1</v>
+      </c>
+      <c r="D2077" t="s">
+        <v>2079</v>
+      </c>
+    </row>
+    <row r="2078" spans="1:4">
+      <c r="A2078" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2078">
+        <v>61</v>
+      </c>
+      <c r="C2078">
+        <v>4401.2</v>
+      </c>
+      <c r="D2078" t="s">
+        <v>2080</v>
+      </c>
+    </row>
+    <row r="2079" spans="1:4">
+      <c r="A2079" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2079">
+        <v>62</v>
+      </c>
+      <c r="C2079">
+        <v>4386.4</v>
+      </c>
+      <c r="D2079" t="s">
+        <v>2081</v>
+      </c>
+    </row>
+    <row r="2080" spans="1:4">
+      <c r="A2080" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2080">
+        <v>63</v>
+      </c>
+      <c r="C2080">
+        <v>4381.2</v>
+      </c>
+      <c r="D2080" t="s">
+        <v>2082</v>
+      </c>
+    </row>
+    <row r="2081" spans="1:4">
+      <c r="A2081" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2081">
+        <v>64</v>
+      </c>
+      <c r="C2081">
+        <v>4410.3</v>
+      </c>
+      <c r="D2081" t="s">
+        <v>2083</v>
+      </c>
+    </row>
+    <row r="2082" spans="1:4">
+      <c r="A2082" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2082">
+        <v>65</v>
+      </c>
+      <c r="C2082">
+        <v>4439.1</v>
+      </c>
+      <c r="D2082" t="s">
+        <v>2084</v>
+      </c>
+    </row>
+    <row r="2083" spans="1:4">
+      <c r="A2083" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2083">
+        <v>66</v>
+      </c>
+      <c r="C2083">
+        <v>4400.3</v>
+      </c>
+      <c r="D2083" t="s">
+        <v>2085</v>
+      </c>
+    </row>
+    <row r="2084" spans="1:4">
+      <c r="A2084" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2084">
+        <v>67</v>
+      </c>
+      <c r="C2084">
+        <v>4379.2</v>
+      </c>
+      <c r="D2084" t="s">
+        <v>2086</v>
+      </c>
+    </row>
+    <row r="2085" spans="1:4">
+      <c r="A2085" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2085">
+        <v>68</v>
+      </c>
+      <c r="C2085">
+        <v>4340.9</v>
+      </c>
+      <c r="D2085" t="s">
+        <v>2087</v>
+      </c>
+    </row>
+    <row r="2086" spans="1:4">
+      <c r="A2086" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2086">
+        <v>69</v>
+      </c>
+      <c r="C2086">
+        <v>4233.4</v>
+      </c>
+      <c r="D2086" t="s">
+        <v>2088</v>
+      </c>
+    </row>
+    <row r="2087" spans="1:4">
+      <c r="A2087" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2087">
+        <v>70</v>
+      </c>
+      <c r="C2087">
+        <v>4158.8</v>
+      </c>
+      <c r="D2087" t="s">
+        <v>2089</v>
+      </c>
+    </row>
+    <row r="2088" spans="1:4">
+      <c r="A2088" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2088">
+        <v>71</v>
+      </c>
+      <c r="C2088">
+        <v>4124.3</v>
+      </c>
+      <c r="D2088" t="s">
+        <v>2090</v>
+      </c>
+    </row>
+    <row r="2089" spans="1:4">
+      <c r="A2089" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2089">
+        <v>72</v>
+      </c>
+      <c r="C2089">
+        <v>4078.9</v>
+      </c>
+      <c r="D2089" t="s">
+        <v>2091</v>
+      </c>
+    </row>
+    <row r="2090" spans="1:4">
+      <c r="A2090" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2090">
+        <v>73</v>
+      </c>
+      <c r="C2090">
+        <v>4674.8</v>
+      </c>
+      <c r="D2090" t="s">
+        <v>2092</v>
+      </c>
+    </row>
+    <row r="2091" spans="1:4">
+      <c r="A2091" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2091">
+        <v>74</v>
+      </c>
+      <c r="C2091">
+        <v>4605</v>
+      </c>
+      <c r="D2091" t="s">
+        <v>2093</v>
+      </c>
+    </row>
+    <row r="2092" spans="1:4">
+      <c r="A2092" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2092">
+        <v>75</v>
+      </c>
+      <c r="C2092">
+        <v>4576.5</v>
+      </c>
+      <c r="D2092" t="s">
+        <v>2094</v>
+      </c>
+    </row>
+    <row r="2093" spans="1:4">
+      <c r="A2093" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2093">
+        <v>76</v>
+      </c>
+      <c r="C2093">
+        <v>4575.9</v>
+      </c>
+      <c r="D2093" t="s">
+        <v>2095</v>
+      </c>
+    </row>
+    <row r="2094" spans="1:4">
+      <c r="A2094" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2094">
+        <v>77</v>
+      </c>
+      <c r="C2094">
+        <v>4501.2</v>
+      </c>
+      <c r="D2094" t="s">
+        <v>2096</v>
+      </c>
+    </row>
+    <row r="2095" spans="1:4">
+      <c r="A2095" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2095">
+        <v>78</v>
+      </c>
+      <c r="C2095">
+        <v>4519.7</v>
+      </c>
+      <c r="D2095" t="s">
+        <v>2097</v>
+      </c>
+    </row>
+    <row r="2096" spans="1:4">
+      <c r="A2096" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2096">
+        <v>79</v>
+      </c>
+      <c r="C2096">
+        <v>4446.6</v>
+      </c>
+      <c r="D2096" t="s">
+        <v>2098</v>
+      </c>
+    </row>
+    <row r="2097" spans="1:4">
+      <c r="A2097" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2097">
+        <v>80</v>
+      </c>
+      <c r="C2097">
+        <v>4429.2</v>
+      </c>
+      <c r="D2097" t="s">
+        <v>2099</v>
+      </c>
+    </row>
+    <row r="2098" spans="1:4">
+      <c r="A2098" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2098">
+        <v>81</v>
+      </c>
+      <c r="C2098">
+        <v>4475.1</v>
+      </c>
+      <c r="D2098" t="s">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="2099" spans="1:4">
+      <c r="A2099" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2099">
+        <v>82</v>
+      </c>
+      <c r="C2099">
+        <v>4496.2</v>
+      </c>
+      <c r="D2099" t="s">
+        <v>2101</v>
+      </c>
+    </row>
+    <row r="2100" spans="1:4">
+      <c r="A2100" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2100">
+        <v>83</v>
+      </c>
+      <c r="C2100">
+        <v>4528.5</v>
+      </c>
+      <c r="D2100" t="s">
+        <v>2102</v>
+      </c>
+    </row>
+    <row r="2101" spans="1:4">
+      <c r="A2101" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2101">
+        <v>84</v>
+      </c>
+      <c r="C2101">
+        <v>4550.7</v>
+      </c>
+      <c r="D2101" t="s">
+        <v>2103</v>
+      </c>
+    </row>
+    <row r="2102" spans="1:4">
+      <c r="A2102" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2102">
+        <v>85</v>
+      </c>
+      <c r="C2102">
+        <v>4634.6</v>
+      </c>
+      <c r="D2102" t="s">
+        <v>2104</v>
+      </c>
+    </row>
+    <row r="2103" spans="1:4">
+      <c r="A2103" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2103">
+        <v>86</v>
+      </c>
+      <c r="C2103">
+        <v>4642.3</v>
+      </c>
+      <c r="D2103" t="s">
+        <v>2105</v>
+      </c>
+    </row>
+    <row r="2104" spans="1:4">
+      <c r="A2104" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2104">
+        <v>87</v>
+      </c>
+      <c r="C2104">
+        <v>4684.8</v>
+      </c>
+      <c r="D2104" t="s">
+        <v>2106</v>
+      </c>
+    </row>
+    <row r="2105" spans="1:4">
+      <c r="A2105" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2105">
+        <v>88</v>
+      </c>
+      <c r="C2105">
+        <v>4653.5</v>
+      </c>
+      <c r="D2105" t="s">
+        <v>2107</v>
+      </c>
+    </row>
+    <row r="2106" spans="1:4">
+      <c r="A2106" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2106">
+        <v>89</v>
+      </c>
+      <c r="C2106">
+        <v>4481.9</v>
+      </c>
+      <c r="D2106" t="s">
+        <v>2108</v>
+      </c>
+    </row>
+    <row r="2107" spans="1:4">
+      <c r="A2107" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2107">
+        <v>90</v>
+      </c>
+      <c r="C2107">
+        <v>4463.7</v>
+      </c>
+      <c r="D2107" t="s">
+        <v>2109</v>
+      </c>
+    </row>
+    <row r="2108" spans="1:4">
+      <c r="A2108" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2108">
+        <v>91</v>
+      </c>
+      <c r="C2108">
+        <v>4440.4</v>
+      </c>
+      <c r="D2108" t="s">
+        <v>2110</v>
+      </c>
+    </row>
+    <row r="2109" spans="1:4">
+      <c r="A2109" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2109">
+        <v>92</v>
+      </c>
+      <c r="C2109">
+        <v>4473.1</v>
+      </c>
+      <c r="D2109" t="s">
+        <v>2111</v>
+      </c>
+    </row>
+    <row r="2110" spans="1:4">
+      <c r="A2110" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2110">
+        <v>93</v>
+      </c>
+      <c r="C2110">
+        <v>4399.7</v>
+      </c>
+      <c r="D2110" t="s">
+        <v>2112</v>
+      </c>
+    </row>
+    <row r="2111" spans="1:4">
+      <c r="A2111" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2111">
+        <v>94</v>
+      </c>
+      <c r="C2111">
+        <v>4335.6</v>
+      </c>
+      <c r="D2111" t="s">
+        <v>2113</v>
+      </c>
+    </row>
+    <row r="2112" spans="1:4">
+      <c r="A2112" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2112">
+        <v>95</v>
+      </c>
+      <c r="C2112">
+        <v>4320.6</v>
+      </c>
+      <c r="D2112" t="s">
+        <v>2114</v>
+      </c>
+    </row>
+    <row r="2113" spans="1:4">
+      <c r="A2113" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2113">
+        <v>96</v>
+      </c>
+      <c r="C2113">
+        <v>4342.5</v>
+      </c>
+      <c r="D2113" t="s">
+        <v>2115</v>
       </c>
     </row>
   </sheetData>

--- a/Market Fundamentals/Transelectrica_data/Cons_Prod_final/Weekly_Production_2026.xlsx
+++ b/Market Fundamentals/Transelectrica_data/Cons_Prod_final/Weekly_Production_2026.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2116" uniqueCount="2116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2500" uniqueCount="2500">
   <si>
     <t>Date</t>
   </si>
@@ -6362,6 +6362,1158 @@
   </si>
   <si>
     <t>22.05.202696.0</t>
+  </si>
+  <si>
+    <t>23.05.20261.0</t>
+  </si>
+  <si>
+    <t>23.05.20262.0</t>
+  </si>
+  <si>
+    <t>23.05.20263.0</t>
+  </si>
+  <si>
+    <t>23.05.20264.0</t>
+  </si>
+  <si>
+    <t>23.05.20265.0</t>
+  </si>
+  <si>
+    <t>23.05.20266.0</t>
+  </si>
+  <si>
+    <t>23.05.20267.0</t>
+  </si>
+  <si>
+    <t>23.05.20268.0</t>
+  </si>
+  <si>
+    <t>23.05.20269.0</t>
+  </si>
+  <si>
+    <t>23.05.202610.0</t>
+  </si>
+  <si>
+    <t>23.05.202611.0</t>
+  </si>
+  <si>
+    <t>23.05.202612.0</t>
+  </si>
+  <si>
+    <t>23.05.202613.0</t>
+  </si>
+  <si>
+    <t>23.05.202614.0</t>
+  </si>
+  <si>
+    <t>23.05.202615.0</t>
+  </si>
+  <si>
+    <t>23.05.202616.0</t>
+  </si>
+  <si>
+    <t>23.05.202617.0</t>
+  </si>
+  <si>
+    <t>23.05.202618.0</t>
+  </si>
+  <si>
+    <t>23.05.202619.0</t>
+  </si>
+  <si>
+    <t>23.05.202620.0</t>
+  </si>
+  <si>
+    <t>23.05.202621.0</t>
+  </si>
+  <si>
+    <t>23.05.202622.0</t>
+  </si>
+  <si>
+    <t>23.05.202623.0</t>
+  </si>
+  <si>
+    <t>23.05.202624.0</t>
+  </si>
+  <si>
+    <t>23.05.202625.0</t>
+  </si>
+  <si>
+    <t>23.05.202626.0</t>
+  </si>
+  <si>
+    <t>23.05.202627.0</t>
+  </si>
+  <si>
+    <t>23.05.202628.0</t>
+  </si>
+  <si>
+    <t>23.05.202629.0</t>
+  </si>
+  <si>
+    <t>23.05.202630.0</t>
+  </si>
+  <si>
+    <t>23.05.202631.0</t>
+  </si>
+  <si>
+    <t>23.05.202632.0</t>
+  </si>
+  <si>
+    <t>23.05.202633.0</t>
+  </si>
+  <si>
+    <t>23.05.202634.0</t>
+  </si>
+  <si>
+    <t>23.05.202635.0</t>
+  </si>
+  <si>
+    <t>23.05.202636.0</t>
+  </si>
+  <si>
+    <t>23.05.202637.0</t>
+  </si>
+  <si>
+    <t>23.05.202638.0</t>
+  </si>
+  <si>
+    <t>23.05.202639.0</t>
+  </si>
+  <si>
+    <t>23.05.202640.0</t>
+  </si>
+  <si>
+    <t>23.05.202641.0</t>
+  </si>
+  <si>
+    <t>23.05.202642.0</t>
+  </si>
+  <si>
+    <t>23.05.202643.0</t>
+  </si>
+  <si>
+    <t>23.05.202644.0</t>
+  </si>
+  <si>
+    <t>23.05.202645.0</t>
+  </si>
+  <si>
+    <t>23.05.202646.0</t>
+  </si>
+  <si>
+    <t>23.05.202647.0</t>
+  </si>
+  <si>
+    <t>23.05.202648.0</t>
+  </si>
+  <si>
+    <t>23.05.202649.0</t>
+  </si>
+  <si>
+    <t>23.05.202650.0</t>
+  </si>
+  <si>
+    <t>23.05.202651.0</t>
+  </si>
+  <si>
+    <t>23.05.202652.0</t>
+  </si>
+  <si>
+    <t>23.05.202653.0</t>
+  </si>
+  <si>
+    <t>23.05.202654.0</t>
+  </si>
+  <si>
+    <t>23.05.202655.0</t>
+  </si>
+  <si>
+    <t>23.05.202656.0</t>
+  </si>
+  <si>
+    <t>23.05.202657.0</t>
+  </si>
+  <si>
+    <t>23.05.202658.0</t>
+  </si>
+  <si>
+    <t>23.05.202659.0</t>
+  </si>
+  <si>
+    <t>23.05.202660.0</t>
+  </si>
+  <si>
+    <t>23.05.202661.0</t>
+  </si>
+  <si>
+    <t>23.05.202662.0</t>
+  </si>
+  <si>
+    <t>23.05.202663.0</t>
+  </si>
+  <si>
+    <t>23.05.202664.0</t>
+  </si>
+  <si>
+    <t>23.05.202665.0</t>
+  </si>
+  <si>
+    <t>23.05.202666.0</t>
+  </si>
+  <si>
+    <t>23.05.202667.0</t>
+  </si>
+  <si>
+    <t>23.05.202668.0</t>
+  </si>
+  <si>
+    <t>23.05.202669.0</t>
+  </si>
+  <si>
+    <t>23.05.202670.0</t>
+  </si>
+  <si>
+    <t>23.05.202671.0</t>
+  </si>
+  <si>
+    <t>23.05.202672.0</t>
+  </si>
+  <si>
+    <t>23.05.202673.0</t>
+  </si>
+  <si>
+    <t>23.05.202674.0</t>
+  </si>
+  <si>
+    <t>23.05.202675.0</t>
+  </si>
+  <si>
+    <t>23.05.202676.0</t>
+  </si>
+  <si>
+    <t>23.05.202677.0</t>
+  </si>
+  <si>
+    <t>23.05.202678.0</t>
+  </si>
+  <si>
+    <t>23.05.202679.0</t>
+  </si>
+  <si>
+    <t>23.05.202680.0</t>
+  </si>
+  <si>
+    <t>23.05.202681.0</t>
+  </si>
+  <si>
+    <t>23.05.202682.0</t>
+  </si>
+  <si>
+    <t>23.05.202683.0</t>
+  </si>
+  <si>
+    <t>23.05.202684.0</t>
+  </si>
+  <si>
+    <t>23.05.202685.0</t>
+  </si>
+  <si>
+    <t>23.05.202686.0</t>
+  </si>
+  <si>
+    <t>23.05.202687.0</t>
+  </si>
+  <si>
+    <t>23.05.202688.0</t>
+  </si>
+  <si>
+    <t>23.05.202689.0</t>
+  </si>
+  <si>
+    <t>23.05.202690.0</t>
+  </si>
+  <si>
+    <t>23.05.202691.0</t>
+  </si>
+  <si>
+    <t>23.05.202692.0</t>
+  </si>
+  <si>
+    <t>23.05.202693.0</t>
+  </si>
+  <si>
+    <t>23.05.202694.0</t>
+  </si>
+  <si>
+    <t>23.05.202695.0</t>
+  </si>
+  <si>
+    <t>23.05.202696.0</t>
+  </si>
+  <si>
+    <t>24.05.20261.0</t>
+  </si>
+  <si>
+    <t>24.05.20262.0</t>
+  </si>
+  <si>
+    <t>24.05.20263.0</t>
+  </si>
+  <si>
+    <t>24.05.20264.0</t>
+  </si>
+  <si>
+    <t>24.05.20265.0</t>
+  </si>
+  <si>
+    <t>24.05.20266.0</t>
+  </si>
+  <si>
+    <t>24.05.20267.0</t>
+  </si>
+  <si>
+    <t>24.05.20268.0</t>
+  </si>
+  <si>
+    <t>24.05.20269.0</t>
+  </si>
+  <si>
+    <t>24.05.202610.0</t>
+  </si>
+  <si>
+    <t>24.05.202611.0</t>
+  </si>
+  <si>
+    <t>24.05.202612.0</t>
+  </si>
+  <si>
+    <t>24.05.202613.0</t>
+  </si>
+  <si>
+    <t>24.05.202614.0</t>
+  </si>
+  <si>
+    <t>24.05.202615.0</t>
+  </si>
+  <si>
+    <t>24.05.202616.0</t>
+  </si>
+  <si>
+    <t>24.05.202617.0</t>
+  </si>
+  <si>
+    <t>24.05.202618.0</t>
+  </si>
+  <si>
+    <t>24.05.202619.0</t>
+  </si>
+  <si>
+    <t>24.05.202620.0</t>
+  </si>
+  <si>
+    <t>24.05.202621.0</t>
+  </si>
+  <si>
+    <t>24.05.202622.0</t>
+  </si>
+  <si>
+    <t>24.05.202623.0</t>
+  </si>
+  <si>
+    <t>24.05.202624.0</t>
+  </si>
+  <si>
+    <t>24.05.202625.0</t>
+  </si>
+  <si>
+    <t>24.05.202626.0</t>
+  </si>
+  <si>
+    <t>24.05.202627.0</t>
+  </si>
+  <si>
+    <t>24.05.202628.0</t>
+  </si>
+  <si>
+    <t>24.05.202629.0</t>
+  </si>
+  <si>
+    <t>24.05.202630.0</t>
+  </si>
+  <si>
+    <t>24.05.202631.0</t>
+  </si>
+  <si>
+    <t>24.05.202632.0</t>
+  </si>
+  <si>
+    <t>24.05.202633.0</t>
+  </si>
+  <si>
+    <t>24.05.202634.0</t>
+  </si>
+  <si>
+    <t>24.05.202635.0</t>
+  </si>
+  <si>
+    <t>24.05.202636.0</t>
+  </si>
+  <si>
+    <t>24.05.202637.0</t>
+  </si>
+  <si>
+    <t>24.05.202638.0</t>
+  </si>
+  <si>
+    <t>24.05.202639.0</t>
+  </si>
+  <si>
+    <t>24.05.202640.0</t>
+  </si>
+  <si>
+    <t>24.05.202641.0</t>
+  </si>
+  <si>
+    <t>24.05.202642.0</t>
+  </si>
+  <si>
+    <t>24.05.202643.0</t>
+  </si>
+  <si>
+    <t>24.05.202644.0</t>
+  </si>
+  <si>
+    <t>24.05.202645.0</t>
+  </si>
+  <si>
+    <t>24.05.202646.0</t>
+  </si>
+  <si>
+    <t>24.05.202647.0</t>
+  </si>
+  <si>
+    <t>24.05.202648.0</t>
+  </si>
+  <si>
+    <t>24.05.202649.0</t>
+  </si>
+  <si>
+    <t>24.05.202650.0</t>
+  </si>
+  <si>
+    <t>24.05.202651.0</t>
+  </si>
+  <si>
+    <t>24.05.202652.0</t>
+  </si>
+  <si>
+    <t>24.05.202653.0</t>
+  </si>
+  <si>
+    <t>24.05.202654.0</t>
+  </si>
+  <si>
+    <t>24.05.202655.0</t>
+  </si>
+  <si>
+    <t>24.05.202656.0</t>
+  </si>
+  <si>
+    <t>24.05.202657.0</t>
+  </si>
+  <si>
+    <t>24.05.202658.0</t>
+  </si>
+  <si>
+    <t>24.05.202659.0</t>
+  </si>
+  <si>
+    <t>24.05.202660.0</t>
+  </si>
+  <si>
+    <t>24.05.202661.0</t>
+  </si>
+  <si>
+    <t>24.05.202662.0</t>
+  </si>
+  <si>
+    <t>24.05.202663.0</t>
+  </si>
+  <si>
+    <t>24.05.202664.0</t>
+  </si>
+  <si>
+    <t>24.05.202665.0</t>
+  </si>
+  <si>
+    <t>24.05.202666.0</t>
+  </si>
+  <si>
+    <t>24.05.202667.0</t>
+  </si>
+  <si>
+    <t>24.05.202668.0</t>
+  </si>
+  <si>
+    <t>24.05.202669.0</t>
+  </si>
+  <si>
+    <t>24.05.202670.0</t>
+  </si>
+  <si>
+    <t>24.05.202671.0</t>
+  </si>
+  <si>
+    <t>24.05.202672.0</t>
+  </si>
+  <si>
+    <t>24.05.202673.0</t>
+  </si>
+  <si>
+    <t>24.05.202674.0</t>
+  </si>
+  <si>
+    <t>24.05.202675.0</t>
+  </si>
+  <si>
+    <t>24.05.202676.0</t>
+  </si>
+  <si>
+    <t>24.05.202677.0</t>
+  </si>
+  <si>
+    <t>24.05.202678.0</t>
+  </si>
+  <si>
+    <t>24.05.202679.0</t>
+  </si>
+  <si>
+    <t>24.05.202680.0</t>
+  </si>
+  <si>
+    <t>24.05.202681.0</t>
+  </si>
+  <si>
+    <t>24.05.202682.0</t>
+  </si>
+  <si>
+    <t>24.05.202683.0</t>
+  </si>
+  <si>
+    <t>24.05.202684.0</t>
+  </si>
+  <si>
+    <t>24.05.202685.0</t>
+  </si>
+  <si>
+    <t>24.05.202686.0</t>
+  </si>
+  <si>
+    <t>24.05.202687.0</t>
+  </si>
+  <si>
+    <t>24.05.202688.0</t>
+  </si>
+  <si>
+    <t>24.05.202689.0</t>
+  </si>
+  <si>
+    <t>24.05.202690.0</t>
+  </si>
+  <si>
+    <t>24.05.202691.0</t>
+  </si>
+  <si>
+    <t>24.05.202692.0</t>
+  </si>
+  <si>
+    <t>24.05.202693.0</t>
+  </si>
+  <si>
+    <t>24.05.202694.0</t>
+  </si>
+  <si>
+    <t>24.05.202695.0</t>
+  </si>
+  <si>
+    <t>24.05.202696.0</t>
+  </si>
+  <si>
+    <t>25.05.20261.0</t>
+  </si>
+  <si>
+    <t>25.05.20262.0</t>
+  </si>
+  <si>
+    <t>25.05.20263.0</t>
+  </si>
+  <si>
+    <t>25.05.20264.0</t>
+  </si>
+  <si>
+    <t>25.05.20265.0</t>
+  </si>
+  <si>
+    <t>25.05.20266.0</t>
+  </si>
+  <si>
+    <t>25.05.20267.0</t>
+  </si>
+  <si>
+    <t>25.05.20268.0</t>
+  </si>
+  <si>
+    <t>25.05.20269.0</t>
+  </si>
+  <si>
+    <t>25.05.202610.0</t>
+  </si>
+  <si>
+    <t>25.05.202611.0</t>
+  </si>
+  <si>
+    <t>25.05.202612.0</t>
+  </si>
+  <si>
+    <t>25.05.202613.0</t>
+  </si>
+  <si>
+    <t>25.05.202614.0</t>
+  </si>
+  <si>
+    <t>25.05.202615.0</t>
+  </si>
+  <si>
+    <t>25.05.202616.0</t>
+  </si>
+  <si>
+    <t>25.05.202617.0</t>
+  </si>
+  <si>
+    <t>25.05.202618.0</t>
+  </si>
+  <si>
+    <t>25.05.202619.0</t>
+  </si>
+  <si>
+    <t>25.05.202620.0</t>
+  </si>
+  <si>
+    <t>25.05.202621.0</t>
+  </si>
+  <si>
+    <t>25.05.202622.0</t>
+  </si>
+  <si>
+    <t>25.05.202623.0</t>
+  </si>
+  <si>
+    <t>25.05.202624.0</t>
+  </si>
+  <si>
+    <t>25.05.202625.0</t>
+  </si>
+  <si>
+    <t>25.05.202626.0</t>
+  </si>
+  <si>
+    <t>25.05.202627.0</t>
+  </si>
+  <si>
+    <t>25.05.202628.0</t>
+  </si>
+  <si>
+    <t>25.05.202629.0</t>
+  </si>
+  <si>
+    <t>25.05.202630.0</t>
+  </si>
+  <si>
+    <t>25.05.202631.0</t>
+  </si>
+  <si>
+    <t>25.05.202632.0</t>
+  </si>
+  <si>
+    <t>25.05.202633.0</t>
+  </si>
+  <si>
+    <t>25.05.202634.0</t>
+  </si>
+  <si>
+    <t>25.05.202635.0</t>
+  </si>
+  <si>
+    <t>25.05.202636.0</t>
+  </si>
+  <si>
+    <t>25.05.202637.0</t>
+  </si>
+  <si>
+    <t>25.05.202638.0</t>
+  </si>
+  <si>
+    <t>25.05.202639.0</t>
+  </si>
+  <si>
+    <t>25.05.202640.0</t>
+  </si>
+  <si>
+    <t>25.05.202641.0</t>
+  </si>
+  <si>
+    <t>25.05.202642.0</t>
+  </si>
+  <si>
+    <t>25.05.202643.0</t>
+  </si>
+  <si>
+    <t>25.05.202644.0</t>
+  </si>
+  <si>
+    <t>25.05.202645.0</t>
+  </si>
+  <si>
+    <t>25.05.202646.0</t>
+  </si>
+  <si>
+    <t>25.05.202647.0</t>
+  </si>
+  <si>
+    <t>25.05.202648.0</t>
+  </si>
+  <si>
+    <t>25.05.202649.0</t>
+  </si>
+  <si>
+    <t>25.05.202650.0</t>
+  </si>
+  <si>
+    <t>25.05.202651.0</t>
+  </si>
+  <si>
+    <t>25.05.202652.0</t>
+  </si>
+  <si>
+    <t>25.05.202653.0</t>
+  </si>
+  <si>
+    <t>25.05.202654.0</t>
+  </si>
+  <si>
+    <t>25.05.202655.0</t>
+  </si>
+  <si>
+    <t>25.05.202656.0</t>
+  </si>
+  <si>
+    <t>25.05.202657.0</t>
+  </si>
+  <si>
+    <t>25.05.202658.0</t>
+  </si>
+  <si>
+    <t>25.05.202659.0</t>
+  </si>
+  <si>
+    <t>25.05.202660.0</t>
+  </si>
+  <si>
+    <t>25.05.202661.0</t>
+  </si>
+  <si>
+    <t>25.05.202662.0</t>
+  </si>
+  <si>
+    <t>25.05.202663.0</t>
+  </si>
+  <si>
+    <t>25.05.202664.0</t>
+  </si>
+  <si>
+    <t>25.05.202665.0</t>
+  </si>
+  <si>
+    <t>25.05.202666.0</t>
+  </si>
+  <si>
+    <t>25.05.202667.0</t>
+  </si>
+  <si>
+    <t>25.05.202668.0</t>
+  </si>
+  <si>
+    <t>25.05.202669.0</t>
+  </si>
+  <si>
+    <t>25.05.202670.0</t>
+  </si>
+  <si>
+    <t>25.05.202671.0</t>
+  </si>
+  <si>
+    <t>25.05.202672.0</t>
+  </si>
+  <si>
+    <t>25.05.202673.0</t>
+  </si>
+  <si>
+    <t>25.05.202674.0</t>
+  </si>
+  <si>
+    <t>25.05.202675.0</t>
+  </si>
+  <si>
+    <t>25.05.202676.0</t>
+  </si>
+  <si>
+    <t>25.05.202677.0</t>
+  </si>
+  <si>
+    <t>25.05.202678.0</t>
+  </si>
+  <si>
+    <t>25.05.202679.0</t>
+  </si>
+  <si>
+    <t>25.05.202680.0</t>
+  </si>
+  <si>
+    <t>25.05.202681.0</t>
+  </si>
+  <si>
+    <t>25.05.202682.0</t>
+  </si>
+  <si>
+    <t>25.05.202683.0</t>
+  </si>
+  <si>
+    <t>25.05.202684.0</t>
+  </si>
+  <si>
+    <t>25.05.202685.0</t>
+  </si>
+  <si>
+    <t>25.05.202686.0</t>
+  </si>
+  <si>
+    <t>25.05.202687.0</t>
+  </si>
+  <si>
+    <t>25.05.202688.0</t>
+  </si>
+  <si>
+    <t>25.05.202689.0</t>
+  </si>
+  <si>
+    <t>25.05.202690.0</t>
+  </si>
+  <si>
+    <t>25.05.202691.0</t>
+  </si>
+  <si>
+    <t>25.05.202692.0</t>
+  </si>
+  <si>
+    <t>25.05.202693.0</t>
+  </si>
+  <si>
+    <t>25.05.202694.0</t>
+  </si>
+  <si>
+    <t>25.05.202695.0</t>
+  </si>
+  <si>
+    <t>25.05.202696.0</t>
+  </si>
+  <si>
+    <t>26.05.20261.0</t>
+  </si>
+  <si>
+    <t>26.05.20262.0</t>
+  </si>
+  <si>
+    <t>26.05.20263.0</t>
+  </si>
+  <si>
+    <t>26.05.20264.0</t>
+  </si>
+  <si>
+    <t>26.05.20265.0</t>
+  </si>
+  <si>
+    <t>26.05.20266.0</t>
+  </si>
+  <si>
+    <t>26.05.20267.0</t>
+  </si>
+  <si>
+    <t>26.05.20268.0</t>
+  </si>
+  <si>
+    <t>26.05.20269.0</t>
+  </si>
+  <si>
+    <t>26.05.202610.0</t>
+  </si>
+  <si>
+    <t>26.05.202611.0</t>
+  </si>
+  <si>
+    <t>26.05.202612.0</t>
+  </si>
+  <si>
+    <t>26.05.202613.0</t>
+  </si>
+  <si>
+    <t>26.05.202614.0</t>
+  </si>
+  <si>
+    <t>26.05.202615.0</t>
+  </si>
+  <si>
+    <t>26.05.202616.0</t>
+  </si>
+  <si>
+    <t>26.05.202617.0</t>
+  </si>
+  <si>
+    <t>26.05.202618.0</t>
+  </si>
+  <si>
+    <t>26.05.202619.0</t>
+  </si>
+  <si>
+    <t>26.05.202620.0</t>
+  </si>
+  <si>
+    <t>26.05.202621.0</t>
+  </si>
+  <si>
+    <t>26.05.202622.0</t>
+  </si>
+  <si>
+    <t>26.05.202623.0</t>
+  </si>
+  <si>
+    <t>26.05.202624.0</t>
+  </si>
+  <si>
+    <t>26.05.202625.0</t>
+  </si>
+  <si>
+    <t>26.05.202626.0</t>
+  </si>
+  <si>
+    <t>26.05.202627.0</t>
+  </si>
+  <si>
+    <t>26.05.202628.0</t>
+  </si>
+  <si>
+    <t>26.05.202629.0</t>
+  </si>
+  <si>
+    <t>26.05.202630.0</t>
+  </si>
+  <si>
+    <t>26.05.202631.0</t>
+  </si>
+  <si>
+    <t>26.05.202632.0</t>
+  </si>
+  <si>
+    <t>26.05.202633.0</t>
+  </si>
+  <si>
+    <t>26.05.202634.0</t>
+  </si>
+  <si>
+    <t>26.05.202635.0</t>
+  </si>
+  <si>
+    <t>26.05.202636.0</t>
+  </si>
+  <si>
+    <t>26.05.202637.0</t>
+  </si>
+  <si>
+    <t>26.05.202638.0</t>
+  </si>
+  <si>
+    <t>26.05.202639.0</t>
+  </si>
+  <si>
+    <t>26.05.202640.0</t>
+  </si>
+  <si>
+    <t>26.05.202641.0</t>
+  </si>
+  <si>
+    <t>26.05.202642.0</t>
+  </si>
+  <si>
+    <t>26.05.202643.0</t>
+  </si>
+  <si>
+    <t>26.05.202644.0</t>
+  </si>
+  <si>
+    <t>26.05.202645.0</t>
+  </si>
+  <si>
+    <t>26.05.202646.0</t>
+  </si>
+  <si>
+    <t>26.05.202647.0</t>
+  </si>
+  <si>
+    <t>26.05.202648.0</t>
+  </si>
+  <si>
+    <t>26.05.202649.0</t>
+  </si>
+  <si>
+    <t>26.05.202650.0</t>
+  </si>
+  <si>
+    <t>26.05.202651.0</t>
+  </si>
+  <si>
+    <t>26.05.202652.0</t>
+  </si>
+  <si>
+    <t>26.05.202653.0</t>
+  </si>
+  <si>
+    <t>26.05.202654.0</t>
+  </si>
+  <si>
+    <t>26.05.202655.0</t>
+  </si>
+  <si>
+    <t>26.05.202656.0</t>
+  </si>
+  <si>
+    <t>26.05.202657.0</t>
+  </si>
+  <si>
+    <t>26.05.202658.0</t>
+  </si>
+  <si>
+    <t>26.05.202659.0</t>
+  </si>
+  <si>
+    <t>26.05.202660.0</t>
+  </si>
+  <si>
+    <t>26.05.202661.0</t>
+  </si>
+  <si>
+    <t>26.05.202662.0</t>
+  </si>
+  <si>
+    <t>26.05.202663.0</t>
+  </si>
+  <si>
+    <t>26.05.202664.0</t>
+  </si>
+  <si>
+    <t>26.05.202665.0</t>
+  </si>
+  <si>
+    <t>26.05.202666.0</t>
+  </si>
+  <si>
+    <t>26.05.202667.0</t>
+  </si>
+  <si>
+    <t>26.05.202668.0</t>
+  </si>
+  <si>
+    <t>26.05.202669.0</t>
+  </si>
+  <si>
+    <t>26.05.202670.0</t>
+  </si>
+  <si>
+    <t>26.05.202671.0</t>
+  </si>
+  <si>
+    <t>26.05.202672.0</t>
+  </si>
+  <si>
+    <t>26.05.202673.0</t>
+  </si>
+  <si>
+    <t>26.05.202674.0</t>
+  </si>
+  <si>
+    <t>26.05.202675.0</t>
+  </si>
+  <si>
+    <t>26.05.202676.0</t>
+  </si>
+  <si>
+    <t>26.05.202677.0</t>
+  </si>
+  <si>
+    <t>26.05.202678.0</t>
+  </si>
+  <si>
+    <t>26.05.202679.0</t>
+  </si>
+  <si>
+    <t>26.05.202680.0</t>
+  </si>
+  <si>
+    <t>26.05.202681.0</t>
+  </si>
+  <si>
+    <t>26.05.202682.0</t>
+  </si>
+  <si>
+    <t>26.05.202683.0</t>
+  </si>
+  <si>
+    <t>26.05.202684.0</t>
+  </si>
+  <si>
+    <t>26.05.202685.0</t>
+  </si>
+  <si>
+    <t>26.05.202686.0</t>
+  </si>
+  <si>
+    <t>26.05.202687.0</t>
+  </si>
+  <si>
+    <t>26.05.202688.0</t>
+  </si>
+  <si>
+    <t>26.05.202689.0</t>
+  </si>
+  <si>
+    <t>26.05.202690.0</t>
+  </si>
+  <si>
+    <t>26.05.202691.0</t>
+  </si>
+  <si>
+    <t>26.05.202692.0</t>
+  </si>
+  <si>
+    <t>26.05.202693.0</t>
+  </si>
+  <si>
+    <t>26.05.202694.0</t>
+  </si>
+  <si>
+    <t>26.05.202695.0</t>
+  </si>
+  <si>
+    <t>26.05.202696.0</t>
   </si>
 </sst>
 </file>
@@ -6723,7 +7875,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D2113"/>
+  <dimension ref="A1:D2497"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -26908,7 +28060,7 @@
         <v>1</v>
       </c>
       <c r="C1442">
-        <v>3654</v>
+        <v>4986.1</v>
       </c>
       <c r="D1442" t="s">
         <v>1444</v>
@@ -26922,7 +28074,7 @@
         <v>2</v>
       </c>
       <c r="C1443">
-        <v>3639.3</v>
+        <v>4945</v>
       </c>
       <c r="D1443" t="s">
         <v>1445</v>
@@ -26936,7 +28088,7 @@
         <v>3</v>
       </c>
       <c r="C1444">
-        <v>3638</v>
+        <v>4940.9</v>
       </c>
       <c r="D1444" t="s">
         <v>1446</v>
@@ -26950,7 +28102,7 @@
         <v>4</v>
       </c>
       <c r="C1445">
-        <v>3596</v>
+        <v>4917.9</v>
       </c>
       <c r="D1445" t="s">
         <v>1447</v>
@@ -26964,7 +28116,7 @@
         <v>5</v>
       </c>
       <c r="C1446">
-        <v>3602</v>
+        <v>4632.3</v>
       </c>
       <c r="D1446" t="s">
         <v>1448</v>
@@ -26978,7 +28130,7 @@
         <v>6</v>
       </c>
       <c r="C1447">
-        <v>3595.8</v>
+        <v>4603</v>
       </c>
       <c r="D1447" t="s">
         <v>1449</v>
@@ -26992,7 +28144,7 @@
         <v>7</v>
       </c>
       <c r="C1448">
-        <v>3567.6</v>
+        <v>4587.8</v>
       </c>
       <c r="D1448" t="s">
         <v>1450</v>
@@ -27006,7 +28158,7 @@
         <v>8</v>
       </c>
       <c r="C1449">
-        <v>3584.3</v>
+        <v>4583.7</v>
       </c>
       <c r="D1449" t="s">
         <v>1451</v>
@@ -27020,7 +28172,7 @@
         <v>9</v>
       </c>
       <c r="C1450">
-        <v>3429.6</v>
+        <v>4600.6</v>
       </c>
       <c r="D1450" t="s">
         <v>1452</v>
@@ -27034,7 +28186,7 @@
         <v>10</v>
       </c>
       <c r="C1451">
-        <v>3429.5</v>
+        <v>4581.4</v>
       </c>
       <c r="D1451" t="s">
         <v>1453</v>
@@ -27048,7 +28200,7 @@
         <v>11</v>
       </c>
       <c r="C1452">
-        <v>3417.1</v>
+        <v>4569.4</v>
       </c>
       <c r="D1452" t="s">
         <v>1454</v>
@@ -27062,7 +28214,7 @@
         <v>12</v>
       </c>
       <c r="C1453">
-        <v>3451.4</v>
+        <v>4566</v>
       </c>
       <c r="D1453" t="s">
         <v>1455</v>
@@ -27076,7 +28228,7 @@
         <v>13</v>
       </c>
       <c r="C1454">
-        <v>3527.7</v>
+        <v>4543.1</v>
       </c>
       <c r="D1454" t="s">
         <v>1456</v>
@@ -27090,7 +28242,7 @@
         <v>14</v>
       </c>
       <c r="C1455">
-        <v>3524.4</v>
+        <v>4524</v>
       </c>
       <c r="D1455" t="s">
         <v>1457</v>
@@ -27104,7 +28256,7 @@
         <v>15</v>
       </c>
       <c r="C1456">
-        <v>3532.9</v>
+        <v>4494.5</v>
       </c>
       <c r="D1456" t="s">
         <v>1458</v>
@@ -27118,7 +28270,7 @@
         <v>16</v>
       </c>
       <c r="C1457">
-        <v>3533.2</v>
+        <v>4502.6</v>
       </c>
       <c r="D1457" t="s">
         <v>1459</v>
@@ -27132,7 +28284,7 @@
         <v>17</v>
       </c>
       <c r="C1458">
-        <v>3487.3</v>
+        <v>4380.6</v>
       </c>
       <c r="D1458" t="s">
         <v>1460</v>
@@ -27146,7 +28298,7 @@
         <v>18</v>
       </c>
       <c r="C1459">
-        <v>3471.4</v>
+        <v>4350</v>
       </c>
       <c r="D1459" t="s">
         <v>1461</v>
@@ -27160,7 +28312,7 @@
         <v>19</v>
       </c>
       <c r="C1460">
-        <v>3461.6</v>
+        <v>4349</v>
       </c>
       <c r="D1460" t="s">
         <v>1462</v>
@@ -27174,7 +28326,7 @@
         <v>20</v>
       </c>
       <c r="C1461">
-        <v>3453.2</v>
+        <v>4324.7</v>
       </c>
       <c r="D1461" t="s">
         <v>1463</v>
@@ -27188,7 +28340,7 @@
         <v>21</v>
       </c>
       <c r="C1462">
-        <v>3484.8</v>
+        <v>4342.9</v>
       </c>
       <c r="D1462" t="s">
         <v>1464</v>
@@ -27202,7 +28354,7 @@
         <v>22</v>
       </c>
       <c r="C1463">
-        <v>3428.5</v>
+        <v>4337.9</v>
       </c>
       <c r="D1463" t="s">
         <v>1465</v>
@@ -27216,7 +28368,7 @@
         <v>23</v>
       </c>
       <c r="C1464">
-        <v>3421.9</v>
+        <v>4338.9</v>
       </c>
       <c r="D1464" t="s">
         <v>1466</v>
@@ -27230,7 +28382,7 @@
         <v>24</v>
       </c>
       <c r="C1465">
-        <v>3430.3</v>
+        <v>4363.1</v>
       </c>
       <c r="D1465" t="s">
         <v>1467</v>
@@ -27244,7 +28396,7 @@
         <v>25</v>
       </c>
       <c r="C1466">
-        <v>3623</v>
+        <v>4344.5</v>
       </c>
       <c r="D1466" t="s">
         <v>1468</v>
@@ -27258,7 +28410,7 @@
         <v>26</v>
       </c>
       <c r="C1467">
-        <v>3580.3</v>
+        <v>4371.3</v>
       </c>
       <c r="D1467" t="s">
         <v>1469</v>
@@ -27272,7 +28424,7 @@
         <v>27</v>
       </c>
       <c r="C1468">
-        <v>3559.6</v>
+        <v>4407.1</v>
       </c>
       <c r="D1468" t="s">
         <v>1470</v>
@@ -27286,7 +28438,7 @@
         <v>28</v>
       </c>
       <c r="C1469">
-        <v>3501.4</v>
+        <v>4443.6</v>
       </c>
       <c r="D1469" t="s">
         <v>1471</v>
@@ -27300,7 +28452,7 @@
         <v>29</v>
       </c>
       <c r="C1470">
-        <v>3420.4</v>
+        <v>4455.5</v>
       </c>
       <c r="D1470" t="s">
         <v>1472</v>
@@ -27314,7 +28466,7 @@
         <v>30</v>
       </c>
       <c r="C1471">
-        <v>3412.5</v>
+        <v>4473.6</v>
       </c>
       <c r="D1471" t="s">
         <v>1473</v>
@@ -27328,7 +28480,7 @@
         <v>31</v>
       </c>
       <c r="C1472">
-        <v>3456.2</v>
+        <v>4510.6</v>
       </c>
       <c r="D1472" t="s">
         <v>1474</v>
@@ -27342,7 +28494,7 @@
         <v>32</v>
       </c>
       <c r="C1473">
-        <v>3538.5</v>
+        <v>4507.1</v>
       </c>
       <c r="D1473" t="s">
         <v>1475</v>
@@ -27356,7 +28508,7 @@
         <v>33</v>
       </c>
       <c r="C1474">
-        <v>3469.1</v>
+        <v>4510.2</v>
       </c>
       <c r="D1474" t="s">
         <v>1476</v>
@@ -27370,7 +28522,7 @@
         <v>34</v>
       </c>
       <c r="C1475">
-        <v>3513.8</v>
+        <v>4521</v>
       </c>
       <c r="D1475" t="s">
         <v>1477</v>
@@ -27384,7 +28536,7 @@
         <v>35</v>
       </c>
       <c r="C1476">
-        <v>3609.7</v>
+        <v>4587.2</v>
       </c>
       <c r="D1476" t="s">
         <v>1478</v>
@@ -27398,7 +28550,7 @@
         <v>36</v>
       </c>
       <c r="C1477">
-        <v>3703</v>
+        <v>4641.7</v>
       </c>
       <c r="D1477" t="s">
         <v>1479</v>
@@ -27412,7 +28564,7 @@
         <v>37</v>
       </c>
       <c r="C1478">
-        <v>3916</v>
+        <v>4726.6</v>
       </c>
       <c r="D1478" t="s">
         <v>1480</v>
@@ -27426,7 +28578,7 @@
         <v>38</v>
       </c>
       <c r="C1479">
-        <v>3995.1</v>
+        <v>4752.5</v>
       </c>
       <c r="D1479" t="s">
         <v>1481</v>
@@ -27440,7 +28592,7 @@
         <v>39</v>
       </c>
       <c r="C1480">
-        <v>4083.3</v>
+        <v>4886.5</v>
       </c>
       <c r="D1480" t="s">
         <v>1482</v>
@@ -27454,7 +28606,7 @@
         <v>40</v>
       </c>
       <c r="C1481">
-        <v>4177.3</v>
+        <v>4939.3</v>
       </c>
       <c r="D1481" t="s">
         <v>1483</v>
@@ -27468,7 +28620,7 @@
         <v>41</v>
       </c>
       <c r="C1482">
-        <v>4520.7</v>
+        <v>5084.2</v>
       </c>
       <c r="D1482" t="s">
         <v>1484</v>
@@ -27482,7 +28634,7 @@
         <v>42</v>
       </c>
       <c r="C1483">
-        <v>4638.9</v>
+        <v>5204</v>
       </c>
       <c r="D1483" t="s">
         <v>1485</v>
@@ -27496,7 +28648,7 @@
         <v>43</v>
       </c>
       <c r="C1484">
-        <v>4675.7</v>
+        <v>5308.3</v>
       </c>
       <c r="D1484" t="s">
         <v>1486</v>
@@ -27510,7 +28662,7 @@
         <v>44</v>
       </c>
       <c r="C1485">
-        <v>4776</v>
+        <v>5357.9</v>
       </c>
       <c r="D1485" t="s">
         <v>1487</v>
@@ -27524,7 +28676,7 @@
         <v>45</v>
       </c>
       <c r="C1486">
-        <v>4669.9</v>
+        <v>5073</v>
       </c>
       <c r="D1486" t="s">
         <v>1488</v>
@@ -27538,7 +28690,7 @@
         <v>46</v>
       </c>
       <c r="C1487">
-        <v>4725.4</v>
+        <v>5118.9</v>
       </c>
       <c r="D1487" t="s">
         <v>1489</v>
@@ -27552,7 +28704,7 @@
         <v>47</v>
       </c>
       <c r="C1488">
-        <v>4765.9</v>
+        <v>5210.1</v>
       </c>
       <c r="D1488" t="s">
         <v>1490</v>
@@ -27566,7 +28718,7 @@
         <v>48</v>
       </c>
       <c r="C1489">
-        <v>4826.1</v>
+        <v>5325.6</v>
       </c>
       <c r="D1489" t="s">
         <v>1491</v>
@@ -27580,7 +28732,7 @@
         <v>49</v>
       </c>
       <c r="C1490">
-        <v>4809.4</v>
+        <v>5471</v>
       </c>
       <c r="D1490" t="s">
         <v>1492</v>
@@ -27594,7 +28746,7 @@
         <v>50</v>
       </c>
       <c r="C1491">
-        <v>4843.9</v>
+        <v>5536.6</v>
       </c>
       <c r="D1491" t="s">
         <v>1493</v>
@@ -27608,7 +28760,7 @@
         <v>51</v>
       </c>
       <c r="C1492">
-        <v>4849.4</v>
+        <v>5599.6</v>
       </c>
       <c r="D1492" t="s">
         <v>1494</v>
@@ -27622,7 +28774,7 @@
         <v>52</v>
       </c>
       <c r="C1493">
-        <v>4899</v>
+        <v>5650.1</v>
       </c>
       <c r="D1493" t="s">
         <v>1495</v>
@@ -27636,7 +28788,7 @@
         <v>53</v>
       </c>
       <c r="C1494">
-        <v>4785.9</v>
+        <v>5590.3</v>
       </c>
       <c r="D1494" t="s">
         <v>1496</v>
@@ -27650,7 +28802,7 @@
         <v>54</v>
       </c>
       <c r="C1495">
-        <v>4805</v>
+        <v>5617</v>
       </c>
       <c r="D1495" t="s">
         <v>1497</v>
@@ -27664,7 +28816,7 @@
         <v>55</v>
       </c>
       <c r="C1496">
-        <v>4860.4</v>
+        <v>5654.2</v>
       </c>
       <c r="D1496" t="s">
         <v>1498</v>
@@ -27678,7 +28830,7 @@
         <v>56</v>
       </c>
       <c r="C1497">
-        <v>4896.9</v>
+        <v>5684.5</v>
       </c>
       <c r="D1497" t="s">
         <v>1499</v>
@@ -27692,7 +28844,7 @@
         <v>57</v>
       </c>
       <c r="C1498">
-        <v>4989.3</v>
+        <v>5753</v>
       </c>
       <c r="D1498" t="s">
         <v>1500</v>
@@ -27706,7 +28858,7 @@
         <v>58</v>
       </c>
       <c r="C1499">
-        <v>5024.7</v>
+        <v>5779.5</v>
       </c>
       <c r="D1499" t="s">
         <v>1501</v>
@@ -27720,7 +28872,7 @@
         <v>59</v>
       </c>
       <c r="C1500">
-        <v>5108.2</v>
+        <v>5761.3</v>
       </c>
       <c r="D1500" t="s">
         <v>1502</v>
@@ -27734,7 +28886,7 @@
         <v>60</v>
       </c>
       <c r="C1501">
-        <v>5174.4</v>
+        <v>5775.3</v>
       </c>
       <c r="D1501" t="s">
         <v>1503</v>
@@ -27748,7 +28900,7 @@
         <v>61</v>
       </c>
       <c r="C1502">
-        <v>5182.5</v>
+        <v>5653.7</v>
       </c>
       <c r="D1502" t="s">
         <v>1504</v>
@@ -27762,7 +28914,7 @@
         <v>62</v>
       </c>
       <c r="C1503">
-        <v>5236.9</v>
+        <v>5626.4</v>
       </c>
       <c r="D1503" t="s">
         <v>1505</v>
@@ -27776,7 +28928,7 @@
         <v>63</v>
       </c>
       <c r="C1504">
-        <v>5282.6</v>
+        <v>5618.1</v>
       </c>
       <c r="D1504" t="s">
         <v>1506</v>
@@ -27790,7 +28942,7 @@
         <v>64</v>
       </c>
       <c r="C1505">
-        <v>5338</v>
+        <v>5615</v>
       </c>
       <c r="D1505" t="s">
         <v>1507</v>
@@ -27804,7 +28956,7 @@
         <v>65</v>
       </c>
       <c r="C1506">
-        <v>5419.6</v>
+        <v>5364.9</v>
       </c>
       <c r="D1506" t="s">
         <v>1508</v>
@@ -27818,7 +28970,7 @@
         <v>66</v>
       </c>
       <c r="C1507">
-        <v>5408</v>
+        <v>5366.9</v>
       </c>
       <c r="D1507" t="s">
         <v>1509</v>
@@ -27832,7 +28984,7 @@
         <v>67</v>
       </c>
       <c r="C1508">
-        <v>5401.9</v>
+        <v>5360</v>
       </c>
       <c r="D1508" t="s">
         <v>1510</v>
@@ -27846,7 +28998,7 @@
         <v>68</v>
       </c>
       <c r="C1509">
-        <v>5392.4</v>
+        <v>5376.1</v>
       </c>
       <c r="D1509" t="s">
         <v>1511</v>
@@ -27860,7 +29012,7 @@
         <v>69</v>
       </c>
       <c r="C1510">
-        <v>5468.5</v>
+        <v>5343.1</v>
       </c>
       <c r="D1510" t="s">
         <v>1512</v>
@@ -27874,7 +29026,7 @@
         <v>70</v>
       </c>
       <c r="C1511">
-        <v>5409.8</v>
+        <v>5335.6</v>
       </c>
       <c r="D1511" t="s">
         <v>1513</v>
@@ -27888,7 +29040,7 @@
         <v>71</v>
       </c>
       <c r="C1512">
-        <v>5353.7</v>
+        <v>5351.6</v>
       </c>
       <c r="D1512" t="s">
         <v>1514</v>
@@ -27902,7 +29054,7 @@
         <v>72</v>
       </c>
       <c r="C1513">
-        <v>5330.3</v>
+        <v>5360.2</v>
       </c>
       <c r="D1513" t="s">
         <v>1515</v>
@@ -27916,7 +29068,7 @@
         <v>73</v>
       </c>
       <c r="C1514">
-        <v>5480.4</v>
+        <v>5759.6</v>
       </c>
       <c r="D1514" t="s">
         <v>1516</v>
@@ -27930,7 +29082,7 @@
         <v>74</v>
       </c>
       <c r="C1515">
-        <v>5388.3</v>
+        <v>5721.3</v>
       </c>
       <c r="D1515" t="s">
         <v>1517</v>
@@ -27944,7 +29096,7 @@
         <v>75</v>
       </c>
       <c r="C1516">
-        <v>5338.7</v>
+        <v>5686.9</v>
       </c>
       <c r="D1516" t="s">
         <v>1518</v>
@@ -27958,7 +29110,7 @@
         <v>76</v>
       </c>
       <c r="C1517">
-        <v>5301.3</v>
+        <v>5635.6</v>
       </c>
       <c r="D1517" t="s">
         <v>1519</v>
@@ -27972,7 +29124,7 @@
         <v>77</v>
       </c>
       <c r="C1518">
-        <v>5443</v>
+        <v>6314.8</v>
       </c>
       <c r="D1518" t="s">
         <v>1520</v>
@@ -27986,7 +29138,7 @@
         <v>78</v>
       </c>
       <c r="C1519">
-        <v>5440.3</v>
+        <v>6297.6</v>
       </c>
       <c r="D1519" t="s">
         <v>1521</v>
@@ -28000,7 +29152,7 @@
         <v>79</v>
       </c>
       <c r="C1520">
-        <v>5433</v>
+        <v>6250.5</v>
       </c>
       <c r="D1520" t="s">
         <v>1522</v>
@@ -28014,7 +29166,7 @@
         <v>80</v>
       </c>
       <c r="C1521">
-        <v>5434.9</v>
+        <v>6221.7</v>
       </c>
       <c r="D1521" t="s">
         <v>1523</v>
@@ -28028,7 +29180,7 @@
         <v>81</v>
       </c>
       <c r="C1522">
-        <v>5451.5</v>
+        <v>6287.4</v>
       </c>
       <c r="D1522" t="s">
         <v>1524</v>
@@ -28042,7 +29194,7 @@
         <v>82</v>
       </c>
       <c r="C1523">
-        <v>5485.5</v>
+        <v>6297.9</v>
       </c>
       <c r="D1523" t="s">
         <v>1525</v>
@@ -28056,7 +29208,7 @@
         <v>83</v>
       </c>
       <c r="C1524">
-        <v>5491</v>
+        <v>6263</v>
       </c>
       <c r="D1524" t="s">
         <v>1526</v>
@@ -28070,7 +29222,7 @@
         <v>84</v>
       </c>
       <c r="C1525">
-        <v>5453.7</v>
+        <v>6205.5</v>
       </c>
       <c r="D1525" t="s">
         <v>1527</v>
@@ -28084,7 +29236,7 @@
         <v>85</v>
       </c>
       <c r="C1526">
-        <v>5618.2</v>
+        <v>6341.1</v>
       </c>
       <c r="D1526" t="s">
         <v>1528</v>
@@ -28098,7 +29250,7 @@
         <v>86</v>
       </c>
       <c r="C1527">
-        <v>5609.5</v>
+        <v>6276</v>
       </c>
       <c r="D1527" t="s">
         <v>1529</v>
@@ -28112,7 +29264,7 @@
         <v>87</v>
       </c>
       <c r="C1528">
-        <v>5620.8</v>
+        <v>6233.2</v>
       </c>
       <c r="D1528" t="s">
         <v>1530</v>
@@ -28126,7 +29278,7 @@
         <v>88</v>
       </c>
       <c r="C1529">
-        <v>5638.5</v>
+        <v>6219</v>
       </c>
       <c r="D1529" t="s">
         <v>1531</v>
@@ -28140,7 +29292,7 @@
         <v>89</v>
       </c>
       <c r="C1530">
-        <v>5638.3</v>
+        <v>5998</v>
       </c>
       <c r="D1530" t="s">
         <v>1532</v>
@@ -28154,7 +29306,7 @@
         <v>90</v>
       </c>
       <c r="C1531">
-        <v>5635.8</v>
+        <v>5923.6</v>
       </c>
       <c r="D1531" t="s">
         <v>1533</v>
@@ -28168,7 +29320,7 @@
         <v>91</v>
       </c>
       <c r="C1532">
-        <v>5580.4</v>
+        <v>5865.3</v>
       </c>
       <c r="D1532" t="s">
         <v>1534</v>
@@ -28182,7 +29334,7 @@
         <v>92</v>
       </c>
       <c r="C1533">
-        <v>5578.1</v>
+        <v>5830.4</v>
       </c>
       <c r="D1533" t="s">
         <v>1535</v>
@@ -28196,7 +29348,7 @@
         <v>93</v>
       </c>
       <c r="C1534">
-        <v>5292.2</v>
+        <v>5619.6</v>
       </c>
       <c r="D1534" t="s">
         <v>1536</v>
@@ -28210,7 +29362,7 @@
         <v>94</v>
       </c>
       <c r="C1535">
-        <v>5245</v>
+        <v>5578.3</v>
       </c>
       <c r="D1535" t="s">
         <v>1537</v>
@@ -28224,7 +29376,7 @@
         <v>95</v>
       </c>
       <c r="C1536">
-        <v>5234.1</v>
+        <v>5546.8</v>
       </c>
       <c r="D1536" t="s">
         <v>1538</v>
@@ -28238,7 +29390,7 @@
         <v>96</v>
       </c>
       <c r="C1537">
-        <v>5197.6</v>
+        <v>5495.8</v>
       </c>
       <c r="D1537" t="s">
         <v>1539</v>
@@ -28252,7 +29404,7 @@
         <v>1</v>
       </c>
       <c r="C1538">
-        <v>5326</v>
+        <v>5202.4</v>
       </c>
       <c r="D1538" t="s">
         <v>1540</v>
@@ -28266,7 +29418,7 @@
         <v>2</v>
       </c>
       <c r="C1539">
-        <v>5286.2</v>
+        <v>5170</v>
       </c>
       <c r="D1539" t="s">
         <v>1541</v>
@@ -28280,7 +29432,7 @@
         <v>3</v>
       </c>
       <c r="C1540">
-        <v>5209.7</v>
+        <v>5145.6</v>
       </c>
       <c r="D1540" t="s">
         <v>1542</v>
@@ -28294,7 +29446,7 @@
         <v>4</v>
       </c>
       <c r="C1541">
-        <v>5087.7</v>
+        <v>5120.2</v>
       </c>
       <c r="D1541" t="s">
         <v>1543</v>
@@ -28308,7 +29460,7 @@
         <v>5</v>
       </c>
       <c r="C1542">
-        <v>4613.4</v>
+        <v>4867.2</v>
       </c>
       <c r="D1542" t="s">
         <v>1544</v>
@@ -28322,7 +29474,7 @@
         <v>6</v>
       </c>
       <c r="C1543">
-        <v>4558.2</v>
+        <v>4803.4</v>
       </c>
       <c r="D1543" t="s">
         <v>1545</v>
@@ -28336,7 +29488,7 @@
         <v>7</v>
       </c>
       <c r="C1544">
-        <v>4499.8</v>
+        <v>4776.1</v>
       </c>
       <c r="D1544" t="s">
         <v>1546</v>
@@ -28350,7 +29502,7 @@
         <v>8</v>
       </c>
       <c r="C1545">
-        <v>4454.3</v>
+        <v>4710.7</v>
       </c>
       <c r="D1545" t="s">
         <v>1547</v>
@@ -28364,7 +29516,7 @@
         <v>9</v>
       </c>
       <c r="C1546">
-        <v>4175.1</v>
+        <v>4682.6</v>
       </c>
       <c r="D1546" t="s">
         <v>1548</v>
@@ -28378,7 +29530,7 @@
         <v>10</v>
       </c>
       <c r="C1547">
-        <v>4144.8</v>
+        <v>4651.9</v>
       </c>
       <c r="D1547" t="s">
         <v>1549</v>
@@ -28392,7 +29544,7 @@
         <v>11</v>
       </c>
       <c r="C1548">
-        <v>4120.6</v>
+        <v>4630</v>
       </c>
       <c r="D1548" t="s">
         <v>1550</v>
@@ -28406,7 +29558,7 @@
         <v>12</v>
       </c>
       <c r="C1549">
-        <v>4101.4</v>
+        <v>4628.2</v>
       </c>
       <c r="D1549" t="s">
         <v>1551</v>
@@ -28420,7 +29572,7 @@
         <v>13</v>
       </c>
       <c r="C1550">
-        <v>4114</v>
+        <v>4589.7</v>
       </c>
       <c r="D1550" t="s">
         <v>1552</v>
@@ -28434,7 +29586,7 @@
         <v>14</v>
       </c>
       <c r="C1551">
-        <v>4071.1</v>
+        <v>4580.1</v>
       </c>
       <c r="D1551" t="s">
         <v>1553</v>
@@ -28448,7 +29600,7 @@
         <v>15</v>
       </c>
       <c r="C1552">
-        <v>4025.4</v>
+        <v>4553.2</v>
       </c>
       <c r="D1552" t="s">
         <v>1554</v>
@@ -28462,7 +29614,7 @@
         <v>16</v>
       </c>
       <c r="C1553">
-        <v>3985.9</v>
+        <v>4538.6</v>
       </c>
       <c r="D1553" t="s">
         <v>1555</v>
@@ -28476,7 +29628,7 @@
         <v>17</v>
       </c>
       <c r="C1554">
-        <v>3945.9</v>
+        <v>4484.7</v>
       </c>
       <c r="D1554" t="s">
         <v>1556</v>
@@ -28490,7 +29642,7 @@
         <v>18</v>
       </c>
       <c r="C1555">
-        <v>3889.2</v>
+        <v>4476.3</v>
       </c>
       <c r="D1555" t="s">
         <v>1557</v>
@@ -28504,7 +29656,7 @@
         <v>19</v>
       </c>
       <c r="C1556">
-        <v>3827.8</v>
+        <v>4462.7</v>
       </c>
       <c r="D1556" t="s">
         <v>1558</v>
@@ -28518,7 +29670,7 @@
         <v>20</v>
       </c>
       <c r="C1557">
-        <v>3783.5</v>
+        <v>4434.2</v>
       </c>
       <c r="D1557" t="s">
         <v>1559</v>
@@ -28532,7 +29684,7 @@
         <v>21</v>
       </c>
       <c r="C1558">
-        <v>3785.6</v>
+        <v>4399.1</v>
       </c>
       <c r="D1558" t="s">
         <v>1560</v>
@@ -28546,7 +29698,7 @@
         <v>22</v>
       </c>
       <c r="C1559">
-        <v>3735.6</v>
+        <v>4390.5</v>
       </c>
       <c r="D1559" t="s">
         <v>1561</v>
@@ -28560,7 +29712,7 @@
         <v>23</v>
       </c>
       <c r="C1560">
-        <v>3653.4</v>
+        <v>4401.9</v>
       </c>
       <c r="D1560" t="s">
         <v>1562</v>
@@ -28574,7 +29726,7 @@
         <v>24</v>
       </c>
       <c r="C1561">
-        <v>3556.6</v>
+        <v>4398.1</v>
       </c>
       <c r="D1561" t="s">
         <v>1563</v>
@@ -28588,7 +29740,7 @@
         <v>25</v>
       </c>
       <c r="C1562">
-        <v>3506.8</v>
+        <v>4375.8</v>
       </c>
       <c r="D1562" t="s">
         <v>1564</v>
@@ -28602,7 +29754,7 @@
         <v>26</v>
       </c>
       <c r="C1563">
-        <v>3441.3</v>
+        <v>4374</v>
       </c>
       <c r="D1563" t="s">
         <v>1565</v>
@@ -28616,7 +29768,7 @@
         <v>27</v>
       </c>
       <c r="C1564">
-        <v>3373.1</v>
+        <v>4364.3</v>
       </c>
       <c r="D1564" t="s">
         <v>1566</v>
@@ -28630,7 +29782,7 @@
         <v>28</v>
       </c>
       <c r="C1565">
-        <v>3296.4</v>
+        <v>4351.5</v>
       </c>
       <c r="D1565" t="s">
         <v>1567</v>
@@ -28644,7 +29796,7 @@
         <v>29</v>
       </c>
       <c r="C1566">
-        <v>3230.9</v>
+        <v>4198.4</v>
       </c>
       <c r="D1566" t="s">
         <v>1568</v>
@@ -28658,7 +29810,7 @@
         <v>30</v>
       </c>
       <c r="C1567">
-        <v>3176.5</v>
+        <v>4161.1</v>
       </c>
       <c r="D1567" t="s">
         <v>1569</v>
@@ -28672,7 +29824,7 @@
         <v>31</v>
       </c>
       <c r="C1568">
-        <v>3222.3</v>
+        <v>4239.3</v>
       </c>
       <c r="D1568" t="s">
         <v>1570</v>
@@ -28686,7 +29838,7 @@
         <v>32</v>
       </c>
       <c r="C1569">
-        <v>3299.7</v>
+        <v>4237.1</v>
       </c>
       <c r="D1569" t="s">
         <v>1571</v>
@@ -28700,7 +29852,7 @@
         <v>33</v>
       </c>
       <c r="C1570">
-        <v>3191.3</v>
+        <v>4364.2</v>
       </c>
       <c r="D1570" t="s">
         <v>1572</v>
@@ -28714,7 +29866,7 @@
         <v>34</v>
       </c>
       <c r="C1571">
-        <v>3313</v>
+        <v>4432.4</v>
       </c>
       <c r="D1571" t="s">
         <v>1573</v>
@@ -28728,7 +29880,7 @@
         <v>35</v>
       </c>
       <c r="C1572">
-        <v>3419.6</v>
+        <v>4494.8</v>
       </c>
       <c r="D1572" t="s">
         <v>1574</v>
@@ -28742,7 +29894,7 @@
         <v>36</v>
       </c>
       <c r="C1573">
-        <v>3584.8</v>
+        <v>4571.9</v>
       </c>
       <c r="D1573" t="s">
         <v>1575</v>
@@ -28756,7 +29908,7 @@
         <v>37</v>
       </c>
       <c r="C1574">
-        <v>3476.5</v>
+        <v>4631.9</v>
       </c>
       <c r="D1574" t="s">
         <v>1576</v>
@@ -28770,7 +29922,7 @@
         <v>38</v>
       </c>
       <c r="C1575">
-        <v>3529.5</v>
+        <v>4722.8</v>
       </c>
       <c r="D1575" t="s">
         <v>1577</v>
@@ -28784,7 +29936,7 @@
         <v>39</v>
       </c>
       <c r="C1576">
-        <v>3616.2</v>
+        <v>4806.3</v>
       </c>
       <c r="D1576" t="s">
         <v>1578</v>
@@ -28798,7 +29950,7 @@
         <v>40</v>
       </c>
       <c r="C1577">
-        <v>3704.8</v>
+        <v>4855.6</v>
       </c>
       <c r="D1577" t="s">
         <v>1579</v>
@@ -28812,7 +29964,7 @@
         <v>41</v>
       </c>
       <c r="C1578">
-        <v>3900.7</v>
+        <v>4303.9</v>
       </c>
       <c r="D1578" t="s">
         <v>1580</v>
@@ -28826,7 +29978,7 @@
         <v>42</v>
       </c>
       <c r="C1579">
-        <v>3929.9</v>
+        <v>4335.3</v>
       </c>
       <c r="D1579" t="s">
         <v>1581</v>
@@ -28840,7 +29992,7 @@
         <v>43</v>
       </c>
       <c r="C1580">
-        <v>3968.3</v>
+        <v>4352.8</v>
       </c>
       <c r="D1580" t="s">
         <v>1582</v>
@@ -28854,7 +30006,7 @@
         <v>44</v>
       </c>
       <c r="C1581">
-        <v>4027.5</v>
+        <v>4344.9</v>
       </c>
       <c r="D1581" t="s">
         <v>1583</v>
@@ -28868,7 +30020,7 @@
         <v>45</v>
       </c>
       <c r="C1582">
-        <v>4058</v>
+        <v>4259.3</v>
       </c>
       <c r="D1582" t="s">
         <v>1584</v>
@@ -28882,7 +30034,7 @@
         <v>46</v>
       </c>
       <c r="C1583">
-        <v>4083.3</v>
+        <v>4232.4</v>
       </c>
       <c r="D1583" t="s">
         <v>1585</v>
@@ -28896,7 +30048,7 @@
         <v>47</v>
       </c>
       <c r="C1584">
-        <v>4094.1</v>
+        <v>4245.1</v>
       </c>
       <c r="D1584" t="s">
         <v>1586</v>
@@ -28910,7 +30062,7 @@
         <v>48</v>
       </c>
       <c r="C1585">
-        <v>4140.1</v>
+        <v>4202.7</v>
       </c>
       <c r="D1585" t="s">
         <v>1587</v>
@@ -28924,7 +30076,7 @@
         <v>49</v>
       </c>
       <c r="C1586">
-        <v>3966.1</v>
+        <v>4299.4</v>
       </c>
       <c r="D1586" t="s">
         <v>1588</v>
@@ -28938,7 +30090,7 @@
         <v>50</v>
       </c>
       <c r="C1587">
-        <v>3958.2</v>
+        <v>4274</v>
       </c>
       <c r="D1587" t="s">
         <v>1589</v>
@@ -28952,7 +30104,7 @@
         <v>51</v>
       </c>
       <c r="C1588">
-        <v>3945.5</v>
+        <v>4252</v>
       </c>
       <c r="D1588" t="s">
         <v>1590</v>
@@ -28966,7 +30118,7 @@
         <v>52</v>
       </c>
       <c r="C1589">
-        <v>3950</v>
+        <v>4275.3</v>
       </c>
       <c r="D1589" t="s">
         <v>1591</v>
@@ -28980,7 +30132,7 @@
         <v>53</v>
       </c>
       <c r="C1590">
-        <v>3917.1</v>
+        <v>4246.8</v>
       </c>
       <c r="D1590" t="s">
         <v>1592</v>
@@ -28994,7 +30146,7 @@
         <v>54</v>
       </c>
       <c r="C1591">
-        <v>3888.4</v>
+        <v>4257.8</v>
       </c>
       <c r="D1591" t="s">
         <v>1593</v>
@@ -29008,7 +30160,7 @@
         <v>55</v>
       </c>
       <c r="C1592">
-        <v>3903.8</v>
+        <v>4220.9</v>
       </c>
       <c r="D1592" t="s">
         <v>1594</v>
@@ -29022,7 +30174,7 @@
         <v>56</v>
       </c>
       <c r="C1593">
-        <v>3918.2</v>
+        <v>4175.5</v>
       </c>
       <c r="D1593" t="s">
         <v>1595</v>
@@ -29036,7 +30188,7 @@
         <v>57</v>
       </c>
       <c r="C1594">
-        <v>3960.2</v>
+        <v>4195.1</v>
       </c>
       <c r="D1594" t="s">
         <v>1596</v>
@@ -29050,7 +30202,7 @@
         <v>58</v>
       </c>
       <c r="C1595">
-        <v>3937</v>
+        <v>4152</v>
       </c>
       <c r="D1595" t="s">
         <v>1597</v>
@@ -29064,7 +30216,7 @@
         <v>59</v>
       </c>
       <c r="C1596">
-        <v>3928</v>
+        <v>4117.1</v>
       </c>
       <c r="D1596" t="s">
         <v>1598</v>
@@ -29078,7 +30230,7 @@
         <v>60</v>
       </c>
       <c r="C1597">
-        <v>3955.1</v>
+        <v>4067.1</v>
       </c>
       <c r="D1597" t="s">
         <v>1599</v>
@@ -29092,7 +30244,7 @@
         <v>61</v>
       </c>
       <c r="C1598">
-        <v>3981.2</v>
+        <v>4007.6</v>
       </c>
       <c r="D1598" t="s">
         <v>1600</v>
@@ -29106,7 +30258,7 @@
         <v>62</v>
       </c>
       <c r="C1599">
-        <v>3916.4</v>
+        <v>3949.5</v>
       </c>
       <c r="D1599" t="s">
         <v>1601</v>
@@ -29120,7 +30272,7 @@
         <v>63</v>
       </c>
       <c r="C1600">
-        <v>3871.2</v>
+        <v>3939.3</v>
       </c>
       <c r="D1600" t="s">
         <v>1602</v>
@@ -29134,7 +30286,7 @@
         <v>64</v>
       </c>
       <c r="C1601">
-        <v>3880.3</v>
+        <v>3950.3</v>
       </c>
       <c r="D1601" t="s">
         <v>1603</v>
@@ -29148,7 +30300,7 @@
         <v>65</v>
       </c>
       <c r="C1602">
-        <v>3899.1</v>
+        <v>3611.9</v>
       </c>
       <c r="D1602" t="s">
         <v>1604</v>
@@ -29162,7 +30314,7 @@
         <v>66</v>
       </c>
       <c r="C1603">
-        <v>3860.3</v>
+        <v>3585.2</v>
       </c>
       <c r="D1603" t="s">
         <v>1605</v>
@@ -29176,7 +30328,7 @@
         <v>67</v>
       </c>
       <c r="C1604">
-        <v>3869.2</v>
+        <v>3584.2</v>
       </c>
       <c r="D1604" t="s">
         <v>1606</v>
@@ -29190,7 +30342,7 @@
         <v>68</v>
       </c>
       <c r="C1605">
-        <v>3850.9</v>
+        <v>3549.4</v>
       </c>
       <c r="D1605" t="s">
         <v>1607</v>
@@ -29204,7 +30356,7 @@
         <v>69</v>
       </c>
       <c r="C1606">
-        <v>3763.4</v>
+        <v>4139.9</v>
       </c>
       <c r="D1606" t="s">
         <v>1608</v>
@@ -29218,7 +30370,7 @@
         <v>70</v>
       </c>
       <c r="C1607">
-        <v>3698.8</v>
+        <v>4091.5</v>
       </c>
       <c r="D1607" t="s">
         <v>1609</v>
@@ -29232,7 +30384,7 @@
         <v>71</v>
       </c>
       <c r="C1608">
-        <v>3654.3</v>
+        <v>4035.6</v>
       </c>
       <c r="D1608" t="s">
         <v>1610</v>
@@ -29246,7 +30398,7 @@
         <v>72</v>
       </c>
       <c r="C1609">
-        <v>3578.9</v>
+        <v>4000.8</v>
       </c>
       <c r="D1609" t="s">
         <v>1611</v>
@@ -29260,7 +30412,7 @@
         <v>73</v>
       </c>
       <c r="C1610">
-        <v>4134.8</v>
+        <v>4180.3</v>
       </c>
       <c r="D1610" t="s">
         <v>1612</v>
@@ -29274,7 +30426,7 @@
         <v>74</v>
       </c>
       <c r="C1611">
-        <v>4035</v>
+        <v>4158.4</v>
       </c>
       <c r="D1611" t="s">
         <v>1613</v>
@@ -29288,7 +30440,7 @@
         <v>75</v>
       </c>
       <c r="C1612">
-        <v>3966.5</v>
+        <v>4138.6</v>
       </c>
       <c r="D1612" t="s">
         <v>1614</v>
@@ -29302,7 +30454,7 @@
         <v>76</v>
       </c>
       <c r="C1613">
-        <v>3935.9</v>
+        <v>4094.3</v>
       </c>
       <c r="D1613" t="s">
         <v>1615</v>
@@ -29316,7 +30468,7 @@
         <v>77</v>
       </c>
       <c r="C1614">
-        <v>3861.2</v>
+        <v>4604.9</v>
       </c>
       <c r="D1614" t="s">
         <v>1616</v>
@@ -29330,7 +30482,7 @@
         <v>78</v>
       </c>
       <c r="C1615">
-        <v>3889.7</v>
+        <v>4612.1</v>
       </c>
       <c r="D1615" t="s">
         <v>1617</v>
@@ -29344,7 +30496,7 @@
         <v>79</v>
       </c>
       <c r="C1616">
-        <v>3836.6</v>
+        <v>4597.8</v>
       </c>
       <c r="D1616" t="s">
         <v>1618</v>
@@ -29358,7 +30510,7 @@
         <v>80</v>
       </c>
       <c r="C1617">
-        <v>3819.2</v>
+        <v>4560</v>
       </c>
       <c r="D1617" t="s">
         <v>1619</v>
@@ -29372,7 +30524,7 @@
         <v>81</v>
       </c>
       <c r="C1618">
-        <v>3875.1</v>
+        <v>4638</v>
       </c>
       <c r="D1618" t="s">
         <v>1620</v>
@@ -29386,7 +30538,7 @@
         <v>82</v>
       </c>
       <c r="C1619">
-        <v>3906.2</v>
+        <v>4662.5</v>
       </c>
       <c r="D1619" t="s">
         <v>1621</v>
@@ -29400,7 +30552,7 @@
         <v>83</v>
       </c>
       <c r="C1620">
-        <v>3908.5</v>
+        <v>4640.7</v>
       </c>
       <c r="D1620" t="s">
         <v>1622</v>
@@ -29414,7 +30566,7 @@
         <v>84</v>
       </c>
       <c r="C1621">
-        <v>3900.7</v>
+        <v>4608.2</v>
       </c>
       <c r="D1621" t="s">
         <v>1623</v>
@@ -29428,7 +30580,7 @@
         <v>85</v>
       </c>
       <c r="C1622">
-        <v>3924.6</v>
+        <v>4641.3</v>
       </c>
       <c r="D1622" t="s">
         <v>1624</v>
@@ -29442,7 +30594,7 @@
         <v>86</v>
       </c>
       <c r="C1623">
-        <v>3902.3</v>
+        <v>4594.6</v>
       </c>
       <c r="D1623" t="s">
         <v>1625</v>
@@ -29456,7 +30608,7 @@
         <v>87</v>
       </c>
       <c r="C1624">
-        <v>3964.8</v>
+        <v>4578.8</v>
       </c>
       <c r="D1624" t="s">
         <v>1626</v>
@@ -29470,7 +30622,7 @@
         <v>88</v>
       </c>
       <c r="C1625">
-        <v>3963.5</v>
+        <v>4555.1</v>
       </c>
       <c r="D1625" t="s">
         <v>1627</v>
@@ -29484,7 +30636,7 @@
         <v>89</v>
       </c>
       <c r="C1626">
-        <v>3791.9</v>
+        <v>4469.3</v>
       </c>
       <c r="D1626" t="s">
         <v>1628</v>
@@ -29498,7 +30650,7 @@
         <v>90</v>
       </c>
       <c r="C1627">
-        <v>3823.7</v>
+        <v>4485.9</v>
       </c>
       <c r="D1627" t="s">
         <v>1629</v>
@@ -29512,7 +30664,7 @@
         <v>91</v>
       </c>
       <c r="C1628">
-        <v>3810.4</v>
+        <v>4431.3</v>
       </c>
       <c r="D1628" t="s">
         <v>1630</v>
@@ -29526,7 +30678,7 @@
         <v>92</v>
       </c>
       <c r="C1629">
-        <v>3873.1</v>
+        <v>4390.9</v>
       </c>
       <c r="D1629" t="s">
         <v>1631</v>
@@ -29540,7 +30692,7 @@
         <v>93</v>
       </c>
       <c r="C1630">
-        <v>3789.7</v>
+        <v>4011.8</v>
       </c>
       <c r="D1630" t="s">
         <v>1632</v>
@@ -29554,7 +30706,7 @@
         <v>94</v>
       </c>
       <c r="C1631">
-        <v>3765.6</v>
+        <v>4007.6</v>
       </c>
       <c r="D1631" t="s">
         <v>1633</v>
@@ -29568,7 +30720,7 @@
         <v>95</v>
       </c>
       <c r="C1632">
-        <v>3760.6</v>
+        <v>3987.1</v>
       </c>
       <c r="D1632" t="s">
         <v>1634</v>
@@ -29582,7 +30734,7 @@
         <v>96</v>
       </c>
       <c r="C1633">
-        <v>3802.5</v>
+        <v>3960.5</v>
       </c>
       <c r="D1633" t="s">
         <v>1635</v>
@@ -29596,7 +30748,7 @@
         <v>1</v>
       </c>
       <c r="C1634">
-        <v>5106</v>
+        <v>5052.4</v>
       </c>
       <c r="D1634" t="s">
         <v>1636</v>
@@ -29610,7 +30762,7 @@
         <v>2</v>
       </c>
       <c r="C1635">
-        <v>5096.2</v>
+        <v>5050</v>
       </c>
       <c r="D1635" t="s">
         <v>1637</v>
@@ -29624,7 +30776,7 @@
         <v>3</v>
       </c>
       <c r="C1636">
-        <v>4989.7</v>
+        <v>5015.6</v>
       </c>
       <c r="D1636" t="s">
         <v>1638</v>
@@ -29638,7 +30790,7 @@
         <v>4</v>
       </c>
       <c r="C1637">
-        <v>4867.7</v>
+        <v>4970.2</v>
       </c>
       <c r="D1637" t="s">
         <v>1639</v>
@@ -29652,7 +30804,7 @@
         <v>5</v>
       </c>
       <c r="C1638">
-        <v>4423.4</v>
+        <v>4737.2</v>
       </c>
       <c r="D1638" t="s">
         <v>1640</v>
@@ -29666,7 +30818,7 @@
         <v>6</v>
       </c>
       <c r="C1639">
-        <v>4388.2</v>
+        <v>4693.4</v>
       </c>
       <c r="D1639" t="s">
         <v>1641</v>
@@ -29680,7 +30832,7 @@
         <v>7</v>
       </c>
       <c r="C1640">
-        <v>4339.8</v>
+        <v>4676.1</v>
       </c>
       <c r="D1640" t="s">
         <v>1642</v>
@@ -29694,7 +30846,7 @@
         <v>8</v>
       </c>
       <c r="C1641">
-        <v>4304.3</v>
+        <v>4620.7</v>
       </c>
       <c r="D1641" t="s">
         <v>1643</v>
@@ -29708,7 +30860,7 @@
         <v>9</v>
       </c>
       <c r="C1642">
-        <v>4015.1</v>
+        <v>4592.6</v>
       </c>
       <c r="D1642" t="s">
         <v>1644</v>
@@ -29722,7 +30874,7 @@
         <v>10</v>
       </c>
       <c r="C1643">
-        <v>3994.8</v>
+        <v>4571.9</v>
       </c>
       <c r="D1643" t="s">
         <v>1645</v>
@@ -29736,7 +30888,7 @@
         <v>11</v>
       </c>
       <c r="C1644">
-        <v>3960.6</v>
+        <v>4540</v>
       </c>
       <c r="D1644" t="s">
         <v>1646</v>
@@ -29750,7 +30902,7 @@
         <v>12</v>
       </c>
       <c r="C1645">
-        <v>3961.4</v>
+        <v>4548.2</v>
       </c>
       <c r="D1645" t="s">
         <v>1647</v>
@@ -29764,7 +30916,7 @@
         <v>13</v>
       </c>
       <c r="C1646">
-        <v>3984</v>
+        <v>4539.7</v>
       </c>
       <c r="D1646" t="s">
         <v>1648</v>
@@ -29778,7 +30930,7 @@
         <v>14</v>
       </c>
       <c r="C1647">
-        <v>3971.1</v>
+        <v>4540.1</v>
       </c>
       <c r="D1647" t="s">
         <v>1649</v>
@@ -29792,7 +30944,7 @@
         <v>15</v>
       </c>
       <c r="C1648">
-        <v>3955.4</v>
+        <v>4523.2</v>
       </c>
       <c r="D1648" t="s">
         <v>1650</v>
@@ -29806,7 +30958,7 @@
         <v>16</v>
       </c>
       <c r="C1649">
-        <v>3935.9</v>
+        <v>4518.6</v>
       </c>
       <c r="D1649" t="s">
         <v>1651</v>
@@ -29820,7 +30972,7 @@
         <v>17</v>
       </c>
       <c r="C1650">
-        <v>3905.9</v>
+        <v>4464.7</v>
       </c>
       <c r="D1650" t="s">
         <v>1652</v>
@@ -29834,7 +30986,7 @@
         <v>18</v>
       </c>
       <c r="C1651">
-        <v>3869.2</v>
+        <v>4466.3</v>
       </c>
       <c r="D1651" t="s">
         <v>1653</v>
@@ -29848,7 +31000,7 @@
         <v>19</v>
       </c>
       <c r="C1652">
-        <v>3827.8</v>
+        <v>4462.7</v>
       </c>
       <c r="D1652" t="s">
         <v>1654</v>
@@ -29862,7 +31014,7 @@
         <v>20</v>
       </c>
       <c r="C1653">
-        <v>3803.5</v>
+        <v>4464.2</v>
       </c>
       <c r="D1653" t="s">
         <v>1655</v>
@@ -29876,7 +31028,7 @@
         <v>21</v>
       </c>
       <c r="C1654">
-        <v>3855.6</v>
+        <v>4499.1</v>
       </c>
       <c r="D1654" t="s">
         <v>1656</v>
@@ -29890,7 +31042,7 @@
         <v>22</v>
       </c>
       <c r="C1655">
-        <v>3875.6</v>
+        <v>4570.5</v>
       </c>
       <c r="D1655" t="s">
         <v>1657</v>
@@ -29904,7 +31056,7 @@
         <v>23</v>
       </c>
       <c r="C1656">
-        <v>3883.4</v>
+        <v>4661.9</v>
       </c>
       <c r="D1656" t="s">
         <v>1658</v>
@@ -29918,7 +31070,7 @@
         <v>24</v>
       </c>
       <c r="C1657">
-        <v>3896.6</v>
+        <v>4768.1</v>
       </c>
       <c r="D1657" t="s">
         <v>1659</v>
@@ -29932,7 +31084,7 @@
         <v>25</v>
       </c>
       <c r="C1658">
-        <v>3966.8</v>
+        <v>4875.8</v>
       </c>
       <c r="D1658" t="s">
         <v>1660</v>
@@ -29946,7 +31098,7 @@
         <v>26</v>
       </c>
       <c r="C1659">
-        <v>4031.3</v>
+        <v>5004</v>
       </c>
       <c r="D1659" t="s">
         <v>1661</v>
@@ -29960,7 +31112,7 @@
         <v>27</v>
       </c>
       <c r="C1660">
-        <v>4103.1</v>
+        <v>5134.3</v>
       </c>
       <c r="D1660" t="s">
         <v>1662</v>
@@ -29974,7 +31126,7 @@
         <v>28</v>
       </c>
       <c r="C1661">
-        <v>4146.4</v>
+        <v>5251.5</v>
       </c>
       <c r="D1661" t="s">
         <v>1663</v>
@@ -29988,7 +31140,7 @@
         <v>29</v>
       </c>
       <c r="C1662">
-        <v>4200.9</v>
+        <v>5218.4</v>
       </c>
       <c r="D1662" t="s">
         <v>1664</v>
@@ -30002,7 +31154,7 @@
         <v>30</v>
       </c>
       <c r="C1663">
-        <v>4236.5</v>
+        <v>5281.1</v>
       </c>
       <c r="D1663" t="s">
         <v>1665</v>
@@ -30016,7 +31168,7 @@
         <v>31</v>
       </c>
       <c r="C1664">
-        <v>4362.3</v>
+        <v>5439.3</v>
       </c>
       <c r="D1664" t="s">
         <v>1666</v>
@@ -30030,7 +31182,7 @@
         <v>32</v>
       </c>
       <c r="C1665">
-        <v>4489.7</v>
+        <v>5487.1</v>
       </c>
       <c r="D1665" t="s">
         <v>1667</v>
@@ -30044,7 +31196,7 @@
         <v>33</v>
       </c>
       <c r="C1666">
-        <v>4421.3</v>
+        <v>5604.2</v>
       </c>
       <c r="D1666" t="s">
         <v>1668</v>
@@ -30058,7 +31210,7 @@
         <v>34</v>
       </c>
       <c r="C1667">
-        <v>4523</v>
+        <v>5662.4</v>
       </c>
       <c r="D1667" t="s">
         <v>1669</v>
@@ -30072,7 +31224,7 @@
         <v>35</v>
       </c>
       <c r="C1668">
-        <v>4619.6</v>
+        <v>5724.8</v>
       </c>
       <c r="D1668" t="s">
         <v>1670</v>
@@ -30086,7 +31238,7 @@
         <v>36</v>
       </c>
       <c r="C1669">
-        <v>4794.8</v>
+        <v>5791.9</v>
       </c>
       <c r="D1669" t="s">
         <v>1671</v>
@@ -30100,7 +31252,7 @@
         <v>37</v>
       </c>
       <c r="C1670">
-        <v>4696.5</v>
+        <v>5861.9</v>
       </c>
       <c r="D1670" t="s">
         <v>1672</v>
@@ -30114,7 +31266,7 @@
         <v>38</v>
       </c>
       <c r="C1671">
-        <v>4729.5</v>
+        <v>5932.8</v>
       </c>
       <c r="D1671" t="s">
         <v>1673</v>
@@ -30128,7 +31280,7 @@
         <v>39</v>
       </c>
       <c r="C1672">
-        <v>4796.2</v>
+        <v>5976.3</v>
       </c>
       <c r="D1672" t="s">
         <v>1674</v>
@@ -30142,7 +31294,7 @@
         <v>40</v>
       </c>
       <c r="C1673">
-        <v>4864.8</v>
+        <v>5995.6</v>
       </c>
       <c r="D1673" t="s">
         <v>1675</v>
@@ -30156,7 +31308,7 @@
         <v>41</v>
       </c>
       <c r="C1674">
-        <v>5030.7</v>
+        <v>5403.9</v>
       </c>
       <c r="D1674" t="s">
         <v>1676</v>
@@ -30170,7 +31322,7 @@
         <v>42</v>
       </c>
       <c r="C1675">
-        <v>5019.9</v>
+        <v>5405.3</v>
       </c>
       <c r="D1675" t="s">
         <v>1677</v>
@@ -30184,7 +31336,7 @@
         <v>43</v>
       </c>
       <c r="C1676">
-        <v>5018.3</v>
+        <v>5392.8</v>
       </c>
       <c r="D1676" t="s">
         <v>1678</v>
@@ -30198,7 +31350,7 @@
         <v>44</v>
       </c>
       <c r="C1677">
-        <v>5017.5</v>
+        <v>5354.9</v>
       </c>
       <c r="D1677" t="s">
         <v>1679</v>
@@ -30212,7 +31364,7 @@
         <v>45</v>
       </c>
       <c r="C1678">
-        <v>4998</v>
+        <v>5269.3</v>
       </c>
       <c r="D1678" t="s">
         <v>1680</v>
@@ -30226,7 +31378,7 @@
         <v>46</v>
       </c>
       <c r="C1679">
-        <v>4973.3</v>
+        <v>5232.4</v>
       </c>
       <c r="D1679" t="s">
         <v>1681</v>
@@ -30240,7 +31392,7 @@
         <v>47</v>
       </c>
       <c r="C1680">
-        <v>4924.1</v>
+        <v>5215.1</v>
       </c>
       <c r="D1680" t="s">
         <v>1682</v>
@@ -30254,7 +31406,7 @@
         <v>48</v>
       </c>
       <c r="C1681">
-        <v>4910.1</v>
+        <v>5142.7</v>
       </c>
       <c r="D1681" t="s">
         <v>1683</v>
@@ -30268,7 +31420,7 @@
         <v>49</v>
       </c>
       <c r="C1682">
-        <v>4686.1</v>
+        <v>5249.4</v>
       </c>
       <c r="D1682" t="s">
         <v>1684</v>
@@ -30282,7 +31434,7 @@
         <v>50</v>
       </c>
       <c r="C1683">
-        <v>4628.2</v>
+        <v>5214</v>
       </c>
       <c r="D1683" t="s">
         <v>1685</v>
@@ -30296,7 +31448,7 @@
         <v>51</v>
       </c>
       <c r="C1684">
-        <v>4585.5</v>
+        <v>5192</v>
       </c>
       <c r="D1684" t="s">
         <v>1686</v>
@@ -30310,7 +31462,7 @@
         <v>52</v>
       </c>
       <c r="C1685">
-        <v>4570</v>
+        <v>5215.3</v>
       </c>
       <c r="D1685" t="s">
         <v>1687</v>
@@ -30324,7 +31476,7 @@
         <v>53</v>
       </c>
       <c r="C1686">
-        <v>4517.1</v>
+        <v>5186.8</v>
       </c>
       <c r="D1686" t="s">
         <v>1688</v>
@@ -30338,7 +31490,7 @@
         <v>54</v>
       </c>
       <c r="C1687">
-        <v>4488.4</v>
+        <v>5217.8</v>
       </c>
       <c r="D1687" t="s">
         <v>1689</v>
@@ -30352,7 +31504,7 @@
         <v>55</v>
       </c>
       <c r="C1688">
-        <v>4513.8</v>
+        <v>5200.9</v>
       </c>
       <c r="D1688" t="s">
         <v>1690</v>
@@ -30366,7 +31518,7 @@
         <v>56</v>
       </c>
       <c r="C1689">
-        <v>4528.2</v>
+        <v>5185.5</v>
       </c>
       <c r="D1689" t="s">
         <v>1691</v>
@@ -30380,7 +31532,7 @@
         <v>57</v>
       </c>
       <c r="C1690">
-        <v>4590.2</v>
+        <v>5275.1</v>
       </c>
       <c r="D1690" t="s">
         <v>1692</v>
@@ -30394,7 +31546,7 @@
         <v>58</v>
       </c>
       <c r="C1691">
-        <v>4587</v>
+        <v>5252</v>
       </c>
       <c r="D1691" t="s">
         <v>1693</v>
@@ -30408,7 +31560,7 @@
         <v>59</v>
       </c>
       <c r="C1692">
-        <v>4588</v>
+        <v>5217.1</v>
       </c>
       <c r="D1692" t="s">
         <v>1694</v>
@@ -30422,7 +31574,7 @@
         <v>60</v>
       </c>
       <c r="C1693">
-        <v>4625.1</v>
+        <v>5167.1</v>
       </c>
       <c r="D1693" t="s">
         <v>1695</v>
@@ -30436,7 +31588,7 @@
         <v>61</v>
       </c>
       <c r="C1694">
-        <v>4661.2</v>
+        <v>5107.6</v>
       </c>
       <c r="D1694" t="s">
         <v>1696</v>
@@ -30450,7 +31602,7 @@
         <v>62</v>
       </c>
       <c r="C1695">
-        <v>4616.4</v>
+        <v>5049.5</v>
       </c>
       <c r="D1695" t="s">
         <v>1697</v>
@@ -30464,7 +31616,7 @@
         <v>63</v>
       </c>
       <c r="C1696">
-        <v>4571.2</v>
+        <v>5039.3</v>
       </c>
       <c r="D1696" t="s">
         <v>1698</v>
@@ -30478,7 +31630,7 @@
         <v>64</v>
       </c>
       <c r="C1697">
-        <v>4580.3</v>
+        <v>5030.3</v>
       </c>
       <c r="D1697" t="s">
         <v>1699</v>
@@ -30492,7 +31644,7 @@
         <v>65</v>
       </c>
       <c r="C1698">
-        <v>4609.1</v>
+        <v>4681.9</v>
       </c>
       <c r="D1698" t="s">
         <v>1700</v>
@@ -30506,7 +31658,7 @@
         <v>66</v>
       </c>
       <c r="C1699">
-        <v>4560.3</v>
+        <v>4655.2</v>
       </c>
       <c r="D1699" t="s">
         <v>1701</v>
@@ -30520,7 +31672,7 @@
         <v>67</v>
       </c>
       <c r="C1700">
-        <v>4549.2</v>
+        <v>4654.2</v>
       </c>
       <c r="D1700" t="s">
         <v>1702</v>
@@ -30534,7 +31686,7 @@
         <v>68</v>
       </c>
       <c r="C1701">
-        <v>4510.9</v>
+        <v>4619.4</v>
       </c>
       <c r="D1701" t="s">
         <v>1703</v>
@@ -30548,7 +31700,7 @@
         <v>69</v>
       </c>
       <c r="C1702">
-        <v>4413.4</v>
+        <v>5219.9</v>
       </c>
       <c r="D1702" t="s">
         <v>1704</v>
@@ -30562,7 +31714,7 @@
         <v>70</v>
       </c>
       <c r="C1703">
-        <v>4338.8</v>
+        <v>5161.5</v>
       </c>
       <c r="D1703" t="s">
         <v>1705</v>
@@ -30576,7 +31728,7 @@
         <v>71</v>
       </c>
       <c r="C1704">
-        <v>4294.3</v>
+        <v>5105.6</v>
       </c>
       <c r="D1704" t="s">
         <v>1706</v>
@@ -30590,7 +31742,7 @@
         <v>72</v>
       </c>
       <c r="C1705">
-        <v>4238.9</v>
+        <v>5060.8</v>
       </c>
       <c r="D1705" t="s">
         <v>1707</v>
@@ -30604,7 +31756,7 @@
         <v>73</v>
       </c>
       <c r="C1706">
-        <v>4814.8</v>
+        <v>5200.3</v>
       </c>
       <c r="D1706" t="s">
         <v>1708</v>
@@ -30618,7 +31770,7 @@
         <v>74</v>
       </c>
       <c r="C1707">
-        <v>4745</v>
+        <v>5158.4</v>
       </c>
       <c r="D1707" t="s">
         <v>1709</v>
@@ -30632,7 +31784,7 @@
         <v>75</v>
       </c>
       <c r="C1708">
-        <v>4716.5</v>
+        <v>5128.6</v>
       </c>
       <c r="D1708" t="s">
         <v>1710</v>
@@ -30646,7 +31798,7 @@
         <v>76</v>
       </c>
       <c r="C1709">
-        <v>4715.9</v>
+        <v>5094.3</v>
       </c>
       <c r="D1709" t="s">
         <v>1711</v>
@@ -30660,7 +31812,7 @@
         <v>77</v>
       </c>
       <c r="C1710">
-        <v>4651.2</v>
+        <v>5594.9</v>
       </c>
       <c r="D1710" t="s">
         <v>1712</v>
@@ -30674,7 +31826,7 @@
         <v>78</v>
       </c>
       <c r="C1711">
-        <v>4689.7</v>
+        <v>5592.1</v>
       </c>
       <c r="D1711" t="s">
         <v>1713</v>
@@ -30688,7 +31840,7 @@
         <v>79</v>
       </c>
       <c r="C1712">
-        <v>4636.6</v>
+        <v>5567.8</v>
       </c>
       <c r="D1712" t="s">
         <v>1714</v>
@@ -30702,7 +31854,7 @@
         <v>80</v>
       </c>
       <c r="C1713">
-        <v>4609.2</v>
+        <v>5500</v>
       </c>
       <c r="D1713" t="s">
         <v>1715</v>
@@ -30716,7 +31868,7 @@
         <v>81</v>
       </c>
       <c r="C1714">
-        <v>4675.1</v>
+        <v>5538</v>
       </c>
       <c r="D1714" t="s">
         <v>1716</v>
@@ -30730,7 +31882,7 @@
         <v>82</v>
       </c>
       <c r="C1715">
-        <v>4716.2</v>
+        <v>5552.5</v>
       </c>
       <c r="D1715" t="s">
         <v>1717</v>
@@ -30744,7 +31896,7 @@
         <v>83</v>
       </c>
       <c r="C1716">
-        <v>4758.5</v>
+        <v>5540.7</v>
       </c>
       <c r="D1716" t="s">
         <v>1718</v>
@@ -30758,7 +31910,7 @@
         <v>84</v>
       </c>
       <c r="C1717">
-        <v>4800.7</v>
+        <v>5538.2</v>
       </c>
       <c r="D1717" t="s">
         <v>1719</v>
@@ -30772,7 +31924,7 @@
         <v>85</v>
       </c>
       <c r="C1718">
-        <v>4824.6</v>
+        <v>5551.3</v>
       </c>
       <c r="D1718" t="s">
         <v>1720</v>
@@ -30786,7 +31938,7 @@
         <v>86</v>
       </c>
       <c r="C1719">
-        <v>4812.3</v>
+        <v>5524.6</v>
       </c>
       <c r="D1719" t="s">
         <v>1721</v>
@@ -30800,7 +31952,7 @@
         <v>87</v>
       </c>
       <c r="C1720">
-        <v>4864.8</v>
+        <v>5518.8</v>
       </c>
       <c r="D1720" t="s">
         <v>1722</v>
@@ -30814,7 +31966,7 @@
         <v>88</v>
       </c>
       <c r="C1721">
-        <v>4803.5</v>
+        <v>5445.1</v>
       </c>
       <c r="D1721" t="s">
         <v>1723</v>
@@ -30828,7 +31980,7 @@
         <v>89</v>
       </c>
       <c r="C1722">
-        <v>4581.9</v>
+        <v>5299.3</v>
       </c>
       <c r="D1722" t="s">
         <v>1724</v>
@@ -30842,7 +31994,7 @@
         <v>90</v>
       </c>
       <c r="C1723">
-        <v>4573.7</v>
+        <v>5305.9</v>
       </c>
       <c r="D1723" t="s">
         <v>1725</v>
@@ -30856,7 +32008,7 @@
         <v>91</v>
       </c>
       <c r="C1724">
-        <v>4540.4</v>
+        <v>5241.3</v>
       </c>
       <c r="D1724" t="s">
         <v>1726</v>
@@ -30870,7 +32022,7 @@
         <v>92</v>
       </c>
       <c r="C1725">
-        <v>4563.1</v>
+        <v>5170.9</v>
       </c>
       <c r="D1725" t="s">
         <v>1727</v>
@@ -30884,7 +32036,7 @@
         <v>93</v>
       </c>
       <c r="C1726">
-        <v>4399.7</v>
+        <v>4661.8</v>
       </c>
       <c r="D1726" t="s">
         <v>1728</v>
@@ -30898,7 +32050,7 @@
         <v>94</v>
       </c>
       <c r="C1727">
-        <v>4295.6</v>
+        <v>4587.6</v>
       </c>
       <c r="D1727" t="s">
         <v>1729</v>
@@ -30912,7 +32064,7 @@
         <v>95</v>
       </c>
       <c r="C1728">
-        <v>4330.6</v>
+        <v>4607.1</v>
       </c>
       <c r="D1728" t="s">
         <v>1730</v>
@@ -30926,7 +32078,7 @@
         <v>96</v>
       </c>
       <c r="C1729">
-        <v>4362.5</v>
+        <v>4580.5</v>
       </c>
       <c r="D1729" t="s">
         <v>1731</v>
@@ -36306,6 +37458,5382 @@
       </c>
       <c r="D2113" t="s">
         <v>2115</v>
+      </c>
+    </row>
+    <row r="2114" spans="1:4">
+      <c r="A2114" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2114">
+        <v>1</v>
+      </c>
+      <c r="C2114">
+        <v>5566</v>
+      </c>
+      <c r="D2114" t="s">
+        <v>2116</v>
+      </c>
+    </row>
+    <row r="2115" spans="1:4">
+      <c r="A2115" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2115">
+        <v>2</v>
+      </c>
+      <c r="C2115">
+        <v>5506.2</v>
+      </c>
+      <c r="D2115" t="s">
+        <v>2117</v>
+      </c>
+    </row>
+    <row r="2116" spans="1:4">
+      <c r="A2116" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2116">
+        <v>3</v>
+      </c>
+      <c r="C2116">
+        <v>5379.7</v>
+      </c>
+      <c r="D2116" t="s">
+        <v>2118</v>
+      </c>
+    </row>
+    <row r="2117" spans="1:4">
+      <c r="A2117" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2117">
+        <v>4</v>
+      </c>
+      <c r="C2117">
+        <v>5257.7</v>
+      </c>
+      <c r="D2117" t="s">
+        <v>2119</v>
+      </c>
+    </row>
+    <row r="2118" spans="1:4">
+      <c r="A2118" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2118">
+        <v>5</v>
+      </c>
+      <c r="C2118">
+        <v>4803.4</v>
+      </c>
+      <c r="D2118" t="s">
+        <v>2120</v>
+      </c>
+    </row>
+    <row r="2119" spans="1:4">
+      <c r="A2119" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2119">
+        <v>6</v>
+      </c>
+      <c r="C2119">
+        <v>4758.2</v>
+      </c>
+      <c r="D2119" t="s">
+        <v>2121</v>
+      </c>
+    </row>
+    <row r="2120" spans="1:4">
+      <c r="A2120" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2120">
+        <v>7</v>
+      </c>
+      <c r="C2120">
+        <v>4709.8</v>
+      </c>
+      <c r="D2120" t="s">
+        <v>2122</v>
+      </c>
+    </row>
+    <row r="2121" spans="1:4">
+      <c r="A2121" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2121">
+        <v>8</v>
+      </c>
+      <c r="C2121">
+        <v>4674.3</v>
+      </c>
+      <c r="D2121" t="s">
+        <v>2123</v>
+      </c>
+    </row>
+    <row r="2122" spans="1:4">
+      <c r="A2122" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2122">
+        <v>9</v>
+      </c>
+      <c r="C2122">
+        <v>4395.1</v>
+      </c>
+      <c r="D2122" t="s">
+        <v>2124</v>
+      </c>
+    </row>
+    <row r="2123" spans="1:4">
+      <c r="A2123" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2123">
+        <v>10</v>
+      </c>
+      <c r="C2123">
+        <v>4354.8</v>
+      </c>
+      <c r="D2123" t="s">
+        <v>2125</v>
+      </c>
+    </row>
+    <row r="2124" spans="1:4">
+      <c r="A2124" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2124">
+        <v>11</v>
+      </c>
+      <c r="C2124">
+        <v>4320.6</v>
+      </c>
+      <c r="D2124" t="s">
+        <v>2126</v>
+      </c>
+    </row>
+    <row r="2125" spans="1:4">
+      <c r="A2125" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2125">
+        <v>12</v>
+      </c>
+      <c r="C2125">
+        <v>4291.4</v>
+      </c>
+      <c r="D2125" t="s">
+        <v>2127</v>
+      </c>
+    </row>
+    <row r="2126" spans="1:4">
+      <c r="A2126" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2126">
+        <v>13</v>
+      </c>
+      <c r="C2126">
+        <v>4284</v>
+      </c>
+      <c r="D2126" t="s">
+        <v>2128</v>
+      </c>
+    </row>
+    <row r="2127" spans="1:4">
+      <c r="A2127" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2127">
+        <v>14</v>
+      </c>
+      <c r="C2127">
+        <v>4241.1</v>
+      </c>
+      <c r="D2127" t="s">
+        <v>2129</v>
+      </c>
+    </row>
+    <row r="2128" spans="1:4">
+      <c r="A2128" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2128">
+        <v>15</v>
+      </c>
+      <c r="C2128">
+        <v>4215.4</v>
+      </c>
+      <c r="D2128" t="s">
+        <v>2130</v>
+      </c>
+    </row>
+    <row r="2129" spans="1:4">
+      <c r="A2129" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2129">
+        <v>16</v>
+      </c>
+      <c r="C2129">
+        <v>4185.9</v>
+      </c>
+      <c r="D2129" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="2130" spans="1:4">
+      <c r="A2130" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2130">
+        <v>17</v>
+      </c>
+      <c r="C2130">
+        <v>4155.9</v>
+      </c>
+      <c r="D2130" t="s">
+        <v>2132</v>
+      </c>
+    </row>
+    <row r="2131" spans="1:4">
+      <c r="A2131" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2131">
+        <v>18</v>
+      </c>
+      <c r="C2131">
+        <v>4109.2</v>
+      </c>
+      <c r="D2131" t="s">
+        <v>2133</v>
+      </c>
+    </row>
+    <row r="2132" spans="1:4">
+      <c r="A2132" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2132">
+        <v>19</v>
+      </c>
+      <c r="C2132">
+        <v>4057.8</v>
+      </c>
+      <c r="D2132" t="s">
+        <v>2134</v>
+      </c>
+    </row>
+    <row r="2133" spans="1:4">
+      <c r="A2133" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2133">
+        <v>20</v>
+      </c>
+      <c r="C2133">
+        <v>4003.5</v>
+      </c>
+      <c r="D2133" t="s">
+        <v>2135</v>
+      </c>
+    </row>
+    <row r="2134" spans="1:4">
+      <c r="A2134" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2134">
+        <v>21</v>
+      </c>
+      <c r="C2134">
+        <v>3995.6</v>
+      </c>
+      <c r="D2134" t="s">
+        <v>2136</v>
+      </c>
+    </row>
+    <row r="2135" spans="1:4">
+      <c r="A2135" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2135">
+        <v>22</v>
+      </c>
+      <c r="C2135">
+        <v>3935.6</v>
+      </c>
+      <c r="D2135" t="s">
+        <v>2137</v>
+      </c>
+    </row>
+    <row r="2136" spans="1:4">
+      <c r="A2136" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2136">
+        <v>23</v>
+      </c>
+      <c r="C2136">
+        <v>3853.4</v>
+      </c>
+      <c r="D2136" t="s">
+        <v>2138</v>
+      </c>
+    </row>
+    <row r="2137" spans="1:4">
+      <c r="A2137" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2137">
+        <v>24</v>
+      </c>
+      <c r="C2137">
+        <v>3766.6</v>
+      </c>
+      <c r="D2137" t="s">
+        <v>2139</v>
+      </c>
+    </row>
+    <row r="2138" spans="1:4">
+      <c r="A2138" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2138">
+        <v>25</v>
+      </c>
+      <c r="C2138">
+        <v>3726.8</v>
+      </c>
+      <c r="D2138" t="s">
+        <v>2140</v>
+      </c>
+    </row>
+    <row r="2139" spans="1:4">
+      <c r="A2139" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2139">
+        <v>26</v>
+      </c>
+      <c r="C2139">
+        <v>3671.3</v>
+      </c>
+      <c r="D2139" t="s">
+        <v>2141</v>
+      </c>
+    </row>
+    <row r="2140" spans="1:4">
+      <c r="A2140" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2140">
+        <v>27</v>
+      </c>
+      <c r="C2140">
+        <v>3623.1</v>
+      </c>
+      <c r="D2140" t="s">
+        <v>2142</v>
+      </c>
+    </row>
+    <row r="2141" spans="1:4">
+      <c r="A2141" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2141">
+        <v>28</v>
+      </c>
+      <c r="C2141">
+        <v>3566.4</v>
+      </c>
+      <c r="D2141" t="s">
+        <v>2143</v>
+      </c>
+    </row>
+    <row r="2142" spans="1:4">
+      <c r="A2142" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2142">
+        <v>29</v>
+      </c>
+      <c r="C2142">
+        <v>3520.9</v>
+      </c>
+      <c r="D2142" t="s">
+        <v>2144</v>
+      </c>
+    </row>
+    <row r="2143" spans="1:4">
+      <c r="A2143" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2143">
+        <v>30</v>
+      </c>
+      <c r="C2143">
+        <v>3476.5</v>
+      </c>
+      <c r="D2143" t="s">
+        <v>2145</v>
+      </c>
+    </row>
+    <row r="2144" spans="1:4">
+      <c r="A2144" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2144">
+        <v>31</v>
+      </c>
+      <c r="C2144">
+        <v>3522.3</v>
+      </c>
+      <c r="D2144" t="s">
+        <v>2146</v>
+      </c>
+    </row>
+    <row r="2145" spans="1:4">
+      <c r="A2145" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2145">
+        <v>32</v>
+      </c>
+      <c r="C2145">
+        <v>3599.7</v>
+      </c>
+      <c r="D2145" t="s">
+        <v>2147</v>
+      </c>
+    </row>
+    <row r="2146" spans="1:4">
+      <c r="A2146" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2146">
+        <v>33</v>
+      </c>
+      <c r="C2146">
+        <v>3501.3</v>
+      </c>
+      <c r="D2146" t="s">
+        <v>2148</v>
+      </c>
+    </row>
+    <row r="2147" spans="1:4">
+      <c r="A2147" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2147">
+        <v>34</v>
+      </c>
+      <c r="C2147">
+        <v>3573</v>
+      </c>
+      <c r="D2147" t="s">
+        <v>2149</v>
+      </c>
+    </row>
+    <row r="2148" spans="1:4">
+      <c r="A2148" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2148">
+        <v>35</v>
+      </c>
+      <c r="C2148">
+        <v>3619.6</v>
+      </c>
+      <c r="D2148" t="s">
+        <v>2150</v>
+      </c>
+    </row>
+    <row r="2149" spans="1:4">
+      <c r="A2149" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2149">
+        <v>36</v>
+      </c>
+      <c r="C2149">
+        <v>3734.8</v>
+      </c>
+      <c r="D2149" t="s">
+        <v>2151</v>
+      </c>
+    </row>
+    <row r="2150" spans="1:4">
+      <c r="A2150" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2150">
+        <v>37</v>
+      </c>
+      <c r="C2150">
+        <v>3546.5</v>
+      </c>
+      <c r="D2150" t="s">
+        <v>2152</v>
+      </c>
+    </row>
+    <row r="2151" spans="1:4">
+      <c r="A2151" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2151">
+        <v>38</v>
+      </c>
+      <c r="C2151">
+        <v>3539.5</v>
+      </c>
+      <c r="D2151" t="s">
+        <v>2153</v>
+      </c>
+    </row>
+    <row r="2152" spans="1:4">
+      <c r="A2152" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2152">
+        <v>39</v>
+      </c>
+      <c r="C2152">
+        <v>3596.2</v>
+      </c>
+      <c r="D2152" t="s">
+        <v>2154</v>
+      </c>
+    </row>
+    <row r="2153" spans="1:4">
+      <c r="A2153" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2153">
+        <v>40</v>
+      </c>
+      <c r="C2153">
+        <v>3674.8</v>
+      </c>
+      <c r="D2153" t="s">
+        <v>2155</v>
+      </c>
+    </row>
+    <row r="2154" spans="1:4">
+      <c r="A2154" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2154">
+        <v>41</v>
+      </c>
+      <c r="C2154">
+        <v>3890.7</v>
+      </c>
+      <c r="D2154" t="s">
+        <v>2156</v>
+      </c>
+    </row>
+    <row r="2155" spans="1:4">
+      <c r="A2155" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2155">
+        <v>42</v>
+      </c>
+      <c r="C2155">
+        <v>3919.9</v>
+      </c>
+      <c r="D2155" t="s">
+        <v>2157</v>
+      </c>
+    </row>
+    <row r="2156" spans="1:4">
+      <c r="A2156" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2156">
+        <v>43</v>
+      </c>
+      <c r="C2156">
+        <v>3948.3</v>
+      </c>
+      <c r="D2156" t="s">
+        <v>2158</v>
+      </c>
+    </row>
+    <row r="2157" spans="1:4">
+      <c r="A2157" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2157">
+        <v>44</v>
+      </c>
+      <c r="C2157">
+        <v>3977.5</v>
+      </c>
+      <c r="D2157" t="s">
+        <v>2159</v>
+      </c>
+    </row>
+    <row r="2158" spans="1:4">
+      <c r="A2158" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2158">
+        <v>45</v>
+      </c>
+      <c r="C2158">
+        <v>3968</v>
+      </c>
+      <c r="D2158" t="s">
+        <v>2160</v>
+      </c>
+    </row>
+    <row r="2159" spans="1:4">
+      <c r="A2159" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2159">
+        <v>46</v>
+      </c>
+      <c r="C2159">
+        <v>3953.3</v>
+      </c>
+      <c r="D2159" t="s">
+        <v>2161</v>
+      </c>
+    </row>
+    <row r="2160" spans="1:4">
+      <c r="A2160" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2160">
+        <v>47</v>
+      </c>
+      <c r="C2160">
+        <v>3934.1</v>
+      </c>
+      <c r="D2160" t="s">
+        <v>2162</v>
+      </c>
+    </row>
+    <row r="2161" spans="1:4">
+      <c r="A2161" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2161">
+        <v>48</v>
+      </c>
+      <c r="C2161">
+        <v>3960.1</v>
+      </c>
+      <c r="D2161" t="s">
+        <v>2163</v>
+      </c>
+    </row>
+    <row r="2162" spans="1:4">
+      <c r="A2162" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2162">
+        <v>49</v>
+      </c>
+      <c r="C2162">
+        <v>3776.1</v>
+      </c>
+      <c r="D2162" t="s">
+        <v>2164</v>
+      </c>
+    </row>
+    <row r="2163" spans="1:4">
+      <c r="A2163" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2163">
+        <v>50</v>
+      </c>
+      <c r="C2163">
+        <v>3768.2</v>
+      </c>
+      <c r="D2163" t="s">
+        <v>2165</v>
+      </c>
+    </row>
+    <row r="2164" spans="1:4">
+      <c r="A2164" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2164">
+        <v>51</v>
+      </c>
+      <c r="C2164">
+        <v>3745.5</v>
+      </c>
+      <c r="D2164" t="s">
+        <v>2166</v>
+      </c>
+    </row>
+    <row r="2165" spans="1:4">
+      <c r="A2165" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2165">
+        <v>52</v>
+      </c>
+      <c r="C2165">
+        <v>3740</v>
+      </c>
+      <c r="D2165" t="s">
+        <v>2167</v>
+      </c>
+    </row>
+    <row r="2166" spans="1:4">
+      <c r="A2166" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2166">
+        <v>53</v>
+      </c>
+      <c r="C2166">
+        <v>3697.1</v>
+      </c>
+      <c r="D2166" t="s">
+        <v>2168</v>
+      </c>
+    </row>
+    <row r="2167" spans="1:4">
+      <c r="A2167" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2167">
+        <v>54</v>
+      </c>
+      <c r="C2167">
+        <v>3668.4</v>
+      </c>
+      <c r="D2167" t="s">
+        <v>2169</v>
+      </c>
+    </row>
+    <row r="2168" spans="1:4">
+      <c r="A2168" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2168">
+        <v>55</v>
+      </c>
+      <c r="C2168">
+        <v>3673.8</v>
+      </c>
+      <c r="D2168" t="s">
+        <v>2170</v>
+      </c>
+    </row>
+    <row r="2169" spans="1:4">
+      <c r="A2169" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2169">
+        <v>56</v>
+      </c>
+      <c r="C2169">
+        <v>3678.2</v>
+      </c>
+      <c r="D2169" t="s">
+        <v>2171</v>
+      </c>
+    </row>
+    <row r="2170" spans="1:4">
+      <c r="A2170" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2170">
+        <v>57</v>
+      </c>
+      <c r="C2170">
+        <v>3730.2</v>
+      </c>
+      <c r="D2170" t="s">
+        <v>2172</v>
+      </c>
+    </row>
+    <row r="2171" spans="1:4">
+      <c r="A2171" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2171">
+        <v>58</v>
+      </c>
+      <c r="C2171">
+        <v>3717</v>
+      </c>
+      <c r="D2171" t="s">
+        <v>2173</v>
+      </c>
+    </row>
+    <row r="2172" spans="1:4">
+      <c r="A2172" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2172">
+        <v>59</v>
+      </c>
+      <c r="C2172">
+        <v>3728</v>
+      </c>
+      <c r="D2172" t="s">
+        <v>2174</v>
+      </c>
+    </row>
+    <row r="2173" spans="1:4">
+      <c r="A2173" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2173">
+        <v>60</v>
+      </c>
+      <c r="C2173">
+        <v>3775.1</v>
+      </c>
+      <c r="D2173" t="s">
+        <v>2175</v>
+      </c>
+    </row>
+    <row r="2174" spans="1:4">
+      <c r="A2174" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2174">
+        <v>61</v>
+      </c>
+      <c r="C2174">
+        <v>3821.2</v>
+      </c>
+      <c r="D2174" t="s">
+        <v>2176</v>
+      </c>
+    </row>
+    <row r="2175" spans="1:4">
+      <c r="A2175" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2175">
+        <v>62</v>
+      </c>
+      <c r="C2175">
+        <v>3796.4</v>
+      </c>
+      <c r="D2175" t="s">
+        <v>2177</v>
+      </c>
+    </row>
+    <row r="2176" spans="1:4">
+      <c r="A2176" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2176">
+        <v>63</v>
+      </c>
+      <c r="C2176">
+        <v>3771.2</v>
+      </c>
+      <c r="D2176" t="s">
+        <v>2178</v>
+      </c>
+    </row>
+    <row r="2177" spans="1:4">
+      <c r="A2177" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2177">
+        <v>64</v>
+      </c>
+      <c r="C2177">
+        <v>3790.3</v>
+      </c>
+      <c r="D2177" t="s">
+        <v>2179</v>
+      </c>
+    </row>
+    <row r="2178" spans="1:4">
+      <c r="A2178" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2178">
+        <v>65</v>
+      </c>
+      <c r="C2178">
+        <v>3819.1</v>
+      </c>
+      <c r="D2178" t="s">
+        <v>2180</v>
+      </c>
+    </row>
+    <row r="2179" spans="1:4">
+      <c r="A2179" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2179">
+        <v>66</v>
+      </c>
+      <c r="C2179">
+        <v>3780.3</v>
+      </c>
+      <c r="D2179" t="s">
+        <v>2181</v>
+      </c>
+    </row>
+    <row r="2180" spans="1:4">
+      <c r="A2180" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2180">
+        <v>67</v>
+      </c>
+      <c r="C2180">
+        <v>3769.2</v>
+      </c>
+      <c r="D2180" t="s">
+        <v>2182</v>
+      </c>
+    </row>
+    <row r="2181" spans="1:4">
+      <c r="A2181" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2181">
+        <v>68</v>
+      </c>
+      <c r="C2181">
+        <v>3740.9</v>
+      </c>
+      <c r="D2181" t="s">
+        <v>2183</v>
+      </c>
+    </row>
+    <row r="2182" spans="1:4">
+      <c r="A2182" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2182">
+        <v>69</v>
+      </c>
+      <c r="C2182">
+        <v>3663.4</v>
+      </c>
+      <c r="D2182" t="s">
+        <v>2184</v>
+      </c>
+    </row>
+    <row r="2183" spans="1:4">
+      <c r="A2183" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2183">
+        <v>70</v>
+      </c>
+      <c r="C2183">
+        <v>3608.8</v>
+      </c>
+      <c r="D2183" t="s">
+        <v>2185</v>
+      </c>
+    </row>
+    <row r="2184" spans="1:4">
+      <c r="A2184" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2184">
+        <v>71</v>
+      </c>
+      <c r="C2184">
+        <v>3584.3</v>
+      </c>
+      <c r="D2184" t="s">
+        <v>2186</v>
+      </c>
+    </row>
+    <row r="2185" spans="1:4">
+      <c r="A2185" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2185">
+        <v>72</v>
+      </c>
+      <c r="C2185">
+        <v>3538.9</v>
+      </c>
+      <c r="D2185" t="s">
+        <v>2187</v>
+      </c>
+    </row>
+    <row r="2186" spans="1:4">
+      <c r="A2186" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2186">
+        <v>73</v>
+      </c>
+      <c r="C2186">
+        <v>4144.8</v>
+      </c>
+      <c r="D2186" t="s">
+        <v>2188</v>
+      </c>
+    </row>
+    <row r="2187" spans="1:4">
+      <c r="A2187" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2187">
+        <v>74</v>
+      </c>
+      <c r="C2187">
+        <v>4085</v>
+      </c>
+      <c r="D2187" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="2188" spans="1:4">
+      <c r="A2188" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2188">
+        <v>75</v>
+      </c>
+      <c r="C2188">
+        <v>4046.5</v>
+      </c>
+      <c r="D2188" t="s">
+        <v>2190</v>
+      </c>
+    </row>
+    <row r="2189" spans="1:4">
+      <c r="A2189" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2189">
+        <v>76</v>
+      </c>
+      <c r="C2189">
+        <v>4045.9</v>
+      </c>
+      <c r="D2189" t="s">
+        <v>2191</v>
+      </c>
+    </row>
+    <row r="2190" spans="1:4">
+      <c r="A2190" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2190">
+        <v>77</v>
+      </c>
+      <c r="C2190">
+        <v>3971.2</v>
+      </c>
+      <c r="D2190" t="s">
+        <v>2192</v>
+      </c>
+    </row>
+    <row r="2191" spans="1:4">
+      <c r="A2191" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2191">
+        <v>78</v>
+      </c>
+      <c r="C2191">
+        <v>3979.7</v>
+      </c>
+      <c r="D2191" t="s">
+        <v>2193</v>
+      </c>
+    </row>
+    <row r="2192" spans="1:4">
+      <c r="A2192" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2192">
+        <v>79</v>
+      </c>
+      <c r="C2192">
+        <v>3906.6</v>
+      </c>
+      <c r="D2192" t="s">
+        <v>2194</v>
+      </c>
+    </row>
+    <row r="2193" spans="1:4">
+      <c r="A2193" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2193">
+        <v>80</v>
+      </c>
+      <c r="C2193">
+        <v>3879.2</v>
+      </c>
+      <c r="D2193" t="s">
+        <v>2195</v>
+      </c>
+    </row>
+    <row r="2194" spans="1:4">
+      <c r="A2194" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2194">
+        <v>81</v>
+      </c>
+      <c r="C2194">
+        <v>3925.1</v>
+      </c>
+      <c r="D2194" t="s">
+        <v>2196</v>
+      </c>
+    </row>
+    <row r="2195" spans="1:4">
+      <c r="A2195" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2195">
+        <v>82</v>
+      </c>
+      <c r="C2195">
+        <v>3946.2</v>
+      </c>
+      <c r="D2195" t="s">
+        <v>2197</v>
+      </c>
+    </row>
+    <row r="2196" spans="1:4">
+      <c r="A2196" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2196">
+        <v>83</v>
+      </c>
+      <c r="C2196">
+        <v>3988.5</v>
+      </c>
+      <c r="D2196" t="s">
+        <v>2198</v>
+      </c>
+    </row>
+    <row r="2197" spans="1:4">
+      <c r="A2197" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2197">
+        <v>84</v>
+      </c>
+      <c r="C2197">
+        <v>4030.7</v>
+      </c>
+      <c r="D2197" t="s">
+        <v>2199</v>
+      </c>
+    </row>
+    <row r="2198" spans="1:4">
+      <c r="A2198" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2198">
+        <v>85</v>
+      </c>
+      <c r="C2198">
+        <v>4134.6</v>
+      </c>
+      <c r="D2198" t="s">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="2199" spans="1:4">
+      <c r="A2199" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2199">
+        <v>86</v>
+      </c>
+      <c r="C2199">
+        <v>4172.3</v>
+      </c>
+      <c r="D2199" t="s">
+        <v>2201</v>
+      </c>
+    </row>
+    <row r="2200" spans="1:4">
+      <c r="A2200" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2200">
+        <v>87</v>
+      </c>
+      <c r="C2200">
+        <v>4234.8</v>
+      </c>
+      <c r="D2200" t="s">
+        <v>2202</v>
+      </c>
+    </row>
+    <row r="2201" spans="1:4">
+      <c r="A2201" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2201">
+        <v>88</v>
+      </c>
+      <c r="C2201">
+        <v>4213.5</v>
+      </c>
+      <c r="D2201" t="s">
+        <v>2203</v>
+      </c>
+    </row>
+    <row r="2202" spans="1:4">
+      <c r="A2202" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2202">
+        <v>89</v>
+      </c>
+      <c r="C2202">
+        <v>4051.9</v>
+      </c>
+      <c r="D2202" t="s">
+        <v>2204</v>
+      </c>
+    </row>
+    <row r="2203" spans="1:4">
+      <c r="A2203" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2203">
+        <v>90</v>
+      </c>
+      <c r="C2203">
+        <v>4043.7</v>
+      </c>
+      <c r="D2203" t="s">
+        <v>2205</v>
+      </c>
+    </row>
+    <row r="2204" spans="1:4">
+      <c r="A2204" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2204">
+        <v>91</v>
+      </c>
+      <c r="C2204">
+        <v>4040.4</v>
+      </c>
+      <c r="D2204" t="s">
+        <v>2206</v>
+      </c>
+    </row>
+    <row r="2205" spans="1:4">
+      <c r="A2205" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2205">
+        <v>92</v>
+      </c>
+      <c r="C2205">
+        <v>4103.1</v>
+      </c>
+      <c r="D2205" t="s">
+        <v>2207</v>
+      </c>
+    </row>
+    <row r="2206" spans="1:4">
+      <c r="A2206" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2206">
+        <v>93</v>
+      </c>
+      <c r="C2206">
+        <v>4049.7</v>
+      </c>
+      <c r="D2206" t="s">
+        <v>2208</v>
+      </c>
+    </row>
+    <row r="2207" spans="1:4">
+      <c r="A2207" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2207">
+        <v>94</v>
+      </c>
+      <c r="C2207">
+        <v>4005.6</v>
+      </c>
+      <c r="D2207" t="s">
+        <v>2209</v>
+      </c>
+    </row>
+    <row r="2208" spans="1:4">
+      <c r="A2208" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2208">
+        <v>95</v>
+      </c>
+      <c r="C2208">
+        <v>4010.6</v>
+      </c>
+      <c r="D2208" t="s">
+        <v>2210</v>
+      </c>
+    </row>
+    <row r="2209" spans="1:4">
+      <c r="A2209" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2209">
+        <v>96</v>
+      </c>
+      <c r="C2209">
+        <v>4042.5</v>
+      </c>
+      <c r="D2209" t="s">
+        <v>2211</v>
+      </c>
+    </row>
+    <row r="2210" spans="1:4">
+      <c r="A2210" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2210">
+        <v>1</v>
+      </c>
+      <c r="C2210">
+        <v>5256</v>
+      </c>
+      <c r="D2210" t="s">
+        <v>2212</v>
+      </c>
+    </row>
+    <row r="2211" spans="1:4">
+      <c r="A2211" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2211">
+        <v>2</v>
+      </c>
+      <c r="C2211">
+        <v>5196.2</v>
+      </c>
+      <c r="D2211" t="s">
+        <v>2213</v>
+      </c>
+    </row>
+    <row r="2212" spans="1:4">
+      <c r="A2212" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2212">
+        <v>3</v>
+      </c>
+      <c r="C2212">
+        <v>5069.7</v>
+      </c>
+      <c r="D2212" t="s">
+        <v>2214</v>
+      </c>
+    </row>
+    <row r="2213" spans="1:4">
+      <c r="A2213" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2213">
+        <v>4</v>
+      </c>
+      <c r="C2213">
+        <v>4947.7</v>
+      </c>
+      <c r="D2213" t="s">
+        <v>2215</v>
+      </c>
+    </row>
+    <row r="2214" spans="1:4">
+      <c r="A2214" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2214">
+        <v>5</v>
+      </c>
+      <c r="C2214">
+        <v>4483.4</v>
+      </c>
+      <c r="D2214" t="s">
+        <v>2216</v>
+      </c>
+    </row>
+    <row r="2215" spans="1:4">
+      <c r="A2215" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2215">
+        <v>6</v>
+      </c>
+      <c r="C2215">
+        <v>4438.2</v>
+      </c>
+      <c r="D2215" t="s">
+        <v>2217</v>
+      </c>
+    </row>
+    <row r="2216" spans="1:4">
+      <c r="A2216" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2216">
+        <v>7</v>
+      </c>
+      <c r="C2216">
+        <v>4389.8</v>
+      </c>
+      <c r="D2216" t="s">
+        <v>2218</v>
+      </c>
+    </row>
+    <row r="2217" spans="1:4">
+      <c r="A2217" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2217">
+        <v>8</v>
+      </c>
+      <c r="C2217">
+        <v>4344.3</v>
+      </c>
+      <c r="D2217" t="s">
+        <v>2219</v>
+      </c>
+    </row>
+    <row r="2218" spans="1:4">
+      <c r="A2218" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2218">
+        <v>9</v>
+      </c>
+      <c r="C2218">
+        <v>4055.1</v>
+      </c>
+      <c r="D2218" t="s">
+        <v>2220</v>
+      </c>
+    </row>
+    <row r="2219" spans="1:4">
+      <c r="A2219" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2219">
+        <v>10</v>
+      </c>
+      <c r="C2219">
+        <v>4014.8</v>
+      </c>
+      <c r="D2219" t="s">
+        <v>2221</v>
+      </c>
+    </row>
+    <row r="2220" spans="1:4">
+      <c r="A2220" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2220">
+        <v>11</v>
+      </c>
+      <c r="C2220">
+        <v>3980.6</v>
+      </c>
+      <c r="D2220" t="s">
+        <v>2222</v>
+      </c>
+    </row>
+    <row r="2221" spans="1:4">
+      <c r="A2221" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2221">
+        <v>12</v>
+      </c>
+      <c r="C2221">
+        <v>3961.4</v>
+      </c>
+      <c r="D2221" t="s">
+        <v>2223</v>
+      </c>
+    </row>
+    <row r="2222" spans="1:4">
+      <c r="A2222" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2222">
+        <v>13</v>
+      </c>
+      <c r="C2222">
+        <v>3964</v>
+      </c>
+      <c r="D2222" t="s">
+        <v>2224</v>
+      </c>
+    </row>
+    <row r="2223" spans="1:4">
+      <c r="A2223" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2223">
+        <v>14</v>
+      </c>
+      <c r="C2223">
+        <v>3931.1</v>
+      </c>
+      <c r="D2223" t="s">
+        <v>2225</v>
+      </c>
+    </row>
+    <row r="2224" spans="1:4">
+      <c r="A2224" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2224">
+        <v>15</v>
+      </c>
+      <c r="C2224">
+        <v>3895.4</v>
+      </c>
+      <c r="D2224" t="s">
+        <v>2226</v>
+      </c>
+    </row>
+    <row r="2225" spans="1:4">
+      <c r="A2225" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2225">
+        <v>16</v>
+      </c>
+      <c r="C2225">
+        <v>3865.9</v>
+      </c>
+      <c r="D2225" t="s">
+        <v>2227</v>
+      </c>
+    </row>
+    <row r="2226" spans="1:4">
+      <c r="A2226" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2226">
+        <v>17</v>
+      </c>
+      <c r="C2226">
+        <v>3845.9</v>
+      </c>
+      <c r="D2226" t="s">
+        <v>2228</v>
+      </c>
+    </row>
+    <row r="2227" spans="1:4">
+      <c r="A2227" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2227">
+        <v>18</v>
+      </c>
+      <c r="C2227">
+        <v>3789.2</v>
+      </c>
+      <c r="D2227" t="s">
+        <v>2229</v>
+      </c>
+    </row>
+    <row r="2228" spans="1:4">
+      <c r="A2228" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2228">
+        <v>19</v>
+      </c>
+      <c r="C2228">
+        <v>3717.8</v>
+      </c>
+      <c r="D2228" t="s">
+        <v>2230</v>
+      </c>
+    </row>
+    <row r="2229" spans="1:4">
+      <c r="A2229" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2229">
+        <v>20</v>
+      </c>
+      <c r="C2229">
+        <v>3633.5</v>
+      </c>
+      <c r="D2229" t="s">
+        <v>2231</v>
+      </c>
+    </row>
+    <row r="2230" spans="1:4">
+      <c r="A2230" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2230">
+        <v>21</v>
+      </c>
+      <c r="C2230">
+        <v>3605.6</v>
+      </c>
+      <c r="D2230" t="s">
+        <v>2232</v>
+      </c>
+    </row>
+    <row r="2231" spans="1:4">
+      <c r="A2231" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2231">
+        <v>22</v>
+      </c>
+      <c r="C2231">
+        <v>3525.6</v>
+      </c>
+      <c r="D2231" t="s">
+        <v>2233</v>
+      </c>
+    </row>
+    <row r="2232" spans="1:4">
+      <c r="A2232" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2232">
+        <v>23</v>
+      </c>
+      <c r="C2232">
+        <v>3433.4</v>
+      </c>
+      <c r="D2232" t="s">
+        <v>2234</v>
+      </c>
+    </row>
+    <row r="2233" spans="1:4">
+      <c r="A2233" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2233">
+        <v>24</v>
+      </c>
+      <c r="C2233">
+        <v>3346.6</v>
+      </c>
+      <c r="D2233" t="s">
+        <v>2235</v>
+      </c>
+    </row>
+    <row r="2234" spans="1:4">
+      <c r="A2234" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2234">
+        <v>25</v>
+      </c>
+      <c r="C2234">
+        <v>3316.8</v>
+      </c>
+      <c r="D2234" t="s">
+        <v>2236</v>
+      </c>
+    </row>
+    <row r="2235" spans="1:4">
+      <c r="A2235" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2235">
+        <v>26</v>
+      </c>
+      <c r="C2235">
+        <v>3251.3</v>
+      </c>
+      <c r="D2235" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2236" spans="1:4">
+      <c r="A2236" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2236">
+        <v>27</v>
+      </c>
+      <c r="C2236">
+        <v>3173.1</v>
+      </c>
+      <c r="D2236" t="s">
+        <v>2238</v>
+      </c>
+    </row>
+    <row r="2237" spans="1:4">
+      <c r="A2237" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2237">
+        <v>28</v>
+      </c>
+      <c r="C2237">
+        <v>3056.4</v>
+      </c>
+      <c r="D2237" t="s">
+        <v>2239</v>
+      </c>
+    </row>
+    <row r="2238" spans="1:4">
+      <c r="A2238" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2238">
+        <v>29</v>
+      </c>
+      <c r="C2238">
+        <v>2950.9</v>
+      </c>
+      <c r="D2238" t="s">
+        <v>2240</v>
+      </c>
+    </row>
+    <row r="2239" spans="1:4">
+      <c r="A2239" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2239">
+        <v>30</v>
+      </c>
+      <c r="C2239">
+        <v>2846.5</v>
+      </c>
+      <c r="D2239" t="s">
+        <v>2241</v>
+      </c>
+    </row>
+    <row r="2240" spans="1:4">
+      <c r="A2240" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2240">
+        <v>31</v>
+      </c>
+      <c r="C2240">
+        <v>2842.3</v>
+      </c>
+      <c r="D2240" t="s">
+        <v>2242</v>
+      </c>
+    </row>
+    <row r="2241" spans="1:4">
+      <c r="A2241" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2241">
+        <v>32</v>
+      </c>
+      <c r="C2241">
+        <v>2879.7</v>
+      </c>
+      <c r="D2241" t="s">
+        <v>2243</v>
+      </c>
+    </row>
+    <row r="2242" spans="1:4">
+      <c r="A2242" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2242">
+        <v>33</v>
+      </c>
+      <c r="C2242">
+        <v>2741.3</v>
+      </c>
+      <c r="D2242" t="s">
+        <v>2244</v>
+      </c>
+    </row>
+    <row r="2243" spans="1:4">
+      <c r="A2243" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2243">
+        <v>34</v>
+      </c>
+      <c r="C2243">
+        <v>2783</v>
+      </c>
+      <c r="D2243" t="s">
+        <v>2245</v>
+      </c>
+    </row>
+    <row r="2244" spans="1:4">
+      <c r="A2244" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2244">
+        <v>35</v>
+      </c>
+      <c r="C2244">
+        <v>2809.6</v>
+      </c>
+      <c r="D2244" t="s">
+        <v>2246</v>
+      </c>
+    </row>
+    <row r="2245" spans="1:4">
+      <c r="A2245" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2245">
+        <v>36</v>
+      </c>
+      <c r="C2245">
+        <v>2904.8</v>
+      </c>
+      <c r="D2245" t="s">
+        <v>2247</v>
+      </c>
+    </row>
+    <row r="2246" spans="1:4">
+      <c r="A2246" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2246">
+        <v>37</v>
+      </c>
+      <c r="C2246">
+        <v>2706.5</v>
+      </c>
+      <c r="D2246" t="s">
+        <v>2248</v>
+      </c>
+    </row>
+    <row r="2247" spans="1:4">
+      <c r="A2247" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2247">
+        <v>38</v>
+      </c>
+      <c r="C2247">
+        <v>2679.5</v>
+      </c>
+      <c r="D2247" t="s">
+        <v>2249</v>
+      </c>
+    </row>
+    <row r="2248" spans="1:4">
+      <c r="A2248" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2248">
+        <v>39</v>
+      </c>
+      <c r="C2248">
+        <v>2716.2</v>
+      </c>
+      <c r="D2248" t="s">
+        <v>2250</v>
+      </c>
+    </row>
+    <row r="2249" spans="1:4">
+      <c r="A2249" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2249">
+        <v>40</v>
+      </c>
+      <c r="C2249">
+        <v>2794.8</v>
+      </c>
+      <c r="D2249" t="s">
+        <v>2251</v>
+      </c>
+    </row>
+    <row r="2250" spans="1:4">
+      <c r="A2250" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2250">
+        <v>41</v>
+      </c>
+      <c r="C2250">
+        <v>2990.7</v>
+      </c>
+      <c r="D2250" t="s">
+        <v>2252</v>
+      </c>
+    </row>
+    <row r="2251" spans="1:4">
+      <c r="A2251" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2251">
+        <v>42</v>
+      </c>
+      <c r="C2251">
+        <v>3009.9</v>
+      </c>
+      <c r="D2251" t="s">
+        <v>2253</v>
+      </c>
+    </row>
+    <row r="2252" spans="1:4">
+      <c r="A2252" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2252">
+        <v>43</v>
+      </c>
+      <c r="C2252">
+        <v>3048.3</v>
+      </c>
+      <c r="D2252" t="s">
+        <v>2254</v>
+      </c>
+    </row>
+    <row r="2253" spans="1:4">
+      <c r="A2253" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2253">
+        <v>44</v>
+      </c>
+      <c r="C2253">
+        <v>3077.5</v>
+      </c>
+      <c r="D2253" t="s">
+        <v>2255</v>
+      </c>
+    </row>
+    <row r="2254" spans="1:4">
+      <c r="A2254" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2254">
+        <v>45</v>
+      </c>
+      <c r="C2254">
+        <v>3078</v>
+      </c>
+      <c r="D2254" t="s">
+        <v>2256</v>
+      </c>
+    </row>
+    <row r="2255" spans="1:4">
+      <c r="A2255" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2255">
+        <v>46</v>
+      </c>
+      <c r="C2255">
+        <v>3073.3</v>
+      </c>
+      <c r="D2255" t="s">
+        <v>2257</v>
+      </c>
+    </row>
+    <row r="2256" spans="1:4">
+      <c r="A2256" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2256">
+        <v>47</v>
+      </c>
+      <c r="C2256">
+        <v>3064.1</v>
+      </c>
+      <c r="D2256" t="s">
+        <v>2258</v>
+      </c>
+    </row>
+    <row r="2257" spans="1:4">
+      <c r="A2257" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2257">
+        <v>48</v>
+      </c>
+      <c r="C2257">
+        <v>3100.1</v>
+      </c>
+      <c r="D2257" t="s">
+        <v>2259</v>
+      </c>
+    </row>
+    <row r="2258" spans="1:4">
+      <c r="A2258" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2258">
+        <v>49</v>
+      </c>
+      <c r="C2258">
+        <v>2916.1</v>
+      </c>
+      <c r="D2258" t="s">
+        <v>2260</v>
+      </c>
+    </row>
+    <row r="2259" spans="1:4">
+      <c r="A2259" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2259">
+        <v>50</v>
+      </c>
+      <c r="C2259">
+        <v>2908.2</v>
+      </c>
+      <c r="D2259" t="s">
+        <v>2261</v>
+      </c>
+    </row>
+    <row r="2260" spans="1:4">
+      <c r="A2260" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2260">
+        <v>51</v>
+      </c>
+      <c r="C2260">
+        <v>2905.5</v>
+      </c>
+      <c r="D2260" t="s">
+        <v>2262</v>
+      </c>
+    </row>
+    <row r="2261" spans="1:4">
+      <c r="A2261" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2261">
+        <v>52</v>
+      </c>
+      <c r="C2261">
+        <v>2920</v>
+      </c>
+      <c r="D2261" t="s">
+        <v>2263</v>
+      </c>
+    </row>
+    <row r="2262" spans="1:4">
+      <c r="A2262" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2262">
+        <v>53</v>
+      </c>
+      <c r="C2262">
+        <v>2897.1</v>
+      </c>
+      <c r="D2262" t="s">
+        <v>2264</v>
+      </c>
+    </row>
+    <row r="2263" spans="1:4">
+      <c r="A2263" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2263">
+        <v>54</v>
+      </c>
+      <c r="C2263">
+        <v>2878.4</v>
+      </c>
+      <c r="D2263" t="s">
+        <v>2265</v>
+      </c>
+    </row>
+    <row r="2264" spans="1:4">
+      <c r="A2264" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2264">
+        <v>55</v>
+      </c>
+      <c r="C2264">
+        <v>2903.8</v>
+      </c>
+      <c r="D2264" t="s">
+        <v>2266</v>
+      </c>
+    </row>
+    <row r="2265" spans="1:4">
+      <c r="A2265" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2265">
+        <v>56</v>
+      </c>
+      <c r="C2265">
+        <v>2908.2</v>
+      </c>
+      <c r="D2265" t="s">
+        <v>2267</v>
+      </c>
+    </row>
+    <row r="2266" spans="1:4">
+      <c r="A2266" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2266">
+        <v>57</v>
+      </c>
+      <c r="C2266">
+        <v>2950.2</v>
+      </c>
+      <c r="D2266" t="s">
+        <v>2268</v>
+      </c>
+    </row>
+    <row r="2267" spans="1:4">
+      <c r="A2267" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2267">
+        <v>58</v>
+      </c>
+      <c r="C2267">
+        <v>2937</v>
+      </c>
+      <c r="D2267" t="s">
+        <v>2269</v>
+      </c>
+    </row>
+    <row r="2268" spans="1:4">
+      <c r="A2268" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2268">
+        <v>59</v>
+      </c>
+      <c r="C2268">
+        <v>2948</v>
+      </c>
+      <c r="D2268" t="s">
+        <v>2270</v>
+      </c>
+    </row>
+    <row r="2269" spans="1:4">
+      <c r="A2269" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2269">
+        <v>60</v>
+      </c>
+      <c r="C2269">
+        <v>3005.1</v>
+      </c>
+      <c r="D2269" t="s">
+        <v>2271</v>
+      </c>
+    </row>
+    <row r="2270" spans="1:4">
+      <c r="A2270" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2270">
+        <v>61</v>
+      </c>
+      <c r="C2270">
+        <v>3071.2</v>
+      </c>
+      <c r="D2270" t="s">
+        <v>2272</v>
+      </c>
+    </row>
+    <row r="2271" spans="1:4">
+      <c r="A2271" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2271">
+        <v>62</v>
+      </c>
+      <c r="C2271">
+        <v>3056.4</v>
+      </c>
+      <c r="D2271" t="s">
+        <v>2273</v>
+      </c>
+    </row>
+    <row r="2272" spans="1:4">
+      <c r="A2272" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2272">
+        <v>63</v>
+      </c>
+      <c r="C2272">
+        <v>3061.2</v>
+      </c>
+      <c r="D2272" t="s">
+        <v>2274</v>
+      </c>
+    </row>
+    <row r="2273" spans="1:4">
+      <c r="A2273" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2273">
+        <v>64</v>
+      </c>
+      <c r="C2273">
+        <v>3100.3</v>
+      </c>
+      <c r="D2273" t="s">
+        <v>2275</v>
+      </c>
+    </row>
+    <row r="2274" spans="1:4">
+      <c r="A2274" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2274">
+        <v>65</v>
+      </c>
+      <c r="C2274">
+        <v>3149.1</v>
+      </c>
+      <c r="D2274" t="s">
+        <v>2276</v>
+      </c>
+    </row>
+    <row r="2275" spans="1:4">
+      <c r="A2275" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2275">
+        <v>66</v>
+      </c>
+      <c r="C2275">
+        <v>3130.3</v>
+      </c>
+      <c r="D2275" t="s">
+        <v>2277</v>
+      </c>
+    </row>
+    <row r="2276" spans="1:4">
+      <c r="A2276" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2276">
+        <v>67</v>
+      </c>
+      <c r="C2276">
+        <v>3129.2</v>
+      </c>
+      <c r="D2276" t="s">
+        <v>2278</v>
+      </c>
+    </row>
+    <row r="2277" spans="1:4">
+      <c r="A2277" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2277">
+        <v>68</v>
+      </c>
+      <c r="C2277">
+        <v>3110.9</v>
+      </c>
+      <c r="D2277" t="s">
+        <v>2279</v>
+      </c>
+    </row>
+    <row r="2278" spans="1:4">
+      <c r="A2278" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2278">
+        <v>69</v>
+      </c>
+      <c r="C2278">
+        <v>3023.4</v>
+      </c>
+      <c r="D2278" t="s">
+        <v>2280</v>
+      </c>
+    </row>
+    <row r="2279" spans="1:4">
+      <c r="A2279" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2279">
+        <v>70</v>
+      </c>
+      <c r="C2279">
+        <v>2978.8</v>
+      </c>
+      <c r="D2279" t="s">
+        <v>2281</v>
+      </c>
+    </row>
+    <row r="2280" spans="1:4">
+      <c r="A2280" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2280">
+        <v>71</v>
+      </c>
+      <c r="C2280">
+        <v>2954.3</v>
+      </c>
+      <c r="D2280" t="s">
+        <v>2282</v>
+      </c>
+    </row>
+    <row r="2281" spans="1:4">
+      <c r="A2281" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2281">
+        <v>72</v>
+      </c>
+      <c r="C2281">
+        <v>2928.9</v>
+      </c>
+      <c r="D2281" t="s">
+        <v>2283</v>
+      </c>
+    </row>
+    <row r="2282" spans="1:4">
+      <c r="A2282" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2282">
+        <v>73</v>
+      </c>
+      <c r="C2282">
+        <v>3554.8</v>
+      </c>
+      <c r="D2282" t="s">
+        <v>2284</v>
+      </c>
+    </row>
+    <row r="2283" spans="1:4">
+      <c r="A2283" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2283">
+        <v>74</v>
+      </c>
+      <c r="C2283">
+        <v>3505</v>
+      </c>
+      <c r="D2283" t="s">
+        <v>2285</v>
+      </c>
+    </row>
+    <row r="2284" spans="1:4">
+      <c r="A2284" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2284">
+        <v>75</v>
+      </c>
+      <c r="C2284">
+        <v>3496.5</v>
+      </c>
+      <c r="D2284" t="s">
+        <v>2286</v>
+      </c>
+    </row>
+    <row r="2285" spans="1:4">
+      <c r="A2285" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2285">
+        <v>76</v>
+      </c>
+      <c r="C2285">
+        <v>3505.9</v>
+      </c>
+      <c r="D2285" t="s">
+        <v>2287</v>
+      </c>
+    </row>
+    <row r="2286" spans="1:4">
+      <c r="A2286" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2286">
+        <v>77</v>
+      </c>
+      <c r="C2286">
+        <v>3451.2</v>
+      </c>
+      <c r="D2286" t="s">
+        <v>2288</v>
+      </c>
+    </row>
+    <row r="2287" spans="1:4">
+      <c r="A2287" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2287">
+        <v>78</v>
+      </c>
+      <c r="C2287">
+        <v>3469.7</v>
+      </c>
+      <c r="D2287" t="s">
+        <v>2289</v>
+      </c>
+    </row>
+    <row r="2288" spans="1:4">
+      <c r="A2288" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2288">
+        <v>79</v>
+      </c>
+      <c r="C2288">
+        <v>3406.6</v>
+      </c>
+      <c r="D2288" t="s">
+        <v>2290</v>
+      </c>
+    </row>
+    <row r="2289" spans="1:4">
+      <c r="A2289" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2289">
+        <v>80</v>
+      </c>
+      <c r="C2289">
+        <v>3379.2</v>
+      </c>
+      <c r="D2289" t="s">
+        <v>2291</v>
+      </c>
+    </row>
+    <row r="2290" spans="1:4">
+      <c r="A2290" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2290">
+        <v>81</v>
+      </c>
+      <c r="C2290">
+        <v>3425.1</v>
+      </c>
+      <c r="D2290" t="s">
+        <v>2292</v>
+      </c>
+    </row>
+    <row r="2291" spans="1:4">
+      <c r="A2291" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2291">
+        <v>82</v>
+      </c>
+      <c r="C2291">
+        <v>3446.2</v>
+      </c>
+      <c r="D2291" t="s">
+        <v>2293</v>
+      </c>
+    </row>
+    <row r="2292" spans="1:4">
+      <c r="A2292" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2292">
+        <v>83</v>
+      </c>
+      <c r="C2292">
+        <v>3498.5</v>
+      </c>
+      <c r="D2292" t="s">
+        <v>2294</v>
+      </c>
+    </row>
+    <row r="2293" spans="1:4">
+      <c r="A2293" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2293">
+        <v>84</v>
+      </c>
+      <c r="C2293">
+        <v>3580.7</v>
+      </c>
+      <c r="D2293" t="s">
+        <v>2295</v>
+      </c>
+    </row>
+    <row r="2294" spans="1:4">
+      <c r="A2294" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2294">
+        <v>85</v>
+      </c>
+      <c r="C2294">
+        <v>3724.6</v>
+      </c>
+      <c r="D2294" t="s">
+        <v>2296</v>
+      </c>
+    </row>
+    <row r="2295" spans="1:4">
+      <c r="A2295" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2295">
+        <v>86</v>
+      </c>
+      <c r="C2295">
+        <v>3782.3</v>
+      </c>
+      <c r="D2295" t="s">
+        <v>2297</v>
+      </c>
+    </row>
+    <row r="2296" spans="1:4">
+      <c r="A2296" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2296">
+        <v>87</v>
+      </c>
+      <c r="C2296">
+        <v>3874.8</v>
+      </c>
+      <c r="D2296" t="s">
+        <v>2298</v>
+      </c>
+    </row>
+    <row r="2297" spans="1:4">
+      <c r="A2297" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2297">
+        <v>88</v>
+      </c>
+      <c r="C2297">
+        <v>3873.5</v>
+      </c>
+      <c r="D2297" t="s">
+        <v>2299</v>
+      </c>
+    </row>
+    <row r="2298" spans="1:4">
+      <c r="A2298" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2298">
+        <v>89</v>
+      </c>
+      <c r="C2298">
+        <v>3721.9</v>
+      </c>
+      <c r="D2298" t="s">
+        <v>2300</v>
+      </c>
+    </row>
+    <row r="2299" spans="1:4">
+      <c r="A2299" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2299">
+        <v>90</v>
+      </c>
+      <c r="C2299">
+        <v>3713.7</v>
+      </c>
+      <c r="D2299" t="s">
+        <v>2301</v>
+      </c>
+    </row>
+    <row r="2300" spans="1:4">
+      <c r="A2300" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2300">
+        <v>91</v>
+      </c>
+      <c r="C2300">
+        <v>3720.4</v>
+      </c>
+      <c r="D2300" t="s">
+        <v>2302</v>
+      </c>
+    </row>
+    <row r="2301" spans="1:4">
+      <c r="A2301" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2301">
+        <v>92</v>
+      </c>
+      <c r="C2301">
+        <v>3783.1</v>
+      </c>
+      <c r="D2301" t="s">
+        <v>2303</v>
+      </c>
+    </row>
+    <row r="2302" spans="1:4">
+      <c r="A2302" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2302">
+        <v>93</v>
+      </c>
+      <c r="C2302">
+        <v>3729.7</v>
+      </c>
+      <c r="D2302" t="s">
+        <v>2304</v>
+      </c>
+    </row>
+    <row r="2303" spans="1:4">
+      <c r="A2303" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2303">
+        <v>94</v>
+      </c>
+      <c r="C2303">
+        <v>3695.6</v>
+      </c>
+      <c r="D2303" t="s">
+        <v>2305</v>
+      </c>
+    </row>
+    <row r="2304" spans="1:4">
+      <c r="A2304" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2304">
+        <v>95</v>
+      </c>
+      <c r="C2304">
+        <v>3710.6</v>
+      </c>
+      <c r="D2304" t="s">
+        <v>2306</v>
+      </c>
+    </row>
+    <row r="2305" spans="1:4">
+      <c r="A2305" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2305">
+        <v>96</v>
+      </c>
+      <c r="C2305">
+        <v>3762.5</v>
+      </c>
+      <c r="D2305" t="s">
+        <v>2307</v>
+      </c>
+    </row>
+    <row r="2306" spans="1:4">
+      <c r="A2306" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2306">
+        <v>1</v>
+      </c>
+      <c r="C2306">
+        <v>4976</v>
+      </c>
+      <c r="D2306" t="s">
+        <v>2308</v>
+      </c>
+    </row>
+    <row r="2307" spans="1:4">
+      <c r="A2307" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2307">
+        <v>2</v>
+      </c>
+      <c r="C2307">
+        <v>4936.2</v>
+      </c>
+      <c r="D2307" t="s">
+        <v>2309</v>
+      </c>
+    </row>
+    <row r="2308" spans="1:4">
+      <c r="A2308" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2308">
+        <v>3</v>
+      </c>
+      <c r="C2308">
+        <v>4819.7</v>
+      </c>
+      <c r="D2308" t="s">
+        <v>2310</v>
+      </c>
+    </row>
+    <row r="2309" spans="1:4">
+      <c r="A2309" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2309">
+        <v>4</v>
+      </c>
+      <c r="C2309">
+        <v>4707.7</v>
+      </c>
+      <c r="D2309" t="s">
+        <v>2311</v>
+      </c>
+    </row>
+    <row r="2310" spans="1:4">
+      <c r="A2310" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2310">
+        <v>5</v>
+      </c>
+      <c r="C2310">
+        <v>4253.4</v>
+      </c>
+      <c r="D2310" t="s">
+        <v>2312</v>
+      </c>
+    </row>
+    <row r="2311" spans="1:4">
+      <c r="A2311" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2311">
+        <v>6</v>
+      </c>
+      <c r="C2311">
+        <v>4218.2</v>
+      </c>
+      <c r="D2311" t="s">
+        <v>2313</v>
+      </c>
+    </row>
+    <row r="2312" spans="1:4">
+      <c r="A2312" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2312">
+        <v>7</v>
+      </c>
+      <c r="C2312">
+        <v>4169.8</v>
+      </c>
+      <c r="D2312" t="s">
+        <v>2314</v>
+      </c>
+    </row>
+    <row r="2313" spans="1:4">
+      <c r="A2313" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2313">
+        <v>8</v>
+      </c>
+      <c r="C2313">
+        <v>4134.3</v>
+      </c>
+      <c r="D2313" t="s">
+        <v>2315</v>
+      </c>
+    </row>
+    <row r="2314" spans="1:4">
+      <c r="A2314" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2314">
+        <v>9</v>
+      </c>
+      <c r="C2314">
+        <v>3865.1</v>
+      </c>
+      <c r="D2314" t="s">
+        <v>2316</v>
+      </c>
+    </row>
+    <row r="2315" spans="1:4">
+      <c r="A2315" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2315">
+        <v>10</v>
+      </c>
+      <c r="C2315">
+        <v>3844.8</v>
+      </c>
+      <c r="D2315" t="s">
+        <v>2317</v>
+      </c>
+    </row>
+    <row r="2316" spans="1:4">
+      <c r="A2316" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2316">
+        <v>11</v>
+      </c>
+      <c r="C2316">
+        <v>3820.6</v>
+      </c>
+      <c r="D2316" t="s">
+        <v>2318</v>
+      </c>
+    </row>
+    <row r="2317" spans="1:4">
+      <c r="A2317" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2317">
+        <v>12</v>
+      </c>
+      <c r="C2317">
+        <v>3811.4</v>
+      </c>
+      <c r="D2317" t="s">
+        <v>2319</v>
+      </c>
+    </row>
+    <row r="2318" spans="1:4">
+      <c r="A2318" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2318">
+        <v>13</v>
+      </c>
+      <c r="C2318">
+        <v>3834</v>
+      </c>
+      <c r="D2318" t="s">
+        <v>2320</v>
+      </c>
+    </row>
+    <row r="2319" spans="1:4">
+      <c r="A2319" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2319">
+        <v>14</v>
+      </c>
+      <c r="C2319">
+        <v>3811.1</v>
+      </c>
+      <c r="D2319" t="s">
+        <v>2321</v>
+      </c>
+    </row>
+    <row r="2320" spans="1:4">
+      <c r="A2320" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2320">
+        <v>15</v>
+      </c>
+      <c r="C2320">
+        <v>3795.4</v>
+      </c>
+      <c r="D2320" t="s">
+        <v>2322</v>
+      </c>
+    </row>
+    <row r="2321" spans="1:4">
+      <c r="A2321" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2321">
+        <v>16</v>
+      </c>
+      <c r="C2321">
+        <v>3775.9</v>
+      </c>
+      <c r="D2321" t="s">
+        <v>2323</v>
+      </c>
+    </row>
+    <row r="2322" spans="1:4">
+      <c r="A2322" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2322">
+        <v>17</v>
+      </c>
+      <c r="C2322">
+        <v>3755.9</v>
+      </c>
+      <c r="D2322" t="s">
+        <v>2324</v>
+      </c>
+    </row>
+    <row r="2323" spans="1:4">
+      <c r="A2323" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2323">
+        <v>18</v>
+      </c>
+      <c r="C2323">
+        <v>3719.2</v>
+      </c>
+      <c r="D2323" t="s">
+        <v>2325</v>
+      </c>
+    </row>
+    <row r="2324" spans="1:4">
+      <c r="A2324" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2324">
+        <v>19</v>
+      </c>
+      <c r="C2324">
+        <v>3677.8</v>
+      </c>
+      <c r="D2324" t="s">
+        <v>2326</v>
+      </c>
+    </row>
+    <row r="2325" spans="1:4">
+      <c r="A2325" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2325">
+        <v>20</v>
+      </c>
+      <c r="C2325">
+        <v>3643.5</v>
+      </c>
+      <c r="D2325" t="s">
+        <v>2327</v>
+      </c>
+    </row>
+    <row r="2326" spans="1:4">
+      <c r="A2326" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2326">
+        <v>21</v>
+      </c>
+      <c r="C2326">
+        <v>3665.6</v>
+      </c>
+      <c r="D2326" t="s">
+        <v>2328</v>
+      </c>
+    </row>
+    <row r="2327" spans="1:4">
+      <c r="A2327" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2327">
+        <v>22</v>
+      </c>
+      <c r="C2327">
+        <v>3655.6</v>
+      </c>
+      <c r="D2327" t="s">
+        <v>2329</v>
+      </c>
+    </row>
+    <row r="2328" spans="1:4">
+      <c r="A2328" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2328">
+        <v>23</v>
+      </c>
+      <c r="C2328">
+        <v>3653.4</v>
+      </c>
+      <c r="D2328" t="s">
+        <v>2330</v>
+      </c>
+    </row>
+    <row r="2329" spans="1:4">
+      <c r="A2329" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2329">
+        <v>24</v>
+      </c>
+      <c r="C2329">
+        <v>3666.6</v>
+      </c>
+      <c r="D2329" t="s">
+        <v>2331</v>
+      </c>
+    </row>
+    <row r="2330" spans="1:4">
+      <c r="A2330" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2330">
+        <v>25</v>
+      </c>
+      <c r="C2330">
+        <v>3746.8</v>
+      </c>
+      <c r="D2330" t="s">
+        <v>2332</v>
+      </c>
+    </row>
+    <row r="2331" spans="1:4">
+      <c r="A2331" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2331">
+        <v>26</v>
+      </c>
+      <c r="C2331">
+        <v>3811.3</v>
+      </c>
+      <c r="D2331" t="s">
+        <v>2333</v>
+      </c>
+    </row>
+    <row r="2332" spans="1:4">
+      <c r="A2332" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2332">
+        <v>27</v>
+      </c>
+      <c r="C2332">
+        <v>3883.1</v>
+      </c>
+      <c r="D2332" t="s">
+        <v>2334</v>
+      </c>
+    </row>
+    <row r="2333" spans="1:4">
+      <c r="A2333" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2333">
+        <v>28</v>
+      </c>
+      <c r="C2333">
+        <v>3926.4</v>
+      </c>
+      <c r="D2333" t="s">
+        <v>2335</v>
+      </c>
+    </row>
+    <row r="2334" spans="1:4">
+      <c r="A2334" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2334">
+        <v>29</v>
+      </c>
+      <c r="C2334">
+        <v>3980.9</v>
+      </c>
+      <c r="D2334" t="s">
+        <v>2336</v>
+      </c>
+    </row>
+    <row r="2335" spans="1:4">
+      <c r="A2335" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2335">
+        <v>30</v>
+      </c>
+      <c r="C2335">
+        <v>4016.5</v>
+      </c>
+      <c r="D2335" t="s">
+        <v>2337</v>
+      </c>
+    </row>
+    <row r="2336" spans="1:4">
+      <c r="A2336" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2336">
+        <v>31</v>
+      </c>
+      <c r="C2336">
+        <v>4112.3</v>
+      </c>
+      <c r="D2336" t="s">
+        <v>2338</v>
+      </c>
+    </row>
+    <row r="2337" spans="1:4">
+      <c r="A2337" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2337">
+        <v>32</v>
+      </c>
+      <c r="C2337">
+        <v>4209.7</v>
+      </c>
+      <c r="D2337" t="s">
+        <v>2339</v>
+      </c>
+    </row>
+    <row r="2338" spans="1:4">
+      <c r="A2338" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2338">
+        <v>33</v>
+      </c>
+      <c r="C2338">
+        <v>4111.3</v>
+      </c>
+      <c r="D2338" t="s">
+        <v>2340</v>
+      </c>
+    </row>
+    <row r="2339" spans="1:4">
+      <c r="A2339" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2339">
+        <v>34</v>
+      </c>
+      <c r="C2339">
+        <v>4173</v>
+      </c>
+      <c r="D2339" t="s">
+        <v>2341</v>
+      </c>
+    </row>
+    <row r="2340" spans="1:4">
+      <c r="A2340" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2340">
+        <v>35</v>
+      </c>
+      <c r="C2340">
+        <v>4229.6</v>
+      </c>
+      <c r="D2340" t="s">
+        <v>2342</v>
+      </c>
+    </row>
+    <row r="2341" spans="1:4">
+      <c r="A2341" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2341">
+        <v>36</v>
+      </c>
+      <c r="C2341">
+        <v>4334.8</v>
+      </c>
+      <c r="D2341" t="s">
+        <v>2343</v>
+      </c>
+    </row>
+    <row r="2342" spans="1:4">
+      <c r="A2342" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2342">
+        <v>37</v>
+      </c>
+      <c r="C2342">
+        <v>4156.5</v>
+      </c>
+      <c r="D2342" t="s">
+        <v>2344</v>
+      </c>
+    </row>
+    <row r="2343" spans="1:4">
+      <c r="A2343" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2343">
+        <v>38</v>
+      </c>
+      <c r="C2343">
+        <v>4129.5</v>
+      </c>
+      <c r="D2343" t="s">
+        <v>2345</v>
+      </c>
+    </row>
+    <row r="2344" spans="1:4">
+      <c r="A2344" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2344">
+        <v>39</v>
+      </c>
+      <c r="C2344">
+        <v>4156.2</v>
+      </c>
+      <c r="D2344" t="s">
+        <v>2346</v>
+      </c>
+    </row>
+    <row r="2345" spans="1:4">
+      <c r="A2345" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2345">
+        <v>40</v>
+      </c>
+      <c r="C2345">
+        <v>4204.8</v>
+      </c>
+      <c r="D2345" t="s">
+        <v>2347</v>
+      </c>
+    </row>
+    <row r="2346" spans="1:4">
+      <c r="A2346" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2346">
+        <v>41</v>
+      </c>
+      <c r="C2346">
+        <v>4380.7</v>
+      </c>
+      <c r="D2346" t="s">
+        <v>2348</v>
+      </c>
+    </row>
+    <row r="2347" spans="1:4">
+      <c r="A2347" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2347">
+        <v>42</v>
+      </c>
+      <c r="C2347">
+        <v>4359.9</v>
+      </c>
+      <c r="D2347" t="s">
+        <v>2349</v>
+      </c>
+    </row>
+    <row r="2348" spans="1:4">
+      <c r="A2348" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2348">
+        <v>43</v>
+      </c>
+      <c r="C2348">
+        <v>4348.3</v>
+      </c>
+      <c r="D2348" t="s">
+        <v>2350</v>
+      </c>
+    </row>
+    <row r="2349" spans="1:4">
+      <c r="A2349" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2349">
+        <v>44</v>
+      </c>
+      <c r="C2349">
+        <v>4347.5</v>
+      </c>
+      <c r="D2349" t="s">
+        <v>2351</v>
+      </c>
+    </row>
+    <row r="2350" spans="1:4">
+      <c r="A2350" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2350">
+        <v>45</v>
+      </c>
+      <c r="C2350">
+        <v>4298</v>
+      </c>
+      <c r="D2350" t="s">
+        <v>2352</v>
+      </c>
+    </row>
+    <row r="2351" spans="1:4">
+      <c r="A2351" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2351">
+        <v>46</v>
+      </c>
+      <c r="C2351">
+        <v>4263.3</v>
+      </c>
+      <c r="D2351" t="s">
+        <v>2353</v>
+      </c>
+    </row>
+    <row r="2352" spans="1:4">
+      <c r="A2352" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2352">
+        <v>47</v>
+      </c>
+      <c r="C2352">
+        <v>4224.1</v>
+      </c>
+      <c r="D2352" t="s">
+        <v>2354</v>
+      </c>
+    </row>
+    <row r="2353" spans="1:4">
+      <c r="A2353" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2353">
+        <v>48</v>
+      </c>
+      <c r="C2353">
+        <v>4250.1</v>
+      </c>
+      <c r="D2353" t="s">
+        <v>2355</v>
+      </c>
+    </row>
+    <row r="2354" spans="1:4">
+      <c r="A2354" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2354">
+        <v>49</v>
+      </c>
+      <c r="C2354">
+        <v>4076.1</v>
+      </c>
+      <c r="D2354" t="s">
+        <v>2356</v>
+      </c>
+    </row>
+    <row r="2355" spans="1:4">
+      <c r="A2355" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2355">
+        <v>50</v>
+      </c>
+      <c r="C2355">
+        <v>4068.2</v>
+      </c>
+      <c r="D2355" t="s">
+        <v>2357</v>
+      </c>
+    </row>
+    <row r="2356" spans="1:4">
+      <c r="A2356" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2356">
+        <v>51</v>
+      </c>
+      <c r="C2356">
+        <v>4075.5</v>
+      </c>
+      <c r="D2356" t="s">
+        <v>2358</v>
+      </c>
+    </row>
+    <row r="2357" spans="1:4">
+      <c r="A2357" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2357">
+        <v>52</v>
+      </c>
+      <c r="C2357">
+        <v>4090</v>
+      </c>
+      <c r="D2357" t="s">
+        <v>2359</v>
+      </c>
+    </row>
+    <row r="2358" spans="1:4">
+      <c r="A2358" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2358">
+        <v>53</v>
+      </c>
+      <c r="C2358">
+        <v>4087.1</v>
+      </c>
+      <c r="D2358" t="s">
+        <v>2360</v>
+      </c>
+    </row>
+    <row r="2359" spans="1:4">
+      <c r="A2359" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2359">
+        <v>54</v>
+      </c>
+      <c r="C2359">
+        <v>4068.4</v>
+      </c>
+      <c r="D2359" t="s">
+        <v>2361</v>
+      </c>
+    </row>
+    <row r="2360" spans="1:4">
+      <c r="A2360" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2360">
+        <v>55</v>
+      </c>
+      <c r="C2360">
+        <v>4093.8</v>
+      </c>
+      <c r="D2360" t="s">
+        <v>2362</v>
+      </c>
+    </row>
+    <row r="2361" spans="1:4">
+      <c r="A2361" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2361">
+        <v>56</v>
+      </c>
+      <c r="C2361">
+        <v>4098.2</v>
+      </c>
+      <c r="D2361" t="s">
+        <v>2363</v>
+      </c>
+    </row>
+    <row r="2362" spans="1:4">
+      <c r="A2362" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2362">
+        <v>57</v>
+      </c>
+      <c r="C2362">
+        <v>4130.2</v>
+      </c>
+      <c r="D2362" t="s">
+        <v>2364</v>
+      </c>
+    </row>
+    <row r="2363" spans="1:4">
+      <c r="A2363" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2363">
+        <v>58</v>
+      </c>
+      <c r="C2363">
+        <v>4117</v>
+      </c>
+      <c r="D2363" t="s">
+        <v>2365</v>
+      </c>
+    </row>
+    <row r="2364" spans="1:4">
+      <c r="A2364" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2364">
+        <v>59</v>
+      </c>
+      <c r="C2364">
+        <v>4148</v>
+      </c>
+      <c r="D2364" t="s">
+        <v>2366</v>
+      </c>
+    </row>
+    <row r="2365" spans="1:4">
+      <c r="A2365" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2365">
+        <v>60</v>
+      </c>
+      <c r="C2365">
+        <v>4215.1</v>
+      </c>
+      <c r="D2365" t="s">
+        <v>2367</v>
+      </c>
+    </row>
+    <row r="2366" spans="1:4">
+      <c r="A2366" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2366">
+        <v>61</v>
+      </c>
+      <c r="C2366">
+        <v>4301.2</v>
+      </c>
+      <c r="D2366" t="s">
+        <v>2368</v>
+      </c>
+    </row>
+    <row r="2367" spans="1:4">
+      <c r="A2367" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2367">
+        <v>62</v>
+      </c>
+      <c r="C2367">
+        <v>4306.4</v>
+      </c>
+      <c r="D2367" t="s">
+        <v>2369</v>
+      </c>
+    </row>
+    <row r="2368" spans="1:4">
+      <c r="A2368" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2368">
+        <v>63</v>
+      </c>
+      <c r="C2368">
+        <v>4301.2</v>
+      </c>
+      <c r="D2368" t="s">
+        <v>2370</v>
+      </c>
+    </row>
+    <row r="2369" spans="1:4">
+      <c r="A2369" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2369">
+        <v>64</v>
+      </c>
+      <c r="C2369">
+        <v>4330.3</v>
+      </c>
+      <c r="D2369" t="s">
+        <v>2371</v>
+      </c>
+    </row>
+    <row r="2370" spans="1:4">
+      <c r="A2370" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2370">
+        <v>65</v>
+      </c>
+      <c r="C2370">
+        <v>4359.1</v>
+      </c>
+      <c r="D2370" t="s">
+        <v>2372</v>
+      </c>
+    </row>
+    <row r="2371" spans="1:4">
+      <c r="A2371" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2371">
+        <v>66</v>
+      </c>
+      <c r="C2371">
+        <v>4300.3</v>
+      </c>
+      <c r="D2371" t="s">
+        <v>2373</v>
+      </c>
+    </row>
+    <row r="2372" spans="1:4">
+      <c r="A2372" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2372">
+        <v>67</v>
+      </c>
+      <c r="C2372">
+        <v>4289.2</v>
+      </c>
+      <c r="D2372" t="s">
+        <v>2374</v>
+      </c>
+    </row>
+    <row r="2373" spans="1:4">
+      <c r="A2373" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2373">
+        <v>68</v>
+      </c>
+      <c r="C2373">
+        <v>4240.9</v>
+      </c>
+      <c r="D2373" t="s">
+        <v>2375</v>
+      </c>
+    </row>
+    <row r="2374" spans="1:4">
+      <c r="A2374" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2374">
+        <v>69</v>
+      </c>
+      <c r="C2374">
+        <v>4123.4</v>
+      </c>
+      <c r="D2374" t="s">
+        <v>2376</v>
+      </c>
+    </row>
+    <row r="2375" spans="1:4">
+      <c r="A2375" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2375">
+        <v>70</v>
+      </c>
+      <c r="C2375">
+        <v>4058.8</v>
+      </c>
+      <c r="D2375" t="s">
+        <v>2377</v>
+      </c>
+    </row>
+    <row r="2376" spans="1:4">
+      <c r="A2376" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2376">
+        <v>71</v>
+      </c>
+      <c r="C2376">
+        <v>4024.3</v>
+      </c>
+      <c r="D2376" t="s">
+        <v>2378</v>
+      </c>
+    </row>
+    <row r="2377" spans="1:4">
+      <c r="A2377" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2377">
+        <v>72</v>
+      </c>
+      <c r="C2377">
+        <v>3988.9</v>
+      </c>
+      <c r="D2377" t="s">
+        <v>2379</v>
+      </c>
+    </row>
+    <row r="2378" spans="1:4">
+      <c r="A2378" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2378">
+        <v>73</v>
+      </c>
+      <c r="C2378">
+        <v>4594.8</v>
+      </c>
+      <c r="D2378" t="s">
+        <v>2380</v>
+      </c>
+    </row>
+    <row r="2379" spans="1:4">
+      <c r="A2379" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2379">
+        <v>74</v>
+      </c>
+      <c r="C2379">
+        <v>4535</v>
+      </c>
+      <c r="D2379" t="s">
+        <v>2381</v>
+      </c>
+    </row>
+    <row r="2380" spans="1:4">
+      <c r="A2380" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2380">
+        <v>75</v>
+      </c>
+      <c r="C2380">
+        <v>4516.5</v>
+      </c>
+      <c r="D2380" t="s">
+        <v>2382</v>
+      </c>
+    </row>
+    <row r="2381" spans="1:4">
+      <c r="A2381" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2381">
+        <v>76</v>
+      </c>
+      <c r="C2381">
+        <v>4505.9</v>
+      </c>
+      <c r="D2381" t="s">
+        <v>2383</v>
+      </c>
+    </row>
+    <row r="2382" spans="1:4">
+      <c r="A2382" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2382">
+        <v>77</v>
+      </c>
+      <c r="C2382">
+        <v>4431.2</v>
+      </c>
+      <c r="D2382" t="s">
+        <v>2384</v>
+      </c>
+    </row>
+    <row r="2383" spans="1:4">
+      <c r="A2383" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2383">
+        <v>78</v>
+      </c>
+      <c r="C2383">
+        <v>4439.7</v>
+      </c>
+      <c r="D2383" t="s">
+        <v>2385</v>
+      </c>
+    </row>
+    <row r="2384" spans="1:4">
+      <c r="A2384" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2384">
+        <v>79</v>
+      </c>
+      <c r="C2384">
+        <v>4376.6</v>
+      </c>
+      <c r="D2384" t="s">
+        <v>2386</v>
+      </c>
+    </row>
+    <row r="2385" spans="1:4">
+      <c r="A2385" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2385">
+        <v>80</v>
+      </c>
+      <c r="C2385">
+        <v>4349.2</v>
+      </c>
+      <c r="D2385" t="s">
+        <v>2387</v>
+      </c>
+    </row>
+    <row r="2386" spans="1:4">
+      <c r="A2386" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2386">
+        <v>81</v>
+      </c>
+      <c r="C2386">
+        <v>4395.1</v>
+      </c>
+      <c r="D2386" t="s">
+        <v>2388</v>
+      </c>
+    </row>
+    <row r="2387" spans="1:4">
+      <c r="A2387" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2387">
+        <v>82</v>
+      </c>
+      <c r="C2387">
+        <v>4426.2</v>
+      </c>
+      <c r="D2387" t="s">
+        <v>2389</v>
+      </c>
+    </row>
+    <row r="2388" spans="1:4">
+      <c r="A2388" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2388">
+        <v>83</v>
+      </c>
+      <c r="C2388">
+        <v>4468.5</v>
+      </c>
+      <c r="D2388" t="s">
+        <v>2390</v>
+      </c>
+    </row>
+    <row r="2389" spans="1:4">
+      <c r="A2389" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2389">
+        <v>84</v>
+      </c>
+      <c r="C2389">
+        <v>4510.7</v>
+      </c>
+      <c r="D2389" t="s">
+        <v>2391</v>
+      </c>
+    </row>
+    <row r="2390" spans="1:4">
+      <c r="A2390" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2390">
+        <v>85</v>
+      </c>
+      <c r="C2390">
+        <v>4614.6</v>
+      </c>
+      <c r="D2390" t="s">
+        <v>2392</v>
+      </c>
+    </row>
+    <row r="2391" spans="1:4">
+      <c r="A2391" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2391">
+        <v>86</v>
+      </c>
+      <c r="C2391">
+        <v>4642.3</v>
+      </c>
+      <c r="D2391" t="s">
+        <v>2393</v>
+      </c>
+    </row>
+    <row r="2392" spans="1:4">
+      <c r="A2392" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2392">
+        <v>87</v>
+      </c>
+      <c r="C2392">
+        <v>4694.8</v>
+      </c>
+      <c r="D2392" t="s">
+        <v>2394</v>
+      </c>
+    </row>
+    <row r="2393" spans="1:4">
+      <c r="A2393" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2393">
+        <v>88</v>
+      </c>
+      <c r="C2393">
+        <v>4653.5</v>
+      </c>
+      <c r="D2393" t="s">
+        <v>2395</v>
+      </c>
+    </row>
+    <row r="2394" spans="1:4">
+      <c r="A2394" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2394">
+        <v>89</v>
+      </c>
+      <c r="C2394">
+        <v>4471.9</v>
+      </c>
+      <c r="D2394" t="s">
+        <v>2396</v>
+      </c>
+    </row>
+    <row r="2395" spans="1:4">
+      <c r="A2395" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2395">
+        <v>90</v>
+      </c>
+      <c r="C2395">
+        <v>4433.7</v>
+      </c>
+      <c r="D2395" t="s">
+        <v>2397</v>
+      </c>
+    </row>
+    <row r="2396" spans="1:4">
+      <c r="A2396" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2396">
+        <v>91</v>
+      </c>
+      <c r="C2396">
+        <v>4400.4</v>
+      </c>
+      <c r="D2396" t="s">
+        <v>2398</v>
+      </c>
+    </row>
+    <row r="2397" spans="1:4">
+      <c r="A2397" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2397">
+        <v>92</v>
+      </c>
+      <c r="C2397">
+        <v>4423.1</v>
+      </c>
+      <c r="D2397" t="s">
+        <v>2399</v>
+      </c>
+    </row>
+    <row r="2398" spans="1:4">
+      <c r="A2398" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2398">
+        <v>93</v>
+      </c>
+      <c r="C2398">
+        <v>4329.7</v>
+      </c>
+      <c r="D2398" t="s">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="2399" spans="1:4">
+      <c r="A2399" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2399">
+        <v>94</v>
+      </c>
+      <c r="C2399">
+        <v>4265.6</v>
+      </c>
+      <c r="D2399" t="s">
+        <v>2401</v>
+      </c>
+    </row>
+    <row r="2400" spans="1:4">
+      <c r="A2400" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2400">
+        <v>95</v>
+      </c>
+      <c r="C2400">
+        <v>4250.6</v>
+      </c>
+      <c r="D2400" t="s">
+        <v>2402</v>
+      </c>
+    </row>
+    <row r="2401" spans="1:4">
+      <c r="A2401" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2401">
+        <v>96</v>
+      </c>
+      <c r="C2401">
+        <v>4282.5</v>
+      </c>
+      <c r="D2401" t="s">
+        <v>2403</v>
+      </c>
+    </row>
+    <row r="2402" spans="1:4">
+      <c r="A2402" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2402">
+        <v>1</v>
+      </c>
+      <c r="C2402">
+        <v>5506</v>
+      </c>
+      <c r="D2402" t="s">
+        <v>2404</v>
+      </c>
+    </row>
+    <row r="2403" spans="1:4">
+      <c r="A2403" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2403">
+        <v>2</v>
+      </c>
+      <c r="C2403">
+        <v>5456.2</v>
+      </c>
+      <c r="D2403" t="s">
+        <v>2405</v>
+      </c>
+    </row>
+    <row r="2404" spans="1:4">
+      <c r="A2404" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2404">
+        <v>3</v>
+      </c>
+      <c r="C2404">
+        <v>5329.7</v>
+      </c>
+      <c r="D2404" t="s">
+        <v>2406</v>
+      </c>
+    </row>
+    <row r="2405" spans="1:4">
+      <c r="A2405" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2405">
+        <v>4</v>
+      </c>
+      <c r="C2405">
+        <v>5217.7</v>
+      </c>
+      <c r="D2405" t="s">
+        <v>2407</v>
+      </c>
+    </row>
+    <row r="2406" spans="1:4">
+      <c r="A2406" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2406">
+        <v>5</v>
+      </c>
+      <c r="C2406">
+        <v>4763.4</v>
+      </c>
+      <c r="D2406" t="s">
+        <v>2408</v>
+      </c>
+    </row>
+    <row r="2407" spans="1:4">
+      <c r="A2407" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2407">
+        <v>6</v>
+      </c>
+      <c r="C2407">
+        <v>4728.2</v>
+      </c>
+      <c r="D2407" t="s">
+        <v>2409</v>
+      </c>
+    </row>
+    <row r="2408" spans="1:4">
+      <c r="A2408" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2408">
+        <v>7</v>
+      </c>
+      <c r="C2408">
+        <v>4679.8</v>
+      </c>
+      <c r="D2408" t="s">
+        <v>2410</v>
+      </c>
+    </row>
+    <row r="2409" spans="1:4">
+      <c r="A2409" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2409">
+        <v>8</v>
+      </c>
+      <c r="C2409">
+        <v>4644.3</v>
+      </c>
+      <c r="D2409" t="s">
+        <v>2411</v>
+      </c>
+    </row>
+    <row r="2410" spans="1:4">
+      <c r="A2410" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2410">
+        <v>9</v>
+      </c>
+      <c r="C2410">
+        <v>4355.1</v>
+      </c>
+      <c r="D2410" t="s">
+        <v>2412</v>
+      </c>
+    </row>
+    <row r="2411" spans="1:4">
+      <c r="A2411" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2411">
+        <v>10</v>
+      </c>
+      <c r="C2411">
+        <v>4324.8</v>
+      </c>
+      <c r="D2411" t="s">
+        <v>2413</v>
+      </c>
+    </row>
+    <row r="2412" spans="1:4">
+      <c r="A2412" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2412">
+        <v>11</v>
+      </c>
+      <c r="C2412">
+        <v>4300.6</v>
+      </c>
+      <c r="D2412" t="s">
+        <v>2414</v>
+      </c>
+    </row>
+    <row r="2413" spans="1:4">
+      <c r="A2413" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2413">
+        <v>12</v>
+      </c>
+      <c r="C2413">
+        <v>4281.4</v>
+      </c>
+      <c r="D2413" t="s">
+        <v>2415</v>
+      </c>
+    </row>
+    <row r="2414" spans="1:4">
+      <c r="A2414" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2414">
+        <v>13</v>
+      </c>
+      <c r="C2414">
+        <v>4304</v>
+      </c>
+      <c r="D2414" t="s">
+        <v>2416</v>
+      </c>
+    </row>
+    <row r="2415" spans="1:4">
+      <c r="A2415" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2415">
+        <v>14</v>
+      </c>
+      <c r="C2415">
+        <v>4271.1</v>
+      </c>
+      <c r="D2415" t="s">
+        <v>2417</v>
+      </c>
+    </row>
+    <row r="2416" spans="1:4">
+      <c r="A2416" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2416">
+        <v>15</v>
+      </c>
+      <c r="C2416">
+        <v>4255.4</v>
+      </c>
+      <c r="D2416" t="s">
+        <v>2418</v>
+      </c>
+    </row>
+    <row r="2417" spans="1:4">
+      <c r="A2417" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2417">
+        <v>16</v>
+      </c>
+      <c r="C2417">
+        <v>4225.9</v>
+      </c>
+      <c r="D2417" t="s">
+        <v>2419</v>
+      </c>
+    </row>
+    <row r="2418" spans="1:4">
+      <c r="A2418" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2418">
+        <v>17</v>
+      </c>
+      <c r="C2418">
+        <v>4205.9</v>
+      </c>
+      <c r="D2418" t="s">
+        <v>2420</v>
+      </c>
+    </row>
+    <row r="2419" spans="1:4">
+      <c r="A2419" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2419">
+        <v>18</v>
+      </c>
+      <c r="C2419">
+        <v>4159.2</v>
+      </c>
+      <c r="D2419" t="s">
+        <v>2421</v>
+      </c>
+    </row>
+    <row r="2420" spans="1:4">
+      <c r="A2420" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2420">
+        <v>19</v>
+      </c>
+      <c r="C2420">
+        <v>4117.8</v>
+      </c>
+      <c r="D2420" t="s">
+        <v>2422</v>
+      </c>
+    </row>
+    <row r="2421" spans="1:4">
+      <c r="A2421" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2421">
+        <v>20</v>
+      </c>
+      <c r="C2421">
+        <v>4073.5</v>
+      </c>
+      <c r="D2421" t="s">
+        <v>2423</v>
+      </c>
+    </row>
+    <row r="2422" spans="1:4">
+      <c r="A2422" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2422">
+        <v>21</v>
+      </c>
+      <c r="C2422">
+        <v>4095.6</v>
+      </c>
+      <c r="D2422" t="s">
+        <v>2424</v>
+      </c>
+    </row>
+    <row r="2423" spans="1:4">
+      <c r="A2423" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2423">
+        <v>22</v>
+      </c>
+      <c r="C2423">
+        <v>4065.6</v>
+      </c>
+      <c r="D2423" t="s">
+        <v>2425</v>
+      </c>
+    </row>
+    <row r="2424" spans="1:4">
+      <c r="A2424" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2424">
+        <v>23</v>
+      </c>
+      <c r="C2424">
+        <v>4033.4</v>
+      </c>
+      <c r="D2424" t="s">
+        <v>2426</v>
+      </c>
+    </row>
+    <row r="2425" spans="1:4">
+      <c r="A2425" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2425">
+        <v>24</v>
+      </c>
+      <c r="C2425">
+        <v>4006.6</v>
+      </c>
+      <c r="D2425" t="s">
+        <v>2427</v>
+      </c>
+    </row>
+    <row r="2426" spans="1:4">
+      <c r="A2426" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2426">
+        <v>25</v>
+      </c>
+      <c r="C2426">
+        <v>4046.8</v>
+      </c>
+      <c r="D2426" t="s">
+        <v>2428</v>
+      </c>
+    </row>
+    <row r="2427" spans="1:4">
+      <c r="A2427" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2427">
+        <v>26</v>
+      </c>
+      <c r="C2427">
+        <v>4081.3</v>
+      </c>
+      <c r="D2427" t="s">
+        <v>2429</v>
+      </c>
+    </row>
+    <row r="2428" spans="1:4">
+      <c r="A2428" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2428">
+        <v>27</v>
+      </c>
+      <c r="C2428">
+        <v>4123.1</v>
+      </c>
+      <c r="D2428" t="s">
+        <v>2430</v>
+      </c>
+    </row>
+    <row r="2429" spans="1:4">
+      <c r="A2429" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2429">
+        <v>28</v>
+      </c>
+      <c r="C2429">
+        <v>4156.4</v>
+      </c>
+      <c r="D2429" t="s">
+        <v>2431</v>
+      </c>
+    </row>
+    <row r="2430" spans="1:4">
+      <c r="A2430" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2430">
+        <v>29</v>
+      </c>
+      <c r="C2430">
+        <v>4200.9</v>
+      </c>
+      <c r="D2430" t="s">
+        <v>2432</v>
+      </c>
+    </row>
+    <row r="2431" spans="1:4">
+      <c r="A2431" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2431">
+        <v>30</v>
+      </c>
+      <c r="C2431">
+        <v>4216.5</v>
+      </c>
+      <c r="D2431" t="s">
+        <v>2433</v>
+      </c>
+    </row>
+    <row r="2432" spans="1:4">
+      <c r="A2432" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2432">
+        <v>31</v>
+      </c>
+      <c r="C2432">
+        <v>4312.3</v>
+      </c>
+      <c r="D2432" t="s">
+        <v>2434</v>
+      </c>
+    </row>
+    <row r="2433" spans="1:4">
+      <c r="A2433" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2433">
+        <v>32</v>
+      </c>
+      <c r="C2433">
+        <v>4389.7</v>
+      </c>
+      <c r="D2433" t="s">
+        <v>2435</v>
+      </c>
+    </row>
+    <row r="2434" spans="1:4">
+      <c r="A2434" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2434">
+        <v>33</v>
+      </c>
+      <c r="C2434">
+        <v>4261.3</v>
+      </c>
+      <c r="D2434" t="s">
+        <v>2436</v>
+      </c>
+    </row>
+    <row r="2435" spans="1:4">
+      <c r="A2435" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2435">
+        <v>34</v>
+      </c>
+      <c r="C2435">
+        <v>4313</v>
+      </c>
+      <c r="D2435" t="s">
+        <v>2437</v>
+      </c>
+    </row>
+    <row r="2436" spans="1:4">
+      <c r="A2436" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2436">
+        <v>35</v>
+      </c>
+      <c r="C2436">
+        <v>4349.6</v>
+      </c>
+      <c r="D2436" t="s">
+        <v>2438</v>
+      </c>
+    </row>
+    <row r="2437" spans="1:4">
+      <c r="A2437" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2437">
+        <v>36</v>
+      </c>
+      <c r="C2437">
+        <v>4464.8</v>
+      </c>
+      <c r="D2437" t="s">
+        <v>2439</v>
+      </c>
+    </row>
+    <row r="2438" spans="1:4">
+      <c r="A2438" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2438">
+        <v>37</v>
+      </c>
+      <c r="C2438">
+        <v>4286.5</v>
+      </c>
+      <c r="D2438" t="s">
+        <v>2440</v>
+      </c>
+    </row>
+    <row r="2439" spans="1:4">
+      <c r="A2439" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2439">
+        <v>38</v>
+      </c>
+      <c r="C2439">
+        <v>4269.5</v>
+      </c>
+      <c r="D2439" t="s">
+        <v>2441</v>
+      </c>
+    </row>
+    <row r="2440" spans="1:4">
+      <c r="A2440" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2440">
+        <v>39</v>
+      </c>
+      <c r="C2440">
+        <v>4306.2</v>
+      </c>
+      <c r="D2440" t="s">
+        <v>2442</v>
+      </c>
+    </row>
+    <row r="2441" spans="1:4">
+      <c r="A2441" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2441">
+        <v>40</v>
+      </c>
+      <c r="C2441">
+        <v>4364.8</v>
+      </c>
+      <c r="D2441" t="s">
+        <v>2443</v>
+      </c>
+    </row>
+    <row r="2442" spans="1:4">
+      <c r="A2442" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2442">
+        <v>41</v>
+      </c>
+      <c r="C2442">
+        <v>4530.7</v>
+      </c>
+      <c r="D2442" t="s">
+        <v>2444</v>
+      </c>
+    </row>
+    <row r="2443" spans="1:4">
+      <c r="A2443" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2443">
+        <v>42</v>
+      </c>
+      <c r="C2443">
+        <v>4519.9</v>
+      </c>
+      <c r="D2443" t="s">
+        <v>2445</v>
+      </c>
+    </row>
+    <row r="2444" spans="1:4">
+      <c r="A2444" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2444">
+        <v>43</v>
+      </c>
+      <c r="C2444">
+        <v>4508.3</v>
+      </c>
+      <c r="D2444" t="s">
+        <v>2446</v>
+      </c>
+    </row>
+    <row r="2445" spans="1:4">
+      <c r="A2445" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2445">
+        <v>44</v>
+      </c>
+      <c r="C2445">
+        <v>4497.5</v>
+      </c>
+      <c r="D2445" t="s">
+        <v>2447</v>
+      </c>
+    </row>
+    <row r="2446" spans="1:4">
+      <c r="A2446" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2446">
+        <v>45</v>
+      </c>
+      <c r="C2446">
+        <v>4448</v>
+      </c>
+      <c r="D2446" t="s">
+        <v>2448</v>
+      </c>
+    </row>
+    <row r="2447" spans="1:4">
+      <c r="A2447" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2447">
+        <v>46</v>
+      </c>
+      <c r="C2447">
+        <v>4403.3</v>
+      </c>
+      <c r="D2447" t="s">
+        <v>2449</v>
+      </c>
+    </row>
+    <row r="2448" spans="1:4">
+      <c r="A2448" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2448">
+        <v>47</v>
+      </c>
+      <c r="C2448">
+        <v>4374.1</v>
+      </c>
+      <c r="D2448" t="s">
+        <v>2450</v>
+      </c>
+    </row>
+    <row r="2449" spans="1:4">
+      <c r="A2449" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2449">
+        <v>48</v>
+      </c>
+      <c r="C2449">
+        <v>4400.1</v>
+      </c>
+      <c r="D2449" t="s">
+        <v>2451</v>
+      </c>
+    </row>
+    <row r="2450" spans="1:4">
+      <c r="A2450" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2450">
+        <v>49</v>
+      </c>
+      <c r="C2450">
+        <v>4226.1</v>
+      </c>
+      <c r="D2450" t="s">
+        <v>2452</v>
+      </c>
+    </row>
+    <row r="2451" spans="1:4">
+      <c r="A2451" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2451">
+        <v>50</v>
+      </c>
+      <c r="C2451">
+        <v>4218.2</v>
+      </c>
+      <c r="D2451" t="s">
+        <v>2453</v>
+      </c>
+    </row>
+    <row r="2452" spans="1:4">
+      <c r="A2452" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2452">
+        <v>51</v>
+      </c>
+      <c r="C2452">
+        <v>4215.5</v>
+      </c>
+      <c r="D2452" t="s">
+        <v>2454</v>
+      </c>
+    </row>
+    <row r="2453" spans="1:4">
+      <c r="A2453" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2453">
+        <v>52</v>
+      </c>
+      <c r="C2453">
+        <v>4230</v>
+      </c>
+      <c r="D2453" t="s">
+        <v>2455</v>
+      </c>
+    </row>
+    <row r="2454" spans="1:4">
+      <c r="A2454" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2454">
+        <v>53</v>
+      </c>
+      <c r="C2454">
+        <v>4217.1</v>
+      </c>
+      <c r="D2454" t="s">
+        <v>2456</v>
+      </c>
+    </row>
+    <row r="2455" spans="1:4">
+      <c r="A2455" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2455">
+        <v>54</v>
+      </c>
+      <c r="C2455">
+        <v>4198.4</v>
+      </c>
+      <c r="D2455" t="s">
+        <v>2457</v>
+      </c>
+    </row>
+    <row r="2456" spans="1:4">
+      <c r="A2456" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2456">
+        <v>55</v>
+      </c>
+      <c r="C2456">
+        <v>4223.8</v>
+      </c>
+      <c r="D2456" t="s">
+        <v>2458</v>
+      </c>
+    </row>
+    <row r="2457" spans="1:4">
+      <c r="A2457" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2457">
+        <v>56</v>
+      </c>
+      <c r="C2457">
+        <v>4228.2</v>
+      </c>
+      <c r="D2457" t="s">
+        <v>2459</v>
+      </c>
+    </row>
+    <row r="2458" spans="1:4">
+      <c r="A2458" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2458">
+        <v>57</v>
+      </c>
+      <c r="C2458">
+        <v>4280.2</v>
+      </c>
+      <c r="D2458" t="s">
+        <v>2460</v>
+      </c>
+    </row>
+    <row r="2459" spans="1:4">
+      <c r="A2459" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2459">
+        <v>58</v>
+      </c>
+      <c r="C2459">
+        <v>4267</v>
+      </c>
+      <c r="D2459" t="s">
+        <v>2461</v>
+      </c>
+    </row>
+    <row r="2460" spans="1:4">
+      <c r="A2460" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2460">
+        <v>59</v>
+      </c>
+      <c r="C2460">
+        <v>4278</v>
+      </c>
+      <c r="D2460" t="s">
+        <v>2462</v>
+      </c>
+    </row>
+    <row r="2461" spans="1:4">
+      <c r="A2461" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2461">
+        <v>60</v>
+      </c>
+      <c r="C2461">
+        <v>4325.1</v>
+      </c>
+      <c r="D2461" t="s">
+        <v>2463</v>
+      </c>
+    </row>
+    <row r="2462" spans="1:4">
+      <c r="A2462" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2462">
+        <v>61</v>
+      </c>
+      <c r="C2462">
+        <v>4381.2</v>
+      </c>
+      <c r="D2462" t="s">
+        <v>2464</v>
+      </c>
+    </row>
+    <row r="2463" spans="1:4">
+      <c r="A2463" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2463">
+        <v>62</v>
+      </c>
+      <c r="C2463">
+        <v>4356.4</v>
+      </c>
+      <c r="D2463" t="s">
+        <v>2465</v>
+      </c>
+    </row>
+    <row r="2464" spans="1:4">
+      <c r="A2464" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2464">
+        <v>63</v>
+      </c>
+      <c r="C2464">
+        <v>4341.2</v>
+      </c>
+      <c r="D2464" t="s">
+        <v>2466</v>
+      </c>
+    </row>
+    <row r="2465" spans="1:4">
+      <c r="A2465" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2465">
+        <v>64</v>
+      </c>
+      <c r="C2465">
+        <v>4370.3</v>
+      </c>
+      <c r="D2465" t="s">
+        <v>2467</v>
+      </c>
+    </row>
+    <row r="2466" spans="1:4">
+      <c r="A2466" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2466">
+        <v>65</v>
+      </c>
+      <c r="C2466">
+        <v>4399.1</v>
+      </c>
+      <c r="D2466" t="s">
+        <v>2468</v>
+      </c>
+    </row>
+    <row r="2467" spans="1:4">
+      <c r="A2467" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2467">
+        <v>66</v>
+      </c>
+      <c r="C2467">
+        <v>4350.3</v>
+      </c>
+      <c r="D2467" t="s">
+        <v>2469</v>
+      </c>
+    </row>
+    <row r="2468" spans="1:4">
+      <c r="A2468" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2468">
+        <v>67</v>
+      </c>
+      <c r="C2468">
+        <v>4339.2</v>
+      </c>
+      <c r="D2468" t="s">
+        <v>2470</v>
+      </c>
+    </row>
+    <row r="2469" spans="1:4">
+      <c r="A2469" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2469">
+        <v>68</v>
+      </c>
+      <c r="C2469">
+        <v>4280.9</v>
+      </c>
+      <c r="D2469" t="s">
+        <v>2471</v>
+      </c>
+    </row>
+    <row r="2470" spans="1:4">
+      <c r="A2470" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2470">
+        <v>69</v>
+      </c>
+      <c r="C2470">
+        <v>4173.4</v>
+      </c>
+      <c r="D2470" t="s">
+        <v>2472</v>
+      </c>
+    </row>
+    <row r="2471" spans="1:4">
+      <c r="A2471" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2471">
+        <v>70</v>
+      </c>
+      <c r="C2471">
+        <v>4098.8</v>
+      </c>
+      <c r="D2471" t="s">
+        <v>2473</v>
+      </c>
+    </row>
+    <row r="2472" spans="1:4">
+      <c r="A2472" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2472">
+        <v>71</v>
+      </c>
+      <c r="C2472">
+        <v>4064.3</v>
+      </c>
+      <c r="D2472" t="s">
+        <v>2474</v>
+      </c>
+    </row>
+    <row r="2473" spans="1:4">
+      <c r="A2473" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2473">
+        <v>72</v>
+      </c>
+      <c r="C2473">
+        <v>4018.9</v>
+      </c>
+      <c r="D2473" t="s">
+        <v>2475</v>
+      </c>
+    </row>
+    <row r="2474" spans="1:4">
+      <c r="A2474" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2474">
+        <v>73</v>
+      </c>
+      <c r="C2474">
+        <v>4634.8</v>
+      </c>
+      <c r="D2474" t="s">
+        <v>2476</v>
+      </c>
+    </row>
+    <row r="2475" spans="1:4">
+      <c r="A2475" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2475">
+        <v>74</v>
+      </c>
+      <c r="C2475">
+        <v>4575</v>
+      </c>
+      <c r="D2475" t="s">
+        <v>2477</v>
+      </c>
+    </row>
+    <row r="2476" spans="1:4">
+      <c r="A2476" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2476">
+        <v>75</v>
+      </c>
+      <c r="C2476">
+        <v>4556.5</v>
+      </c>
+      <c r="D2476" t="s">
+        <v>2478</v>
+      </c>
+    </row>
+    <row r="2477" spans="1:4">
+      <c r="A2477" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2477">
+        <v>76</v>
+      </c>
+      <c r="C2477">
+        <v>4545.9</v>
+      </c>
+      <c r="D2477" t="s">
+        <v>2479</v>
+      </c>
+    </row>
+    <row r="2478" spans="1:4">
+      <c r="A2478" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2478">
+        <v>77</v>
+      </c>
+      <c r="C2478">
+        <v>4471.2</v>
+      </c>
+      <c r="D2478" t="s">
+        <v>2480</v>
+      </c>
+    </row>
+    <row r="2479" spans="1:4">
+      <c r="A2479" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2479">
+        <v>78</v>
+      </c>
+      <c r="C2479">
+        <v>4489.7</v>
+      </c>
+      <c r="D2479" t="s">
+        <v>2481</v>
+      </c>
+    </row>
+    <row r="2480" spans="1:4">
+      <c r="A2480" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2480">
+        <v>79</v>
+      </c>
+      <c r="C2480">
+        <v>4416.6</v>
+      </c>
+      <c r="D2480" t="s">
+        <v>2482</v>
+      </c>
+    </row>
+    <row r="2481" spans="1:4">
+      <c r="A2481" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2481">
+        <v>80</v>
+      </c>
+      <c r="C2481">
+        <v>4389.2</v>
+      </c>
+      <c r="D2481" t="s">
+        <v>2483</v>
+      </c>
+    </row>
+    <row r="2482" spans="1:4">
+      <c r="A2482" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2482">
+        <v>81</v>
+      </c>
+      <c r="C2482">
+        <v>4435.1</v>
+      </c>
+      <c r="D2482" t="s">
+        <v>2484</v>
+      </c>
+    </row>
+    <row r="2483" spans="1:4">
+      <c r="A2483" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2483">
+        <v>82</v>
+      </c>
+      <c r="C2483">
+        <v>4456.2</v>
+      </c>
+      <c r="D2483" t="s">
+        <v>2485</v>
+      </c>
+    </row>
+    <row r="2484" spans="1:4">
+      <c r="A2484" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2484">
+        <v>83</v>
+      </c>
+      <c r="C2484">
+        <v>4498.5</v>
+      </c>
+      <c r="D2484" t="s">
+        <v>2486</v>
+      </c>
+    </row>
+    <row r="2485" spans="1:4">
+      <c r="A2485" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2485">
+        <v>84</v>
+      </c>
+      <c r="C2485">
+        <v>4540.7</v>
+      </c>
+      <c r="D2485" t="s">
+        <v>2487</v>
+      </c>
+    </row>
+    <row r="2486" spans="1:4">
+      <c r="A2486" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2486">
+        <v>85</v>
+      </c>
+      <c r="C2486">
+        <v>4644.6</v>
+      </c>
+      <c r="D2486" t="s">
+        <v>2488</v>
+      </c>
+    </row>
+    <row r="2487" spans="1:4">
+      <c r="A2487" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2487">
+        <v>86</v>
+      </c>
+      <c r="C2487">
+        <v>4662.3</v>
+      </c>
+      <c r="D2487" t="s">
+        <v>2489</v>
+      </c>
+    </row>
+    <row r="2488" spans="1:4">
+      <c r="A2488" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2488">
+        <v>87</v>
+      </c>
+      <c r="C2488">
+        <v>4714.8</v>
+      </c>
+      <c r="D2488" t="s">
+        <v>2490</v>
+      </c>
+    </row>
+    <row r="2489" spans="1:4">
+      <c r="A2489" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2489">
+        <v>88</v>
+      </c>
+      <c r="C2489">
+        <v>4683.5</v>
+      </c>
+      <c r="D2489" t="s">
+        <v>2491</v>
+      </c>
+    </row>
+    <row r="2490" spans="1:4">
+      <c r="A2490" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2490">
+        <v>89</v>
+      </c>
+      <c r="C2490">
+        <v>4501.9</v>
+      </c>
+      <c r="D2490" t="s">
+        <v>2492</v>
+      </c>
+    </row>
+    <row r="2491" spans="1:4">
+      <c r="A2491" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2491">
+        <v>90</v>
+      </c>
+      <c r="C2491">
+        <v>4463.7</v>
+      </c>
+      <c r="D2491" t="s">
+        <v>2493</v>
+      </c>
+    </row>
+    <row r="2492" spans="1:4">
+      <c r="A2492" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2492">
+        <v>91</v>
+      </c>
+      <c r="C2492">
+        <v>4430.4</v>
+      </c>
+      <c r="D2492" t="s">
+        <v>2494</v>
+      </c>
+    </row>
+    <row r="2493" spans="1:4">
+      <c r="A2493" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2493">
+        <v>92</v>
+      </c>
+      <c r="C2493">
+        <v>4463.1</v>
+      </c>
+      <c r="D2493" t="s">
+        <v>2495</v>
+      </c>
+    </row>
+    <row r="2494" spans="1:4">
+      <c r="A2494" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2494">
+        <v>93</v>
+      </c>
+      <c r="C2494">
+        <v>4369.7</v>
+      </c>
+      <c r="D2494" t="s">
+        <v>2496</v>
+      </c>
+    </row>
+    <row r="2495" spans="1:4">
+      <c r="A2495" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2495">
+        <v>94</v>
+      </c>
+      <c r="C2495">
+        <v>4295.6</v>
+      </c>
+      <c r="D2495" t="s">
+        <v>2497</v>
+      </c>
+    </row>
+    <row r="2496" spans="1:4">
+      <c r="A2496" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2496">
+        <v>95</v>
+      </c>
+      <c r="C2496">
+        <v>4290.6</v>
+      </c>
+      <c r="D2496" t="s">
+        <v>2498</v>
+      </c>
+    </row>
+    <row r="2497" spans="1:4">
+      <c r="A2497" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2497">
+        <v>96</v>
+      </c>
+      <c r="C2497">
+        <v>4312.5</v>
+      </c>
+      <c r="D2497" t="s">
+        <v>2499</v>
       </c>
     </row>
   </sheetData>

--- a/Market Fundamentals/Transelectrica_data/Cons_Prod_final/Weekly_Production_2026.xlsx
+++ b/Market Fundamentals/Transelectrica_data/Cons_Prod_final/Weekly_Production_2026.xlsx
@@ -42940,7 +42940,7 @@
         <v>1</v>
       </c>
       <c r="C2402">
-        <v>4927</v>
+        <v>4330.6</v>
       </c>
       <c r="D2402" t="s">
         <v>2404</v>
@@ -42954,7 +42954,7 @@
         <v>2</v>
       </c>
       <c r="C2403">
-        <v>4910.5</v>
+        <v>4389.7</v>
       </c>
       <c r="D2403" t="s">
         <v>2405</v>
@@ -42968,7 +42968,7 @@
         <v>3</v>
       </c>
       <c r="C2404">
-        <v>4874.6</v>
+        <v>4396.3</v>
       </c>
       <c r="D2404" t="s">
         <v>2406</v>
@@ -42982,7 +42982,7 @@
         <v>4</v>
       </c>
       <c r="C2405">
-        <v>4867.5</v>
+        <v>4409.2</v>
       </c>
       <c r="D2405" t="s">
         <v>2407</v>
@@ -42996,7 +42996,7 @@
         <v>5</v>
       </c>
       <c r="C2406">
-        <v>4791.5</v>
+        <v>4549.3</v>
       </c>
       <c r="D2406" t="s">
         <v>2408</v>
@@ -43010,7 +43010,7 @@
         <v>6</v>
       </c>
       <c r="C2407">
-        <v>4764.8</v>
+        <v>4578.6</v>
       </c>
       <c r="D2407" t="s">
         <v>2409</v>
@@ -43024,7 +43024,7 @@
         <v>7</v>
       </c>
       <c r="C2408">
-        <v>4747.6</v>
+        <v>4617.1</v>
       </c>
       <c r="D2408" t="s">
         <v>2410</v>
@@ -43038,7 +43038,7 @@
         <v>8</v>
       </c>
       <c r="C2409">
-        <v>4734.2</v>
+        <v>4667.5</v>
       </c>
       <c r="D2409" t="s">
         <v>2411</v>
@@ -43052,7 +43052,7 @@
         <v>9</v>
       </c>
       <c r="C2410">
-        <v>4615.9</v>
+        <v>4534.8</v>
       </c>
       <c r="D2410" t="s">
         <v>2412</v>
@@ -43066,7 +43066,7 @@
         <v>10</v>
       </c>
       <c r="C2411">
-        <v>4575</v>
+        <v>4552.4</v>
       </c>
       <c r="D2411" t="s">
         <v>2413</v>
@@ -43080,7 +43080,7 @@
         <v>11</v>
       </c>
       <c r="C2412">
-        <v>4597.2</v>
+        <v>4596.4</v>
       </c>
       <c r="D2412" t="s">
         <v>2414</v>
@@ -43094,7 +43094,7 @@
         <v>12</v>
       </c>
       <c r="C2413">
-        <v>4599.4</v>
+        <v>4624.6</v>
       </c>
       <c r="D2413" t="s">
         <v>2415</v>
@@ -43108,7 +43108,7 @@
         <v>13</v>
       </c>
       <c r="C2414">
-        <v>4577.9</v>
+        <v>4642.8</v>
       </c>
       <c r="D2414" t="s">
         <v>2416</v>
@@ -43122,7 +43122,7 @@
         <v>14</v>
       </c>
       <c r="C2415">
-        <v>4589.8</v>
+        <v>4644.9</v>
       </c>
       <c r="D2415" t="s">
         <v>2417</v>
@@ -43136,7 +43136,7 @@
         <v>15</v>
       </c>
       <c r="C2416">
-        <v>4597.7</v>
+        <v>4650.5</v>
       </c>
       <c r="D2416" t="s">
         <v>2418</v>
@@ -43150,7 +43150,7 @@
         <v>16</v>
       </c>
       <c r="C2417">
-        <v>4599.4</v>
+        <v>4662.2</v>
       </c>
       <c r="D2417" t="s">
         <v>2419</v>
@@ -43164,7 +43164,7 @@
         <v>17</v>
       </c>
       <c r="C2418">
-        <v>4563.9</v>
+        <v>4613.7</v>
       </c>
       <c r="D2418" t="s">
         <v>2420</v>
@@ -43178,7 +43178,7 @@
         <v>18</v>
       </c>
       <c r="C2419">
-        <v>4562.6</v>
+        <v>4623.8</v>
       </c>
       <c r="D2419" t="s">
         <v>2421</v>
@@ -43192,7 +43192,7 @@
         <v>19</v>
       </c>
       <c r="C2420">
-        <v>4562.4</v>
+        <v>4621.8</v>
       </c>
       <c r="D2420" t="s">
         <v>2422</v>
@@ -43206,7 +43206,7 @@
         <v>20</v>
       </c>
       <c r="C2421">
-        <v>4557.5</v>
+        <v>4629.5</v>
       </c>
       <c r="D2421" t="s">
         <v>2423</v>
@@ -43220,7 +43220,7 @@
         <v>21</v>
       </c>
       <c r="C2422">
-        <v>4576.3</v>
+        <v>4691</v>
       </c>
       <c r="D2422" t="s">
         <v>2424</v>
@@ -43234,7 +43234,7 @@
         <v>22</v>
       </c>
       <c r="C2423">
-        <v>4589.3</v>
+        <v>4709.5</v>
       </c>
       <c r="D2423" t="s">
         <v>2425</v>
@@ -43248,7 +43248,7 @@
         <v>23</v>
       </c>
       <c r="C2424">
-        <v>4612.3</v>
+        <v>4759</v>
       </c>
       <c r="D2424" t="s">
         <v>2426</v>
@@ -43262,7 +43262,7 @@
         <v>24</v>
       </c>
       <c r="C2425">
-        <v>4623.1</v>
+        <v>4809.7</v>
       </c>
       <c r="D2425" t="s">
         <v>2427</v>
@@ -43276,7 +43276,7 @@
         <v>25</v>
       </c>
       <c r="C2426">
-        <v>4696.6</v>
+        <v>5051.7</v>
       </c>
       <c r="D2426" t="s">
         <v>2428</v>
@@ -43290,7 +43290,7 @@
         <v>26</v>
       </c>
       <c r="C2427">
-        <v>4726.4</v>
+        <v>5073.8</v>
       </c>
       <c r="D2427" t="s">
         <v>2429</v>
@@ -43304,7 +43304,7 @@
         <v>27</v>
       </c>
       <c r="C2428">
-        <v>4739</v>
+        <v>5106.8</v>
       </c>
       <c r="D2428" t="s">
         <v>2430</v>
@@ -43318,7 +43318,7 @@
         <v>28</v>
       </c>
       <c r="C2429">
-        <v>4745.3</v>
+        <v>5177.1</v>
       </c>
       <c r="D2429" t="s">
         <v>2431</v>
@@ -43332,7 +43332,7 @@
         <v>29</v>
       </c>
       <c r="C2430">
-        <v>4733</v>
+        <v>5241.1</v>
       </c>
       <c r="D2430" t="s">
         <v>2432</v>
@@ -43346,7 +43346,7 @@
         <v>30</v>
       </c>
       <c r="C2431">
-        <v>4786.5</v>
+        <v>5277.5</v>
       </c>
       <c r="D2431" t="s">
         <v>2433</v>
@@ -43360,7 +43360,7 @@
         <v>31</v>
       </c>
       <c r="C2432">
-        <v>4835.9</v>
+        <v>5390</v>
       </c>
       <c r="D2432" t="s">
         <v>2434</v>
@@ -43374,7 +43374,7 @@
         <v>32</v>
       </c>
       <c r="C2433">
-        <v>4917.2</v>
+        <v>5467.9</v>
       </c>
       <c r="D2433" t="s">
         <v>2435</v>
@@ -43388,7 +43388,7 @@
         <v>33</v>
       </c>
       <c r="C2434">
-        <v>4692.3</v>
+        <v>5299.4</v>
       </c>
       <c r="D2434" t="s">
         <v>2436</v>
@@ -43402,7 +43402,7 @@
         <v>34</v>
       </c>
       <c r="C2435">
-        <v>4650.5</v>
+        <v>5363.1</v>
       </c>
       <c r="D2435" t="s">
         <v>2437</v>
@@ -43416,7 +43416,7 @@
         <v>35</v>
       </c>
       <c r="C2436">
-        <v>4716.2</v>
+        <v>5458</v>
       </c>
       <c r="D2436" t="s">
         <v>2438</v>
@@ -43430,7 +43430,7 @@
         <v>36</v>
       </c>
       <c r="C2437">
-        <v>4811.9</v>
+        <v>5553.6</v>
       </c>
       <c r="D2437" t="s">
         <v>2439</v>
@@ -43444,7 +43444,7 @@
         <v>37</v>
       </c>
       <c r="C2438">
-        <v>4650</v>
+        <v>5193.4</v>
       </c>
       <c r="D2438" t="s">
         <v>2440</v>
@@ -43458,7 +43458,7 @@
         <v>38</v>
       </c>
       <c r="C2439">
-        <v>4638.8</v>
+        <v>5235</v>
       </c>
       <c r="D2439" t="s">
         <v>2441</v>
@@ -43472,7 +43472,7 @@
         <v>39</v>
       </c>
       <c r="C2440">
-        <v>4677.3</v>
+        <v>5306.4</v>
       </c>
       <c r="D2440" t="s">
         <v>2442</v>
@@ -43486,7 +43486,7 @@
         <v>40</v>
       </c>
       <c r="C2441">
-        <v>4695.4</v>
+        <v>5390.7</v>
       </c>
       <c r="D2441" t="s">
         <v>2443</v>
@@ -43500,7 +43500,7 @@
         <v>41</v>
       </c>
       <c r="C2442">
-        <v>4566</v>
+        <v>5428.5</v>
       </c>
       <c r="D2442" t="s">
         <v>2444</v>
@@ -43514,7 +43514,7 @@
         <v>42</v>
       </c>
       <c r="C2443">
-        <v>4579.9</v>
+        <v>5460.5</v>
       </c>
       <c r="D2443" t="s">
         <v>2445</v>
@@ -43528,7 +43528,7 @@
         <v>43</v>
       </c>
       <c r="C2444">
-        <v>4474.2</v>
+        <v>5551.4</v>
       </c>
       <c r="D2444" t="s">
         <v>2446</v>
@@ -43542,7 +43542,7 @@
         <v>44</v>
       </c>
       <c r="C2445">
-        <v>4348.6</v>
+        <v>5590.3</v>
       </c>
       <c r="D2445" t="s">
         <v>2447</v>
@@ -43556,7 +43556,7 @@
         <v>45</v>
       </c>
       <c r="C2446">
-        <v>4145.3</v>
+        <v>5023.2</v>
       </c>
       <c r="D2446" t="s">
         <v>2448</v>
@@ -43570,7 +43570,7 @@
         <v>46</v>
       </c>
       <c r="C2447">
-        <v>4177.9</v>
+        <v>5020.9</v>
       </c>
       <c r="D2447" t="s">
         <v>2449</v>
@@ -43584,7 +43584,7 @@
         <v>47</v>
       </c>
       <c r="C2448">
-        <v>4225.5</v>
+        <v>4887.5</v>
       </c>
       <c r="D2448" t="s">
         <v>2450</v>
@@ -43598,7 +43598,7 @@
         <v>48</v>
       </c>
       <c r="C2449">
-        <v>4246.3</v>
+        <v>4971</v>
       </c>
       <c r="D2449" t="s">
         <v>2451</v>
@@ -43612,7 +43612,7 @@
         <v>49</v>
       </c>
       <c r="C2450">
-        <v>4344.6</v>
+        <v>4859.7</v>
       </c>
       <c r="D2450" t="s">
         <v>2452</v>
@@ -43626,7 +43626,7 @@
         <v>50</v>
       </c>
       <c r="C2451">
-        <v>4313.8</v>
+        <v>4790.2</v>
       </c>
       <c r="D2451" t="s">
         <v>2453</v>
@@ -43640,7 +43640,7 @@
         <v>51</v>
       </c>
       <c r="C2452">
-        <v>4337</v>
+        <v>4852.6</v>
       </c>
       <c r="D2452" t="s">
         <v>2454</v>
@@ -43654,7 +43654,7 @@
         <v>52</v>
       </c>
       <c r="C2453">
-        <v>4349.7</v>
+        <v>4891.8</v>
       </c>
       <c r="D2453" t="s">
         <v>2455</v>
@@ -43668,7 +43668,7 @@
         <v>53</v>
       </c>
       <c r="C2454">
-        <v>4267.6</v>
+        <v>4869.4</v>
       </c>
       <c r="D2454" t="s">
         <v>2456</v>
@@ -43682,7 +43682,7 @@
         <v>54</v>
       </c>
       <c r="C2455">
-        <v>4241.5</v>
+        <v>4849.6</v>
       </c>
       <c r="D2455" t="s">
         <v>2457</v>
@@ -43696,7 +43696,7 @@
         <v>55</v>
       </c>
       <c r="C2456">
-        <v>4268.3</v>
+        <v>4858</v>
       </c>
       <c r="D2456" t="s">
         <v>2458</v>
@@ -43710,7 +43710,7 @@
         <v>56</v>
       </c>
       <c r="C2457">
-        <v>4270.3</v>
+        <v>4814.6</v>
       </c>
       <c r="D2457" t="s">
         <v>2459</v>
@@ -43724,7 +43724,7 @@
         <v>57</v>
       </c>
       <c r="C2458">
-        <v>4198.9</v>
+        <v>4953</v>
       </c>
       <c r="D2458" t="s">
         <v>2460</v>
@@ -43738,7 +43738,7 @@
         <v>58</v>
       </c>
       <c r="C2459">
-        <v>4223.3</v>
+        <v>4928</v>
       </c>
       <c r="D2459" t="s">
         <v>2461</v>
@@ -43752,7 +43752,7 @@
         <v>59</v>
       </c>
       <c r="C2460">
-        <v>4248.9</v>
+        <v>4971.1</v>
       </c>
       <c r="D2460" t="s">
         <v>2462</v>
@@ -43766,7 +43766,7 @@
         <v>60</v>
       </c>
       <c r="C2461">
-        <v>4353.7</v>
+        <v>5005.8</v>
       </c>
       <c r="D2461" t="s">
         <v>2463</v>
@@ -43780,7 +43780,7 @@
         <v>61</v>
       </c>
       <c r="C2462">
-        <v>4324.1</v>
+        <v>4857.8</v>
       </c>
       <c r="D2462" t="s">
         <v>2464</v>
@@ -43794,7 +43794,7 @@
         <v>62</v>
       </c>
       <c r="C2463">
-        <v>4324.7</v>
+        <v>4963.1</v>
       </c>
       <c r="D2463" t="s">
         <v>2465</v>
@@ -43808,7 +43808,7 @@
         <v>63</v>
       </c>
       <c r="C2464">
-        <v>4313.4</v>
+        <v>4920.8</v>
       </c>
       <c r="D2464" t="s">
         <v>2466</v>
@@ -43822,7 +43822,7 @@
         <v>64</v>
       </c>
       <c r="C2465">
-        <v>4261.1</v>
+        <v>4773.2</v>
       </c>
       <c r="D2465" t="s">
         <v>2467</v>
@@ -43836,7 +43836,7 @@
         <v>65</v>
       </c>
       <c r="C2466">
-        <v>4317.1</v>
+        <v>4681.1</v>
       </c>
       <c r="D2466" t="s">
         <v>2468</v>
@@ -43850,7 +43850,7 @@
         <v>66</v>
       </c>
       <c r="C2467">
-        <v>4274.9</v>
+        <v>4636.7</v>
       </c>
       <c r="D2467" t="s">
         <v>2469</v>
@@ -43864,7 +43864,7 @@
         <v>67</v>
       </c>
       <c r="C2468">
-        <v>4219.5</v>
+        <v>4565.4</v>
       </c>
       <c r="D2468" t="s">
         <v>2470</v>
@@ -43878,7 +43878,7 @@
         <v>68</v>
       </c>
       <c r="C2469">
-        <v>4190.7</v>
+        <v>4542.3</v>
       </c>
       <c r="D2469" t="s">
         <v>2471</v>
@@ -43892,7 +43892,7 @@
         <v>69</v>
       </c>
       <c r="C2470">
-        <v>4446.9</v>
+        <v>4726.1</v>
       </c>
       <c r="D2470" t="s">
         <v>2472</v>
@@ -43906,7 +43906,7 @@
         <v>70</v>
       </c>
       <c r="C2471">
-        <v>4337.2</v>
+        <v>4757.4</v>
       </c>
       <c r="D2471" t="s">
         <v>2473</v>
@@ -43920,7 +43920,7 @@
         <v>71</v>
       </c>
       <c r="C2472">
-        <v>4263.9</v>
+        <v>4647.5</v>
       </c>
       <c r="D2472" t="s">
         <v>2474</v>
@@ -43934,7 +43934,7 @@
         <v>72</v>
       </c>
       <c r="C2473">
-        <v>4209.8</v>
+        <v>4504</v>
       </c>
       <c r="D2473" t="s">
         <v>2475</v>
@@ -43948,7 +43948,7 @@
         <v>73</v>
       </c>
       <c r="C2474">
-        <v>4274.9</v>
+        <v>5211.4</v>
       </c>
       <c r="D2474" t="s">
         <v>2476</v>
@@ -43962,7 +43962,7 @@
         <v>74</v>
       </c>
       <c r="C2475">
-        <v>4210</v>
+        <v>5069.4</v>
       </c>
       <c r="D2475" t="s">
         <v>2477</v>
@@ -43976,7 +43976,7 @@
         <v>75</v>
       </c>
       <c r="C2476">
-        <v>4175</v>
+        <v>4939.2</v>
       </c>
       <c r="D2476" t="s">
         <v>2478</v>
@@ -43990,7 +43990,7 @@
         <v>76</v>
       </c>
       <c r="C2477">
-        <v>4171.1</v>
+        <v>4862.4</v>
       </c>
       <c r="D2477" t="s">
         <v>2479</v>
@@ -44004,7 +44004,7 @@
         <v>77</v>
       </c>
       <c r="C2478">
-        <v>4678.8</v>
+        <v>5138</v>
       </c>
       <c r="D2478" t="s">
         <v>2480</v>
@@ -44018,7 +44018,7 @@
         <v>78</v>
       </c>
       <c r="C2479">
-        <v>4700.9</v>
+        <v>5111.8</v>
       </c>
       <c r="D2479" t="s">
         <v>2481</v>
@@ -44032,7 +44032,7 @@
         <v>79</v>
       </c>
       <c r="C2480">
-        <v>4690.7</v>
+        <v>5019.2</v>
       </c>
       <c r="D2480" t="s">
         <v>2482</v>
@@ -44046,7 +44046,7 @@
         <v>80</v>
       </c>
       <c r="C2481">
-        <v>4713.1</v>
+        <v>4992.7</v>
       </c>
       <c r="D2481" t="s">
         <v>2483</v>
@@ -44060,7 +44060,7 @@
         <v>81</v>
       </c>
       <c r="C2482">
-        <v>4910.7</v>
+        <v>5500.6</v>
       </c>
       <c r="D2482" t="s">
         <v>2484</v>
@@ -44074,7 +44074,7 @@
         <v>82</v>
       </c>
       <c r="C2483">
-        <v>4968</v>
+        <v>5528.1</v>
       </c>
       <c r="D2483" t="s">
         <v>2485</v>
@@ -44088,7 +44088,7 @@
         <v>83</v>
       </c>
       <c r="C2484">
-        <v>5015.1</v>
+        <v>5595.5</v>
       </c>
       <c r="D2484" t="s">
         <v>2486</v>
@@ -44102,7 +44102,7 @@
         <v>84</v>
       </c>
       <c r="C2485">
-        <v>5088.2</v>
+        <v>5729.8</v>
       </c>
       <c r="D2485" t="s">
         <v>2487</v>
@@ -44116,7 +44116,7 @@
         <v>85</v>
       </c>
       <c r="C2486">
-        <v>5186.7</v>
+        <v>5838.5</v>
       </c>
       <c r="D2486" t="s">
         <v>2488</v>
@@ -44130,7 +44130,7 @@
         <v>86</v>
       </c>
       <c r="C2487">
-        <v>5163.8</v>
+        <v>5859.6</v>
       </c>
       <c r="D2487" t="s">
         <v>2489</v>
@@ -44144,7 +44144,7 @@
         <v>87</v>
       </c>
       <c r="C2488">
-        <v>5171.2</v>
+        <v>5926</v>
       </c>
       <c r="D2488" t="s">
         <v>2490</v>
@@ -44158,7 +44158,7 @@
         <v>88</v>
       </c>
       <c r="C2489">
-        <v>5126.3</v>
+        <v>5924.5</v>
       </c>
       <c r="D2489" t="s">
         <v>2491</v>
@@ -44172,7 +44172,7 @@
         <v>89</v>
       </c>
       <c r="C2490">
-        <v>4926</v>
+        <v>5807.6</v>
       </c>
       <c r="D2490" t="s">
         <v>2492</v>
@@ -44186,7 +44186,7 @@
         <v>90</v>
       </c>
       <c r="C2491">
-        <v>4974</v>
+        <v>5731.2</v>
       </c>
       <c r="D2491" t="s">
         <v>2493</v>
@@ -44200,7 +44200,7 @@
         <v>91</v>
       </c>
       <c r="C2492">
-        <v>4975.9</v>
+        <v>5713.4</v>
       </c>
       <c r="D2492" t="s">
         <v>2494</v>
@@ -44214,7 +44214,7 @@
         <v>92</v>
       </c>
       <c r="C2493">
-        <v>4959.3</v>
+        <v>5686.7</v>
       </c>
       <c r="D2493" t="s">
         <v>2495</v>
@@ -44228,7 +44228,7 @@
         <v>93</v>
       </c>
       <c r="C2494">
-        <v>4683.3</v>
+        <v>5385.9</v>
       </c>
       <c r="D2494" t="s">
         <v>2496</v>
@@ -44242,7 +44242,7 @@
         <v>94</v>
       </c>
       <c r="C2495">
-        <v>4585.7</v>
+        <v>5336.8</v>
       </c>
       <c r="D2495" t="s">
         <v>2497</v>
@@ -44256,7 +44256,7 @@
         <v>95</v>
       </c>
       <c r="C2496">
-        <v>4611.7</v>
+        <v>5300.4</v>
       </c>
       <c r="D2496" t="s">
         <v>2498</v>
@@ -44270,7 +44270,7 @@
         <v>96</v>
       </c>
       <c r="C2497">
-        <v>4584.8</v>
+        <v>5277.3</v>
       </c>
       <c r="D2497" t="s">
         <v>2499</v>
@@ -44284,7 +44284,7 @@
         <v>1</v>
       </c>
       <c r="C2498">
-        <v>5107.6</v>
+        <v>4420.6</v>
       </c>
       <c r="D2498" t="s">
         <v>2500</v>
@@ -44298,7 +44298,7 @@
         <v>2</v>
       </c>
       <c r="C2499">
-        <v>5179.2</v>
+        <v>4509.7</v>
       </c>
       <c r="D2499" t="s">
         <v>2501</v>
@@ -44312,7 +44312,7 @@
         <v>3</v>
       </c>
       <c r="C2500">
-        <v>5180.8</v>
+        <v>4496.3</v>
       </c>
       <c r="D2500" t="s">
         <v>2502</v>
@@ -44326,7 +44326,7 @@
         <v>4</v>
       </c>
       <c r="C2501">
-        <v>5176.2</v>
+        <v>4489.2</v>
       </c>
       <c r="D2501" t="s">
         <v>2503</v>
@@ -44340,7 +44340,7 @@
         <v>5</v>
       </c>
       <c r="C2502">
-        <v>5251.5</v>
+        <v>4649.3</v>
       </c>
       <c r="D2502" t="s">
         <v>2504</v>
@@ -44354,7 +44354,7 @@
         <v>6</v>
       </c>
       <c r="C2503">
-        <v>5245.4</v>
+        <v>4668.6</v>
       </c>
       <c r="D2503" t="s">
         <v>2505</v>
@@ -44368,7 +44368,7 @@
         <v>7</v>
       </c>
       <c r="C2504">
-        <v>5245.1</v>
+        <v>4667.1</v>
       </c>
       <c r="D2504" t="s">
         <v>2506</v>
@@ -44382,7 +44382,7 @@
         <v>8</v>
       </c>
       <c r="C2505">
-        <v>5249.2</v>
+        <v>4687.5</v>
       </c>
       <c r="D2505" t="s">
         <v>2507</v>
@@ -44396,7 +44396,7 @@
         <v>9</v>
       </c>
       <c r="C2506">
-        <v>5118.8</v>
+        <v>4534.8</v>
       </c>
       <c r="D2506" t="s">
         <v>2508</v>
@@ -44410,7 +44410,7 @@
         <v>10</v>
       </c>
       <c r="C2507">
-        <v>5124.1</v>
+        <v>4532.4</v>
       </c>
       <c r="D2507" t="s">
         <v>2509</v>
@@ -44424,7 +44424,7 @@
         <v>11</v>
       </c>
       <c r="C2508">
-        <v>5145.6</v>
+        <v>4556.4</v>
       </c>
       <c r="D2508" t="s">
         <v>2510</v>
@@ -44438,7 +44438,7 @@
         <v>12</v>
       </c>
       <c r="C2509">
-        <v>5171.9</v>
+        <v>4594.6</v>
       </c>
       <c r="D2509" t="s">
         <v>2511</v>
@@ -44452,7 +44452,7 @@
         <v>13</v>
       </c>
       <c r="C2510">
-        <v>5007.1</v>
+        <v>4632.8</v>
       </c>
       <c r="D2510" t="s">
         <v>2512</v>
@@ -44466,7 +44466,7 @@
         <v>14</v>
       </c>
       <c r="C2511">
-        <v>5042.6</v>
+        <v>4644.9</v>
       </c>
       <c r="D2511" t="s">
         <v>2513</v>
@@ -44480,7 +44480,7 @@
         <v>15</v>
       </c>
       <c r="C2512">
-        <v>5043.3</v>
+        <v>4650.5</v>
       </c>
       <c r="D2512" t="s">
         <v>2514</v>
@@ -44494,7 +44494,7 @@
         <v>16</v>
       </c>
       <c r="C2513">
-        <v>5024.4</v>
+        <v>4652.2</v>
       </c>
       <c r="D2513" t="s">
         <v>2515</v>
@@ -44508,7 +44508,7 @@
         <v>17</v>
       </c>
       <c r="C2514">
-        <v>5088.3</v>
+        <v>4593.7</v>
       </c>
       <c r="D2514" t="s">
         <v>2516</v>
@@ -44522,7 +44522,7 @@
         <v>18</v>
       </c>
       <c r="C2515">
-        <v>5086.3</v>
+        <v>4593.8</v>
       </c>
       <c r="D2515" t="s">
         <v>2517</v>
@@ -44536,7 +44536,7 @@
         <v>19</v>
       </c>
       <c r="C2516">
-        <v>5089.5</v>
+        <v>4591.8</v>
       </c>
       <c r="D2516" t="s">
         <v>2518</v>
@@ -44550,7 +44550,7 @@
         <v>20</v>
       </c>
       <c r="C2517">
-        <v>5069.2</v>
+        <v>4609.5</v>
       </c>
       <c r="D2517" t="s">
         <v>2519</v>
@@ -44564,7 +44564,7 @@
         <v>21</v>
       </c>
       <c r="C2518">
-        <v>5097.2</v>
+        <v>4701</v>
       </c>
       <c r="D2518" t="s">
         <v>2520</v>
@@ -44578,7 +44578,7 @@
         <v>22</v>
       </c>
       <c r="C2519">
-        <v>5130.2</v>
+        <v>4749.5</v>
       </c>
       <c r="D2519" t="s">
         <v>2521</v>
@@ -44592,7 +44592,7 @@
         <v>23</v>
       </c>
       <c r="C2520">
-        <v>5166.6</v>
+        <v>4819</v>
       </c>
       <c r="D2520" t="s">
         <v>2522</v>
@@ -44606,7 +44606,7 @@
         <v>24</v>
       </c>
       <c r="C2521">
-        <v>5181.9</v>
+        <v>4879.7</v>
       </c>
       <c r="D2521" t="s">
         <v>2523</v>
@@ -44620,7 +44620,7 @@
         <v>25</v>
       </c>
       <c r="C2522">
-        <v>5430.7</v>
+        <v>5151.7</v>
       </c>
       <c r="D2522" t="s">
         <v>2524</v>
@@ -44634,7 +44634,7 @@
         <v>26</v>
       </c>
       <c r="C2523">
-        <v>5460.8</v>
+        <v>5183.8</v>
       </c>
       <c r="D2523" t="s">
         <v>2525</v>
@@ -44648,7 +44648,7 @@
         <v>27</v>
       </c>
       <c r="C2524">
-        <v>5492.7</v>
+        <v>5236.8</v>
       </c>
       <c r="D2524" t="s">
         <v>2526</v>
@@ -44662,7 +44662,7 @@
         <v>28</v>
       </c>
       <c r="C2525">
-        <v>5505.1</v>
+        <v>5277.1</v>
       </c>
       <c r="D2525" t="s">
         <v>2527</v>
@@ -44676,7 +44676,7 @@
         <v>29</v>
       </c>
       <c r="C2526">
-        <v>5449.7</v>
+        <v>5251.1</v>
       </c>
       <c r="D2526" t="s">
         <v>2528</v>
@@ -44690,7 +44690,7 @@
         <v>30</v>
       </c>
       <c r="C2527">
-        <v>5475.1</v>
+        <v>5267.5</v>
       </c>
       <c r="D2527" t="s">
         <v>2529</v>
@@ -44704,7 +44704,7 @@
         <v>31</v>
       </c>
       <c r="C2528">
-        <v>5545</v>
+        <v>5390</v>
       </c>
       <c r="D2528" t="s">
         <v>2530</v>
@@ -44718,7 +44718,7 @@
         <v>32</v>
       </c>
       <c r="C2529">
-        <v>5633.1</v>
+        <v>5467.9</v>
       </c>
       <c r="D2529" t="s">
         <v>2531</v>
@@ -44732,7 +44732,7 @@
         <v>33</v>
       </c>
       <c r="C2530">
-        <v>5366.6</v>
+        <v>5299.4</v>
       </c>
       <c r="D2530" t="s">
         <v>2532</v>
@@ -44746,7 +44746,7 @@
         <v>34</v>
       </c>
       <c r="C2531">
-        <v>5255.8</v>
+        <v>5353.1</v>
       </c>
       <c r="D2531" t="s">
         <v>2533</v>
@@ -44760,7 +44760,7 @@
         <v>35</v>
       </c>
       <c r="C2532">
-        <v>5341.9</v>
+        <v>5458</v>
       </c>
       <c r="D2532" t="s">
         <v>2534</v>
@@ -44774,7 +44774,7 @@
         <v>36</v>
       </c>
       <c r="C2533">
-        <v>5359.6</v>
+        <v>5553.6</v>
       </c>
       <c r="D2533" t="s">
         <v>2535</v>
@@ -44788,7 +44788,7 @@
         <v>37</v>
       </c>
       <c r="C2534">
-        <v>5498.6</v>
+        <v>5213.4</v>
       </c>
       <c r="D2534" t="s">
         <v>2536</v>
@@ -44802,7 +44802,7 @@
         <v>38</v>
       </c>
       <c r="C2535">
-        <v>5497.8</v>
+        <v>5265</v>
       </c>
       <c r="D2535" t="s">
         <v>2537</v>
@@ -44816,7 +44816,7 @@
         <v>39</v>
       </c>
       <c r="C2536">
-        <v>5470.7</v>
+        <v>5356.4</v>
       </c>
       <c r="D2536" t="s">
         <v>2538</v>
@@ -44830,7 +44830,7 @@
         <v>40</v>
       </c>
       <c r="C2537">
-        <v>5474.3</v>
+        <v>5430.7</v>
       </c>
       <c r="D2537" t="s">
         <v>2539</v>
@@ -44844,7 +44844,7 @@
         <v>41</v>
       </c>
       <c r="C2538">
-        <v>5423.8</v>
+        <v>5458.5</v>
       </c>
       <c r="D2538" t="s">
         <v>2540</v>
@@ -44858,7 +44858,7 @@
         <v>42</v>
       </c>
       <c r="C2539">
-        <v>5311.7</v>
+        <v>5490.5</v>
       </c>
       <c r="D2539" t="s">
         <v>2541</v>
@@ -44872,7 +44872,7 @@
         <v>43</v>
       </c>
       <c r="C2540">
-        <v>5321</v>
+        <v>5571.4</v>
       </c>
       <c r="D2540" t="s">
         <v>2542</v>
@@ -44886,7 +44886,7 @@
         <v>44</v>
       </c>
       <c r="C2541">
-        <v>5249.1</v>
+        <v>5620.3</v>
       </c>
       <c r="D2541" t="s">
         <v>2543</v>
@@ -44900,7 +44900,7 @@
         <v>45</v>
       </c>
       <c r="C2542">
-        <v>4813.5</v>
+        <v>5083.2</v>
       </c>
       <c r="D2542" t="s">
         <v>2544</v>
@@ -44914,7 +44914,7 @@
         <v>46</v>
       </c>
       <c r="C2543">
-        <v>4808.1</v>
+        <v>5090.9</v>
       </c>
       <c r="D2543" t="s">
         <v>2545</v>
@@ -44928,7 +44928,7 @@
         <v>47</v>
       </c>
       <c r="C2544">
-        <v>4856.8</v>
+        <v>4927.5</v>
       </c>
       <c r="D2544" t="s">
         <v>2546</v>
@@ -44942,7 +44942,7 @@
         <v>48</v>
       </c>
       <c r="C2545">
-        <v>4808.6</v>
+        <v>4981</v>
       </c>
       <c r="D2545" t="s">
         <v>2547</v>
@@ -44956,7 +44956,7 @@
         <v>49</v>
       </c>
       <c r="C2546">
-        <v>4679.7</v>
+        <v>4859.7</v>
       </c>
       <c r="D2546" t="s">
         <v>2548</v>
@@ -44970,7 +44970,7 @@
         <v>50</v>
       </c>
       <c r="C2547">
-        <v>4645.8</v>
+        <v>4790.2</v>
       </c>
       <c r="D2547" t="s">
         <v>2549</v>
@@ -44984,7 +44984,7 @@
         <v>51</v>
       </c>
       <c r="C2548">
-        <v>4610.6</v>
+        <v>4862.6</v>
       </c>
       <c r="D2548" t="s">
         <v>2550</v>
@@ -44998,7 +44998,7 @@
         <v>52</v>
       </c>
       <c r="C2549">
-        <v>4580.3</v>
+        <v>4891.8</v>
       </c>
       <c r="D2549" t="s">
         <v>2551</v>
@@ -45012,7 +45012,7 @@
         <v>53</v>
       </c>
       <c r="C2550">
-        <v>4469.6</v>
+        <v>4839.4</v>
       </c>
       <c r="D2550" t="s">
         <v>2552</v>
@@ -45026,7 +45026,7 @@
         <v>54</v>
       </c>
       <c r="C2551">
-        <v>4420.7</v>
+        <v>4829.6</v>
       </c>
       <c r="D2551" t="s">
         <v>2553</v>
@@ -45040,7 +45040,7 @@
         <v>55</v>
       </c>
       <c r="C2552">
-        <v>4391.7</v>
+        <v>4838</v>
       </c>
       <c r="D2552" t="s">
         <v>2554</v>
@@ -45054,7 +45054,7 @@
         <v>56</v>
       </c>
       <c r="C2553">
-        <v>4370.5</v>
+        <v>4824.6</v>
       </c>
       <c r="D2553" t="s">
         <v>2555</v>
@@ -45068,7 +45068,7 @@
         <v>57</v>
       </c>
       <c r="C2554">
-        <v>4268.1</v>
+        <v>4983</v>
       </c>
       <c r="D2554" t="s">
         <v>2556</v>
@@ -45082,7 +45082,7 @@
         <v>58</v>
       </c>
       <c r="C2555">
-        <v>4273.8</v>
+        <v>4988</v>
       </c>
       <c r="D2555" t="s">
         <v>2557</v>
@@ -45096,7 +45096,7 @@
         <v>59</v>
       </c>
       <c r="C2556">
-        <v>4268.3</v>
+        <v>5061.1</v>
       </c>
       <c r="D2556" t="s">
         <v>2558</v>
@@ -45110,7 +45110,7 @@
         <v>60</v>
       </c>
       <c r="C2557">
-        <v>4274.1</v>
+        <v>5105.8</v>
       </c>
       <c r="D2557" t="s">
         <v>2559</v>
@@ -45124,7 +45124,7 @@
         <v>61</v>
       </c>
       <c r="C2558">
-        <v>4350.6</v>
+        <v>4947.8</v>
       </c>
       <c r="D2558" t="s">
         <v>2560</v>
@@ -45138,7 +45138,7 @@
         <v>62</v>
       </c>
       <c r="C2559">
-        <v>4311.5</v>
+        <v>5053.1</v>
       </c>
       <c r="D2559" t="s">
         <v>2561</v>
@@ -45152,7 +45152,7 @@
         <v>63</v>
       </c>
       <c r="C2560">
-        <v>4356</v>
+        <v>5020.8</v>
       </c>
       <c r="D2560" t="s">
         <v>2562</v>
@@ -45166,7 +45166,7 @@
         <v>64</v>
       </c>
       <c r="C2561">
-        <v>4345</v>
+        <v>4893.2</v>
       </c>
       <c r="D2561" t="s">
         <v>2563</v>
@@ -45180,7 +45180,7 @@
         <v>65</v>
       </c>
       <c r="C2562">
-        <v>4381.2</v>
+        <v>4811.1</v>
       </c>
       <c r="D2562" t="s">
         <v>2564</v>
@@ -45194,7 +45194,7 @@
         <v>66</v>
       </c>
       <c r="C2563">
-        <v>4325.7</v>
+        <v>4766.7</v>
       </c>
       <c r="D2563" t="s">
         <v>2565</v>
@@ -45208,7 +45208,7 @@
         <v>67</v>
       </c>
       <c r="C2564">
-        <v>4282.2</v>
+        <v>4705.4</v>
       </c>
       <c r="D2564" t="s">
         <v>2566</v>
@@ -45222,7 +45222,7 @@
         <v>68</v>
       </c>
       <c r="C2565">
-        <v>4278.4</v>
+        <v>4682.3</v>
       </c>
       <c r="D2565" t="s">
         <v>2567</v>
@@ -45236,7 +45236,7 @@
         <v>69</v>
       </c>
       <c r="C2566">
-        <v>4495.1</v>
+        <v>4886.1</v>
       </c>
       <c r="D2566" t="s">
         <v>2568</v>
@@ -45250,7 +45250,7 @@
         <v>70</v>
       </c>
       <c r="C2567">
-        <v>4452.7</v>
+        <v>4927.4</v>
       </c>
       <c r="D2567" t="s">
         <v>2569</v>
@@ -45264,7 +45264,7 @@
         <v>71</v>
       </c>
       <c r="C2568">
-        <v>4463.3</v>
+        <v>4827.5</v>
       </c>
       <c r="D2568" t="s">
         <v>2570</v>
@@ -45278,7 +45278,7 @@
         <v>72</v>
       </c>
       <c r="C2569">
-        <v>4475.1</v>
+        <v>4684</v>
       </c>
       <c r="D2569" t="s">
         <v>2571</v>
@@ -45292,7 +45292,7 @@
         <v>73</v>
       </c>
       <c r="C2570">
-        <v>5134.6</v>
+        <v>5341.4</v>
       </c>
       <c r="D2570" t="s">
         <v>2572</v>
@@ -45306,7 +45306,7 @@
         <v>74</v>
       </c>
       <c r="C2571">
-        <v>5123.7</v>
+        <v>5209.4</v>
       </c>
       <c r="D2571" t="s">
         <v>2573</v>
@@ -45320,7 +45320,7 @@
         <v>75</v>
       </c>
       <c r="C2572">
-        <v>5124.6</v>
+        <v>5069.2</v>
       </c>
       <c r="D2572" t="s">
         <v>2574</v>
@@ -45334,7 +45334,7 @@
         <v>76</v>
       </c>
       <c r="C2573">
-        <v>5178.2</v>
+        <v>4982.4</v>
       </c>
       <c r="D2573" t="s">
         <v>2575</v>
@@ -45348,7 +45348,7 @@
         <v>77</v>
       </c>
       <c r="C2574">
-        <v>5431.7</v>
+        <v>5278</v>
       </c>
       <c r="D2574" t="s">
         <v>2576</v>
@@ -45362,7 +45362,7 @@
         <v>78</v>
       </c>
       <c r="C2575">
-        <v>5462.4</v>
+        <v>5261.8</v>
       </c>
       <c r="D2575" t="s">
         <v>2577</v>
@@ -45376,7 +45376,7 @@
         <v>79</v>
       </c>
       <c r="C2576">
-        <v>5437.4</v>
+        <v>5189.2</v>
       </c>
       <c r="D2576" t="s">
         <v>2578</v>
@@ -45390,7 +45390,7 @@
         <v>80</v>
       </c>
       <c r="C2577">
-        <v>5466.3</v>
+        <v>5172.7</v>
       </c>
       <c r="D2577" t="s">
         <v>2579</v>
@@ -45404,7 +45404,7 @@
         <v>81</v>
       </c>
       <c r="C2578">
-        <v>5453.1</v>
+        <v>5700.6</v>
       </c>
       <c r="D2578" t="s">
         <v>2580</v>
@@ -45418,7 +45418,7 @@
         <v>82</v>
       </c>
       <c r="C2579">
-        <v>5445.8</v>
+        <v>5728.1</v>
       </c>
       <c r="D2579" t="s">
         <v>2581</v>
@@ -45432,7 +45432,7 @@
         <v>83</v>
       </c>
       <c r="C2580">
-        <v>5470.2</v>
+        <v>5785.5</v>
       </c>
       <c r="D2580" t="s">
         <v>2582</v>
@@ -45446,7 +45446,7 @@
         <v>84</v>
       </c>
       <c r="C2581">
-        <v>5503.6</v>
+        <v>5909.8</v>
       </c>
       <c r="D2581" t="s">
         <v>2583</v>
@@ -45460,7 +45460,7 @@
         <v>85</v>
       </c>
       <c r="C2582">
-        <v>5615</v>
+        <v>5938.5</v>
       </c>
       <c r="D2582" t="s">
         <v>2584</v>
@@ -45474,7 +45474,7 @@
         <v>86</v>
       </c>
       <c r="C2583">
-        <v>5557.5</v>
+        <v>5959.6</v>
       </c>
       <c r="D2583" t="s">
         <v>2585</v>
@@ -45488,7 +45488,7 @@
         <v>87</v>
       </c>
       <c r="C2584">
-        <v>5561.4</v>
+        <v>6016</v>
       </c>
       <c r="D2584" t="s">
         <v>2586</v>
@@ -45502,7 +45502,7 @@
         <v>88</v>
       </c>
       <c r="C2585">
-        <v>5509.9</v>
+        <v>6034.5</v>
       </c>
       <c r="D2585" t="s">
         <v>2587</v>
@@ -45516,7 +45516,7 @@
         <v>89</v>
       </c>
       <c r="C2586">
-        <v>5341.8</v>
+        <v>5957.6</v>
       </c>
       <c r="D2586" t="s">
         <v>2588</v>
@@ -45530,7 +45530,7 @@
         <v>90</v>
       </c>
       <c r="C2587">
-        <v>5250.4</v>
+        <v>5941.2</v>
       </c>
       <c r="D2587" t="s">
         <v>2589</v>
@@ -45544,7 +45544,7 @@
         <v>91</v>
       </c>
       <c r="C2588">
-        <v>5248.5</v>
+        <v>5933.4</v>
       </c>
       <c r="D2588" t="s">
         <v>2590</v>
@@ -45558,7 +45558,7 @@
         <v>92</v>
       </c>
       <c r="C2589">
-        <v>5150.2</v>
+        <v>5906.7</v>
       </c>
       <c r="D2589" t="s">
         <v>2591</v>
@@ -45572,7 +45572,7 @@
         <v>93</v>
       </c>
       <c r="C2590">
-        <v>4752.8</v>
+        <v>5545.9</v>
       </c>
       <c r="D2590" t="s">
         <v>2592</v>
@@ -45586,7 +45586,7 @@
         <v>94</v>
       </c>
       <c r="C2591">
-        <v>4668.9</v>
+        <v>5476.8</v>
       </c>
       <c r="D2591" t="s">
         <v>2593</v>
@@ -45600,7 +45600,7 @@
         <v>95</v>
       </c>
       <c r="C2592">
-        <v>4743.5</v>
+        <v>5460.4</v>
       </c>
       <c r="D2592" t="s">
         <v>2594</v>
@@ -45614,7 +45614,7 @@
         <v>96</v>
       </c>
       <c r="C2593">
-        <v>4682.3</v>
+        <v>5437.3</v>
       </c>
       <c r="D2593" t="s">
         <v>2595</v>
@@ -45628,7 +45628,7 @@
         <v>1</v>
       </c>
       <c r="C2594">
-        <v>5167.6</v>
+        <v>4580.6</v>
       </c>
       <c r="D2594" t="s">
         <v>2596</v>
@@ -45642,7 +45642,7 @@
         <v>2</v>
       </c>
       <c r="C2595">
-        <v>5239.2</v>
+        <v>4649.7</v>
       </c>
       <c r="D2595" t="s">
         <v>2597</v>
@@ -45656,7 +45656,7 @@
         <v>3</v>
       </c>
       <c r="C2596">
-        <v>5240.8</v>
+        <v>4666.3</v>
       </c>
       <c r="D2596" t="s">
         <v>2598</v>
@@ -45670,7 +45670,7 @@
         <v>4</v>
       </c>
       <c r="C2597">
-        <v>5236.2</v>
+        <v>4669.2</v>
       </c>
       <c r="D2597" t="s">
         <v>2599</v>
@@ -45684,7 +45684,7 @@
         <v>5</v>
       </c>
       <c r="C2598">
-        <v>5311.5</v>
+        <v>4819.3</v>
       </c>
       <c r="D2598" t="s">
         <v>2600</v>
@@ -45698,7 +45698,7 @@
         <v>6</v>
       </c>
       <c r="C2599">
-        <v>5305.4</v>
+        <v>4828.6</v>
       </c>
       <c r="D2599" t="s">
         <v>2601</v>
@@ -45712,7 +45712,7 @@
         <v>7</v>
       </c>
       <c r="C2600">
-        <v>5305.1</v>
+        <v>4827.1</v>
       </c>
       <c r="D2600" t="s">
         <v>2602</v>
@@ -45726,7 +45726,7 @@
         <v>8</v>
       </c>
       <c r="C2601">
-        <v>5309.2</v>
+        <v>4847.5</v>
       </c>
       <c r="D2601" t="s">
         <v>2603</v>
@@ -45740,7 +45740,7 @@
         <v>9</v>
       </c>
       <c r="C2602">
-        <v>5178.8</v>
+        <v>4694.8</v>
       </c>
       <c r="D2602" t="s">
         <v>2604</v>
@@ -45754,7 +45754,7 @@
         <v>10</v>
       </c>
       <c r="C2603">
-        <v>5184.1</v>
+        <v>4682.4</v>
       </c>
       <c r="D2603" t="s">
         <v>2605</v>
@@ -45768,7 +45768,7 @@
         <v>11</v>
       </c>
       <c r="C2604">
-        <v>5205.6</v>
+        <v>4696.4</v>
       </c>
       <c r="D2604" t="s">
         <v>2606</v>
@@ -45782,7 +45782,7 @@
         <v>12</v>
       </c>
       <c r="C2605">
-        <v>5231.9</v>
+        <v>4714.6</v>
       </c>
       <c r="D2605" t="s">
         <v>2607</v>
@@ -45796,7 +45796,7 @@
         <v>13</v>
       </c>
       <c r="C2606">
-        <v>5067.1</v>
+        <v>4742.8</v>
       </c>
       <c r="D2606" t="s">
         <v>2608</v>
@@ -45810,7 +45810,7 @@
         <v>14</v>
       </c>
       <c r="C2607">
-        <v>5102.6</v>
+        <v>4744.9</v>
       </c>
       <c r="D2607" t="s">
         <v>2609</v>
@@ -45824,7 +45824,7 @@
         <v>15</v>
       </c>
       <c r="C2608">
-        <v>5103.3</v>
+        <v>4740.5</v>
       </c>
       <c r="D2608" t="s">
         <v>2610</v>
@@ -45838,7 +45838,7 @@
         <v>16</v>
       </c>
       <c r="C2609">
-        <v>5084.4</v>
+        <v>4752.2</v>
       </c>
       <c r="D2609" t="s">
         <v>2611</v>
@@ -45852,7 +45852,7 @@
         <v>17</v>
       </c>
       <c r="C2610">
-        <v>5148.3</v>
+        <v>4693.7</v>
       </c>
       <c r="D2610" t="s">
         <v>2612</v>
@@ -45866,7 +45866,7 @@
         <v>18</v>
       </c>
       <c r="C2611">
-        <v>5146.3</v>
+        <v>4703.8</v>
       </c>
       <c r="D2611" t="s">
         <v>2613</v>
@@ -45880,7 +45880,7 @@
         <v>19</v>
       </c>
       <c r="C2612">
-        <v>5149.5</v>
+        <v>4721.8</v>
       </c>
       <c r="D2612" t="s">
         <v>2614</v>
@@ -45894,7 +45894,7 @@
         <v>20</v>
       </c>
       <c r="C2613">
-        <v>5129.2</v>
+        <v>4749.5</v>
       </c>
       <c r="D2613" t="s">
         <v>2615</v>
@@ -45908,7 +45908,7 @@
         <v>21</v>
       </c>
       <c r="C2614">
-        <v>5157.2</v>
+        <v>4841</v>
       </c>
       <c r="D2614" t="s">
         <v>2616</v>
@@ -45922,7 +45922,7 @@
         <v>22</v>
       </c>
       <c r="C2615">
-        <v>5190.2</v>
+        <v>4879.5</v>
       </c>
       <c r="D2615" t="s">
         <v>2617</v>
@@ -45936,7 +45936,7 @@
         <v>23</v>
       </c>
       <c r="C2616">
-        <v>5226.6</v>
+        <v>4949</v>
       </c>
       <c r="D2616" t="s">
         <v>2618</v>
@@ -45950,7 +45950,7 @@
         <v>24</v>
       </c>
       <c r="C2617">
-        <v>5241.9</v>
+        <v>4989.7</v>
       </c>
       <c r="D2617" t="s">
         <v>2619</v>
@@ -45964,7 +45964,7 @@
         <v>25</v>
       </c>
       <c r="C2618">
-        <v>5490.7</v>
+        <v>5251.7</v>
       </c>
       <c r="D2618" t="s">
         <v>2620</v>
@@ -45978,7 +45978,7 @@
         <v>26</v>
       </c>
       <c r="C2619">
-        <v>5560.8</v>
+        <v>5263.8</v>
       </c>
       <c r="D2619" t="s">
         <v>2621</v>
@@ -45992,7 +45992,7 @@
         <v>27</v>
       </c>
       <c r="C2620">
-        <v>5592.7</v>
+        <v>5316.8</v>
       </c>
       <c r="D2620" t="s">
         <v>2622</v>
@@ -46006,7 +46006,7 @@
         <v>28</v>
       </c>
       <c r="C2621">
-        <v>5605.1</v>
+        <v>5357.1</v>
       </c>
       <c r="D2621" t="s">
         <v>2623</v>
@@ -46020,7 +46020,7 @@
         <v>29</v>
       </c>
       <c r="C2622">
-        <v>5549.7</v>
+        <v>5351.1</v>
       </c>
       <c r="D2622" t="s">
         <v>2624</v>
@@ -46034,7 +46034,7 @@
         <v>30</v>
       </c>
       <c r="C2623">
-        <v>5575.1</v>
+        <v>5387.5</v>
       </c>
       <c r="D2623" t="s">
         <v>2625</v>
@@ -46048,7 +46048,7 @@
         <v>31</v>
       </c>
       <c r="C2624">
-        <v>5645</v>
+        <v>5510</v>
       </c>
       <c r="D2624" t="s">
         <v>2626</v>
@@ -46062,7 +46062,7 @@
         <v>32</v>
       </c>
       <c r="C2625">
-        <v>5733.1</v>
+        <v>5597.9</v>
       </c>
       <c r="D2625" t="s">
         <v>2627</v>
@@ -46076,7 +46076,7 @@
         <v>33</v>
       </c>
       <c r="C2626">
-        <v>5466.6</v>
+        <v>5469.4</v>
       </c>
       <c r="D2626" t="s">
         <v>2628</v>
@@ -46090,7 +46090,7 @@
         <v>34</v>
       </c>
       <c r="C2627">
-        <v>5355.8</v>
+        <v>5573.1</v>
       </c>
       <c r="D2627" t="s">
         <v>2629</v>
@@ -46104,7 +46104,7 @@
         <v>35</v>
       </c>
       <c r="C2628">
-        <v>5441.9</v>
+        <v>5688</v>
       </c>
       <c r="D2628" t="s">
         <v>2630</v>
@@ -46118,7 +46118,7 @@
         <v>36</v>
       </c>
       <c r="C2629">
-        <v>5459.6</v>
+        <v>5783.6</v>
       </c>
       <c r="D2629" t="s">
         <v>2631</v>
@@ -46132,7 +46132,7 @@
         <v>37</v>
       </c>
       <c r="C2630">
-        <v>5598.6</v>
+        <v>5453.4</v>
       </c>
       <c r="D2630" t="s">
         <v>2632</v>
@@ -46146,7 +46146,7 @@
         <v>38</v>
       </c>
       <c r="C2631">
-        <v>5597.8</v>
+        <v>5485</v>
       </c>
       <c r="D2631" t="s">
         <v>2633</v>
@@ -46160,7 +46160,7 @@
         <v>39</v>
       </c>
       <c r="C2632">
-        <v>5570.7</v>
+        <v>5556.4</v>
       </c>
       <c r="D2632" t="s">
         <v>2634</v>
@@ -46174,7 +46174,7 @@
         <v>40</v>
       </c>
       <c r="C2633">
-        <v>5574.3</v>
+        <v>5610.7</v>
       </c>
       <c r="D2633" t="s">
         <v>2635</v>
@@ -46188,7 +46188,7 @@
         <v>41</v>
       </c>
       <c r="C2634">
-        <v>5523.8</v>
+        <v>5608.5</v>
       </c>
       <c r="D2634" t="s">
         <v>2636</v>
@@ -46202,7 +46202,7 @@
         <v>42</v>
       </c>
       <c r="C2635">
-        <v>5411.7</v>
+        <v>5630.5</v>
       </c>
       <c r="D2635" t="s">
         <v>2637</v>
@@ -46216,7 +46216,7 @@
         <v>43</v>
       </c>
       <c r="C2636">
-        <v>5421</v>
+        <v>5691.4</v>
       </c>
       <c r="D2636" t="s">
         <v>2638</v>
@@ -46230,7 +46230,7 @@
         <v>44</v>
       </c>
       <c r="C2637">
-        <v>5349.1</v>
+        <v>5730.3</v>
       </c>
       <c r="D2637" t="s">
         <v>2639</v>
@@ -46244,7 +46244,7 @@
         <v>45</v>
       </c>
       <c r="C2638">
-        <v>4873.5</v>
+        <v>5183.2</v>
       </c>
       <c r="D2638" t="s">
         <v>2640</v>
@@ -46258,7 +46258,7 @@
         <v>46</v>
       </c>
       <c r="C2639">
-        <v>4868.1</v>
+        <v>5190.9</v>
       </c>
       <c r="D2639" t="s">
         <v>2641</v>
@@ -46272,7 +46272,7 @@
         <v>47</v>
       </c>
       <c r="C2640">
-        <v>4916.8</v>
+        <v>5017.5</v>
       </c>
       <c r="D2640" t="s">
         <v>2642</v>
@@ -46286,7 +46286,7 @@
         <v>48</v>
       </c>
       <c r="C2641">
-        <v>4868.6</v>
+        <v>5071</v>
       </c>
       <c r="D2641" t="s">
         <v>2643</v>
@@ -46300,7 +46300,7 @@
         <v>49</v>
       </c>
       <c r="C2642">
-        <v>4739.7</v>
+        <v>4949.7</v>
       </c>
       <c r="D2642" t="s">
         <v>2644</v>
@@ -46314,7 +46314,7 @@
         <v>50</v>
       </c>
       <c r="C2643">
-        <v>4705.8</v>
+        <v>4870.2</v>
       </c>
       <c r="D2643" t="s">
         <v>2645</v>
@@ -46328,7 +46328,7 @@
         <v>51</v>
       </c>
       <c r="C2644">
-        <v>4670.6</v>
+        <v>4922.6</v>
       </c>
       <c r="D2644" t="s">
         <v>2646</v>
@@ -46342,7 +46342,7 @@
         <v>52</v>
       </c>
       <c r="C2645">
-        <v>4640.3</v>
+        <v>4941.8</v>
       </c>
       <c r="D2645" t="s">
         <v>2647</v>
@@ -46356,7 +46356,7 @@
         <v>53</v>
       </c>
       <c r="C2646">
-        <v>4529.6</v>
+        <v>4879.4</v>
       </c>
       <c r="D2646" t="s">
         <v>2648</v>
@@ -46370,7 +46370,7 @@
         <v>54</v>
       </c>
       <c r="C2647">
-        <v>4480.7</v>
+        <v>4849.6</v>
       </c>
       <c r="D2647" t="s">
         <v>2649</v>
@@ -46384,7 +46384,7 @@
         <v>55</v>
       </c>
       <c r="C2648">
-        <v>4451.7</v>
+        <v>4848</v>
       </c>
       <c r="D2648" t="s">
         <v>2650</v>
@@ -46398,7 +46398,7 @@
         <v>56</v>
       </c>
       <c r="C2649">
-        <v>4430.5</v>
+        <v>4814.6</v>
       </c>
       <c r="D2649" t="s">
         <v>2651</v>
@@ -46412,7 +46412,7 @@
         <v>57</v>
       </c>
       <c r="C2650">
-        <v>4328.1</v>
+        <v>4973</v>
       </c>
       <c r="D2650" t="s">
         <v>2652</v>
@@ -46426,7 +46426,7 @@
         <v>58</v>
       </c>
       <c r="C2651">
-        <v>4333.8</v>
+        <v>4978</v>
       </c>
       <c r="D2651" t="s">
         <v>2653</v>
@@ -46440,7 +46440,7 @@
         <v>59</v>
       </c>
       <c r="C2652">
-        <v>4328.3</v>
+        <v>5041.1</v>
       </c>
       <c r="D2652" t="s">
         <v>2654</v>
@@ -46454,7 +46454,7 @@
         <v>60</v>
       </c>
       <c r="C2653">
-        <v>4334.1</v>
+        <v>5085.8</v>
       </c>
       <c r="D2653" t="s">
         <v>2655</v>
@@ -46468,7 +46468,7 @@
         <v>61</v>
       </c>
       <c r="C2654">
-        <v>4410.6</v>
+        <v>4927.8</v>
       </c>
       <c r="D2654" t="s">
         <v>2656</v>
@@ -46482,7 +46482,7 @@
         <v>62</v>
       </c>
       <c r="C2655">
-        <v>4371.5</v>
+        <v>5013.1</v>
       </c>
       <c r="D2655" t="s">
         <v>2657</v>
@@ -46496,7 +46496,7 @@
         <v>63</v>
       </c>
       <c r="C2656">
-        <v>4416</v>
+        <v>4980.8</v>
       </c>
       <c r="D2656" t="s">
         <v>2658</v>
@@ -46510,7 +46510,7 @@
         <v>64</v>
       </c>
       <c r="C2657">
-        <v>4405</v>
+        <v>4833.2</v>
       </c>
       <c r="D2657" t="s">
         <v>2659</v>
@@ -46524,7 +46524,7 @@
         <v>65</v>
       </c>
       <c r="C2658">
-        <v>4441.2</v>
+        <v>4751.1</v>
       </c>
       <c r="D2658" t="s">
         <v>2660</v>
@@ -46538,7 +46538,7 @@
         <v>66</v>
       </c>
       <c r="C2659">
-        <v>4385.7</v>
+        <v>4696.7</v>
       </c>
       <c r="D2659" t="s">
         <v>2661</v>
@@ -46552,7 +46552,7 @@
         <v>67</v>
       </c>
       <c r="C2660">
-        <v>4342.2</v>
+        <v>4635.4</v>
       </c>
       <c r="D2660" t="s">
         <v>2662</v>
@@ -46566,7 +46566,7 @@
         <v>68</v>
       </c>
       <c r="C2661">
-        <v>4338.4</v>
+        <v>4612.3</v>
       </c>
       <c r="D2661" t="s">
         <v>2663</v>
@@ -46580,7 +46580,7 @@
         <v>69</v>
       </c>
       <c r="C2662">
-        <v>4555.1</v>
+        <v>4806.1</v>
       </c>
       <c r="D2662" t="s">
         <v>2664</v>
@@ -46594,7 +46594,7 @@
         <v>70</v>
       </c>
       <c r="C2663">
-        <v>4512.7</v>
+        <v>4837.4</v>
       </c>
       <c r="D2663" t="s">
         <v>2665</v>
@@ -46608,7 +46608,7 @@
         <v>71</v>
       </c>
       <c r="C2664">
-        <v>4523.3</v>
+        <v>4717.5</v>
       </c>
       <c r="D2664" t="s">
         <v>2666</v>
@@ -46622,7 +46622,7 @@
         <v>72</v>
       </c>
       <c r="C2665">
-        <v>4535.1</v>
+        <v>4564</v>
       </c>
       <c r="D2665" t="s">
         <v>2667</v>
@@ -46636,7 +46636,7 @@
         <v>73</v>
       </c>
       <c r="C2666">
-        <v>5194.6</v>
+        <v>5201.4</v>
       </c>
       <c r="D2666" t="s">
         <v>2668</v>
@@ -46650,7 +46650,7 @@
         <v>74</v>
       </c>
       <c r="C2667">
-        <v>5183.7</v>
+        <v>5029.4</v>
       </c>
       <c r="D2667" t="s">
         <v>2669</v>
@@ -46664,7 +46664,7 @@
         <v>75</v>
       </c>
       <c r="C2668">
-        <v>5184.6</v>
+        <v>4879.2</v>
       </c>
       <c r="D2668" t="s">
         <v>2670</v>
@@ -46678,7 +46678,7 @@
         <v>76</v>
       </c>
       <c r="C2669">
-        <v>5238.2</v>
+        <v>4772.4</v>
       </c>
       <c r="D2669" t="s">
         <v>2671</v>
@@ -46692,7 +46692,7 @@
         <v>77</v>
       </c>
       <c r="C2670">
-        <v>5491.7</v>
+        <v>5068</v>
       </c>
       <c r="D2670" t="s">
         <v>2672</v>
@@ -46706,7 +46706,7 @@
         <v>78</v>
       </c>
       <c r="C2671">
-        <v>5522.4</v>
+        <v>5041.8</v>
       </c>
       <c r="D2671" t="s">
         <v>2673</v>
@@ -46720,7 +46720,7 @@
         <v>79</v>
       </c>
       <c r="C2672">
-        <v>5497.4</v>
+        <v>4979.2</v>
       </c>
       <c r="D2672" t="s">
         <v>2674</v>
@@ -46734,7 +46734,7 @@
         <v>80</v>
       </c>
       <c r="C2673">
-        <v>5526.3</v>
+        <v>4972.7</v>
       </c>
       <c r="D2673" t="s">
         <v>2675</v>
@@ -46748,7 +46748,7 @@
         <v>81</v>
       </c>
       <c r="C2674">
-        <v>5513.1</v>
+        <v>5520.6</v>
       </c>
       <c r="D2674" t="s">
         <v>2676</v>
@@ -46762,7 +46762,7 @@
         <v>82</v>
       </c>
       <c r="C2675">
-        <v>5505.8</v>
+        <v>5568.1</v>
       </c>
       <c r="D2675" t="s">
         <v>2677</v>
@@ -46776,7 +46776,7 @@
         <v>83</v>
       </c>
       <c r="C2676">
-        <v>5530.2</v>
+        <v>5645.5</v>
       </c>
       <c r="D2676" t="s">
         <v>2678</v>
@@ -46790,7 +46790,7 @@
         <v>84</v>
       </c>
       <c r="C2677">
-        <v>5563.6</v>
+        <v>5779.8</v>
       </c>
       <c r="D2677" t="s">
         <v>2679</v>
@@ -46804,7 +46804,7 @@
         <v>85</v>
       </c>
       <c r="C2678">
-        <v>5675</v>
+        <v>5838.5</v>
       </c>
       <c r="D2678" t="s">
         <v>2680</v>
@@ -46818,7 +46818,7 @@
         <v>86</v>
       </c>
       <c r="C2679">
-        <v>5617.5</v>
+        <v>5859.6</v>
       </c>
       <c r="D2679" t="s">
         <v>2681</v>
@@ -46832,7 +46832,7 @@
         <v>87</v>
       </c>
       <c r="C2680">
-        <v>5621.4</v>
+        <v>5926</v>
       </c>
       <c r="D2680" t="s">
         <v>2682</v>
@@ -46846,7 +46846,7 @@
         <v>88</v>
       </c>
       <c r="C2681">
-        <v>5569.9</v>
+        <v>5934.5</v>
       </c>
       <c r="D2681" t="s">
         <v>2683</v>
@@ -46860,7 +46860,7 @@
         <v>89</v>
       </c>
       <c r="C2682">
-        <v>5401.8</v>
+        <v>5847.6</v>
       </c>
       <c r="D2682" t="s">
         <v>2684</v>
@@ -46874,7 +46874,7 @@
         <v>90</v>
       </c>
       <c r="C2683">
-        <v>5310.4</v>
+        <v>5821.2</v>
       </c>
       <c r="D2683" t="s">
         <v>2685</v>
@@ -46888,7 +46888,7 @@
         <v>91</v>
       </c>
       <c r="C2684">
-        <v>5308.5</v>
+        <v>5813.4</v>
       </c>
       <c r="D2684" t="s">
         <v>2686</v>
@@ -46902,7 +46902,7 @@
         <v>92</v>
       </c>
       <c r="C2685">
-        <v>5210.2</v>
+        <v>5796.7</v>
       </c>
       <c r="D2685" t="s">
         <v>2687</v>
@@ -46916,7 +46916,7 @@
         <v>93</v>
       </c>
       <c r="C2686">
-        <v>4812.8</v>
+        <v>5445.9</v>
       </c>
       <c r="D2686" t="s">
         <v>2688</v>
@@ -46930,7 +46930,7 @@
         <v>94</v>
       </c>
       <c r="C2687">
-        <v>4728.9</v>
+        <v>5386.8</v>
       </c>
       <c r="D2687" t="s">
         <v>2689</v>
@@ -46944,7 +46944,7 @@
         <v>95</v>
       </c>
       <c r="C2688">
-        <v>4803.5</v>
+        <v>5370.4</v>
       </c>
       <c r="D2688" t="s">
         <v>2690</v>
@@ -46958,7 +46958,7 @@
         <v>96</v>
       </c>
       <c r="C2689">
-        <v>4742.3</v>
+        <v>5347.3</v>
       </c>
       <c r="D2689" t="s">
         <v>2691</v>

--- a/Market Fundamentals/Transelectrica_data/Cons_Prod_final/Weekly_Production_2026.xlsx
+++ b/Market Fundamentals/Transelectrica_data/Cons_Prod_final/Weekly_Production_2026.xlsx
@@ -44284,7 +44284,7 @@
         <v>1</v>
       </c>
       <c r="C2498">
-        <v>4420.6</v>
+        <v>5203.4</v>
       </c>
       <c r="D2498" t="s">
         <v>2500</v>
@@ -44298,7 +44298,7 @@
         <v>2</v>
       </c>
       <c r="C2499">
-        <v>4509.7</v>
+        <v>5224.3</v>
       </c>
       <c r="D2499" t="s">
         <v>2501</v>
@@ -44312,7 +44312,7 @@
         <v>3</v>
       </c>
       <c r="C2500">
-        <v>4496.3</v>
+        <v>5190.2</v>
       </c>
       <c r="D2500" t="s">
         <v>2502</v>
@@ -44326,7 +44326,7 @@
         <v>4</v>
       </c>
       <c r="C2501">
-        <v>4489.2</v>
+        <v>5148.1</v>
       </c>
       <c r="D2501" t="s">
         <v>2503</v>
@@ -44340,7 +44340,7 @@
         <v>5</v>
       </c>
       <c r="C2502">
-        <v>4649.3</v>
+        <v>4252.7</v>
       </c>
       <c r="D2502" t="s">
         <v>2504</v>
@@ -44354,7 +44354,7 @@
         <v>6</v>
       </c>
       <c r="C2503">
-        <v>4668.6</v>
+        <v>4215</v>
       </c>
       <c r="D2503" t="s">
         <v>2505</v>
@@ -44368,7 +44368,7 @@
         <v>7</v>
       </c>
       <c r="C2504">
-        <v>4667.1</v>
+        <v>4206.2</v>
       </c>
       <c r="D2504" t="s">
         <v>2506</v>
@@ -44382,7 +44382,7 @@
         <v>8</v>
       </c>
       <c r="C2505">
-        <v>4687.5</v>
+        <v>4180</v>
       </c>
       <c r="D2505" t="s">
         <v>2507</v>
@@ -44396,7 +44396,7 @@
         <v>9</v>
       </c>
       <c r="C2506">
-        <v>4534.8</v>
+        <v>4116.4</v>
       </c>
       <c r="D2506" t="s">
         <v>2508</v>
@@ -44410,7 +44410,7 @@
         <v>10</v>
       </c>
       <c r="C2507">
-        <v>4532.4</v>
+        <v>4106.1</v>
       </c>
       <c r="D2507" t="s">
         <v>2509</v>
@@ -44424,7 +44424,7 @@
         <v>11</v>
       </c>
       <c r="C2508">
-        <v>4556.4</v>
+        <v>4093.2</v>
       </c>
       <c r="D2508" t="s">
         <v>2510</v>
@@ -44438,7 +44438,7 @@
         <v>12</v>
       </c>
       <c r="C2509">
-        <v>4594.6</v>
+        <v>4082.1</v>
       </c>
       <c r="D2509" t="s">
         <v>2511</v>
@@ -44452,7 +44452,7 @@
         <v>13</v>
       </c>
       <c r="C2510">
-        <v>4632.8</v>
+        <v>4072.1</v>
       </c>
       <c r="D2510" t="s">
         <v>2512</v>
@@ -44466,7 +44466,7 @@
         <v>14</v>
       </c>
       <c r="C2511">
-        <v>4644.9</v>
+        <v>4064.1</v>
       </c>
       <c r="D2511" t="s">
         <v>2513</v>
@@ -44480,7 +44480,7 @@
         <v>15</v>
       </c>
       <c r="C2512">
-        <v>4650.5</v>
+        <v>4051.7</v>
       </c>
       <c r="D2512" t="s">
         <v>2514</v>
@@ -44494,7 +44494,7 @@
         <v>16</v>
       </c>
       <c r="C2513">
-        <v>4652.2</v>
+        <v>4037.1</v>
       </c>
       <c r="D2513" t="s">
         <v>2515</v>
@@ -44508,7 +44508,7 @@
         <v>17</v>
       </c>
       <c r="C2514">
-        <v>4593.7</v>
+        <v>3887.3</v>
       </c>
       <c r="D2514" t="s">
         <v>2516</v>
@@ -44522,7 +44522,7 @@
         <v>18</v>
       </c>
       <c r="C2515">
-        <v>4593.8</v>
+        <v>3868.5</v>
       </c>
       <c r="D2515" t="s">
         <v>2517</v>
@@ -44536,7 +44536,7 @@
         <v>19</v>
       </c>
       <c r="C2516">
-        <v>4591.8</v>
+        <v>3844.1</v>
       </c>
       <c r="D2516" t="s">
         <v>2518</v>
@@ -44550,7 +44550,7 @@
         <v>20</v>
       </c>
       <c r="C2517">
-        <v>4609.5</v>
+        <v>3817.1</v>
       </c>
       <c r="D2517" t="s">
         <v>2519</v>
@@ -44564,7 +44564,7 @@
         <v>21</v>
       </c>
       <c r="C2518">
-        <v>4701</v>
+        <v>3792.8</v>
       </c>
       <c r="D2518" t="s">
         <v>2520</v>
@@ -44578,7 +44578,7 @@
         <v>22</v>
       </c>
       <c r="C2519">
-        <v>4749.5</v>
+        <v>3772.8</v>
       </c>
       <c r="D2519" t="s">
         <v>2521</v>
@@ -44592,7 +44592,7 @@
         <v>23</v>
       </c>
       <c r="C2520">
-        <v>4819</v>
+        <v>3743.3</v>
       </c>
       <c r="D2520" t="s">
         <v>2522</v>
@@ -44606,7 +44606,7 @@
         <v>24</v>
       </c>
       <c r="C2521">
-        <v>4879.7</v>
+        <v>3691.6</v>
       </c>
       <c r="D2521" t="s">
         <v>2523</v>
@@ -44620,7 +44620,7 @@
         <v>25</v>
       </c>
       <c r="C2522">
-        <v>5151.7</v>
+        <v>3974.3</v>
       </c>
       <c r="D2522" t="s">
         <v>2524</v>
@@ -44634,7 +44634,7 @@
         <v>26</v>
       </c>
       <c r="C2523">
-        <v>5183.8</v>
+        <v>4028.1</v>
       </c>
       <c r="D2523" t="s">
         <v>2525</v>
@@ -44648,7 +44648,7 @@
         <v>27</v>
       </c>
       <c r="C2524">
-        <v>5236.8</v>
+        <v>4088.6</v>
       </c>
       <c r="D2524" t="s">
         <v>2526</v>
@@ -44662,7 +44662,7 @@
         <v>28</v>
       </c>
       <c r="C2525">
-        <v>5277.1</v>
+        <v>4191</v>
       </c>
       <c r="D2525" t="s">
         <v>2527</v>
@@ -44676,7 +44676,7 @@
         <v>29</v>
       </c>
       <c r="C2526">
-        <v>5251.1</v>
+        <v>4323.4</v>
       </c>
       <c r="D2526" t="s">
         <v>2528</v>
@@ -44690,7 +44690,7 @@
         <v>30</v>
       </c>
       <c r="C2527">
-        <v>5267.5</v>
+        <v>4414.1</v>
       </c>
       <c r="D2527" t="s">
         <v>2529</v>
@@ -44704,7 +44704,7 @@
         <v>31</v>
       </c>
       <c r="C2528">
-        <v>5390</v>
+        <v>4532.4</v>
       </c>
       <c r="D2528" t="s">
         <v>2530</v>
@@ -44718,7 +44718,7 @@
         <v>32</v>
       </c>
       <c r="C2529">
-        <v>5467.9</v>
+        <v>4651</v>
       </c>
       <c r="D2529" t="s">
         <v>2531</v>
@@ -44732,7 +44732,7 @@
         <v>33</v>
       </c>
       <c r="C2530">
-        <v>5299.4</v>
+        <v>4201.1</v>
       </c>
       <c r="D2530" t="s">
         <v>2532</v>
@@ -44746,7 +44746,7 @@
         <v>34</v>
       </c>
       <c r="C2531">
-        <v>5353.1</v>
+        <v>4282.7</v>
       </c>
       <c r="D2531" t="s">
         <v>2533</v>
@@ -44760,7 +44760,7 @@
         <v>35</v>
       </c>
       <c r="C2532">
-        <v>5458</v>
+        <v>4345.8</v>
       </c>
       <c r="D2532" t="s">
         <v>2534</v>
@@ -44774,7 +44774,7 @@
         <v>36</v>
       </c>
       <c r="C2533">
-        <v>5553.6</v>
+        <v>4509.4</v>
       </c>
       <c r="D2533" t="s">
         <v>2535</v>
@@ -44788,7 +44788,7 @@
         <v>37</v>
       </c>
       <c r="C2534">
-        <v>5213.4</v>
+        <v>4445.2</v>
       </c>
       <c r="D2534" t="s">
         <v>2536</v>
@@ -44802,7 +44802,7 @@
         <v>38</v>
       </c>
       <c r="C2535">
-        <v>5265</v>
+        <v>4462.1</v>
       </c>
       <c r="D2535" t="s">
         <v>2537</v>
@@ -44816,7 +44816,7 @@
         <v>39</v>
       </c>
       <c r="C2536">
-        <v>5356.4</v>
+        <v>4548.2</v>
       </c>
       <c r="D2536" t="s">
         <v>2538</v>
@@ -44830,7 +44830,7 @@
         <v>40</v>
       </c>
       <c r="C2537">
-        <v>5430.7</v>
+        <v>4586.3</v>
       </c>
       <c r="D2537" t="s">
         <v>2539</v>
@@ -44844,7 +44844,7 @@
         <v>41</v>
       </c>
       <c r="C2538">
-        <v>5458.5</v>
+        <v>4739.5</v>
       </c>
       <c r="D2538" t="s">
         <v>2540</v>
@@ -44858,7 +44858,7 @@
         <v>42</v>
       </c>
       <c r="C2539">
-        <v>5490.5</v>
+        <v>4789.1</v>
       </c>
       <c r="D2539" t="s">
         <v>2541</v>
@@ -44872,7 +44872,7 @@
         <v>43</v>
       </c>
       <c r="C2540">
-        <v>5571.4</v>
+        <v>4853.8</v>
       </c>
       <c r="D2540" t="s">
         <v>2542</v>
@@ -44886,7 +44886,7 @@
         <v>44</v>
       </c>
       <c r="C2541">
-        <v>5620.3</v>
+        <v>4894.9</v>
       </c>
       <c r="D2541" t="s">
         <v>2543</v>
@@ -44900,7 +44900,7 @@
         <v>45</v>
       </c>
       <c r="C2542">
-        <v>5083.2</v>
+        <v>4453.2</v>
       </c>
       <c r="D2542" t="s">
         <v>2544</v>
@@ -44914,7 +44914,7 @@
         <v>46</v>
       </c>
       <c r="C2543">
-        <v>5090.9</v>
+        <v>4470.9</v>
       </c>
       <c r="D2543" t="s">
         <v>2545</v>
@@ -44928,7 +44928,7 @@
         <v>47</v>
       </c>
       <c r="C2544">
-        <v>4927.5</v>
+        <v>4549.4</v>
       </c>
       <c r="D2544" t="s">
         <v>2546</v>
@@ -44942,7 +44942,7 @@
         <v>48</v>
       </c>
       <c r="C2545">
-        <v>4981</v>
+        <v>4594</v>
       </c>
       <c r="D2545" t="s">
         <v>2547</v>
@@ -44956,7 +44956,7 @@
         <v>49</v>
       </c>
       <c r="C2546">
-        <v>4859.7</v>
+        <v>4648.4</v>
       </c>
       <c r="D2546" t="s">
         <v>2548</v>
@@ -44970,7 +44970,7 @@
         <v>50</v>
       </c>
       <c r="C2547">
-        <v>4790.2</v>
+        <v>4654.8</v>
       </c>
       <c r="D2547" t="s">
         <v>2549</v>
@@ -44984,7 +44984,7 @@
         <v>51</v>
       </c>
       <c r="C2548">
-        <v>4862.6</v>
+        <v>4715.1</v>
       </c>
       <c r="D2548" t="s">
         <v>2550</v>
@@ -44998,7 +44998,7 @@
         <v>52</v>
       </c>
       <c r="C2549">
-        <v>4891.8</v>
+        <v>4752.4</v>
       </c>
       <c r="D2549" t="s">
         <v>2551</v>
@@ -45012,7 +45012,7 @@
         <v>53</v>
       </c>
       <c r="C2550">
-        <v>4839.4</v>
+        <v>4621.1</v>
       </c>
       <c r="D2550" t="s">
         <v>2552</v>
@@ -45026,7 +45026,7 @@
         <v>54</v>
       </c>
       <c r="C2551">
-        <v>4829.6</v>
+        <v>4647.8</v>
       </c>
       <c r="D2551" t="s">
         <v>2553</v>
@@ -45040,7 +45040,7 @@
         <v>55</v>
       </c>
       <c r="C2552">
-        <v>4838</v>
+        <v>4747</v>
       </c>
       <c r="D2552" t="s">
         <v>2554</v>
@@ -45054,7 +45054,7 @@
         <v>56</v>
       </c>
       <c r="C2553">
-        <v>4824.6</v>
+        <v>4782.4</v>
       </c>
       <c r="D2553" t="s">
         <v>2555</v>
@@ -45068,7 +45068,7 @@
         <v>57</v>
       </c>
       <c r="C2554">
-        <v>4983</v>
+        <v>4818.1</v>
       </c>
       <c r="D2554" t="s">
         <v>2556</v>
@@ -45082,7 +45082,7 @@
         <v>58</v>
       </c>
       <c r="C2555">
-        <v>4988</v>
+        <v>4870.5</v>
       </c>
       <c r="D2555" t="s">
         <v>2557</v>
@@ -45096,7 +45096,7 @@
         <v>59</v>
       </c>
       <c r="C2556">
-        <v>5061.1</v>
+        <v>4922.6</v>
       </c>
       <c r="D2556" t="s">
         <v>2558</v>
@@ -45110,7 +45110,7 @@
         <v>60</v>
       </c>
       <c r="C2557">
-        <v>5105.8</v>
+        <v>4962.9</v>
       </c>
       <c r="D2557" t="s">
         <v>2559</v>
@@ -45124,7 +45124,7 @@
         <v>61</v>
       </c>
       <c r="C2558">
-        <v>4947.8</v>
+        <v>4908.7</v>
       </c>
       <c r="D2558" t="s">
         <v>2560</v>
@@ -45138,7 +45138,7 @@
         <v>62</v>
       </c>
       <c r="C2559">
-        <v>5053.1</v>
+        <v>4950.1</v>
       </c>
       <c r="D2559" t="s">
         <v>2561</v>
@@ -45152,7 +45152,7 @@
         <v>63</v>
       </c>
       <c r="C2560">
-        <v>5020.8</v>
+        <v>4964.4</v>
       </c>
       <c r="D2560" t="s">
         <v>2562</v>
@@ -45166,7 +45166,7 @@
         <v>64</v>
       </c>
       <c r="C2561">
-        <v>4893.2</v>
+        <v>4971.7</v>
       </c>
       <c r="D2561" t="s">
         <v>2563</v>
@@ -45180,7 +45180,7 @@
         <v>65</v>
       </c>
       <c r="C2562">
-        <v>4811.1</v>
+        <v>4724.8</v>
       </c>
       <c r="D2562" t="s">
         <v>2564</v>
@@ -45194,7 +45194,7 @@
         <v>66</v>
       </c>
       <c r="C2563">
-        <v>4766.7</v>
+        <v>4726.3</v>
       </c>
       <c r="D2563" t="s">
         <v>2565</v>
@@ -45208,7 +45208,7 @@
         <v>67</v>
       </c>
       <c r="C2564">
-        <v>4705.4</v>
+        <v>4666.2</v>
       </c>
       <c r="D2564" t="s">
         <v>2566</v>
@@ -45222,7 +45222,7 @@
         <v>68</v>
       </c>
       <c r="C2565">
-        <v>4682.3</v>
+        <v>4678.8</v>
       </c>
       <c r="D2565" t="s">
         <v>2567</v>
@@ -45236,7 +45236,7 @@
         <v>69</v>
       </c>
       <c r="C2566">
-        <v>4886.1</v>
+        <v>5140.4</v>
       </c>
       <c r="D2566" t="s">
         <v>2568</v>
@@ -45250,7 +45250,7 @@
         <v>70</v>
       </c>
       <c r="C2567">
-        <v>4927.4</v>
+        <v>5037.8</v>
       </c>
       <c r="D2567" t="s">
         <v>2569</v>
@@ -45264,7 +45264,7 @@
         <v>71</v>
       </c>
       <c r="C2568">
-        <v>4827.5</v>
+        <v>4978.2</v>
       </c>
       <c r="D2568" t="s">
         <v>2570</v>
@@ -45278,7 +45278,7 @@
         <v>72</v>
       </c>
       <c r="C2569">
-        <v>4684</v>
+        <v>4821.6</v>
       </c>
       <c r="D2569" t="s">
         <v>2571</v>
@@ -45292,7 +45292,7 @@
         <v>73</v>
       </c>
       <c r="C2570">
-        <v>5341.4</v>
+        <v>5626</v>
       </c>
       <c r="D2570" t="s">
         <v>2572</v>
@@ -45306,7 +45306,7 @@
         <v>74</v>
       </c>
       <c r="C2571">
-        <v>5209.4</v>
+        <v>5456</v>
       </c>
       <c r="D2571" t="s">
         <v>2573</v>
@@ -45320,7 +45320,7 @@
         <v>75</v>
       </c>
       <c r="C2572">
-        <v>5069.2</v>
+        <v>5336.3</v>
       </c>
       <c r="D2572" t="s">
         <v>2574</v>
@@ -45334,7 +45334,7 @@
         <v>76</v>
       </c>
       <c r="C2573">
-        <v>4982.4</v>
+        <v>5353.5</v>
       </c>
       <c r="D2573" t="s">
         <v>2575</v>
@@ -45348,7 +45348,7 @@
         <v>77</v>
       </c>
       <c r="C2574">
-        <v>5278</v>
+        <v>5430.4</v>
       </c>
       <c r="D2574" t="s">
         <v>2576</v>
@@ -45362,7 +45362,7 @@
         <v>78</v>
       </c>
       <c r="C2575">
-        <v>5261.8</v>
+        <v>5379.7</v>
       </c>
       <c r="D2575" t="s">
         <v>2577</v>
@@ -45376,7 +45376,7 @@
         <v>79</v>
       </c>
       <c r="C2576">
-        <v>5189.2</v>
+        <v>5335.3</v>
       </c>
       <c r="D2576" t="s">
         <v>2578</v>
@@ -45390,7 +45390,7 @@
         <v>80</v>
       </c>
       <c r="C2577">
-        <v>5172.7</v>
+        <v>5287.4</v>
       </c>
       <c r="D2577" t="s">
         <v>2579</v>
@@ -45404,7 +45404,7 @@
         <v>81</v>
       </c>
       <c r="C2578">
-        <v>5700.6</v>
+        <v>5681.6</v>
       </c>
       <c r="D2578" t="s">
         <v>2580</v>
@@ -45418,7 +45418,7 @@
         <v>82</v>
       </c>
       <c r="C2579">
-        <v>5728.1</v>
+        <v>5601.4</v>
       </c>
       <c r="D2579" t="s">
         <v>2581</v>
@@ -45432,7 +45432,7 @@
         <v>83</v>
       </c>
       <c r="C2580">
-        <v>5785.5</v>
+        <v>5679.7</v>
       </c>
       <c r="D2580" t="s">
         <v>2582</v>
@@ -45446,7 +45446,7 @@
         <v>84</v>
       </c>
       <c r="C2581">
-        <v>5909.8</v>
+        <v>5737.1</v>
       </c>
       <c r="D2581" t="s">
         <v>2583</v>
@@ -45460,7 +45460,7 @@
         <v>85</v>
       </c>
       <c r="C2582">
-        <v>5938.5</v>
+        <v>5745.6</v>
       </c>
       <c r="D2582" t="s">
         <v>2584</v>
@@ -45474,7 +45474,7 @@
         <v>86</v>
       </c>
       <c r="C2583">
-        <v>5959.6</v>
+        <v>5709.4</v>
       </c>
       <c r="D2583" t="s">
         <v>2585</v>
@@ -45488,7 +45488,7 @@
         <v>87</v>
       </c>
       <c r="C2584">
-        <v>6016</v>
+        <v>5737.4</v>
       </c>
       <c r="D2584" t="s">
         <v>2586</v>
@@ -45502,7 +45502,7 @@
         <v>88</v>
       </c>
       <c r="C2585">
-        <v>6034.5</v>
+        <v>5698.6</v>
       </c>
       <c r="D2585" t="s">
         <v>2587</v>
@@ -45516,7 +45516,7 @@
         <v>89</v>
       </c>
       <c r="C2586">
-        <v>5957.6</v>
+        <v>5340.8</v>
       </c>
       <c r="D2586" t="s">
         <v>2588</v>
@@ -45530,7 +45530,7 @@
         <v>90</v>
       </c>
       <c r="C2587">
-        <v>5941.2</v>
+        <v>5327.9</v>
       </c>
       <c r="D2587" t="s">
         <v>2589</v>
@@ -45544,7 +45544,7 @@
         <v>91</v>
       </c>
       <c r="C2588">
-        <v>5933.4</v>
+        <v>5292.6</v>
       </c>
       <c r="D2588" t="s">
         <v>2590</v>
@@ -45558,7 +45558,7 @@
         <v>92</v>
       </c>
       <c r="C2589">
-        <v>5906.7</v>
+        <v>5274.1</v>
       </c>
       <c r="D2589" t="s">
         <v>2591</v>
@@ -45572,7 +45572,7 @@
         <v>93</v>
       </c>
       <c r="C2590">
-        <v>5545.9</v>
+        <v>5013.9</v>
       </c>
       <c r="D2590" t="s">
         <v>2592</v>
@@ -45586,7 +45586,7 @@
         <v>94</v>
       </c>
       <c r="C2591">
-        <v>5476.8</v>
+        <v>4965.1</v>
       </c>
       <c r="D2591" t="s">
         <v>2593</v>
@@ -45600,7 +45600,7 @@
         <v>95</v>
       </c>
       <c r="C2592">
-        <v>5460.4</v>
+        <v>4981.3</v>
       </c>
       <c r="D2592" t="s">
         <v>2594</v>
@@ -45614,7 +45614,7 @@
         <v>96</v>
       </c>
       <c r="C2593">
-        <v>5437.3</v>
+        <v>4942.8</v>
       </c>
       <c r="D2593" t="s">
         <v>2595</v>
@@ -45628,7 +45628,7 @@
         <v>1</v>
       </c>
       <c r="C2594">
-        <v>4580.6</v>
+        <v>5283.4</v>
       </c>
       <c r="D2594" t="s">
         <v>2596</v>
@@ -45642,7 +45642,7 @@
         <v>2</v>
       </c>
       <c r="C2595">
-        <v>4649.7</v>
+        <v>5334.3</v>
       </c>
       <c r="D2595" t="s">
         <v>2597</v>
@@ -45656,7 +45656,7 @@
         <v>3</v>
       </c>
       <c r="C2596">
-        <v>4666.3</v>
+        <v>5280.2</v>
       </c>
       <c r="D2596" t="s">
         <v>2598</v>
@@ -45670,7 +45670,7 @@
         <v>4</v>
       </c>
       <c r="C2597">
-        <v>4669.2</v>
+        <v>5228.1</v>
       </c>
       <c r="D2597" t="s">
         <v>2599</v>
@@ -45684,7 +45684,7 @@
         <v>5</v>
       </c>
       <c r="C2598">
-        <v>4819.3</v>
+        <v>4382.7</v>
       </c>
       <c r="D2598" t="s">
         <v>2600</v>
@@ -45698,7 +45698,7 @@
         <v>6</v>
       </c>
       <c r="C2599">
-        <v>4828.6</v>
+        <v>4345</v>
       </c>
       <c r="D2599" t="s">
         <v>2601</v>
@@ -45712,7 +45712,7 @@
         <v>7</v>
       </c>
       <c r="C2600">
-        <v>4827.1</v>
+        <v>4296.2</v>
       </c>
       <c r="D2600" t="s">
         <v>2602</v>
@@ -45726,7 +45726,7 @@
         <v>8</v>
       </c>
       <c r="C2601">
-        <v>4847.5</v>
+        <v>4240</v>
       </c>
       <c r="D2601" t="s">
         <v>2603</v>
@@ -45740,7 +45740,7 @@
         <v>9</v>
       </c>
       <c r="C2602">
-        <v>4694.8</v>
+        <v>4156.4</v>
       </c>
       <c r="D2602" t="s">
         <v>2604</v>
@@ -45754,7 +45754,7 @@
         <v>10</v>
       </c>
       <c r="C2603">
-        <v>4682.4</v>
+        <v>4106.1</v>
       </c>
       <c r="D2603" t="s">
         <v>2605</v>
@@ -45768,7 +45768,7 @@
         <v>11</v>
       </c>
       <c r="C2604">
-        <v>4696.4</v>
+        <v>4063.2</v>
       </c>
       <c r="D2604" t="s">
         <v>2606</v>
@@ -45782,7 +45782,7 @@
         <v>12</v>
       </c>
       <c r="C2605">
-        <v>4714.6</v>
+        <v>4032.1</v>
       </c>
       <c r="D2605" t="s">
         <v>2607</v>
@@ -45796,7 +45796,7 @@
         <v>13</v>
       </c>
       <c r="C2606">
-        <v>4742.8</v>
+        <v>3972.1</v>
       </c>
       <c r="D2606" t="s">
         <v>2608</v>
@@ -45810,7 +45810,7 @@
         <v>14</v>
       </c>
       <c r="C2607">
-        <v>4744.9</v>
+        <v>3964.1</v>
       </c>
       <c r="D2607" t="s">
         <v>2609</v>
@@ -45824,7 +45824,7 @@
         <v>15</v>
       </c>
       <c r="C2608">
-        <v>4740.5</v>
+        <v>3951.7</v>
       </c>
       <c r="D2608" t="s">
         <v>2610</v>
@@ -45838,7 +45838,7 @@
         <v>16</v>
       </c>
       <c r="C2609">
-        <v>4752.2</v>
+        <v>3937.1</v>
       </c>
       <c r="D2609" t="s">
         <v>2611</v>
@@ -45852,7 +45852,7 @@
         <v>17</v>
       </c>
       <c r="C2610">
-        <v>4693.7</v>
+        <v>3797.3</v>
       </c>
       <c r="D2610" t="s">
         <v>2612</v>
@@ -45866,7 +45866,7 @@
         <v>18</v>
       </c>
       <c r="C2611">
-        <v>4703.8</v>
+        <v>3788.5</v>
       </c>
       <c r="D2611" t="s">
         <v>2613</v>
@@ -45880,7 +45880,7 @@
         <v>19</v>
       </c>
       <c r="C2612">
-        <v>4721.8</v>
+        <v>3774.1</v>
       </c>
       <c r="D2612" t="s">
         <v>2614</v>
@@ -45894,7 +45894,7 @@
         <v>20</v>
       </c>
       <c r="C2613">
-        <v>4749.5</v>
+        <v>3777.1</v>
       </c>
       <c r="D2613" t="s">
         <v>2615</v>
@@ -45908,7 +45908,7 @@
         <v>21</v>
       </c>
       <c r="C2614">
-        <v>4841</v>
+        <v>3812.8</v>
       </c>
       <c r="D2614" t="s">
         <v>2616</v>
@@ -45922,7 +45922,7 @@
         <v>22</v>
       </c>
       <c r="C2615">
-        <v>4879.5</v>
+        <v>3822.8</v>
       </c>
       <c r="D2615" t="s">
         <v>2617</v>
@@ -45936,7 +45936,7 @@
         <v>23</v>
       </c>
       <c r="C2616">
-        <v>4949</v>
+        <v>3853.3</v>
       </c>
       <c r="D2616" t="s">
         <v>2618</v>
@@ -45950,7 +45950,7 @@
         <v>24</v>
       </c>
       <c r="C2617">
-        <v>4989.7</v>
+        <v>3871.6</v>
       </c>
       <c r="D2617" t="s">
         <v>2619</v>
@@ -45964,7 +45964,7 @@
         <v>25</v>
       </c>
       <c r="C2618">
-        <v>5251.7</v>
+        <v>4134.3</v>
       </c>
       <c r="D2618" t="s">
         <v>2620</v>
@@ -45978,7 +45978,7 @@
         <v>26</v>
       </c>
       <c r="C2619">
-        <v>5263.8</v>
+        <v>4178.1</v>
       </c>
       <c r="D2619" t="s">
         <v>2621</v>
@@ -45992,7 +45992,7 @@
         <v>27</v>
       </c>
       <c r="C2620">
-        <v>5316.8</v>
+        <v>4238.6</v>
       </c>
       <c r="D2620" t="s">
         <v>2622</v>
@@ -46006,7 +46006,7 @@
         <v>28</v>
       </c>
       <c r="C2621">
-        <v>5357.1</v>
+        <v>4321</v>
       </c>
       <c r="D2621" t="s">
         <v>2623</v>
@@ -46020,7 +46020,7 @@
         <v>29</v>
       </c>
       <c r="C2622">
-        <v>5351.1</v>
+        <v>4413.4</v>
       </c>
       <c r="D2622" t="s">
         <v>2624</v>
@@ -46034,7 +46034,7 @@
         <v>30</v>
       </c>
       <c r="C2623">
-        <v>5387.5</v>
+        <v>4514.1</v>
       </c>
       <c r="D2623" t="s">
         <v>2625</v>
@@ -46048,7 +46048,7 @@
         <v>31</v>
       </c>
       <c r="C2624">
-        <v>5510</v>
+        <v>4662.4</v>
       </c>
       <c r="D2624" t="s">
         <v>2626</v>
@@ -46062,7 +46062,7 @@
         <v>32</v>
       </c>
       <c r="C2625">
-        <v>5597.9</v>
+        <v>4811</v>
       </c>
       <c r="D2625" t="s">
         <v>2627</v>
@@ -46076,7 +46076,7 @@
         <v>33</v>
       </c>
       <c r="C2626">
-        <v>5469.4</v>
+        <v>4431.1</v>
       </c>
       <c r="D2626" t="s">
         <v>2628</v>
@@ -46090,7 +46090,7 @@
         <v>34</v>
       </c>
       <c r="C2627">
-        <v>5573.1</v>
+        <v>4572.7</v>
       </c>
       <c r="D2627" t="s">
         <v>2629</v>
@@ -46104,7 +46104,7 @@
         <v>35</v>
       </c>
       <c r="C2628">
-        <v>5688</v>
+        <v>4685.8</v>
       </c>
       <c r="D2628" t="s">
         <v>2630</v>
@@ -46118,7 +46118,7 @@
         <v>36</v>
       </c>
       <c r="C2629">
-        <v>5783.6</v>
+        <v>4869.4</v>
       </c>
       <c r="D2629" t="s">
         <v>2631</v>
@@ -46132,7 +46132,7 @@
         <v>37</v>
       </c>
       <c r="C2630">
-        <v>5453.4</v>
+        <v>4825.2</v>
       </c>
       <c r="D2630" t="s">
         <v>2632</v>
@@ -46146,7 +46146,7 @@
         <v>38</v>
       </c>
       <c r="C2631">
-        <v>5485</v>
+        <v>4852.1</v>
       </c>
       <c r="D2631" t="s">
         <v>2633</v>
@@ -46160,7 +46160,7 @@
         <v>39</v>
       </c>
       <c r="C2632">
-        <v>5556.4</v>
+        <v>4918.2</v>
       </c>
       <c r="D2632" t="s">
         <v>2634</v>
@@ -46174,7 +46174,7 @@
         <v>40</v>
       </c>
       <c r="C2633">
-        <v>5610.7</v>
+        <v>4946.3</v>
       </c>
       <c r="D2633" t="s">
         <v>2635</v>
@@ -46188,7 +46188,7 @@
         <v>41</v>
       </c>
       <c r="C2634">
-        <v>5608.5</v>
+        <v>5079.5</v>
       </c>
       <c r="D2634" t="s">
         <v>2636</v>
@@ -46202,7 +46202,7 @@
         <v>42</v>
       </c>
       <c r="C2635">
-        <v>5630.5</v>
+        <v>5109.1</v>
       </c>
       <c r="D2635" t="s">
         <v>2637</v>
@@ -46216,7 +46216,7 @@
         <v>43</v>
       </c>
       <c r="C2636">
-        <v>5691.4</v>
+        <v>5133.8</v>
       </c>
       <c r="D2636" t="s">
         <v>2638</v>
@@ -46230,7 +46230,7 @@
         <v>44</v>
       </c>
       <c r="C2637">
-        <v>5730.3</v>
+        <v>5164.9</v>
       </c>
       <c r="D2637" t="s">
         <v>2639</v>
@@ -46244,7 +46244,7 @@
         <v>45</v>
       </c>
       <c r="C2638">
-        <v>5183.2</v>
+        <v>4743.2</v>
       </c>
       <c r="D2638" t="s">
         <v>2640</v>
@@ -46258,7 +46258,7 @@
         <v>46</v>
       </c>
       <c r="C2639">
-        <v>5190.9</v>
+        <v>4750.9</v>
       </c>
       <c r="D2639" t="s">
         <v>2641</v>
@@ -46272,7 +46272,7 @@
         <v>47</v>
       </c>
       <c r="C2640">
-        <v>5017.5</v>
+        <v>4779.4</v>
       </c>
       <c r="D2640" t="s">
         <v>2642</v>
@@ -46286,7 +46286,7 @@
         <v>48</v>
       </c>
       <c r="C2641">
-        <v>5071</v>
+        <v>4784</v>
       </c>
       <c r="D2641" t="s">
         <v>2643</v>
@@ -46300,7 +46300,7 @@
         <v>49</v>
       </c>
       <c r="C2642">
-        <v>4949.7</v>
+        <v>4778.4</v>
       </c>
       <c r="D2642" t="s">
         <v>2644</v>
@@ -46314,7 +46314,7 @@
         <v>50</v>
       </c>
       <c r="C2643">
-        <v>4870.2</v>
+        <v>4754.8</v>
       </c>
       <c r="D2643" t="s">
         <v>2645</v>
@@ -46328,7 +46328,7 @@
         <v>51</v>
       </c>
       <c r="C2644">
-        <v>4922.6</v>
+        <v>4795.1</v>
       </c>
       <c r="D2644" t="s">
         <v>2646</v>
@@ -46342,7 +46342,7 @@
         <v>52</v>
       </c>
       <c r="C2645">
-        <v>4941.8</v>
+        <v>4822.4</v>
       </c>
       <c r="D2645" t="s">
         <v>2647</v>
@@ -46356,7 +46356,7 @@
         <v>53</v>
       </c>
       <c r="C2646">
-        <v>4879.4</v>
+        <v>4671.1</v>
       </c>
       <c r="D2646" t="s">
         <v>2648</v>
@@ -46370,7 +46370,7 @@
         <v>54</v>
       </c>
       <c r="C2647">
-        <v>4849.6</v>
+        <v>4687.8</v>
       </c>
       <c r="D2647" t="s">
         <v>2649</v>
@@ -46384,7 +46384,7 @@
         <v>55</v>
       </c>
       <c r="C2648">
-        <v>4848</v>
+        <v>4797</v>
       </c>
       <c r="D2648" t="s">
         <v>2650</v>
@@ -46398,7 +46398,7 @@
         <v>56</v>
       </c>
       <c r="C2649">
-        <v>4814.6</v>
+        <v>4822.4</v>
       </c>
       <c r="D2649" t="s">
         <v>2651</v>
@@ -46412,7 +46412,7 @@
         <v>57</v>
       </c>
       <c r="C2650">
-        <v>4973</v>
+        <v>4848.1</v>
       </c>
       <c r="D2650" t="s">
         <v>2652</v>
@@ -46426,7 +46426,7 @@
         <v>58</v>
       </c>
       <c r="C2651">
-        <v>4978</v>
+        <v>4890.5</v>
       </c>
       <c r="D2651" t="s">
         <v>2653</v>
@@ -46440,7 +46440,7 @@
         <v>59</v>
       </c>
       <c r="C2652">
-        <v>5041.1</v>
+        <v>4942.6</v>
       </c>
       <c r="D2652" t="s">
         <v>2654</v>
@@ -46454,7 +46454,7 @@
         <v>60</v>
       </c>
       <c r="C2653">
-        <v>5085.8</v>
+        <v>4952.9</v>
       </c>
       <c r="D2653" t="s">
         <v>2655</v>
@@ -46468,7 +46468,7 @@
         <v>61</v>
       </c>
       <c r="C2654">
-        <v>4927.8</v>
+        <v>4878.7</v>
       </c>
       <c r="D2654" t="s">
         <v>2656</v>
@@ -46482,7 +46482,7 @@
         <v>62</v>
       </c>
       <c r="C2655">
-        <v>5013.1</v>
+        <v>4910.1</v>
       </c>
       <c r="D2655" t="s">
         <v>2657</v>
@@ -46496,7 +46496,7 @@
         <v>63</v>
       </c>
       <c r="C2656">
-        <v>4980.8</v>
+        <v>4904.4</v>
       </c>
       <c r="D2656" t="s">
         <v>2658</v>
@@ -46510,7 +46510,7 @@
         <v>64</v>
       </c>
       <c r="C2657">
-        <v>4833.2</v>
+        <v>4891.7</v>
       </c>
       <c r="D2657" t="s">
         <v>2659</v>
@@ -46524,7 +46524,7 @@
         <v>65</v>
       </c>
       <c r="C2658">
-        <v>4751.1</v>
+        <v>4614.8</v>
       </c>
       <c r="D2658" t="s">
         <v>2660</v>
@@ -46538,7 +46538,7 @@
         <v>66</v>
       </c>
       <c r="C2659">
-        <v>4696.7</v>
+        <v>4596.3</v>
       </c>
       <c r="D2659" t="s">
         <v>2661</v>
@@ -46552,7 +46552,7 @@
         <v>67</v>
       </c>
       <c r="C2660">
-        <v>4635.4</v>
+        <v>4516.2</v>
       </c>
       <c r="D2660" t="s">
         <v>2662</v>
@@ -46566,7 +46566,7 @@
         <v>68</v>
       </c>
       <c r="C2661">
-        <v>4612.3</v>
+        <v>4508.8</v>
       </c>
       <c r="D2661" t="s">
         <v>2663</v>
@@ -46580,7 +46580,7 @@
         <v>69</v>
       </c>
       <c r="C2662">
-        <v>4806.1</v>
+        <v>4940.4</v>
       </c>
       <c r="D2662" t="s">
         <v>2664</v>
@@ -46594,7 +46594,7 @@
         <v>70</v>
       </c>
       <c r="C2663">
-        <v>4837.4</v>
+        <v>4837.8</v>
       </c>
       <c r="D2663" t="s">
         <v>2665</v>
@@ -46608,7 +46608,7 @@
         <v>71</v>
       </c>
       <c r="C2664">
-        <v>4717.5</v>
+        <v>4758.2</v>
       </c>
       <c r="D2664" t="s">
         <v>2666</v>
@@ -46622,7 +46622,7 @@
         <v>72</v>
       </c>
       <c r="C2665">
-        <v>4564</v>
+        <v>4611.6</v>
       </c>
       <c r="D2665" t="s">
         <v>2667</v>
@@ -46636,7 +46636,7 @@
         <v>73</v>
       </c>
       <c r="C2666">
-        <v>5201.4</v>
+        <v>5396</v>
       </c>
       <c r="D2666" t="s">
         <v>2668</v>
@@ -46650,7 +46650,7 @@
         <v>74</v>
       </c>
       <c r="C2667">
-        <v>5029.4</v>
+        <v>5246</v>
       </c>
       <c r="D2667" t="s">
         <v>2669</v>
@@ -46664,7 +46664,7 @@
         <v>75</v>
       </c>
       <c r="C2668">
-        <v>4879.2</v>
+        <v>5126.3</v>
       </c>
       <c r="D2668" t="s">
         <v>2670</v>
@@ -46678,7 +46678,7 @@
         <v>76</v>
       </c>
       <c r="C2669">
-        <v>4772.4</v>
+        <v>5153.5</v>
       </c>
       <c r="D2669" t="s">
         <v>2671</v>
@@ -46692,7 +46692,7 @@
         <v>77</v>
       </c>
       <c r="C2670">
-        <v>5068</v>
+        <v>5250.4</v>
       </c>
       <c r="D2670" t="s">
         <v>2672</v>
@@ -46706,7 +46706,7 @@
         <v>78</v>
       </c>
       <c r="C2671">
-        <v>5041.8</v>
+        <v>5209.7</v>
       </c>
       <c r="D2671" t="s">
         <v>2673</v>
@@ -46720,7 +46720,7 @@
         <v>79</v>
       </c>
       <c r="C2672">
-        <v>4979.2</v>
+        <v>5195.3</v>
       </c>
       <c r="D2672" t="s">
         <v>2674</v>
@@ -46734,7 +46734,7 @@
         <v>80</v>
       </c>
       <c r="C2673">
-        <v>4972.7</v>
+        <v>5157.4</v>
       </c>
       <c r="D2673" t="s">
         <v>2675</v>
@@ -46748,7 +46748,7 @@
         <v>81</v>
       </c>
       <c r="C2674">
-        <v>5520.6</v>
+        <v>5591.6</v>
       </c>
       <c r="D2674" t="s">
         <v>2676</v>
@@ -46762,7 +46762,7 @@
         <v>82</v>
       </c>
       <c r="C2675">
-        <v>5568.1</v>
+        <v>5551.4</v>
       </c>
       <c r="D2675" t="s">
         <v>2677</v>
@@ -46776,7 +46776,7 @@
         <v>83</v>
       </c>
       <c r="C2676">
-        <v>5645.5</v>
+        <v>5659.7</v>
       </c>
       <c r="D2676" t="s">
         <v>2678</v>
@@ -46790,7 +46790,7 @@
         <v>84</v>
       </c>
       <c r="C2677">
-        <v>5779.8</v>
+        <v>5727.1</v>
       </c>
       <c r="D2677" t="s">
         <v>2679</v>
@@ -46804,7 +46804,7 @@
         <v>85</v>
       </c>
       <c r="C2678">
-        <v>5838.5</v>
+        <v>5685.6</v>
       </c>
       <c r="D2678" t="s">
         <v>2680</v>
@@ -46818,7 +46818,7 @@
         <v>86</v>
       </c>
       <c r="C2679">
-        <v>5859.6</v>
+        <v>5629.4</v>
       </c>
       <c r="D2679" t="s">
         <v>2681</v>
@@ -46832,7 +46832,7 @@
         <v>87</v>
       </c>
       <c r="C2680">
-        <v>5926</v>
+        <v>5677.4</v>
       </c>
       <c r="D2680" t="s">
         <v>2682</v>
@@ -46846,7 +46846,7 @@
         <v>88</v>
       </c>
       <c r="C2681">
-        <v>5934.5</v>
+        <v>5648.6</v>
       </c>
       <c r="D2681" t="s">
         <v>2683</v>
@@ -46860,7 +46860,7 @@
         <v>89</v>
       </c>
       <c r="C2682">
-        <v>5847.6</v>
+        <v>5300.8</v>
       </c>
       <c r="D2682" t="s">
         <v>2684</v>
@@ -46874,7 +46874,7 @@
         <v>90</v>
       </c>
       <c r="C2683">
-        <v>5821.2</v>
+        <v>5327.9</v>
       </c>
       <c r="D2683" t="s">
         <v>2685</v>
@@ -46888,7 +46888,7 @@
         <v>91</v>
       </c>
       <c r="C2684">
-        <v>5813.4</v>
+        <v>5282.6</v>
       </c>
       <c r="D2684" t="s">
         <v>2686</v>
@@ -46902,7 +46902,7 @@
         <v>92</v>
       </c>
       <c r="C2685">
-        <v>5796.7</v>
+        <v>5254.1</v>
       </c>
       <c r="D2685" t="s">
         <v>2687</v>
@@ -46916,7 +46916,7 @@
         <v>93</v>
       </c>
       <c r="C2686">
-        <v>5445.9</v>
+        <v>4933.9</v>
       </c>
       <c r="D2686" t="s">
         <v>2688</v>
@@ -46930,7 +46930,7 @@
         <v>94</v>
       </c>
       <c r="C2687">
-        <v>5386.8</v>
+        <v>4845.1</v>
       </c>
       <c r="D2687" t="s">
         <v>2689</v>
@@ -46944,7 +46944,7 @@
         <v>95</v>
       </c>
       <c r="C2688">
-        <v>5370.4</v>
+        <v>4881.3</v>
       </c>
       <c r="D2688" t="s">
         <v>2690</v>
@@ -46958,7 +46958,7 @@
         <v>96</v>
       </c>
       <c r="C2689">
-        <v>5347.3</v>
+        <v>4852.8</v>
       </c>
       <c r="D2689" t="s">
         <v>2691</v>
@@ -46972,7 +46972,7 @@
         <v>1</v>
       </c>
       <c r="C2690">
-        <v>5047.6</v>
+        <v>5233.4</v>
       </c>
       <c r="D2690" t="s">
         <v>2692</v>
@@ -46986,7 +46986,7 @@
         <v>2</v>
       </c>
       <c r="C2691">
-        <v>5119.2</v>
+        <v>5234.3</v>
       </c>
       <c r="D2691" t="s">
         <v>2693</v>
@@ -47000,7 +47000,7 @@
         <v>3</v>
       </c>
       <c r="C2692">
-        <v>5120.8</v>
+        <v>5190.2</v>
       </c>
       <c r="D2692" t="s">
         <v>2694</v>
@@ -47014,7 +47014,7 @@
         <v>4</v>
       </c>
       <c r="C2693">
-        <v>5116.2</v>
+        <v>5148.1</v>
       </c>
       <c r="D2693" t="s">
         <v>2695</v>
@@ -47028,7 +47028,7 @@
         <v>5</v>
       </c>
       <c r="C2694">
-        <v>5191.5</v>
+        <v>4302.7</v>
       </c>
       <c r="D2694" t="s">
         <v>2696</v>
@@ -47042,7 +47042,7 @@
         <v>6</v>
       </c>
       <c r="C2695">
-        <v>5185.4</v>
+        <v>4275</v>
       </c>
       <c r="D2695" t="s">
         <v>2697</v>
@@ -47056,7 +47056,7 @@
         <v>7</v>
       </c>
       <c r="C2696">
-        <v>5185.1</v>
+        <v>4236.2</v>
       </c>
       <c r="D2696" t="s">
         <v>2698</v>
@@ -47070,7 +47070,7 @@
         <v>8</v>
       </c>
       <c r="C2697">
-        <v>5189.2</v>
+        <v>4190</v>
       </c>
       <c r="D2697" t="s">
         <v>2699</v>
@@ -47084,7 +47084,7 @@
         <v>9</v>
       </c>
       <c r="C2698">
-        <v>5058.8</v>
+        <v>4126.4</v>
       </c>
       <c r="D2698" t="s">
         <v>2700</v>
@@ -47098,7 +47098,7 @@
         <v>10</v>
       </c>
       <c r="C2699">
-        <v>5064.1</v>
+        <v>4106.1</v>
       </c>
       <c r="D2699" t="s">
         <v>2701</v>
@@ -47112,7 +47112,7 @@
         <v>11</v>
       </c>
       <c r="C2700">
-        <v>5085.6</v>
+        <v>4073.2</v>
       </c>
       <c r="D2700" t="s">
         <v>2702</v>
@@ -47126,7 +47126,7 @@
         <v>12</v>
       </c>
       <c r="C2701">
-        <v>5111.9</v>
+        <v>4042.1</v>
       </c>
       <c r="D2701" t="s">
         <v>2703</v>
@@ -47140,7 +47140,7 @@
         <v>13</v>
       </c>
       <c r="C2702">
-        <v>4947.1</v>
+        <v>4002.1</v>
       </c>
       <c r="D2702" t="s">
         <v>2704</v>
@@ -47154,7 +47154,7 @@
         <v>14</v>
       </c>
       <c r="C2703">
-        <v>4982.6</v>
+        <v>3984.1</v>
       </c>
       <c r="D2703" t="s">
         <v>2705</v>
@@ -47168,7 +47168,7 @@
         <v>15</v>
       </c>
       <c r="C2704">
-        <v>4983.3</v>
+        <v>3971.7</v>
       </c>
       <c r="D2704" t="s">
         <v>2706</v>
@@ -47182,7 +47182,7 @@
         <v>16</v>
       </c>
       <c r="C2705">
-        <v>4964.4</v>
+        <v>3957.1</v>
       </c>
       <c r="D2705" t="s">
         <v>2707</v>
@@ -47196,7 +47196,7 @@
         <v>17</v>
       </c>
       <c r="C2706">
-        <v>5028.3</v>
+        <v>3807.3</v>
       </c>
       <c r="D2706" t="s">
         <v>2708</v>
@@ -47210,7 +47210,7 @@
         <v>18</v>
       </c>
       <c r="C2707">
-        <v>5026.3</v>
+        <v>3798.5</v>
       </c>
       <c r="D2707" t="s">
         <v>2709</v>
@@ -47224,7 +47224,7 @@
         <v>19</v>
       </c>
       <c r="C2708">
-        <v>5029.5</v>
+        <v>3784.1</v>
       </c>
       <c r="D2708" t="s">
         <v>2710</v>
@@ -47238,7 +47238,7 @@
         <v>20</v>
       </c>
       <c r="C2709">
-        <v>5009.2</v>
+        <v>3797.1</v>
       </c>
       <c r="D2709" t="s">
         <v>2711</v>
@@ -47252,7 +47252,7 @@
         <v>21</v>
       </c>
       <c r="C2710">
-        <v>5037.2</v>
+        <v>3822.8</v>
       </c>
       <c r="D2710" t="s">
         <v>2712</v>
@@ -47266,7 +47266,7 @@
         <v>22</v>
       </c>
       <c r="C2711">
-        <v>5070.2</v>
+        <v>3822.8</v>
       </c>
       <c r="D2711" t="s">
         <v>2713</v>
@@ -47280,7 +47280,7 @@
         <v>23</v>
       </c>
       <c r="C2712">
-        <v>5106.6</v>
+        <v>3833.3</v>
       </c>
       <c r="D2712" t="s">
         <v>2714</v>
@@ -47294,7 +47294,7 @@
         <v>24</v>
       </c>
       <c r="C2713">
-        <v>5121.9</v>
+        <v>3821.6</v>
       </c>
       <c r="D2713" t="s">
         <v>2715</v>
@@ -47308,7 +47308,7 @@
         <v>25</v>
       </c>
       <c r="C2714">
-        <v>5370.7</v>
+        <v>4044.3</v>
       </c>
       <c r="D2714" t="s">
         <v>2716</v>
@@ -47322,7 +47322,7 @@
         <v>26</v>
       </c>
       <c r="C2715">
-        <v>5440.8</v>
+        <v>4058.1</v>
       </c>
       <c r="D2715" t="s">
         <v>2717</v>
@@ -47336,7 +47336,7 @@
         <v>27</v>
       </c>
       <c r="C2716">
-        <v>5472.7</v>
+        <v>4078.6</v>
       </c>
       <c r="D2716" t="s">
         <v>2718</v>
@@ -47350,7 +47350,7 @@
         <v>28</v>
       </c>
       <c r="C2717">
-        <v>5485.1</v>
+        <v>4131</v>
       </c>
       <c r="D2717" t="s">
         <v>2719</v>
@@ -47364,7 +47364,7 @@
         <v>29</v>
       </c>
       <c r="C2718">
-        <v>5429.7</v>
+        <v>4193.4</v>
       </c>
       <c r="D2718" t="s">
         <v>2720</v>
@@ -47378,7 +47378,7 @@
         <v>30</v>
       </c>
       <c r="C2719">
-        <v>5455.1</v>
+        <v>4274.1</v>
       </c>
       <c r="D2719" t="s">
         <v>2721</v>
@@ -47392,7 +47392,7 @@
         <v>31</v>
       </c>
       <c r="C2720">
-        <v>5525</v>
+        <v>4382.4</v>
       </c>
       <c r="D2720" t="s">
         <v>2722</v>
@@ -47406,7 +47406,7 @@
         <v>32</v>
       </c>
       <c r="C2721">
-        <v>5613.1</v>
+        <v>4501</v>
       </c>
       <c r="D2721" t="s">
         <v>2723</v>
@@ -47420,7 +47420,7 @@
         <v>33</v>
       </c>
       <c r="C2722">
-        <v>5346.6</v>
+        <v>4101.1</v>
       </c>
       <c r="D2722" t="s">
         <v>2724</v>
@@ -47434,7 +47434,7 @@
         <v>34</v>
       </c>
       <c r="C2723">
-        <v>5235.8</v>
+        <v>4212.7</v>
       </c>
       <c r="D2723" t="s">
         <v>2725</v>
@@ -47448,7 +47448,7 @@
         <v>35</v>
       </c>
       <c r="C2724">
-        <v>5321.9</v>
+        <v>4285.8</v>
       </c>
       <c r="D2724" t="s">
         <v>2726</v>
@@ -47462,7 +47462,7 @@
         <v>36</v>
       </c>
       <c r="C2725">
-        <v>5339.6</v>
+        <v>4429.4</v>
       </c>
       <c r="D2725" t="s">
         <v>2727</v>
@@ -47476,7 +47476,7 @@
         <v>37</v>
       </c>
       <c r="C2726">
-        <v>5478.6</v>
+        <v>4345.2</v>
       </c>
       <c r="D2726" t="s">
         <v>2728</v>
@@ -47490,7 +47490,7 @@
         <v>38</v>
       </c>
       <c r="C2727">
-        <v>5477.8</v>
+        <v>4352.1</v>
       </c>
       <c r="D2727" t="s">
         <v>2729</v>
@@ -47504,7 +47504,7 @@
         <v>39</v>
       </c>
       <c r="C2728">
-        <v>5450.7</v>
+        <v>4428.2</v>
       </c>
       <c r="D2728" t="s">
         <v>2730</v>
@@ -47518,7 +47518,7 @@
         <v>40</v>
       </c>
       <c r="C2729">
-        <v>5454.3</v>
+        <v>4496.3</v>
       </c>
       <c r="D2729" t="s">
         <v>2731</v>
@@ -47532,7 +47532,7 @@
         <v>41</v>
       </c>
       <c r="C2730">
-        <v>5403.8</v>
+        <v>4679.5</v>
       </c>
       <c r="D2730" t="s">
         <v>2732</v>
@@ -47546,7 +47546,7 @@
         <v>42</v>
       </c>
       <c r="C2731">
-        <v>5291.7</v>
+        <v>4739.1</v>
       </c>
       <c r="D2731" t="s">
         <v>2733</v>
@@ -47560,7 +47560,7 @@
         <v>43</v>
       </c>
       <c r="C2732">
-        <v>5301</v>
+        <v>4773.8</v>
       </c>
       <c r="D2732" t="s">
         <v>2734</v>
@@ -47574,7 +47574,7 @@
         <v>44</v>
       </c>
       <c r="C2733">
-        <v>5229.1</v>
+        <v>4794.9</v>
       </c>
       <c r="D2733" t="s">
         <v>2735</v>
@@ -47588,7 +47588,7 @@
         <v>45</v>
       </c>
       <c r="C2734">
-        <v>4753.5</v>
+        <v>4343.2</v>
       </c>
       <c r="D2734" t="s">
         <v>2736</v>
@@ -47602,7 +47602,7 @@
         <v>46</v>
       </c>
       <c r="C2735">
-        <v>4748.1</v>
+        <v>4330.9</v>
       </c>
       <c r="D2735" t="s">
         <v>2737</v>
@@ -47616,7 +47616,7 @@
         <v>47</v>
       </c>
       <c r="C2736">
-        <v>4796.8</v>
+        <v>4359.4</v>
       </c>
       <c r="D2736" t="s">
         <v>2738</v>
@@ -47630,7 +47630,7 @@
         <v>48</v>
       </c>
       <c r="C2737">
-        <v>4748.6</v>
+        <v>4394</v>
       </c>
       <c r="D2737" t="s">
         <v>2739</v>
@@ -47644,7 +47644,7 @@
         <v>49</v>
       </c>
       <c r="C2738">
-        <v>4619.7</v>
+        <v>4428.4</v>
       </c>
       <c r="D2738" t="s">
         <v>2740</v>
@@ -47658,7 +47658,7 @@
         <v>50</v>
       </c>
       <c r="C2739">
-        <v>4585.8</v>
+        <v>4434.8</v>
       </c>
       <c r="D2739" t="s">
         <v>2741</v>
@@ -47672,7 +47672,7 @@
         <v>51</v>
       </c>
       <c r="C2740">
-        <v>4550.6</v>
+        <v>4505.1</v>
       </c>
       <c r="D2740" t="s">
         <v>2742</v>
@@ -47686,7 +47686,7 @@
         <v>52</v>
       </c>
       <c r="C2741">
-        <v>4520.3</v>
+        <v>4532.4</v>
       </c>
       <c r="D2741" t="s">
         <v>2743</v>
@@ -47700,7 +47700,7 @@
         <v>53</v>
       </c>
       <c r="C2742">
-        <v>4409.6</v>
+        <v>4391.1</v>
       </c>
       <c r="D2742" t="s">
         <v>2744</v>
@@ -47714,7 +47714,7 @@
         <v>54</v>
       </c>
       <c r="C2743">
-        <v>4360.7</v>
+        <v>4397.8</v>
       </c>
       <c r="D2743" t="s">
         <v>2745</v>
@@ -47728,7 +47728,7 @@
         <v>55</v>
       </c>
       <c r="C2744">
-        <v>4331.7</v>
+        <v>4477</v>
       </c>
       <c r="D2744" t="s">
         <v>2746</v>
@@ -47742,7 +47742,7 @@
         <v>56</v>
       </c>
       <c r="C2745">
-        <v>4310.5</v>
+        <v>4482.4</v>
       </c>
       <c r="D2745" t="s">
         <v>2747</v>
@@ -47756,7 +47756,7 @@
         <v>57</v>
       </c>
       <c r="C2746">
-        <v>4208.1</v>
+        <v>4478.1</v>
       </c>
       <c r="D2746" t="s">
         <v>2748</v>
@@ -47770,7 +47770,7 @@
         <v>58</v>
       </c>
       <c r="C2747">
-        <v>4213.8</v>
+        <v>4500.5</v>
       </c>
       <c r="D2747" t="s">
         <v>2749</v>
@@ -47784,7 +47784,7 @@
         <v>59</v>
       </c>
       <c r="C2748">
-        <v>4208.3</v>
+        <v>4542.6</v>
       </c>
       <c r="D2748" t="s">
         <v>2750</v>
@@ -47798,7 +47798,7 @@
         <v>60</v>
       </c>
       <c r="C2749">
-        <v>4214.1</v>
+        <v>4562.9</v>
       </c>
       <c r="D2749" t="s">
         <v>2751</v>
@@ -47812,7 +47812,7 @@
         <v>61</v>
       </c>
       <c r="C2750">
-        <v>4290.6</v>
+        <v>4498.7</v>
       </c>
       <c r="D2750" t="s">
         <v>2752</v>
@@ -47826,7 +47826,7 @@
         <v>62</v>
       </c>
       <c r="C2751">
-        <v>4251.5</v>
+        <v>4550.1</v>
       </c>
       <c r="D2751" t="s">
         <v>2753</v>
@@ -47840,7 +47840,7 @@
         <v>63</v>
       </c>
       <c r="C2752">
-        <v>4296</v>
+        <v>4564.4</v>
       </c>
       <c r="D2752" t="s">
         <v>2754</v>
@@ -47854,7 +47854,7 @@
         <v>64</v>
       </c>
       <c r="C2753">
-        <v>4285</v>
+        <v>4551.7</v>
       </c>
       <c r="D2753" t="s">
         <v>2755</v>
@@ -47868,7 +47868,7 @@
         <v>65</v>
       </c>
       <c r="C2754">
-        <v>4321.2</v>
+        <v>4284.8</v>
       </c>
       <c r="D2754" t="s">
         <v>2756</v>
@@ -47882,7 +47882,7 @@
         <v>66</v>
       </c>
       <c r="C2755">
-        <v>4265.7</v>
+        <v>4266.3</v>
       </c>
       <c r="D2755" t="s">
         <v>2757</v>
@@ -47896,7 +47896,7 @@
         <v>67</v>
       </c>
       <c r="C2756">
-        <v>4222.2</v>
+        <v>4186.2</v>
       </c>
       <c r="D2756" t="s">
         <v>2758</v>
@@ -47910,7 +47910,7 @@
         <v>68</v>
       </c>
       <c r="C2757">
-        <v>4218.4</v>
+        <v>4178.8</v>
       </c>
       <c r="D2757" t="s">
         <v>2759</v>
@@ -47924,7 +47924,7 @@
         <v>69</v>
       </c>
       <c r="C2758">
-        <v>4435.1</v>
+        <v>4620.4</v>
       </c>
       <c r="D2758" t="s">
         <v>2760</v>
@@ -47938,7 +47938,7 @@
         <v>70</v>
       </c>
       <c r="C2759">
-        <v>4392.7</v>
+        <v>4537.8</v>
       </c>
       <c r="D2759" t="s">
         <v>2761</v>
@@ -47952,7 +47952,7 @@
         <v>71</v>
       </c>
       <c r="C2760">
-        <v>4403.3</v>
+        <v>4468.2</v>
       </c>
       <c r="D2760" t="s">
         <v>2762</v>
@@ -47966,7 +47966,7 @@
         <v>72</v>
       </c>
       <c r="C2761">
-        <v>4415.1</v>
+        <v>4351.6</v>
       </c>
       <c r="D2761" t="s">
         <v>2763</v>
@@ -47980,7 +47980,7 @@
         <v>73</v>
       </c>
       <c r="C2762">
-        <v>5074.6</v>
+        <v>5156</v>
       </c>
       <c r="D2762" t="s">
         <v>2764</v>
@@ -47994,7 +47994,7 @@
         <v>74</v>
       </c>
       <c r="C2763">
-        <v>5063.7</v>
+        <v>5016</v>
       </c>
       <c r="D2763" t="s">
         <v>2765</v>
@@ -48008,7 +48008,7 @@
         <v>75</v>
       </c>
       <c r="C2764">
-        <v>5064.6</v>
+        <v>4916.3</v>
       </c>
       <c r="D2764" t="s">
         <v>2766</v>
@@ -48022,7 +48022,7 @@
         <v>76</v>
       </c>
       <c r="C2765">
-        <v>5118.2</v>
+        <v>4953.5</v>
       </c>
       <c r="D2765" t="s">
         <v>2767</v>
@@ -48036,7 +48036,7 @@
         <v>77</v>
       </c>
       <c r="C2766">
-        <v>5371.7</v>
+        <v>5060.4</v>
       </c>
       <c r="D2766" t="s">
         <v>2768</v>
@@ -48050,7 +48050,7 @@
         <v>78</v>
       </c>
       <c r="C2767">
-        <v>5402.4</v>
+        <v>5019.7</v>
       </c>
       <c r="D2767" t="s">
         <v>2769</v>
@@ -48064,7 +48064,7 @@
         <v>79</v>
       </c>
       <c r="C2768">
-        <v>5377.4</v>
+        <v>4985.3</v>
       </c>
       <c r="D2768" t="s">
         <v>2770</v>
@@ -48078,7 +48078,7 @@
         <v>80</v>
       </c>
       <c r="C2769">
-        <v>5406.3</v>
+        <v>4957.4</v>
       </c>
       <c r="D2769" t="s">
         <v>2771</v>
@@ -48092,7 +48092,7 @@
         <v>81</v>
       </c>
       <c r="C2770">
-        <v>5393.1</v>
+        <v>5371.6</v>
       </c>
       <c r="D2770" t="s">
         <v>2772</v>
@@ -48106,7 +48106,7 @@
         <v>82</v>
       </c>
       <c r="C2771">
-        <v>5385.8</v>
+        <v>5301.4</v>
       </c>
       <c r="D2771" t="s">
         <v>2773</v>
@@ -48120,7 +48120,7 @@
         <v>83</v>
       </c>
       <c r="C2772">
-        <v>5410.2</v>
+        <v>5409.7</v>
       </c>
       <c r="D2772" t="s">
         <v>2774</v>
@@ -48134,7 +48134,7 @@
         <v>84</v>
       </c>
       <c r="C2773">
-        <v>5443.6</v>
+        <v>5467.1</v>
       </c>
       <c r="D2773" t="s">
         <v>2775</v>
@@ -48148,7 +48148,7 @@
         <v>85</v>
       </c>
       <c r="C2774">
-        <v>5555</v>
+        <v>5495.6</v>
       </c>
       <c r="D2774" t="s">
         <v>2776</v>
@@ -48162,7 +48162,7 @@
         <v>86</v>
       </c>
       <c r="C2775">
-        <v>5497.5</v>
+        <v>5479.4</v>
       </c>
       <c r="D2775" t="s">
         <v>2777</v>
@@ -48176,7 +48176,7 @@
         <v>87</v>
       </c>
       <c r="C2776">
-        <v>5501.4</v>
+        <v>5517.4</v>
       </c>
       <c r="D2776" t="s">
         <v>2778</v>
@@ -48190,7 +48190,7 @@
         <v>88</v>
       </c>
       <c r="C2777">
-        <v>5449.9</v>
+        <v>5498.6</v>
       </c>
       <c r="D2777" t="s">
         <v>2779</v>
@@ -48204,7 +48204,7 @@
         <v>89</v>
       </c>
       <c r="C2778">
-        <v>5281.8</v>
+        <v>5180.8</v>
       </c>
       <c r="D2778" t="s">
         <v>2780</v>
@@ -48218,7 +48218,7 @@
         <v>90</v>
       </c>
       <c r="C2779">
-        <v>5190.4</v>
+        <v>5177.9</v>
       </c>
       <c r="D2779" t="s">
         <v>2781</v>
@@ -48232,7 +48232,7 @@
         <v>91</v>
       </c>
       <c r="C2780">
-        <v>5188.5</v>
+        <v>5142.6</v>
       </c>
       <c r="D2780" t="s">
         <v>2782</v>
@@ -48246,7 +48246,7 @@
         <v>92</v>
       </c>
       <c r="C2781">
-        <v>5090.2</v>
+        <v>5104.1</v>
       </c>
       <c r="D2781" t="s">
         <v>2783</v>
@@ -48260,7 +48260,7 @@
         <v>93</v>
       </c>
       <c r="C2782">
-        <v>4692.8</v>
+        <v>4853.9</v>
       </c>
       <c r="D2782" t="s">
         <v>2784</v>
@@ -48274,7 +48274,7 @@
         <v>94</v>
       </c>
       <c r="C2783">
-        <v>4608.9</v>
+        <v>4775.1</v>
       </c>
       <c r="D2783" t="s">
         <v>2785</v>
@@ -48288,7 +48288,7 @@
         <v>95</v>
       </c>
       <c r="C2784">
-        <v>4683.5</v>
+        <v>4781.3</v>
       </c>
       <c r="D2784" t="s">
         <v>2786</v>
@@ -48302,7 +48302,7 @@
         <v>96</v>
       </c>
       <c r="C2785">
-        <v>4622.3</v>
+        <v>4752.8</v>
       </c>
       <c r="D2785" t="s">
         <v>2787</v>

--- a/Market Fundamentals/Transelectrica_data/Cons_Prod_final/Weekly_Production_2026.xlsx
+++ b/Market Fundamentals/Transelectrica_data/Cons_Prod_final/Weekly_Production_2026.xlsx
@@ -45628,7 +45628,7 @@
         <v>1</v>
       </c>
       <c r="C2594">
-        <v>5283.4</v>
+        <v>4756.1</v>
       </c>
       <c r="D2594" t="s">
         <v>2596</v>
@@ -45642,7 +45642,7 @@
         <v>2</v>
       </c>
       <c r="C2595">
-        <v>5334.3</v>
+        <v>4802</v>
       </c>
       <c r="D2595" t="s">
         <v>2597</v>
@@ -45656,7 +45656,7 @@
         <v>3</v>
       </c>
       <c r="C2596">
-        <v>5280.2</v>
+        <v>4750.7</v>
       </c>
       <c r="D2596" t="s">
         <v>2598</v>
@@ -45670,7 +45670,7 @@
         <v>4</v>
       </c>
       <c r="C2597">
-        <v>5228.1</v>
+        <v>4731.1</v>
       </c>
       <c r="D2597" t="s">
         <v>2599</v>
@@ -45684,7 +45684,7 @@
         <v>5</v>
       </c>
       <c r="C2598">
-        <v>4382.7</v>
+        <v>4459.5</v>
       </c>
       <c r="D2598" t="s">
         <v>2600</v>
@@ -45698,7 +45698,7 @@
         <v>6</v>
       </c>
       <c r="C2599">
-        <v>4345</v>
+        <v>4460</v>
       </c>
       <c r="D2599" t="s">
         <v>2601</v>
@@ -45712,7 +45712,7 @@
         <v>7</v>
       </c>
       <c r="C2600">
-        <v>4296.2</v>
+        <v>4420.4</v>
       </c>
       <c r="D2600" t="s">
         <v>2602</v>
@@ -45726,7 +45726,7 @@
         <v>8</v>
       </c>
       <c r="C2601">
-        <v>4240</v>
+        <v>4355.9</v>
       </c>
       <c r="D2601" t="s">
         <v>2603</v>
@@ -45740,7 +45740,7 @@
         <v>9</v>
       </c>
       <c r="C2602">
-        <v>4156.4</v>
+        <v>4338</v>
       </c>
       <c r="D2602" t="s">
         <v>2604</v>
@@ -45754,7 +45754,7 @@
         <v>10</v>
       </c>
       <c r="C2603">
-        <v>4106.1</v>
+        <v>4315.7</v>
       </c>
       <c r="D2603" t="s">
         <v>2605</v>
@@ -45768,7 +45768,7 @@
         <v>11</v>
       </c>
       <c r="C2604">
-        <v>4063.2</v>
+        <v>4338.3</v>
       </c>
       <c r="D2604" t="s">
         <v>2606</v>
@@ -45782,7 +45782,7 @@
         <v>12</v>
       </c>
       <c r="C2605">
-        <v>4032.1</v>
+        <v>4351.6</v>
       </c>
       <c r="D2605" t="s">
         <v>2607</v>
@@ -45796,7 +45796,7 @@
         <v>13</v>
       </c>
       <c r="C2606">
-        <v>3972.1</v>
+        <v>4412.7</v>
       </c>
       <c r="D2606" t="s">
         <v>2608</v>
@@ -45810,7 +45810,7 @@
         <v>14</v>
       </c>
       <c r="C2607">
-        <v>3964.1</v>
+        <v>4422.3</v>
       </c>
       <c r="D2607" t="s">
         <v>2609</v>
@@ -45824,7 +45824,7 @@
         <v>15</v>
       </c>
       <c r="C2608">
-        <v>3951.7</v>
+        <v>4436.4</v>
       </c>
       <c r="D2608" t="s">
         <v>2610</v>
@@ -45838,7 +45838,7 @@
         <v>16</v>
       </c>
       <c r="C2609">
-        <v>3937.1</v>
+        <v>4476.7</v>
       </c>
       <c r="D2609" t="s">
         <v>2611</v>
@@ -45852,7 +45852,7 @@
         <v>17</v>
       </c>
       <c r="C2610">
-        <v>3797.3</v>
+        <v>4335.4</v>
       </c>
       <c r="D2610" t="s">
         <v>2612</v>
@@ -45866,7 +45866,7 @@
         <v>18</v>
       </c>
       <c r="C2611">
-        <v>3788.5</v>
+        <v>4338.7</v>
       </c>
       <c r="D2611" t="s">
         <v>2613</v>
@@ -45880,7 +45880,7 @@
         <v>19</v>
       </c>
       <c r="C2612">
-        <v>3774.1</v>
+        <v>4320.1</v>
       </c>
       <c r="D2612" t="s">
         <v>2614</v>
@@ -45894,7 +45894,7 @@
         <v>20</v>
       </c>
       <c r="C2613">
-        <v>3777.1</v>
+        <v>4331.6</v>
       </c>
       <c r="D2613" t="s">
         <v>2615</v>
@@ -45908,7 +45908,7 @@
         <v>21</v>
       </c>
       <c r="C2614">
-        <v>3812.8</v>
+        <v>4264.7</v>
       </c>
       <c r="D2614" t="s">
         <v>2616</v>
@@ -45922,7 +45922,7 @@
         <v>22</v>
       </c>
       <c r="C2615">
-        <v>3822.8</v>
+        <v>4287.8</v>
       </c>
       <c r="D2615" t="s">
         <v>2617</v>
@@ -45936,7 +45936,7 @@
         <v>23</v>
       </c>
       <c r="C2616">
-        <v>3853.3</v>
+        <v>4309.1</v>
       </c>
       <c r="D2616" t="s">
         <v>2618</v>
@@ -45950,7 +45950,7 @@
         <v>24</v>
       </c>
       <c r="C2617">
-        <v>3871.6</v>
+        <v>4318.3</v>
       </c>
       <c r="D2617" t="s">
         <v>2619</v>
@@ -45964,7 +45964,7 @@
         <v>25</v>
       </c>
       <c r="C2618">
-        <v>4134.3</v>
+        <v>4619.2</v>
       </c>
       <c r="D2618" t="s">
         <v>2620</v>
@@ -45978,7 +45978,7 @@
         <v>26</v>
       </c>
       <c r="C2619">
-        <v>4178.1</v>
+        <v>4645.1</v>
       </c>
       <c r="D2619" t="s">
         <v>2621</v>
@@ -45992,7 +45992,7 @@
         <v>27</v>
       </c>
       <c r="C2620">
-        <v>4238.6</v>
+        <v>4684.8</v>
       </c>
       <c r="D2620" t="s">
         <v>2622</v>
@@ -46006,7 +46006,7 @@
         <v>28</v>
       </c>
       <c r="C2621">
-        <v>4321</v>
+        <v>4717.5</v>
       </c>
       <c r="D2621" t="s">
         <v>2623</v>
@@ -46020,7 +46020,7 @@
         <v>29</v>
       </c>
       <c r="C2622">
-        <v>4413.4</v>
+        <v>4562.4</v>
       </c>
       <c r="D2622" t="s">
         <v>2624</v>
@@ -46034,7 +46034,7 @@
         <v>30</v>
       </c>
       <c r="C2623">
-        <v>4514.1</v>
+        <v>4602.3</v>
       </c>
       <c r="D2623" t="s">
         <v>2625</v>
@@ -46048,7 +46048,7 @@
         <v>31</v>
       </c>
       <c r="C2624">
-        <v>4662.4</v>
+        <v>4655.1</v>
       </c>
       <c r="D2624" t="s">
         <v>2626</v>
@@ -46062,7 +46062,7 @@
         <v>32</v>
       </c>
       <c r="C2625">
-        <v>4811</v>
+        <v>4756.4</v>
       </c>
       <c r="D2625" t="s">
         <v>2627</v>
@@ -46076,7 +46076,7 @@
         <v>33</v>
       </c>
       <c r="C2626">
-        <v>4431.1</v>
+        <v>4756.9</v>
       </c>
       <c r="D2626" t="s">
         <v>2628</v>
@@ -46090,7 +46090,7 @@
         <v>34</v>
       </c>
       <c r="C2627">
-        <v>4572.7</v>
+        <v>4883.9</v>
       </c>
       <c r="D2627" t="s">
         <v>2629</v>
@@ -46104,7 +46104,7 @@
         <v>35</v>
       </c>
       <c r="C2628">
-        <v>4685.8</v>
+        <v>4985.9</v>
       </c>
       <c r="D2628" t="s">
         <v>2630</v>
@@ -46118,7 +46118,7 @@
         <v>36</v>
       </c>
       <c r="C2629">
-        <v>4869.4</v>
+        <v>5130.7</v>
       </c>
       <c r="D2629" t="s">
         <v>2631</v>
@@ -46132,7 +46132,7 @@
         <v>37</v>
       </c>
       <c r="C2630">
-        <v>4825.2</v>
+        <v>5142.8</v>
       </c>
       <c r="D2630" t="s">
         <v>2632</v>
@@ -46146,7 +46146,7 @@
         <v>38</v>
       </c>
       <c r="C2631">
-        <v>4852.1</v>
+        <v>5198.3</v>
       </c>
       <c r="D2631" t="s">
         <v>2633</v>
@@ -46160,7 +46160,7 @@
         <v>39</v>
       </c>
       <c r="C2632">
-        <v>4918.2</v>
+        <v>5295.6</v>
       </c>
       <c r="D2632" t="s">
         <v>2634</v>
@@ -46174,7 +46174,7 @@
         <v>40</v>
       </c>
       <c r="C2633">
-        <v>4946.3</v>
+        <v>5316.6</v>
       </c>
       <c r="D2633" t="s">
         <v>2635</v>
@@ -46188,7 +46188,7 @@
         <v>41</v>
       </c>
       <c r="C2634">
-        <v>5079.5</v>
+        <v>5430.6</v>
       </c>
       <c r="D2634" t="s">
         <v>2636</v>
@@ -46202,7 +46202,7 @@
         <v>42</v>
       </c>
       <c r="C2635">
-        <v>5109.1</v>
+        <v>5428.9</v>
       </c>
       <c r="D2635" t="s">
         <v>2637</v>
@@ -46216,7 +46216,7 @@
         <v>43</v>
       </c>
       <c r="C2636">
-        <v>5133.8</v>
+        <v>5483.1</v>
       </c>
       <c r="D2636" t="s">
         <v>2638</v>
@@ -46230,7 +46230,7 @@
         <v>44</v>
       </c>
       <c r="C2637">
-        <v>5164.9</v>
+        <v>5518.7</v>
       </c>
       <c r="D2637" t="s">
         <v>2639</v>
@@ -46244,7 +46244,7 @@
         <v>45</v>
       </c>
       <c r="C2638">
-        <v>4743.2</v>
+        <v>5068.1</v>
       </c>
       <c r="D2638" t="s">
         <v>2640</v>
@@ -46258,7 +46258,7 @@
         <v>46</v>
       </c>
       <c r="C2639">
-        <v>4750.9</v>
+        <v>5050.4</v>
       </c>
       <c r="D2639" t="s">
         <v>2641</v>
@@ -46272,7 +46272,7 @@
         <v>47</v>
       </c>
       <c r="C2640">
-        <v>4779.4</v>
+        <v>5120.1</v>
       </c>
       <c r="D2640" t="s">
         <v>2642</v>
@@ -46286,7 +46286,7 @@
         <v>48</v>
       </c>
       <c r="C2641">
-        <v>4784</v>
+        <v>5116.6</v>
       </c>
       <c r="D2641" t="s">
         <v>2643</v>
@@ -46300,7 +46300,7 @@
         <v>49</v>
       </c>
       <c r="C2642">
-        <v>4778.4</v>
+        <v>4972.3</v>
       </c>
       <c r="D2642" t="s">
         <v>2644</v>
@@ -46314,7 +46314,7 @@
         <v>50</v>
       </c>
       <c r="C2643">
-        <v>4754.8</v>
+        <v>4925</v>
       </c>
       <c r="D2643" t="s">
         <v>2645</v>
@@ -46328,7 +46328,7 @@
         <v>51</v>
       </c>
       <c r="C2644">
-        <v>4795.1</v>
+        <v>4784.7</v>
       </c>
       <c r="D2644" t="s">
         <v>2646</v>
@@ -46342,7 +46342,7 @@
         <v>52</v>
       </c>
       <c r="C2645">
-        <v>4822.4</v>
+        <v>4679.5</v>
       </c>
       <c r="D2645" t="s">
         <v>2647</v>
@@ -46356,7 +46356,7 @@
         <v>53</v>
       </c>
       <c r="C2646">
-        <v>4671.1</v>
+        <v>4782</v>
       </c>
       <c r="D2646" t="s">
         <v>2648</v>
@@ -46370,7 +46370,7 @@
         <v>54</v>
       </c>
       <c r="C2647">
-        <v>4687.8</v>
+        <v>4731.6</v>
       </c>
       <c r="D2647" t="s">
         <v>2649</v>
@@ -46384,7 +46384,7 @@
         <v>55</v>
       </c>
       <c r="C2648">
-        <v>4797</v>
+        <v>4799.4</v>
       </c>
       <c r="D2648" t="s">
         <v>2650</v>
@@ -46398,7 +46398,7 @@
         <v>56</v>
       </c>
       <c r="C2649">
-        <v>4822.4</v>
+        <v>4824.7</v>
       </c>
       <c r="D2649" t="s">
         <v>2651</v>
@@ -46412,7 +46412,7 @@
         <v>57</v>
       </c>
       <c r="C2650">
-        <v>4848.1</v>
+        <v>4905.9</v>
       </c>
       <c r="D2650" t="s">
         <v>2652</v>
@@ -46426,7 +46426,7 @@
         <v>58</v>
       </c>
       <c r="C2651">
-        <v>4890.5</v>
+        <v>4958.9</v>
       </c>
       <c r="D2651" t="s">
         <v>2653</v>
@@ -46440,7 +46440,7 @@
         <v>59</v>
       </c>
       <c r="C2652">
-        <v>4942.6</v>
+        <v>4942</v>
       </c>
       <c r="D2652" t="s">
         <v>2654</v>
@@ -46454,7 +46454,7 @@
         <v>60</v>
       </c>
       <c r="C2653">
-        <v>4952.9</v>
+        <v>4989.1</v>
       </c>
       <c r="D2653" t="s">
         <v>2655</v>
@@ -46468,7 +46468,7 @@
         <v>61</v>
       </c>
       <c r="C2654">
-        <v>4878.7</v>
+        <v>4896.7</v>
       </c>
       <c r="D2654" t="s">
         <v>2656</v>
@@ -46482,7 +46482,7 @@
         <v>62</v>
       </c>
       <c r="C2655">
-        <v>4910.1</v>
+        <v>4965.5</v>
       </c>
       <c r="D2655" t="s">
         <v>2657</v>
@@ -46496,7 +46496,7 @@
         <v>63</v>
       </c>
       <c r="C2656">
-        <v>4904.4</v>
+        <v>4962.9</v>
       </c>
       <c r="D2656" t="s">
         <v>2658</v>
@@ -46510,7 +46510,7 @@
         <v>64</v>
       </c>
       <c r="C2657">
-        <v>4891.7</v>
+        <v>4973.5</v>
       </c>
       <c r="D2657" t="s">
         <v>2659</v>
@@ -46524,7 +46524,7 @@
         <v>65</v>
       </c>
       <c r="C2658">
-        <v>4614.8</v>
+        <v>4991.5</v>
       </c>
       <c r="D2658" t="s">
         <v>2660</v>
@@ -46538,7 +46538,7 @@
         <v>66</v>
       </c>
       <c r="C2659">
-        <v>4596.3</v>
+        <v>5000.4</v>
       </c>
       <c r="D2659" t="s">
         <v>2661</v>
@@ -46552,7 +46552,7 @@
         <v>67</v>
       </c>
       <c r="C2660">
-        <v>4516.2</v>
+        <v>5115</v>
       </c>
       <c r="D2660" t="s">
         <v>2662</v>
@@ -46566,7 +46566,7 @@
         <v>68</v>
       </c>
       <c r="C2661">
-        <v>4508.8</v>
+        <v>5073.5</v>
       </c>
       <c r="D2661" t="s">
         <v>2663</v>
@@ -46580,7 +46580,7 @@
         <v>69</v>
       </c>
       <c r="C2662">
-        <v>4940.4</v>
+        <v>5469.9</v>
       </c>
       <c r="D2662" t="s">
         <v>2664</v>
@@ -46594,7 +46594,7 @@
         <v>70</v>
       </c>
       <c r="C2663">
-        <v>4837.8</v>
+        <v>5410.3</v>
       </c>
       <c r="D2663" t="s">
         <v>2665</v>
@@ -46608,7 +46608,7 @@
         <v>71</v>
       </c>
       <c r="C2664">
-        <v>4758.2</v>
+        <v>5331.1</v>
       </c>
       <c r="D2664" t="s">
         <v>2666</v>
@@ -46622,7 +46622,7 @@
         <v>72</v>
       </c>
       <c r="C2665">
-        <v>4611.6</v>
+        <v>5258.2</v>
       </c>
       <c r="D2665" t="s">
         <v>2667</v>
@@ -46636,7 +46636,7 @@
         <v>73</v>
       </c>
       <c r="C2666">
-        <v>5396</v>
+        <v>5788.1</v>
       </c>
       <c r="D2666" t="s">
         <v>2668</v>
@@ -46650,7 +46650,7 @@
         <v>74</v>
       </c>
       <c r="C2667">
-        <v>5246</v>
+        <v>5703.3</v>
       </c>
       <c r="D2667" t="s">
         <v>2669</v>
@@ -46664,7 +46664,7 @@
         <v>75</v>
       </c>
       <c r="C2668">
-        <v>5126.3</v>
+        <v>5598.6</v>
       </c>
       <c r="D2668" t="s">
         <v>2670</v>
@@ -46678,7 +46678,7 @@
         <v>76</v>
       </c>
       <c r="C2669">
-        <v>5153.5</v>
+        <v>5541.9</v>
       </c>
       <c r="D2669" t="s">
         <v>2671</v>
@@ -46692,7 +46692,7 @@
         <v>77</v>
       </c>
       <c r="C2670">
-        <v>5250.4</v>
+        <v>5469.5</v>
       </c>
       <c r="D2670" t="s">
         <v>2672</v>
@@ -46706,7 +46706,7 @@
         <v>78</v>
       </c>
       <c r="C2671">
-        <v>5209.7</v>
+        <v>5435.7</v>
       </c>
       <c r="D2671" t="s">
         <v>2673</v>
@@ -46720,7 +46720,7 @@
         <v>79</v>
       </c>
       <c r="C2672">
-        <v>5195.3</v>
+        <v>5359</v>
       </c>
       <c r="D2672" t="s">
         <v>2674</v>
@@ -46734,7 +46734,7 @@
         <v>80</v>
       </c>
       <c r="C2673">
-        <v>5157.4</v>
+        <v>5317.4</v>
       </c>
       <c r="D2673" t="s">
         <v>2675</v>
@@ -46748,7 +46748,7 @@
         <v>81</v>
       </c>
       <c r="C2674">
-        <v>5591.6</v>
+        <v>5575</v>
       </c>
       <c r="D2674" t="s">
         <v>2676</v>
@@ -46762,7 +46762,7 @@
         <v>82</v>
       </c>
       <c r="C2675">
-        <v>5551.4</v>
+        <v>5559.7</v>
       </c>
       <c r="D2675" t="s">
         <v>2677</v>
@@ -46776,7 +46776,7 @@
         <v>83</v>
       </c>
       <c r="C2676">
-        <v>5659.7</v>
+        <v>5562</v>
       </c>
       <c r="D2676" t="s">
         <v>2678</v>
@@ -46790,7 +46790,7 @@
         <v>84</v>
       </c>
       <c r="C2677">
-        <v>5727.1</v>
+        <v>5632.1</v>
       </c>
       <c r="D2677" t="s">
         <v>2679</v>
@@ -46804,7 +46804,7 @@
         <v>85</v>
       </c>
       <c r="C2678">
-        <v>5685.6</v>
+        <v>6030.9</v>
       </c>
       <c r="D2678" t="s">
         <v>2680</v>
@@ -46818,7 +46818,7 @@
         <v>86</v>
       </c>
       <c r="C2679">
-        <v>5629.4</v>
+        <v>5989.9</v>
       </c>
       <c r="D2679" t="s">
         <v>2681</v>
@@ -46832,7 +46832,7 @@
         <v>87</v>
       </c>
       <c r="C2680">
-        <v>5677.4</v>
+        <v>5935.5</v>
       </c>
       <c r="D2680" t="s">
         <v>2682</v>
@@ -46846,7 +46846,7 @@
         <v>88</v>
       </c>
       <c r="C2681">
-        <v>5648.6</v>
+        <v>5927</v>
       </c>
       <c r="D2681" t="s">
         <v>2683</v>
@@ -46860,7 +46860,7 @@
         <v>89</v>
       </c>
       <c r="C2682">
-        <v>5300.8</v>
+        <v>5640.6</v>
       </c>
       <c r="D2682" t="s">
         <v>2684</v>
@@ -46874,7 +46874,7 @@
         <v>90</v>
       </c>
       <c r="C2683">
-        <v>5327.9</v>
+        <v>5636.2</v>
       </c>
       <c r="D2683" t="s">
         <v>2685</v>
@@ -46888,7 +46888,7 @@
         <v>91</v>
       </c>
       <c r="C2684">
-        <v>5282.6</v>
+        <v>5559.6</v>
       </c>
       <c r="D2684" t="s">
         <v>2686</v>
@@ -46902,7 +46902,7 @@
         <v>92</v>
       </c>
       <c r="C2685">
-        <v>5254.1</v>
+        <v>5449.3</v>
       </c>
       <c r="D2685" t="s">
         <v>2687</v>
@@ -46916,7 +46916,7 @@
         <v>93</v>
       </c>
       <c r="C2686">
-        <v>4933.9</v>
+        <v>4980.4</v>
       </c>
       <c r="D2686" t="s">
         <v>2688</v>
@@ -46930,7 +46930,7 @@
         <v>94</v>
       </c>
       <c r="C2687">
-        <v>4845.1</v>
+        <v>4875.6</v>
       </c>
       <c r="D2687" t="s">
         <v>2689</v>
@@ -46944,7 +46944,7 @@
         <v>95</v>
       </c>
       <c r="C2688">
-        <v>4881.3</v>
+        <v>4809.4</v>
       </c>
       <c r="D2688" t="s">
         <v>2690</v>
@@ -46958,7 +46958,7 @@
         <v>96</v>
       </c>
       <c r="C2689">
-        <v>4852.8</v>
+        <v>4743.6</v>
       </c>
       <c r="D2689" t="s">
         <v>2691</v>
@@ -46972,7 +46972,7 @@
         <v>1</v>
       </c>
       <c r="C2690">
-        <v>5233.4</v>
+        <v>4656.1</v>
       </c>
       <c r="D2690" t="s">
         <v>2692</v>
@@ -46986,7 +46986,7 @@
         <v>2</v>
       </c>
       <c r="C2691">
-        <v>5234.3</v>
+        <v>4732</v>
       </c>
       <c r="D2691" t="s">
         <v>2693</v>
@@ -47000,7 +47000,7 @@
         <v>3</v>
       </c>
       <c r="C2692">
-        <v>5190.2</v>
+        <v>4680.7</v>
       </c>
       <c r="D2692" t="s">
         <v>2694</v>
@@ -47014,7 +47014,7 @@
         <v>4</v>
       </c>
       <c r="C2693">
-        <v>5148.1</v>
+        <v>4661.1</v>
       </c>
       <c r="D2693" t="s">
         <v>2695</v>
@@ -47028,7 +47028,7 @@
         <v>5</v>
       </c>
       <c r="C2694">
-        <v>4302.7</v>
+        <v>4389.5</v>
       </c>
       <c r="D2694" t="s">
         <v>2696</v>
@@ -47042,7 +47042,7 @@
         <v>6</v>
       </c>
       <c r="C2695">
-        <v>4275</v>
+        <v>4410</v>
       </c>
       <c r="D2695" t="s">
         <v>2697</v>
@@ -47056,7 +47056,7 @@
         <v>7</v>
       </c>
       <c r="C2696">
-        <v>4236.2</v>
+        <v>4380.4</v>
       </c>
       <c r="D2696" t="s">
         <v>2698</v>
@@ -47070,7 +47070,7 @@
         <v>8</v>
       </c>
       <c r="C2697">
-        <v>4190</v>
+        <v>4325.9</v>
       </c>
       <c r="D2697" t="s">
         <v>2699</v>
@@ -47084,7 +47084,7 @@
         <v>9</v>
       </c>
       <c r="C2698">
-        <v>4126.4</v>
+        <v>4288</v>
       </c>
       <c r="D2698" t="s">
         <v>2700</v>
@@ -47098,7 +47098,7 @@
         <v>10</v>
       </c>
       <c r="C2699">
-        <v>4106.1</v>
+        <v>4265.7</v>
       </c>
       <c r="D2699" t="s">
         <v>2701</v>
@@ -47112,7 +47112,7 @@
         <v>11</v>
       </c>
       <c r="C2700">
-        <v>4073.2</v>
+        <v>4298.3</v>
       </c>
       <c r="D2700" t="s">
         <v>2702</v>
@@ -47126,7 +47126,7 @@
         <v>12</v>
       </c>
       <c r="C2701">
-        <v>4042.1</v>
+        <v>4311.6</v>
       </c>
       <c r="D2701" t="s">
         <v>2703</v>
@@ -47140,7 +47140,7 @@
         <v>13</v>
       </c>
       <c r="C2702">
-        <v>4002.1</v>
+        <v>4382.7</v>
       </c>
       <c r="D2702" t="s">
         <v>2704</v>
@@ -47154,7 +47154,7 @@
         <v>14</v>
       </c>
       <c r="C2703">
-        <v>3984.1</v>
+        <v>4402.3</v>
       </c>
       <c r="D2703" t="s">
         <v>2705</v>
@@ -47168,7 +47168,7 @@
         <v>15</v>
       </c>
       <c r="C2704">
-        <v>3971.7</v>
+        <v>4416.4</v>
       </c>
       <c r="D2704" t="s">
         <v>2706</v>
@@ -47182,7 +47182,7 @@
         <v>16</v>
       </c>
       <c r="C2705">
-        <v>3957.1</v>
+        <v>4446.7</v>
       </c>
       <c r="D2705" t="s">
         <v>2707</v>
@@ -47196,7 +47196,7 @@
         <v>17</v>
       </c>
       <c r="C2706">
-        <v>3807.3</v>
+        <v>4295.4</v>
       </c>
       <c r="D2706" t="s">
         <v>2708</v>
@@ -47210,7 +47210,7 @@
         <v>18</v>
       </c>
       <c r="C2707">
-        <v>3798.5</v>
+        <v>4288.7</v>
       </c>
       <c r="D2707" t="s">
         <v>2709</v>
@@ -47224,7 +47224,7 @@
         <v>19</v>
       </c>
       <c r="C2708">
-        <v>3784.1</v>
+        <v>4280.1</v>
       </c>
       <c r="D2708" t="s">
         <v>2710</v>
@@ -47238,7 +47238,7 @@
         <v>20</v>
       </c>
       <c r="C2709">
-        <v>3797.1</v>
+        <v>4281.6</v>
       </c>
       <c r="D2709" t="s">
         <v>2711</v>
@@ -47252,7 +47252,7 @@
         <v>21</v>
       </c>
       <c r="C2710">
-        <v>3822.8</v>
+        <v>4214.7</v>
       </c>
       <c r="D2710" t="s">
         <v>2712</v>
@@ -47266,7 +47266,7 @@
         <v>22</v>
       </c>
       <c r="C2711">
-        <v>3822.8</v>
+        <v>4227.8</v>
       </c>
       <c r="D2711" t="s">
         <v>2713</v>
@@ -47280,7 +47280,7 @@
         <v>23</v>
       </c>
       <c r="C2712">
-        <v>3833.3</v>
+        <v>4249.1</v>
       </c>
       <c r="D2712" t="s">
         <v>2714</v>
@@ -47294,7 +47294,7 @@
         <v>24</v>
       </c>
       <c r="C2713">
-        <v>3821.6</v>
+        <v>4268.3</v>
       </c>
       <c r="D2713" t="s">
         <v>2715</v>
@@ -47308,7 +47308,7 @@
         <v>25</v>
       </c>
       <c r="C2714">
-        <v>4044.3</v>
+        <v>4569.2</v>
       </c>
       <c r="D2714" t="s">
         <v>2716</v>
@@ -47322,7 +47322,7 @@
         <v>26</v>
       </c>
       <c r="C2715">
-        <v>4058.1</v>
+        <v>4595.1</v>
       </c>
       <c r="D2715" t="s">
         <v>2717</v>
@@ -47336,7 +47336,7 @@
         <v>27</v>
       </c>
       <c r="C2716">
-        <v>4078.6</v>
+        <v>4624.8</v>
       </c>
       <c r="D2716" t="s">
         <v>2718</v>
@@ -47350,7 +47350,7 @@
         <v>28</v>
       </c>
       <c r="C2717">
-        <v>4131</v>
+        <v>4647.5</v>
       </c>
       <c r="D2717" t="s">
         <v>2719</v>
@@ -47364,7 +47364,7 @@
         <v>29</v>
       </c>
       <c r="C2718">
-        <v>4193.4</v>
+        <v>4472.4</v>
       </c>
       <c r="D2718" t="s">
         <v>2720</v>
@@ -47378,7 +47378,7 @@
         <v>30</v>
       </c>
       <c r="C2719">
-        <v>4274.1</v>
+        <v>4522.3</v>
       </c>
       <c r="D2719" t="s">
         <v>2721</v>
@@ -47392,7 +47392,7 @@
         <v>31</v>
       </c>
       <c r="C2720">
-        <v>4382.4</v>
+        <v>4555.1</v>
       </c>
       <c r="D2720" t="s">
         <v>2722</v>
@@ -47406,7 +47406,7 @@
         <v>32</v>
       </c>
       <c r="C2721">
-        <v>4501</v>
+        <v>4616.4</v>
       </c>
       <c r="D2721" t="s">
         <v>2723</v>
@@ -47420,7 +47420,7 @@
         <v>33</v>
       </c>
       <c r="C2722">
-        <v>4101.1</v>
+        <v>4546.9</v>
       </c>
       <c r="D2722" t="s">
         <v>2724</v>
@@ -47434,7 +47434,7 @@
         <v>34</v>
       </c>
       <c r="C2723">
-        <v>4212.7</v>
+        <v>4643.9</v>
       </c>
       <c r="D2723" t="s">
         <v>2725</v>
@@ -47448,7 +47448,7 @@
         <v>35</v>
       </c>
       <c r="C2724">
-        <v>4285.8</v>
+        <v>4725.9</v>
       </c>
       <c r="D2724" t="s">
         <v>2726</v>
@@ -47462,7 +47462,7 @@
         <v>36</v>
       </c>
       <c r="C2725">
-        <v>4429.4</v>
+        <v>4840.7</v>
       </c>
       <c r="D2725" t="s">
         <v>2727</v>
@@ -47476,7 +47476,7 @@
         <v>37</v>
       </c>
       <c r="C2726">
-        <v>4345.2</v>
+        <v>4832.8</v>
       </c>
       <c r="D2726" t="s">
         <v>2728</v>
@@ -47490,7 +47490,7 @@
         <v>38</v>
       </c>
       <c r="C2727">
-        <v>4352.1</v>
+        <v>4868.3</v>
       </c>
       <c r="D2727" t="s">
         <v>2729</v>
@@ -47504,7 +47504,7 @@
         <v>39</v>
       </c>
       <c r="C2728">
-        <v>4428.2</v>
+        <v>4965.6</v>
       </c>
       <c r="D2728" t="s">
         <v>2730</v>
@@ -47518,7 +47518,7 @@
         <v>40</v>
       </c>
       <c r="C2729">
-        <v>4496.3</v>
+        <v>4986.6</v>
       </c>
       <c r="D2729" t="s">
         <v>2731</v>
@@ -47532,7 +47532,7 @@
         <v>41</v>
       </c>
       <c r="C2730">
-        <v>4679.5</v>
+        <v>5120.6</v>
       </c>
       <c r="D2730" t="s">
         <v>2732</v>
@@ -47546,7 +47546,7 @@
         <v>42</v>
       </c>
       <c r="C2731">
-        <v>4739.1</v>
+        <v>5128.9</v>
       </c>
       <c r="D2731" t="s">
         <v>2733</v>
@@ -47560,7 +47560,7 @@
         <v>43</v>
       </c>
       <c r="C2732">
-        <v>4773.8</v>
+        <v>5213.1</v>
       </c>
       <c r="D2732" t="s">
         <v>2734</v>
@@ -47574,7 +47574,7 @@
         <v>44</v>
       </c>
       <c r="C2733">
-        <v>4794.9</v>
+        <v>5258.7</v>
       </c>
       <c r="D2733" t="s">
         <v>2735</v>
@@ -47588,7 +47588,7 @@
         <v>45</v>
       </c>
       <c r="C2734">
-        <v>4343.2</v>
+        <v>4838.1</v>
       </c>
       <c r="D2734" t="s">
         <v>2736</v>
@@ -47602,7 +47602,7 @@
         <v>46</v>
       </c>
       <c r="C2735">
-        <v>4330.9</v>
+        <v>4840.4</v>
       </c>
       <c r="D2735" t="s">
         <v>2737</v>
@@ -47616,7 +47616,7 @@
         <v>47</v>
       </c>
       <c r="C2736">
-        <v>4359.4</v>
+        <v>4930.1</v>
       </c>
       <c r="D2736" t="s">
         <v>2738</v>
@@ -47630,7 +47630,7 @@
         <v>48</v>
       </c>
       <c r="C2737">
-        <v>4394</v>
+        <v>4946.6</v>
       </c>
       <c r="D2737" t="s">
         <v>2739</v>
@@ -47644,7 +47644,7 @@
         <v>49</v>
       </c>
       <c r="C2738">
-        <v>4428.4</v>
+        <v>4802.3</v>
       </c>
       <c r="D2738" t="s">
         <v>2740</v>
@@ -47658,7 +47658,7 @@
         <v>50</v>
       </c>
       <c r="C2739">
-        <v>4434.8</v>
+        <v>4765</v>
       </c>
       <c r="D2739" t="s">
         <v>2741</v>
@@ -47672,7 +47672,7 @@
         <v>51</v>
       </c>
       <c r="C2740">
-        <v>4505.1</v>
+        <v>4624.7</v>
       </c>
       <c r="D2740" t="s">
         <v>2742</v>
@@ -47686,7 +47686,7 @@
         <v>52</v>
       </c>
       <c r="C2741">
-        <v>4532.4</v>
+        <v>4509.5</v>
       </c>
       <c r="D2741" t="s">
         <v>2743</v>
@@ -47700,7 +47700,7 @@
         <v>53</v>
       </c>
       <c r="C2742">
-        <v>4391.1</v>
+        <v>4612</v>
       </c>
       <c r="D2742" t="s">
         <v>2744</v>
@@ -47714,7 +47714,7 @@
         <v>54</v>
       </c>
       <c r="C2743">
-        <v>4397.8</v>
+        <v>4551.6</v>
       </c>
       <c r="D2743" t="s">
         <v>2745</v>
@@ -47728,7 +47728,7 @@
         <v>55</v>
       </c>
       <c r="C2744">
-        <v>4477</v>
+        <v>4589.4</v>
       </c>
       <c r="D2744" t="s">
         <v>2746</v>
@@ -47742,7 +47742,7 @@
         <v>56</v>
       </c>
       <c r="C2745">
-        <v>4482.4</v>
+        <v>4594.7</v>
       </c>
       <c r="D2745" t="s">
         <v>2747</v>
@@ -47756,7 +47756,7 @@
         <v>57</v>
       </c>
       <c r="C2746">
-        <v>4478.1</v>
+        <v>4665.9</v>
       </c>
       <c r="D2746" t="s">
         <v>2748</v>
@@ -47770,7 +47770,7 @@
         <v>58</v>
       </c>
       <c r="C2747">
-        <v>4500.5</v>
+        <v>4688.9</v>
       </c>
       <c r="D2747" t="s">
         <v>2749</v>
@@ -47784,7 +47784,7 @@
         <v>59</v>
       </c>
       <c r="C2748">
-        <v>4542.6</v>
+        <v>4652</v>
       </c>
       <c r="D2748" t="s">
         <v>2750</v>
@@ -47798,7 +47798,7 @@
         <v>60</v>
       </c>
       <c r="C2749">
-        <v>4562.9</v>
+        <v>4679.1</v>
       </c>
       <c r="D2749" t="s">
         <v>2751</v>
@@ -47812,7 +47812,7 @@
         <v>61</v>
       </c>
       <c r="C2750">
-        <v>4498.7</v>
+        <v>4586.7</v>
       </c>
       <c r="D2750" t="s">
         <v>2752</v>
@@ -47826,7 +47826,7 @@
         <v>62</v>
       </c>
       <c r="C2751">
-        <v>4550.1</v>
+        <v>4635.5</v>
       </c>
       <c r="D2751" t="s">
         <v>2753</v>
@@ -47840,7 +47840,7 @@
         <v>63</v>
       </c>
       <c r="C2752">
-        <v>4564.4</v>
+        <v>4632.9</v>
       </c>
       <c r="D2752" t="s">
         <v>2754</v>
@@ -47854,7 +47854,7 @@
         <v>64</v>
       </c>
       <c r="C2753">
-        <v>4551.7</v>
+        <v>4643.5</v>
       </c>
       <c r="D2753" t="s">
         <v>2755</v>
@@ -47868,7 +47868,7 @@
         <v>65</v>
       </c>
       <c r="C2754">
-        <v>4284.8</v>
+        <v>4661.5</v>
       </c>
       <c r="D2754" t="s">
         <v>2756</v>
@@ -47882,7 +47882,7 @@
         <v>66</v>
       </c>
       <c r="C2755">
-        <v>4266.3</v>
+        <v>4660.4</v>
       </c>
       <c r="D2755" t="s">
         <v>2757</v>
@@ -47896,7 +47896,7 @@
         <v>67</v>
       </c>
       <c r="C2756">
-        <v>4186.2</v>
+        <v>4765</v>
       </c>
       <c r="D2756" t="s">
         <v>2758</v>
@@ -47910,7 +47910,7 @@
         <v>68</v>
       </c>
       <c r="C2757">
-        <v>4178.8</v>
+        <v>4703.5</v>
       </c>
       <c r="D2757" t="s">
         <v>2759</v>
@@ -47924,7 +47924,7 @@
         <v>69</v>
       </c>
       <c r="C2758">
-        <v>4620.4</v>
+        <v>5109.9</v>
       </c>
       <c r="D2758" t="s">
         <v>2760</v>
@@ -47938,7 +47938,7 @@
         <v>70</v>
       </c>
       <c r="C2759">
-        <v>4537.8</v>
+        <v>5030.3</v>
       </c>
       <c r="D2759" t="s">
         <v>2761</v>
@@ -47952,7 +47952,7 @@
         <v>71</v>
       </c>
       <c r="C2760">
-        <v>4468.2</v>
+        <v>4951.1</v>
       </c>
       <c r="D2760" t="s">
         <v>2762</v>
@@ -47966,7 +47966,7 @@
         <v>72</v>
       </c>
       <c r="C2761">
-        <v>4351.6</v>
+        <v>4868.2</v>
       </c>
       <c r="D2761" t="s">
         <v>2763</v>
@@ -47980,7 +47980,7 @@
         <v>73</v>
       </c>
       <c r="C2762">
-        <v>5156</v>
+        <v>5398.1</v>
       </c>
       <c r="D2762" t="s">
         <v>2764</v>
@@ -47994,7 +47994,7 @@
         <v>74</v>
       </c>
       <c r="C2763">
-        <v>5016</v>
+        <v>5343.3</v>
       </c>
       <c r="D2763" t="s">
         <v>2765</v>
@@ -48008,7 +48008,7 @@
         <v>75</v>
       </c>
       <c r="C2764">
-        <v>4916.3</v>
+        <v>5268.6</v>
       </c>
       <c r="D2764" t="s">
         <v>2766</v>
@@ -48022,7 +48022,7 @@
         <v>76</v>
       </c>
       <c r="C2765">
-        <v>4953.5</v>
+        <v>5261.9</v>
       </c>
       <c r="D2765" t="s">
         <v>2767</v>
@@ -48036,7 +48036,7 @@
         <v>77</v>
       </c>
       <c r="C2766">
-        <v>5060.4</v>
+        <v>5229.5</v>
       </c>
       <c r="D2766" t="s">
         <v>2768</v>
@@ -48050,7 +48050,7 @@
         <v>78</v>
       </c>
       <c r="C2767">
-        <v>5019.7</v>
+        <v>5235.7</v>
       </c>
       <c r="D2767" t="s">
         <v>2769</v>
@@ -48064,7 +48064,7 @@
         <v>79</v>
       </c>
       <c r="C2768">
-        <v>4985.3</v>
+        <v>5179</v>
       </c>
       <c r="D2768" t="s">
         <v>2770</v>
@@ -48078,7 +48078,7 @@
         <v>80</v>
       </c>
       <c r="C2769">
-        <v>4957.4</v>
+        <v>5117.4</v>
       </c>
       <c r="D2769" t="s">
         <v>2771</v>
@@ -48092,7 +48092,7 @@
         <v>81</v>
       </c>
       <c r="C2770">
-        <v>5371.6</v>
+        <v>5375</v>
       </c>
       <c r="D2770" t="s">
         <v>2772</v>
@@ -48106,7 +48106,7 @@
         <v>82</v>
       </c>
       <c r="C2771">
-        <v>5301.4</v>
+        <v>5359.7</v>
       </c>
       <c r="D2771" t="s">
         <v>2773</v>
@@ -48120,7 +48120,7 @@
         <v>83</v>
       </c>
       <c r="C2772">
-        <v>5409.7</v>
+        <v>5372</v>
       </c>
       <c r="D2772" t="s">
         <v>2774</v>
@@ -48134,7 +48134,7 @@
         <v>84</v>
       </c>
       <c r="C2773">
-        <v>5467.1</v>
+        <v>5462.1</v>
       </c>
       <c r="D2773" t="s">
         <v>2775</v>
@@ -48148,7 +48148,7 @@
         <v>85</v>
       </c>
       <c r="C2774">
-        <v>5495.6</v>
+        <v>5890.9</v>
       </c>
       <c r="D2774" t="s">
         <v>2776</v>
@@ -48162,7 +48162,7 @@
         <v>86</v>
       </c>
       <c r="C2775">
-        <v>5479.4</v>
+        <v>5859.9</v>
       </c>
       <c r="D2775" t="s">
         <v>2777</v>
@@ -48176,7 +48176,7 @@
         <v>87</v>
       </c>
       <c r="C2776">
-        <v>5517.4</v>
+        <v>5835.5</v>
       </c>
       <c r="D2776" t="s">
         <v>2778</v>
@@ -48190,7 +48190,7 @@
         <v>88</v>
       </c>
       <c r="C2777">
-        <v>5498.6</v>
+        <v>5797</v>
       </c>
       <c r="D2777" t="s">
         <v>2779</v>
@@ -48204,7 +48204,7 @@
         <v>89</v>
       </c>
       <c r="C2778">
-        <v>5180.8</v>
+        <v>5480.6</v>
       </c>
       <c r="D2778" t="s">
         <v>2780</v>
@@ -48218,7 +48218,7 @@
         <v>90</v>
       </c>
       <c r="C2779">
-        <v>5177.9</v>
+        <v>5496.2</v>
       </c>
       <c r="D2779" t="s">
         <v>2781</v>
@@ -48232,7 +48232,7 @@
         <v>91</v>
       </c>
       <c r="C2780">
-        <v>5142.6</v>
+        <v>5439.6</v>
       </c>
       <c r="D2780" t="s">
         <v>2782</v>
@@ -48246,7 +48246,7 @@
         <v>92</v>
       </c>
       <c r="C2781">
-        <v>5104.1</v>
+        <v>5349.3</v>
       </c>
       <c r="D2781" t="s">
         <v>2783</v>
@@ -48260,7 +48260,7 @@
         <v>93</v>
       </c>
       <c r="C2782">
-        <v>4853.9</v>
+        <v>4800.4</v>
       </c>
       <c r="D2782" t="s">
         <v>2784</v>
@@ -48274,7 +48274,7 @@
         <v>94</v>
       </c>
       <c r="C2783">
-        <v>4775.1</v>
+        <v>4705.6</v>
       </c>
       <c r="D2783" t="s">
         <v>2785</v>
@@ -48288,7 +48288,7 @@
         <v>95</v>
       </c>
       <c r="C2784">
-        <v>4781.3</v>
+        <v>4689.4</v>
       </c>
       <c r="D2784" t="s">
         <v>2786</v>
@@ -48302,7 +48302,7 @@
         <v>96</v>
       </c>
       <c r="C2785">
-        <v>4752.8</v>
+        <v>4673.6</v>
       </c>
       <c r="D2785" t="s">
         <v>2787</v>
@@ -48316,7 +48316,7 @@
         <v>1</v>
       </c>
       <c r="C2786">
-        <v>4735</v>
+        <v>4616.1</v>
       </c>
       <c r="D2786" t="s">
         <v>2788</v>
@@ -48330,7 +48330,7 @@
         <v>2</v>
       </c>
       <c r="C2787">
-        <v>4695</v>
+        <v>4642</v>
       </c>
       <c r="D2787" t="s">
         <v>2789</v>
@@ -48344,7 +48344,7 @@
         <v>3</v>
       </c>
       <c r="C2788">
-        <v>4635</v>
+        <v>4580.7</v>
       </c>
       <c r="D2788" t="s">
         <v>2790</v>
@@ -48358,7 +48358,7 @@
         <v>4</v>
       </c>
       <c r="C2789">
-        <v>4565</v>
+        <v>4541.1</v>
       </c>
       <c r="D2789" t="s">
         <v>2791</v>
@@ -48372,7 +48372,7 @@
         <v>5</v>
       </c>
       <c r="C2790">
-        <v>4277</v>
+        <v>4259.5</v>
       </c>
       <c r="D2790" t="s">
         <v>2792</v>
@@ -48386,7 +48386,7 @@
         <v>6</v>
       </c>
       <c r="C2791">
-        <v>4255.4</v>
+        <v>4270</v>
       </c>
       <c r="D2791" t="s">
         <v>2793</v>
@@ -48400,7 +48400,7 @@
         <v>7</v>
       </c>
       <c r="C2792">
-        <v>4230</v>
+        <v>4240.4</v>
       </c>
       <c r="D2792" t="s">
         <v>2794</v>
@@ -48414,7 +48414,7 @@
         <v>8</v>
       </c>
       <c r="C2793">
-        <v>4218.7</v>
+        <v>4195.9</v>
       </c>
       <c r="D2793" t="s">
         <v>2795</v>
@@ -48428,7 +48428,7 @@
         <v>9</v>
       </c>
       <c r="C2794">
-        <v>4046.5</v>
+        <v>4168</v>
       </c>
       <c r="D2794" t="s">
         <v>2796</v>
@@ -48442,7 +48442,7 @@
         <v>10</v>
       </c>
       <c r="C2795">
-        <v>4028.3</v>
+        <v>4155.7</v>
       </c>
       <c r="D2795" t="s">
         <v>2797</v>
@@ -48456,7 +48456,7 @@
         <v>11</v>
       </c>
       <c r="C2796">
-        <v>4024.6</v>
+        <v>4188.3</v>
       </c>
       <c r="D2796" t="s">
         <v>2798</v>
@@ -48470,7 +48470,7 @@
         <v>12</v>
       </c>
       <c r="C2797">
-        <v>4011.8</v>
+        <v>4201.6</v>
       </c>
       <c r="D2797" t="s">
         <v>2799</v>
@@ -48484,7 +48484,7 @@
         <v>13</v>
       </c>
       <c r="C2798">
-        <v>4008.6</v>
+        <v>4252.7</v>
       </c>
       <c r="D2798" t="s">
         <v>2800</v>
@@ -48498,7 +48498,7 @@
         <v>14</v>
       </c>
       <c r="C2799">
-        <v>4004.2</v>
+        <v>4262.3</v>
       </c>
       <c r="D2799" t="s">
         <v>2801</v>
@@ -48512,7 +48512,7 @@
         <v>15</v>
       </c>
       <c r="C2800">
-        <v>3969.6</v>
+        <v>4266.4</v>
       </c>
       <c r="D2800" t="s">
         <v>2802</v>
@@ -48526,7 +48526,7 @@
         <v>16</v>
       </c>
       <c r="C2801">
-        <v>3955.6</v>
+        <v>4286.7</v>
       </c>
       <c r="D2801" t="s">
         <v>2803</v>
@@ -48540,7 +48540,7 @@
         <v>17</v>
       </c>
       <c r="C2802">
-        <v>3889.6</v>
+        <v>4135.4</v>
       </c>
       <c r="D2802" t="s">
         <v>2804</v>
@@ -48554,7 +48554,7 @@
         <v>18</v>
       </c>
       <c r="C2803">
-        <v>3856.8</v>
+        <v>4118.7</v>
       </c>
       <c r="D2803" t="s">
         <v>2805</v>
@@ -48568,7 +48568,7 @@
         <v>19</v>
       </c>
       <c r="C2804">
-        <v>3853.7</v>
+        <v>4090.1</v>
       </c>
       <c r="D2804" t="s">
         <v>2806</v>
@@ -48582,7 +48582,7 @@
         <v>20</v>
       </c>
       <c r="C2805">
-        <v>3830.4</v>
+        <v>4071.6</v>
       </c>
       <c r="D2805" t="s">
         <v>2807</v>
@@ -48596,7 +48596,7 @@
         <v>21</v>
       </c>
       <c r="C2806">
-        <v>3896.1</v>
+        <v>3974.7</v>
       </c>
       <c r="D2806" t="s">
         <v>2808</v>
@@ -48610,7 +48610,7 @@
         <v>22</v>
       </c>
       <c r="C2807">
-        <v>3821.2</v>
+        <v>3947.8</v>
       </c>
       <c r="D2807" t="s">
         <v>2809</v>
@@ -48624,7 +48624,7 @@
         <v>23</v>
       </c>
       <c r="C2808">
-        <v>3789.8</v>
+        <v>3909.1</v>
       </c>
       <c r="D2808" t="s">
         <v>2810</v>
@@ -48638,7 +48638,7 @@
         <v>24</v>
       </c>
       <c r="C2809">
-        <v>3737.3</v>
+        <v>3858.3</v>
       </c>
       <c r="D2809" t="s">
         <v>2811</v>
@@ -48652,7 +48652,7 @@
         <v>25</v>
       </c>
       <c r="C2810">
-        <v>3853.3</v>
+        <v>4079.2</v>
       </c>
       <c r="D2810" t="s">
         <v>2812</v>
@@ -48666,7 +48666,7 @@
         <v>26</v>
       </c>
       <c r="C2811">
-        <v>3809.5</v>
+        <v>4035.1</v>
       </c>
       <c r="D2811" t="s">
         <v>2813</v>
@@ -48680,7 +48680,7 @@
         <v>27</v>
       </c>
       <c r="C2812">
-        <v>3757.6</v>
+        <v>3984.8</v>
       </c>
       <c r="D2812" t="s">
         <v>2814</v>
@@ -48694,7 +48694,7 @@
         <v>28</v>
       </c>
       <c r="C2813">
-        <v>3758.3</v>
+        <v>3927.5</v>
       </c>
       <c r="D2813" t="s">
         <v>2815</v>
@@ -48708,7 +48708,7 @@
         <v>29</v>
       </c>
       <c r="C2814">
-        <v>3629.8</v>
+        <v>3682.4</v>
       </c>
       <c r="D2814" t="s">
         <v>2816</v>
@@ -48722,7 +48722,7 @@
         <v>30</v>
       </c>
       <c r="C2815">
-        <v>3600.7</v>
+        <v>3652.3</v>
       </c>
       <c r="D2815" t="s">
         <v>2817</v>
@@ -48736,7 +48736,7 @@
         <v>31</v>
       </c>
       <c r="C2816">
-        <v>3659.7</v>
+        <v>3665.1</v>
       </c>
       <c r="D2816" t="s">
         <v>2818</v>
@@ -48750,7 +48750,7 @@
         <v>32</v>
       </c>
       <c r="C2817">
-        <v>3750.8</v>
+        <v>3736.4</v>
       </c>
       <c r="D2817" t="s">
         <v>2819</v>
@@ -48764,7 +48764,7 @@
         <v>33</v>
       </c>
       <c r="C2818">
-        <v>3658.4</v>
+        <v>3716.9</v>
       </c>
       <c r="D2818" t="s">
         <v>2820</v>
@@ -48778,7 +48778,7 @@
         <v>34</v>
       </c>
       <c r="C2819">
-        <v>3747</v>
+        <v>3833.9</v>
       </c>
       <c r="D2819" t="s">
         <v>2821</v>
@@ -48792,7 +48792,7 @@
         <v>35</v>
       </c>
       <c r="C2820">
-        <v>3840.5</v>
+        <v>3935.9</v>
       </c>
       <c r="D2820" t="s">
         <v>2822</v>
@@ -48806,7 +48806,7 @@
         <v>36</v>
       </c>
       <c r="C2821">
-        <v>3937.7</v>
+        <v>4050.7</v>
       </c>
       <c r="D2821" t="s">
         <v>2823</v>
@@ -48820,7 +48820,7 @@
         <v>37</v>
       </c>
       <c r="C2822">
-        <v>4169.1</v>
+        <v>4042.8</v>
       </c>
       <c r="D2822" t="s">
         <v>2824</v>
@@ -48834,7 +48834,7 @@
         <v>38</v>
       </c>
       <c r="C2823">
-        <v>4225.3</v>
+        <v>4098.3</v>
       </c>
       <c r="D2823" t="s">
         <v>2825</v>
@@ -48848,7 +48848,7 @@
         <v>39</v>
       </c>
       <c r="C2824">
-        <v>4310.2</v>
+        <v>4235.6</v>
       </c>
       <c r="D2824" t="s">
         <v>2826</v>
@@ -48862,7 +48862,7 @@
         <v>40</v>
       </c>
       <c r="C2825">
-        <v>4388.3</v>
+        <v>4336.6</v>
       </c>
       <c r="D2825" t="s">
         <v>2827</v>
@@ -48876,7 +48876,7 @@
         <v>41</v>
       </c>
       <c r="C2826">
-        <v>4441.6</v>
+        <v>4540.6</v>
       </c>
       <c r="D2826" t="s">
         <v>2828</v>
@@ -48890,7 +48890,7 @@
         <v>42</v>
       </c>
       <c r="C2827">
-        <v>4454.6</v>
+        <v>4608.9</v>
       </c>
       <c r="D2827" t="s">
         <v>2829</v>
@@ -48904,7 +48904,7 @@
         <v>43</v>
       </c>
       <c r="C2828">
-        <v>4491.6</v>
+        <v>4713.1</v>
       </c>
       <c r="D2828" t="s">
         <v>2830</v>
@@ -48918,7 +48918,7 @@
         <v>44</v>
       </c>
       <c r="C2829">
-        <v>4528</v>
+        <v>4758.7</v>
       </c>
       <c r="D2829" t="s">
         <v>2831</v>
@@ -48932,7 +48932,7 @@
         <v>45</v>
       </c>
       <c r="C2830">
-        <v>4508.7</v>
+        <v>4308.1</v>
       </c>
       <c r="D2830" t="s">
         <v>2832</v>
@@ -48946,7 +48946,7 @@
         <v>46</v>
       </c>
       <c r="C2831">
-        <v>4515.5</v>
+        <v>4300.4</v>
       </c>
       <c r="D2831" t="s">
         <v>2833</v>
@@ -48960,7 +48960,7 @@
         <v>47</v>
       </c>
       <c r="C2832">
-        <v>4502.7</v>
+        <v>4380.1</v>
       </c>
       <c r="D2832" t="s">
         <v>2834</v>
@@ -48974,7 +48974,7 @@
         <v>48</v>
       </c>
       <c r="C2833">
-        <v>4514.2</v>
+        <v>4426.6</v>
       </c>
       <c r="D2833" t="s">
         <v>2835</v>
@@ -48988,7 +48988,7 @@
         <v>49</v>
       </c>
       <c r="C2834">
-        <v>4306.8</v>
+        <v>4322.3</v>
       </c>
       <c r="D2834" t="s">
         <v>2836</v>
@@ -49002,7 +49002,7 @@
         <v>50</v>
       </c>
       <c r="C2835">
-        <v>4290.2</v>
+        <v>4315</v>
       </c>
       <c r="D2835" t="s">
         <v>2837</v>
@@ -49016,7 +49016,7 @@
         <v>51</v>
       </c>
       <c r="C2836">
-        <v>4246.2</v>
+        <v>4194.7</v>
       </c>
       <c r="D2836" t="s">
         <v>2838</v>
@@ -49030,7 +49030,7 @@
         <v>52</v>
       </c>
       <c r="C2837">
-        <v>4227.7</v>
+        <v>4089.5</v>
       </c>
       <c r="D2837" t="s">
         <v>2839</v>
@@ -49044,7 +49044,7 @@
         <v>53</v>
       </c>
       <c r="C2838">
-        <v>4205.7</v>
+        <v>4172</v>
       </c>
       <c r="D2838" t="s">
         <v>2840</v>
@@ -49058,7 +49058,7 @@
         <v>54</v>
       </c>
       <c r="C2839">
-        <v>4179.5</v>
+        <v>4091.6</v>
       </c>
       <c r="D2839" t="s">
         <v>2841</v>
@@ -49072,7 +49072,7 @@
         <v>55</v>
       </c>
       <c r="C2840">
-        <v>4177.9</v>
+        <v>4109.4</v>
       </c>
       <c r="D2840" t="s">
         <v>2842</v>
@@ -49086,7 +49086,7 @@
         <v>56</v>
       </c>
       <c r="C2841">
-        <v>4190.4</v>
+        <v>4084.7</v>
       </c>
       <c r="D2841" t="s">
         <v>2843</v>
@@ -49100,7 +49100,7 @@
         <v>57</v>
       </c>
       <c r="C2842">
-        <v>4203.2</v>
+        <v>4125.9</v>
       </c>
       <c r="D2842" t="s">
         <v>2844</v>
@@ -49114,7 +49114,7 @@
         <v>58</v>
       </c>
       <c r="C2843">
-        <v>4209.6</v>
+        <v>4148.9</v>
       </c>
       <c r="D2843" t="s">
         <v>2845</v>
@@ -49128,7 +49128,7 @@
         <v>59</v>
       </c>
       <c r="C2844">
-        <v>4236</v>
+        <v>4142</v>
       </c>
       <c r="D2844" t="s">
         <v>2846</v>
@@ -49142,7 +49142,7 @@
         <v>60</v>
       </c>
       <c r="C2845">
-        <v>4240.7</v>
+        <v>4229.1</v>
       </c>
       <c r="D2845" t="s">
         <v>2847</v>
@@ -49156,7 +49156,7 @@
         <v>61</v>
       </c>
       <c r="C2846">
-        <v>4209.6</v>
+        <v>4216.7</v>
       </c>
       <c r="D2846" t="s">
         <v>2848</v>
@@ -49170,7 +49170,7 @@
         <v>62</v>
       </c>
       <c r="C2847">
-        <v>4172.4</v>
+        <v>4345.5</v>
       </c>
       <c r="D2847" t="s">
         <v>2849</v>
@@ -49184,7 +49184,7 @@
         <v>63</v>
       </c>
       <c r="C2848">
-        <v>4158</v>
+        <v>4402.9</v>
       </c>
       <c r="D2848" t="s">
         <v>2850</v>
@@ -49198,7 +49198,7 @@
         <v>64</v>
       </c>
       <c r="C2849">
-        <v>4126.6</v>
+        <v>4443.5</v>
       </c>
       <c r="D2849" t="s">
         <v>2851</v>
@@ -49212,7 +49212,7 @@
         <v>65</v>
       </c>
       <c r="C2850">
-        <v>4213.9</v>
+        <v>4471.5</v>
       </c>
       <c r="D2850" t="s">
         <v>2852</v>
@@ -49226,7 +49226,7 @@
         <v>66</v>
       </c>
       <c r="C2851">
-        <v>4159.2</v>
+        <v>4460.4</v>
       </c>
       <c r="D2851" t="s">
         <v>2853</v>
@@ -49240,7 +49240,7 @@
         <v>67</v>
       </c>
       <c r="C2852">
-        <v>4118.7</v>
+        <v>4555</v>
       </c>
       <c r="D2852" t="s">
         <v>2854</v>
@@ -49254,7 +49254,7 @@
         <v>68</v>
       </c>
       <c r="C2853">
-        <v>4110.8</v>
+        <v>4483.5</v>
       </c>
       <c r="D2853" t="s">
         <v>2855</v>
@@ -49268,7 +49268,7 @@
         <v>69</v>
       </c>
       <c r="C2854">
-        <v>4054.8</v>
+        <v>4879.9</v>
       </c>
       <c r="D2854" t="s">
         <v>2856</v>
@@ -49282,7 +49282,7 @@
         <v>70</v>
       </c>
       <c r="C2855">
-        <v>4007</v>
+        <v>4800.3</v>
       </c>
       <c r="D2855" t="s">
         <v>2857</v>
@@ -49296,7 +49296,7 @@
         <v>71</v>
       </c>
       <c r="C2856">
-        <v>3890.8</v>
+        <v>4741.1</v>
       </c>
       <c r="D2856" t="s">
         <v>2858</v>
@@ -49310,7 +49310,7 @@
         <v>72</v>
       </c>
       <c r="C2857">
-        <v>3892.2</v>
+        <v>4708.2</v>
       </c>
       <c r="D2857" t="s">
         <v>2859</v>
@@ -49324,7 +49324,7 @@
         <v>73</v>
       </c>
       <c r="C2858">
-        <v>4043.8</v>
+        <v>5278.1</v>
       </c>
       <c r="D2858" t="s">
         <v>2860</v>
@@ -49338,7 +49338,7 @@
         <v>74</v>
       </c>
       <c r="C2859">
-        <v>3960.4</v>
+        <v>5233.3</v>
       </c>
       <c r="D2859" t="s">
         <v>2861</v>
@@ -49352,7 +49352,7 @@
         <v>75</v>
       </c>
       <c r="C2860">
-        <v>3899.7</v>
+        <v>5138.6</v>
       </c>
       <c r="D2860" t="s">
         <v>2862</v>
@@ -49366,7 +49366,7 @@
         <v>76</v>
       </c>
       <c r="C2861">
-        <v>3831.8</v>
+        <v>5071.9</v>
       </c>
       <c r="D2861" t="s">
         <v>2863</v>
@@ -49380,7 +49380,7 @@
         <v>77</v>
       </c>
       <c r="C2862">
-        <v>4073.1</v>
+        <v>4969.5</v>
       </c>
       <c r="D2862" t="s">
         <v>2864</v>
@@ -49394,7 +49394,7 @@
         <v>78</v>
       </c>
       <c r="C2863">
-        <v>4044.6</v>
+        <v>4885.7</v>
       </c>
       <c r="D2863" t="s">
         <v>2865</v>
@@ -49408,7 +49408,7 @@
         <v>79</v>
       </c>
       <c r="C2864">
-        <v>3972.6</v>
+        <v>4759</v>
       </c>
       <c r="D2864" t="s">
         <v>2866</v>
@@ -49422,7 +49422,7 @@
         <v>80</v>
       </c>
       <c r="C2865">
-        <v>3964.5</v>
+        <v>4647.4</v>
       </c>
       <c r="D2865" t="s">
         <v>2867</v>
@@ -49436,7 +49436,7 @@
         <v>81</v>
       </c>
       <c r="C2866">
-        <v>4278.8</v>
+        <v>4865</v>
       </c>
       <c r="D2866" t="s">
         <v>2868</v>
@@ -49450,7 +49450,7 @@
         <v>82</v>
       </c>
       <c r="C2867">
-        <v>4294.2</v>
+        <v>4809.7</v>
       </c>
       <c r="D2867" t="s">
         <v>2869</v>
@@ -49464,7 +49464,7 @@
         <v>83</v>
       </c>
       <c r="C2868">
-        <v>4405.7</v>
+        <v>4822</v>
       </c>
       <c r="D2868" t="s">
         <v>2870</v>
@@ -49478,7 +49478,7 @@
         <v>84</v>
       </c>
       <c r="C2869">
-        <v>4402.2</v>
+        <v>4902.1</v>
       </c>
       <c r="D2869" t="s">
         <v>2871</v>
@@ -49492,7 +49492,7 @@
         <v>85</v>
       </c>
       <c r="C2870">
-        <v>4575.1</v>
+        <v>5380.9</v>
       </c>
       <c r="D2870" t="s">
         <v>2872</v>
@@ -49506,7 +49506,7 @@
         <v>86</v>
       </c>
       <c r="C2871">
-        <v>4581</v>
+        <v>5399.9</v>
       </c>
       <c r="D2871" t="s">
         <v>2873</v>
@@ -49520,7 +49520,7 @@
         <v>87</v>
       </c>
       <c r="C2872">
-        <v>4570.1</v>
+        <v>5365.5</v>
       </c>
       <c r="D2872" t="s">
         <v>2874</v>
@@ -49534,7 +49534,7 @@
         <v>88</v>
       </c>
       <c r="C2873">
-        <v>4565.8</v>
+        <v>5327</v>
       </c>
       <c r="D2873" t="s">
         <v>2875</v>
@@ -49548,7 +49548,7 @@
         <v>89</v>
       </c>
       <c r="C2874">
-        <v>4425</v>
+        <v>5020.6</v>
       </c>
       <c r="D2874" t="s">
         <v>2876</v>
@@ -49562,7 +49562,7 @@
         <v>90</v>
       </c>
       <c r="C2875">
-        <v>4520.7</v>
+        <v>4996.2</v>
       </c>
       <c r="D2875" t="s">
         <v>2877</v>
@@ -49576,7 +49576,7 @@
         <v>91</v>
       </c>
       <c r="C2876">
-        <v>4519.6</v>
+        <v>4949.6</v>
       </c>
       <c r="D2876" t="s">
         <v>2878</v>
@@ -49590,7 +49590,7 @@
         <v>92</v>
       </c>
       <c r="C2877">
-        <v>4527.1</v>
+        <v>4909.3</v>
       </c>
       <c r="D2877" t="s">
         <v>2879</v>
@@ -49604,7 +49604,7 @@
         <v>93</v>
       </c>
       <c r="C2878">
-        <v>4068.2</v>
+        <v>4470.4</v>
       </c>
       <c r="D2878" t="s">
         <v>2880</v>
@@ -49618,7 +49618,7 @@
         <v>94</v>
       </c>
       <c r="C2879">
-        <v>4121.6</v>
+        <v>4395.6</v>
       </c>
       <c r="D2879" t="s">
         <v>2881</v>
@@ -49632,7 +49632,7 @@
         <v>95</v>
       </c>
       <c r="C2880">
-        <v>4146.9</v>
+        <v>4339.4</v>
       </c>
       <c r="D2880" t="s">
         <v>2882</v>
@@ -49646,7 +49646,7 @@
         <v>96</v>
       </c>
       <c r="C2881">
-        <v>4155.7</v>
+        <v>4283.6</v>
       </c>
       <c r="D2881" t="s">
         <v>2883</v>

--- a/Market Fundamentals/Transelectrica_data/Cons_Prod_final/Weekly_Production_2026.xlsx
+++ b/Market Fundamentals/Transelectrica_data/Cons_Prod_final/Weekly_Production_2026.xlsx
@@ -46972,7 +46972,7 @@
         <v>1</v>
       </c>
       <c r="C2690">
-        <v>4656.1</v>
+        <v>4550.9</v>
       </c>
       <c r="D2690" t="s">
         <v>2692</v>
@@ -46986,7 +46986,7 @@
         <v>2</v>
       </c>
       <c r="C2691">
-        <v>4732</v>
+        <v>4580.8</v>
       </c>
       <c r="D2691" t="s">
         <v>2693</v>
@@ -47000,7 +47000,7 @@
         <v>3</v>
       </c>
       <c r="C2692">
-        <v>4680.7</v>
+        <v>4578.9</v>
       </c>
       <c r="D2692" t="s">
         <v>2694</v>
@@ -47014,7 +47014,7 @@
         <v>4</v>
       </c>
       <c r="C2693">
-        <v>4661.1</v>
+        <v>4578.4</v>
       </c>
       <c r="D2693" t="s">
         <v>2695</v>
@@ -47028,7 +47028,7 @@
         <v>5</v>
       </c>
       <c r="C2694">
-        <v>4389.5</v>
+        <v>4319.4</v>
       </c>
       <c r="D2694" t="s">
         <v>2696</v>
@@ -47042,7 +47042,7 @@
         <v>6</v>
       </c>
       <c r="C2695">
-        <v>4410</v>
+        <v>4301.9</v>
       </c>
       <c r="D2695" t="s">
         <v>2697</v>
@@ -47056,7 +47056,7 @@
         <v>7</v>
       </c>
       <c r="C2696">
-        <v>4380.4</v>
+        <v>4297.5</v>
       </c>
       <c r="D2696" t="s">
         <v>2698</v>
@@ -47070,7 +47070,7 @@
         <v>8</v>
       </c>
       <c r="C2697">
-        <v>4325.9</v>
+        <v>4236</v>
       </c>
       <c r="D2697" t="s">
         <v>2699</v>
@@ -47084,7 +47084,7 @@
         <v>9</v>
       </c>
       <c r="C2698">
-        <v>4288</v>
+        <v>4264.3</v>
       </c>
       <c r="D2698" t="s">
         <v>2700</v>
@@ -47098,7 +47098,7 @@
         <v>10</v>
       </c>
       <c r="C2699">
-        <v>4265.7</v>
+        <v>4289.9</v>
       </c>
       <c r="D2699" t="s">
         <v>2701</v>
@@ -47112,7 +47112,7 @@
         <v>11</v>
       </c>
       <c r="C2700">
-        <v>4298.3</v>
+        <v>4311.2</v>
       </c>
       <c r="D2700" t="s">
         <v>2702</v>
@@ -47126,7 +47126,7 @@
         <v>12</v>
       </c>
       <c r="C2701">
-        <v>4311.6</v>
+        <v>4334.3</v>
       </c>
       <c r="D2701" t="s">
         <v>2703</v>
@@ -47140,7 +47140,7 @@
         <v>13</v>
       </c>
       <c r="C2702">
-        <v>4382.7</v>
+        <v>4187.4</v>
       </c>
       <c r="D2702" t="s">
         <v>2704</v>
@@ -47154,7 +47154,7 @@
         <v>14</v>
       </c>
       <c r="C2703">
-        <v>4402.3</v>
+        <v>4207.2</v>
       </c>
       <c r="D2703" t="s">
         <v>2705</v>
@@ -47168,7 +47168,7 @@
         <v>15</v>
       </c>
       <c r="C2704">
-        <v>4416.4</v>
+        <v>4220</v>
       </c>
       <c r="D2704" t="s">
         <v>2706</v>
@@ -47182,7 +47182,7 @@
         <v>16</v>
       </c>
       <c r="C2705">
-        <v>4446.7</v>
+        <v>4223.9</v>
       </c>
       <c r="D2705" t="s">
         <v>2707</v>
@@ -47196,7 +47196,7 @@
         <v>17</v>
       </c>
       <c r="C2706">
-        <v>4295.4</v>
+        <v>4214.6</v>
       </c>
       <c r="D2706" t="s">
         <v>2708</v>
@@ -47210,7 +47210,7 @@
         <v>18</v>
       </c>
       <c r="C2707">
-        <v>4288.7</v>
+        <v>4225.2</v>
       </c>
       <c r="D2707" t="s">
         <v>2709</v>
@@ -47224,7 +47224,7 @@
         <v>19</v>
       </c>
       <c r="C2708">
-        <v>4280.1</v>
+        <v>4229.8</v>
       </c>
       <c r="D2708" t="s">
         <v>2710</v>
@@ -47238,7 +47238,7 @@
         <v>20</v>
       </c>
       <c r="C2709">
-        <v>4281.6</v>
+        <v>4237.3</v>
       </c>
       <c r="D2709" t="s">
         <v>2711</v>
@@ -47252,7 +47252,7 @@
         <v>21</v>
       </c>
       <c r="C2710">
-        <v>4214.7</v>
+        <v>4289.7</v>
       </c>
       <c r="D2710" t="s">
         <v>2712</v>
@@ -47266,7 +47266,7 @@
         <v>22</v>
       </c>
       <c r="C2711">
-        <v>4227.8</v>
+        <v>4337.9</v>
       </c>
       <c r="D2711" t="s">
         <v>2713</v>
@@ -47280,7 +47280,7 @@
         <v>23</v>
       </c>
       <c r="C2712">
-        <v>4249.1</v>
+        <v>4362.2</v>
       </c>
       <c r="D2712" t="s">
         <v>2714</v>
@@ -47294,7 +47294,7 @@
         <v>24</v>
       </c>
       <c r="C2713">
-        <v>4268.3</v>
+        <v>4407.8</v>
       </c>
       <c r="D2713" t="s">
         <v>2715</v>
@@ -47308,7 +47308,7 @@
         <v>25</v>
       </c>
       <c r="C2714">
-        <v>4569.2</v>
+        <v>4658.1</v>
       </c>
       <c r="D2714" t="s">
         <v>2716</v>
@@ -47322,7 +47322,7 @@
         <v>26</v>
       </c>
       <c r="C2715">
-        <v>4595.1</v>
+        <v>4687</v>
       </c>
       <c r="D2715" t="s">
         <v>2717</v>
@@ -47336,7 +47336,7 @@
         <v>27</v>
       </c>
       <c r="C2716">
-        <v>4624.8</v>
+        <v>4740.3</v>
       </c>
       <c r="D2716" t="s">
         <v>2718</v>
@@ -47350,7 +47350,7 @@
         <v>28</v>
       </c>
       <c r="C2717">
-        <v>4647.5</v>
+        <v>4828.7</v>
       </c>
       <c r="D2717" t="s">
         <v>2719</v>
@@ -47364,7 +47364,7 @@
         <v>29</v>
       </c>
       <c r="C2718">
-        <v>4472.4</v>
+        <v>4964</v>
       </c>
       <c r="D2718" t="s">
         <v>2720</v>
@@ -47378,7 +47378,7 @@
         <v>30</v>
       </c>
       <c r="C2719">
-        <v>4522.3</v>
+        <v>5062.9</v>
       </c>
       <c r="D2719" t="s">
         <v>2721</v>
@@ -47392,7 +47392,7 @@
         <v>31</v>
       </c>
       <c r="C2720">
-        <v>4555.1</v>
+        <v>5137.3</v>
       </c>
       <c r="D2720" t="s">
         <v>2722</v>
@@ -47406,7 +47406,7 @@
         <v>32</v>
       </c>
       <c r="C2721">
-        <v>4616.4</v>
+        <v>5278.5</v>
       </c>
       <c r="D2721" t="s">
         <v>2723</v>
@@ -47420,7 +47420,7 @@
         <v>33</v>
       </c>
       <c r="C2722">
-        <v>4546.9</v>
+        <v>5131.1</v>
       </c>
       <c r="D2722" t="s">
         <v>2724</v>
@@ -47434,7 +47434,7 @@
         <v>34</v>
       </c>
       <c r="C2723">
-        <v>4643.9</v>
+        <v>5252.2</v>
       </c>
       <c r="D2723" t="s">
         <v>2725</v>
@@ -47448,7 +47448,7 @@
         <v>35</v>
       </c>
       <c r="C2724">
-        <v>4725.9</v>
+        <v>5348.7</v>
       </c>
       <c r="D2724" t="s">
         <v>2726</v>
@@ -47462,7 +47462,7 @@
         <v>36</v>
       </c>
       <c r="C2725">
-        <v>4840.7</v>
+        <v>5443.9</v>
       </c>
       <c r="D2725" t="s">
         <v>2727</v>
@@ -47476,7 +47476,7 @@
         <v>37</v>
       </c>
       <c r="C2726">
-        <v>4832.8</v>
+        <v>5311</v>
       </c>
       <c r="D2726" t="s">
         <v>2728</v>
@@ -47490,7 +47490,7 @@
         <v>38</v>
       </c>
       <c r="C2727">
-        <v>4868.3</v>
+        <v>5343.7</v>
       </c>
       <c r="D2727" t="s">
         <v>2729</v>
@@ -47504,7 +47504,7 @@
         <v>39</v>
       </c>
       <c r="C2728">
-        <v>4965.6</v>
+        <v>5425.6</v>
       </c>
       <c r="D2728" t="s">
         <v>2730</v>
@@ -47518,7 +47518,7 @@
         <v>40</v>
       </c>
       <c r="C2729">
-        <v>4986.6</v>
+        <v>5487.3</v>
       </c>
       <c r="D2729" t="s">
         <v>2731</v>
@@ -47532,7 +47532,7 @@
         <v>41</v>
       </c>
       <c r="C2730">
-        <v>5120.6</v>
+        <v>5520</v>
       </c>
       <c r="D2730" t="s">
         <v>2732</v>
@@ -47546,7 +47546,7 @@
         <v>42</v>
       </c>
       <c r="C2731">
-        <v>5128.9</v>
+        <v>5583.9</v>
       </c>
       <c r="D2731" t="s">
         <v>2733</v>
@@ -47560,7 +47560,7 @@
         <v>43</v>
       </c>
       <c r="C2732">
-        <v>5213.1</v>
+        <v>5633.5</v>
       </c>
       <c r="D2732" t="s">
         <v>2734</v>
@@ -47574,7 +47574,7 @@
         <v>44</v>
       </c>
       <c r="C2733">
-        <v>5258.7</v>
+        <v>5698.9</v>
       </c>
       <c r="D2733" t="s">
         <v>2735</v>
@@ -47588,7 +47588,7 @@
         <v>45</v>
       </c>
       <c r="C2734">
-        <v>4838.1</v>
+        <v>5570.7</v>
       </c>
       <c r="D2734" t="s">
         <v>2736</v>
@@ -47602,7 +47602,7 @@
         <v>46</v>
       </c>
       <c r="C2735">
-        <v>4840.4</v>
+        <v>5593.1</v>
       </c>
       <c r="D2735" t="s">
         <v>2737</v>
@@ -47616,7 +47616,7 @@
         <v>47</v>
       </c>
       <c r="C2736">
-        <v>4930.1</v>
+        <v>5639.9</v>
       </c>
       <c r="D2736" t="s">
         <v>2738</v>
@@ -47630,7 +47630,7 @@
         <v>48</v>
       </c>
       <c r="C2737">
-        <v>4946.6</v>
+        <v>5714.1</v>
       </c>
       <c r="D2737" t="s">
         <v>2739</v>
@@ -47644,7 +47644,7 @@
         <v>49</v>
       </c>
       <c r="C2738">
-        <v>4802.3</v>
+        <v>5673.2</v>
       </c>
       <c r="D2738" t="s">
         <v>2740</v>
@@ -47658,7 +47658,7 @@
         <v>50</v>
       </c>
       <c r="C2739">
-        <v>4765</v>
+        <v>5525.2</v>
       </c>
       <c r="D2739" t="s">
         <v>2741</v>
@@ -47672,7 +47672,7 @@
         <v>51</v>
       </c>
       <c r="C2740">
-        <v>4624.7</v>
+        <v>5581.2</v>
       </c>
       <c r="D2740" t="s">
         <v>2742</v>
@@ -47686,7 +47686,7 @@
         <v>52</v>
       </c>
       <c r="C2741">
-        <v>4509.5</v>
+        <v>5565.8</v>
       </c>
       <c r="D2741" t="s">
         <v>2743</v>
@@ -47700,7 +47700,7 @@
         <v>53</v>
       </c>
       <c r="C2742">
-        <v>4612</v>
+        <v>5485</v>
       </c>
       <c r="D2742" t="s">
         <v>2744</v>
@@ -47714,7 +47714,7 @@
         <v>54</v>
       </c>
       <c r="C2743">
-        <v>4551.6</v>
+        <v>5493.9</v>
       </c>
       <c r="D2743" t="s">
         <v>2745</v>
@@ -47728,7 +47728,7 @@
         <v>55</v>
       </c>
       <c r="C2744">
-        <v>4589.4</v>
+        <v>5529.2</v>
       </c>
       <c r="D2744" t="s">
         <v>2746</v>
@@ -47742,7 +47742,7 @@
         <v>56</v>
       </c>
       <c r="C2745">
-        <v>4594.7</v>
+        <v>5539.8</v>
       </c>
       <c r="D2745" t="s">
         <v>2747</v>
@@ -47756,7 +47756,7 @@
         <v>57</v>
       </c>
       <c r="C2746">
-        <v>4665.9</v>
+        <v>5530</v>
       </c>
       <c r="D2746" t="s">
         <v>2748</v>
@@ -47770,7 +47770,7 @@
         <v>58</v>
       </c>
       <c r="C2747">
-        <v>4688.9</v>
+        <v>5523.1</v>
       </c>
       <c r="D2747" t="s">
         <v>2749</v>
@@ -47784,7 +47784,7 @@
         <v>59</v>
       </c>
       <c r="C2748">
-        <v>4652</v>
+        <v>5504.8</v>
       </c>
       <c r="D2748" t="s">
         <v>2750</v>
@@ -47798,7 +47798,7 @@
         <v>60</v>
       </c>
       <c r="C2749">
-        <v>4679.1</v>
+        <v>5437</v>
       </c>
       <c r="D2749" t="s">
         <v>2751</v>
@@ -47812,7 +47812,7 @@
         <v>61</v>
       </c>
       <c r="C2750">
-        <v>4586.7</v>
+        <v>5436.5</v>
       </c>
       <c r="D2750" t="s">
         <v>2752</v>
@@ -47826,7 +47826,7 @@
         <v>62</v>
       </c>
       <c r="C2751">
-        <v>4635.5</v>
+        <v>5460.8</v>
       </c>
       <c r="D2751" t="s">
         <v>2753</v>
@@ -47840,7 +47840,7 @@
         <v>63</v>
       </c>
       <c r="C2752">
-        <v>4632.9</v>
+        <v>5411.9</v>
       </c>
       <c r="D2752" t="s">
         <v>2754</v>
@@ -47854,7 +47854,7 @@
         <v>64</v>
       </c>
       <c r="C2753">
-        <v>4643.5</v>
+        <v>5361.7</v>
       </c>
       <c r="D2753" t="s">
         <v>2755</v>
@@ -47868,7 +47868,7 @@
         <v>65</v>
       </c>
       <c r="C2754">
-        <v>4661.5</v>
+        <v>5475.4</v>
       </c>
       <c r="D2754" t="s">
         <v>2756</v>
@@ -47882,7 +47882,7 @@
         <v>66</v>
       </c>
       <c r="C2755">
-        <v>4660.4</v>
+        <v>5396.2</v>
       </c>
       <c r="D2755" t="s">
         <v>2757</v>
@@ -47896,7 +47896,7 @@
         <v>67</v>
       </c>
       <c r="C2756">
-        <v>4765</v>
+        <v>5321</v>
       </c>
       <c r="D2756" t="s">
         <v>2758</v>
@@ -47910,7 +47910,7 @@
         <v>68</v>
       </c>
       <c r="C2757">
-        <v>4703.5</v>
+        <v>5213.6</v>
       </c>
       <c r="D2757" t="s">
         <v>2759</v>
@@ -47924,7 +47924,7 @@
         <v>69</v>
       </c>
       <c r="C2758">
-        <v>5109.9</v>
+        <v>5590.6</v>
       </c>
       <c r="D2758" t="s">
         <v>2760</v>
@@ -47938,7 +47938,7 @@
         <v>70</v>
       </c>
       <c r="C2759">
-        <v>5030.3</v>
+        <v>5480.3</v>
       </c>
       <c r="D2759" t="s">
         <v>2761</v>
@@ -47952,7 +47952,7 @@
         <v>71</v>
       </c>
       <c r="C2760">
-        <v>4951.1</v>
+        <v>5339.6</v>
       </c>
       <c r="D2760" t="s">
         <v>2762</v>
@@ -47966,7 +47966,7 @@
         <v>72</v>
       </c>
       <c r="C2761">
-        <v>4868.2</v>
+        <v>5200.7</v>
       </c>
       <c r="D2761" t="s">
         <v>2763</v>
@@ -47980,7 +47980,7 @@
         <v>73</v>
       </c>
       <c r="C2762">
-        <v>5398.1</v>
+        <v>5591.2</v>
       </c>
       <c r="D2762" t="s">
         <v>2764</v>
@@ -47994,7 +47994,7 @@
         <v>74</v>
       </c>
       <c r="C2763">
-        <v>5343.3</v>
+        <v>5441.2</v>
       </c>
       <c r="D2763" t="s">
         <v>2765</v>
@@ -48008,7 +48008,7 @@
         <v>75</v>
       </c>
       <c r="C2764">
-        <v>5268.6</v>
+        <v>5292.5</v>
       </c>
       <c r="D2764" t="s">
         <v>2766</v>
@@ -48022,7 +48022,7 @@
         <v>76</v>
       </c>
       <c r="C2765">
-        <v>5261.9</v>
+        <v>5184.8</v>
       </c>
       <c r="D2765" t="s">
         <v>2767</v>
@@ -48036,7 +48036,7 @@
         <v>77</v>
       </c>
       <c r="C2766">
-        <v>5229.5</v>
+        <v>5387.7</v>
       </c>
       <c r="D2766" t="s">
         <v>2768</v>
@@ -48050,7 +48050,7 @@
         <v>78</v>
       </c>
       <c r="C2767">
-        <v>5235.7</v>
+        <v>5323.7</v>
       </c>
       <c r="D2767" t="s">
         <v>2769</v>
@@ -48064,7 +48064,7 @@
         <v>79</v>
       </c>
       <c r="C2768">
-        <v>5179</v>
+        <v>5213.2</v>
       </c>
       <c r="D2768" t="s">
         <v>2770</v>
@@ -48078,7 +48078,7 @@
         <v>80</v>
       </c>
       <c r="C2769">
-        <v>5117.4</v>
+        <v>5117</v>
       </c>
       <c r="D2769" t="s">
         <v>2771</v>
@@ -48092,7 +48092,7 @@
         <v>81</v>
       </c>
       <c r="C2770">
-        <v>5375</v>
+        <v>5302.5</v>
       </c>
       <c r="D2770" t="s">
         <v>2772</v>
@@ -48106,7 +48106,7 @@
         <v>82</v>
       </c>
       <c r="C2771">
-        <v>5359.7</v>
+        <v>5270.8</v>
       </c>
       <c r="D2771" t="s">
         <v>2773</v>
@@ -48120,7 +48120,7 @@
         <v>83</v>
       </c>
       <c r="C2772">
-        <v>5372</v>
+        <v>5212.7</v>
       </c>
       <c r="D2772" t="s">
         <v>2774</v>
@@ -48134,7 +48134,7 @@
         <v>84</v>
       </c>
       <c r="C2773">
-        <v>5462.1</v>
+        <v>5340.8</v>
       </c>
       <c r="D2773" t="s">
         <v>2775</v>
@@ -48148,7 +48148,7 @@
         <v>85</v>
       </c>
       <c r="C2774">
-        <v>5890.9</v>
+        <v>5497.2</v>
       </c>
       <c r="D2774" t="s">
         <v>2776</v>
@@ -48162,7 +48162,7 @@
         <v>86</v>
       </c>
       <c r="C2775">
-        <v>5859.9</v>
+        <v>5428.7</v>
       </c>
       <c r="D2775" t="s">
         <v>2777</v>
@@ -48176,7 +48176,7 @@
         <v>87</v>
       </c>
       <c r="C2776">
-        <v>5835.5</v>
+        <v>5403.2</v>
       </c>
       <c r="D2776" t="s">
         <v>2778</v>
@@ -48190,7 +48190,7 @@
         <v>88</v>
       </c>
       <c r="C2777">
-        <v>5797</v>
+        <v>5317.5</v>
       </c>
       <c r="D2777" t="s">
         <v>2779</v>
@@ -48204,7 +48204,7 @@
         <v>89</v>
       </c>
       <c r="C2778">
-        <v>5480.6</v>
+        <v>5000.7</v>
       </c>
       <c r="D2778" t="s">
         <v>2780</v>
@@ -48218,7 +48218,7 @@
         <v>90</v>
       </c>
       <c r="C2779">
-        <v>5496.2</v>
+        <v>4892.8</v>
       </c>
       <c r="D2779" t="s">
         <v>2781</v>
@@ -48232,7 +48232,7 @@
         <v>91</v>
       </c>
       <c r="C2780">
-        <v>5439.6</v>
+        <v>4831.5</v>
       </c>
       <c r="D2780" t="s">
         <v>2782</v>
@@ -48246,7 +48246,7 @@
         <v>92</v>
       </c>
       <c r="C2781">
-        <v>5349.3</v>
+        <v>4769.8</v>
       </c>
       <c r="D2781" t="s">
         <v>2783</v>
@@ -48260,7 +48260,7 @@
         <v>93</v>
       </c>
       <c r="C2782">
-        <v>4800.4</v>
+        <v>4472.9</v>
       </c>
       <c r="D2782" t="s">
         <v>2784</v>
@@ -48274,7 +48274,7 @@
         <v>94</v>
       </c>
       <c r="C2783">
-        <v>4705.6</v>
+        <v>4419.6</v>
       </c>
       <c r="D2783" t="s">
         <v>2785</v>
@@ -48288,7 +48288,7 @@
         <v>95</v>
       </c>
       <c r="C2784">
-        <v>4689.4</v>
+        <v>4393.4</v>
       </c>
       <c r="D2784" t="s">
         <v>2786</v>
@@ -48302,7 +48302,7 @@
         <v>96</v>
       </c>
       <c r="C2785">
-        <v>4673.6</v>
+        <v>4337.6</v>
       </c>
       <c r="D2785" t="s">
         <v>2787</v>
@@ -48316,7 +48316,7 @@
         <v>1</v>
       </c>
       <c r="C2786">
-        <v>4616.1</v>
+        <v>4480.9</v>
       </c>
       <c r="D2786" t="s">
         <v>2788</v>
@@ -48330,7 +48330,7 @@
         <v>2</v>
       </c>
       <c r="C2787">
-        <v>4642</v>
+        <v>4530.8</v>
       </c>
       <c r="D2787" t="s">
         <v>2789</v>
@@ -48344,7 +48344,7 @@
         <v>3</v>
       </c>
       <c r="C2788">
-        <v>4580.7</v>
+        <v>4528.9</v>
       </c>
       <c r="D2788" t="s">
         <v>2790</v>
@@ -48358,7 +48358,7 @@
         <v>4</v>
       </c>
       <c r="C2789">
-        <v>4541.1</v>
+        <v>4498.4</v>
       </c>
       <c r="D2789" t="s">
         <v>2791</v>
@@ -48372,7 +48372,7 @@
         <v>5</v>
       </c>
       <c r="C2790">
-        <v>4259.5</v>
+        <v>4239.4</v>
       </c>
       <c r="D2790" t="s">
         <v>2792</v>
@@ -48386,7 +48386,7 @@
         <v>6</v>
       </c>
       <c r="C2791">
-        <v>4270</v>
+        <v>4211.9</v>
       </c>
       <c r="D2791" t="s">
         <v>2793</v>
@@ -48400,7 +48400,7 @@
         <v>7</v>
       </c>
       <c r="C2792">
-        <v>4240.4</v>
+        <v>4197.5</v>
       </c>
       <c r="D2792" t="s">
         <v>2794</v>
@@ -48414,7 +48414,7 @@
         <v>8</v>
       </c>
       <c r="C2793">
-        <v>4195.9</v>
+        <v>4126</v>
       </c>
       <c r="D2793" t="s">
         <v>2795</v>
@@ -48428,7 +48428,7 @@
         <v>9</v>
       </c>
       <c r="C2794">
-        <v>4168</v>
+        <v>4164.3</v>
       </c>
       <c r="D2794" t="s">
         <v>2796</v>
@@ -48442,7 +48442,7 @@
         <v>10</v>
       </c>
       <c r="C2795">
-        <v>4155.7</v>
+        <v>4169.9</v>
       </c>
       <c r="D2795" t="s">
         <v>2797</v>
@@ -48456,7 +48456,7 @@
         <v>11</v>
       </c>
       <c r="C2796">
-        <v>4188.3</v>
+        <v>4181.2</v>
       </c>
       <c r="D2796" t="s">
         <v>2798</v>
@@ -48470,7 +48470,7 @@
         <v>12</v>
       </c>
       <c r="C2797">
-        <v>4201.6</v>
+        <v>4184.3</v>
       </c>
       <c r="D2797" t="s">
         <v>2799</v>
@@ -48484,7 +48484,7 @@
         <v>13</v>
       </c>
       <c r="C2798">
-        <v>4252.7</v>
+        <v>4037.4</v>
       </c>
       <c r="D2798" t="s">
         <v>2800</v>
@@ -48498,7 +48498,7 @@
         <v>14</v>
       </c>
       <c r="C2799">
-        <v>4262.3</v>
+        <v>4047.2</v>
       </c>
       <c r="D2799" t="s">
         <v>2801</v>
@@ -48512,7 +48512,7 @@
         <v>15</v>
       </c>
       <c r="C2800">
-        <v>4266.4</v>
+        <v>4060</v>
       </c>
       <c r="D2800" t="s">
         <v>2802</v>
@@ -48526,7 +48526,7 @@
         <v>16</v>
       </c>
       <c r="C2801">
-        <v>4286.7</v>
+        <v>4043.9</v>
       </c>
       <c r="D2801" t="s">
         <v>2803</v>
@@ -48540,7 +48540,7 @@
         <v>17</v>
       </c>
       <c r="C2802">
-        <v>4135.4</v>
+        <v>4014.6</v>
       </c>
       <c r="D2802" t="s">
         <v>2804</v>
@@ -48554,7 +48554,7 @@
         <v>18</v>
       </c>
       <c r="C2803">
-        <v>4118.7</v>
+        <v>4015.2</v>
       </c>
       <c r="D2803" t="s">
         <v>2805</v>
@@ -48568,7 +48568,7 @@
         <v>19</v>
       </c>
       <c r="C2804">
-        <v>4090.1</v>
+        <v>4009.8</v>
       </c>
       <c r="D2804" t="s">
         <v>2806</v>
@@ -48582,7 +48582,7 @@
         <v>20</v>
       </c>
       <c r="C2805">
-        <v>4071.6</v>
+        <v>4007.3</v>
       </c>
       <c r="D2805" t="s">
         <v>2807</v>
@@ -48596,7 +48596,7 @@
         <v>21</v>
       </c>
       <c r="C2806">
-        <v>3974.7</v>
+        <v>4029.7</v>
       </c>
       <c r="D2806" t="s">
         <v>2808</v>
@@ -48610,7 +48610,7 @@
         <v>22</v>
       </c>
       <c r="C2807">
-        <v>3947.8</v>
+        <v>4037.9</v>
       </c>
       <c r="D2807" t="s">
         <v>2809</v>
@@ -48624,7 +48624,7 @@
         <v>23</v>
       </c>
       <c r="C2808">
-        <v>3909.1</v>
+        <v>4022.2</v>
       </c>
       <c r="D2808" t="s">
         <v>2810</v>
@@ -48638,7 +48638,7 @@
         <v>24</v>
       </c>
       <c r="C2809">
-        <v>3858.3</v>
+        <v>4007.8</v>
       </c>
       <c r="D2809" t="s">
         <v>2811</v>
@@ -48652,7 +48652,7 @@
         <v>25</v>
       </c>
       <c r="C2810">
-        <v>4079.2</v>
+        <v>4198.1</v>
       </c>
       <c r="D2810" t="s">
         <v>2812</v>
@@ -48666,7 +48666,7 @@
         <v>26</v>
       </c>
       <c r="C2811">
-        <v>4035.1</v>
+        <v>4157</v>
       </c>
       <c r="D2811" t="s">
         <v>2813</v>
@@ -48680,7 +48680,7 @@
         <v>27</v>
       </c>
       <c r="C2812">
-        <v>3984.8</v>
+        <v>4150.3</v>
       </c>
       <c r="D2812" t="s">
         <v>2814</v>
@@ -48694,7 +48694,7 @@
         <v>28</v>
       </c>
       <c r="C2813">
-        <v>3927.5</v>
+        <v>4158.7</v>
       </c>
       <c r="D2813" t="s">
         <v>2815</v>
@@ -48708,7 +48708,7 @@
         <v>29</v>
       </c>
       <c r="C2814">
-        <v>3682.4</v>
+        <v>4174</v>
       </c>
       <c r="D2814" t="s">
         <v>2816</v>
@@ -48722,7 +48722,7 @@
         <v>30</v>
       </c>
       <c r="C2815">
-        <v>3652.3</v>
+        <v>4212.9</v>
       </c>
       <c r="D2815" t="s">
         <v>2817</v>
@@ -48736,7 +48736,7 @@
         <v>31</v>
       </c>
       <c r="C2816">
-        <v>3665.1</v>
+        <v>4267.3</v>
       </c>
       <c r="D2816" t="s">
         <v>2818</v>
@@ -48750,7 +48750,7 @@
         <v>32</v>
       </c>
       <c r="C2817">
-        <v>3736.4</v>
+        <v>4378.5</v>
       </c>
       <c r="D2817" t="s">
         <v>2819</v>
@@ -48764,7 +48764,7 @@
         <v>33</v>
       </c>
       <c r="C2818">
-        <v>3716.9</v>
+        <v>4231.1</v>
       </c>
       <c r="D2818" t="s">
         <v>2820</v>
@@ -48778,7 +48778,7 @@
         <v>34</v>
       </c>
       <c r="C2819">
-        <v>3833.9</v>
+        <v>4352.2</v>
       </c>
       <c r="D2819" t="s">
         <v>2821</v>
@@ -48792,7 +48792,7 @@
         <v>35</v>
       </c>
       <c r="C2820">
-        <v>3935.9</v>
+        <v>4478.7</v>
       </c>
       <c r="D2820" t="s">
         <v>2822</v>
@@ -48806,7 +48806,7 @@
         <v>36</v>
       </c>
       <c r="C2821">
-        <v>4050.7</v>
+        <v>4603.9</v>
       </c>
       <c r="D2821" t="s">
         <v>2823</v>
@@ -48820,7 +48820,7 @@
         <v>37</v>
       </c>
       <c r="C2822">
-        <v>4042.8</v>
+        <v>4531</v>
       </c>
       <c r="D2822" t="s">
         <v>2824</v>
@@ -48834,7 +48834,7 @@
         <v>38</v>
       </c>
       <c r="C2823">
-        <v>4098.3</v>
+        <v>4613.7</v>
       </c>
       <c r="D2823" t="s">
         <v>2825</v>
@@ -48848,7 +48848,7 @@
         <v>39</v>
       </c>
       <c r="C2824">
-        <v>4235.6</v>
+        <v>4735.6</v>
       </c>
       <c r="D2824" t="s">
         <v>2826</v>
@@ -48862,7 +48862,7 @@
         <v>40</v>
       </c>
       <c r="C2825">
-        <v>4336.6</v>
+        <v>4837.3</v>
       </c>
       <c r="D2825" t="s">
         <v>2827</v>
@@ -48876,7 +48876,7 @@
         <v>41</v>
       </c>
       <c r="C2826">
-        <v>4540.6</v>
+        <v>4900</v>
       </c>
       <c r="D2826" t="s">
         <v>2828</v>
@@ -48890,7 +48890,7 @@
         <v>42</v>
       </c>
       <c r="C2827">
-        <v>4608.9</v>
+        <v>4983.9</v>
       </c>
       <c r="D2827" t="s">
         <v>2829</v>
@@ -48904,7 +48904,7 @@
         <v>43</v>
       </c>
       <c r="C2828">
-        <v>4713.1</v>
+        <v>5063.5</v>
       </c>
       <c r="D2828" t="s">
         <v>2830</v>
@@ -48918,7 +48918,7 @@
         <v>44</v>
       </c>
       <c r="C2829">
-        <v>4758.7</v>
+        <v>5148.9</v>
       </c>
       <c r="D2829" t="s">
         <v>2831</v>
@@ -48932,7 +48932,7 @@
         <v>45</v>
       </c>
       <c r="C2830">
-        <v>4308.1</v>
+        <v>5060.7</v>
       </c>
       <c r="D2830" t="s">
         <v>2832</v>
@@ -48946,7 +48946,7 @@
         <v>46</v>
       </c>
       <c r="C2831">
-        <v>4300.4</v>
+        <v>5113.1</v>
       </c>
       <c r="D2831" t="s">
         <v>2833</v>
@@ -48960,7 +48960,7 @@
         <v>47</v>
       </c>
       <c r="C2832">
-        <v>4380.1</v>
+        <v>5199.9</v>
       </c>
       <c r="D2832" t="s">
         <v>2834</v>
@@ -48974,7 +48974,7 @@
         <v>48</v>
       </c>
       <c r="C2833">
-        <v>4426.6</v>
+        <v>5284.1</v>
       </c>
       <c r="D2833" t="s">
         <v>2835</v>
@@ -48988,7 +48988,7 @@
         <v>49</v>
       </c>
       <c r="C2834">
-        <v>4322.3</v>
+        <v>5253.2</v>
       </c>
       <c r="D2834" t="s">
         <v>2836</v>
@@ -49002,7 +49002,7 @@
         <v>50</v>
       </c>
       <c r="C2835">
-        <v>4315</v>
+        <v>5115.2</v>
       </c>
       <c r="D2835" t="s">
         <v>2837</v>
@@ -49016,7 +49016,7 @@
         <v>51</v>
       </c>
       <c r="C2836">
-        <v>4194.7</v>
+        <v>5171.2</v>
       </c>
       <c r="D2836" t="s">
         <v>2838</v>
@@ -49030,7 +49030,7 @@
         <v>52</v>
       </c>
       <c r="C2837">
-        <v>4089.5</v>
+        <v>5145.8</v>
       </c>
       <c r="D2837" t="s">
         <v>2839</v>
@@ -49044,7 +49044,7 @@
         <v>53</v>
       </c>
       <c r="C2838">
-        <v>4172</v>
+        <v>5055</v>
       </c>
       <c r="D2838" t="s">
         <v>2840</v>
@@ -49058,7 +49058,7 @@
         <v>54</v>
       </c>
       <c r="C2839">
-        <v>4091.6</v>
+        <v>5053.9</v>
       </c>
       <c r="D2839" t="s">
         <v>2841</v>
@@ -49072,7 +49072,7 @@
         <v>55</v>
       </c>
       <c r="C2840">
-        <v>4109.4</v>
+        <v>5099.2</v>
       </c>
       <c r="D2840" t="s">
         <v>2842</v>
@@ -49086,7 +49086,7 @@
         <v>56</v>
       </c>
       <c r="C2841">
-        <v>4084.7</v>
+        <v>5109.8</v>
       </c>
       <c r="D2841" t="s">
         <v>2843</v>
@@ -49100,7 +49100,7 @@
         <v>57</v>
       </c>
       <c r="C2842">
-        <v>4125.9</v>
+        <v>5110</v>
       </c>
       <c r="D2842" t="s">
         <v>2844</v>
@@ -49114,7 +49114,7 @@
         <v>58</v>
       </c>
       <c r="C2843">
-        <v>4148.9</v>
+        <v>5103.1</v>
       </c>
       <c r="D2843" t="s">
         <v>2845</v>
@@ -49128,7 +49128,7 @@
         <v>59</v>
       </c>
       <c r="C2844">
-        <v>4142</v>
+        <v>5104.8</v>
       </c>
       <c r="D2844" t="s">
         <v>2846</v>
@@ -49142,7 +49142,7 @@
         <v>60</v>
       </c>
       <c r="C2845">
-        <v>4229.1</v>
+        <v>5047</v>
       </c>
       <c r="D2845" t="s">
         <v>2847</v>
@@ -49156,7 +49156,7 @@
         <v>61</v>
       </c>
       <c r="C2846">
-        <v>4216.7</v>
+        <v>5056.5</v>
       </c>
       <c r="D2846" t="s">
         <v>2848</v>
@@ -49170,7 +49170,7 @@
         <v>62</v>
       </c>
       <c r="C2847">
-        <v>4345.5</v>
+        <v>5090.8</v>
       </c>
       <c r="D2847" t="s">
         <v>2849</v>
@@ -49184,7 +49184,7 @@
         <v>63</v>
       </c>
       <c r="C2848">
-        <v>4402.9</v>
+        <v>5071.9</v>
       </c>
       <c r="D2848" t="s">
         <v>2850</v>
@@ -49198,7 +49198,7 @@
         <v>64</v>
       </c>
       <c r="C2849">
-        <v>4443.5</v>
+        <v>5041.7</v>
       </c>
       <c r="D2849" t="s">
         <v>2851</v>
@@ -49212,7 +49212,7 @@
         <v>65</v>
       </c>
       <c r="C2850">
-        <v>4471.5</v>
+        <v>5165.4</v>
       </c>
       <c r="D2850" t="s">
         <v>2852</v>
@@ -49226,7 +49226,7 @@
         <v>66</v>
       </c>
       <c r="C2851">
-        <v>4460.4</v>
+        <v>5086.2</v>
       </c>
       <c r="D2851" t="s">
         <v>2853</v>
@@ -49240,7 +49240,7 @@
         <v>67</v>
       </c>
       <c r="C2852">
-        <v>4555</v>
+        <v>5021</v>
       </c>
       <c r="D2852" t="s">
         <v>2854</v>
@@ -49254,7 +49254,7 @@
         <v>68</v>
       </c>
       <c r="C2853">
-        <v>4483.5</v>
+        <v>4923.6</v>
       </c>
       <c r="D2853" t="s">
         <v>2855</v>
@@ -49268,7 +49268,7 @@
         <v>69</v>
       </c>
       <c r="C2854">
-        <v>4879.9</v>
+        <v>5320.6</v>
       </c>
       <c r="D2854" t="s">
         <v>2856</v>
@@ -49282,7 +49282,7 @@
         <v>70</v>
       </c>
       <c r="C2855">
-        <v>4800.3</v>
+        <v>5210.3</v>
       </c>
       <c r="D2855" t="s">
         <v>2857</v>
@@ -49296,7 +49296,7 @@
         <v>71</v>
       </c>
       <c r="C2856">
-        <v>4741.1</v>
+        <v>5089.6</v>
       </c>
       <c r="D2856" t="s">
         <v>2858</v>
@@ -49310,7 +49310,7 @@
         <v>72</v>
       </c>
       <c r="C2857">
-        <v>4708.2</v>
+        <v>4950.7</v>
       </c>
       <c r="D2857" t="s">
         <v>2859</v>
@@ -49324,7 +49324,7 @@
         <v>73</v>
       </c>
       <c r="C2858">
-        <v>5278.1</v>
+        <v>5311.2</v>
       </c>
       <c r="D2858" t="s">
         <v>2860</v>
@@ -49338,7 +49338,7 @@
         <v>74</v>
       </c>
       <c r="C2859">
-        <v>5233.3</v>
+        <v>5151.2</v>
       </c>
       <c r="D2859" t="s">
         <v>2861</v>
@@ -49352,7 +49352,7 @@
         <v>75</v>
       </c>
       <c r="C2860">
-        <v>5138.6</v>
+        <v>4982.5</v>
       </c>
       <c r="D2860" t="s">
         <v>2862</v>
@@ -49366,7 +49366,7 @@
         <v>76</v>
       </c>
       <c r="C2861">
-        <v>5071.9</v>
+        <v>4834.8</v>
       </c>
       <c r="D2861" t="s">
         <v>2863</v>
@@ -49380,7 +49380,7 @@
         <v>77</v>
       </c>
       <c r="C2862">
-        <v>4969.5</v>
+        <v>5007.7</v>
       </c>
       <c r="D2862" t="s">
         <v>2864</v>
@@ -49394,7 +49394,7 @@
         <v>78</v>
       </c>
       <c r="C2863">
-        <v>4885.7</v>
+        <v>4893.7</v>
       </c>
       <c r="D2863" t="s">
         <v>2865</v>
@@ -49408,7 +49408,7 @@
         <v>79</v>
       </c>
       <c r="C2864">
-        <v>4759</v>
+        <v>4763.2</v>
       </c>
       <c r="D2864" t="s">
         <v>2866</v>
@@ -49422,7 +49422,7 @@
         <v>80</v>
       </c>
       <c r="C2865">
-        <v>4647.4</v>
+        <v>4637</v>
       </c>
       <c r="D2865" t="s">
         <v>2867</v>
@@ -49436,7 +49436,7 @@
         <v>81</v>
       </c>
       <c r="C2866">
-        <v>4865</v>
+        <v>4812.5</v>
       </c>
       <c r="D2866" t="s">
         <v>2868</v>
@@ -49450,7 +49450,7 @@
         <v>82</v>
       </c>
       <c r="C2867">
-        <v>4809.7</v>
+        <v>4780.8</v>
       </c>
       <c r="D2867" t="s">
         <v>2869</v>
@@ -49464,7 +49464,7 @@
         <v>83</v>
       </c>
       <c r="C2868">
-        <v>4822</v>
+        <v>4722.7</v>
       </c>
       <c r="D2868" t="s">
         <v>2870</v>
@@ -49478,7 +49478,7 @@
         <v>84</v>
       </c>
       <c r="C2869">
-        <v>4902.1</v>
+        <v>4840.8</v>
       </c>
       <c r="D2869" t="s">
         <v>2871</v>
@@ -49492,7 +49492,7 @@
         <v>85</v>
       </c>
       <c r="C2870">
-        <v>5380.9</v>
+        <v>4937.2</v>
       </c>
       <c r="D2870" t="s">
         <v>2872</v>
@@ -49506,7 +49506,7 @@
         <v>86</v>
       </c>
       <c r="C2871">
-        <v>5399.9</v>
+        <v>4858.7</v>
       </c>
       <c r="D2871" t="s">
         <v>2873</v>
@@ -49520,7 +49520,7 @@
         <v>87</v>
       </c>
       <c r="C2872">
-        <v>5365.5</v>
+        <v>4853.2</v>
       </c>
       <c r="D2872" t="s">
         <v>2874</v>
@@ -49534,7 +49534,7 @@
         <v>88</v>
       </c>
       <c r="C2873">
-        <v>5327</v>
+        <v>4797.5</v>
       </c>
       <c r="D2873" t="s">
         <v>2875</v>
@@ -49548,7 +49548,7 @@
         <v>89</v>
       </c>
       <c r="C2874">
-        <v>5020.6</v>
+        <v>4520.7</v>
       </c>
       <c r="D2874" t="s">
         <v>2876</v>
@@ -49562,7 +49562,7 @@
         <v>90</v>
       </c>
       <c r="C2875">
-        <v>4996.2</v>
+        <v>4472.8</v>
       </c>
       <c r="D2875" t="s">
         <v>2877</v>
@@ -49576,7 +49576,7 @@
         <v>91</v>
       </c>
       <c r="C2876">
-        <v>4949.6</v>
+        <v>4401.5</v>
       </c>
       <c r="D2876" t="s">
         <v>2878</v>
@@ -49590,7 +49590,7 @@
         <v>92</v>
       </c>
       <c r="C2877">
-        <v>4909.3</v>
+        <v>4359.8</v>
       </c>
       <c r="D2877" t="s">
         <v>2879</v>
@@ -49604,7 +49604,7 @@
         <v>93</v>
       </c>
       <c r="C2878">
-        <v>4470.4</v>
+        <v>4062.9</v>
       </c>
       <c r="D2878" t="s">
         <v>2880</v>
@@ -49618,7 +49618,7 @@
         <v>94</v>
       </c>
       <c r="C2879">
-        <v>4395.6</v>
+        <v>4009.6</v>
       </c>
       <c r="D2879" t="s">
         <v>2881</v>
@@ -49632,7 +49632,7 @@
         <v>95</v>
       </c>
       <c r="C2880">
-        <v>4339.4</v>
+        <v>3993.4</v>
       </c>
       <c r="D2880" t="s">
         <v>2882</v>
@@ -49646,7 +49646,7 @@
         <v>96</v>
       </c>
       <c r="C2881">
-        <v>4283.6</v>
+        <v>3937.6</v>
       </c>
       <c r="D2881" t="s">
         <v>2883</v>
@@ -49660,7 +49660,7 @@
         <v>1</v>
       </c>
       <c r="C2882">
-        <v>4465</v>
+        <v>3950.6</v>
       </c>
       <c r="D2882" t="s">
         <v>2884</v>
@@ -49674,7 +49674,7 @@
         <v>2</v>
       </c>
       <c r="C2883">
-        <v>4415</v>
+        <v>4009.7</v>
       </c>
       <c r="D2883" t="s">
         <v>2885</v>
@@ -49688,7 +49688,7 @@
         <v>3</v>
       </c>
       <c r="C2884">
-        <v>4365</v>
+        <v>4016.3</v>
       </c>
       <c r="D2884" t="s">
         <v>2886</v>
@@ -49702,7 +49702,7 @@
         <v>4</v>
       </c>
       <c r="C2885">
-        <v>4295</v>
+        <v>4029.2</v>
       </c>
       <c r="D2885" t="s">
         <v>2887</v>
@@ -49716,7 +49716,7 @@
         <v>5</v>
       </c>
       <c r="C2886">
-        <v>4007</v>
+        <v>4169.3</v>
       </c>
       <c r="D2886" t="s">
         <v>2888</v>
@@ -49730,7 +49730,7 @@
         <v>6</v>
       </c>
       <c r="C2887">
-        <v>3975.4</v>
+        <v>4178.6</v>
       </c>
       <c r="D2887" t="s">
         <v>2889</v>
@@ -49744,7 +49744,7 @@
         <v>7</v>
       </c>
       <c r="C2888">
-        <v>3960</v>
+        <v>4197.1</v>
       </c>
       <c r="D2888" t="s">
         <v>2890</v>
@@ -49758,7 +49758,7 @@
         <v>8</v>
       </c>
       <c r="C2889">
-        <v>3948.7</v>
+        <v>4227.5</v>
       </c>
       <c r="D2889" t="s">
         <v>2891</v>
@@ -49772,7 +49772,7 @@
         <v>9</v>
       </c>
       <c r="C2890">
-        <v>3776.5</v>
+        <v>4084.8</v>
       </c>
       <c r="D2890" t="s">
         <v>2892</v>
@@ -49786,7 +49786,7 @@
         <v>10</v>
       </c>
       <c r="C2891">
-        <v>3758.3</v>
+        <v>4102.4</v>
       </c>
       <c r="D2891" t="s">
         <v>2893</v>
@@ -49800,7 +49800,7 @@
         <v>11</v>
       </c>
       <c r="C2892">
-        <v>3764.6</v>
+        <v>4136.4</v>
       </c>
       <c r="D2892" t="s">
         <v>2894</v>
@@ -49814,7 +49814,7 @@
         <v>12</v>
       </c>
       <c r="C2893">
-        <v>3741.8</v>
+        <v>4164.6</v>
       </c>
       <c r="D2893" t="s">
         <v>2895</v>
@@ -49828,7 +49828,7 @@
         <v>13</v>
       </c>
       <c r="C2894">
-        <v>3748.6</v>
+        <v>4192.8</v>
       </c>
       <c r="D2894" t="s">
         <v>2896</v>
@@ -49842,7 +49842,7 @@
         <v>14</v>
       </c>
       <c r="C2895">
-        <v>3724.2</v>
+        <v>4194.9</v>
       </c>
       <c r="D2895" t="s">
         <v>2897</v>
@@ -49856,7 +49856,7 @@
         <v>15</v>
       </c>
       <c r="C2896">
-        <v>3689.6</v>
+        <v>4180.5</v>
       </c>
       <c r="D2896" t="s">
         <v>2898</v>
@@ -49870,7 +49870,7 @@
         <v>16</v>
       </c>
       <c r="C2897">
-        <v>3665.6</v>
+        <v>4192.2</v>
       </c>
       <c r="D2897" t="s">
         <v>2899</v>
@@ -49884,7 +49884,7 @@
         <v>17</v>
       </c>
       <c r="C2898">
-        <v>3599.6</v>
+        <v>4103.7</v>
       </c>
       <c r="D2898" t="s">
         <v>2900</v>
@@ -49898,7 +49898,7 @@
         <v>18</v>
       </c>
       <c r="C2899">
-        <v>3566.8</v>
+        <v>4103.8</v>
       </c>
       <c r="D2899" t="s">
         <v>2901</v>
@@ -49912,7 +49912,7 @@
         <v>19</v>
       </c>
       <c r="C2900">
-        <v>3563.7</v>
+        <v>4081.8</v>
       </c>
       <c r="D2900" t="s">
         <v>2902</v>
@@ -49926,7 +49926,7 @@
         <v>20</v>
       </c>
       <c r="C2901">
-        <v>3500.4</v>
+        <v>4069.5</v>
       </c>
       <c r="D2901" t="s">
         <v>2903</v>
@@ -49940,7 +49940,7 @@
         <v>21</v>
       </c>
       <c r="C2902">
-        <v>3526.1</v>
+        <v>4101</v>
       </c>
       <c r="D2902" t="s">
         <v>2904</v>
@@ -49954,7 +49954,7 @@
         <v>22</v>
       </c>
       <c r="C2903">
-        <v>3461.2</v>
+        <v>4079.5</v>
       </c>
       <c r="D2903" t="s">
         <v>2905</v>
@@ -49968,7 +49968,7 @@
         <v>23</v>
       </c>
       <c r="C2904">
-        <v>3409.8</v>
+        <v>4059</v>
       </c>
       <c r="D2904" t="s">
         <v>2906</v>
@@ -49982,7 +49982,7 @@
         <v>24</v>
       </c>
       <c r="C2905">
-        <v>3347.3</v>
+        <v>4019.7</v>
       </c>
       <c r="D2905" t="s">
         <v>2907</v>
@@ -49996,7 +49996,7 @@
         <v>25</v>
       </c>
       <c r="C2906">
-        <v>3443.3</v>
+        <v>4181.7</v>
       </c>
       <c r="D2906" t="s">
         <v>2908</v>
@@ -50010,7 +50010,7 @@
         <v>26</v>
       </c>
       <c r="C2907">
-        <v>3359.5</v>
+        <v>4093.8</v>
       </c>
       <c r="D2907" t="s">
         <v>2909</v>
@@ -50024,7 +50024,7 @@
         <v>27</v>
       </c>
       <c r="C2908">
-        <v>3257.6</v>
+        <v>4046.8</v>
       </c>
       <c r="D2908" t="s">
         <v>2910</v>
@@ -50038,7 +50038,7 @@
         <v>28</v>
       </c>
       <c r="C2909">
-        <v>3208.3</v>
+        <v>3987.1</v>
       </c>
       <c r="D2909" t="s">
         <v>2911</v>
@@ -50052,7 +50052,7 @@
         <v>29</v>
       </c>
       <c r="C2910">
-        <v>3019.8</v>
+        <v>3871.1</v>
       </c>
       <c r="D2910" t="s">
         <v>2912</v>
@@ -50066,7 +50066,7 @@
         <v>30</v>
       </c>
       <c r="C2911">
-        <v>2920.7</v>
+        <v>3827.5</v>
       </c>
       <c r="D2911" t="s">
         <v>2913</v>
@@ -50080,7 +50080,7 @@
         <v>31</v>
       </c>
       <c r="C2912">
-        <v>2899.7</v>
+        <v>3890</v>
       </c>
       <c r="D2912" t="s">
         <v>2914</v>
@@ -50094,7 +50094,7 @@
         <v>32</v>
       </c>
       <c r="C2913">
-        <v>2940.8</v>
+        <v>3907.9</v>
       </c>
       <c r="D2913" t="s">
         <v>2915</v>
@@ -50108,7 +50108,7 @@
         <v>33</v>
       </c>
       <c r="C2914">
-        <v>2798.4</v>
+        <v>3739.4</v>
       </c>
       <c r="D2914" t="s">
         <v>2916</v>
@@ -50122,7 +50122,7 @@
         <v>34</v>
       </c>
       <c r="C2915">
-        <v>2807</v>
+        <v>3813.1</v>
       </c>
       <c r="D2915" t="s">
         <v>2917</v>
@@ -50136,7 +50136,7 @@
         <v>35</v>
       </c>
       <c r="C2916">
-        <v>2900.5</v>
+        <v>3928</v>
       </c>
       <c r="D2916" t="s">
         <v>2918</v>
@@ -50150,7 +50150,7 @@
         <v>36</v>
       </c>
       <c r="C2917">
-        <v>2967.7</v>
+        <v>4033.6</v>
       </c>
       <c r="D2917" t="s">
         <v>2919</v>
@@ -50164,7 +50164,7 @@
         <v>37</v>
       </c>
       <c r="C2918">
-        <v>3169.1</v>
+        <v>3723.4</v>
       </c>
       <c r="D2918" t="s">
         <v>2920</v>
@@ -50178,7 +50178,7 @@
         <v>38</v>
       </c>
       <c r="C2919">
-        <v>3195.3</v>
+        <v>3805</v>
       </c>
       <c r="D2919" t="s">
         <v>2921</v>
@@ -50192,7 +50192,7 @@
         <v>39</v>
       </c>
       <c r="C2920">
-        <v>3260.2</v>
+        <v>3916.4</v>
       </c>
       <c r="D2920" t="s">
         <v>2922</v>
@@ -50206,7 +50206,7 @@
         <v>40</v>
       </c>
       <c r="C2921">
-        <v>3308.3</v>
+        <v>4030.7</v>
       </c>
       <c r="D2921" t="s">
         <v>2923</v>
@@ -50220,7 +50220,7 @@
         <v>41</v>
       </c>
       <c r="C2922">
-        <v>3361.6</v>
+        <v>4078.5</v>
       </c>
       <c r="D2922" t="s">
         <v>2924</v>
@@ -50234,7 +50234,7 @@
         <v>42</v>
       </c>
       <c r="C2923">
-        <v>3364.6</v>
+        <v>4140.5</v>
       </c>
       <c r="D2923" t="s">
         <v>2925</v>
@@ -50248,7 +50248,7 @@
         <v>43</v>
       </c>
       <c r="C2924">
-        <v>3401.6</v>
+        <v>4241.4</v>
       </c>
       <c r="D2924" t="s">
         <v>2926</v>
@@ -50262,7 +50262,7 @@
         <v>44</v>
       </c>
       <c r="C2925">
-        <v>3448</v>
+        <v>4300.3</v>
       </c>
       <c r="D2925" t="s">
         <v>2927</v>
@@ -50276,7 +50276,7 @@
         <v>45</v>
       </c>
       <c r="C2926">
-        <v>3438.7</v>
+        <v>3773.2</v>
       </c>
       <c r="D2926" t="s">
         <v>2928</v>
@@ -50290,7 +50290,7 @@
         <v>46</v>
       </c>
       <c r="C2927">
-        <v>3475.5</v>
+        <v>3770.9</v>
       </c>
       <c r="D2927" t="s">
         <v>2929</v>
@@ -50304,7 +50304,7 @@
         <v>47</v>
       </c>
       <c r="C2928">
-        <v>3492.7</v>
+        <v>3597.5</v>
       </c>
       <c r="D2928" t="s">
         <v>2930</v>
@@ -50318,7 +50318,7 @@
         <v>48</v>
       </c>
       <c r="C2929">
-        <v>3534.2</v>
+        <v>3641</v>
       </c>
       <c r="D2929" t="s">
         <v>2931</v>
@@ -50332,7 +50332,7 @@
         <v>49</v>
       </c>
       <c r="C2930">
-        <v>3366.8</v>
+        <v>3499.7</v>
       </c>
       <c r="D2930" t="s">
         <v>2932</v>
@@ -50346,7 +50346,7 @@
         <v>50</v>
       </c>
       <c r="C2931">
-        <v>3380.2</v>
+        <v>3410.2</v>
       </c>
       <c r="D2931" t="s">
         <v>2933</v>
@@ -50360,7 +50360,7 @@
         <v>51</v>
       </c>
       <c r="C2932">
-        <v>3366.2</v>
+        <v>3452.6</v>
       </c>
       <c r="D2932" t="s">
         <v>2934</v>
@@ -50374,7 +50374,7 @@
         <v>52</v>
       </c>
       <c r="C2933">
-        <v>3367.7</v>
+        <v>3471.8</v>
       </c>
       <c r="D2933" t="s">
         <v>2935</v>
@@ -50388,7 +50388,7 @@
         <v>53</v>
       </c>
       <c r="C2934">
-        <v>3355.7</v>
+        <v>3409.4</v>
       </c>
       <c r="D2934" t="s">
         <v>2936</v>
@@ -50402,7 +50402,7 @@
         <v>54</v>
       </c>
       <c r="C2935">
-        <v>3329.5</v>
+        <v>3389.6</v>
       </c>
       <c r="D2935" t="s">
         <v>2937</v>
@@ -50416,7 +50416,7 @@
         <v>55</v>
       </c>
       <c r="C2936">
-        <v>3327.9</v>
+        <v>3398</v>
       </c>
       <c r="D2936" t="s">
         <v>2938</v>
@@ -50430,7 +50430,7 @@
         <v>56</v>
       </c>
       <c r="C2937">
-        <v>3330.4</v>
+        <v>3374.6</v>
       </c>
       <c r="D2937" t="s">
         <v>2939</v>
@@ -50444,7 +50444,7 @@
         <v>57</v>
       </c>
       <c r="C2938">
-        <v>3333.2</v>
+        <v>3543</v>
       </c>
       <c r="D2938" t="s">
         <v>2940</v>
@@ -50458,7 +50458,7 @@
         <v>58</v>
       </c>
       <c r="C2939">
-        <v>3339.6</v>
+        <v>3548</v>
       </c>
       <c r="D2939" t="s">
         <v>2941</v>
@@ -50472,7 +50472,7 @@
         <v>59</v>
       </c>
       <c r="C2940">
-        <v>3356</v>
+        <v>3621.1</v>
       </c>
       <c r="D2940" t="s">
         <v>2942</v>
@@ -50486,7 +50486,7 @@
         <v>60</v>
       </c>
       <c r="C2941">
-        <v>3370.7</v>
+        <v>3665.8</v>
       </c>
       <c r="D2941" t="s">
         <v>2943</v>
@@ -50500,7 +50500,7 @@
         <v>61</v>
       </c>
       <c r="C2942">
-        <v>3359.6</v>
+        <v>3507.8</v>
       </c>
       <c r="D2942" t="s">
         <v>2944</v>
@@ -50514,7 +50514,7 @@
         <v>62</v>
       </c>
       <c r="C2943">
-        <v>3332.4</v>
+        <v>3613.1</v>
       </c>
       <c r="D2943" t="s">
         <v>2945</v>
@@ -50528,7 +50528,7 @@
         <v>63</v>
       </c>
       <c r="C2944">
-        <v>3338</v>
+        <v>3580.8</v>
       </c>
       <c r="D2944" t="s">
         <v>2946</v>
@@ -50542,7 +50542,7 @@
         <v>64</v>
       </c>
       <c r="C2945">
-        <v>3326.6</v>
+        <v>3453.2</v>
       </c>
       <c r="D2945" t="s">
         <v>2947</v>
@@ -50556,7 +50556,7 @@
         <v>65</v>
       </c>
       <c r="C2946">
-        <v>3443.9</v>
+        <v>3381.1</v>
       </c>
       <c r="D2946" t="s">
         <v>2948</v>
@@ -50570,7 +50570,7 @@
         <v>66</v>
       </c>
       <c r="C2947">
-        <v>3409.2</v>
+        <v>3336.7</v>
       </c>
       <c r="D2947" t="s">
         <v>2949</v>
@@ -50584,7 +50584,7 @@
         <v>67</v>
       </c>
       <c r="C2948">
-        <v>3378.7</v>
+        <v>3275.4</v>
       </c>
       <c r="D2948" t="s">
         <v>2950</v>
@@ -50598,7 +50598,7 @@
         <v>68</v>
       </c>
       <c r="C2949">
-        <v>3370.8</v>
+        <v>3262.3</v>
       </c>
       <c r="D2949" t="s">
         <v>2951</v>
@@ -50612,7 +50612,7 @@
         <v>69</v>
       </c>
       <c r="C2950">
-        <v>3324.8</v>
+        <v>3456.1</v>
       </c>
       <c r="D2950" t="s">
         <v>2952</v>
@@ -50626,7 +50626,7 @@
         <v>70</v>
       </c>
       <c r="C2951">
-        <v>3267</v>
+        <v>3487.4</v>
       </c>
       <c r="D2951" t="s">
         <v>2953</v>
@@ -50640,7 +50640,7 @@
         <v>71</v>
       </c>
       <c r="C2952">
-        <v>3140.8</v>
+        <v>3367.5</v>
       </c>
       <c r="D2952" t="s">
         <v>2954</v>
@@ -50654,7 +50654,7 @@
         <v>72</v>
       </c>
       <c r="C2953">
-        <v>3132.2</v>
+        <v>3214</v>
       </c>
       <c r="D2953" t="s">
         <v>2955</v>
@@ -50668,7 +50668,7 @@
         <v>73</v>
       </c>
       <c r="C2954">
-        <v>3263.8</v>
+        <v>3861.4</v>
       </c>
       <c r="D2954" t="s">
         <v>2956</v>
@@ -50682,7 +50682,7 @@
         <v>74</v>
       </c>
       <c r="C2955">
-        <v>3190.4</v>
+        <v>3709.4</v>
       </c>
       <c r="D2955" t="s">
         <v>2957</v>
@@ -50696,7 +50696,7 @@
         <v>75</v>
       </c>
       <c r="C2956">
-        <v>3129.7</v>
+        <v>3559.2</v>
       </c>
       <c r="D2956" t="s">
         <v>2958</v>
@@ -50710,7 +50710,7 @@
         <v>76</v>
       </c>
       <c r="C2957">
-        <v>3081.8</v>
+        <v>3462.4</v>
       </c>
       <c r="D2957" t="s">
         <v>2959</v>
@@ -50724,7 +50724,7 @@
         <v>77</v>
       </c>
       <c r="C2958">
-        <v>3353.1</v>
+        <v>3738</v>
       </c>
       <c r="D2958" t="s">
         <v>2960</v>
@@ -50738,7 +50738,7 @@
         <v>78</v>
       </c>
       <c r="C2959">
-        <v>3374.6</v>
+        <v>3701.8</v>
       </c>
       <c r="D2959" t="s">
         <v>2961</v>
@@ -50752,7 +50752,7 @@
         <v>79</v>
       </c>
       <c r="C2960">
-        <v>3372.6</v>
+        <v>3619.2</v>
       </c>
       <c r="D2960" t="s">
         <v>2962</v>
@@ -50766,7 +50766,7 @@
         <v>80</v>
       </c>
       <c r="C2961">
-        <v>3434.5</v>
+        <v>3592.7</v>
       </c>
       <c r="D2961" t="s">
         <v>2963</v>
@@ -50780,7 +50780,7 @@
         <v>81</v>
       </c>
       <c r="C2962">
-        <v>3768.8</v>
+        <v>4120.6</v>
       </c>
       <c r="D2962" t="s">
         <v>2964</v>
@@ -50794,7 +50794,7 @@
         <v>82</v>
       </c>
       <c r="C2963">
-        <v>3854.2</v>
+        <v>4168.1</v>
       </c>
       <c r="D2963" t="s">
         <v>2965</v>
@@ -50808,7 +50808,7 @@
         <v>83</v>
       </c>
       <c r="C2964">
-        <v>3965.7</v>
+        <v>4265.5</v>
       </c>
       <c r="D2964" t="s">
         <v>2966</v>
@@ -50822,7 +50822,7 @@
         <v>84</v>
       </c>
       <c r="C2965">
-        <v>4032.2</v>
+        <v>4429.8</v>
       </c>
       <c r="D2965" t="s">
         <v>2967</v>
@@ -50836,7 +50836,7 @@
         <v>85</v>
       </c>
       <c r="C2966">
-        <v>4235.1</v>
+        <v>4518.5</v>
       </c>
       <c r="D2966" t="s">
         <v>2968</v>
@@ -50850,7 +50850,7 @@
         <v>86</v>
       </c>
       <c r="C2967">
-        <v>4251</v>
+        <v>4579.6</v>
       </c>
       <c r="D2967" t="s">
         <v>2969</v>
@@ -50864,7 +50864,7 @@
         <v>87</v>
       </c>
       <c r="C2968">
-        <v>4310.1</v>
+        <v>4676</v>
       </c>
       <c r="D2968" t="s">
         <v>2970</v>
@@ -50878,7 +50878,7 @@
         <v>88</v>
       </c>
       <c r="C2969">
-        <v>4335.8</v>
+        <v>4744.5</v>
       </c>
       <c r="D2969" t="s">
         <v>2971</v>
@@ -50892,7 +50892,7 @@
         <v>89</v>
       </c>
       <c r="C2970">
-        <v>4165</v>
+        <v>4707.6</v>
       </c>
       <c r="D2970" t="s">
         <v>2972</v>
@@ -50906,7 +50906,7 @@
         <v>90</v>
       </c>
       <c r="C2971">
-        <v>4240.7</v>
+        <v>4701.2</v>
       </c>
       <c r="D2971" t="s">
         <v>2973</v>
@@ -50920,7 +50920,7 @@
         <v>91</v>
       </c>
       <c r="C2972">
-        <v>4229.6</v>
+        <v>4713.4</v>
       </c>
       <c r="D2972" t="s">
         <v>2974</v>
@@ -50934,7 +50934,7 @@
         <v>92</v>
       </c>
       <c r="C2973">
-        <v>4257.1</v>
+        <v>4736.7</v>
       </c>
       <c r="D2973" t="s">
         <v>2975</v>
@@ -50948,7 +50948,7 @@
         <v>93</v>
       </c>
       <c r="C2974">
-        <v>3808.2</v>
+        <v>4475.9</v>
       </c>
       <c r="D2974" t="s">
         <v>2976</v>
@@ -50962,7 +50962,7 @@
         <v>94</v>
       </c>
       <c r="C2975">
-        <v>3871.6</v>
+        <v>4476.8</v>
       </c>
       <c r="D2975" t="s">
         <v>2977</v>
@@ -50976,7 +50976,7 @@
         <v>95</v>
       </c>
       <c r="C2976">
-        <v>3896.9</v>
+        <v>4430.4</v>
       </c>
       <c r="D2976" t="s">
         <v>2978</v>
@@ -50990,7 +50990,7 @@
         <v>96</v>
       </c>
       <c r="C2977">
-        <v>3905.7</v>
+        <v>4417.3</v>
       </c>
       <c r="D2977" t="s">
         <v>2979</v>

--- a/Market Fundamentals/Transelectrica_data/Cons_Prod_final/Weekly_Production_2026.xlsx
+++ b/Market Fundamentals/Transelectrica_data/Cons_Prod_final/Weekly_Production_2026.xlsx
@@ -7324,7 +7324,7 @@
         <v>1</v>
       </c>
       <c r="C290">
-        <v>4496.2</v>
+        <v>4815.8</v>
       </c>
       <c r="D290" t="s">
         <v>292</v>
@@ -7338,7 +7338,7 @@
         <v>2</v>
       </c>
       <c r="C291">
-        <v>4502.9</v>
+        <v>4815.9</v>
       </c>
       <c r="D291" t="s">
         <v>293</v>
@@ -7352,7 +7352,7 @@
         <v>3</v>
       </c>
       <c r="C292">
-        <v>4474</v>
+        <v>4801.9</v>
       </c>
       <c r="D292" t="s">
         <v>294</v>
@@ -7366,7 +7366,7 @@
         <v>4</v>
       </c>
       <c r="C293">
-        <v>4422.7</v>
+        <v>4774.2</v>
       </c>
       <c r="D293" t="s">
         <v>295</v>
@@ -7380,7 +7380,7 @@
         <v>5</v>
       </c>
       <c r="C294">
-        <v>4494</v>
+        <v>4430.1</v>
       </c>
       <c r="D294" t="s">
         <v>296</v>
@@ -7394,7 +7394,7 @@
         <v>6</v>
       </c>
       <c r="C295">
-        <v>4452.2</v>
+        <v>4388.1</v>
       </c>
       <c r="D295" t="s">
         <v>297</v>
@@ -7408,7 +7408,7 @@
         <v>7</v>
       </c>
       <c r="C296">
-        <v>4396.5</v>
+        <v>4364.9</v>
       </c>
       <c r="D296" t="s">
         <v>298</v>
@@ -7422,7 +7422,7 @@
         <v>8</v>
       </c>
       <c r="C297">
-        <v>4383</v>
+        <v>4351.2</v>
       </c>
       <c r="D297" t="s">
         <v>299</v>
@@ -7436,7 +7436,7 @@
         <v>9</v>
       </c>
       <c r="C298">
-        <v>4326.3</v>
+        <v>4437.3</v>
       </c>
       <c r="D298" t="s">
         <v>300</v>
@@ -7450,7 +7450,7 @@
         <v>10</v>
       </c>
       <c r="C299">
-        <v>4300.3</v>
+        <v>4435.9</v>
       </c>
       <c r="D299" t="s">
         <v>301</v>
@@ -7464,7 +7464,7 @@
         <v>11</v>
       </c>
       <c r="C300">
-        <v>4259.9</v>
+        <v>4441.3</v>
       </c>
       <c r="D300" t="s">
         <v>302</v>
@@ -7478,7 +7478,7 @@
         <v>12</v>
       </c>
       <c r="C301">
-        <v>4241</v>
+        <v>4459.9</v>
       </c>
       <c r="D301" t="s">
         <v>303</v>
@@ -7492,7 +7492,7 @@
         <v>13</v>
       </c>
       <c r="C302">
-        <v>4108.6</v>
+        <v>4286.2</v>
       </c>
       <c r="D302" t="s">
         <v>304</v>
@@ -7506,7 +7506,7 @@
         <v>14</v>
       </c>
       <c r="C303">
-        <v>4099.2</v>
+        <v>4284.2</v>
       </c>
       <c r="D303" t="s">
         <v>305</v>
@@ -7520,7 +7520,7 @@
         <v>15</v>
       </c>
       <c r="C304">
-        <v>4070.3</v>
+        <v>4280.1</v>
       </c>
       <c r="D304" t="s">
         <v>306</v>
@@ -7534,7 +7534,7 @@
         <v>16</v>
       </c>
       <c r="C305">
-        <v>4062.4</v>
+        <v>4282</v>
       </c>
       <c r="D305" t="s">
         <v>307</v>
@@ -7548,7 +7548,7 @@
         <v>17</v>
       </c>
       <c r="C306">
-        <v>3974.5</v>
+        <v>4197.8</v>
       </c>
       <c r="D306" t="s">
         <v>308</v>
@@ -7562,7 +7562,7 @@
         <v>18</v>
       </c>
       <c r="C307">
-        <v>3968.4</v>
+        <v>4189.3</v>
       </c>
       <c r="D307" t="s">
         <v>309</v>
@@ -7576,7 +7576,7 @@
         <v>19</v>
       </c>
       <c r="C308">
-        <v>3953.7</v>
+        <v>4184.6</v>
       </c>
       <c r="D308" t="s">
         <v>310</v>
@@ -7590,7 +7590,7 @@
         <v>20</v>
       </c>
       <c r="C309">
-        <v>3946.4</v>
+        <v>4154.8</v>
       </c>
       <c r="D309" t="s">
         <v>311</v>
@@ -7604,7 +7604,7 @@
         <v>21</v>
       </c>
       <c r="C310">
-        <v>4012.3</v>
+        <v>4150.4</v>
       </c>
       <c r="D310" t="s">
         <v>312</v>
@@ -7618,7 +7618,7 @@
         <v>22</v>
       </c>
       <c r="C311">
-        <v>4064.8</v>
+        <v>4196.5</v>
       </c>
       <c r="D311" t="s">
         <v>313</v>
@@ -7632,7 +7632,7 @@
         <v>23</v>
       </c>
       <c r="C312">
-        <v>4123.6</v>
+        <v>4204.1</v>
       </c>
       <c r="D312" t="s">
         <v>314</v>
@@ -7646,7 +7646,7 @@
         <v>24</v>
       </c>
       <c r="C313">
-        <v>4177.5</v>
+        <v>4216.4</v>
       </c>
       <c r="D313" t="s">
         <v>315</v>
@@ -7660,7 +7660,7 @@
         <v>25</v>
       </c>
       <c r="C314">
-        <v>4458.4</v>
+        <v>4527.1</v>
       </c>
       <c r="D314" t="s">
         <v>316</v>
@@ -7674,7 +7674,7 @@
         <v>26</v>
       </c>
       <c r="C315">
-        <v>4537.7</v>
+        <v>4540.6</v>
       </c>
       <c r="D315" t="s">
         <v>317</v>
@@ -7688,7 +7688,7 @@
         <v>27</v>
       </c>
       <c r="C316">
-        <v>4612.1</v>
+        <v>4571.3</v>
       </c>
       <c r="D316" t="s">
         <v>318</v>
@@ -7702,7 +7702,7 @@
         <v>28</v>
       </c>
       <c r="C317">
-        <v>4722</v>
+        <v>4633.1</v>
       </c>
       <c r="D317" t="s">
         <v>319</v>
@@ -7716,7 +7716,7 @@
         <v>29</v>
       </c>
       <c r="C318">
-        <v>4758.3</v>
+        <v>4777.7</v>
       </c>
       <c r="D318" t="s">
         <v>320</v>
@@ -7730,7 +7730,7 @@
         <v>30</v>
       </c>
       <c r="C319">
-        <v>4888.7</v>
+        <v>4872.6</v>
       </c>
       <c r="D319" t="s">
         <v>321</v>
@@ -7744,7 +7744,7 @@
         <v>31</v>
       </c>
       <c r="C320">
-        <v>5057.2</v>
+        <v>4998</v>
       </c>
       <c r="D320" t="s">
         <v>322</v>
@@ -7758,7 +7758,7 @@
         <v>32</v>
       </c>
       <c r="C321">
-        <v>5211.3</v>
+        <v>5074.1</v>
       </c>
       <c r="D321" t="s">
         <v>323</v>
@@ -7772,7 +7772,7 @@
         <v>33</v>
       </c>
       <c r="C322">
-        <v>5154.9</v>
+        <v>4953.3</v>
       </c>
       <c r="D322" t="s">
         <v>324</v>
@@ -7786,7 +7786,7 @@
         <v>34</v>
       </c>
       <c r="C323">
-        <v>5311.5</v>
+        <v>5047</v>
       </c>
       <c r="D323" t="s">
         <v>325</v>
@@ -7800,7 +7800,7 @@
         <v>35</v>
       </c>
       <c r="C324">
-        <v>5452.5</v>
+        <v>5135</v>
       </c>
       <c r="D324" t="s">
         <v>326</v>
@@ -7814,7 +7814,7 @@
         <v>36</v>
       </c>
       <c r="C325">
-        <v>5582.6</v>
+        <v>5165.4</v>
       </c>
       <c r="D325" t="s">
         <v>327</v>
@@ -7828,7 +7828,7 @@
         <v>37</v>
       </c>
       <c r="C326">
-        <v>5718.8</v>
+        <v>5078.5</v>
       </c>
       <c r="D326" t="s">
         <v>328</v>
@@ -7842,7 +7842,7 @@
         <v>38</v>
       </c>
       <c r="C327">
-        <v>5810.2</v>
+        <v>5086.9</v>
       </c>
       <c r="D327" t="s">
         <v>329</v>
@@ -7856,7 +7856,7 @@
         <v>39</v>
       </c>
       <c r="C328">
-        <v>5835.9</v>
+        <v>5093.3</v>
       </c>
       <c r="D328" t="s">
         <v>330</v>
@@ -7870,7 +7870,7 @@
         <v>40</v>
       </c>
       <c r="C329">
-        <v>5917.9</v>
+        <v>5094.3</v>
       </c>
       <c r="D329" t="s">
         <v>331</v>
@@ -7884,7 +7884,7 @@
         <v>41</v>
       </c>
       <c r="C330">
-        <v>6166.9</v>
+        <v>4854.1</v>
       </c>
       <c r="D330" t="s">
         <v>332</v>
@@ -7898,7 +7898,7 @@
         <v>42</v>
       </c>
       <c r="C331">
-        <v>6245.2</v>
+        <v>4908.1</v>
       </c>
       <c r="D331" t="s">
         <v>333</v>
@@ -7912,7 +7912,7 @@
         <v>43</v>
       </c>
       <c r="C332">
-        <v>6313.7</v>
+        <v>4924.7</v>
       </c>
       <c r="D332" t="s">
         <v>334</v>
@@ -7926,7 +7926,7 @@
         <v>44</v>
       </c>
       <c r="C333">
-        <v>6382.4</v>
+        <v>4983.8</v>
       </c>
       <c r="D333" t="s">
         <v>335</v>
@@ -7940,7 +7940,7 @@
         <v>45</v>
       </c>
       <c r="C334">
-        <v>6359.5</v>
+        <v>4870.3</v>
       </c>
       <c r="D334" t="s">
         <v>336</v>
@@ -7954,7 +7954,7 @@
         <v>46</v>
       </c>
       <c r="C335">
-        <v>6416.5</v>
+        <v>4911.2</v>
       </c>
       <c r="D335" t="s">
         <v>337</v>
@@ -7968,7 +7968,7 @@
         <v>47</v>
       </c>
       <c r="C336">
-        <v>6439.6</v>
+        <v>4994.7</v>
       </c>
       <c r="D336" t="s">
         <v>338</v>
@@ -7982,7 +7982,7 @@
         <v>48</v>
       </c>
       <c r="C337">
-        <v>6474.2</v>
+        <v>5020.5</v>
       </c>
       <c r="D337" t="s">
         <v>339</v>
@@ -7996,7 +7996,7 @@
         <v>49</v>
       </c>
       <c r="C338">
-        <v>6173.4</v>
+        <v>4906.1</v>
       </c>
       <c r="D338" t="s">
         <v>340</v>
@@ -8010,7 +8010,7 @@
         <v>50</v>
       </c>
       <c r="C339">
-        <v>6227.1</v>
+        <v>4955.4</v>
       </c>
       <c r="D339" t="s">
         <v>341</v>
@@ -8024,7 +8024,7 @@
         <v>51</v>
       </c>
       <c r="C340">
-        <v>6263</v>
+        <v>4980.8</v>
       </c>
       <c r="D340" t="s">
         <v>342</v>
@@ -8038,7 +8038,7 @@
         <v>52</v>
       </c>
       <c r="C341">
-        <v>6276.4</v>
+        <v>4998.9</v>
       </c>
       <c r="D341" t="s">
         <v>343</v>
@@ -8052,7 +8052,7 @@
         <v>53</v>
       </c>
       <c r="C342">
-        <v>6417</v>
+        <v>4973.7</v>
       </c>
       <c r="D342" t="s">
         <v>344</v>
@@ -8066,7 +8066,7 @@
         <v>54</v>
       </c>
       <c r="C343">
-        <v>6431.3</v>
+        <v>4995</v>
       </c>
       <c r="D343" t="s">
         <v>345</v>
@@ -8080,7 +8080,7 @@
         <v>55</v>
       </c>
       <c r="C344">
-        <v>6436.4</v>
+        <v>5038</v>
       </c>
       <c r="D344" t="s">
         <v>346</v>
@@ -8094,7 +8094,7 @@
         <v>56</v>
       </c>
       <c r="C345">
-        <v>6450.9</v>
+        <v>5071.1</v>
       </c>
       <c r="D345" t="s">
         <v>347</v>
@@ -8108,7 +8108,7 @@
         <v>57</v>
       </c>
       <c r="C346">
-        <v>6436.1</v>
+        <v>4982.8</v>
       </c>
       <c r="D346" t="s">
         <v>348</v>
@@ -8122,7 +8122,7 @@
         <v>58</v>
       </c>
       <c r="C347">
-        <v>6479.3</v>
+        <v>5004.3</v>
       </c>
       <c r="D347" t="s">
         <v>349</v>
@@ -8136,7 +8136,7 @@
         <v>59</v>
       </c>
       <c r="C348">
-        <v>6473.6</v>
+        <v>5010.9</v>
       </c>
       <c r="D348" t="s">
         <v>350</v>
@@ -8150,7 +8150,7 @@
         <v>60</v>
       </c>
       <c r="C349">
-        <v>6420.5</v>
+        <v>5041.5</v>
       </c>
       <c r="D349" t="s">
         <v>351</v>
@@ -8164,7 +8164,7 @@
         <v>61</v>
       </c>
       <c r="C350">
-        <v>6282.7</v>
+        <v>5042.3</v>
       </c>
       <c r="D350" t="s">
         <v>352</v>
@@ -8178,7 +8178,7 @@
         <v>62</v>
       </c>
       <c r="C351">
-        <v>6233.1</v>
+        <v>4989.3</v>
       </c>
       <c r="D351" t="s">
         <v>353</v>
@@ -8192,7 +8192,7 @@
         <v>63</v>
       </c>
       <c r="C352">
-        <v>6197.5</v>
+        <v>4966.9</v>
       </c>
       <c r="D352" t="s">
         <v>354</v>
@@ -8206,7 +8206,7 @@
         <v>64</v>
       </c>
       <c r="C353">
-        <v>6102.5</v>
+        <v>4969.2</v>
       </c>
       <c r="D353" t="s">
         <v>355</v>
@@ -8220,7 +8220,7 @@
         <v>65</v>
       </c>
       <c r="C354">
-        <v>6073.3</v>
+        <v>4816.2</v>
       </c>
       <c r="D354" t="s">
         <v>356</v>
@@ -8234,7 +8234,7 @@
         <v>66</v>
       </c>
       <c r="C355">
-        <v>5976.7</v>
+        <v>4750</v>
       </c>
       <c r="D355" t="s">
         <v>357</v>
@@ -8248,7 +8248,7 @@
         <v>67</v>
       </c>
       <c r="C356">
-        <v>5886.3</v>
+        <v>4756.6</v>
       </c>
       <c r="D356" t="s">
         <v>358</v>
@@ -8262,7 +8262,7 @@
         <v>68</v>
       </c>
       <c r="C357">
-        <v>5842.2</v>
+        <v>4775.1</v>
       </c>
       <c r="D357" t="s">
         <v>359</v>
@@ -8276,7 +8276,7 @@
         <v>69</v>
       </c>
       <c r="C358">
-        <v>5966.2</v>
+        <v>4908.3</v>
       </c>
       <c r="D358" t="s">
         <v>360</v>
@@ -8290,7 +8290,7 @@
         <v>70</v>
       </c>
       <c r="C359">
-        <v>5819.4</v>
+        <v>4834.8</v>
       </c>
       <c r="D359" t="s">
         <v>361</v>
@@ -8304,7 +8304,7 @@
         <v>71</v>
       </c>
       <c r="C360">
-        <v>5783.7</v>
+        <v>4787.6</v>
       </c>
       <c r="D360" t="s">
         <v>362</v>
@@ -8318,7 +8318,7 @@
         <v>72</v>
       </c>
       <c r="C361">
-        <v>5713.2</v>
+        <v>4769</v>
       </c>
       <c r="D361" t="s">
         <v>363</v>
@@ -8332,7 +8332,7 @@
         <v>73</v>
       </c>
       <c r="C362">
-        <v>5663.9</v>
+        <v>5279.3</v>
       </c>
       <c r="D362" t="s">
         <v>364</v>
@@ -8346,7 +8346,7 @@
         <v>74</v>
       </c>
       <c r="C363">
-        <v>5556</v>
+        <v>5152.7</v>
       </c>
       <c r="D363" t="s">
         <v>365</v>
@@ -8360,7 +8360,7 @@
         <v>75</v>
       </c>
       <c r="C364">
-        <v>5468.9</v>
+        <v>5123.2</v>
       </c>
       <c r="D364" t="s">
         <v>366</v>
@@ -8374,7 +8374,7 @@
         <v>76</v>
       </c>
       <c r="C365">
-        <v>5417.6</v>
+        <v>5087.5</v>
       </c>
       <c r="D365" t="s">
         <v>367</v>
@@ -8388,7 +8388,7 @@
         <v>77</v>
       </c>
       <c r="C366">
-        <v>5696.9</v>
+        <v>5752.2</v>
       </c>
       <c r="D366" t="s">
         <v>368</v>
@@ -8402,7 +8402,7 @@
         <v>78</v>
       </c>
       <c r="C367">
-        <v>5682</v>
+        <v>5724.5</v>
       </c>
       <c r="D367" t="s">
         <v>369</v>
@@ -8416,7 +8416,7 @@
         <v>79</v>
       </c>
       <c r="C368">
-        <v>5629</v>
+        <v>5658.6</v>
       </c>
       <c r="D368" t="s">
         <v>370</v>
@@ -8430,7 +8430,7 @@
         <v>80</v>
       </c>
       <c r="C369">
-        <v>5595.6</v>
+        <v>5603</v>
       </c>
       <c r="D369" t="s">
         <v>371</v>
@@ -8444,7 +8444,7 @@
         <v>81</v>
       </c>
       <c r="C370">
-        <v>5604.4</v>
+        <v>5758</v>
       </c>
       <c r="D370" t="s">
         <v>372</v>
@@ -8458,7 +8458,7 @@
         <v>82</v>
       </c>
       <c r="C371">
-        <v>5581</v>
+        <v>5751</v>
       </c>
       <c r="D371" t="s">
         <v>373</v>
@@ -8472,7 +8472,7 @@
         <v>83</v>
       </c>
       <c r="C372">
-        <v>5556.5</v>
+        <v>5727.8</v>
       </c>
       <c r="D372" t="s">
         <v>374</v>
@@ -8486,7 +8486,7 @@
         <v>84</v>
       </c>
       <c r="C373">
-        <v>5583.2</v>
+        <v>5744.3</v>
       </c>
       <c r="D373" t="s">
         <v>375</v>
@@ -8500,7 +8500,7 @@
         <v>85</v>
       </c>
       <c r="C374">
-        <v>5651.5</v>
+        <v>5843.7</v>
       </c>
       <c r="D374" t="s">
         <v>376</v>
@@ -8514,7 +8514,7 @@
         <v>86</v>
       </c>
       <c r="C375">
-        <v>5602.7</v>
+        <v>5837.5</v>
       </c>
       <c r="D375" t="s">
         <v>377</v>
@@ -8528,7 +8528,7 @@
         <v>87</v>
       </c>
       <c r="C376">
-        <v>5562.1</v>
+        <v>5810.4</v>
       </c>
       <c r="D376" t="s">
         <v>378</v>
@@ -8542,7 +8542,7 @@
         <v>88</v>
       </c>
       <c r="C377">
-        <v>5505.2</v>
+        <v>5769.6</v>
       </c>
       <c r="D377" t="s">
         <v>379</v>
@@ -8556,7 +8556,7 @@
         <v>89</v>
       </c>
       <c r="C378">
-        <v>5311.9</v>
+        <v>5643.1</v>
       </c>
       <c r="D378" t="s">
         <v>380</v>
@@ -8570,7 +8570,7 @@
         <v>90</v>
       </c>
       <c r="C379">
-        <v>5305.5</v>
+        <v>5567.1</v>
       </c>
       <c r="D379" t="s">
         <v>381</v>
@@ -8584,7 +8584,7 @@
         <v>91</v>
       </c>
       <c r="C380">
-        <v>5317.3</v>
+        <v>5553.3</v>
       </c>
       <c r="D380" t="s">
         <v>382</v>
@@ -8598,7 +8598,7 @@
         <v>92</v>
       </c>
       <c r="C381">
-        <v>5283.4</v>
+        <v>5481.8</v>
       </c>
       <c r="D381" t="s">
         <v>383</v>
@@ -8612,7 +8612,7 @@
         <v>93</v>
       </c>
       <c r="C382">
-        <v>4846.9</v>
+        <v>4902</v>
       </c>
       <c r="D382" t="s">
         <v>384</v>
@@ -8626,7 +8626,7 @@
         <v>94</v>
       </c>
       <c r="C383">
-        <v>4803.9</v>
+        <v>4797.1</v>
       </c>
       <c r="D383" t="s">
         <v>385</v>
@@ -8640,7 +8640,7 @@
         <v>95</v>
       </c>
       <c r="C384">
-        <v>4827.9</v>
+        <v>4772.3</v>
       </c>
       <c r="D384" t="s">
         <v>386</v>
@@ -8654,7 +8654,7 @@
         <v>96</v>
       </c>
       <c r="C385">
-        <v>4815.2</v>
+        <v>4749.4</v>
       </c>
       <c r="D385" t="s">
         <v>387</v>
@@ -8668,7 +8668,7 @@
         <v>1</v>
       </c>
       <c r="C386">
-        <v>4650.6</v>
+        <v>4765.8</v>
       </c>
       <c r="D386" t="s">
         <v>388</v>
@@ -8682,7 +8682,7 @@
         <v>2</v>
       </c>
       <c r="C387">
-        <v>4689.7</v>
+        <v>4765.9</v>
       </c>
       <c r="D387" t="s">
         <v>389</v>
@@ -8696,7 +8696,7 @@
         <v>3</v>
       </c>
       <c r="C388">
-        <v>4676.3</v>
+        <v>4741.9</v>
       </c>
       <c r="D388" t="s">
         <v>390</v>
@@ -8710,7 +8710,7 @@
         <v>4</v>
       </c>
       <c r="C389">
-        <v>4689.2</v>
+        <v>4734.2</v>
       </c>
       <c r="D389" t="s">
         <v>391</v>
@@ -8724,7 +8724,7 @@
         <v>5</v>
       </c>
       <c r="C390">
-        <v>4839.3</v>
+        <v>4400.1</v>
       </c>
       <c r="D390" t="s">
         <v>392</v>
@@ -8738,7 +8738,7 @@
         <v>6</v>
       </c>
       <c r="C391">
-        <v>4858.6</v>
+        <v>4388.1</v>
       </c>
       <c r="D391" t="s">
         <v>393</v>
@@ -8752,7 +8752,7 @@
         <v>7</v>
       </c>
       <c r="C392">
-        <v>4877.1</v>
+        <v>4384.9</v>
       </c>
       <c r="D392" t="s">
         <v>394</v>
@@ -8766,7 +8766,7 @@
         <v>8</v>
       </c>
       <c r="C393">
-        <v>4907.5</v>
+        <v>4381.2</v>
       </c>
       <c r="D393" t="s">
         <v>395</v>
@@ -8780,7 +8780,7 @@
         <v>9</v>
       </c>
       <c r="C394">
-        <v>4754.8</v>
+        <v>4437.3</v>
       </c>
       <c r="D394" t="s">
         <v>396</v>
@@ -8794,7 +8794,7 @@
         <v>10</v>
       </c>
       <c r="C395">
-        <v>4762.4</v>
+        <v>4435.9</v>
       </c>
       <c r="D395" t="s">
         <v>397</v>
@@ -8808,7 +8808,7 @@
         <v>11</v>
       </c>
       <c r="C396">
-        <v>4786.4</v>
+        <v>4431.3</v>
       </c>
       <c r="D396" t="s">
         <v>398</v>
@@ -8822,7 +8822,7 @@
         <v>12</v>
       </c>
       <c r="C397">
-        <v>4814.6</v>
+        <v>4449.9</v>
       </c>
       <c r="D397" t="s">
         <v>399</v>
@@ -8836,7 +8836,7 @@
         <v>13</v>
       </c>
       <c r="C398">
-        <v>4842.8</v>
+        <v>4266.2</v>
       </c>
       <c r="D398" t="s">
         <v>400</v>
@@ -8850,7 +8850,7 @@
         <v>14</v>
       </c>
       <c r="C399">
-        <v>4854.9</v>
+        <v>4264.2</v>
       </c>
       <c r="D399" t="s">
         <v>401</v>
@@ -8864,7 +8864,7 @@
         <v>15</v>
       </c>
       <c r="C400">
-        <v>4860.5</v>
+        <v>4260.1</v>
       </c>
       <c r="D400" t="s">
         <v>402</v>
@@ -8878,7 +8878,7 @@
         <v>16</v>
       </c>
       <c r="C401">
-        <v>4872.2</v>
+        <v>4262</v>
       </c>
       <c r="D401" t="s">
         <v>403</v>
@@ -8892,7 +8892,7 @@
         <v>17</v>
       </c>
       <c r="C402">
-        <v>4823.7</v>
+        <v>4177.8</v>
       </c>
       <c r="D402" t="s">
         <v>404</v>
@@ -8906,7 +8906,7 @@
         <v>18</v>
       </c>
       <c r="C403">
-        <v>4833.8</v>
+        <v>4169.3</v>
       </c>
       <c r="D403" t="s">
         <v>405</v>
@@ -8920,7 +8920,7 @@
         <v>19</v>
       </c>
       <c r="C404">
-        <v>4851.8</v>
+        <v>4174.6</v>
       </c>
       <c r="D404" t="s">
         <v>406</v>
@@ -8934,7 +8934,7 @@
         <v>20</v>
       </c>
       <c r="C405">
-        <v>4879.5</v>
+        <v>4144.8</v>
       </c>
       <c r="D405" t="s">
         <v>407</v>
@@ -8948,7 +8948,7 @@
         <v>21</v>
       </c>
       <c r="C406">
-        <v>4971</v>
+        <v>4150.4</v>
       </c>
       <c r="D406" t="s">
         <v>408</v>
@@ -8962,7 +8962,7 @@
         <v>22</v>
       </c>
       <c r="C407">
-        <v>4999.5</v>
+        <v>4206.5</v>
       </c>
       <c r="D407" t="s">
         <v>409</v>
@@ -8976,7 +8976,7 @@
         <v>23</v>
       </c>
       <c r="C408">
-        <v>5039</v>
+        <v>4244.1</v>
       </c>
       <c r="D408" t="s">
         <v>410</v>
@@ -8990,7 +8990,7 @@
         <v>24</v>
       </c>
       <c r="C409">
-        <v>5079.7</v>
+        <v>4296.4</v>
       </c>
       <c r="D409" t="s">
         <v>411</v>
@@ -9004,7 +9004,7 @@
         <v>25</v>
       </c>
       <c r="C410">
-        <v>5321.7</v>
+        <v>4657.1</v>
       </c>
       <c r="D410" t="s">
         <v>412</v>
@@ -9018,7 +9018,7 @@
         <v>26</v>
       </c>
       <c r="C411">
-        <v>5333.8</v>
+        <v>4710.6</v>
       </c>
       <c r="D411" t="s">
         <v>413</v>
@@ -9032,7 +9032,7 @@
         <v>27</v>
       </c>
       <c r="C412">
-        <v>5396.8</v>
+        <v>4771.3</v>
       </c>
       <c r="D412" t="s">
         <v>414</v>
@@ -9046,7 +9046,7 @@
         <v>28</v>
       </c>
       <c r="C413">
-        <v>5467.1</v>
+        <v>4793.1</v>
       </c>
       <c r="D413" t="s">
         <v>415</v>
@@ -9060,7 +9060,7 @@
         <v>29</v>
       </c>
       <c r="C414">
-        <v>5511.1</v>
+        <v>4877.7</v>
       </c>
       <c r="D414" t="s">
         <v>416</v>
@@ -9074,7 +9074,7 @@
         <v>30</v>
       </c>
       <c r="C415">
-        <v>5597.5</v>
+        <v>4942.6</v>
       </c>
       <c r="D415" t="s">
         <v>417</v>
@@ -9088,7 +9088,7 @@
         <v>31</v>
       </c>
       <c r="C416">
-        <v>5750</v>
+        <v>5038</v>
       </c>
       <c r="D416" t="s">
         <v>418</v>
@@ -9102,7 +9102,7 @@
         <v>32</v>
       </c>
       <c r="C417">
-        <v>5877.9</v>
+        <v>5084.1</v>
       </c>
       <c r="D417" t="s">
         <v>419</v>
@@ -9116,7 +9116,7 @@
         <v>33</v>
       </c>
       <c r="C418">
-        <v>5779.4</v>
+        <v>4943.3</v>
       </c>
       <c r="D418" t="s">
         <v>420</v>
@@ -9130,7 +9130,7 @@
         <v>34</v>
       </c>
       <c r="C419">
-        <v>5903.1</v>
+        <v>5027</v>
       </c>
       <c r="D419" t="s">
         <v>421</v>
@@ -9144,7 +9144,7 @@
         <v>35</v>
       </c>
       <c r="C420">
-        <v>6028</v>
+        <v>5105</v>
       </c>
       <c r="D420" t="s">
         <v>422</v>
@@ -9158,7 +9158,7 @@
         <v>36</v>
       </c>
       <c r="C421">
-        <v>6123.6</v>
+        <v>5135.4</v>
       </c>
       <c r="D421" t="s">
         <v>423</v>
@@ -9172,7 +9172,7 @@
         <v>37</v>
       </c>
       <c r="C422">
-        <v>5783.4</v>
+        <v>5068.5</v>
       </c>
       <c r="D422" t="s">
         <v>424</v>
@@ -9186,7 +9186,7 @@
         <v>38</v>
       </c>
       <c r="C423">
-        <v>5845</v>
+        <v>5096.9</v>
       </c>
       <c r="D423" t="s">
         <v>425</v>
@@ -9200,7 +9200,7 @@
         <v>39</v>
       </c>
       <c r="C424">
-        <v>5946.4</v>
+        <v>5123.3</v>
       </c>
       <c r="D424" t="s">
         <v>426</v>
@@ -9214,7 +9214,7 @@
         <v>40</v>
       </c>
       <c r="C425">
-        <v>6060.7</v>
+        <v>5144.3</v>
       </c>
       <c r="D425" t="s">
         <v>427</v>
@@ -9228,7 +9228,7 @@
         <v>41</v>
       </c>
       <c r="C426">
-        <v>6128.5</v>
+        <v>4904.1</v>
       </c>
       <c r="D426" t="s">
         <v>428</v>
@@ -9242,7 +9242,7 @@
         <v>42</v>
       </c>
       <c r="C427">
-        <v>6190.5</v>
+        <v>4958.1</v>
       </c>
       <c r="D427" t="s">
         <v>429</v>
@@ -9256,7 +9256,7 @@
         <v>43</v>
       </c>
       <c r="C428">
-        <v>6271.4</v>
+        <v>4974.7</v>
       </c>
       <c r="D428" t="s">
         <v>430</v>
@@ -9270,7 +9270,7 @@
         <v>44</v>
       </c>
       <c r="C429">
-        <v>6280.3</v>
+        <v>5013.8</v>
       </c>
       <c r="D429" t="s">
         <v>431</v>
@@ -9284,7 +9284,7 @@
         <v>45</v>
       </c>
       <c r="C430">
-        <v>5693.2</v>
+        <v>4900.3</v>
       </c>
       <c r="D430" t="s">
         <v>432</v>
@@ -9298,7 +9298,7 @@
         <v>46</v>
       </c>
       <c r="C431">
-        <v>5640.9</v>
+        <v>4921.2</v>
       </c>
       <c r="D431" t="s">
         <v>433</v>
@@ -9312,7 +9312,7 @@
         <v>47</v>
       </c>
       <c r="C432">
-        <v>5447.5</v>
+        <v>4974.7</v>
       </c>
       <c r="D432" t="s">
         <v>434</v>
@@ -9326,7 +9326,7 @@
         <v>48</v>
       </c>
       <c r="C433">
-        <v>5481</v>
+        <v>4980.5</v>
       </c>
       <c r="D433" t="s">
         <v>435</v>
@@ -9340,7 +9340,7 @@
         <v>49</v>
       </c>
       <c r="C434">
-        <v>5349.7</v>
+        <v>4846.1</v>
       </c>
       <c r="D434" t="s">
         <v>436</v>
@@ -9354,7 +9354,7 @@
         <v>50</v>
       </c>
       <c r="C435">
-        <v>5280.2</v>
+        <v>4875.4</v>
       </c>
       <c r="D435" t="s">
         <v>437</v>
@@ -9368,7 +9368,7 @@
         <v>51</v>
       </c>
       <c r="C436">
-        <v>5342.6</v>
+        <v>4890.8</v>
       </c>
       <c r="D436" t="s">
         <v>438</v>
@@ -9382,7 +9382,7 @@
         <v>52</v>
       </c>
       <c r="C437">
-        <v>5381.8</v>
+        <v>4898.9</v>
       </c>
       <c r="D437" t="s">
         <v>439</v>
@@ -9396,7 +9396,7 @@
         <v>53</v>
       </c>
       <c r="C438">
-        <v>5339.4</v>
+        <v>4853.7</v>
       </c>
       <c r="D438" t="s">
         <v>440</v>
@@ -9410,7 +9410,7 @@
         <v>54</v>
       </c>
       <c r="C439">
-        <v>5319.6</v>
+        <v>4825</v>
       </c>
       <c r="D439" t="s">
         <v>441</v>
@@ -9424,7 +9424,7 @@
         <v>55</v>
       </c>
       <c r="C440">
-        <v>5328</v>
+        <v>4838</v>
       </c>
       <c r="D440" t="s">
         <v>442</v>
@@ -9438,7 +9438,7 @@
         <v>56</v>
       </c>
       <c r="C441">
-        <v>5284.6</v>
+        <v>4831.1</v>
       </c>
       <c r="D441" t="s">
         <v>443</v>
@@ -9452,7 +9452,7 @@
         <v>57</v>
       </c>
       <c r="C442">
-        <v>5413</v>
+        <v>4732.8</v>
       </c>
       <c r="D442" t="s">
         <v>444</v>
@@ -9466,7 +9466,7 @@
         <v>58</v>
       </c>
       <c r="C443">
-        <v>5408</v>
+        <v>4754.3</v>
       </c>
       <c r="D443" t="s">
         <v>445</v>
@@ -9480,7 +9480,7 @@
         <v>59</v>
       </c>
       <c r="C444">
-        <v>5471.1</v>
+        <v>4750.9</v>
       </c>
       <c r="D444" t="s">
         <v>446</v>
@@ -9494,7 +9494,7 @@
         <v>60</v>
       </c>
       <c r="C445">
-        <v>5525.8</v>
+        <v>4761.5</v>
       </c>
       <c r="D445" t="s">
         <v>447</v>
@@ -9508,7 +9508,7 @@
         <v>61</v>
       </c>
       <c r="C446">
-        <v>5397.8</v>
+        <v>4742.3</v>
       </c>
       <c r="D446" t="s">
         <v>448</v>
@@ -9522,7 +9522,7 @@
         <v>62</v>
       </c>
       <c r="C447">
-        <v>5523.1</v>
+        <v>4679.3</v>
       </c>
       <c r="D447" t="s">
         <v>449</v>
@@ -9536,7 +9536,7 @@
         <v>63</v>
       </c>
       <c r="C448">
-        <v>5510.8</v>
+        <v>4656.9</v>
       </c>
       <c r="D448" t="s">
         <v>450</v>
@@ -9550,7 +9550,7 @@
         <v>64</v>
       </c>
       <c r="C449">
-        <v>5393.2</v>
+        <v>4659.2</v>
       </c>
       <c r="D449" t="s">
         <v>451</v>
@@ -9564,7 +9564,7 @@
         <v>65</v>
       </c>
       <c r="C450">
-        <v>5321.1</v>
+        <v>4516.2</v>
       </c>
       <c r="D450" t="s">
         <v>452</v>
@@ -9578,7 +9578,7 @@
         <v>66</v>
       </c>
       <c r="C451">
-        <v>5276.7</v>
+        <v>4450</v>
       </c>
       <c r="D451" t="s">
         <v>453</v>
@@ -9592,7 +9592,7 @@
         <v>67</v>
       </c>
       <c r="C452">
-        <v>5205.4</v>
+        <v>4456.6</v>
       </c>
       <c r="D452" t="s">
         <v>454</v>
@@ -9606,7 +9606,7 @@
         <v>68</v>
       </c>
       <c r="C453">
-        <v>5172.3</v>
+        <v>4485.1</v>
       </c>
       <c r="D453" t="s">
         <v>455</v>
@@ -9620,7 +9620,7 @@
         <v>69</v>
       </c>
       <c r="C454">
-        <v>5356.1</v>
+        <v>4618.3</v>
       </c>
       <c r="D454" t="s">
         <v>456</v>
@@ -9634,7 +9634,7 @@
         <v>70</v>
       </c>
       <c r="C455">
-        <v>5367.4</v>
+        <v>4564.8</v>
       </c>
       <c r="D455" t="s">
         <v>457</v>
@@ -9648,7 +9648,7 @@
         <v>71</v>
       </c>
       <c r="C456">
-        <v>5237.5</v>
+        <v>4537.6</v>
       </c>
       <c r="D456" t="s">
         <v>458</v>
@@ -9662,7 +9662,7 @@
         <v>72</v>
       </c>
       <c r="C457">
-        <v>5064</v>
+        <v>4519</v>
       </c>
       <c r="D457" t="s">
         <v>459</v>
@@ -9676,7 +9676,7 @@
         <v>73</v>
       </c>
       <c r="C458">
-        <v>5691.4</v>
+        <v>5019.3</v>
       </c>
       <c r="D458" t="s">
         <v>460</v>
@@ -9690,7 +9690,7 @@
         <v>74</v>
       </c>
       <c r="C459">
-        <v>5509.4</v>
+        <v>4912.7</v>
       </c>
       <c r="D459" t="s">
         <v>461</v>
@@ -9704,7 +9704,7 @@
         <v>75</v>
       </c>
       <c r="C460">
-        <v>5329.2</v>
+        <v>4893.2</v>
       </c>
       <c r="D460" t="s">
         <v>462</v>
@@ -9718,7 +9718,7 @@
         <v>76</v>
       </c>
       <c r="C461">
-        <v>5202.4</v>
+        <v>4887.5</v>
       </c>
       <c r="D461" t="s">
         <v>463</v>
@@ -9732,7 +9732,7 @@
         <v>77</v>
       </c>
       <c r="C462">
-        <v>5458</v>
+        <v>5582.2</v>
       </c>
       <c r="D462" t="s">
         <v>464</v>
@@ -9746,7 +9746,7 @@
         <v>78</v>
       </c>
       <c r="C463">
-        <v>5391.8</v>
+        <v>5584.5</v>
       </c>
       <c r="D463" t="s">
         <v>465</v>
@@ -9760,7 +9760,7 @@
         <v>79</v>
       </c>
       <c r="C464">
-        <v>5279.2</v>
+        <v>5528.6</v>
       </c>
       <c r="D464" t="s">
         <v>466</v>
@@ -9774,7 +9774,7 @@
         <v>80</v>
       </c>
       <c r="C465">
-        <v>5232.7</v>
+        <v>5503</v>
       </c>
       <c r="D465" t="s">
         <v>467</v>
@@ -9788,7 +9788,7 @@
         <v>81</v>
       </c>
       <c r="C466">
-        <v>5710.6</v>
+        <v>5678</v>
       </c>
       <c r="D466" t="s">
         <v>468</v>
@@ -9802,7 +9802,7 @@
         <v>82</v>
       </c>
       <c r="C467">
-        <v>5698.1</v>
+        <v>5701</v>
       </c>
       <c r="D467" t="s">
         <v>469</v>
@@ -9816,7 +9816,7 @@
         <v>83</v>
       </c>
       <c r="C468">
-        <v>5755.5</v>
+        <v>5657.8</v>
       </c>
       <c r="D468" t="s">
         <v>470</v>
@@ -9830,7 +9830,7 @@
         <v>84</v>
       </c>
       <c r="C469">
-        <v>5849.8</v>
+        <v>5634.3</v>
       </c>
       <c r="D469" t="s">
         <v>471</v>
@@ -9844,7 +9844,7 @@
         <v>85</v>
       </c>
       <c r="C470">
-        <v>5938.5</v>
+        <v>5693.7</v>
       </c>
       <c r="D470" t="s">
         <v>472</v>
@@ -9858,7 +9858,7 @@
         <v>86</v>
       </c>
       <c r="C471">
-        <v>5989.6</v>
+        <v>5677.5</v>
       </c>
       <c r="D471" t="s">
         <v>473</v>
@@ -9872,7 +9872,7 @@
         <v>87</v>
       </c>
       <c r="C472">
-        <v>6036</v>
+        <v>5650.4</v>
       </c>
       <c r="D472" t="s">
         <v>474</v>
@@ -9886,7 +9886,7 @@
         <v>88</v>
       </c>
       <c r="C473">
-        <v>6044.5</v>
+        <v>5629.6</v>
       </c>
       <c r="D473" t="s">
         <v>475</v>
@@ -9900,7 +9900,7 @@
         <v>89</v>
       </c>
       <c r="C474">
-        <v>5967.6</v>
+        <v>5543.1</v>
       </c>
       <c r="D474" t="s">
         <v>476</v>
@@ -9914,7 +9914,7 @@
         <v>90</v>
       </c>
       <c r="C475">
-        <v>5891.2</v>
+        <v>5517.1</v>
       </c>
       <c r="D475" t="s">
         <v>477</v>
@@ -9928,7 +9928,7 @@
         <v>91</v>
       </c>
       <c r="C476">
-        <v>5873.4</v>
+        <v>5533.3</v>
       </c>
       <c r="D476" t="s">
         <v>478</v>
@@ -9942,7 +9942,7 @@
         <v>92</v>
       </c>
       <c r="C477">
-        <v>5876.7</v>
+        <v>5501.8</v>
       </c>
       <c r="D477" t="s">
         <v>479</v>
@@ -9956,7 +9956,7 @@
         <v>93</v>
       </c>
       <c r="C478">
-        <v>5605.9</v>
+        <v>4882</v>
       </c>
       <c r="D478" t="s">
         <v>480</v>
@@ -9970,7 +9970,7 @@
         <v>94</v>
       </c>
       <c r="C479">
-        <v>5556.8</v>
+        <v>4797.1</v>
       </c>
       <c r="D479" t="s">
         <v>481</v>
@@ -9984,7 +9984,7 @@
         <v>95</v>
       </c>
       <c r="C480">
-        <v>5500.4</v>
+        <v>4762.3</v>
       </c>
       <c r="D480" t="s">
         <v>482</v>
@@ -9998,7 +9998,7 @@
         <v>96</v>
       </c>
       <c r="C481">
-        <v>5467.3</v>
+        <v>4749.4</v>
       </c>
       <c r="D481" t="s">
         <v>483</v>

--- a/Market Fundamentals/Transelectrica_data/Cons_Prod_final/Weekly_Production_2026.xlsx
+++ b/Market Fundamentals/Transelectrica_data/Cons_Prod_final/Weekly_Production_2026.xlsx
@@ -30460,7 +30460,7 @@
         <v>1</v>
       </c>
       <c r="C1634">
-        <v>4162.3</v>
+        <v>4837.7</v>
       </c>
       <c r="D1634" t="s">
         <v>1636</v>
@@ -30474,7 +30474,7 @@
         <v>2</v>
       </c>
       <c r="C1635">
-        <v>4176.7</v>
+        <v>4834</v>
       </c>
       <c r="D1635" t="s">
         <v>1637</v>
@@ -30488,7 +30488,7 @@
         <v>3</v>
       </c>
       <c r="C1636">
-        <v>4145.2</v>
+        <v>4833.5</v>
       </c>
       <c r="D1636" t="s">
         <v>1638</v>
@@ -30502,7 +30502,7 @@
         <v>4</v>
       </c>
       <c r="C1637">
-        <v>4139.1</v>
+        <v>4811.2</v>
       </c>
       <c r="D1637" t="s">
         <v>1639</v>
@@ -30516,7 +30516,7 @@
         <v>5</v>
       </c>
       <c r="C1638">
-        <v>4327.1</v>
+        <v>4848.6</v>
       </c>
       <c r="D1638" t="s">
         <v>1640</v>
@@ -30530,7 +30530,7 @@
         <v>6</v>
       </c>
       <c r="C1639">
-        <v>4335.6</v>
+        <v>4839.4</v>
       </c>
       <c r="D1639" t="s">
         <v>1641</v>
@@ -30544,7 +30544,7 @@
         <v>7</v>
       </c>
       <c r="C1640">
-        <v>4299</v>
+        <v>4845.2</v>
       </c>
       <c r="D1640" t="s">
         <v>1642</v>
@@ -30558,7 +30558,7 @@
         <v>8</v>
       </c>
       <c r="C1641">
-        <v>4265.7</v>
+        <v>4831.8</v>
       </c>
       <c r="D1641" t="s">
         <v>1643</v>
@@ -30572,7 +30572,7 @@
         <v>9</v>
       </c>
       <c r="C1642">
-        <v>4287.4</v>
+        <v>4826.9</v>
       </c>
       <c r="D1642" t="s">
         <v>1644</v>
@@ -30586,7 +30586,7 @@
         <v>10</v>
       </c>
       <c r="C1643">
-        <v>4221.6</v>
+        <v>4819.8</v>
       </c>
       <c r="D1643" t="s">
         <v>1645</v>
@@ -30600,7 +30600,7 @@
         <v>11</v>
       </c>
       <c r="C1644">
-        <v>4216.8</v>
+        <v>4802.6</v>
       </c>
       <c r="D1644" t="s">
         <v>1646</v>
@@ -30614,7 +30614,7 @@
         <v>12</v>
       </c>
       <c r="C1645">
-        <v>4157.4</v>
+        <v>4747.4</v>
       </c>
       <c r="D1645" t="s">
         <v>1647</v>
@@ -30628,7 +30628,7 @@
         <v>13</v>
       </c>
       <c r="C1646">
-        <v>3980</v>
+        <v>4686.2</v>
       </c>
       <c r="D1646" t="s">
         <v>1648</v>
@@ -30642,7 +30642,7 @@
         <v>14</v>
       </c>
       <c r="C1647">
-        <v>3989.1</v>
+        <v>4573.9</v>
       </c>
       <c r="D1647" t="s">
         <v>1649</v>
@@ -30656,7 +30656,7 @@
         <v>15</v>
       </c>
       <c r="C1648">
-        <v>3948</v>
+        <v>4583.9</v>
       </c>
       <c r="D1648" t="s">
         <v>1650</v>
@@ -30670,7 +30670,7 @@
         <v>16</v>
       </c>
       <c r="C1649">
-        <v>3885.5</v>
+        <v>4563.9</v>
       </c>
       <c r="D1649" t="s">
         <v>1651</v>
@@ -30684,7 +30684,7 @@
         <v>17</v>
       </c>
       <c r="C1650">
-        <v>3720.6</v>
+        <v>4608.2</v>
       </c>
       <c r="D1650" t="s">
         <v>1652</v>
@@ -30698,7 +30698,7 @@
         <v>18</v>
       </c>
       <c r="C1651">
-        <v>3714.6</v>
+        <v>4609.3</v>
       </c>
       <c r="D1651" t="s">
         <v>1653</v>
@@ -30712,7 +30712,7 @@
         <v>19</v>
       </c>
       <c r="C1652">
-        <v>3707.6</v>
+        <v>4593.9</v>
       </c>
       <c r="D1652" t="s">
         <v>1654</v>
@@ -30726,7 +30726,7 @@
         <v>20</v>
       </c>
       <c r="C1653">
-        <v>3693</v>
+        <v>4583.8</v>
       </c>
       <c r="D1653" t="s">
         <v>1655</v>
@@ -30740,7 +30740,7 @@
         <v>21</v>
       </c>
       <c r="C1654">
-        <v>3684.6</v>
+        <v>4507.6</v>
       </c>
       <c r="D1654" t="s">
         <v>1656</v>
@@ -30754,7 +30754,7 @@
         <v>22</v>
       </c>
       <c r="C1655">
-        <v>3691.7</v>
+        <v>4556.1</v>
       </c>
       <c r="D1655" t="s">
         <v>1657</v>
@@ -30768,7 +30768,7 @@
         <v>23</v>
       </c>
       <c r="C1656">
-        <v>3672.1</v>
+        <v>4599.9</v>
       </c>
       <c r="D1656" t="s">
         <v>1658</v>
@@ -30782,7 +30782,7 @@
         <v>24</v>
       </c>
       <c r="C1657">
-        <v>3791.6</v>
+        <v>4584</v>
       </c>
       <c r="D1657" t="s">
         <v>1659</v>
@@ -30796,7 +30796,7 @@
         <v>25</v>
       </c>
       <c r="C1658">
-        <v>3897.8</v>
+        <v>4676</v>
       </c>
       <c r="D1658" t="s">
         <v>1660</v>
@@ -30810,7 +30810,7 @@
         <v>26</v>
       </c>
       <c r="C1659">
-        <v>3955.9</v>
+        <v>4726</v>
       </c>
       <c r="D1659" t="s">
         <v>1661</v>
@@ -30824,7 +30824,7 @@
         <v>27</v>
       </c>
       <c r="C1660">
-        <v>3985.2</v>
+        <v>4858.2</v>
       </c>
       <c r="D1660" t="s">
         <v>1662</v>
@@ -30838,7 +30838,7 @@
         <v>28</v>
       </c>
       <c r="C1661">
-        <v>4033.1</v>
+        <v>4903</v>
       </c>
       <c r="D1661" t="s">
         <v>1663</v>
@@ -30852,7 +30852,7 @@
         <v>29</v>
       </c>
       <c r="C1662">
-        <v>4322.7</v>
+        <v>4995.3</v>
       </c>
       <c r="D1662" t="s">
         <v>1664</v>
@@ -30866,7 +30866,7 @@
         <v>30</v>
       </c>
       <c r="C1663">
-        <v>4428.1</v>
+        <v>5055.2</v>
       </c>
       <c r="D1663" t="s">
         <v>1665</v>
@@ -30880,7 +30880,7 @@
         <v>31</v>
       </c>
       <c r="C1664">
-        <v>4550.2</v>
+        <v>5168.6</v>
       </c>
       <c r="D1664" t="s">
         <v>1666</v>
@@ -30894,7 +30894,7 @@
         <v>32</v>
       </c>
       <c r="C1665">
-        <v>4670.7</v>
+        <v>5260.7</v>
       </c>
       <c r="D1665" t="s">
         <v>1667</v>
@@ -30908,7 +30908,7 @@
         <v>33</v>
       </c>
       <c r="C1666">
-        <v>5050.6</v>
+        <v>5648.6</v>
       </c>
       <c r="D1666" t="s">
         <v>1668</v>
@@ -30922,7 +30922,7 @@
         <v>34</v>
       </c>
       <c r="C1667">
-        <v>5235.2</v>
+        <v>5769.2</v>
       </c>
       <c r="D1667" t="s">
         <v>1669</v>
@@ -30936,7 +30936,7 @@
         <v>35</v>
       </c>
       <c r="C1668">
-        <v>5422.3</v>
+        <v>5859.1</v>
       </c>
       <c r="D1668" t="s">
         <v>1670</v>
@@ -30950,7 +30950,7 @@
         <v>36</v>
       </c>
       <c r="C1669">
-        <v>5586.2</v>
+        <v>5941.7</v>
       </c>
       <c r="D1669" t="s">
         <v>1671</v>
@@ -30964,7 +30964,7 @@
         <v>37</v>
       </c>
       <c r="C1670">
-        <v>5533.8</v>
+        <v>5830.9</v>
       </c>
       <c r="D1670" t="s">
         <v>1672</v>
@@ -30978,7 +30978,7 @@
         <v>38</v>
       </c>
       <c r="C1671">
-        <v>5690</v>
+        <v>5913.1</v>
       </c>
       <c r="D1671" t="s">
         <v>1673</v>
@@ -30992,7 +30992,7 @@
         <v>39</v>
       </c>
       <c r="C1672">
-        <v>5656</v>
+        <v>5952.2</v>
       </c>
       <c r="D1672" t="s">
         <v>1674</v>
@@ -31006,7 +31006,7 @@
         <v>40</v>
       </c>
       <c r="C1673">
-        <v>5797</v>
+        <v>6018.6</v>
       </c>
       <c r="D1673" t="s">
         <v>1675</v>
@@ -31020,7 +31020,7 @@
         <v>41</v>
       </c>
       <c r="C1674">
-        <v>5708.7</v>
+        <v>5915.7</v>
       </c>
       <c r="D1674" t="s">
         <v>1676</v>
@@ -31034,7 +31034,7 @@
         <v>42</v>
       </c>
       <c r="C1675">
-        <v>5720.4</v>
+        <v>5988.6</v>
       </c>
       <c r="D1675" t="s">
         <v>1677</v>
@@ -31048,7 +31048,7 @@
         <v>43</v>
       </c>
       <c r="C1676">
-        <v>5795.4</v>
+        <v>6057.9</v>
       </c>
       <c r="D1676" t="s">
         <v>1678</v>
@@ -31062,7 +31062,7 @@
         <v>44</v>
       </c>
       <c r="C1677">
-        <v>5882.9</v>
+        <v>6138.8</v>
       </c>
       <c r="D1677" t="s">
         <v>1679</v>
@@ -31076,7 +31076,7 @@
         <v>45</v>
       </c>
       <c r="C1678">
-        <v>6005.5</v>
+        <v>6181.8</v>
       </c>
       <c r="D1678" t="s">
         <v>1680</v>
@@ -31090,7 +31090,7 @@
         <v>46</v>
       </c>
       <c r="C1679">
-        <v>6063</v>
+        <v>6238.2</v>
       </c>
       <c r="D1679" t="s">
         <v>1681</v>
@@ -31104,7 +31104,7 @@
         <v>47</v>
       </c>
       <c r="C1680">
-        <v>6060.5</v>
+        <v>6273.9</v>
       </c>
       <c r="D1680" t="s">
         <v>1682</v>
@@ -31118,7 +31118,7 @@
         <v>48</v>
       </c>
       <c r="C1681">
-        <v>6061.6</v>
+        <v>6277.3</v>
       </c>
       <c r="D1681" t="s">
         <v>1683</v>
@@ -31132,7 +31132,7 @@
         <v>49</v>
       </c>
       <c r="C1682">
-        <v>6338.1</v>
+        <v>6320.8</v>
       </c>
       <c r="D1682" t="s">
         <v>1684</v>
@@ -31146,7 +31146,7 @@
         <v>50</v>
       </c>
       <c r="C1683">
-        <v>6374.7</v>
+        <v>6333.7</v>
       </c>
       <c r="D1683" t="s">
         <v>1685</v>
@@ -31160,7 +31160,7 @@
         <v>51</v>
       </c>
       <c r="C1684">
-        <v>6389.7</v>
+        <v>6300.5</v>
       </c>
       <c r="D1684" t="s">
         <v>1686</v>
@@ -31174,7 +31174,7 @@
         <v>52</v>
       </c>
       <c r="C1685">
-        <v>6410.9</v>
+        <v>6425</v>
       </c>
       <c r="D1685" t="s">
         <v>1687</v>
@@ -31188,7 +31188,7 @@
         <v>53</v>
       </c>
       <c r="C1686">
-        <v>6293.8</v>
+        <v>6300</v>
       </c>
       <c r="D1686" t="s">
         <v>1688</v>
@@ -31202,7 +31202,7 @@
         <v>54</v>
       </c>
       <c r="C1687">
-        <v>6295.3</v>
+        <v>6322</v>
       </c>
       <c r="D1687" t="s">
         <v>1689</v>
@@ -31216,7 +31216,7 @@
         <v>55</v>
       </c>
       <c r="C1688">
-        <v>6253.1</v>
+        <v>6361.6</v>
       </c>
       <c r="D1688" t="s">
         <v>1690</v>
@@ -31230,7 +31230,7 @@
         <v>56</v>
       </c>
       <c r="C1689">
-        <v>6342.7</v>
+        <v>6351.1</v>
       </c>
       <c r="D1689" t="s">
         <v>1691</v>
@@ -31244,7 +31244,7 @@
         <v>57</v>
       </c>
       <c r="C1690">
-        <v>6394.9</v>
+        <v>6484.2</v>
       </c>
       <c r="D1690" t="s">
         <v>1692</v>
@@ -31258,7 +31258,7 @@
         <v>58</v>
       </c>
       <c r="C1691">
-        <v>6448.2</v>
+        <v>6509.4</v>
       </c>
       <c r="D1691" t="s">
         <v>1693</v>
@@ -31272,7 +31272,7 @@
         <v>59</v>
       </c>
       <c r="C1692">
-        <v>6483.8</v>
+        <v>6550.8</v>
       </c>
       <c r="D1692" t="s">
         <v>1694</v>
@@ -31286,7 +31286,7 @@
         <v>60</v>
       </c>
       <c r="C1693">
-        <v>6525.2</v>
+        <v>6580.5</v>
       </c>
       <c r="D1693" t="s">
         <v>1695</v>
@@ -31300,7 +31300,7 @@
         <v>61</v>
       </c>
       <c r="C1694">
-        <v>6517.6</v>
+        <v>6665.8</v>
       </c>
       <c r="D1694" t="s">
         <v>1696</v>
@@ -31314,7 +31314,7 @@
         <v>62</v>
       </c>
       <c r="C1695">
-        <v>6493.1</v>
+        <v>6637.5</v>
       </c>
       <c r="D1695" t="s">
         <v>1697</v>
@@ -31328,7 +31328,7 @@
         <v>63</v>
       </c>
       <c r="C1696">
-        <v>6469.3</v>
+        <v>6697.7</v>
       </c>
       <c r="D1696" t="s">
         <v>1698</v>
@@ -31342,7 +31342,7 @@
         <v>64</v>
       </c>
       <c r="C1697">
-        <v>6449.6</v>
+        <v>6730.6</v>
       </c>
       <c r="D1697" t="s">
         <v>1699</v>
@@ -31356,7 +31356,7 @@
         <v>65</v>
       </c>
       <c r="C1698">
-        <v>6264.4</v>
+        <v>6621.7</v>
       </c>
       <c r="D1698" t="s">
         <v>1700</v>
@@ -31370,7 +31370,7 @@
         <v>66</v>
       </c>
       <c r="C1699">
-        <v>6188.8</v>
+        <v>6537.8</v>
       </c>
       <c r="D1699" t="s">
         <v>1701</v>
@@ -31384,7 +31384,7 @@
         <v>67</v>
       </c>
       <c r="C1700">
-        <v>6125.4</v>
+        <v>6476.9</v>
       </c>
       <c r="D1700" t="s">
         <v>1702</v>
@@ -31398,7 +31398,7 @@
         <v>68</v>
       </c>
       <c r="C1701">
-        <v>6104.8</v>
+        <v>6407.9</v>
       </c>
       <c r="D1701" t="s">
         <v>1703</v>
@@ -31412,7 +31412,7 @@
         <v>69</v>
       </c>
       <c r="C1702">
-        <v>6249.2</v>
+        <v>6429.5</v>
       </c>
       <c r="D1702" t="s">
         <v>1704</v>
@@ -31426,7 +31426,7 @@
         <v>70</v>
       </c>
       <c r="C1703">
-        <v>6116.2</v>
+        <v>6324.8</v>
       </c>
       <c r="D1703" t="s">
         <v>1705</v>
@@ -31440,7 +31440,7 @@
         <v>71</v>
       </c>
       <c r="C1704">
-        <v>6023.9</v>
+        <v>6213.8</v>
       </c>
       <c r="D1704" t="s">
         <v>1706</v>
@@ -31454,7 +31454,7 @@
         <v>72</v>
       </c>
       <c r="C1705">
-        <v>5910.1</v>
+        <v>6136.1</v>
       </c>
       <c r="D1705" t="s">
         <v>1707</v>
@@ -31468,7 +31468,7 @@
         <v>73</v>
       </c>
       <c r="C1706">
-        <v>5596.5</v>
+        <v>6014.7</v>
       </c>
       <c r="D1706" t="s">
         <v>1708</v>
@@ -31482,7 +31482,7 @@
         <v>74</v>
       </c>
       <c r="C1707">
-        <v>5443.3</v>
+        <v>5895.4</v>
       </c>
       <c r="D1707" t="s">
         <v>1709</v>
@@ -31496,7 +31496,7 @@
         <v>75</v>
       </c>
       <c r="C1708">
-        <v>5303.1</v>
+        <v>5784.9</v>
       </c>
       <c r="D1708" t="s">
         <v>1710</v>
@@ -31510,7 +31510,7 @@
         <v>76</v>
       </c>
       <c r="C1709">
-        <v>5206.8</v>
+        <v>5707.7</v>
       </c>
       <c r="D1709" t="s">
         <v>1711</v>
@@ -31524,7 +31524,7 @@
         <v>77</v>
       </c>
       <c r="C1710">
-        <v>5106.4</v>
+        <v>5379.9</v>
       </c>
       <c r="D1710" t="s">
         <v>1712</v>
@@ -31538,7 +31538,7 @@
         <v>78</v>
       </c>
       <c r="C1711">
-        <v>5071.1</v>
+        <v>5348.7</v>
       </c>
       <c r="D1711" t="s">
         <v>1713</v>
@@ -31552,7 +31552,7 @@
         <v>79</v>
       </c>
       <c r="C1712">
-        <v>5070.7</v>
+        <v>5298.5</v>
       </c>
       <c r="D1712" t="s">
         <v>1714</v>
@@ -31566,7 +31566,7 @@
         <v>80</v>
       </c>
       <c r="C1713">
-        <v>5115.2</v>
+        <v>5256.1</v>
       </c>
       <c r="D1713" t="s">
         <v>1715</v>
@@ -31580,7 +31580,7 @@
         <v>81</v>
       </c>
       <c r="C1714">
-        <v>5438.1</v>
+        <v>5653.8</v>
       </c>
       <c r="D1714" t="s">
         <v>1716</v>
@@ -31594,7 +31594,7 @@
         <v>82</v>
       </c>
       <c r="C1715">
-        <v>5517.7</v>
+        <v>5741</v>
       </c>
       <c r="D1715" t="s">
         <v>1717</v>
@@ -31608,7 +31608,7 @@
         <v>83</v>
       </c>
       <c r="C1716">
-        <v>5612.2</v>
+        <v>5747.5</v>
       </c>
       <c r="D1716" t="s">
         <v>1718</v>
@@ -31622,7 +31622,7 @@
         <v>84</v>
       </c>
       <c r="C1717">
-        <v>5670.9</v>
+        <v>5732.4</v>
       </c>
       <c r="D1717" t="s">
         <v>1719</v>
@@ -31636,7 +31636,7 @@
         <v>85</v>
       </c>
       <c r="C1718">
-        <v>5744</v>
+        <v>5715.6</v>
       </c>
       <c r="D1718" t="s">
         <v>1720</v>
@@ -31650,7 +31650,7 @@
         <v>86</v>
       </c>
       <c r="C1719">
-        <v>5770.2</v>
+        <v>5713.1</v>
       </c>
       <c r="D1719" t="s">
         <v>1721</v>
@@ -31664,7 +31664,7 @@
         <v>87</v>
       </c>
       <c r="C1720">
-        <v>5801.2</v>
+        <v>5696.5</v>
       </c>
       <c r="D1720" t="s">
         <v>1722</v>
@@ -31678,7 +31678,7 @@
         <v>88</v>
       </c>
       <c r="C1721">
-        <v>5648.9</v>
+        <v>5622.9</v>
       </c>
       <c r="D1721" t="s">
         <v>1723</v>
@@ -31692,7 +31692,7 @@
         <v>89</v>
       </c>
       <c r="C1722">
-        <v>5364.5</v>
+        <v>5371</v>
       </c>
       <c r="D1722" t="s">
         <v>1724</v>
@@ -31706,7 +31706,7 @@
         <v>90</v>
       </c>
       <c r="C1723">
-        <v>5241.4</v>
+        <v>5276.5</v>
       </c>
       <c r="D1723" t="s">
         <v>1725</v>
@@ -31720,7 +31720,7 @@
         <v>91</v>
       </c>
       <c r="C1724">
-        <v>5173</v>
+        <v>5178.9</v>
       </c>
       <c r="D1724" t="s">
         <v>1726</v>
@@ -31734,7 +31734,7 @@
         <v>92</v>
       </c>
       <c r="C1725">
-        <v>5127.4</v>
+        <v>5148.2</v>
       </c>
       <c r="D1725" t="s">
         <v>1727</v>
@@ -31748,7 +31748,7 @@
         <v>93</v>
       </c>
       <c r="C1726">
-        <v>4999.7</v>
+        <v>5055.2</v>
       </c>
       <c r="D1726" t="s">
         <v>1728</v>
@@ -31762,7 +31762,7 @@
         <v>94</v>
       </c>
       <c r="C1727">
-        <v>4936.2</v>
+        <v>4972.4</v>
       </c>
       <c r="D1727" t="s">
         <v>1729</v>
@@ -31776,7 +31776,7 @@
         <v>95</v>
       </c>
       <c r="C1728">
-        <v>4880.5</v>
+        <v>4943.1</v>
       </c>
       <c r="D1728" t="s">
         <v>1730</v>
@@ -31790,7 +31790,7 @@
         <v>96</v>
       </c>
       <c r="C1729">
-        <v>4867.6</v>
+        <v>4932.2</v>
       </c>
       <c r="D1729" t="s">
         <v>1731</v>
@@ -31804,7 +31804,7 @@
         <v>1</v>
       </c>
       <c r="C1730">
-        <v>5381.1</v>
+        <v>4937.7</v>
       </c>
       <c r="D1730" t="s">
         <v>1732</v>
@@ -31818,7 +31818,7 @@
         <v>2</v>
       </c>
       <c r="C1731">
-        <v>5460.8</v>
+        <v>4964</v>
       </c>
       <c r="D1731" t="s">
         <v>1733</v>
@@ -31832,7 +31832,7 @@
         <v>3</v>
       </c>
       <c r="C1732">
-        <v>5480.1</v>
+        <v>4973.5</v>
       </c>
       <c r="D1732" t="s">
         <v>1734</v>
@@ -31846,7 +31846,7 @@
         <v>4</v>
       </c>
       <c r="C1733">
-        <v>5524.3</v>
+        <v>4931.2</v>
       </c>
       <c r="D1733" t="s">
         <v>1735</v>
@@ -31860,7 +31860,7 @@
         <v>5</v>
       </c>
       <c r="C1734">
-        <v>5545.1</v>
+        <v>4958.6</v>
       </c>
       <c r="D1734" t="s">
         <v>1736</v>
@@ -31874,7 +31874,7 @@
         <v>6</v>
       </c>
       <c r="C1735">
-        <v>5566.4</v>
+        <v>4949.4</v>
       </c>
       <c r="D1735" t="s">
         <v>1737</v>
@@ -31888,7 +31888,7 @@
         <v>7</v>
       </c>
       <c r="C1736">
-        <v>5579.5</v>
+        <v>4945.2</v>
       </c>
       <c r="D1736" t="s">
         <v>1738</v>
@@ -31902,7 +31902,7 @@
         <v>8</v>
       </c>
       <c r="C1737">
-        <v>5574.1</v>
+        <v>4911.8</v>
       </c>
       <c r="D1737" t="s">
         <v>1739</v>
@@ -31916,7 +31916,7 @@
         <v>9</v>
       </c>
       <c r="C1738">
-        <v>5589.1</v>
+        <v>4906.9</v>
       </c>
       <c r="D1738" t="s">
         <v>1740</v>
@@ -31930,7 +31930,7 @@
         <v>10</v>
       </c>
       <c r="C1739">
-        <v>5574.7</v>
+        <v>4889.8</v>
       </c>
       <c r="D1739" t="s">
         <v>1741</v>
@@ -31944,7 +31944,7 @@
         <v>11</v>
       </c>
       <c r="C1740">
-        <v>5568.5</v>
+        <v>4892.6</v>
       </c>
       <c r="D1740" t="s">
         <v>1742</v>
@@ -31958,7 +31958,7 @@
         <v>12</v>
       </c>
       <c r="C1741">
-        <v>5586.5</v>
+        <v>4827.4</v>
       </c>
       <c r="D1741" t="s">
         <v>1743</v>
@@ -31972,7 +31972,7 @@
         <v>13</v>
       </c>
       <c r="C1742">
-        <v>5473.5</v>
+        <v>4766.2</v>
       </c>
       <c r="D1742" t="s">
         <v>1744</v>
@@ -31986,7 +31986,7 @@
         <v>14</v>
       </c>
       <c r="C1743">
-        <v>5487.4</v>
+        <v>4653.9</v>
       </c>
       <c r="D1743" t="s">
         <v>1745</v>
@@ -32000,7 +32000,7 @@
         <v>15</v>
       </c>
       <c r="C1744">
-        <v>5506.4</v>
+        <v>4643.9</v>
       </c>
       <c r="D1744" t="s">
         <v>1746</v>
@@ -32014,7 +32014,7 @@
         <v>16</v>
       </c>
       <c r="C1745">
-        <v>5523.9</v>
+        <v>4633.9</v>
       </c>
       <c r="D1745" t="s">
         <v>1747</v>
@@ -32028,7 +32028,7 @@
         <v>17</v>
       </c>
       <c r="C1746">
-        <v>5540.5</v>
+        <v>4648.2</v>
       </c>
       <c r="D1746" t="s">
         <v>1748</v>
@@ -32042,7 +32042,7 @@
         <v>18</v>
       </c>
       <c r="C1747">
-        <v>5540</v>
+        <v>4639.3</v>
       </c>
       <c r="D1747" t="s">
         <v>1749</v>
@@ -32056,7 +32056,7 @@
         <v>19</v>
       </c>
       <c r="C1748">
-        <v>5513.5</v>
+        <v>4633.9</v>
       </c>
       <c r="D1748" t="s">
         <v>1750</v>
@@ -32070,7 +32070,7 @@
         <v>20</v>
       </c>
       <c r="C1749">
-        <v>5520.7</v>
+        <v>4633.8</v>
       </c>
       <c r="D1749" t="s">
         <v>1751</v>
@@ -32084,7 +32084,7 @@
         <v>21</v>
       </c>
       <c r="C1750">
-        <v>5554.2</v>
+        <v>4567.6</v>
       </c>
       <c r="D1750" t="s">
         <v>1752</v>
@@ -32098,7 +32098,7 @@
         <v>22</v>
       </c>
       <c r="C1751">
-        <v>5574.9</v>
+        <v>4636.1</v>
       </c>
       <c r="D1751" t="s">
         <v>1753</v>
@@ -32112,7 +32112,7 @@
         <v>23</v>
       </c>
       <c r="C1752">
-        <v>5636</v>
+        <v>4699.9</v>
       </c>
       <c r="D1752" t="s">
         <v>1754</v>
@@ -32126,7 +32126,7 @@
         <v>24</v>
       </c>
       <c r="C1753">
-        <v>5663.2</v>
+        <v>4694</v>
       </c>
       <c r="D1753" t="s">
         <v>1755</v>
@@ -32140,7 +32140,7 @@
         <v>25</v>
       </c>
       <c r="C1754">
-        <v>5644.8</v>
+        <v>4786</v>
       </c>
       <c r="D1754" t="s">
         <v>1756</v>
@@ -32154,7 +32154,7 @@
         <v>26</v>
       </c>
       <c r="C1755">
-        <v>5645.7</v>
+        <v>4846</v>
       </c>
       <c r="D1755" t="s">
         <v>1757</v>
@@ -32168,7 +32168,7 @@
         <v>27</v>
       </c>
       <c r="C1756">
-        <v>5701.8</v>
+        <v>4978.2</v>
       </c>
       <c r="D1756" t="s">
         <v>1758</v>
@@ -32182,7 +32182,7 @@
         <v>28</v>
       </c>
       <c r="C1757">
-        <v>5765.1</v>
+        <v>5013</v>
       </c>
       <c r="D1757" t="s">
         <v>1759</v>
@@ -32196,7 +32196,7 @@
         <v>29</v>
       </c>
       <c r="C1758">
-        <v>6026.9</v>
+        <v>5085.3</v>
       </c>
       <c r="D1758" t="s">
         <v>1760</v>
@@ -32210,7 +32210,7 @@
         <v>30</v>
       </c>
       <c r="C1759">
-        <v>6067.8</v>
+        <v>5135.2</v>
       </c>
       <c r="D1759" t="s">
         <v>1761</v>
@@ -32224,7 +32224,7 @@
         <v>31</v>
       </c>
       <c r="C1760">
-        <v>6112.2</v>
+        <v>5228.6</v>
       </c>
       <c r="D1760" t="s">
         <v>1762</v>
@@ -32238,7 +32238,7 @@
         <v>32</v>
       </c>
       <c r="C1761">
-        <v>6169</v>
+        <v>5300.7</v>
       </c>
       <c r="D1761" t="s">
         <v>1763</v>
@@ -32252,7 +32252,7 @@
         <v>33</v>
       </c>
       <c r="C1762">
-        <v>6165.9</v>
+        <v>5678.6</v>
       </c>
       <c r="D1762" t="s">
         <v>1764</v>
@@ -32266,7 +32266,7 @@
         <v>34</v>
       </c>
       <c r="C1763">
-        <v>6253.4</v>
+        <v>5779.2</v>
       </c>
       <c r="D1763" t="s">
         <v>1765</v>
@@ -32280,7 +32280,7 @@
         <v>35</v>
       </c>
       <c r="C1764">
-        <v>6365.8</v>
+        <v>5869.1</v>
       </c>
       <c r="D1764" t="s">
         <v>1766</v>
@@ -32294,7 +32294,7 @@
         <v>36</v>
       </c>
       <c r="C1765">
-        <v>6306.1</v>
+        <v>5951.7</v>
       </c>
       <c r="D1765" t="s">
         <v>1767</v>
@@ -32308,7 +32308,7 @@
         <v>37</v>
       </c>
       <c r="C1766">
-        <v>6053.5</v>
+        <v>5840.9</v>
       </c>
       <c r="D1766" t="s">
         <v>1768</v>
@@ -32322,7 +32322,7 @@
         <v>38</v>
       </c>
       <c r="C1767">
-        <v>6091.6</v>
+        <v>5933.1</v>
       </c>
       <c r="D1767" t="s">
         <v>1769</v>
@@ -32336,7 +32336,7 @@
         <v>39</v>
       </c>
       <c r="C1768">
-        <v>6163.8</v>
+        <v>5972.2</v>
       </c>
       <c r="D1768" t="s">
         <v>1770</v>
@@ -32350,7 +32350,7 @@
         <v>40</v>
       </c>
       <c r="C1769">
-        <v>6180.9</v>
+        <v>6048.6</v>
       </c>
       <c r="D1769" t="s">
         <v>1771</v>
@@ -32364,7 +32364,7 @@
         <v>41</v>
       </c>
       <c r="C1770">
-        <v>6113.4</v>
+        <v>5955.7</v>
       </c>
       <c r="D1770" t="s">
         <v>1772</v>
@@ -32378,7 +32378,7 @@
         <v>42</v>
       </c>
       <c r="C1771">
-        <v>6124.8</v>
+        <v>6038.6</v>
       </c>
       <c r="D1771" t="s">
         <v>1773</v>
@@ -32392,7 +32392,7 @@
         <v>43</v>
       </c>
       <c r="C1772">
-        <v>6182.9</v>
+        <v>6117.9</v>
       </c>
       <c r="D1772" t="s">
         <v>1774</v>
@@ -32406,7 +32406,7 @@
         <v>44</v>
       </c>
       <c r="C1773">
-        <v>6207.1</v>
+        <v>6208.8</v>
       </c>
       <c r="D1773" t="s">
         <v>1775</v>
@@ -32420,7 +32420,7 @@
         <v>45</v>
       </c>
       <c r="C1774">
-        <v>5392.5</v>
+        <v>6271.8</v>
       </c>
       <c r="D1774" t="s">
         <v>1776</v>
@@ -32434,7 +32434,7 @@
         <v>46</v>
       </c>
       <c r="C1775">
-        <v>5414.4</v>
+        <v>6348.2</v>
       </c>
       <c r="D1775" t="s">
         <v>1777</v>
@@ -32448,7 +32448,7 @@
         <v>47</v>
       </c>
       <c r="C1776">
-        <v>5415.1</v>
+        <v>6403.9</v>
       </c>
       <c r="D1776" t="s">
         <v>1778</v>
@@ -32462,7 +32462,7 @@
         <v>48</v>
       </c>
       <c r="C1777">
-        <v>5469.3</v>
+        <v>6437.3</v>
       </c>
       <c r="D1777" t="s">
         <v>1779</v>
@@ -32476,7 +32476,7 @@
         <v>49</v>
       </c>
       <c r="C1778">
-        <v>5302.3</v>
+        <v>6500.8</v>
       </c>
       <c r="D1778" t="s">
         <v>1780</v>
@@ -32490,7 +32490,7 @@
         <v>50</v>
       </c>
       <c r="C1779">
-        <v>5327.7</v>
+        <v>6523.7</v>
       </c>
       <c r="D1779" t="s">
         <v>1781</v>
@@ -32504,7 +32504,7 @@
         <v>51</v>
       </c>
       <c r="C1780">
-        <v>5208</v>
+        <v>6510.5</v>
       </c>
       <c r="D1780" t="s">
         <v>1782</v>
@@ -32518,7 +32518,7 @@
         <v>52</v>
       </c>
       <c r="C1781">
-        <v>5172.9</v>
+        <v>6635</v>
       </c>
       <c r="D1781" t="s">
         <v>1783</v>
@@ -32532,7 +32532,7 @@
         <v>53</v>
       </c>
       <c r="C1782">
-        <v>5245.8</v>
+        <v>6500</v>
       </c>
       <c r="D1782" t="s">
         <v>1784</v>
@@ -32546,7 +32546,7 @@
         <v>54</v>
       </c>
       <c r="C1783">
-        <v>5201.9</v>
+        <v>6522</v>
       </c>
       <c r="D1783" t="s">
         <v>1785</v>
@@ -32560,7 +32560,7 @@
         <v>55</v>
       </c>
       <c r="C1784">
-        <v>5217.6</v>
+        <v>6551.6</v>
       </c>
       <c r="D1784" t="s">
         <v>1786</v>
@@ -32574,7 +32574,7 @@
         <v>56</v>
       </c>
       <c r="C1785">
-        <v>5249.4</v>
+        <v>6531.1</v>
       </c>
       <c r="D1785" t="s">
         <v>1787</v>
@@ -32588,7 +32588,7 @@
         <v>57</v>
       </c>
       <c r="C1786">
-        <v>5263.4</v>
+        <v>6664.2</v>
       </c>
       <c r="D1786" t="s">
         <v>1788</v>
@@ -32602,7 +32602,7 @@
         <v>58</v>
       </c>
       <c r="C1787">
-        <v>5289.3</v>
+        <v>6699.4</v>
       </c>
       <c r="D1787" t="s">
         <v>1789</v>
@@ -32616,7 +32616,7 @@
         <v>59</v>
       </c>
       <c r="C1788">
-        <v>5302.4</v>
+        <v>6750.8</v>
       </c>
       <c r="D1788" t="s">
         <v>1790</v>
@@ -32630,7 +32630,7 @@
         <v>60</v>
       </c>
       <c r="C1789">
-        <v>5340.2</v>
+        <v>6790.5</v>
       </c>
       <c r="D1789" t="s">
         <v>1791</v>
@@ -32644,7 +32644,7 @@
         <v>61</v>
       </c>
       <c r="C1790">
-        <v>5520.9</v>
+        <v>6905.8</v>
       </c>
       <c r="D1790" t="s">
         <v>1792</v>
@@ -32658,7 +32658,7 @@
         <v>62</v>
       </c>
       <c r="C1791">
-        <v>5530.1</v>
+        <v>6917.5</v>
       </c>
       <c r="D1791" t="s">
         <v>1793</v>
@@ -32672,7 +32672,7 @@
         <v>63</v>
       </c>
       <c r="C1792">
-        <v>5545.6</v>
+        <v>7007.7</v>
       </c>
       <c r="D1792" t="s">
         <v>1794</v>
@@ -32686,7 +32686,7 @@
         <v>64</v>
       </c>
       <c r="C1793">
-        <v>5507.7</v>
+        <v>7070.6</v>
       </c>
       <c r="D1793" t="s">
         <v>1795</v>
@@ -32700,7 +32700,7 @@
         <v>65</v>
       </c>
       <c r="C1794">
-        <v>5353</v>
+        <v>6971.7</v>
       </c>
       <c r="D1794" t="s">
         <v>1796</v>
@@ -32714,7 +32714,7 @@
         <v>66</v>
       </c>
       <c r="C1795">
-        <v>5304.1</v>
+        <v>6887.8</v>
       </c>
       <c r="D1795" t="s">
         <v>1797</v>
@@ -32728,7 +32728,7 @@
         <v>67</v>
       </c>
       <c r="C1796">
-        <v>5261.6</v>
+        <v>6836.9</v>
       </c>
       <c r="D1796" t="s">
         <v>1798</v>
@@ -32742,7 +32742,7 @@
         <v>68</v>
       </c>
       <c r="C1797">
-        <v>5254.9</v>
+        <v>6777.9</v>
       </c>
       <c r="D1797" t="s">
         <v>1799</v>
@@ -32756,7 +32756,7 @@
         <v>69</v>
       </c>
       <c r="C1798">
-        <v>5666.3</v>
+        <v>6779.5</v>
       </c>
       <c r="D1798" t="s">
         <v>1800</v>
@@ -32770,7 +32770,7 @@
         <v>70</v>
       </c>
       <c r="C1799">
-        <v>5590</v>
+        <v>6664.8</v>
       </c>
       <c r="D1799" t="s">
         <v>1801</v>
@@ -32784,7 +32784,7 @@
         <v>71</v>
       </c>
       <c r="C1800">
-        <v>5478.5</v>
+        <v>6533.8</v>
       </c>
       <c r="D1800" t="s">
         <v>1802</v>
@@ -32798,7 +32798,7 @@
         <v>72</v>
       </c>
       <c r="C1801">
-        <v>5346.4</v>
+        <v>6436.1</v>
       </c>
       <c r="D1801" t="s">
         <v>1803</v>
@@ -32812,7 +32812,7 @@
         <v>73</v>
       </c>
       <c r="C1802">
-        <v>5329.2</v>
+        <v>6304.7</v>
       </c>
       <c r="D1802" t="s">
         <v>1804</v>
@@ -32826,7 +32826,7 @@
         <v>74</v>
       </c>
       <c r="C1803">
-        <v>5165.3</v>
+        <v>6175.4</v>
       </c>
       <c r="D1803" t="s">
         <v>1805</v>
@@ -32840,7 +32840,7 @@
         <v>75</v>
       </c>
       <c r="C1804">
-        <v>4976.7</v>
+        <v>6064.9</v>
       </c>
       <c r="D1804" t="s">
         <v>1806</v>
@@ -32854,7 +32854,7 @@
         <v>76</v>
       </c>
       <c r="C1805">
-        <v>4893.1</v>
+        <v>5987.7</v>
       </c>
       <c r="D1805" t="s">
         <v>1807</v>
@@ -32868,7 +32868,7 @@
         <v>77</v>
       </c>
       <c r="C1806">
-        <v>4880.3</v>
+        <v>5699.9</v>
       </c>
       <c r="D1806" t="s">
         <v>1808</v>
@@ -32882,7 +32882,7 @@
         <v>78</v>
       </c>
       <c r="C1807">
-        <v>4799.2</v>
+        <v>5658.7</v>
       </c>
       <c r="D1807" t="s">
         <v>1809</v>
@@ -32896,7 +32896,7 @@
         <v>79</v>
       </c>
       <c r="C1808">
-        <v>4716.6</v>
+        <v>5588.5</v>
       </c>
       <c r="D1808" t="s">
         <v>1810</v>
@@ -32910,7 +32910,7 @@
         <v>80</v>
       </c>
       <c r="C1809">
-        <v>4714.2</v>
+        <v>5516.1</v>
       </c>
       <c r="D1809" t="s">
         <v>1811</v>
@@ -32924,7 +32924,7 @@
         <v>81</v>
       </c>
       <c r="C1810">
-        <v>5083.7</v>
+        <v>5863.8</v>
       </c>
       <c r="D1810" t="s">
         <v>1812</v>
@@ -32938,7 +32938,7 @@
         <v>82</v>
       </c>
       <c r="C1811">
-        <v>5157.8</v>
+        <v>5891</v>
       </c>
       <c r="D1811" t="s">
         <v>1813</v>
@@ -32952,7 +32952,7 @@
         <v>83</v>
       </c>
       <c r="C1812">
-        <v>5176.2</v>
+        <v>5847.5</v>
       </c>
       <c r="D1812" t="s">
         <v>1814</v>
@@ -32966,7 +32966,7 @@
         <v>84</v>
       </c>
       <c r="C1813">
-        <v>5185.4</v>
+        <v>5802.4</v>
       </c>
       <c r="D1813" t="s">
         <v>1815</v>
@@ -32980,7 +32980,7 @@
         <v>85</v>
       </c>
       <c r="C1814">
-        <v>5138.2</v>
+        <v>5775.6</v>
       </c>
       <c r="D1814" t="s">
         <v>1816</v>
@@ -32994,7 +32994,7 @@
         <v>86</v>
       </c>
       <c r="C1815">
-        <v>5113.6</v>
+        <v>5713.1</v>
       </c>
       <c r="D1815" t="s">
         <v>1817</v>
@@ -33008,7 +33008,7 @@
         <v>87</v>
       </c>
       <c r="C1816">
-        <v>5137.7</v>
+        <v>5706.5</v>
       </c>
       <c r="D1816" t="s">
         <v>1818</v>
@@ -33022,7 +33022,7 @@
         <v>88</v>
       </c>
       <c r="C1817">
-        <v>5042.2</v>
+        <v>5662.9</v>
       </c>
       <c r="D1817" t="s">
         <v>1819</v>
@@ -33036,7 +33036,7 @@
         <v>89</v>
       </c>
       <c r="C1818">
-        <v>4644.4</v>
+        <v>5411</v>
       </c>
       <c r="D1818" t="s">
         <v>1820</v>
@@ -33050,7 +33050,7 @@
         <v>90</v>
       </c>
       <c r="C1819">
-        <v>4568.5</v>
+        <v>5346.5</v>
       </c>
       <c r="D1819" t="s">
         <v>1821</v>
@@ -33064,7 +33064,7 @@
         <v>91</v>
       </c>
       <c r="C1820">
-        <v>4492.5</v>
+        <v>5248.9</v>
       </c>
       <c r="D1820" t="s">
         <v>1822</v>
@@ -33078,7 +33078,7 @@
         <v>92</v>
       </c>
       <c r="C1821">
-        <v>4412.2</v>
+        <v>5238.2</v>
       </c>
       <c r="D1821" t="s">
         <v>1823</v>
@@ -33092,7 +33092,7 @@
         <v>93</v>
       </c>
       <c r="C1822">
-        <v>4091</v>
+        <v>5125.2</v>
       </c>
       <c r="D1822" t="s">
         <v>1824</v>
@@ -33106,7 +33106,7 @@
         <v>94</v>
       </c>
       <c r="C1823">
-        <v>3977.8</v>
+        <v>5042.4</v>
       </c>
       <c r="D1823" t="s">
         <v>1825</v>
@@ -33120,7 +33120,7 @@
         <v>95</v>
       </c>
       <c r="C1824">
-        <v>4004</v>
+        <v>5043.1</v>
       </c>
       <c r="D1824" t="s">
         <v>1826</v>
@@ -33134,7 +33134,7 @@
         <v>96</v>
       </c>
       <c r="C1825">
-        <v>3990.3</v>
+        <v>5052.2</v>
       </c>
       <c r="D1825" t="s">
         <v>1827</v>

--- a/Market Fundamentals/Transelectrica_data/Cons_Prod_final/Weekly_Production_2026.xlsx
+++ b/Market Fundamentals/Transelectrica_data/Cons_Prod_final/Weekly_Production_2026.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2404" uniqueCount="2404">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2500" uniqueCount="2500">
   <si>
     <t>Date</t>
   </si>
@@ -7226,6 +7226,294 @@
   </si>
   <si>
     <t>25.08.202696.0</t>
+  </si>
+  <si>
+    <t>26.08.20261.0</t>
+  </si>
+  <si>
+    <t>26.08.20262.0</t>
+  </si>
+  <si>
+    <t>26.08.20263.0</t>
+  </si>
+  <si>
+    <t>26.08.20264.0</t>
+  </si>
+  <si>
+    <t>26.08.20265.0</t>
+  </si>
+  <si>
+    <t>26.08.20266.0</t>
+  </si>
+  <si>
+    <t>26.08.20267.0</t>
+  </si>
+  <si>
+    <t>26.08.20268.0</t>
+  </si>
+  <si>
+    <t>26.08.20269.0</t>
+  </si>
+  <si>
+    <t>26.08.202610.0</t>
+  </si>
+  <si>
+    <t>26.08.202611.0</t>
+  </si>
+  <si>
+    <t>26.08.202612.0</t>
+  </si>
+  <si>
+    <t>26.08.202613.0</t>
+  </si>
+  <si>
+    <t>26.08.202614.0</t>
+  </si>
+  <si>
+    <t>26.08.202615.0</t>
+  </si>
+  <si>
+    <t>26.08.202616.0</t>
+  </si>
+  <si>
+    <t>26.08.202617.0</t>
+  </si>
+  <si>
+    <t>26.08.202618.0</t>
+  </si>
+  <si>
+    <t>26.08.202619.0</t>
+  </si>
+  <si>
+    <t>26.08.202620.0</t>
+  </si>
+  <si>
+    <t>26.08.202621.0</t>
+  </si>
+  <si>
+    <t>26.08.202622.0</t>
+  </si>
+  <si>
+    <t>26.08.202623.0</t>
+  </si>
+  <si>
+    <t>26.08.202624.0</t>
+  </si>
+  <si>
+    <t>26.08.202625.0</t>
+  </si>
+  <si>
+    <t>26.08.202626.0</t>
+  </si>
+  <si>
+    <t>26.08.202627.0</t>
+  </si>
+  <si>
+    <t>26.08.202628.0</t>
+  </si>
+  <si>
+    <t>26.08.202629.0</t>
+  </si>
+  <si>
+    <t>26.08.202630.0</t>
+  </si>
+  <si>
+    <t>26.08.202631.0</t>
+  </si>
+  <si>
+    <t>26.08.202632.0</t>
+  </si>
+  <si>
+    <t>26.08.202633.0</t>
+  </si>
+  <si>
+    <t>26.08.202634.0</t>
+  </si>
+  <si>
+    <t>26.08.202635.0</t>
+  </si>
+  <si>
+    <t>26.08.202636.0</t>
+  </si>
+  <si>
+    <t>26.08.202637.0</t>
+  </si>
+  <si>
+    <t>26.08.202638.0</t>
+  </si>
+  <si>
+    <t>26.08.202639.0</t>
+  </si>
+  <si>
+    <t>26.08.202640.0</t>
+  </si>
+  <si>
+    <t>26.08.202641.0</t>
+  </si>
+  <si>
+    <t>26.08.202642.0</t>
+  </si>
+  <si>
+    <t>26.08.202643.0</t>
+  </si>
+  <si>
+    <t>26.08.202644.0</t>
+  </si>
+  <si>
+    <t>26.08.202645.0</t>
+  </si>
+  <si>
+    <t>26.08.202646.0</t>
+  </si>
+  <si>
+    <t>26.08.202647.0</t>
+  </si>
+  <si>
+    <t>26.08.202648.0</t>
+  </si>
+  <si>
+    <t>26.08.202649.0</t>
+  </si>
+  <si>
+    <t>26.08.202650.0</t>
+  </si>
+  <si>
+    <t>26.08.202651.0</t>
+  </si>
+  <si>
+    <t>26.08.202652.0</t>
+  </si>
+  <si>
+    <t>26.08.202653.0</t>
+  </si>
+  <si>
+    <t>26.08.202654.0</t>
+  </si>
+  <si>
+    <t>26.08.202655.0</t>
+  </si>
+  <si>
+    <t>26.08.202656.0</t>
+  </si>
+  <si>
+    <t>26.08.202657.0</t>
+  </si>
+  <si>
+    <t>26.08.202658.0</t>
+  </si>
+  <si>
+    <t>26.08.202659.0</t>
+  </si>
+  <si>
+    <t>26.08.202660.0</t>
+  </si>
+  <si>
+    <t>26.08.202661.0</t>
+  </si>
+  <si>
+    <t>26.08.202662.0</t>
+  </si>
+  <si>
+    <t>26.08.202663.0</t>
+  </si>
+  <si>
+    <t>26.08.202664.0</t>
+  </si>
+  <si>
+    <t>26.08.202665.0</t>
+  </si>
+  <si>
+    <t>26.08.202666.0</t>
+  </si>
+  <si>
+    <t>26.08.202667.0</t>
+  </si>
+  <si>
+    <t>26.08.202668.0</t>
+  </si>
+  <si>
+    <t>26.08.202669.0</t>
+  </si>
+  <si>
+    <t>26.08.202670.0</t>
+  </si>
+  <si>
+    <t>26.08.202671.0</t>
+  </si>
+  <si>
+    <t>26.08.202672.0</t>
+  </si>
+  <si>
+    <t>26.08.202673.0</t>
+  </si>
+  <si>
+    <t>26.08.202674.0</t>
+  </si>
+  <si>
+    <t>26.08.202675.0</t>
+  </si>
+  <si>
+    <t>26.08.202676.0</t>
+  </si>
+  <si>
+    <t>26.08.202677.0</t>
+  </si>
+  <si>
+    <t>26.08.202678.0</t>
+  </si>
+  <si>
+    <t>26.08.202679.0</t>
+  </si>
+  <si>
+    <t>26.08.202680.0</t>
+  </si>
+  <si>
+    <t>26.08.202681.0</t>
+  </si>
+  <si>
+    <t>26.08.202682.0</t>
+  </si>
+  <si>
+    <t>26.08.202683.0</t>
+  </si>
+  <si>
+    <t>26.08.202684.0</t>
+  </si>
+  <si>
+    <t>26.08.202685.0</t>
+  </si>
+  <si>
+    <t>26.08.202686.0</t>
+  </si>
+  <si>
+    <t>26.08.202687.0</t>
+  </si>
+  <si>
+    <t>26.08.202688.0</t>
+  </si>
+  <si>
+    <t>26.08.202689.0</t>
+  </si>
+  <si>
+    <t>26.08.202690.0</t>
+  </si>
+  <si>
+    <t>26.08.202691.0</t>
+  </si>
+  <si>
+    <t>26.08.202692.0</t>
+  </si>
+  <si>
+    <t>26.08.202693.0</t>
+  </si>
+  <si>
+    <t>26.08.202694.0</t>
+  </si>
+  <si>
+    <t>26.08.202695.0</t>
+  </si>
+  <si>
+    <t>26.08.202696.0</t>
   </si>
 </sst>
 </file>
@@ -7587,7 +7875,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D2401"/>
+  <dimension ref="A1:D2497"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -31804,7 +32092,7 @@
         <v>1</v>
       </c>
       <c r="C1730">
-        <v>4937.7</v>
+        <v>4916.7</v>
       </c>
       <c r="D1730" t="s">
         <v>1732</v>
@@ -31818,7 +32106,7 @@
         <v>2</v>
       </c>
       <c r="C1731">
-        <v>4964</v>
+        <v>4931</v>
       </c>
       <c r="D1731" t="s">
         <v>1733</v>
@@ -31832,7 +32120,7 @@
         <v>3</v>
       </c>
       <c r="C1732">
-        <v>4973.5</v>
+        <v>4916.8</v>
       </c>
       <c r="D1732" t="s">
         <v>1734</v>
@@ -31846,7 +32134,7 @@
         <v>4</v>
       </c>
       <c r="C1733">
-        <v>4931.2</v>
+        <v>4910.5</v>
       </c>
       <c r="D1733" t="s">
         <v>1735</v>
@@ -31860,7 +32148,7 @@
         <v>5</v>
       </c>
       <c r="C1734">
-        <v>4958.6</v>
+        <v>4887</v>
       </c>
       <c r="D1734" t="s">
         <v>1736</v>
@@ -31874,7 +32162,7 @@
         <v>6</v>
       </c>
       <c r="C1735">
-        <v>4949.4</v>
+        <v>4838.9</v>
       </c>
       <c r="D1735" t="s">
         <v>1737</v>
@@ -31888,7 +32176,7 @@
         <v>7</v>
       </c>
       <c r="C1736">
-        <v>4945.2</v>
+        <v>4774.8</v>
       </c>
       <c r="D1736" t="s">
         <v>1738</v>
@@ -31902,7 +32190,7 @@
         <v>8</v>
       </c>
       <c r="C1737">
-        <v>4911.8</v>
+        <v>4684.4</v>
       </c>
       <c r="D1737" t="s">
         <v>1739</v>
@@ -31916,7 +32204,7 @@
         <v>9</v>
       </c>
       <c r="C1738">
-        <v>4906.9</v>
+        <v>4703.5</v>
       </c>
       <c r="D1738" t="s">
         <v>1740</v>
@@ -31930,7 +32218,7 @@
         <v>10</v>
       </c>
       <c r="C1739">
-        <v>4889.8</v>
+        <v>4639</v>
       </c>
       <c r="D1739" t="s">
         <v>1741</v>
@@ -31944,7 +32232,7 @@
         <v>11</v>
       </c>
       <c r="C1740">
-        <v>4892.6</v>
+        <v>4624.3</v>
       </c>
       <c r="D1740" t="s">
         <v>1742</v>
@@ -31958,7 +32246,7 @@
         <v>12</v>
       </c>
       <c r="C1741">
-        <v>4827.4</v>
+        <v>4510.5</v>
       </c>
       <c r="D1741" t="s">
         <v>1743</v>
@@ -31972,7 +32260,7 @@
         <v>13</v>
       </c>
       <c r="C1742">
-        <v>4766.2</v>
+        <v>4389.9</v>
       </c>
       <c r="D1742" t="s">
         <v>1744</v>
@@ -31986,7 +32274,7 @@
         <v>14</v>
       </c>
       <c r="C1743">
-        <v>4653.9</v>
+        <v>4430.1</v>
       </c>
       <c r="D1743" t="s">
         <v>1745</v>
@@ -32000,7 +32288,7 @@
         <v>15</v>
       </c>
       <c r="C1744">
-        <v>4643.9</v>
+        <v>4424.8</v>
       </c>
       <c r="D1744" t="s">
         <v>1746</v>
@@ -32014,7 +32302,7 @@
         <v>16</v>
       </c>
       <c r="C1745">
-        <v>4633.9</v>
+        <v>4364.9</v>
       </c>
       <c r="D1745" t="s">
         <v>1747</v>
@@ -32028,7 +32316,7 @@
         <v>17</v>
       </c>
       <c r="C1746">
-        <v>4648.2</v>
+        <v>4218.4</v>
       </c>
       <c r="D1746" t="s">
         <v>1748</v>
@@ -32042,7 +32330,7 @@
         <v>18</v>
       </c>
       <c r="C1747">
-        <v>4639.3</v>
+        <v>4205.2</v>
       </c>
       <c r="D1747" t="s">
         <v>1749</v>
@@ -32056,7 +32344,7 @@
         <v>19</v>
       </c>
       <c r="C1748">
-        <v>4633.9</v>
+        <v>4193.1</v>
       </c>
       <c r="D1748" t="s">
         <v>1750</v>
@@ -32070,7 +32358,7 @@
         <v>20</v>
       </c>
       <c r="C1749">
-        <v>4633.8</v>
+        <v>4181.3</v>
       </c>
       <c r="D1749" t="s">
         <v>1751</v>
@@ -32084,7 +32372,7 @@
         <v>21</v>
       </c>
       <c r="C1750">
-        <v>4567.6</v>
+        <v>4023.1</v>
       </c>
       <c r="D1750" t="s">
         <v>1752</v>
@@ -32098,7 +32386,7 @@
         <v>22</v>
       </c>
       <c r="C1751">
-        <v>4636.1</v>
+        <v>4006.8</v>
       </c>
       <c r="D1751" t="s">
         <v>1753</v>
@@ -32112,7 +32400,7 @@
         <v>23</v>
       </c>
       <c r="C1752">
-        <v>4699.9</v>
+        <v>3976.6</v>
       </c>
       <c r="D1752" t="s">
         <v>1754</v>
@@ -32126,7 +32414,7 @@
         <v>24</v>
       </c>
       <c r="C1753">
-        <v>4694</v>
+        <v>4068.3</v>
       </c>
       <c r="D1753" t="s">
         <v>1755</v>
@@ -32140,7 +32428,7 @@
         <v>25</v>
       </c>
       <c r="C1754">
-        <v>4786</v>
+        <v>4100.5</v>
       </c>
       <c r="D1754" t="s">
         <v>1756</v>
@@ -32154,7 +32442,7 @@
         <v>26</v>
       </c>
       <c r="C1755">
-        <v>4846</v>
+        <v>4123</v>
       </c>
       <c r="D1755" t="s">
         <v>1757</v>
@@ -32168,7 +32456,7 @@
         <v>27</v>
       </c>
       <c r="C1756">
-        <v>4978.2</v>
+        <v>4135.3</v>
       </c>
       <c r="D1756" t="s">
         <v>1758</v>
@@ -32182,7 +32470,7 @@
         <v>28</v>
       </c>
       <c r="C1757">
-        <v>5013</v>
+        <v>4231.9</v>
       </c>
       <c r="D1757" t="s">
         <v>1759</v>
@@ -32196,7 +32484,7 @@
         <v>29</v>
       </c>
       <c r="C1758">
-        <v>5085.3</v>
+        <v>4319.7</v>
       </c>
       <c r="D1758" t="s">
         <v>1760</v>
@@ -32210,7 +32498,7 @@
         <v>30</v>
       </c>
       <c r="C1759">
-        <v>5135.2</v>
+        <v>4428.6</v>
       </c>
       <c r="D1759" t="s">
         <v>1761</v>
@@ -32224,7 +32512,7 @@
         <v>31</v>
       </c>
       <c r="C1760">
-        <v>5228.6</v>
+        <v>4514.8</v>
       </c>
       <c r="D1760" t="s">
         <v>1762</v>
@@ -32238,7 +32526,7 @@
         <v>32</v>
       </c>
       <c r="C1761">
-        <v>5300.7</v>
+        <v>4616.3</v>
       </c>
       <c r="D1761" t="s">
         <v>1763</v>
@@ -32252,7 +32540,7 @@
         <v>33</v>
       </c>
       <c r="C1762">
-        <v>5678.6</v>
+        <v>4788.4</v>
       </c>
       <c r="D1762" t="s">
         <v>1764</v>
@@ -32266,7 +32554,7 @@
         <v>34</v>
       </c>
       <c r="C1763">
-        <v>5779.2</v>
+        <v>4945.3</v>
       </c>
       <c r="D1763" t="s">
         <v>1765</v>
@@ -32280,7 +32568,7 @@
         <v>35</v>
       </c>
       <c r="C1764">
-        <v>5869.1</v>
+        <v>5069.7</v>
       </c>
       <c r="D1764" t="s">
         <v>1766</v>
@@ -32294,7 +32582,7 @@
         <v>36</v>
       </c>
       <c r="C1765">
-        <v>5951.7</v>
+        <v>5159.4</v>
       </c>
       <c r="D1765" t="s">
         <v>1767</v>
@@ -32308,7 +32596,7 @@
         <v>37</v>
       </c>
       <c r="C1766">
-        <v>5840.9</v>
+        <v>5444.7</v>
       </c>
       <c r="D1766" t="s">
         <v>1768</v>
@@ -32322,7 +32610,7 @@
         <v>38</v>
       </c>
       <c r="C1767">
-        <v>5933.1</v>
+        <v>5557.5</v>
       </c>
       <c r="D1767" t="s">
         <v>1769</v>
@@ -32336,7 +32624,7 @@
         <v>39</v>
       </c>
       <c r="C1768">
-        <v>5972.2</v>
+        <v>5607.7</v>
       </c>
       <c r="D1768" t="s">
         <v>1770</v>
@@ -32350,7 +32638,7 @@
         <v>40</v>
       </c>
       <c r="C1769">
-        <v>6048.6</v>
+        <v>5570.9</v>
       </c>
       <c r="D1769" t="s">
         <v>1771</v>
@@ -32364,7 +32652,7 @@
         <v>41</v>
       </c>
       <c r="C1770">
-        <v>5955.7</v>
+        <v>5766.7</v>
       </c>
       <c r="D1770" t="s">
         <v>1772</v>
@@ -32378,7 +32666,7 @@
         <v>42</v>
       </c>
       <c r="C1771">
-        <v>6038.6</v>
+        <v>5752.9</v>
       </c>
       <c r="D1771" t="s">
         <v>1773</v>
@@ -32392,7 +32680,7 @@
         <v>43</v>
       </c>
       <c r="C1772">
-        <v>6117.9</v>
+        <v>5852.5</v>
       </c>
       <c r="D1772" t="s">
         <v>1774</v>
@@ -32406,7 +32694,7 @@
         <v>44</v>
       </c>
       <c r="C1773">
-        <v>6208.8</v>
+        <v>5931.1</v>
       </c>
       <c r="D1773" t="s">
         <v>1775</v>
@@ -32420,7 +32708,7 @@
         <v>45</v>
       </c>
       <c r="C1774">
-        <v>6271.8</v>
+        <v>5964</v>
       </c>
       <c r="D1774" t="s">
         <v>1776</v>
@@ -32434,7 +32722,7 @@
         <v>46</v>
       </c>
       <c r="C1775">
-        <v>6348.2</v>
+        <v>6007.2</v>
       </c>
       <c r="D1775" t="s">
         <v>1777</v>
@@ -32448,7 +32736,7 @@
         <v>47</v>
       </c>
       <c r="C1776">
-        <v>6403.9</v>
+        <v>6048.6</v>
       </c>
       <c r="D1776" t="s">
         <v>1778</v>
@@ -32462,7 +32750,7 @@
         <v>48</v>
       </c>
       <c r="C1777">
-        <v>6437.3</v>
+        <v>6100</v>
       </c>
       <c r="D1777" t="s">
         <v>1779</v>
@@ -32476,7 +32764,7 @@
         <v>49</v>
       </c>
       <c r="C1778">
-        <v>6500.8</v>
+        <v>6110.2</v>
       </c>
       <c r="D1778" t="s">
         <v>1780</v>
@@ -32490,7 +32778,7 @@
         <v>50</v>
       </c>
       <c r="C1779">
-        <v>6523.7</v>
+        <v>6080.5</v>
       </c>
       <c r="D1779" t="s">
         <v>1781</v>
@@ -32504,7 +32792,7 @@
         <v>51</v>
       </c>
       <c r="C1780">
-        <v>6510.5</v>
+        <v>6044.9</v>
       </c>
       <c r="D1780" t="s">
         <v>1782</v>
@@ -32518,7 +32806,7 @@
         <v>52</v>
       </c>
       <c r="C1781">
-        <v>6635</v>
+        <v>6041.8</v>
       </c>
       <c r="D1781" t="s">
         <v>1783</v>
@@ -32532,7 +32820,7 @@
         <v>53</v>
       </c>
       <c r="C1782">
-        <v>6500</v>
+        <v>5838.4</v>
       </c>
       <c r="D1782" t="s">
         <v>1784</v>
@@ -32546,7 +32834,7 @@
         <v>54</v>
       </c>
       <c r="C1783">
-        <v>6522</v>
+        <v>5773.5</v>
       </c>
       <c r="D1783" t="s">
         <v>1785</v>
@@ -32560,7 +32848,7 @@
         <v>55</v>
       </c>
       <c r="C1784">
-        <v>6551.6</v>
+        <v>5795.7</v>
       </c>
       <c r="D1784" t="s">
         <v>1786</v>
@@ -32574,7 +32862,7 @@
         <v>56</v>
       </c>
       <c r="C1785">
-        <v>6531.1</v>
+        <v>5743.1</v>
       </c>
       <c r="D1785" t="s">
         <v>1787</v>
@@ -32588,7 +32876,7 @@
         <v>57</v>
       </c>
       <c r="C1786">
-        <v>6664.2</v>
+        <v>5503.5</v>
       </c>
       <c r="D1786" t="s">
         <v>1788</v>
@@ -32602,7 +32890,7 @@
         <v>58</v>
       </c>
       <c r="C1787">
-        <v>6699.4</v>
+        <v>5514.8</v>
       </c>
       <c r="D1787" t="s">
         <v>1789</v>
@@ -32616,7 +32904,7 @@
         <v>59</v>
       </c>
       <c r="C1788">
-        <v>6750.8</v>
+        <v>5532.1</v>
       </c>
       <c r="D1788" t="s">
         <v>1790</v>
@@ -32630,7 +32918,7 @@
         <v>60</v>
       </c>
       <c r="C1789">
-        <v>6790.5</v>
+        <v>5546</v>
       </c>
       <c r="D1789" t="s">
         <v>1791</v>
@@ -32644,7 +32932,7 @@
         <v>61</v>
       </c>
       <c r="C1790">
-        <v>6905.8</v>
+        <v>5525.7</v>
       </c>
       <c r="D1790" t="s">
         <v>1792</v>
@@ -32658,7 +32946,7 @@
         <v>62</v>
       </c>
       <c r="C1791">
-        <v>6917.5</v>
+        <v>5504.5</v>
       </c>
       <c r="D1791" t="s">
         <v>1793</v>
@@ -32672,7 +32960,7 @@
         <v>63</v>
       </c>
       <c r="C1792">
-        <v>7007.7</v>
+        <v>5467.9</v>
       </c>
       <c r="D1792" t="s">
         <v>1794</v>
@@ -32686,7 +32974,7 @@
         <v>64</v>
       </c>
       <c r="C1793">
-        <v>7070.6</v>
+        <v>5454.3</v>
       </c>
       <c r="D1793" t="s">
         <v>1795</v>
@@ -32700,7 +32988,7 @@
         <v>65</v>
       </c>
       <c r="C1794">
-        <v>6971.7</v>
+        <v>5250.9</v>
       </c>
       <c r="D1794" t="s">
         <v>1796</v>
@@ -32714,7 +33002,7 @@
         <v>66</v>
       </c>
       <c r="C1795">
-        <v>6887.8</v>
+        <v>5202.7</v>
       </c>
       <c r="D1795" t="s">
         <v>1797</v>
@@ -32728,7 +33016,7 @@
         <v>67</v>
       </c>
       <c r="C1796">
-        <v>6836.9</v>
+        <v>5246.9</v>
       </c>
       <c r="D1796" t="s">
         <v>1798</v>
@@ -32742,7 +33030,7 @@
         <v>68</v>
       </c>
       <c r="C1797">
-        <v>6777.9</v>
+        <v>5210.5</v>
       </c>
       <c r="D1797" t="s">
         <v>1799</v>
@@ -32756,7 +33044,7 @@
         <v>69</v>
       </c>
       <c r="C1798">
-        <v>6779.5</v>
+        <v>5778.5</v>
       </c>
       <c r="D1798" t="s">
         <v>1800</v>
@@ -32770,7 +33058,7 @@
         <v>70</v>
       </c>
       <c r="C1799">
-        <v>6664.8</v>
+        <v>5681.6</v>
       </c>
       <c r="D1799" t="s">
         <v>1801</v>
@@ -32784,7 +33072,7 @@
         <v>71</v>
       </c>
       <c r="C1800">
-        <v>6533.8</v>
+        <v>5571.1</v>
       </c>
       <c r="D1800" t="s">
         <v>1802</v>
@@ -32798,7 +33086,7 @@
         <v>72</v>
       </c>
       <c r="C1801">
-        <v>6436.1</v>
+        <v>5486.6</v>
       </c>
       <c r="D1801" t="s">
         <v>1803</v>
@@ -32812,7 +33100,7 @@
         <v>73</v>
       </c>
       <c r="C1802">
-        <v>6304.7</v>
+        <v>5246.3</v>
       </c>
       <c r="D1802" t="s">
         <v>1804</v>
@@ -32826,7 +33114,7 @@
         <v>74</v>
       </c>
       <c r="C1803">
-        <v>6175.4</v>
+        <v>5132.8</v>
       </c>
       <c r="D1803" t="s">
         <v>1805</v>
@@ -32840,7 +33128,7 @@
         <v>75</v>
       </c>
       <c r="C1804">
-        <v>6064.9</v>
+        <v>5040.8</v>
       </c>
       <c r="D1804" t="s">
         <v>1806</v>
@@ -32854,7 +33142,7 @@
         <v>76</v>
       </c>
       <c r="C1805">
-        <v>5987.7</v>
+        <v>4921.8</v>
       </c>
       <c r="D1805" t="s">
         <v>1807</v>
@@ -32868,7 +33156,7 @@
         <v>77</v>
       </c>
       <c r="C1806">
-        <v>5699.9</v>
+        <v>4888.2</v>
       </c>
       <c r="D1806" t="s">
         <v>1808</v>
@@ -32882,7 +33170,7 @@
         <v>78</v>
       </c>
       <c r="C1807">
-        <v>5658.7</v>
+        <v>4856.1</v>
       </c>
       <c r="D1807" t="s">
         <v>1809</v>
@@ -32896,7 +33184,7 @@
         <v>79</v>
       </c>
       <c r="C1808">
-        <v>5588.5</v>
+        <v>4802.5</v>
       </c>
       <c r="D1808" t="s">
         <v>1810</v>
@@ -32910,7 +33198,7 @@
         <v>80</v>
       </c>
       <c r="C1809">
-        <v>5516.1</v>
+        <v>4836.6</v>
       </c>
       <c r="D1809" t="s">
         <v>1811</v>
@@ -32924,7 +33212,7 @@
         <v>81</v>
       </c>
       <c r="C1810">
-        <v>5863.8</v>
+        <v>5182.6</v>
       </c>
       <c r="D1810" t="s">
         <v>1812</v>
@@ -32938,7 +33226,7 @@
         <v>82</v>
       </c>
       <c r="C1811">
-        <v>5891</v>
+        <v>5262.9</v>
       </c>
       <c r="D1811" t="s">
         <v>1813</v>
@@ -32952,7 +33240,7 @@
         <v>83</v>
       </c>
       <c r="C1812">
-        <v>5847.5</v>
+        <v>5288.1</v>
       </c>
       <c r="D1812" t="s">
         <v>1814</v>
@@ -32966,7 +33254,7 @@
         <v>84</v>
       </c>
       <c r="C1813">
-        <v>5802.4</v>
+        <v>5301.1</v>
       </c>
       <c r="D1813" t="s">
         <v>1815</v>
@@ -32980,7 +33268,7 @@
         <v>85</v>
       </c>
       <c r="C1814">
-        <v>5775.6</v>
+        <v>5303.4</v>
       </c>
       <c r="D1814" t="s">
         <v>1816</v>
@@ -32994,7 +33282,7 @@
         <v>86</v>
       </c>
       <c r="C1815">
-        <v>5713.1</v>
+        <v>5309.8</v>
       </c>
       <c r="D1815" t="s">
         <v>1817</v>
@@ -33008,7 +33296,7 @@
         <v>87</v>
       </c>
       <c r="C1816">
-        <v>5706.5</v>
+        <v>5311.2</v>
       </c>
       <c r="D1816" t="s">
         <v>1818</v>
@@ -33022,7 +33310,7 @@
         <v>88</v>
       </c>
       <c r="C1817">
-        <v>5662.9</v>
+        <v>5324.9</v>
       </c>
       <c r="D1817" t="s">
         <v>1819</v>
@@ -33036,7 +33324,7 @@
         <v>89</v>
       </c>
       <c r="C1818">
-        <v>5411</v>
+        <v>5337.1</v>
       </c>
       <c r="D1818" t="s">
         <v>1820</v>
@@ -33050,7 +33338,7 @@
         <v>90</v>
       </c>
       <c r="C1819">
-        <v>5346.5</v>
+        <v>5290.6</v>
       </c>
       <c r="D1819" t="s">
         <v>1821</v>
@@ -33064,7 +33352,7 @@
         <v>91</v>
       </c>
       <c r="C1820">
-        <v>5248.9</v>
+        <v>5099.5</v>
       </c>
       <c r="D1820" t="s">
         <v>1822</v>
@@ -33078,7 +33366,7 @@
         <v>92</v>
       </c>
       <c r="C1821">
-        <v>5238.2</v>
+        <v>5060.2</v>
       </c>
       <c r="D1821" t="s">
         <v>1823</v>
@@ -33092,7 +33380,7 @@
         <v>93</v>
       </c>
       <c r="C1822">
-        <v>5125.2</v>
+        <v>4852.1</v>
       </c>
       <c r="D1822" t="s">
         <v>1824</v>
@@ -33106,7 +33394,7 @@
         <v>94</v>
       </c>
       <c r="C1823">
-        <v>5042.4</v>
+        <v>4830.1</v>
       </c>
       <c r="D1823" t="s">
         <v>1825</v>
@@ -33120,7 +33408,7 @@
         <v>95</v>
       </c>
       <c r="C1824">
-        <v>5043.1</v>
+        <v>4826.8</v>
       </c>
       <c r="D1824" t="s">
         <v>1826</v>
@@ -33134,7 +33422,7 @@
         <v>96</v>
       </c>
       <c r="C1825">
-        <v>5052.2</v>
+        <v>4772.7</v>
       </c>
       <c r="D1825" t="s">
         <v>1827</v>
@@ -33148,7 +33436,7 @@
         <v>1</v>
       </c>
       <c r="C1826">
-        <v>5481.1</v>
+        <v>5006.7</v>
       </c>
       <c r="D1826" t="s">
         <v>1828</v>
@@ -33162,7 +33450,7 @@
         <v>2</v>
       </c>
       <c r="C1827">
-        <v>5560.8</v>
+        <v>5051</v>
       </c>
       <c r="D1827" t="s">
         <v>1829</v>
@@ -33176,7 +33464,7 @@
         <v>3</v>
       </c>
       <c r="C1828">
-        <v>5590.1</v>
+        <v>5036.8</v>
       </c>
       <c r="D1828" t="s">
         <v>1830</v>
@@ -33190,7 +33478,7 @@
         <v>4</v>
       </c>
       <c r="C1829">
-        <v>5624.3</v>
+        <v>5020.5</v>
       </c>
       <c r="D1829" t="s">
         <v>1831</v>
@@ -33204,7 +33492,7 @@
         <v>5</v>
       </c>
       <c r="C1830">
-        <v>5645.1</v>
+        <v>5007</v>
       </c>
       <c r="D1830" t="s">
         <v>1832</v>
@@ -33218,7 +33506,7 @@
         <v>6</v>
       </c>
       <c r="C1831">
-        <v>5656.4</v>
+        <v>4948.9</v>
       </c>
       <c r="D1831" t="s">
         <v>1833</v>
@@ -33232,7 +33520,7 @@
         <v>7</v>
       </c>
       <c r="C1832">
-        <v>5659.5</v>
+        <v>4894.8</v>
       </c>
       <c r="D1832" t="s">
         <v>1834</v>
@@ -33246,7 +33534,7 @@
         <v>8</v>
       </c>
       <c r="C1833">
-        <v>5664.1</v>
+        <v>4784.4</v>
       </c>
       <c r="D1833" t="s">
         <v>1835</v>
@@ -33260,7 +33548,7 @@
         <v>9</v>
       </c>
       <c r="C1834">
-        <v>5679.1</v>
+        <v>4803.5</v>
       </c>
       <c r="D1834" t="s">
         <v>1836</v>
@@ -33274,7 +33562,7 @@
         <v>10</v>
       </c>
       <c r="C1835">
-        <v>5664.7</v>
+        <v>4709</v>
       </c>
       <c r="D1835" t="s">
         <v>1837</v>
@@ -33288,7 +33576,7 @@
         <v>11</v>
       </c>
       <c r="C1836">
-        <v>5658.5</v>
+        <v>4634.3</v>
       </c>
       <c r="D1836" t="s">
         <v>1838</v>
@@ -33302,7 +33590,7 @@
         <v>12</v>
       </c>
       <c r="C1837">
-        <v>5676.5</v>
+        <v>4500.5</v>
       </c>
       <c r="D1837" t="s">
         <v>1839</v>
@@ -33316,7 +33604,7 @@
         <v>13</v>
       </c>
       <c r="C1838">
-        <v>5553.5</v>
+        <v>4379.9</v>
       </c>
       <c r="D1838" t="s">
         <v>1840</v>
@@ -33330,7 +33618,7 @@
         <v>14</v>
       </c>
       <c r="C1839">
-        <v>5567.4</v>
+        <v>4430.1</v>
       </c>
       <c r="D1839" t="s">
         <v>1841</v>
@@ -33344,7 +33632,7 @@
         <v>15</v>
       </c>
       <c r="C1840">
-        <v>5586.4</v>
+        <v>4454.8</v>
       </c>
       <c r="D1840" t="s">
         <v>1842</v>
@@ -33358,7 +33646,7 @@
         <v>16</v>
       </c>
       <c r="C1841">
-        <v>5593.9</v>
+        <v>4404.9</v>
       </c>
       <c r="D1841" t="s">
         <v>1843</v>
@@ -33372,7 +33660,7 @@
         <v>17</v>
       </c>
       <c r="C1842">
-        <v>5610.5</v>
+        <v>4238.4</v>
       </c>
       <c r="D1842" t="s">
         <v>1844</v>
@@ -33386,7 +33674,7 @@
         <v>18</v>
       </c>
       <c r="C1843">
-        <v>5620</v>
+        <v>4205.2</v>
       </c>
       <c r="D1843" t="s">
         <v>1845</v>
@@ -33400,7 +33688,7 @@
         <v>19</v>
       </c>
       <c r="C1844">
-        <v>5593.5</v>
+        <v>4183.1</v>
       </c>
       <c r="D1844" t="s">
         <v>1846</v>
@@ -33414,7 +33702,7 @@
         <v>20</v>
       </c>
       <c r="C1845">
-        <v>5600.7</v>
+        <v>4171.3</v>
       </c>
       <c r="D1845" t="s">
         <v>1847</v>
@@ -33428,7 +33716,7 @@
         <v>21</v>
       </c>
       <c r="C1846">
-        <v>5634.2</v>
+        <v>4033.1</v>
       </c>
       <c r="D1846" t="s">
         <v>1848</v>
@@ -33442,7 +33730,7 @@
         <v>22</v>
       </c>
       <c r="C1847">
-        <v>5644.9</v>
+        <v>4046.8</v>
       </c>
       <c r="D1847" t="s">
         <v>1849</v>
@@ -33456,7 +33744,7 @@
         <v>23</v>
       </c>
       <c r="C1848">
-        <v>5706</v>
+        <v>4056.6</v>
       </c>
       <c r="D1848" t="s">
         <v>1850</v>
@@ -33470,7 +33758,7 @@
         <v>24</v>
       </c>
       <c r="C1849">
-        <v>5733.2</v>
+        <v>4198.3</v>
       </c>
       <c r="D1849" t="s">
         <v>1851</v>
@@ -33484,7 +33772,7 @@
         <v>25</v>
       </c>
       <c r="C1850">
-        <v>5714.8</v>
+        <v>4270.5</v>
       </c>
       <c r="D1850" t="s">
         <v>1852</v>
@@ -33498,7 +33786,7 @@
         <v>26</v>
       </c>
       <c r="C1851">
-        <v>5715.7</v>
+        <v>4293</v>
       </c>
       <c r="D1851" t="s">
         <v>1853</v>
@@ -33512,7 +33800,7 @@
         <v>27</v>
       </c>
       <c r="C1852">
-        <v>5761.8</v>
+        <v>4295.3</v>
       </c>
       <c r="D1852" t="s">
         <v>1854</v>
@@ -33526,7 +33814,7 @@
         <v>28</v>
       </c>
       <c r="C1853">
-        <v>5825.1</v>
+        <v>4361.9</v>
       </c>
       <c r="D1853" t="s">
         <v>1855</v>
@@ -33540,7 +33828,7 @@
         <v>29</v>
       </c>
       <c r="C1854">
-        <v>6086.9</v>
+        <v>4409.7</v>
       </c>
       <c r="D1854" t="s">
         <v>1856</v>
@@ -33554,7 +33842,7 @@
         <v>30</v>
       </c>
       <c r="C1855">
-        <v>6127.8</v>
+        <v>4438.6</v>
       </c>
       <c r="D1855" t="s">
         <v>1857</v>
@@ -33568,7 +33856,7 @@
         <v>31</v>
       </c>
       <c r="C1856">
-        <v>6162.2</v>
+        <v>4454.8</v>
       </c>
       <c r="D1856" t="s">
         <v>1858</v>
@@ -33582,7 +33870,7 @@
         <v>32</v>
       </c>
       <c r="C1857">
-        <v>6219</v>
+        <v>4506.3</v>
       </c>
       <c r="D1857" t="s">
         <v>1859</v>
@@ -33596,7 +33884,7 @@
         <v>33</v>
       </c>
       <c r="C1858">
-        <v>6215.9</v>
+        <v>4568.4</v>
       </c>
       <c r="D1858" t="s">
         <v>1860</v>
@@ -33610,7 +33898,7 @@
         <v>34</v>
       </c>
       <c r="C1859">
-        <v>6303.4</v>
+        <v>4645.3</v>
       </c>
       <c r="D1859" t="s">
         <v>1861</v>
@@ -33624,7 +33912,7 @@
         <v>35</v>
       </c>
       <c r="C1860">
-        <v>6405.8</v>
+        <v>4709.7</v>
       </c>
       <c r="D1860" t="s">
         <v>1862</v>
@@ -33638,7 +33926,7 @@
         <v>36</v>
       </c>
       <c r="C1861">
-        <v>6346.1</v>
+        <v>4739.4</v>
       </c>
       <c r="D1861" t="s">
         <v>1863</v>
@@ -33652,7 +33940,7 @@
         <v>37</v>
       </c>
       <c r="C1862">
-        <v>6083.5</v>
+        <v>4984.7</v>
       </c>
       <c r="D1862" t="s">
         <v>1864</v>
@@ -33666,7 +33954,7 @@
         <v>38</v>
       </c>
       <c r="C1863">
-        <v>6131.6</v>
+        <v>5057.5</v>
       </c>
       <c r="D1863" t="s">
         <v>1865</v>
@@ -33680,7 +33968,7 @@
         <v>39</v>
       </c>
       <c r="C1864">
-        <v>6203.8</v>
+        <v>5087.7</v>
       </c>
       <c r="D1864" t="s">
         <v>1866</v>
@@ -33694,7 +33982,7 @@
         <v>40</v>
       </c>
       <c r="C1865">
-        <v>6220.9</v>
+        <v>5030.9</v>
       </c>
       <c r="D1865" t="s">
         <v>1867</v>
@@ -33708,7 +33996,7 @@
         <v>41</v>
       </c>
       <c r="C1866">
-        <v>6143.4</v>
+        <v>5226.7</v>
       </c>
       <c r="D1866" t="s">
         <v>1868</v>
@@ -33722,7 +34010,7 @@
         <v>42</v>
       </c>
       <c r="C1867">
-        <v>6154.8</v>
+        <v>5202.9</v>
       </c>
       <c r="D1867" t="s">
         <v>1869</v>
@@ -33736,7 +34024,7 @@
         <v>43</v>
       </c>
       <c r="C1868">
-        <v>6212.9</v>
+        <v>5322.5</v>
       </c>
       <c r="D1868" t="s">
         <v>1870</v>
@@ -33750,7 +34038,7 @@
         <v>44</v>
       </c>
       <c r="C1869">
-        <v>6237.1</v>
+        <v>5421.1</v>
       </c>
       <c r="D1869" t="s">
         <v>1871</v>
@@ -33764,7 +34052,7 @@
         <v>45</v>
       </c>
       <c r="C1870">
-        <v>5412.5</v>
+        <v>5494</v>
       </c>
       <c r="D1870" t="s">
         <v>1872</v>
@@ -33778,7 +34066,7 @@
         <v>46</v>
       </c>
       <c r="C1871">
-        <v>5434.4</v>
+        <v>5587.2</v>
       </c>
       <c r="D1871" t="s">
         <v>1873</v>
@@ -33792,7 +34080,7 @@
         <v>47</v>
       </c>
       <c r="C1872">
-        <v>5425.1</v>
+        <v>5678.6</v>
       </c>
       <c r="D1872" t="s">
         <v>1874</v>
@@ -33806,7 +34094,7 @@
         <v>48</v>
       </c>
       <c r="C1873">
-        <v>5479.3</v>
+        <v>5780</v>
       </c>
       <c r="D1873" t="s">
         <v>1875</v>
@@ -33820,7 +34108,7 @@
         <v>49</v>
       </c>
       <c r="C1874">
-        <v>5312.3</v>
+        <v>5860.2</v>
       </c>
       <c r="D1874" t="s">
         <v>1876</v>
@@ -33834,7 +34122,7 @@
         <v>50</v>
       </c>
       <c r="C1875">
-        <v>5337.7</v>
+        <v>5890.5</v>
       </c>
       <c r="D1875" t="s">
         <v>1877</v>
@@ -33848,7 +34136,7 @@
         <v>51</v>
       </c>
       <c r="C1876">
-        <v>5228</v>
+        <v>5914.9</v>
       </c>
       <c r="D1876" t="s">
         <v>1878</v>
@@ -33862,7 +34150,7 @@
         <v>52</v>
       </c>
       <c r="C1877">
-        <v>5192.9</v>
+        <v>5941.8</v>
       </c>
       <c r="D1877" t="s">
         <v>1879</v>
@@ -33876,7 +34164,7 @@
         <v>53</v>
       </c>
       <c r="C1878">
-        <v>5265.8</v>
+        <v>5778.4</v>
       </c>
       <c r="D1878" t="s">
         <v>1880</v>
@@ -33890,7 +34178,7 @@
         <v>54</v>
       </c>
       <c r="C1879">
-        <v>5221.9</v>
+        <v>5733.5</v>
       </c>
       <c r="D1879" t="s">
         <v>1881</v>
@@ -33904,7 +34192,7 @@
         <v>55</v>
       </c>
       <c r="C1880">
-        <v>5227.6</v>
+        <v>5775.7</v>
       </c>
       <c r="D1880" t="s">
         <v>1882</v>
@@ -33918,7 +34206,7 @@
         <v>56</v>
       </c>
       <c r="C1881">
-        <v>5259.4</v>
+        <v>5733.1</v>
       </c>
       <c r="D1881" t="s">
         <v>1883</v>
@@ -33932,7 +34220,7 @@
         <v>57</v>
       </c>
       <c r="C1882">
-        <v>5283.4</v>
+        <v>5513.5</v>
       </c>
       <c r="D1882" t="s">
         <v>1884</v>
@@ -33946,7 +34234,7 @@
         <v>58</v>
       </c>
       <c r="C1883">
-        <v>5299.3</v>
+        <v>5544.8</v>
       </c>
       <c r="D1883" t="s">
         <v>1885</v>
@@ -33960,7 +34248,7 @@
         <v>59</v>
       </c>
       <c r="C1884">
-        <v>5322.4</v>
+        <v>5582.1</v>
       </c>
       <c r="D1884" t="s">
         <v>1886</v>
@@ -33974,7 +34262,7 @@
         <v>60</v>
       </c>
       <c r="C1885">
-        <v>5360.2</v>
+        <v>5636</v>
       </c>
       <c r="D1885" t="s">
         <v>1887</v>
@@ -33988,7 +34276,7 @@
         <v>61</v>
       </c>
       <c r="C1886">
-        <v>5550.9</v>
+        <v>5655.7</v>
       </c>
       <c r="D1886" t="s">
         <v>1888</v>
@@ -34002,7 +34290,7 @@
         <v>62</v>
       </c>
       <c r="C1887">
-        <v>5590.1</v>
+        <v>5674.5</v>
       </c>
       <c r="D1887" t="s">
         <v>1889</v>
@@ -34016,7 +34304,7 @@
         <v>63</v>
       </c>
       <c r="C1888">
-        <v>5615.6</v>
+        <v>5687.9</v>
       </c>
       <c r="D1888" t="s">
         <v>1890</v>
@@ -34030,7 +34318,7 @@
         <v>64</v>
       </c>
       <c r="C1889">
-        <v>5607.7</v>
+        <v>5714.3</v>
       </c>
       <c r="D1889" t="s">
         <v>1891</v>
@@ -34044,7 +34332,7 @@
         <v>65</v>
       </c>
       <c r="C1890">
-        <v>5473</v>
+        <v>5530.9</v>
       </c>
       <c r="D1890" t="s">
         <v>1892</v>
@@ -34058,7 +34346,7 @@
         <v>66</v>
       </c>
       <c r="C1891">
-        <v>5434.1</v>
+        <v>5492.7</v>
       </c>
       <c r="D1891" t="s">
         <v>1893</v>
@@ -34072,7 +34360,7 @@
         <v>67</v>
       </c>
       <c r="C1892">
-        <v>5401.6</v>
+        <v>5546.9</v>
       </c>
       <c r="D1892" t="s">
         <v>1894</v>
@@ -34086,7 +34374,7 @@
         <v>68</v>
       </c>
       <c r="C1893">
-        <v>5384.9</v>
+        <v>5510.5</v>
       </c>
       <c r="D1893" t="s">
         <v>1895</v>
@@ -34100,7 +34388,7 @@
         <v>69</v>
       </c>
       <c r="C1894">
-        <v>5786.3</v>
+        <v>6078.5</v>
       </c>
       <c r="D1894" t="s">
         <v>1896</v>
@@ -34114,7 +34402,7 @@
         <v>70</v>
       </c>
       <c r="C1895">
-        <v>5710</v>
+        <v>5981.6</v>
       </c>
       <c r="D1895" t="s">
         <v>1897</v>
@@ -34128,7 +34416,7 @@
         <v>71</v>
       </c>
       <c r="C1896">
-        <v>5588.5</v>
+        <v>5871.1</v>
       </c>
       <c r="D1896" t="s">
         <v>1898</v>
@@ -34142,7 +34430,7 @@
         <v>72</v>
       </c>
       <c r="C1897">
-        <v>5446.4</v>
+        <v>5786.6</v>
       </c>
       <c r="D1897" t="s">
         <v>1899</v>
@@ -34156,7 +34444,7 @@
         <v>73</v>
       </c>
       <c r="C1898">
-        <v>5439.2</v>
+        <v>5556.3</v>
       </c>
       <c r="D1898" t="s">
         <v>1900</v>
@@ -34170,7 +34458,7 @@
         <v>74</v>
       </c>
       <c r="C1899">
-        <v>5275.3</v>
+        <v>5432.8</v>
       </c>
       <c r="D1899" t="s">
         <v>1901</v>
@@ -34184,7 +34472,7 @@
         <v>75</v>
       </c>
       <c r="C1900">
-        <v>5086.7</v>
+        <v>5340.8</v>
       </c>
       <c r="D1900" t="s">
         <v>1902</v>
@@ -34198,7 +34486,7 @@
         <v>76</v>
       </c>
       <c r="C1901">
-        <v>5003.1</v>
+        <v>5231.8</v>
       </c>
       <c r="D1901" t="s">
         <v>1903</v>
@@ -34212,7 +34500,7 @@
         <v>77</v>
       </c>
       <c r="C1902">
-        <v>4980.3</v>
+        <v>5208.2</v>
       </c>
       <c r="D1902" t="s">
         <v>1904</v>
@@ -34226,7 +34514,7 @@
         <v>78</v>
       </c>
       <c r="C1903">
-        <v>4889.2</v>
+        <v>5176.1</v>
       </c>
       <c r="D1903" t="s">
         <v>1905</v>
@@ -34240,7 +34528,7 @@
         <v>79</v>
       </c>
       <c r="C1904">
-        <v>4786.6</v>
+        <v>5112.5</v>
       </c>
       <c r="D1904" t="s">
         <v>1906</v>
@@ -34254,7 +34542,7 @@
         <v>80</v>
       </c>
       <c r="C1905">
-        <v>4774.2</v>
+        <v>5106.6</v>
       </c>
       <c r="D1905" t="s">
         <v>1907</v>
@@ -34268,7 +34556,7 @@
         <v>81</v>
       </c>
       <c r="C1906">
-        <v>5143.7</v>
+        <v>5422.6</v>
       </c>
       <c r="D1906" t="s">
         <v>1908</v>
@@ -34282,7 +34570,7 @@
         <v>82</v>
       </c>
       <c r="C1907">
-        <v>5207.8</v>
+        <v>5492.9</v>
       </c>
       <c r="D1907" t="s">
         <v>1909</v>
@@ -34296,7 +34584,7 @@
         <v>83</v>
       </c>
       <c r="C1908">
-        <v>5206.2</v>
+        <v>5508.1</v>
       </c>
       <c r="D1908" t="s">
         <v>1910</v>
@@ -34310,7 +34598,7 @@
         <v>84</v>
       </c>
       <c r="C1909">
-        <v>5185.4</v>
+        <v>5491.1</v>
       </c>
       <c r="D1909" t="s">
         <v>1911</v>
@@ -34324,7 +34612,7 @@
         <v>85</v>
       </c>
       <c r="C1910">
-        <v>5138.2</v>
+        <v>5493.4</v>
       </c>
       <c r="D1910" t="s">
         <v>1912</v>
@@ -34338,7 +34626,7 @@
         <v>86</v>
       </c>
       <c r="C1911">
-        <v>5113.6</v>
+        <v>5519.8</v>
       </c>
       <c r="D1911" t="s">
         <v>1913</v>
@@ -34352,7 +34640,7 @@
         <v>87</v>
       </c>
       <c r="C1912">
-        <v>5177.7</v>
+        <v>5521.2</v>
       </c>
       <c r="D1912" t="s">
         <v>1914</v>
@@ -34366,7 +34654,7 @@
         <v>88</v>
       </c>
       <c r="C1913">
-        <v>5122.2</v>
+        <v>5514.9</v>
       </c>
       <c r="D1913" t="s">
         <v>1915</v>
@@ -34380,7 +34668,7 @@
         <v>89</v>
       </c>
       <c r="C1914">
-        <v>4754.4</v>
+        <v>5457.1</v>
       </c>
       <c r="D1914" t="s">
         <v>1916</v>
@@ -34394,7 +34682,7 @@
         <v>90</v>
       </c>
       <c r="C1915">
-        <v>4698.5</v>
+        <v>5400.6</v>
       </c>
       <c r="D1915" t="s">
         <v>1917</v>
@@ -34408,7 +34696,7 @@
         <v>91</v>
       </c>
       <c r="C1916">
-        <v>4622.5</v>
+        <v>5209.5</v>
       </c>
       <c r="D1916" t="s">
         <v>1918</v>
@@ -34422,7 +34710,7 @@
         <v>92</v>
       </c>
       <c r="C1917">
-        <v>4542.2</v>
+        <v>5190.2</v>
       </c>
       <c r="D1917" t="s">
         <v>1919</v>
@@ -34436,7 +34724,7 @@
         <v>93</v>
       </c>
       <c r="C1918">
-        <v>4241</v>
+        <v>4962.1</v>
       </c>
       <c r="D1918" t="s">
         <v>1920</v>
@@ -34450,7 +34738,7 @@
         <v>94</v>
       </c>
       <c r="C1919">
-        <v>4127.8</v>
+        <v>4900.1</v>
       </c>
       <c r="D1919" t="s">
         <v>1921</v>
@@ -34464,7 +34752,7 @@
         <v>95</v>
       </c>
       <c r="C1920">
-        <v>4154</v>
+        <v>4926.8</v>
       </c>
       <c r="D1920" t="s">
         <v>1922</v>
@@ -34478,7 +34766,7 @@
         <v>96</v>
       </c>
       <c r="C1921">
-        <v>4140.3</v>
+        <v>4892.7</v>
       </c>
       <c r="D1921" t="s">
         <v>1923</v>
@@ -41202,6 +41490,1350 @@
       </c>
       <c r="D2401" t="s">
         <v>2403</v>
+      </c>
+    </row>
+    <row r="2402" spans="1:4">
+      <c r="A2402" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2402">
+        <v>1</v>
+      </c>
+      <c r="C2402">
+        <v>5077.7</v>
+      </c>
+      <c r="D2402" t="s">
+        <v>2404</v>
+      </c>
+    </row>
+    <row r="2403" spans="1:4">
+      <c r="A2403" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2403">
+        <v>2</v>
+      </c>
+      <c r="C2403">
+        <v>5104</v>
+      </c>
+      <c r="D2403" t="s">
+        <v>2405</v>
+      </c>
+    </row>
+    <row r="2404" spans="1:4">
+      <c r="A2404" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2404">
+        <v>3</v>
+      </c>
+      <c r="C2404">
+        <v>5123.5</v>
+      </c>
+      <c r="D2404" t="s">
+        <v>2406</v>
+      </c>
+    </row>
+    <row r="2405" spans="1:4">
+      <c r="A2405" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2405">
+        <v>4</v>
+      </c>
+      <c r="C2405">
+        <v>5091.2</v>
+      </c>
+      <c r="D2405" t="s">
+        <v>2407</v>
+      </c>
+    </row>
+    <row r="2406" spans="1:4">
+      <c r="A2406" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2406">
+        <v>5</v>
+      </c>
+      <c r="C2406">
+        <v>5108.6</v>
+      </c>
+      <c r="D2406" t="s">
+        <v>2408</v>
+      </c>
+    </row>
+    <row r="2407" spans="1:4">
+      <c r="A2407" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2407">
+        <v>6</v>
+      </c>
+      <c r="C2407">
+        <v>5099.4</v>
+      </c>
+      <c r="D2407" t="s">
+        <v>2409</v>
+      </c>
+    </row>
+    <row r="2408" spans="1:4">
+      <c r="A2408" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2408">
+        <v>7</v>
+      </c>
+      <c r="C2408">
+        <v>5085.2</v>
+      </c>
+      <c r="D2408" t="s">
+        <v>2410</v>
+      </c>
+    </row>
+    <row r="2409" spans="1:4">
+      <c r="A2409" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2409">
+        <v>8</v>
+      </c>
+      <c r="C2409">
+        <v>5061.8</v>
+      </c>
+      <c r="D2409" t="s">
+        <v>2411</v>
+      </c>
+    </row>
+    <row r="2410" spans="1:4">
+      <c r="A2410" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2410">
+        <v>9</v>
+      </c>
+      <c r="C2410">
+        <v>5056.9</v>
+      </c>
+      <c r="D2410" t="s">
+        <v>2412</v>
+      </c>
+    </row>
+    <row r="2411" spans="1:4">
+      <c r="A2411" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2411">
+        <v>10</v>
+      </c>
+      <c r="C2411">
+        <v>5049.8</v>
+      </c>
+      <c r="D2411" t="s">
+        <v>2413</v>
+      </c>
+    </row>
+    <row r="2412" spans="1:4">
+      <c r="A2412" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2412">
+        <v>11</v>
+      </c>
+      <c r="C2412">
+        <v>5042.6</v>
+      </c>
+      <c r="D2412" t="s">
+        <v>2414</v>
+      </c>
+    </row>
+    <row r="2413" spans="1:4">
+      <c r="A2413" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2413">
+        <v>12</v>
+      </c>
+      <c r="C2413">
+        <v>4977.4</v>
+      </c>
+      <c r="D2413" t="s">
+        <v>2415</v>
+      </c>
+    </row>
+    <row r="2414" spans="1:4">
+      <c r="A2414" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2414">
+        <v>13</v>
+      </c>
+      <c r="C2414">
+        <v>4916.2</v>
+      </c>
+      <c r="D2414" t="s">
+        <v>2416</v>
+      </c>
+    </row>
+    <row r="2415" spans="1:4">
+      <c r="A2415" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2415">
+        <v>14</v>
+      </c>
+      <c r="C2415">
+        <v>4803.9</v>
+      </c>
+      <c r="D2415" t="s">
+        <v>2417</v>
+      </c>
+    </row>
+    <row r="2416" spans="1:4">
+      <c r="A2416" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2416">
+        <v>15</v>
+      </c>
+      <c r="C2416">
+        <v>4803.9</v>
+      </c>
+      <c r="D2416" t="s">
+        <v>2418</v>
+      </c>
+    </row>
+    <row r="2417" spans="1:4">
+      <c r="A2417" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2417">
+        <v>16</v>
+      </c>
+      <c r="C2417">
+        <v>4773.9</v>
+      </c>
+      <c r="D2417" t="s">
+        <v>2419</v>
+      </c>
+    </row>
+    <row r="2418" spans="1:4">
+      <c r="A2418" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2418">
+        <v>17</v>
+      </c>
+      <c r="C2418">
+        <v>4798.2</v>
+      </c>
+      <c r="D2418" t="s">
+        <v>2420</v>
+      </c>
+    </row>
+    <row r="2419" spans="1:4">
+      <c r="A2419" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2419">
+        <v>18</v>
+      </c>
+      <c r="C2419">
+        <v>4789.3</v>
+      </c>
+      <c r="D2419" t="s">
+        <v>2421</v>
+      </c>
+    </row>
+    <row r="2420" spans="1:4">
+      <c r="A2420" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2420">
+        <v>19</v>
+      </c>
+      <c r="C2420">
+        <v>4793.9</v>
+      </c>
+      <c r="D2420" t="s">
+        <v>2422</v>
+      </c>
+    </row>
+    <row r="2421" spans="1:4">
+      <c r="A2421" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2421">
+        <v>20</v>
+      </c>
+      <c r="C2421">
+        <v>4793.8</v>
+      </c>
+      <c r="D2421" t="s">
+        <v>2423</v>
+      </c>
+    </row>
+    <row r="2422" spans="1:4">
+      <c r="A2422" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2422">
+        <v>21</v>
+      </c>
+      <c r="C2422">
+        <v>4727.6</v>
+      </c>
+      <c r="D2422" t="s">
+        <v>2424</v>
+      </c>
+    </row>
+    <row r="2423" spans="1:4">
+      <c r="A2423" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2423">
+        <v>22</v>
+      </c>
+      <c r="C2423">
+        <v>4796.1</v>
+      </c>
+      <c r="D2423" t="s">
+        <v>2425</v>
+      </c>
+    </row>
+    <row r="2424" spans="1:4">
+      <c r="A2424" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2424">
+        <v>23</v>
+      </c>
+      <c r="C2424">
+        <v>4849.9</v>
+      </c>
+      <c r="D2424" t="s">
+        <v>2426</v>
+      </c>
+    </row>
+    <row r="2425" spans="1:4">
+      <c r="A2425" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2425">
+        <v>24</v>
+      </c>
+      <c r="C2425">
+        <v>4844</v>
+      </c>
+      <c r="D2425" t="s">
+        <v>2427</v>
+      </c>
+    </row>
+    <row r="2426" spans="1:4">
+      <c r="A2426" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2426">
+        <v>25</v>
+      </c>
+      <c r="C2426">
+        <v>4936</v>
+      </c>
+      <c r="D2426" t="s">
+        <v>2428</v>
+      </c>
+    </row>
+    <row r="2427" spans="1:4">
+      <c r="A2427" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2427">
+        <v>26</v>
+      </c>
+      <c r="C2427">
+        <v>4986</v>
+      </c>
+      <c r="D2427" t="s">
+        <v>2429</v>
+      </c>
+    </row>
+    <row r="2428" spans="1:4">
+      <c r="A2428" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2428">
+        <v>27</v>
+      </c>
+      <c r="C2428">
+        <v>5128.2</v>
+      </c>
+      <c r="D2428" t="s">
+        <v>2430</v>
+      </c>
+    </row>
+    <row r="2429" spans="1:4">
+      <c r="A2429" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2429">
+        <v>28</v>
+      </c>
+      <c r="C2429">
+        <v>5173</v>
+      </c>
+      <c r="D2429" t="s">
+        <v>2431</v>
+      </c>
+    </row>
+    <row r="2430" spans="1:4">
+      <c r="A2430" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2430">
+        <v>29</v>
+      </c>
+      <c r="C2430">
+        <v>5265.3</v>
+      </c>
+      <c r="D2430" t="s">
+        <v>2432</v>
+      </c>
+    </row>
+    <row r="2431" spans="1:4">
+      <c r="A2431" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2431">
+        <v>30</v>
+      </c>
+      <c r="C2431">
+        <v>5335.2</v>
+      </c>
+      <c r="D2431" t="s">
+        <v>2433</v>
+      </c>
+    </row>
+    <row r="2432" spans="1:4">
+      <c r="A2432" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2432">
+        <v>31</v>
+      </c>
+      <c r="C2432">
+        <v>5458.6</v>
+      </c>
+      <c r="D2432" t="s">
+        <v>2434</v>
+      </c>
+    </row>
+    <row r="2433" spans="1:4">
+      <c r="A2433" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2433">
+        <v>32</v>
+      </c>
+      <c r="C2433">
+        <v>5560.7</v>
+      </c>
+      <c r="D2433" t="s">
+        <v>2435</v>
+      </c>
+    </row>
+    <row r="2434" spans="1:4">
+      <c r="A2434" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2434">
+        <v>33</v>
+      </c>
+      <c r="C2434">
+        <v>5958.6</v>
+      </c>
+      <c r="D2434" t="s">
+        <v>2436</v>
+      </c>
+    </row>
+    <row r="2435" spans="1:4">
+      <c r="A2435" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2435">
+        <v>34</v>
+      </c>
+      <c r="C2435">
+        <v>6069.2</v>
+      </c>
+      <c r="D2435" t="s">
+        <v>2437</v>
+      </c>
+    </row>
+    <row r="2436" spans="1:4">
+      <c r="A2436" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2436">
+        <v>35</v>
+      </c>
+      <c r="C2436">
+        <v>6149.1</v>
+      </c>
+      <c r="D2436" t="s">
+        <v>2438</v>
+      </c>
+    </row>
+    <row r="2437" spans="1:4">
+      <c r="A2437" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2437">
+        <v>36</v>
+      </c>
+      <c r="C2437">
+        <v>6201.7</v>
+      </c>
+      <c r="D2437" t="s">
+        <v>2439</v>
+      </c>
+    </row>
+    <row r="2438" spans="1:4">
+      <c r="A2438" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2438">
+        <v>37</v>
+      </c>
+      <c r="C2438">
+        <v>6060.9</v>
+      </c>
+      <c r="D2438" t="s">
+        <v>2440</v>
+      </c>
+    </row>
+    <row r="2439" spans="1:4">
+      <c r="A2439" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2439">
+        <v>38</v>
+      </c>
+      <c r="C2439">
+        <v>6113.1</v>
+      </c>
+      <c r="D2439" t="s">
+        <v>2441</v>
+      </c>
+    </row>
+    <row r="2440" spans="1:4">
+      <c r="A2440" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2440">
+        <v>39</v>
+      </c>
+      <c r="C2440">
+        <v>6102.2</v>
+      </c>
+      <c r="D2440" t="s">
+        <v>2442</v>
+      </c>
+    </row>
+    <row r="2441" spans="1:4">
+      <c r="A2441" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2441">
+        <v>40</v>
+      </c>
+      <c r="C2441">
+        <v>6138.6</v>
+      </c>
+      <c r="D2441" t="s">
+        <v>2443</v>
+      </c>
+    </row>
+    <row r="2442" spans="1:4">
+      <c r="A2442" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2442">
+        <v>41</v>
+      </c>
+      <c r="C2442">
+        <v>6005.7</v>
+      </c>
+      <c r="D2442" t="s">
+        <v>2444</v>
+      </c>
+    </row>
+    <row r="2443" spans="1:4">
+      <c r="A2443" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2443">
+        <v>42</v>
+      </c>
+      <c r="C2443">
+        <v>6058.6</v>
+      </c>
+      <c r="D2443" t="s">
+        <v>2445</v>
+      </c>
+    </row>
+    <row r="2444" spans="1:4">
+      <c r="A2444" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2444">
+        <v>43</v>
+      </c>
+      <c r="C2444">
+        <v>6117.9</v>
+      </c>
+      <c r="D2444" t="s">
+        <v>2446</v>
+      </c>
+    </row>
+    <row r="2445" spans="1:4">
+      <c r="A2445" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2445">
+        <v>44</v>
+      </c>
+      <c r="C2445">
+        <v>6218.8</v>
+      </c>
+      <c r="D2445" t="s">
+        <v>2447</v>
+      </c>
+    </row>
+    <row r="2446" spans="1:4">
+      <c r="A2446" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2446">
+        <v>45</v>
+      </c>
+      <c r="C2446">
+        <v>6281.8</v>
+      </c>
+      <c r="D2446" t="s">
+        <v>2448</v>
+      </c>
+    </row>
+    <row r="2447" spans="1:4">
+      <c r="A2447" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2447">
+        <v>46</v>
+      </c>
+      <c r="C2447">
+        <v>6388.2</v>
+      </c>
+      <c r="D2447" t="s">
+        <v>2449</v>
+      </c>
+    </row>
+    <row r="2448" spans="1:4">
+      <c r="A2448" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2448">
+        <v>47</v>
+      </c>
+      <c r="C2448">
+        <v>6473.9</v>
+      </c>
+      <c r="D2448" t="s">
+        <v>2450</v>
+      </c>
+    </row>
+    <row r="2449" spans="1:4">
+      <c r="A2449" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2449">
+        <v>48</v>
+      </c>
+      <c r="C2449">
+        <v>6527.3</v>
+      </c>
+      <c r="D2449" t="s">
+        <v>2451</v>
+      </c>
+    </row>
+    <row r="2450" spans="1:4">
+      <c r="A2450" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2450">
+        <v>49</v>
+      </c>
+      <c r="C2450">
+        <v>6620.8</v>
+      </c>
+      <c r="D2450" t="s">
+        <v>2452</v>
+      </c>
+    </row>
+    <row r="2451" spans="1:4">
+      <c r="A2451" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2451">
+        <v>50</v>
+      </c>
+      <c r="C2451">
+        <v>6663.7</v>
+      </c>
+      <c r="D2451" t="s">
+        <v>2453</v>
+      </c>
+    </row>
+    <row r="2452" spans="1:4">
+      <c r="A2452" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2452">
+        <v>51</v>
+      </c>
+      <c r="C2452">
+        <v>6660.5</v>
+      </c>
+      <c r="D2452" t="s">
+        <v>2454</v>
+      </c>
+    </row>
+    <row r="2453" spans="1:4">
+      <c r="A2453" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2453">
+        <v>52</v>
+      </c>
+      <c r="C2453">
+        <v>6785</v>
+      </c>
+      <c r="D2453" t="s">
+        <v>2455</v>
+      </c>
+    </row>
+    <row r="2454" spans="1:4">
+      <c r="A2454" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2454">
+        <v>53</v>
+      </c>
+      <c r="C2454">
+        <v>6660</v>
+      </c>
+      <c r="D2454" t="s">
+        <v>2456</v>
+      </c>
+    </row>
+    <row r="2455" spans="1:4">
+      <c r="A2455" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2455">
+        <v>54</v>
+      </c>
+      <c r="C2455">
+        <v>6672</v>
+      </c>
+      <c r="D2455" t="s">
+        <v>2457</v>
+      </c>
+    </row>
+    <row r="2456" spans="1:4">
+      <c r="A2456" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2456">
+        <v>55</v>
+      </c>
+      <c r="C2456">
+        <v>6701.6</v>
+      </c>
+      <c r="D2456" t="s">
+        <v>2458</v>
+      </c>
+    </row>
+    <row r="2457" spans="1:4">
+      <c r="A2457" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2457">
+        <v>56</v>
+      </c>
+      <c r="C2457">
+        <v>6671.1</v>
+      </c>
+      <c r="D2457" t="s">
+        <v>2459</v>
+      </c>
+    </row>
+    <row r="2458" spans="1:4">
+      <c r="A2458" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2458">
+        <v>57</v>
+      </c>
+      <c r="C2458">
+        <v>6804.2</v>
+      </c>
+      <c r="D2458" t="s">
+        <v>2460</v>
+      </c>
+    </row>
+    <row r="2459" spans="1:4">
+      <c r="A2459" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2459">
+        <v>58</v>
+      </c>
+      <c r="C2459">
+        <v>6839.4</v>
+      </c>
+      <c r="D2459" t="s">
+        <v>2461</v>
+      </c>
+    </row>
+    <row r="2460" spans="1:4">
+      <c r="A2460" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2460">
+        <v>59</v>
+      </c>
+      <c r="C2460">
+        <v>6900.8</v>
+      </c>
+      <c r="D2460" t="s">
+        <v>2462</v>
+      </c>
+    </row>
+    <row r="2461" spans="1:4">
+      <c r="A2461" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2461">
+        <v>60</v>
+      </c>
+      <c r="C2461">
+        <v>6950.5</v>
+      </c>
+      <c r="D2461" t="s">
+        <v>2463</v>
+      </c>
+    </row>
+    <row r="2462" spans="1:4">
+      <c r="A2462" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2462">
+        <v>61</v>
+      </c>
+      <c r="C2462">
+        <v>7065.8</v>
+      </c>
+      <c r="D2462" t="s">
+        <v>2464</v>
+      </c>
+    </row>
+    <row r="2463" spans="1:4">
+      <c r="A2463" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2463">
+        <v>62</v>
+      </c>
+      <c r="C2463">
+        <v>7067.5</v>
+      </c>
+      <c r="D2463" t="s">
+        <v>2465</v>
+      </c>
+    </row>
+    <row r="2464" spans="1:4">
+      <c r="A2464" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2464">
+        <v>63</v>
+      </c>
+      <c r="C2464">
+        <v>7157.7</v>
+      </c>
+      <c r="D2464" t="s">
+        <v>2466</v>
+      </c>
+    </row>
+    <row r="2465" spans="1:4">
+      <c r="A2465" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2465">
+        <v>64</v>
+      </c>
+      <c r="C2465">
+        <v>7220.6</v>
+      </c>
+      <c r="D2465" t="s">
+        <v>2467</v>
+      </c>
+    </row>
+    <row r="2466" spans="1:4">
+      <c r="A2466" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2466">
+        <v>65</v>
+      </c>
+      <c r="C2466">
+        <v>7111.7</v>
+      </c>
+      <c r="D2466" t="s">
+        <v>2468</v>
+      </c>
+    </row>
+    <row r="2467" spans="1:4">
+      <c r="A2467" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2467">
+        <v>66</v>
+      </c>
+      <c r="C2467">
+        <v>7037.8</v>
+      </c>
+      <c r="D2467" t="s">
+        <v>2469</v>
+      </c>
+    </row>
+    <row r="2468" spans="1:4">
+      <c r="A2468" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2468">
+        <v>67</v>
+      </c>
+      <c r="C2468">
+        <v>6996.9</v>
+      </c>
+      <c r="D2468" t="s">
+        <v>2470</v>
+      </c>
+    </row>
+    <row r="2469" spans="1:4">
+      <c r="A2469" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2469">
+        <v>68</v>
+      </c>
+      <c r="C2469">
+        <v>6937.9</v>
+      </c>
+      <c r="D2469" t="s">
+        <v>2471</v>
+      </c>
+    </row>
+    <row r="2470" spans="1:4">
+      <c r="A2470" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2470">
+        <v>69</v>
+      </c>
+      <c r="C2470">
+        <v>6959.5</v>
+      </c>
+      <c r="D2470" t="s">
+        <v>2472</v>
+      </c>
+    </row>
+    <row r="2471" spans="1:4">
+      <c r="A2471" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2471">
+        <v>70</v>
+      </c>
+      <c r="C2471">
+        <v>6854.8</v>
+      </c>
+      <c r="D2471" t="s">
+        <v>2473</v>
+      </c>
+    </row>
+    <row r="2472" spans="1:4">
+      <c r="A2472" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2472">
+        <v>71</v>
+      </c>
+      <c r="C2472">
+        <v>6733.8</v>
+      </c>
+      <c r="D2472" t="s">
+        <v>2474</v>
+      </c>
+    </row>
+    <row r="2473" spans="1:4">
+      <c r="A2473" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2473">
+        <v>72</v>
+      </c>
+      <c r="C2473">
+        <v>6636.1</v>
+      </c>
+      <c r="D2473" t="s">
+        <v>2475</v>
+      </c>
+    </row>
+    <row r="2474" spans="1:4">
+      <c r="A2474" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2474">
+        <v>73</v>
+      </c>
+      <c r="C2474">
+        <v>6484.7</v>
+      </c>
+      <c r="D2474" t="s">
+        <v>2476</v>
+      </c>
+    </row>
+    <row r="2475" spans="1:4">
+      <c r="A2475" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2475">
+        <v>74</v>
+      </c>
+      <c r="C2475">
+        <v>6335.4</v>
+      </c>
+      <c r="D2475" t="s">
+        <v>2477</v>
+      </c>
+    </row>
+    <row r="2476" spans="1:4">
+      <c r="A2476" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2476">
+        <v>75</v>
+      </c>
+      <c r="C2476">
+        <v>6204.9</v>
+      </c>
+      <c r="D2476" t="s">
+        <v>2478</v>
+      </c>
+    </row>
+    <row r="2477" spans="1:4">
+      <c r="A2477" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2477">
+        <v>76</v>
+      </c>
+      <c r="C2477">
+        <v>6117.7</v>
+      </c>
+      <c r="D2477" t="s">
+        <v>2479</v>
+      </c>
+    </row>
+    <row r="2478" spans="1:4">
+      <c r="A2478" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2478">
+        <v>77</v>
+      </c>
+      <c r="C2478">
+        <v>5829.9</v>
+      </c>
+      <c r="D2478" t="s">
+        <v>2480</v>
+      </c>
+    </row>
+    <row r="2479" spans="1:4">
+      <c r="A2479" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2479">
+        <v>78</v>
+      </c>
+      <c r="C2479">
+        <v>5798.7</v>
+      </c>
+      <c r="D2479" t="s">
+        <v>2481</v>
+      </c>
+    </row>
+    <row r="2480" spans="1:4">
+      <c r="A2480" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2480">
+        <v>79</v>
+      </c>
+      <c r="C2480">
+        <v>5758.5</v>
+      </c>
+      <c r="D2480" t="s">
+        <v>2482</v>
+      </c>
+    </row>
+    <row r="2481" spans="1:4">
+      <c r="A2481" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2481">
+        <v>80</v>
+      </c>
+      <c r="C2481">
+        <v>5706.1</v>
+      </c>
+      <c r="D2481" t="s">
+        <v>2483</v>
+      </c>
+    </row>
+    <row r="2482" spans="1:4">
+      <c r="A2482" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2482">
+        <v>81</v>
+      </c>
+      <c r="C2482">
+        <v>6073.8</v>
+      </c>
+      <c r="D2482" t="s">
+        <v>2484</v>
+      </c>
+    </row>
+    <row r="2483" spans="1:4">
+      <c r="A2483" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2483">
+        <v>82</v>
+      </c>
+      <c r="C2483">
+        <v>6131</v>
+      </c>
+      <c r="D2483" t="s">
+        <v>2485</v>
+      </c>
+    </row>
+    <row r="2484" spans="1:4">
+      <c r="A2484" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2484">
+        <v>83</v>
+      </c>
+      <c r="C2484">
+        <v>6107.5</v>
+      </c>
+      <c r="D2484" t="s">
+        <v>2486</v>
+      </c>
+    </row>
+    <row r="2485" spans="1:4">
+      <c r="A2485" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2485">
+        <v>84</v>
+      </c>
+      <c r="C2485">
+        <v>6102.4</v>
+      </c>
+      <c r="D2485" t="s">
+        <v>2487</v>
+      </c>
+    </row>
+    <row r="2486" spans="1:4">
+      <c r="A2486" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2486">
+        <v>85</v>
+      </c>
+      <c r="C2486">
+        <v>6065.6</v>
+      </c>
+      <c r="D2486" t="s">
+        <v>2488</v>
+      </c>
+    </row>
+    <row r="2487" spans="1:4">
+      <c r="A2487" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2487">
+        <v>86</v>
+      </c>
+      <c r="C2487">
+        <v>6033.1</v>
+      </c>
+      <c r="D2487" t="s">
+        <v>2489</v>
+      </c>
+    </row>
+    <row r="2488" spans="1:4">
+      <c r="A2488" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2488">
+        <v>87</v>
+      </c>
+      <c r="C2488">
+        <v>6006.5</v>
+      </c>
+      <c r="D2488" t="s">
+        <v>2490</v>
+      </c>
+    </row>
+    <row r="2489" spans="1:4">
+      <c r="A2489" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2489">
+        <v>88</v>
+      </c>
+      <c r="C2489">
+        <v>5932.9</v>
+      </c>
+      <c r="D2489" t="s">
+        <v>2491</v>
+      </c>
+    </row>
+    <row r="2490" spans="1:4">
+      <c r="A2490" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2490">
+        <v>89</v>
+      </c>
+      <c r="C2490">
+        <v>5631</v>
+      </c>
+      <c r="D2490" t="s">
+        <v>2492</v>
+      </c>
+    </row>
+    <row r="2491" spans="1:4">
+      <c r="A2491" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2491">
+        <v>90</v>
+      </c>
+      <c r="C2491">
+        <v>5546.5</v>
+      </c>
+      <c r="D2491" t="s">
+        <v>2493</v>
+      </c>
+    </row>
+    <row r="2492" spans="1:4">
+      <c r="A2492" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2492">
+        <v>91</v>
+      </c>
+      <c r="C2492">
+        <v>5458.9</v>
+      </c>
+      <c r="D2492" t="s">
+        <v>2494</v>
+      </c>
+    </row>
+    <row r="2493" spans="1:4">
+      <c r="A2493" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2493">
+        <v>92</v>
+      </c>
+      <c r="C2493">
+        <v>5418.2</v>
+      </c>
+      <c r="D2493" t="s">
+        <v>2495</v>
+      </c>
+    </row>
+    <row r="2494" spans="1:4">
+      <c r="A2494" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2494">
+        <v>93</v>
+      </c>
+      <c r="C2494">
+        <v>5245.2</v>
+      </c>
+      <c r="D2494" t="s">
+        <v>2496</v>
+      </c>
+    </row>
+    <row r="2495" spans="1:4">
+      <c r="A2495" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2495">
+        <v>94</v>
+      </c>
+      <c r="C2495">
+        <v>5142.4</v>
+      </c>
+      <c r="D2495" t="s">
+        <v>2497</v>
+      </c>
+    </row>
+    <row r="2496" spans="1:4">
+      <c r="A2496" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2496">
+        <v>95</v>
+      </c>
+      <c r="C2496">
+        <v>5143.1</v>
+      </c>
+      <c r="D2496" t="s">
+        <v>2498</v>
+      </c>
+    </row>
+    <row r="2497" spans="1:4">
+      <c r="A2497" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2497">
+        <v>96</v>
+      </c>
+      <c r="C2497">
+        <v>5152.2</v>
+      </c>
+      <c r="D2497" t="s">
+        <v>2499</v>
       </c>
     </row>
   </sheetData>

--- a/Market Fundamentals/Transelectrica_data/Cons_Prod_final/Weekly_Production_2026.xlsx
+++ b/Market Fundamentals/Transelectrica_data/Cons_Prod_final/Weekly_Production_2026.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2500" uniqueCount="2500">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2692" uniqueCount="2692">
   <si>
     <t>Date</t>
   </si>
@@ -7514,6 +7514,582 @@
   </si>
   <si>
     <t>26.08.202696.0</t>
+  </si>
+  <si>
+    <t>27.08.20261.0</t>
+  </si>
+  <si>
+    <t>27.08.20262.0</t>
+  </si>
+  <si>
+    <t>27.08.20263.0</t>
+  </si>
+  <si>
+    <t>27.08.20264.0</t>
+  </si>
+  <si>
+    <t>27.08.20265.0</t>
+  </si>
+  <si>
+    <t>27.08.20266.0</t>
+  </si>
+  <si>
+    <t>27.08.20267.0</t>
+  </si>
+  <si>
+    <t>27.08.20268.0</t>
+  </si>
+  <si>
+    <t>27.08.20269.0</t>
+  </si>
+  <si>
+    <t>27.08.202610.0</t>
+  </si>
+  <si>
+    <t>27.08.202611.0</t>
+  </si>
+  <si>
+    <t>27.08.202612.0</t>
+  </si>
+  <si>
+    <t>27.08.202613.0</t>
+  </si>
+  <si>
+    <t>27.08.202614.0</t>
+  </si>
+  <si>
+    <t>27.08.202615.0</t>
+  </si>
+  <si>
+    <t>27.08.202616.0</t>
+  </si>
+  <si>
+    <t>27.08.202617.0</t>
+  </si>
+  <si>
+    <t>27.08.202618.0</t>
+  </si>
+  <si>
+    <t>27.08.202619.0</t>
+  </si>
+  <si>
+    <t>27.08.202620.0</t>
+  </si>
+  <si>
+    <t>27.08.202621.0</t>
+  </si>
+  <si>
+    <t>27.08.202622.0</t>
+  </si>
+  <si>
+    <t>27.08.202623.0</t>
+  </si>
+  <si>
+    <t>27.08.202624.0</t>
+  </si>
+  <si>
+    <t>27.08.202625.0</t>
+  </si>
+  <si>
+    <t>27.08.202626.0</t>
+  </si>
+  <si>
+    <t>27.08.202627.0</t>
+  </si>
+  <si>
+    <t>27.08.202628.0</t>
+  </si>
+  <si>
+    <t>27.08.202629.0</t>
+  </si>
+  <si>
+    <t>27.08.202630.0</t>
+  </si>
+  <si>
+    <t>27.08.202631.0</t>
+  </si>
+  <si>
+    <t>27.08.202632.0</t>
+  </si>
+  <si>
+    <t>27.08.202633.0</t>
+  </si>
+  <si>
+    <t>27.08.202634.0</t>
+  </si>
+  <si>
+    <t>27.08.202635.0</t>
+  </si>
+  <si>
+    <t>27.08.202636.0</t>
+  </si>
+  <si>
+    <t>27.08.202637.0</t>
+  </si>
+  <si>
+    <t>27.08.202638.0</t>
+  </si>
+  <si>
+    <t>27.08.202639.0</t>
+  </si>
+  <si>
+    <t>27.08.202640.0</t>
+  </si>
+  <si>
+    <t>27.08.202641.0</t>
+  </si>
+  <si>
+    <t>27.08.202642.0</t>
+  </si>
+  <si>
+    <t>27.08.202643.0</t>
+  </si>
+  <si>
+    <t>27.08.202644.0</t>
+  </si>
+  <si>
+    <t>27.08.202645.0</t>
+  </si>
+  <si>
+    <t>27.08.202646.0</t>
+  </si>
+  <si>
+    <t>27.08.202647.0</t>
+  </si>
+  <si>
+    <t>27.08.202648.0</t>
+  </si>
+  <si>
+    <t>27.08.202649.0</t>
+  </si>
+  <si>
+    <t>27.08.202650.0</t>
+  </si>
+  <si>
+    <t>27.08.202651.0</t>
+  </si>
+  <si>
+    <t>27.08.202652.0</t>
+  </si>
+  <si>
+    <t>27.08.202653.0</t>
+  </si>
+  <si>
+    <t>27.08.202654.0</t>
+  </si>
+  <si>
+    <t>27.08.202655.0</t>
+  </si>
+  <si>
+    <t>27.08.202656.0</t>
+  </si>
+  <si>
+    <t>27.08.202657.0</t>
+  </si>
+  <si>
+    <t>27.08.202658.0</t>
+  </si>
+  <si>
+    <t>27.08.202659.0</t>
+  </si>
+  <si>
+    <t>27.08.202660.0</t>
+  </si>
+  <si>
+    <t>27.08.202661.0</t>
+  </si>
+  <si>
+    <t>27.08.202662.0</t>
+  </si>
+  <si>
+    <t>27.08.202663.0</t>
+  </si>
+  <si>
+    <t>27.08.202664.0</t>
+  </si>
+  <si>
+    <t>27.08.202665.0</t>
+  </si>
+  <si>
+    <t>27.08.202666.0</t>
+  </si>
+  <si>
+    <t>27.08.202667.0</t>
+  </si>
+  <si>
+    <t>27.08.202668.0</t>
+  </si>
+  <si>
+    <t>27.08.202669.0</t>
+  </si>
+  <si>
+    <t>27.08.202670.0</t>
+  </si>
+  <si>
+    <t>27.08.202671.0</t>
+  </si>
+  <si>
+    <t>27.08.202672.0</t>
+  </si>
+  <si>
+    <t>27.08.202673.0</t>
+  </si>
+  <si>
+    <t>27.08.202674.0</t>
+  </si>
+  <si>
+    <t>27.08.202675.0</t>
+  </si>
+  <si>
+    <t>27.08.202676.0</t>
+  </si>
+  <si>
+    <t>27.08.202677.0</t>
+  </si>
+  <si>
+    <t>27.08.202678.0</t>
+  </si>
+  <si>
+    <t>27.08.202679.0</t>
+  </si>
+  <si>
+    <t>27.08.202680.0</t>
+  </si>
+  <si>
+    <t>27.08.202681.0</t>
+  </si>
+  <si>
+    <t>27.08.202682.0</t>
+  </si>
+  <si>
+    <t>27.08.202683.0</t>
+  </si>
+  <si>
+    <t>27.08.202684.0</t>
+  </si>
+  <si>
+    <t>27.08.202685.0</t>
+  </si>
+  <si>
+    <t>27.08.202686.0</t>
+  </si>
+  <si>
+    <t>27.08.202687.0</t>
+  </si>
+  <si>
+    <t>27.08.202688.0</t>
+  </si>
+  <si>
+    <t>27.08.202689.0</t>
+  </si>
+  <si>
+    <t>27.08.202690.0</t>
+  </si>
+  <si>
+    <t>27.08.202691.0</t>
+  </si>
+  <si>
+    <t>27.08.202692.0</t>
+  </si>
+  <si>
+    <t>27.08.202693.0</t>
+  </si>
+  <si>
+    <t>27.08.202694.0</t>
+  </si>
+  <si>
+    <t>27.08.202695.0</t>
+  </si>
+  <si>
+    <t>27.08.202696.0</t>
+  </si>
+  <si>
+    <t>28.08.20261.0</t>
+  </si>
+  <si>
+    <t>28.08.20262.0</t>
+  </si>
+  <si>
+    <t>28.08.20263.0</t>
+  </si>
+  <si>
+    <t>28.08.20264.0</t>
+  </si>
+  <si>
+    <t>28.08.20265.0</t>
+  </si>
+  <si>
+    <t>28.08.20266.0</t>
+  </si>
+  <si>
+    <t>28.08.20267.0</t>
+  </si>
+  <si>
+    <t>28.08.20268.0</t>
+  </si>
+  <si>
+    <t>28.08.20269.0</t>
+  </si>
+  <si>
+    <t>28.08.202610.0</t>
+  </si>
+  <si>
+    <t>28.08.202611.0</t>
+  </si>
+  <si>
+    <t>28.08.202612.0</t>
+  </si>
+  <si>
+    <t>28.08.202613.0</t>
+  </si>
+  <si>
+    <t>28.08.202614.0</t>
+  </si>
+  <si>
+    <t>28.08.202615.0</t>
+  </si>
+  <si>
+    <t>28.08.202616.0</t>
+  </si>
+  <si>
+    <t>28.08.202617.0</t>
+  </si>
+  <si>
+    <t>28.08.202618.0</t>
+  </si>
+  <si>
+    <t>28.08.202619.0</t>
+  </si>
+  <si>
+    <t>28.08.202620.0</t>
+  </si>
+  <si>
+    <t>28.08.202621.0</t>
+  </si>
+  <si>
+    <t>28.08.202622.0</t>
+  </si>
+  <si>
+    <t>28.08.202623.0</t>
+  </si>
+  <si>
+    <t>28.08.202624.0</t>
+  </si>
+  <si>
+    <t>28.08.202625.0</t>
+  </si>
+  <si>
+    <t>28.08.202626.0</t>
+  </si>
+  <si>
+    <t>28.08.202627.0</t>
+  </si>
+  <si>
+    <t>28.08.202628.0</t>
+  </si>
+  <si>
+    <t>28.08.202629.0</t>
+  </si>
+  <si>
+    <t>28.08.202630.0</t>
+  </si>
+  <si>
+    <t>28.08.202631.0</t>
+  </si>
+  <si>
+    <t>28.08.202632.0</t>
+  </si>
+  <si>
+    <t>28.08.202633.0</t>
+  </si>
+  <si>
+    <t>28.08.202634.0</t>
+  </si>
+  <si>
+    <t>28.08.202635.0</t>
+  </si>
+  <si>
+    <t>28.08.202636.0</t>
+  </si>
+  <si>
+    <t>28.08.202637.0</t>
+  </si>
+  <si>
+    <t>28.08.202638.0</t>
+  </si>
+  <si>
+    <t>28.08.202639.0</t>
+  </si>
+  <si>
+    <t>28.08.202640.0</t>
+  </si>
+  <si>
+    <t>28.08.202641.0</t>
+  </si>
+  <si>
+    <t>28.08.202642.0</t>
+  </si>
+  <si>
+    <t>28.08.202643.0</t>
+  </si>
+  <si>
+    <t>28.08.202644.0</t>
+  </si>
+  <si>
+    <t>28.08.202645.0</t>
+  </si>
+  <si>
+    <t>28.08.202646.0</t>
+  </si>
+  <si>
+    <t>28.08.202647.0</t>
+  </si>
+  <si>
+    <t>28.08.202648.0</t>
+  </si>
+  <si>
+    <t>28.08.202649.0</t>
+  </si>
+  <si>
+    <t>28.08.202650.0</t>
+  </si>
+  <si>
+    <t>28.08.202651.0</t>
+  </si>
+  <si>
+    <t>28.08.202652.0</t>
+  </si>
+  <si>
+    <t>28.08.202653.0</t>
+  </si>
+  <si>
+    <t>28.08.202654.0</t>
+  </si>
+  <si>
+    <t>28.08.202655.0</t>
+  </si>
+  <si>
+    <t>28.08.202656.0</t>
+  </si>
+  <si>
+    <t>28.08.202657.0</t>
+  </si>
+  <si>
+    <t>28.08.202658.0</t>
+  </si>
+  <si>
+    <t>28.08.202659.0</t>
+  </si>
+  <si>
+    <t>28.08.202660.0</t>
+  </si>
+  <si>
+    <t>28.08.202661.0</t>
+  </si>
+  <si>
+    <t>28.08.202662.0</t>
+  </si>
+  <si>
+    <t>28.08.202663.0</t>
+  </si>
+  <si>
+    <t>28.08.202664.0</t>
+  </si>
+  <si>
+    <t>28.08.202665.0</t>
+  </si>
+  <si>
+    <t>28.08.202666.0</t>
+  </si>
+  <si>
+    <t>28.08.202667.0</t>
+  </si>
+  <si>
+    <t>28.08.202668.0</t>
+  </si>
+  <si>
+    <t>28.08.202669.0</t>
+  </si>
+  <si>
+    <t>28.08.202670.0</t>
+  </si>
+  <si>
+    <t>28.08.202671.0</t>
+  </si>
+  <si>
+    <t>28.08.202672.0</t>
+  </si>
+  <si>
+    <t>28.08.202673.0</t>
+  </si>
+  <si>
+    <t>28.08.202674.0</t>
+  </si>
+  <si>
+    <t>28.08.202675.0</t>
+  </si>
+  <si>
+    <t>28.08.202676.0</t>
+  </si>
+  <si>
+    <t>28.08.202677.0</t>
+  </si>
+  <si>
+    <t>28.08.202678.0</t>
+  </si>
+  <si>
+    <t>28.08.202679.0</t>
+  </si>
+  <si>
+    <t>28.08.202680.0</t>
+  </si>
+  <si>
+    <t>28.08.202681.0</t>
+  </si>
+  <si>
+    <t>28.08.202682.0</t>
+  </si>
+  <si>
+    <t>28.08.202683.0</t>
+  </si>
+  <si>
+    <t>28.08.202684.0</t>
+  </si>
+  <si>
+    <t>28.08.202685.0</t>
+  </si>
+  <si>
+    <t>28.08.202686.0</t>
+  </si>
+  <si>
+    <t>28.08.202687.0</t>
+  </si>
+  <si>
+    <t>28.08.202688.0</t>
+  </si>
+  <si>
+    <t>28.08.202689.0</t>
+  </si>
+  <si>
+    <t>28.08.202690.0</t>
+  </si>
+  <si>
+    <t>28.08.202691.0</t>
+  </si>
+  <si>
+    <t>28.08.202692.0</t>
+  </si>
+  <si>
+    <t>28.08.202693.0</t>
+  </si>
+  <si>
+    <t>28.08.202694.0</t>
+  </si>
+  <si>
+    <t>28.08.202695.0</t>
+  </si>
+  <si>
+    <t>28.08.202696.0</t>
   </si>
 </sst>
 </file>
@@ -7875,7 +8451,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D2497"/>
+  <dimension ref="A1:D2689"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -33436,7 +34012,7 @@
         <v>1</v>
       </c>
       <c r="C1826">
-        <v>5006.7</v>
+        <v>4416.6</v>
       </c>
       <c r="D1826" t="s">
         <v>1828</v>
@@ -33450,7 +34026,7 @@
         <v>2</v>
       </c>
       <c r="C1827">
-        <v>5051</v>
+        <v>4420.1</v>
       </c>
       <c r="D1827" t="s">
         <v>1829</v>
@@ -33464,7 +34040,7 @@
         <v>3</v>
       </c>
       <c r="C1828">
-        <v>5036.8</v>
+        <v>4428</v>
       </c>
       <c r="D1828" t="s">
         <v>1830</v>
@@ -33478,7 +34054,7 @@
         <v>4</v>
       </c>
       <c r="C1829">
-        <v>5020.5</v>
+        <v>4421.8</v>
       </c>
       <c r="D1829" t="s">
         <v>1831</v>
@@ -33492,7 +34068,7 @@
         <v>5</v>
       </c>
       <c r="C1830">
-        <v>5007</v>
+        <v>4090.5</v>
       </c>
       <c r="D1830" t="s">
         <v>1832</v>
@@ -33506,7 +34082,7 @@
         <v>6</v>
       </c>
       <c r="C1831">
-        <v>4948.9</v>
+        <v>4096.5</v>
       </c>
       <c r="D1831" t="s">
         <v>1833</v>
@@ -33520,7 +34096,7 @@
         <v>7</v>
       </c>
       <c r="C1832">
-        <v>4894.8</v>
+        <v>4092.5</v>
       </c>
       <c r="D1832" t="s">
         <v>1834</v>
@@ -33534,7 +34110,7 @@
         <v>8</v>
       </c>
       <c r="C1833">
-        <v>4784.4</v>
+        <v>4097</v>
       </c>
       <c r="D1833" t="s">
         <v>1835</v>
@@ -33548,7 +34124,7 @@
         <v>9</v>
       </c>
       <c r="C1834">
-        <v>4803.5</v>
+        <v>4057</v>
       </c>
       <c r="D1834" t="s">
         <v>1836</v>
@@ -33562,7 +34138,7 @@
         <v>10</v>
       </c>
       <c r="C1835">
-        <v>4709</v>
+        <v>4028.2</v>
       </c>
       <c r="D1835" t="s">
         <v>1837</v>
@@ -33576,7 +34152,7 @@
         <v>11</v>
       </c>
       <c r="C1836">
-        <v>4634.3</v>
+        <v>4018.1</v>
       </c>
       <c r="D1836" t="s">
         <v>1838</v>
@@ -33590,7 +34166,7 @@
         <v>12</v>
       </c>
       <c r="C1837">
-        <v>4500.5</v>
+        <v>4015</v>
       </c>
       <c r="D1837" t="s">
         <v>1839</v>
@@ -33604,7 +34180,7 @@
         <v>13</v>
       </c>
       <c r="C1838">
-        <v>4379.9</v>
+        <v>3999.1</v>
       </c>
       <c r="D1838" t="s">
         <v>1840</v>
@@ -33618,7 +34194,7 @@
         <v>14</v>
       </c>
       <c r="C1839">
-        <v>4430.1</v>
+        <v>3942.2</v>
       </c>
       <c r="D1839" t="s">
         <v>1841</v>
@@ -33632,7 +34208,7 @@
         <v>15</v>
       </c>
       <c r="C1840">
-        <v>4454.8</v>
+        <v>3864.3</v>
       </c>
       <c r="D1840" t="s">
         <v>1842</v>
@@ -33646,7 +34222,7 @@
         <v>16</v>
       </c>
       <c r="C1841">
-        <v>4404.9</v>
+        <v>3879.3</v>
       </c>
       <c r="D1841" t="s">
         <v>1843</v>
@@ -33660,7 +34236,7 @@
         <v>17</v>
       </c>
       <c r="C1842">
-        <v>4238.4</v>
+        <v>3765.8</v>
       </c>
       <c r="D1842" t="s">
         <v>1844</v>
@@ -33674,7 +34250,7 @@
         <v>18</v>
       </c>
       <c r="C1843">
-        <v>4205.2</v>
+        <v>3787.5</v>
       </c>
       <c r="D1843" t="s">
         <v>1845</v>
@@ -33688,7 +34264,7 @@
         <v>19</v>
       </c>
       <c r="C1844">
-        <v>4183.1</v>
+        <v>3759</v>
       </c>
       <c r="D1844" t="s">
         <v>1846</v>
@@ -33702,7 +34278,7 @@
         <v>20</v>
       </c>
       <c r="C1845">
-        <v>4171.3</v>
+        <v>3770.7</v>
       </c>
       <c r="D1845" t="s">
         <v>1847</v>
@@ -33716,7 +34292,7 @@
         <v>21</v>
       </c>
       <c r="C1846">
-        <v>4033.1</v>
+        <v>3843.4</v>
       </c>
       <c r="D1846" t="s">
         <v>1848</v>
@@ -33730,7 +34306,7 @@
         <v>22</v>
       </c>
       <c r="C1847">
-        <v>4046.8</v>
+        <v>3886.5</v>
       </c>
       <c r="D1847" t="s">
         <v>1849</v>
@@ -33744,7 +34320,7 @@
         <v>23</v>
       </c>
       <c r="C1848">
-        <v>4056.6</v>
+        <v>3911.8</v>
       </c>
       <c r="D1848" t="s">
         <v>1850</v>
@@ -33758,7 +34334,7 @@
         <v>24</v>
       </c>
       <c r="C1849">
-        <v>4198.3</v>
+        <v>3937.5</v>
       </c>
       <c r="D1849" t="s">
         <v>1851</v>
@@ -33772,7 +34348,7 @@
         <v>25</v>
       </c>
       <c r="C1850">
-        <v>4270.5</v>
+        <v>3989.4</v>
       </c>
       <c r="D1850" t="s">
         <v>1852</v>
@@ -33786,7 +34362,7 @@
         <v>26</v>
       </c>
       <c r="C1851">
-        <v>4293</v>
+        <v>4003.4</v>
       </c>
       <c r="D1851" t="s">
         <v>1853</v>
@@ -33800,7 +34376,7 @@
         <v>27</v>
       </c>
       <c r="C1852">
-        <v>4295.3</v>
+        <v>4117.1</v>
       </c>
       <c r="D1852" t="s">
         <v>1854</v>
@@ -33814,7 +34390,7 @@
         <v>28</v>
       </c>
       <c r="C1853">
-        <v>4361.9</v>
+        <v>4159.7</v>
       </c>
       <c r="D1853" t="s">
         <v>1855</v>
@@ -33828,7 +34404,7 @@
         <v>29</v>
       </c>
       <c r="C1854">
-        <v>4409.7</v>
+        <v>4468.2</v>
       </c>
       <c r="D1854" t="s">
         <v>1856</v>
@@ -33842,7 +34418,7 @@
         <v>30</v>
       </c>
       <c r="C1855">
-        <v>4438.6</v>
+        <v>4550.5</v>
       </c>
       <c r="D1855" t="s">
         <v>1857</v>
@@ -33856,7 +34432,7 @@
         <v>31</v>
       </c>
       <c r="C1856">
-        <v>4454.8</v>
+        <v>4664.3</v>
       </c>
       <c r="D1856" t="s">
         <v>1858</v>
@@ -33870,7 +34446,7 @@
         <v>32</v>
       </c>
       <c r="C1857">
-        <v>4506.3</v>
+        <v>4779.6</v>
       </c>
       <c r="D1857" t="s">
         <v>1859</v>
@@ -33884,7 +34460,7 @@
         <v>33</v>
       </c>
       <c r="C1858">
-        <v>4568.4</v>
+        <v>5192.9</v>
       </c>
       <c r="D1858" t="s">
         <v>1860</v>
@@ -33898,7 +34474,7 @@
         <v>34</v>
       </c>
       <c r="C1859">
-        <v>4645.3</v>
+        <v>5389.3</v>
       </c>
       <c r="D1859" t="s">
         <v>1861</v>
@@ -33912,7 +34488,7 @@
         <v>35</v>
       </c>
       <c r="C1860">
-        <v>4709.7</v>
+        <v>5546.3</v>
       </c>
       <c r="D1860" t="s">
         <v>1862</v>
@@ -33926,7 +34502,7 @@
         <v>36</v>
       </c>
       <c r="C1861">
-        <v>4739.4</v>
+        <v>5653.3</v>
       </c>
       <c r="D1861" t="s">
         <v>1863</v>
@@ -33940,7 +34516,7 @@
         <v>37</v>
       </c>
       <c r="C1862">
-        <v>4984.7</v>
+        <v>5491.5</v>
       </c>
       <c r="D1862" t="s">
         <v>1864</v>
@@ -33954,7 +34530,7 @@
         <v>38</v>
       </c>
       <c r="C1863">
-        <v>5057.5</v>
+        <v>5628.8</v>
       </c>
       <c r="D1863" t="s">
         <v>1865</v>
@@ -33968,7 +34544,7 @@
         <v>39</v>
       </c>
       <c r="C1864">
-        <v>5087.7</v>
+        <v>5724.6</v>
       </c>
       <c r="D1864" t="s">
         <v>1866</v>
@@ -33982,7 +34558,7 @@
         <v>40</v>
       </c>
       <c r="C1865">
-        <v>5030.9</v>
+        <v>5797.8</v>
       </c>
       <c r="D1865" t="s">
         <v>1867</v>
@@ -33996,7 +34572,7 @@
         <v>41</v>
       </c>
       <c r="C1866">
-        <v>5226.7</v>
+        <v>5935.7</v>
       </c>
       <c r="D1866" t="s">
         <v>1868</v>
@@ -34010,7 +34586,7 @@
         <v>42</v>
       </c>
       <c r="C1867">
-        <v>5202.9</v>
+        <v>6024.9</v>
       </c>
       <c r="D1867" t="s">
         <v>1869</v>
@@ -34024,7 +34600,7 @@
         <v>43</v>
       </c>
       <c r="C1868">
-        <v>5322.5</v>
+        <v>6093.6</v>
       </c>
       <c r="D1868" t="s">
         <v>1870</v>
@@ -34038,7 +34614,7 @@
         <v>44</v>
       </c>
       <c r="C1869">
-        <v>5421.1</v>
+        <v>6190.4</v>
       </c>
       <c r="D1869" t="s">
         <v>1871</v>
@@ -34052,7 +34628,7 @@
         <v>45</v>
       </c>
       <c r="C1870">
-        <v>5494</v>
+        <v>6243.6</v>
       </c>
       <c r="D1870" t="s">
         <v>1872</v>
@@ -34066,7 +34642,7 @@
         <v>46</v>
       </c>
       <c r="C1871">
-        <v>5587.2</v>
+        <v>6315.1</v>
       </c>
       <c r="D1871" t="s">
         <v>1873</v>
@@ -34080,7 +34656,7 @@
         <v>47</v>
       </c>
       <c r="C1872">
-        <v>5678.6</v>
+        <v>6382.1</v>
       </c>
       <c r="D1872" t="s">
         <v>1874</v>
@@ -34094,7 +34670,7 @@
         <v>48</v>
       </c>
       <c r="C1873">
-        <v>5780</v>
+        <v>6457.8</v>
       </c>
       <c r="D1873" t="s">
         <v>1875</v>
@@ -34108,7 +34684,7 @@
         <v>49</v>
       </c>
       <c r="C1874">
-        <v>5860.2</v>
+        <v>6132.7</v>
       </c>
       <c r="D1874" t="s">
         <v>1876</v>
@@ -34122,7 +34698,7 @@
         <v>50</v>
       </c>
       <c r="C1875">
-        <v>5890.5</v>
+        <v>6147</v>
       </c>
       <c r="D1875" t="s">
         <v>1877</v>
@@ -34136,7 +34712,7 @@
         <v>51</v>
       </c>
       <c r="C1876">
-        <v>5914.9</v>
+        <v>6167</v>
       </c>
       <c r="D1876" t="s">
         <v>1878</v>
@@ -34150,7 +34726,7 @@
         <v>52</v>
       </c>
       <c r="C1877">
-        <v>5941.8</v>
+        <v>6192.6</v>
       </c>
       <c r="D1877" t="s">
         <v>1879</v>
@@ -34164,7 +34740,7 @@
         <v>53</v>
       </c>
       <c r="C1878">
-        <v>5778.4</v>
+        <v>6156.2</v>
       </c>
       <c r="D1878" t="s">
         <v>1880</v>
@@ -34178,7 +34754,7 @@
         <v>54</v>
       </c>
       <c r="C1879">
-        <v>5733.5</v>
+        <v>6226.7</v>
       </c>
       <c r="D1879" t="s">
         <v>1881</v>
@@ -34192,7 +34768,7 @@
         <v>55</v>
       </c>
       <c r="C1880">
-        <v>5775.7</v>
+        <v>6265.4</v>
       </c>
       <c r="D1880" t="s">
         <v>1882</v>
@@ -34206,7 +34782,7 @@
         <v>56</v>
       </c>
       <c r="C1881">
-        <v>5733.1</v>
+        <v>6337</v>
       </c>
       <c r="D1881" t="s">
         <v>1883</v>
@@ -34220,7 +34796,7 @@
         <v>57</v>
       </c>
       <c r="C1882">
-        <v>5513.5</v>
+        <v>6287.6</v>
       </c>
       <c r="D1882" t="s">
         <v>1884</v>
@@ -34234,7 +34810,7 @@
         <v>58</v>
       </c>
       <c r="C1883">
-        <v>5544.8</v>
+        <v>6314.4</v>
       </c>
       <c r="D1883" t="s">
         <v>1885</v>
@@ -34248,7 +34824,7 @@
         <v>59</v>
       </c>
       <c r="C1884">
-        <v>5582.1</v>
+        <v>6349.2</v>
       </c>
       <c r="D1884" t="s">
         <v>1886</v>
@@ -34262,7 +34838,7 @@
         <v>60</v>
       </c>
       <c r="C1885">
-        <v>5636</v>
+        <v>6399.1</v>
       </c>
       <c r="D1885" t="s">
         <v>1887</v>
@@ -34276,7 +34852,7 @@
         <v>61</v>
       </c>
       <c r="C1886">
-        <v>5655.7</v>
+        <v>6523.1</v>
       </c>
       <c r="D1886" t="s">
         <v>1888</v>
@@ -34290,7 +34866,7 @@
         <v>62</v>
       </c>
       <c r="C1887">
-        <v>5674.5</v>
+        <v>6535</v>
       </c>
       <c r="D1887" t="s">
         <v>1889</v>
@@ -34304,7 +34880,7 @@
         <v>63</v>
       </c>
       <c r="C1888">
-        <v>5687.9</v>
+        <v>6566.4</v>
       </c>
       <c r="D1888" t="s">
         <v>1890</v>
@@ -34318,7 +34894,7 @@
         <v>64</v>
       </c>
       <c r="C1889">
-        <v>5714.3</v>
+        <v>6592.4</v>
       </c>
       <c r="D1889" t="s">
         <v>1891</v>
@@ -34332,7 +34908,7 @@
         <v>65</v>
       </c>
       <c r="C1890">
-        <v>5530.9</v>
+        <v>6348.9</v>
       </c>
       <c r="D1890" t="s">
         <v>1892</v>
@@ -34346,7 +34922,7 @@
         <v>66</v>
       </c>
       <c r="C1891">
-        <v>5492.7</v>
+        <v>6291.9</v>
       </c>
       <c r="D1891" t="s">
         <v>1893</v>
@@ -34360,7 +34936,7 @@
         <v>67</v>
       </c>
       <c r="C1892">
-        <v>5546.9</v>
+        <v>6319.7</v>
       </c>
       <c r="D1892" t="s">
         <v>1894</v>
@@ -34374,7 +34950,7 @@
         <v>68</v>
       </c>
       <c r="C1893">
-        <v>5510.5</v>
+        <v>6298.2</v>
       </c>
       <c r="D1893" t="s">
         <v>1895</v>
@@ -34388,7 +34964,7 @@
         <v>69</v>
       </c>
       <c r="C1894">
-        <v>6078.5</v>
+        <v>6881.4</v>
       </c>
       <c r="D1894" t="s">
         <v>1896</v>
@@ -34402,7 +34978,7 @@
         <v>70</v>
       </c>
       <c r="C1895">
-        <v>5981.6</v>
+        <v>6740.6</v>
       </c>
       <c r="D1895" t="s">
         <v>1897</v>
@@ -34416,7 +34992,7 @@
         <v>71</v>
       </c>
       <c r="C1896">
-        <v>5871.1</v>
+        <v>6579.2</v>
       </c>
       <c r="D1896" t="s">
         <v>1898</v>
@@ -34430,7 +35006,7 @@
         <v>72</v>
       </c>
       <c r="C1897">
-        <v>5786.6</v>
+        <v>6452.2</v>
       </c>
       <c r="D1897" t="s">
         <v>1899</v>
@@ -34444,7 +35020,7 @@
         <v>73</v>
       </c>
       <c r="C1898">
-        <v>5556.3</v>
+        <v>6372.7</v>
       </c>
       <c r="D1898" t="s">
         <v>1900</v>
@@ -34458,7 +35034,7 @@
         <v>74</v>
       </c>
       <c r="C1899">
-        <v>5432.8</v>
+        <v>6217</v>
       </c>
       <c r="D1899" t="s">
         <v>1901</v>
@@ -34472,7 +35048,7 @@
         <v>75</v>
       </c>
       <c r="C1900">
-        <v>5340.8</v>
+        <v>6096.8</v>
       </c>
       <c r="D1900" t="s">
         <v>1902</v>
@@ -34486,7 +35062,7 @@
         <v>76</v>
       </c>
       <c r="C1901">
-        <v>5231.8</v>
+        <v>6015.3</v>
       </c>
       <c r="D1901" t="s">
         <v>1903</v>
@@ -34500,7 +35076,7 @@
         <v>77</v>
       </c>
       <c r="C1902">
-        <v>5208.2</v>
+        <v>5994.1</v>
       </c>
       <c r="D1902" t="s">
         <v>1904</v>
@@ -34514,7 +35090,7 @@
         <v>78</v>
       </c>
       <c r="C1903">
-        <v>5176.1</v>
+        <v>5954.8</v>
       </c>
       <c r="D1903" t="s">
         <v>1905</v>
@@ -34528,7 +35104,7 @@
         <v>79</v>
       </c>
       <c r="C1904">
-        <v>5112.5</v>
+        <v>5931.7</v>
       </c>
       <c r="D1904" t="s">
         <v>1906</v>
@@ -34542,7 +35118,7 @@
         <v>80</v>
       </c>
       <c r="C1905">
-        <v>5106.6</v>
+        <v>6012.3</v>
       </c>
       <c r="D1905" t="s">
         <v>1907</v>
@@ -34556,7 +35132,7 @@
         <v>81</v>
       </c>
       <c r="C1906">
-        <v>5422.6</v>
+        <v>6492.7</v>
       </c>
       <c r="D1906" t="s">
         <v>1908</v>
@@ -34570,7 +35146,7 @@
         <v>82</v>
       </c>
       <c r="C1907">
-        <v>5492.9</v>
+        <v>6495.4</v>
       </c>
       <c r="D1907" t="s">
         <v>1909</v>
@@ -34584,7 +35160,7 @@
         <v>83</v>
       </c>
       <c r="C1908">
-        <v>5508.1</v>
+        <v>6511.6</v>
       </c>
       <c r="D1908" t="s">
         <v>1910</v>
@@ -34598,7 +35174,7 @@
         <v>84</v>
       </c>
       <c r="C1909">
-        <v>5491.1</v>
+        <v>6518.3</v>
       </c>
       <c r="D1909" t="s">
         <v>1911</v>
@@ -34612,7 +35188,7 @@
         <v>85</v>
       </c>
       <c r="C1910">
-        <v>5493.4</v>
+        <v>6365.3</v>
       </c>
       <c r="D1910" t="s">
         <v>1912</v>
@@ -34626,7 +35202,7 @@
         <v>86</v>
       </c>
       <c r="C1911">
-        <v>5519.8</v>
+        <v>6380.6</v>
       </c>
       <c r="D1911" t="s">
         <v>1913</v>
@@ -34640,7 +35216,7 @@
         <v>87</v>
       </c>
       <c r="C1912">
-        <v>5521.2</v>
+        <v>6417.3</v>
       </c>
       <c r="D1912" t="s">
         <v>1914</v>
@@ -34654,7 +35230,7 @@
         <v>88</v>
       </c>
       <c r="C1913">
-        <v>5514.9</v>
+        <v>6362.1</v>
       </c>
       <c r="D1913" t="s">
         <v>1915</v>
@@ -34668,7 +35244,7 @@
         <v>89</v>
       </c>
       <c r="C1914">
-        <v>5457.1</v>
+        <v>6067.1</v>
       </c>
       <c r="D1914" t="s">
         <v>1916</v>
@@ -34682,7 +35258,7 @@
         <v>90</v>
       </c>
       <c r="C1915">
-        <v>5400.6</v>
+        <v>5976.5</v>
       </c>
       <c r="D1915" t="s">
         <v>1917</v>
@@ -34696,7 +35272,7 @@
         <v>91</v>
       </c>
       <c r="C1916">
-        <v>5209.5</v>
+        <v>5902.8</v>
       </c>
       <c r="D1916" t="s">
         <v>1918</v>
@@ -34710,7 +35286,7 @@
         <v>92</v>
       </c>
       <c r="C1917">
-        <v>5190.2</v>
+        <v>5824.2</v>
       </c>
       <c r="D1917" t="s">
         <v>1919</v>
@@ -34724,7 +35300,7 @@
         <v>93</v>
       </c>
       <c r="C1918">
-        <v>4962.1</v>
+        <v>5708.3</v>
       </c>
       <c r="D1918" t="s">
         <v>1920</v>
@@ -34738,7 +35314,7 @@
         <v>94</v>
       </c>
       <c r="C1919">
-        <v>4900.1</v>
+        <v>5620.1</v>
       </c>
       <c r="D1919" t="s">
         <v>1921</v>
@@ -34752,7 +35328,7 @@
         <v>95</v>
       </c>
       <c r="C1920">
-        <v>4926.8</v>
+        <v>5597</v>
       </c>
       <c r="D1920" t="s">
         <v>1922</v>
@@ -34766,7 +35342,7 @@
         <v>96</v>
       </c>
       <c r="C1921">
-        <v>4892.7</v>
+        <v>5571.5</v>
       </c>
       <c r="D1921" t="s">
         <v>1923</v>
@@ -34780,7 +35356,7 @@
         <v>1</v>
       </c>
       <c r="C1922">
-        <v>5541.1</v>
+        <v>5412.9</v>
       </c>
       <c r="D1922" t="s">
         <v>1924</v>
@@ -34794,7 +35370,7 @@
         <v>2</v>
       </c>
       <c r="C1923">
-        <v>5620.8</v>
+        <v>5405.9</v>
       </c>
       <c r="D1923" t="s">
         <v>1925</v>
@@ -34808,7 +35384,7 @@
         <v>3</v>
       </c>
       <c r="C1924">
-        <v>5650.1</v>
+        <v>5367.9</v>
       </c>
       <c r="D1924" t="s">
         <v>1926</v>
@@ -34822,7 +35398,7 @@
         <v>4</v>
       </c>
       <c r="C1925">
-        <v>5684.3</v>
+        <v>5318</v>
       </c>
       <c r="D1925" t="s">
         <v>1927</v>
@@ -34836,7 +35412,7 @@
         <v>5</v>
       </c>
       <c r="C1926">
-        <v>5705.1</v>
+        <v>5192.8</v>
       </c>
       <c r="D1926" t="s">
         <v>1928</v>
@@ -34850,7 +35426,7 @@
         <v>6</v>
       </c>
       <c r="C1927">
-        <v>5716.4</v>
+        <v>5131.1</v>
       </c>
       <c r="D1927" t="s">
         <v>1929</v>
@@ -34864,7 +35440,7 @@
         <v>7</v>
       </c>
       <c r="C1928">
-        <v>5719.5</v>
+        <v>5073</v>
       </c>
       <c r="D1928" t="s">
         <v>1930</v>
@@ -34878,7 +35454,7 @@
         <v>8</v>
       </c>
       <c r="C1929">
-        <v>5724.1</v>
+        <v>5017.6</v>
       </c>
       <c r="D1929" t="s">
         <v>1931</v>
@@ -34892,7 +35468,7 @@
         <v>9</v>
       </c>
       <c r="C1930">
-        <v>5729.1</v>
+        <v>4902.9</v>
       </c>
       <c r="D1930" t="s">
         <v>1932</v>
@@ -34906,7 +35482,7 @@
         <v>10</v>
       </c>
       <c r="C1931">
-        <v>5714.7</v>
+        <v>4852.7</v>
       </c>
       <c r="D1931" t="s">
         <v>1933</v>
@@ -34920,7 +35496,7 @@
         <v>11</v>
       </c>
       <c r="C1932">
-        <v>5708.5</v>
+        <v>4817.8</v>
       </c>
       <c r="D1932" t="s">
         <v>1934</v>
@@ -34934,7 +35510,7 @@
         <v>12</v>
       </c>
       <c r="C1933">
-        <v>5716.5</v>
+        <v>4709.9</v>
       </c>
       <c r="D1933" t="s">
         <v>1935</v>
@@ -34948,7 +35524,7 @@
         <v>13</v>
       </c>
       <c r="C1934">
-        <v>5603.5</v>
+        <v>4717.4</v>
       </c>
       <c r="D1934" t="s">
         <v>1936</v>
@@ -34962,7 +35538,7 @@
         <v>14</v>
       </c>
       <c r="C1935">
-        <v>5607.4</v>
+        <v>4683.6</v>
       </c>
       <c r="D1935" t="s">
         <v>1937</v>
@@ -34976,7 +35552,7 @@
         <v>15</v>
       </c>
       <c r="C1936">
-        <v>5626.4</v>
+        <v>4621.8</v>
       </c>
       <c r="D1936" t="s">
         <v>1938</v>
@@ -34990,7 +35566,7 @@
         <v>16</v>
       </c>
       <c r="C1937">
-        <v>5633.9</v>
+        <v>4632.4</v>
       </c>
       <c r="D1937" t="s">
         <v>1939</v>
@@ -35004,7 +35580,7 @@
         <v>17</v>
       </c>
       <c r="C1938">
-        <v>5650.5</v>
+        <v>4471.5</v>
       </c>
       <c r="D1938" t="s">
         <v>1940</v>
@@ -35018,7 +35594,7 @@
         <v>18</v>
       </c>
       <c r="C1939">
-        <v>5650</v>
+        <v>4465.6</v>
       </c>
       <c r="D1939" t="s">
         <v>1941</v>
@@ -35032,7 +35608,7 @@
         <v>19</v>
       </c>
       <c r="C1940">
-        <v>5623.5</v>
+        <v>4424.1</v>
       </c>
       <c r="D1940" t="s">
         <v>1942</v>
@@ -35046,7 +35622,7 @@
         <v>20</v>
       </c>
       <c r="C1941">
-        <v>5630.7</v>
+        <v>4408</v>
       </c>
       <c r="D1941" t="s">
         <v>1943</v>
@@ -35060,7 +35636,7 @@
         <v>21</v>
       </c>
       <c r="C1942">
-        <v>5664.2</v>
+        <v>4371.9</v>
       </c>
       <c r="D1942" t="s">
         <v>1944</v>
@@ -35074,7 +35650,7 @@
         <v>22</v>
       </c>
       <c r="C1943">
-        <v>5684.9</v>
+        <v>4399.1</v>
       </c>
       <c r="D1943" t="s">
         <v>1945</v>
@@ -35088,7 +35664,7 @@
         <v>23</v>
       </c>
       <c r="C1944">
-        <v>5746</v>
+        <v>4433.1</v>
       </c>
       <c r="D1944" t="s">
         <v>1946</v>
@@ -35102,7 +35678,7 @@
         <v>24</v>
       </c>
       <c r="C1945">
-        <v>5773.2</v>
+        <v>4502.2</v>
       </c>
       <c r="D1945" t="s">
         <v>1947</v>
@@ -35116,7 +35692,7 @@
         <v>25</v>
       </c>
       <c r="C1946">
-        <v>5754.8</v>
+        <v>4460.7</v>
       </c>
       <c r="D1946" t="s">
         <v>1948</v>
@@ -35130,7 +35706,7 @@
         <v>26</v>
       </c>
       <c r="C1947">
-        <v>5755.7</v>
+        <v>4458.4</v>
       </c>
       <c r="D1947" t="s">
         <v>1949</v>
@@ -35144,7 +35720,7 @@
         <v>27</v>
       </c>
       <c r="C1948">
-        <v>5801.8</v>
+        <v>4460.7</v>
       </c>
       <c r="D1948" t="s">
         <v>1950</v>
@@ -35158,7 +35734,7 @@
         <v>28</v>
       </c>
       <c r="C1949">
-        <v>5855.1</v>
+        <v>4488.3</v>
       </c>
       <c r="D1949" t="s">
         <v>1951</v>
@@ -35172,7 +35748,7 @@
         <v>29</v>
       </c>
       <c r="C1950">
-        <v>6106.9</v>
+        <v>4830.5</v>
       </c>
       <c r="D1950" t="s">
         <v>1952</v>
@@ -35186,7 +35762,7 @@
         <v>30</v>
       </c>
       <c r="C1951">
-        <v>6137.8</v>
+        <v>4918.8</v>
       </c>
       <c r="D1951" t="s">
         <v>1953</v>
@@ -35200,7 +35776,7 @@
         <v>31</v>
       </c>
       <c r="C1952">
-        <v>6172.2</v>
+        <v>5106.4</v>
       </c>
       <c r="D1952" t="s">
         <v>1954</v>
@@ -35214,7 +35790,7 @@
         <v>32</v>
       </c>
       <c r="C1953">
-        <v>6229</v>
+        <v>5195.1</v>
       </c>
       <c r="D1953" t="s">
         <v>1955</v>
@@ -35228,7 +35804,7 @@
         <v>33</v>
       </c>
       <c r="C1954">
-        <v>6215.9</v>
+        <v>5506.3</v>
       </c>
       <c r="D1954" t="s">
         <v>1956</v>
@@ -35242,7 +35818,7 @@
         <v>34</v>
       </c>
       <c r="C1955">
-        <v>6293.4</v>
+        <v>5618.5</v>
       </c>
       <c r="D1955" t="s">
         <v>1957</v>
@@ -35256,7 +35832,7 @@
         <v>35</v>
       </c>
       <c r="C1956">
-        <v>6405.8</v>
+        <v>5782.7</v>
       </c>
       <c r="D1956" t="s">
         <v>1958</v>
@@ -35270,7 +35846,7 @@
         <v>36</v>
       </c>
       <c r="C1957">
-        <v>6326.1</v>
+        <v>5879.6</v>
       </c>
       <c r="D1957" t="s">
         <v>1959</v>
@@ -35284,7 +35860,7 @@
         <v>37</v>
       </c>
       <c r="C1958">
-        <v>6073.5</v>
+        <v>5966.6</v>
       </c>
       <c r="D1958" t="s">
         <v>1960</v>
@@ -35298,7 +35874,7 @@
         <v>38</v>
       </c>
       <c r="C1959">
-        <v>6101.6</v>
+        <v>6075.4</v>
       </c>
       <c r="D1959" t="s">
         <v>1961</v>
@@ -35312,7 +35888,7 @@
         <v>39</v>
       </c>
       <c r="C1960">
-        <v>6163.8</v>
+        <v>6112</v>
       </c>
       <c r="D1960" t="s">
         <v>1962</v>
@@ -35326,7 +35902,7 @@
         <v>40</v>
       </c>
       <c r="C1961">
-        <v>6180.9</v>
+        <v>6123.1</v>
       </c>
       <c r="D1961" t="s">
         <v>1963</v>
@@ -35340,7 +35916,7 @@
         <v>41</v>
       </c>
       <c r="C1962">
-        <v>6093.4</v>
+        <v>6146</v>
       </c>
       <c r="D1962" t="s">
         <v>1964</v>
@@ -35354,7 +35930,7 @@
         <v>42</v>
       </c>
       <c r="C1963">
-        <v>6094.8</v>
+        <v>6266.7</v>
       </c>
       <c r="D1963" t="s">
         <v>1965</v>
@@ -35368,7 +35944,7 @@
         <v>43</v>
       </c>
       <c r="C1964">
-        <v>6142.9</v>
+        <v>6362.5</v>
       </c>
       <c r="D1964" t="s">
         <v>1966</v>
@@ -35382,7 +35958,7 @@
         <v>44</v>
       </c>
       <c r="C1965">
-        <v>6157.1</v>
+        <v>6418.7</v>
       </c>
       <c r="D1965" t="s">
         <v>1967</v>
@@ -35396,7 +35972,7 @@
         <v>45</v>
       </c>
       <c r="C1966">
-        <v>5332.5</v>
+        <v>6582.7</v>
       </c>
       <c r="D1966" t="s">
         <v>1968</v>
@@ -35410,7 +35986,7 @@
         <v>46</v>
       </c>
       <c r="C1967">
-        <v>5354.4</v>
+        <v>6595.6</v>
       </c>
       <c r="D1967" t="s">
         <v>1969</v>
@@ -35424,7 +36000,7 @@
         <v>47</v>
       </c>
       <c r="C1968">
-        <v>5355.1</v>
+        <v>6643.7</v>
       </c>
       <c r="D1968" t="s">
         <v>1970</v>
@@ -35438,7 +36014,7 @@
         <v>48</v>
       </c>
       <c r="C1969">
-        <v>5419.3</v>
+        <v>6698.3</v>
       </c>
       <c r="D1969" t="s">
         <v>1971</v>
@@ -35452,7 +36028,7 @@
         <v>49</v>
       </c>
       <c r="C1970">
-        <v>5252.3</v>
+        <v>6691.9</v>
       </c>
       <c r="D1970" t="s">
         <v>1972</v>
@@ -35466,7 +36042,7 @@
         <v>50</v>
       </c>
       <c r="C1971">
-        <v>5287.7</v>
+        <v>6782.2</v>
       </c>
       <c r="D1971" t="s">
         <v>1973</v>
@@ -35480,7 +36056,7 @@
         <v>51</v>
       </c>
       <c r="C1972">
-        <v>5178</v>
+        <v>6874.5</v>
       </c>
       <c r="D1972" t="s">
         <v>1974</v>
@@ -35494,7 +36070,7 @@
         <v>52</v>
       </c>
       <c r="C1973">
-        <v>5152.9</v>
+        <v>6918.4</v>
       </c>
       <c r="D1973" t="s">
         <v>1975</v>
@@ -35508,7 +36084,7 @@
         <v>53</v>
       </c>
       <c r="C1974">
-        <v>5225.8</v>
+        <v>6915.3</v>
       </c>
       <c r="D1974" t="s">
         <v>1976</v>
@@ -35522,7 +36098,7 @@
         <v>54</v>
       </c>
       <c r="C1975">
-        <v>5181.9</v>
+        <v>6971.3</v>
       </c>
       <c r="D1975" t="s">
         <v>1977</v>
@@ -35536,7 +36112,7 @@
         <v>55</v>
       </c>
       <c r="C1976">
-        <v>5187.6</v>
+        <v>7023.6</v>
       </c>
       <c r="D1976" t="s">
         <v>1978</v>
@@ -35550,7 +36126,7 @@
         <v>56</v>
       </c>
       <c r="C1977">
-        <v>5219.4</v>
+        <v>7065.5</v>
       </c>
       <c r="D1977" t="s">
         <v>1979</v>
@@ -35564,7 +36140,7 @@
         <v>57</v>
       </c>
       <c r="C1978">
-        <v>5233.4</v>
+        <v>6775.3</v>
       </c>
       <c r="D1978" t="s">
         <v>1980</v>
@@ -35578,7 +36154,7 @@
         <v>58</v>
       </c>
       <c r="C1979">
-        <v>5259.3</v>
+        <v>6839.8</v>
       </c>
       <c r="D1979" t="s">
         <v>1981</v>
@@ -35592,7 +36168,7 @@
         <v>59</v>
       </c>
       <c r="C1980">
-        <v>5272.4</v>
+        <v>6858.9</v>
       </c>
       <c r="D1980" t="s">
         <v>1982</v>
@@ -35606,7 +36182,7 @@
         <v>60</v>
       </c>
       <c r="C1981">
-        <v>5310.2</v>
+        <v>6882.6</v>
       </c>
       <c r="D1981" t="s">
         <v>1983</v>
@@ -35620,7 +36196,7 @@
         <v>61</v>
       </c>
       <c r="C1982">
-        <v>5490.9</v>
+        <v>7243.4</v>
       </c>
       <c r="D1982" t="s">
         <v>1984</v>
@@ -35634,7 +36210,7 @@
         <v>62</v>
       </c>
       <c r="C1983">
-        <v>5520.1</v>
+        <v>7257.4</v>
       </c>
       <c r="D1983" t="s">
         <v>1985</v>
@@ -35648,7 +36224,7 @@
         <v>63</v>
       </c>
       <c r="C1984">
-        <v>5545.6</v>
+        <v>7209</v>
       </c>
       <c r="D1984" t="s">
         <v>1986</v>
@@ -35662,7 +36238,7 @@
         <v>64</v>
       </c>
       <c r="C1985">
-        <v>5527.7</v>
+        <v>7181.5</v>
       </c>
       <c r="D1985" t="s">
         <v>1987</v>
@@ -35676,7 +36252,7 @@
         <v>65</v>
       </c>
       <c r="C1986">
-        <v>5373</v>
+        <v>7018.6</v>
       </c>
       <c r="D1986" t="s">
         <v>1988</v>
@@ -35690,7 +36266,7 @@
         <v>66</v>
       </c>
       <c r="C1987">
-        <v>5334.1</v>
+        <v>6938.5</v>
       </c>
       <c r="D1987" t="s">
         <v>1989</v>
@@ -35704,7 +36280,7 @@
         <v>67</v>
       </c>
       <c r="C1988">
-        <v>5291.6</v>
+        <v>6866.6</v>
       </c>
       <c r="D1988" t="s">
         <v>1990</v>
@@ -35718,7 +36294,7 @@
         <v>68</v>
       </c>
       <c r="C1989">
-        <v>5274.9</v>
+        <v>6785.5</v>
       </c>
       <c r="D1989" t="s">
         <v>1991</v>
@@ -35732,7 +36308,7 @@
         <v>69</v>
       </c>
       <c r="C1990">
-        <v>5676.3</v>
+        <v>6639.3</v>
       </c>
       <c r="D1990" t="s">
         <v>1992</v>
@@ -35746,7 +36322,7 @@
         <v>70</v>
       </c>
       <c r="C1991">
-        <v>5600</v>
+        <v>6491.6</v>
       </c>
       <c r="D1991" t="s">
         <v>1993</v>
@@ -35760,7 +36336,7 @@
         <v>71</v>
       </c>
       <c r="C1992">
-        <v>5488.5</v>
+        <v>6359.5</v>
       </c>
       <c r="D1992" t="s">
         <v>1994</v>
@@ -35774,7 +36350,7 @@
         <v>72</v>
       </c>
       <c r="C1993">
-        <v>5356.4</v>
+        <v>6220.1</v>
       </c>
       <c r="D1993" t="s">
         <v>1995</v>
@@ -35788,7 +36364,7 @@
         <v>73</v>
       </c>
       <c r="C1994">
-        <v>5359.2</v>
+        <v>6081</v>
       </c>
       <c r="D1994" t="s">
         <v>1996</v>
@@ -35802,7 +36378,7 @@
         <v>74</v>
       </c>
       <c r="C1995">
-        <v>5205.3</v>
+        <v>5892.6</v>
       </c>
       <c r="D1995" t="s">
         <v>1997</v>
@@ -35816,7 +36392,7 @@
         <v>75</v>
       </c>
       <c r="C1996">
-        <v>5016.7</v>
+        <v>5779.7</v>
       </c>
       <c r="D1996" t="s">
         <v>1998</v>
@@ -35830,7 +36406,7 @@
         <v>76</v>
       </c>
       <c r="C1997">
-        <v>4933.1</v>
+        <v>5681.9</v>
       </c>
       <c r="D1997" t="s">
         <v>1999</v>
@@ -35844,7 +36420,7 @@
         <v>77</v>
       </c>
       <c r="C1998">
-        <v>4910.3</v>
+        <v>5496.7</v>
       </c>
       <c r="D1998" t="s">
         <v>2000</v>
@@ -35858,7 +36434,7 @@
         <v>78</v>
       </c>
       <c r="C1999">
-        <v>4809.2</v>
+        <v>5450.1</v>
       </c>
       <c r="D1999" t="s">
         <v>2001</v>
@@ -35872,7 +36448,7 @@
         <v>79</v>
       </c>
       <c r="C2000">
-        <v>4706.6</v>
+        <v>5440.9</v>
       </c>
       <c r="D2000" t="s">
         <v>2002</v>
@@ -35886,7 +36462,7 @@
         <v>80</v>
       </c>
       <c r="C2001">
-        <v>4684.2</v>
+        <v>5437.1</v>
       </c>
       <c r="D2001" t="s">
         <v>2003</v>
@@ -35900,7 +36476,7 @@
         <v>81</v>
       </c>
       <c r="C2002">
-        <v>5053.7</v>
+        <v>5816.3</v>
       </c>
       <c r="D2002" t="s">
         <v>2004</v>
@@ -35914,7 +36490,7 @@
         <v>82</v>
       </c>
       <c r="C2003">
-        <v>5107.8</v>
+        <v>5799</v>
       </c>
       <c r="D2003" t="s">
         <v>2005</v>
@@ -35928,7 +36504,7 @@
         <v>83</v>
       </c>
       <c r="C2004">
-        <v>5126.2</v>
+        <v>5776.9</v>
       </c>
       <c r="D2004" t="s">
         <v>2006</v>
@@ -35942,7 +36518,7 @@
         <v>84</v>
       </c>
       <c r="C2005">
-        <v>5135.4</v>
+        <v>5796.9</v>
       </c>
       <c r="D2005" t="s">
         <v>2007</v>
@@ -35956,7 +36532,7 @@
         <v>85</v>
       </c>
       <c r="C2006">
-        <v>5088.2</v>
+        <v>5646.5</v>
       </c>
       <c r="D2006" t="s">
         <v>2008</v>
@@ -35970,7 +36546,7 @@
         <v>86</v>
       </c>
       <c r="C2007">
-        <v>5053.6</v>
+        <v>5641.1</v>
       </c>
       <c r="D2007" t="s">
         <v>2009</v>
@@ -35984,7 +36560,7 @@
         <v>87</v>
       </c>
       <c r="C2008">
-        <v>5077.7</v>
+        <v>5622.9</v>
       </c>
       <c r="D2008" t="s">
         <v>2010</v>
@@ -35998,7 +36574,7 @@
         <v>88</v>
       </c>
       <c r="C2009">
-        <v>5002.2</v>
+        <v>5480.1</v>
       </c>
       <c r="D2009" t="s">
         <v>2011</v>
@@ -36012,7 +36588,7 @@
         <v>89</v>
       </c>
       <c r="C2010">
-        <v>4644.4</v>
+        <v>5188.1</v>
       </c>
       <c r="D2010" t="s">
         <v>2012</v>
@@ -36026,7 +36602,7 @@
         <v>90</v>
       </c>
       <c r="C2011">
-        <v>4598.5</v>
+        <v>5160.2</v>
       </c>
       <c r="D2011" t="s">
         <v>2013</v>
@@ -36040,7 +36616,7 @@
         <v>91</v>
       </c>
       <c r="C2012">
-        <v>4522.5</v>
+        <v>5099</v>
       </c>
       <c r="D2012" t="s">
         <v>2014</v>
@@ -36054,7 +36630,7 @@
         <v>92</v>
       </c>
       <c r="C2013">
-        <v>4452.2</v>
+        <v>5038.5</v>
       </c>
       <c r="D2013" t="s">
         <v>2015</v>
@@ -36068,7 +36644,7 @@
         <v>93</v>
       </c>
       <c r="C2014">
-        <v>4141</v>
+        <v>4849.4</v>
       </c>
       <c r="D2014" t="s">
         <v>2016</v>
@@ -36082,7 +36658,7 @@
         <v>94</v>
       </c>
       <c r="C2015">
-        <v>4067.8</v>
+        <v>4784.9</v>
       </c>
       <c r="D2015" t="s">
         <v>2017</v>
@@ -36096,7 +36672,7 @@
         <v>95</v>
       </c>
       <c r="C2016">
-        <v>4054</v>
+        <v>4753.7</v>
       </c>
       <c r="D2016" t="s">
         <v>2018</v>
@@ -36110,7 +36686,7 @@
         <v>96</v>
       </c>
       <c r="C2017">
-        <v>4040.3</v>
+        <v>4678.1</v>
       </c>
       <c r="D2017" t="s">
         <v>2019</v>
@@ -36124,7 +36700,7 @@
         <v>1</v>
       </c>
       <c r="C2018">
-        <v>5491.1</v>
+        <v>5362.9</v>
       </c>
       <c r="D2018" t="s">
         <v>2020</v>
@@ -36138,7 +36714,7 @@
         <v>2</v>
       </c>
       <c r="C2019">
-        <v>5550.8</v>
+        <v>5365.9</v>
       </c>
       <c r="D2019" t="s">
         <v>2021</v>
@@ -36152,7 +36728,7 @@
         <v>3</v>
       </c>
       <c r="C2020">
-        <v>5590.1</v>
+        <v>5337.9</v>
       </c>
       <c r="D2020" t="s">
         <v>2022</v>
@@ -36166,7 +36742,7 @@
         <v>4</v>
       </c>
       <c r="C2021">
-        <v>5634.3</v>
+        <v>5278</v>
       </c>
       <c r="D2021" t="s">
         <v>2023</v>
@@ -36180,7 +36756,7 @@
         <v>5</v>
       </c>
       <c r="C2022">
-        <v>5645.1</v>
+        <v>5152.8</v>
       </c>
       <c r="D2022" t="s">
         <v>2024</v>
@@ -36194,7 +36770,7 @@
         <v>6</v>
       </c>
       <c r="C2023">
-        <v>5646.4</v>
+        <v>5111.1</v>
       </c>
       <c r="D2023" t="s">
         <v>2025</v>
@@ -36208,7 +36784,7 @@
         <v>7</v>
       </c>
       <c r="C2024">
-        <v>5649.5</v>
+        <v>5073</v>
       </c>
       <c r="D2024" t="s">
         <v>2026</v>
@@ -36222,7 +36798,7 @@
         <v>8</v>
       </c>
       <c r="C2025">
-        <v>5654.1</v>
+        <v>5017.6</v>
       </c>
       <c r="D2025" t="s">
         <v>2027</v>
@@ -36236,7 +36812,7 @@
         <v>9</v>
       </c>
       <c r="C2026">
-        <v>5669.1</v>
+        <v>4922.9</v>
       </c>
       <c r="D2026" t="s">
         <v>2028</v>
@@ -36250,7 +36826,7 @@
         <v>10</v>
       </c>
       <c r="C2027">
-        <v>5644.7</v>
+        <v>4862.7</v>
       </c>
       <c r="D2027" t="s">
         <v>2029</v>
@@ -36264,7 +36840,7 @@
         <v>11</v>
       </c>
       <c r="C2028">
-        <v>5628.5</v>
+        <v>4817.8</v>
       </c>
       <c r="D2028" t="s">
         <v>2030</v>
@@ -36278,7 +36854,7 @@
         <v>12</v>
       </c>
       <c r="C2029">
-        <v>5636.5</v>
+        <v>4679.9</v>
       </c>
       <c r="D2029" t="s">
         <v>2031</v>
@@ -36292,7 +36868,7 @@
         <v>13</v>
       </c>
       <c r="C2030">
-        <v>5503.5</v>
+        <v>4637.4</v>
       </c>
       <c r="D2030" t="s">
         <v>2032</v>
@@ -36306,7 +36882,7 @@
         <v>14</v>
       </c>
       <c r="C2031">
-        <v>5487.4</v>
+        <v>4573.6</v>
       </c>
       <c r="D2031" t="s">
         <v>2033</v>
@@ -36320,7 +36896,7 @@
         <v>15</v>
       </c>
       <c r="C2032">
-        <v>5496.4</v>
+        <v>4471.8</v>
       </c>
       <c r="D2032" t="s">
         <v>2034</v>
@@ -36334,7 +36910,7 @@
         <v>16</v>
       </c>
       <c r="C2033">
-        <v>5503.9</v>
+        <v>4432.4</v>
       </c>
       <c r="D2033" t="s">
         <v>2035</v>
@@ -36348,7 +36924,7 @@
         <v>17</v>
       </c>
       <c r="C2034">
-        <v>5520.5</v>
+        <v>4231.5</v>
       </c>
       <c r="D2034" t="s">
         <v>2036</v>
@@ -36362,7 +36938,7 @@
         <v>18</v>
       </c>
       <c r="C2035">
-        <v>5510</v>
+        <v>4205.6</v>
       </c>
       <c r="D2035" t="s">
         <v>2037</v>
@@ -36376,7 +36952,7 @@
         <v>19</v>
       </c>
       <c r="C2036">
-        <v>5483.5</v>
+        <v>4154.1</v>
       </c>
       <c r="D2036" t="s">
         <v>2038</v>
@@ -36390,7 +36966,7 @@
         <v>20</v>
       </c>
       <c r="C2037">
-        <v>5470.7</v>
+        <v>4128</v>
       </c>
       <c r="D2037" t="s">
         <v>2039</v>
@@ -36404,7 +36980,7 @@
         <v>21</v>
       </c>
       <c r="C2038">
-        <v>5474.2</v>
+        <v>4041.9</v>
       </c>
       <c r="D2038" t="s">
         <v>2040</v>
@@ -36418,7 +36994,7 @@
         <v>22</v>
       </c>
       <c r="C2039">
-        <v>5454.9</v>
+        <v>4029.1</v>
       </c>
       <c r="D2039" t="s">
         <v>2041</v>
@@ -36432,7 +37008,7 @@
         <v>23</v>
       </c>
       <c r="C2040">
-        <v>5466</v>
+        <v>4063.1</v>
       </c>
       <c r="D2040" t="s">
         <v>2042</v>
@@ -36446,7 +37022,7 @@
         <v>24</v>
       </c>
       <c r="C2041">
-        <v>5423.2</v>
+        <v>4122.2</v>
       </c>
       <c r="D2041" t="s">
         <v>2043</v>
@@ -36460,7 +37036,7 @@
         <v>25</v>
       </c>
       <c r="C2042">
-        <v>5334.8</v>
+        <v>4070.7</v>
       </c>
       <c r="D2042" t="s">
         <v>2044</v>
@@ -36474,7 +37050,7 @@
         <v>26</v>
       </c>
       <c r="C2043">
-        <v>5255.7</v>
+        <v>4018.4</v>
       </c>
       <c r="D2043" t="s">
         <v>2045</v>
@@ -36488,7 +37064,7 @@
         <v>27</v>
       </c>
       <c r="C2044">
-        <v>5221.8</v>
+        <v>3940.7</v>
       </c>
       <c r="D2044" t="s">
         <v>2046</v>
@@ -36502,7 +37078,7 @@
         <v>28</v>
       </c>
       <c r="C2045">
-        <v>5205.1</v>
+        <v>3838.3</v>
       </c>
       <c r="D2045" t="s">
         <v>2047</v>
@@ -36516,7 +37092,7 @@
         <v>29</v>
       </c>
       <c r="C2046">
-        <v>5386.9</v>
+        <v>4000.5</v>
       </c>
       <c r="D2046" t="s">
         <v>2048</v>
@@ -36530,7 +37106,7 @@
         <v>30</v>
       </c>
       <c r="C2047">
-        <v>5357.8</v>
+        <v>3988.8</v>
       </c>
       <c r="D2047" t="s">
         <v>2049</v>
@@ -36544,7 +37120,7 @@
         <v>31</v>
       </c>
       <c r="C2048">
-        <v>5342.2</v>
+        <v>4096.4</v>
       </c>
       <c r="D2048" t="s">
         <v>2050</v>
@@ -36558,7 +37134,7 @@
         <v>32</v>
       </c>
       <c r="C2049">
-        <v>5339</v>
+        <v>4115.1</v>
       </c>
       <c r="D2049" t="s">
         <v>2051</v>
@@ -36572,7 +37148,7 @@
         <v>33</v>
       </c>
       <c r="C2050">
-        <v>5295.9</v>
+        <v>4346.3</v>
       </c>
       <c r="D2050" t="s">
         <v>2052</v>
@@ -36586,7 +37162,7 @@
         <v>34</v>
       </c>
       <c r="C2051">
-        <v>5343.4</v>
+        <v>4398.5</v>
       </c>
       <c r="D2051" t="s">
         <v>2053</v>
@@ -36600,7 +37176,7 @@
         <v>35</v>
       </c>
       <c r="C2052">
-        <v>5425.8</v>
+        <v>4512.7</v>
       </c>
       <c r="D2052" t="s">
         <v>2054</v>
@@ -36614,7 +37190,7 @@
         <v>36</v>
       </c>
       <c r="C2053">
-        <v>5336.1</v>
+        <v>4579.6</v>
       </c>
       <c r="D2053" t="s">
         <v>2055</v>
@@ -36628,7 +37204,7 @@
         <v>37</v>
       </c>
       <c r="C2054">
-        <v>5073.5</v>
+        <v>4696.6</v>
       </c>
       <c r="D2054" t="s">
         <v>2056</v>
@@ -36642,7 +37218,7 @@
         <v>38</v>
       </c>
       <c r="C2055">
-        <v>5101.6</v>
+        <v>4835.4</v>
       </c>
       <c r="D2055" t="s">
         <v>2057</v>
@@ -36656,7 +37232,7 @@
         <v>39</v>
       </c>
       <c r="C2056">
-        <v>5173.8</v>
+        <v>4892</v>
       </c>
       <c r="D2056" t="s">
         <v>2058</v>
@@ -36670,7 +37246,7 @@
         <v>40</v>
       </c>
       <c r="C2057">
-        <v>5200.9</v>
+        <v>4943.1</v>
       </c>
       <c r="D2057" t="s">
         <v>2059</v>
@@ -36684,7 +37260,7 @@
         <v>41</v>
       </c>
       <c r="C2058">
-        <v>5143.4</v>
+        <v>4976</v>
       </c>
       <c r="D2058" t="s">
         <v>2060</v>
@@ -36698,7 +37274,7 @@
         <v>42</v>
       </c>
       <c r="C2059">
-        <v>5164.8</v>
+        <v>5146.7</v>
       </c>
       <c r="D2059" t="s">
         <v>2061</v>
@@ -36712,7 +37288,7 @@
         <v>43</v>
       </c>
       <c r="C2060">
-        <v>5242.9</v>
+        <v>5272.5</v>
       </c>
       <c r="D2060" t="s">
         <v>2062</v>
@@ -36726,7 +37302,7 @@
         <v>44</v>
       </c>
       <c r="C2061">
-        <v>5287.1</v>
+        <v>5378.7</v>
       </c>
       <c r="D2061" t="s">
         <v>2063</v>
@@ -36740,7 +37316,7 @@
         <v>45</v>
       </c>
       <c r="C2062">
-        <v>4492.5</v>
+        <v>5622.7</v>
       </c>
       <c r="D2062" t="s">
         <v>2064</v>
@@ -36754,7 +37330,7 @@
         <v>46</v>
       </c>
       <c r="C2063">
-        <v>4534.4</v>
+        <v>5725.6</v>
       </c>
       <c r="D2063" t="s">
         <v>2065</v>
@@ -36768,7 +37344,7 @@
         <v>47</v>
       </c>
       <c r="C2064">
-        <v>4545.1</v>
+        <v>5783.7</v>
       </c>
       <c r="D2064" t="s">
         <v>2066</v>
@@ -36782,7 +37358,7 @@
         <v>48</v>
       </c>
       <c r="C2065">
-        <v>4619.3</v>
+        <v>5828.3</v>
       </c>
       <c r="D2065" t="s">
         <v>2067</v>
@@ -36796,7 +37372,7 @@
         <v>49</v>
       </c>
       <c r="C2066">
-        <v>4452.3</v>
+        <v>5781.9</v>
       </c>
       <c r="D2066" t="s">
         <v>2068</v>
@@ -36810,7 +37386,7 @@
         <v>50</v>
       </c>
       <c r="C2067">
-        <v>4477.7</v>
+        <v>5862.2</v>
       </c>
       <c r="D2067" t="s">
         <v>2069</v>
@@ -36824,7 +37400,7 @@
         <v>51</v>
       </c>
       <c r="C2068">
-        <v>4358</v>
+        <v>5954.5</v>
       </c>
       <c r="D2068" t="s">
         <v>2070</v>
@@ -36838,7 +37414,7 @@
         <v>52</v>
       </c>
       <c r="C2069">
-        <v>4322.9</v>
+        <v>5988.4</v>
       </c>
       <c r="D2069" t="s">
         <v>2071</v>
@@ -36852,7 +37428,7 @@
         <v>53</v>
       </c>
       <c r="C2070">
-        <v>4385.8</v>
+        <v>5975.3</v>
       </c>
       <c r="D2070" t="s">
         <v>2072</v>
@@ -36866,7 +37442,7 @@
         <v>54</v>
       </c>
       <c r="C2071">
-        <v>4331.9</v>
+        <v>6021.3</v>
       </c>
       <c r="D2071" t="s">
         <v>2073</v>
@@ -36880,7 +37456,7 @@
         <v>55</v>
       </c>
       <c r="C2072">
-        <v>4327.6</v>
+        <v>6083.6</v>
       </c>
       <c r="D2072" t="s">
         <v>2074</v>
@@ -36894,7 +37470,7 @@
         <v>56</v>
       </c>
       <c r="C2073">
-        <v>4349.4</v>
+        <v>6135.5</v>
       </c>
       <c r="D2073" t="s">
         <v>2075</v>
@@ -36908,7 +37484,7 @@
         <v>57</v>
       </c>
       <c r="C2074">
-        <v>4373.4</v>
+        <v>5865.3</v>
       </c>
       <c r="D2074" t="s">
         <v>2076</v>
@@ -36922,7 +37498,7 @@
         <v>58</v>
       </c>
       <c r="C2075">
-        <v>4389.3</v>
+        <v>5959.8</v>
       </c>
       <c r="D2075" t="s">
         <v>2077</v>
@@ -36936,7 +37512,7 @@
         <v>59</v>
       </c>
       <c r="C2076">
-        <v>4402.4</v>
+        <v>6008.9</v>
       </c>
       <c r="D2076" t="s">
         <v>2078</v>
@@ -36950,7 +37526,7 @@
         <v>60</v>
       </c>
       <c r="C2077">
-        <v>4450.2</v>
+        <v>6052.6</v>
       </c>
       <c r="D2077" t="s">
         <v>2079</v>
@@ -36964,7 +37540,7 @@
         <v>61</v>
       </c>
       <c r="C2078">
-        <v>4640.9</v>
+        <v>6423.4</v>
       </c>
       <c r="D2078" t="s">
         <v>2080</v>
@@ -36978,7 +37554,7 @@
         <v>62</v>
       </c>
       <c r="C2079">
-        <v>4670.1</v>
+        <v>6457.4</v>
       </c>
       <c r="D2079" t="s">
         <v>2081</v>
@@ -36992,7 +37568,7 @@
         <v>63</v>
       </c>
       <c r="C2080">
-        <v>4695.6</v>
+        <v>6449</v>
       </c>
       <c r="D2080" t="s">
         <v>2082</v>
@@ -37006,7 +37582,7 @@
         <v>64</v>
       </c>
       <c r="C2081">
-        <v>4687.7</v>
+        <v>6451.5</v>
       </c>
       <c r="D2081" t="s">
         <v>2083</v>
@@ -37020,7 +37596,7 @@
         <v>65</v>
       </c>
       <c r="C2082">
-        <v>4553</v>
+        <v>6318.6</v>
       </c>
       <c r="D2082" t="s">
         <v>2084</v>
@@ -37034,7 +37610,7 @@
         <v>66</v>
       </c>
       <c r="C2083">
-        <v>4534.1</v>
+        <v>6268.5</v>
       </c>
       <c r="D2083" t="s">
         <v>2085</v>
@@ -37048,7 +37624,7 @@
         <v>67</v>
       </c>
       <c r="C2084">
-        <v>4511.6</v>
+        <v>6216.6</v>
       </c>
       <c r="D2084" t="s">
         <v>2086</v>
@@ -37062,7 +37638,7 @@
         <v>68</v>
       </c>
       <c r="C2085">
-        <v>4514.9</v>
+        <v>6115.5</v>
       </c>
       <c r="D2085" t="s">
         <v>2087</v>
@@ -37076,7 +37652,7 @@
         <v>69</v>
       </c>
       <c r="C2086">
-        <v>4946.3</v>
+        <v>5989.3</v>
       </c>
       <c r="D2086" t="s">
         <v>2088</v>
@@ -37090,7 +37666,7 @@
         <v>70</v>
       </c>
       <c r="C2087">
-        <v>4900</v>
+        <v>5831.6</v>
       </c>
       <c r="D2087" t="s">
         <v>2089</v>
@@ -37104,7 +37680,7 @@
         <v>71</v>
       </c>
       <c r="C2088">
-        <v>4808.5</v>
+        <v>5679.5</v>
       </c>
       <c r="D2088" t="s">
         <v>2090</v>
@@ -37118,7 +37694,7 @@
         <v>72</v>
       </c>
       <c r="C2089">
-        <v>4696.4</v>
+        <v>5530.1</v>
       </c>
       <c r="D2089" t="s">
         <v>2091</v>
@@ -37132,7 +37708,7 @@
         <v>73</v>
       </c>
       <c r="C2090">
-        <v>4719.2</v>
+        <v>5351</v>
       </c>
       <c r="D2090" t="s">
         <v>2092</v>
@@ -37146,7 +37722,7 @@
         <v>74</v>
       </c>
       <c r="C2091">
-        <v>4585.3</v>
+        <v>5172.6</v>
       </c>
       <c r="D2091" t="s">
         <v>2093</v>
@@ -37160,7 +37736,7 @@
         <v>75</v>
       </c>
       <c r="C2092">
-        <v>4416.7</v>
+        <v>5059.7</v>
       </c>
       <c r="D2092" t="s">
         <v>2094</v>
@@ -37174,7 +37750,7 @@
         <v>76</v>
       </c>
       <c r="C2093">
-        <v>4353.1</v>
+        <v>4981.9</v>
       </c>
       <c r="D2093" t="s">
         <v>2095</v>
@@ -37188,7 +37764,7 @@
         <v>77</v>
       </c>
       <c r="C2094">
-        <v>4350.3</v>
+        <v>4836.7</v>
       </c>
       <c r="D2094" t="s">
         <v>2096</v>
@@ -37202,7 +37778,7 @@
         <v>78</v>
       </c>
       <c r="C2095">
-        <v>4289.2</v>
+        <v>4820.1</v>
       </c>
       <c r="D2095" t="s">
         <v>2097</v>
@@ -37216,7 +37792,7 @@
         <v>79</v>
       </c>
       <c r="C2096">
-        <v>4216.6</v>
+        <v>4840.9</v>
       </c>
       <c r="D2096" t="s">
         <v>2098</v>
@@ -37230,7 +37806,7 @@
         <v>80</v>
       </c>
       <c r="C2097">
-        <v>4224.2</v>
+        <v>4867.1</v>
       </c>
       <c r="D2097" t="s">
         <v>2099</v>
@@ -37244,7 +37820,7 @@
         <v>81</v>
       </c>
       <c r="C2098">
-        <v>4623.7</v>
+        <v>5296.3</v>
       </c>
       <c r="D2098" t="s">
         <v>2100</v>
@@ -37258,7 +37834,7 @@
         <v>82</v>
       </c>
       <c r="C2099">
-        <v>4707.8</v>
+        <v>5319</v>
       </c>
       <c r="D2099" t="s">
         <v>2101</v>
@@ -37272,7 +37848,7 @@
         <v>83</v>
       </c>
       <c r="C2100">
-        <v>4736.2</v>
+        <v>5286.9</v>
       </c>
       <c r="D2100" t="s">
         <v>2102</v>
@@ -37286,7 +37862,7 @@
         <v>84</v>
       </c>
       <c r="C2101">
-        <v>4735.4</v>
+        <v>5276.9</v>
       </c>
       <c r="D2101" t="s">
         <v>2103</v>
@@ -37300,7 +37876,7 @@
         <v>85</v>
       </c>
       <c r="C2102">
-        <v>4688.2</v>
+        <v>5126.5</v>
       </c>
       <c r="D2102" t="s">
         <v>2104</v>
@@ -37314,7 +37890,7 @@
         <v>86</v>
       </c>
       <c r="C2103">
-        <v>4643.6</v>
+        <v>5121.1</v>
       </c>
       <c r="D2103" t="s">
         <v>2105</v>
@@ -37328,7 +37904,7 @@
         <v>87</v>
       </c>
       <c r="C2104">
-        <v>4677.7</v>
+        <v>5132.9</v>
       </c>
       <c r="D2104" t="s">
         <v>2106</v>
@@ -37342,7 +37918,7 @@
         <v>88</v>
       </c>
       <c r="C2105">
-        <v>4652.2</v>
+        <v>5040.1</v>
       </c>
       <c r="D2105" t="s">
         <v>2107</v>
@@ -37356,7 +37932,7 @@
         <v>89</v>
       </c>
       <c r="C2106">
-        <v>4334.4</v>
+        <v>4848.1</v>
       </c>
       <c r="D2106" t="s">
         <v>2108</v>
@@ -37370,7 +37946,7 @@
         <v>90</v>
       </c>
       <c r="C2107">
-        <v>4318.5</v>
+        <v>4890.2</v>
       </c>
       <c r="D2107" t="s">
         <v>2109</v>
@@ -37384,7 +37960,7 @@
         <v>91</v>
       </c>
       <c r="C2108">
-        <v>4252.5</v>
+        <v>4809</v>
       </c>
       <c r="D2108" t="s">
         <v>2110</v>
@@ -37398,7 +37974,7 @@
         <v>92</v>
       </c>
       <c r="C2109">
-        <v>4172.2</v>
+        <v>4688.5</v>
       </c>
       <c r="D2109" t="s">
         <v>2111</v>
@@ -37412,7 +37988,7 @@
         <v>93</v>
       </c>
       <c r="C2110">
-        <v>3881</v>
+        <v>4399.4</v>
       </c>
       <c r="D2110" t="s">
         <v>2112</v>
@@ -37426,7 +38002,7 @@
         <v>94</v>
       </c>
       <c r="C2111">
-        <v>3787.8</v>
+        <v>4284.9</v>
       </c>
       <c r="D2111" t="s">
         <v>2113</v>
@@ -37440,7 +38016,7 @@
         <v>95</v>
       </c>
       <c r="C2112">
-        <v>3804</v>
+        <v>4303.7</v>
       </c>
       <c r="D2112" t="s">
         <v>2114</v>
@@ -37454,7 +38030,7 @@
         <v>96</v>
       </c>
       <c r="C2113">
-        <v>3790.3</v>
+        <v>4228.1</v>
       </c>
       <c r="D2113" t="s">
         <v>2115</v>
@@ -37468,7 +38044,7 @@
         <v>1</v>
       </c>
       <c r="C2114">
-        <v>5261.1</v>
+        <v>4817.7</v>
       </c>
       <c r="D2114" t="s">
         <v>2116</v>
@@ -37482,7 +38058,7 @@
         <v>2</v>
       </c>
       <c r="C2115">
-        <v>5320.8</v>
+        <v>4854</v>
       </c>
       <c r="D2115" t="s">
         <v>2117</v>
@@ -37496,7 +38072,7 @@
         <v>3</v>
       </c>
       <c r="C2116">
-        <v>5360.1</v>
+        <v>4873.5</v>
       </c>
       <c r="D2116" t="s">
         <v>2118</v>
@@ -37510,7 +38086,7 @@
         <v>4</v>
       </c>
       <c r="C2117">
-        <v>5404.3</v>
+        <v>4821.2</v>
       </c>
       <c r="D2117" t="s">
         <v>2119</v>
@@ -37524,7 +38100,7 @@
         <v>5</v>
       </c>
       <c r="C2118">
-        <v>5405.1</v>
+        <v>4828.6</v>
       </c>
       <c r="D2118" t="s">
         <v>2120</v>
@@ -37538,7 +38114,7 @@
         <v>6</v>
       </c>
       <c r="C2119">
-        <v>5396.4</v>
+        <v>4799.4</v>
       </c>
       <c r="D2119" t="s">
         <v>2121</v>
@@ -37552,7 +38128,7 @@
         <v>7</v>
       </c>
       <c r="C2120">
-        <v>5399.5</v>
+        <v>4775.2</v>
       </c>
       <c r="D2120" t="s">
         <v>2122</v>
@@ -37566,7 +38142,7 @@
         <v>8</v>
       </c>
       <c r="C2121">
-        <v>5404.1</v>
+        <v>4741.8</v>
       </c>
       <c r="D2121" t="s">
         <v>2123</v>
@@ -37580,7 +38156,7 @@
         <v>9</v>
       </c>
       <c r="C2122">
-        <v>5419.1</v>
+        <v>4716.9</v>
       </c>
       <c r="D2122" t="s">
         <v>2124</v>
@@ -37594,7 +38170,7 @@
         <v>10</v>
       </c>
       <c r="C2123">
-        <v>5394.7</v>
+        <v>4689.8</v>
       </c>
       <c r="D2123" t="s">
         <v>2125</v>
@@ -37608,7 +38184,7 @@
         <v>11</v>
       </c>
       <c r="C2124">
-        <v>5378.5</v>
+        <v>4662.6</v>
       </c>
       <c r="D2124" t="s">
         <v>2126</v>
@@ -37622,7 +38198,7 @@
         <v>12</v>
       </c>
       <c r="C2125">
-        <v>5376.5</v>
+        <v>4567.4</v>
       </c>
       <c r="D2125" t="s">
         <v>2127</v>
@@ -37636,7 +38212,7 @@
         <v>13</v>
       </c>
       <c r="C2126">
-        <v>5233.5</v>
+        <v>4466.2</v>
       </c>
       <c r="D2126" t="s">
         <v>2128</v>
@@ -37650,7 +38226,7 @@
         <v>14</v>
       </c>
       <c r="C2127">
-        <v>5217.4</v>
+        <v>4323.9</v>
       </c>
       <c r="D2127" t="s">
         <v>2129</v>
@@ -37664,7 +38240,7 @@
         <v>15</v>
       </c>
       <c r="C2128">
-        <v>5216.4</v>
+        <v>4303.9</v>
       </c>
       <c r="D2128" t="s">
         <v>2130</v>
@@ -37678,7 +38254,7 @@
         <v>16</v>
       </c>
       <c r="C2129">
-        <v>5213.9</v>
+        <v>4263.9</v>
       </c>
       <c r="D2129" t="s">
         <v>2131</v>
@@ -37692,7 +38268,7 @@
         <v>17</v>
       </c>
       <c r="C2130">
-        <v>5220.5</v>
+        <v>4278.2</v>
       </c>
       <c r="D2130" t="s">
         <v>2132</v>
@@ -37706,7 +38282,7 @@
         <v>18</v>
       </c>
       <c r="C2131">
-        <v>5210</v>
+        <v>4269.3</v>
       </c>
       <c r="D2131" t="s">
         <v>2133</v>
@@ -37720,7 +38296,7 @@
         <v>19</v>
       </c>
       <c r="C2132">
-        <v>5183.5</v>
+        <v>4203.9</v>
       </c>
       <c r="D2132" t="s">
         <v>2134</v>
@@ -37734,7 +38310,7 @@
         <v>20</v>
       </c>
       <c r="C2133">
-        <v>5170.7</v>
+        <v>4153.8</v>
       </c>
       <c r="D2133" t="s">
         <v>2135</v>
@@ -37748,7 +38324,7 @@
         <v>21</v>
       </c>
       <c r="C2134">
-        <v>5184.2</v>
+        <v>4037.6</v>
       </c>
       <c r="D2134" t="s">
         <v>2136</v>
@@ -37762,7 +38338,7 @@
         <v>22</v>
       </c>
       <c r="C2135">
-        <v>5164.9</v>
+        <v>4036.1</v>
       </c>
       <c r="D2135" t="s">
         <v>2137</v>
@@ -37776,7 +38352,7 @@
         <v>23</v>
       </c>
       <c r="C2136">
-        <v>5156</v>
+        <v>4019.9</v>
       </c>
       <c r="D2136" t="s">
         <v>2138</v>
@@ -37790,7 +38366,7 @@
         <v>24</v>
       </c>
       <c r="C2137">
-        <v>5113.2</v>
+        <v>3954</v>
       </c>
       <c r="D2137" t="s">
         <v>2139</v>
@@ -37804,7 +38380,7 @@
         <v>25</v>
       </c>
       <c r="C2138">
-        <v>5004.8</v>
+        <v>3926</v>
       </c>
       <c r="D2138" t="s">
         <v>2140</v>
@@ -37818,7 +38394,7 @@
         <v>26</v>
       </c>
       <c r="C2139">
-        <v>4905.7</v>
+        <v>3856</v>
       </c>
       <c r="D2139" t="s">
         <v>2141</v>
@@ -37832,7 +38408,7 @@
         <v>27</v>
       </c>
       <c r="C2140">
-        <v>4841.8</v>
+        <v>3908.2</v>
       </c>
       <c r="D2140" t="s">
         <v>2142</v>
@@ -37846,7 +38422,7 @@
         <v>28</v>
       </c>
       <c r="C2141">
-        <v>4795.1</v>
+        <v>3843</v>
       </c>
       <c r="D2141" t="s">
         <v>2143</v>
@@ -37860,7 +38436,7 @@
         <v>29</v>
       </c>
       <c r="C2142">
-        <v>4946.9</v>
+        <v>3815.3</v>
       </c>
       <c r="D2142" t="s">
         <v>2144</v>
@@ -37874,7 +38450,7 @@
         <v>30</v>
       </c>
       <c r="C2143">
-        <v>4887.8</v>
+        <v>3745.2</v>
       </c>
       <c r="D2143" t="s">
         <v>2145</v>
@@ -37888,7 +38464,7 @@
         <v>31</v>
       </c>
       <c r="C2144">
-        <v>4832.2</v>
+        <v>3758.6</v>
       </c>
       <c r="D2144" t="s">
         <v>2146</v>
@@ -37902,7 +38478,7 @@
         <v>32</v>
       </c>
       <c r="C2145">
-        <v>4809</v>
+        <v>3780.7</v>
       </c>
       <c r="D2145" t="s">
         <v>2147</v>
@@ -37916,7 +38492,7 @@
         <v>33</v>
       </c>
       <c r="C2146">
-        <v>4745.9</v>
+        <v>4118.6</v>
       </c>
       <c r="D2146" t="s">
         <v>2148</v>
@@ -37930,7 +38506,7 @@
         <v>34</v>
       </c>
       <c r="C2147">
-        <v>4783.4</v>
+        <v>4179.2</v>
       </c>
       <c r="D2147" t="s">
         <v>2149</v>
@@ -37944,7 +38520,7 @@
         <v>35</v>
       </c>
       <c r="C2148">
-        <v>4845.8</v>
+        <v>4229.1</v>
       </c>
       <c r="D2148" t="s">
         <v>2150</v>
@@ -37958,7 +38534,7 @@
         <v>36</v>
       </c>
       <c r="C2149">
-        <v>4756.1</v>
+        <v>4281.7</v>
       </c>
       <c r="D2149" t="s">
         <v>2151</v>
@@ -37972,7 +38548,7 @@
         <v>37</v>
       </c>
       <c r="C2150">
-        <v>4483.5</v>
+        <v>4160.9</v>
       </c>
       <c r="D2150" t="s">
         <v>2152</v>
@@ -37986,7 +38562,7 @@
         <v>38</v>
       </c>
       <c r="C2151">
-        <v>4511.6</v>
+        <v>4243.1</v>
       </c>
       <c r="D2151" t="s">
         <v>2153</v>
@@ -38000,7 +38576,7 @@
         <v>39</v>
       </c>
       <c r="C2152">
-        <v>4593.8</v>
+        <v>4302.2</v>
       </c>
       <c r="D2152" t="s">
         <v>2154</v>
@@ -38014,7 +38590,7 @@
         <v>40</v>
       </c>
       <c r="C2153">
-        <v>4620.9</v>
+        <v>4388.6</v>
       </c>
       <c r="D2153" t="s">
         <v>2155</v>
@@ -38028,7 +38604,7 @@
         <v>41</v>
       </c>
       <c r="C2154">
-        <v>4563.4</v>
+        <v>4315.7</v>
       </c>
       <c r="D2154" t="s">
         <v>2156</v>
@@ -38042,7 +38618,7 @@
         <v>42</v>
       </c>
       <c r="C2155">
-        <v>4604.8</v>
+        <v>4428.6</v>
       </c>
       <c r="D2155" t="s">
         <v>2157</v>
@@ -38056,7 +38632,7 @@
         <v>43</v>
       </c>
       <c r="C2156">
-        <v>4682.9</v>
+        <v>4537.9</v>
       </c>
       <c r="D2156" t="s">
         <v>2158</v>
@@ -38070,7 +38646,7 @@
         <v>44</v>
       </c>
       <c r="C2157">
-        <v>4747.1</v>
+        <v>4668.8</v>
       </c>
       <c r="D2157" t="s">
         <v>2159</v>
@@ -38084,7 +38660,7 @@
         <v>45</v>
       </c>
       <c r="C2158">
-        <v>3962.5</v>
+        <v>4761.8</v>
       </c>
       <c r="D2158" t="s">
         <v>2160</v>
@@ -38098,7 +38674,7 @@
         <v>46</v>
       </c>
       <c r="C2159">
-        <v>4014.4</v>
+        <v>4868.2</v>
       </c>
       <c r="D2159" t="s">
         <v>2161</v>
@@ -38112,7 +38688,7 @@
         <v>47</v>
       </c>
       <c r="C2160">
-        <v>4035.1</v>
+        <v>4953.9</v>
       </c>
       <c r="D2160" t="s">
         <v>2162</v>
@@ -38126,7 +38702,7 @@
         <v>48</v>
       </c>
       <c r="C2161">
-        <v>4109.3</v>
+        <v>5007.3</v>
       </c>
       <c r="D2161" t="s">
         <v>2163</v>
@@ -38140,7 +38716,7 @@
         <v>49</v>
       </c>
       <c r="C2162">
-        <v>3962.3</v>
+        <v>5080.8</v>
       </c>
       <c r="D2162" t="s">
         <v>2164</v>
@@ -38154,7 +38730,7 @@
         <v>50</v>
       </c>
       <c r="C2163">
-        <v>3987.7</v>
+        <v>5123.7</v>
       </c>
       <c r="D2163" t="s">
         <v>2165</v>
@@ -38168,7 +38744,7 @@
         <v>51</v>
       </c>
       <c r="C2164">
-        <v>3878</v>
+        <v>5110.5</v>
       </c>
       <c r="D2164" t="s">
         <v>2166</v>
@@ -38182,7 +38758,7 @@
         <v>52</v>
       </c>
       <c r="C2165">
-        <v>3842.9</v>
+        <v>5245</v>
       </c>
       <c r="D2165" t="s">
         <v>2167</v>
@@ -38196,7 +38772,7 @@
         <v>53</v>
       </c>
       <c r="C2166">
-        <v>3915.8</v>
+        <v>5120</v>
       </c>
       <c r="D2166" t="s">
         <v>2168</v>
@@ -38210,7 +38786,7 @@
         <v>54</v>
       </c>
       <c r="C2167">
-        <v>3871.9</v>
+        <v>5142</v>
       </c>
       <c r="D2167" t="s">
         <v>2169</v>
@@ -38224,7 +38800,7 @@
         <v>55</v>
       </c>
       <c r="C2168">
-        <v>3877.6</v>
+        <v>5191.6</v>
       </c>
       <c r="D2168" t="s">
         <v>2170</v>
@@ -38238,7 +38814,7 @@
         <v>56</v>
       </c>
       <c r="C2169">
-        <v>3919.4</v>
+        <v>5181.1</v>
       </c>
       <c r="D2169" t="s">
         <v>2171</v>
@@ -38252,7 +38828,7 @@
         <v>57</v>
       </c>
       <c r="C2170">
-        <v>3943.4</v>
+        <v>5324.2</v>
       </c>
       <c r="D2170" t="s">
         <v>2172</v>
@@ -38266,7 +38842,7 @@
         <v>58</v>
       </c>
       <c r="C2171">
-        <v>3989.3</v>
+        <v>5379.4</v>
       </c>
       <c r="D2171" t="s">
         <v>2173</v>
@@ -38280,7 +38856,7 @@
         <v>59</v>
       </c>
       <c r="C2172">
-        <v>4022.4</v>
+        <v>5450.8</v>
       </c>
       <c r="D2172" t="s">
         <v>2174</v>
@@ -38294,7 +38870,7 @@
         <v>60</v>
       </c>
       <c r="C2173">
-        <v>4090.2</v>
+        <v>5520.5</v>
       </c>
       <c r="D2173" t="s">
         <v>2175</v>
@@ -38308,7 +38884,7 @@
         <v>61</v>
       </c>
       <c r="C2174">
-        <v>4290.9</v>
+        <v>5655.8</v>
       </c>
       <c r="D2174" t="s">
         <v>2176</v>
@@ -38322,7 +38898,7 @@
         <v>62</v>
       </c>
       <c r="C2175">
-        <v>4340.1</v>
+        <v>5687.5</v>
       </c>
       <c r="D2175" t="s">
         <v>2177</v>
@@ -38336,7 +38912,7 @@
         <v>63</v>
       </c>
       <c r="C2176">
-        <v>4385.6</v>
+        <v>5797.7</v>
       </c>
       <c r="D2176" t="s">
         <v>2178</v>
@@ -38350,7 +38926,7 @@
         <v>64</v>
       </c>
       <c r="C2177">
-        <v>4377.7</v>
+        <v>5870.6</v>
       </c>
       <c r="D2177" t="s">
         <v>2179</v>
@@ -38364,7 +38940,7 @@
         <v>65</v>
       </c>
       <c r="C2178">
-        <v>4243</v>
+        <v>5791.7</v>
       </c>
       <c r="D2178" t="s">
         <v>2180</v>
@@ -38378,7 +38954,7 @@
         <v>66</v>
       </c>
       <c r="C2179">
-        <v>4214.1</v>
+        <v>5737.8</v>
       </c>
       <c r="D2179" t="s">
         <v>2181</v>
@@ -38392,7 +38968,7 @@
         <v>67</v>
       </c>
       <c r="C2180">
-        <v>4191.6</v>
+        <v>5706.9</v>
       </c>
       <c r="D2180" t="s">
         <v>2182</v>
@@ -38406,7 +38982,7 @@
         <v>68</v>
       </c>
       <c r="C2181">
-        <v>4194.9</v>
+        <v>5667.9</v>
       </c>
       <c r="D2181" t="s">
         <v>2183</v>
@@ -38420,7 +38996,7 @@
         <v>69</v>
       </c>
       <c r="C2182">
-        <v>4626.3</v>
+        <v>5689.5</v>
       </c>
       <c r="D2182" t="s">
         <v>2184</v>
@@ -38434,7 +39010,7 @@
         <v>70</v>
       </c>
       <c r="C2183">
-        <v>4580</v>
+        <v>5594.8</v>
       </c>
       <c r="D2183" t="s">
         <v>2185</v>
@@ -38448,7 +39024,7 @@
         <v>71</v>
       </c>
       <c r="C2184">
-        <v>4508.5</v>
+        <v>5473.8</v>
       </c>
       <c r="D2184" t="s">
         <v>2186</v>
@@ -38462,7 +39038,7 @@
         <v>72</v>
       </c>
       <c r="C2185">
-        <v>4406.4</v>
+        <v>5396.1</v>
       </c>
       <c r="D2185" t="s">
         <v>2187</v>
@@ -38476,7 +39052,7 @@
         <v>73</v>
       </c>
       <c r="C2186">
-        <v>4429.2</v>
+        <v>5264.7</v>
       </c>
       <c r="D2186" t="s">
         <v>2188</v>
@@ -38490,7 +39066,7 @@
         <v>74</v>
       </c>
       <c r="C2187">
-        <v>4295.3</v>
+        <v>5135.4</v>
       </c>
       <c r="D2187" t="s">
         <v>2189</v>
@@ -38504,7 +39080,7 @@
         <v>75</v>
       </c>
       <c r="C2188">
-        <v>4116.7</v>
+        <v>5024.9</v>
       </c>
       <c r="D2188" t="s">
         <v>2190</v>
@@ -38518,7 +39094,7 @@
         <v>76</v>
       </c>
       <c r="C2189">
-        <v>4043.1</v>
+        <v>4957.7</v>
       </c>
       <c r="D2189" t="s">
         <v>2191</v>
@@ -38532,7 +39108,7 @@
         <v>77</v>
       </c>
       <c r="C2190">
-        <v>4020.3</v>
+        <v>4669.9</v>
       </c>
       <c r="D2190" t="s">
         <v>2192</v>
@@ -38546,7 +39122,7 @@
         <v>78</v>
       </c>
       <c r="C2191">
-        <v>3939.2</v>
+        <v>4638.7</v>
       </c>
       <c r="D2191" t="s">
         <v>2193</v>
@@ -38560,7 +39136,7 @@
         <v>79</v>
       </c>
       <c r="C2192">
-        <v>3866.6</v>
+        <v>4578.5</v>
       </c>
       <c r="D2192" t="s">
         <v>2194</v>
@@ -38574,7 +39150,7 @@
         <v>80</v>
       </c>
       <c r="C2193">
-        <v>3894.2</v>
+        <v>4516.1</v>
       </c>
       <c r="D2193" t="s">
         <v>2195</v>
@@ -38588,7 +39164,7 @@
         <v>81</v>
       </c>
       <c r="C2194">
-        <v>4303.7</v>
+        <v>4863.8</v>
       </c>
       <c r="D2194" t="s">
         <v>2196</v>
@@ -38602,7 +39178,7 @@
         <v>82</v>
       </c>
       <c r="C2195">
-        <v>4407.8</v>
+        <v>4891</v>
       </c>
       <c r="D2195" t="s">
         <v>2197</v>
@@ -38616,7 +39192,7 @@
         <v>83</v>
       </c>
       <c r="C2196">
-        <v>4446.2</v>
+        <v>4847.5</v>
       </c>
       <c r="D2196" t="s">
         <v>2198</v>
@@ -38630,7 +39206,7 @@
         <v>84</v>
       </c>
       <c r="C2197">
-        <v>4435.4</v>
+        <v>4802.4</v>
       </c>
       <c r="D2197" t="s">
         <v>2199</v>
@@ -38644,7 +39220,7 @@
         <v>85</v>
       </c>
       <c r="C2198">
-        <v>4388.2</v>
+        <v>4755.6</v>
       </c>
       <c r="D2198" t="s">
         <v>2200</v>
@@ -38658,7 +39234,7 @@
         <v>86</v>
       </c>
       <c r="C2199">
-        <v>4343.6</v>
+        <v>4743.1</v>
       </c>
       <c r="D2199" t="s">
         <v>2201</v>
@@ -38672,7 +39248,7 @@
         <v>87</v>
       </c>
       <c r="C2200">
-        <v>4367.7</v>
+        <v>4806.5</v>
       </c>
       <c r="D2200" t="s">
         <v>2202</v>
@@ -38686,7 +39262,7 @@
         <v>88</v>
       </c>
       <c r="C2201">
-        <v>4352.2</v>
+        <v>4812.9</v>
       </c>
       <c r="D2201" t="s">
         <v>2203</v>
@@ -38700,7 +39276,7 @@
         <v>89</v>
       </c>
       <c r="C2202">
-        <v>4064.4</v>
+        <v>4601</v>
       </c>
       <c r="D2202" t="s">
         <v>2204</v>
@@ -38714,7 +39290,7 @@
         <v>90</v>
       </c>
       <c r="C2203">
-        <v>4038.5</v>
+        <v>4586.5</v>
       </c>
       <c r="D2203" t="s">
         <v>2205</v>
@@ -38728,7 +39304,7 @@
         <v>91</v>
       </c>
       <c r="C2204">
-        <v>3972.5</v>
+        <v>4518.9</v>
       </c>
       <c r="D2204" t="s">
         <v>2206</v>
@@ -38742,7 +39318,7 @@
         <v>92</v>
       </c>
       <c r="C2205">
-        <v>3932.2</v>
+        <v>4518.2</v>
       </c>
       <c r="D2205" t="s">
         <v>2207</v>
@@ -38756,7 +39332,7 @@
         <v>93</v>
       </c>
       <c r="C2206">
-        <v>3711</v>
+        <v>4435.2</v>
       </c>
       <c r="D2206" t="s">
         <v>2208</v>
@@ -38770,7 +39346,7 @@
         <v>94</v>
       </c>
       <c r="C2207">
-        <v>3637.8</v>
+        <v>4412.4</v>
       </c>
       <c r="D2207" t="s">
         <v>2209</v>
@@ -38784,7 +39360,7 @@
         <v>95</v>
       </c>
       <c r="C2208">
-        <v>3654</v>
+        <v>4383.1</v>
       </c>
       <c r="D2208" t="s">
         <v>2210</v>
@@ -38798,7 +39374,7 @@
         <v>96</v>
       </c>
       <c r="C2209">
-        <v>3640.3</v>
+        <v>4402.2</v>
       </c>
       <c r="D2209" t="s">
         <v>2211</v>
@@ -38812,7 +39388,7 @@
         <v>1</v>
       </c>
       <c r="C2210">
-        <v>5121.1</v>
+        <v>4577.7</v>
       </c>
       <c r="D2210" t="s">
         <v>2212</v>
@@ -38826,7 +39402,7 @@
         <v>2</v>
       </c>
       <c r="C2211">
-        <v>5140.8</v>
+        <v>4614</v>
       </c>
       <c r="D2211" t="s">
         <v>2213</v>
@@ -38840,7 +39416,7 @@
         <v>3</v>
       </c>
       <c r="C2212">
-        <v>5160.1</v>
+        <v>4623.5</v>
       </c>
       <c r="D2212" t="s">
         <v>2214</v>
@@ -38854,7 +39430,7 @@
         <v>4</v>
       </c>
       <c r="C2213">
-        <v>5214.3</v>
+        <v>4581.2</v>
       </c>
       <c r="D2213" t="s">
         <v>2215</v>
@@ -38868,7 +39444,7 @@
         <v>5</v>
       </c>
       <c r="C2214">
-        <v>5235.1</v>
+        <v>4598.6</v>
       </c>
       <c r="D2214" t="s">
         <v>2216</v>
@@ -38882,7 +39458,7 @@
         <v>6</v>
       </c>
       <c r="C2215">
-        <v>5256.4</v>
+        <v>4599.4</v>
       </c>
       <c r="D2215" t="s">
         <v>2217</v>
@@ -38896,7 +39472,7 @@
         <v>7</v>
       </c>
       <c r="C2216">
-        <v>5269.5</v>
+        <v>4595.2</v>
       </c>
       <c r="D2216" t="s">
         <v>2218</v>
@@ -38910,7 +39486,7 @@
         <v>8</v>
       </c>
       <c r="C2217">
-        <v>5274.1</v>
+        <v>4561.8</v>
       </c>
       <c r="D2217" t="s">
         <v>2219</v>
@@ -38924,7 +39500,7 @@
         <v>9</v>
       </c>
       <c r="C2218">
-        <v>5289.1</v>
+        <v>4556.9</v>
       </c>
       <c r="D2218" t="s">
         <v>2220</v>
@@ -38938,7 +39514,7 @@
         <v>10</v>
       </c>
       <c r="C2219">
-        <v>5274.7</v>
+        <v>4529.8</v>
       </c>
       <c r="D2219" t="s">
         <v>2221</v>
@@ -38952,7 +39528,7 @@
         <v>11</v>
       </c>
       <c r="C2220">
-        <v>5268.5</v>
+        <v>4522.6</v>
       </c>
       <c r="D2220" t="s">
         <v>2222</v>
@@ -38966,7 +39542,7 @@
         <v>12</v>
       </c>
       <c r="C2221">
-        <v>5286.5</v>
+        <v>4417.4</v>
       </c>
       <c r="D2221" t="s">
         <v>2223</v>
@@ -38980,7 +39556,7 @@
         <v>13</v>
       </c>
       <c r="C2222">
-        <v>5163.5</v>
+        <v>4366.2</v>
       </c>
       <c r="D2222" t="s">
         <v>2224</v>
@@ -38994,7 +39570,7 @@
         <v>14</v>
       </c>
       <c r="C2223">
-        <v>5167.4</v>
+        <v>4263.9</v>
       </c>
       <c r="D2223" t="s">
         <v>2225</v>
@@ -39008,7 +39584,7 @@
         <v>15</v>
       </c>
       <c r="C2224">
-        <v>5186.4</v>
+        <v>4263.9</v>
       </c>
       <c r="D2224" t="s">
         <v>2226</v>
@@ -39022,7 +39598,7 @@
         <v>16</v>
       </c>
       <c r="C2225">
-        <v>5203.9</v>
+        <v>4233.9</v>
       </c>
       <c r="D2225" t="s">
         <v>2227</v>
@@ -39036,7 +39612,7 @@
         <v>17</v>
       </c>
       <c r="C2226">
-        <v>5230.5</v>
+        <v>4258.2</v>
       </c>
       <c r="D2226" t="s">
         <v>2228</v>
@@ -39050,7 +39626,7 @@
         <v>18</v>
       </c>
       <c r="C2227">
-        <v>5240</v>
+        <v>4259.3</v>
       </c>
       <c r="D2227" t="s">
         <v>2229</v>
@@ -39064,7 +39640,7 @@
         <v>19</v>
       </c>
       <c r="C2228">
-        <v>5233.5</v>
+        <v>4263.9</v>
       </c>
       <c r="D2228" t="s">
         <v>2230</v>
@@ -39078,7 +39654,7 @@
         <v>20</v>
       </c>
       <c r="C2229">
-        <v>5260.7</v>
+        <v>4283.8</v>
       </c>
       <c r="D2229" t="s">
         <v>2231</v>
@@ -39092,7 +39668,7 @@
         <v>21</v>
       </c>
       <c r="C2230">
-        <v>5304.2</v>
+        <v>4247.6</v>
       </c>
       <c r="D2230" t="s">
         <v>2232</v>
@@ -39106,7 +39682,7 @@
         <v>22</v>
       </c>
       <c r="C2231">
-        <v>5334.9</v>
+        <v>4346.1</v>
       </c>
       <c r="D2231" t="s">
         <v>2233</v>
@@ -39120,7 +39696,7 @@
         <v>23</v>
       </c>
       <c r="C2232">
-        <v>5396</v>
+        <v>4439.9</v>
       </c>
       <c r="D2232" t="s">
         <v>2234</v>
@@ -39134,7 +39710,7 @@
         <v>24</v>
       </c>
       <c r="C2233">
-        <v>5423.2</v>
+        <v>4484</v>
       </c>
       <c r="D2233" t="s">
         <v>2235</v>
@@ -39148,7 +39724,7 @@
         <v>25</v>
       </c>
       <c r="C2234">
-        <v>5404.8</v>
+        <v>4636</v>
       </c>
       <c r="D2234" t="s">
         <v>2236</v>
@@ -39162,7 +39738,7 @@
         <v>26</v>
       </c>
       <c r="C2235">
-        <v>5415.7</v>
+        <v>4746</v>
       </c>
       <c r="D2235" t="s">
         <v>2237</v>
@@ -39176,7 +39752,7 @@
         <v>27</v>
       </c>
       <c r="C2236">
-        <v>5491.8</v>
+        <v>4928.2</v>
       </c>
       <c r="D2236" t="s">
         <v>2238</v>
@@ -39190,7 +39766,7 @@
         <v>28</v>
       </c>
       <c r="C2237">
-        <v>5615.1</v>
+        <v>5013</v>
       </c>
       <c r="D2237" t="s">
         <v>2239</v>
@@ -39204,7 +39780,7 @@
         <v>29</v>
       </c>
       <c r="C2238">
-        <v>5956.9</v>
+        <v>5125.3</v>
       </c>
       <c r="D2238" t="s">
         <v>2240</v>
@@ -39218,7 +39794,7 @@
         <v>30</v>
       </c>
       <c r="C2239">
-        <v>6057.8</v>
+        <v>5195.2</v>
       </c>
       <c r="D2239" t="s">
         <v>2241</v>
@@ -39232,7 +39808,7 @@
         <v>31</v>
       </c>
       <c r="C2240">
-        <v>6152.2</v>
+        <v>5288.6</v>
       </c>
       <c r="D2240" t="s">
         <v>2242</v>
@@ -39246,7 +39822,7 @@
         <v>32</v>
       </c>
       <c r="C2241">
-        <v>6239</v>
+        <v>5320.7</v>
       </c>
       <c r="D2241" t="s">
         <v>2243</v>
@@ -39260,7 +39836,7 @@
         <v>33</v>
       </c>
       <c r="C2242">
-        <v>6245.9</v>
+        <v>5678.6</v>
       </c>
       <c r="D2242" t="s">
         <v>2244</v>
@@ -39274,7 +39850,7 @@
         <v>34</v>
       </c>
       <c r="C2243">
-        <v>6343.4</v>
+        <v>5779.2</v>
       </c>
       <c r="D2243" t="s">
         <v>2245</v>
@@ -39288,7 +39864,7 @@
         <v>35</v>
       </c>
       <c r="C2244">
-        <v>6435.8</v>
+        <v>5829.1</v>
       </c>
       <c r="D2244" t="s">
         <v>2246</v>
@@ -39302,7 +39878,7 @@
         <v>36</v>
       </c>
       <c r="C2245">
-        <v>6336.1</v>
+        <v>5871.7</v>
       </c>
       <c r="D2245" t="s">
         <v>2247</v>
@@ -39316,7 +39892,7 @@
         <v>37</v>
       </c>
       <c r="C2246">
-        <v>6033.5</v>
+        <v>5720.9</v>
       </c>
       <c r="D2246" t="s">
         <v>2248</v>
@@ -39330,7 +39906,7 @@
         <v>38</v>
       </c>
       <c r="C2247">
-        <v>6051.6</v>
+        <v>5773.1</v>
       </c>
       <c r="D2247" t="s">
         <v>2249</v>
@@ -39344,7 +39920,7 @@
         <v>39</v>
       </c>
       <c r="C2248">
-        <v>6113.8</v>
+        <v>5792.2</v>
       </c>
       <c r="D2248" t="s">
         <v>2250</v>
@@ -39358,7 +39934,7 @@
         <v>40</v>
       </c>
       <c r="C2249">
-        <v>6140.9</v>
+        <v>5858.6</v>
       </c>
       <c r="D2249" t="s">
         <v>2251</v>
@@ -39372,7 +39948,7 @@
         <v>41</v>
       </c>
       <c r="C2250">
-        <v>6083.4</v>
+        <v>5755.7</v>
       </c>
       <c r="D2250" t="s">
         <v>2252</v>
@@ -39386,7 +39962,7 @@
         <v>42</v>
       </c>
       <c r="C2251">
-        <v>6114.8</v>
+        <v>5848.6</v>
       </c>
       <c r="D2251" t="s">
         <v>2253</v>
@@ -39400,7 +39976,7 @@
         <v>43</v>
       </c>
       <c r="C2252">
-        <v>6182.9</v>
+        <v>5937.9</v>
       </c>
       <c r="D2252" t="s">
         <v>2254</v>
@@ -39414,7 +39990,7 @@
         <v>44</v>
       </c>
       <c r="C2253">
-        <v>6217.1</v>
+        <v>6048.8</v>
       </c>
       <c r="D2253" t="s">
         <v>2255</v>
@@ -39428,7 +40004,7 @@
         <v>45</v>
       </c>
       <c r="C2254">
-        <v>5402.5</v>
+        <v>6121.8</v>
       </c>
       <c r="D2254" t="s">
         <v>2256</v>
@@ -39442,7 +40018,7 @@
         <v>46</v>
       </c>
       <c r="C2255">
-        <v>5414.4</v>
+        <v>6218.2</v>
       </c>
       <c r="D2255" t="s">
         <v>2257</v>
@@ -39456,7 +40032,7 @@
         <v>47</v>
       </c>
       <c r="C2256">
-        <v>5405.1</v>
+        <v>6283.9</v>
       </c>
       <c r="D2256" t="s">
         <v>2258</v>
@@ -39470,7 +40046,7 @@
         <v>48</v>
       </c>
       <c r="C2257">
-        <v>5469.3</v>
+        <v>6327.3</v>
       </c>
       <c r="D2257" t="s">
         <v>2259</v>
@@ -39484,7 +40060,7 @@
         <v>49</v>
       </c>
       <c r="C2258">
-        <v>5302.3</v>
+        <v>6400.8</v>
       </c>
       <c r="D2258" t="s">
         <v>2260</v>
@@ -39498,7 +40074,7 @@
         <v>50</v>
       </c>
       <c r="C2259">
-        <v>5347.7</v>
+        <v>6443.7</v>
       </c>
       <c r="D2259" t="s">
         <v>2261</v>
@@ -39512,7 +40088,7 @@
         <v>51</v>
       </c>
       <c r="C2260">
-        <v>5258</v>
+        <v>6440.5</v>
       </c>
       <c r="D2260" t="s">
         <v>2262</v>
@@ -39526,7 +40102,7 @@
         <v>52</v>
       </c>
       <c r="C2261">
-        <v>5272.9</v>
+        <v>6585</v>
       </c>
       <c r="D2261" t="s">
         <v>2263</v>
@@ -39540,7 +40116,7 @@
         <v>53</v>
       </c>
       <c r="C2262">
-        <v>5385.8</v>
+        <v>6470</v>
       </c>
       <c r="D2262" t="s">
         <v>2264</v>
@@ -39554,7 +40130,7 @@
         <v>54</v>
       </c>
       <c r="C2263">
-        <v>5381.9</v>
+        <v>6492</v>
       </c>
       <c r="D2263" t="s">
         <v>2265</v>
@@ -39568,7 +40144,7 @@
         <v>55</v>
       </c>
       <c r="C2264">
-        <v>5397.6</v>
+        <v>6531.6</v>
       </c>
       <c r="D2264" t="s">
         <v>2266</v>
@@ -39582,7 +40158,7 @@
         <v>56</v>
       </c>
       <c r="C2265">
-        <v>5409.4</v>
+        <v>6511.1</v>
       </c>
       <c r="D2265" t="s">
         <v>2267</v>
@@ -39596,7 +40172,7 @@
         <v>57</v>
       </c>
       <c r="C2266">
-        <v>5393.4</v>
+        <v>6624.2</v>
       </c>
       <c r="D2266" t="s">
         <v>2268</v>
@@ -39610,7 +40186,7 @@
         <v>58</v>
       </c>
       <c r="C2267">
-        <v>5389.3</v>
+        <v>6639.4</v>
       </c>
       <c r="D2267" t="s">
         <v>2269</v>
@@ -39624,7 +40200,7 @@
         <v>59</v>
       </c>
       <c r="C2268">
-        <v>5402.4</v>
+        <v>6660.8</v>
       </c>
       <c r="D2268" t="s">
         <v>2270</v>
@@ -39638,7 +40214,7 @@
         <v>60</v>
       </c>
       <c r="C2269">
-        <v>5460.2</v>
+        <v>6690.5</v>
       </c>
       <c r="D2269" t="s">
         <v>2271</v>
@@ -39652,7 +40228,7 @@
         <v>61</v>
       </c>
       <c r="C2270">
-        <v>5680.9</v>
+        <v>6775.8</v>
       </c>
       <c r="D2270" t="s">
         <v>2272</v>
@@ -39666,7 +40242,7 @@
         <v>62</v>
       </c>
       <c r="C2271">
-        <v>5740.1</v>
+        <v>6767.5</v>
       </c>
       <c r="D2271" t="s">
         <v>2273</v>
@@ -39680,7 +40256,7 @@
         <v>63</v>
       </c>
       <c r="C2272">
-        <v>5785.6</v>
+        <v>6857.7</v>
       </c>
       <c r="D2272" t="s">
         <v>2274</v>
@@ -39694,7 +40270,7 @@
         <v>64</v>
       </c>
       <c r="C2273">
-        <v>5777.7</v>
+        <v>6920.6</v>
       </c>
       <c r="D2273" t="s">
         <v>2275</v>
@@ -39708,7 +40284,7 @@
         <v>65</v>
       </c>
       <c r="C2274">
-        <v>5613</v>
+        <v>6841.7</v>
       </c>
       <c r="D2274" t="s">
         <v>2276</v>
@@ -39722,7 +40298,7 @@
         <v>66</v>
       </c>
       <c r="C2275">
-        <v>5564.1</v>
+        <v>6787.8</v>
       </c>
       <c r="D2275" t="s">
         <v>2277</v>
@@ -39736,7 +40312,7 @@
         <v>67</v>
       </c>
       <c r="C2276">
-        <v>5511.6</v>
+        <v>6756.9</v>
       </c>
       <c r="D2276" t="s">
         <v>2278</v>
@@ -39750,7 +40326,7 @@
         <v>68</v>
       </c>
       <c r="C2277">
-        <v>5484.9</v>
+        <v>6717.9</v>
       </c>
       <c r="D2277" t="s">
         <v>2279</v>
@@ -39764,7 +40340,7 @@
         <v>69</v>
       </c>
       <c r="C2278">
-        <v>5876.3</v>
+        <v>6749.5</v>
       </c>
       <c r="D2278" t="s">
         <v>2280</v>
@@ -39778,7 +40354,7 @@
         <v>70</v>
       </c>
       <c r="C2279">
-        <v>5810</v>
+        <v>6644.8</v>
       </c>
       <c r="D2279" t="s">
         <v>2281</v>
@@ -39792,7 +40368,7 @@
         <v>71</v>
       </c>
       <c r="C2280">
-        <v>5708.5</v>
+        <v>6543.8</v>
       </c>
       <c r="D2280" t="s">
         <v>2282</v>
@@ -39806,7 +40382,7 @@
         <v>72</v>
       </c>
       <c r="C2281">
-        <v>5596.4</v>
+        <v>6466.1</v>
       </c>
       <c r="D2281" t="s">
         <v>2283</v>
@@ -39820,7 +40396,7 @@
         <v>73</v>
       </c>
       <c r="C2282">
-        <v>5629.2</v>
+        <v>6344.7</v>
       </c>
       <c r="D2282" t="s">
         <v>2284</v>
@@ -39834,7 +40410,7 @@
         <v>74</v>
       </c>
       <c r="C2283">
-        <v>5485.3</v>
+        <v>6225.4</v>
       </c>
       <c r="D2283" t="s">
         <v>2285</v>
@@ -39848,7 +40424,7 @@
         <v>75</v>
       </c>
       <c r="C2284">
-        <v>5296.7</v>
+        <v>6104.9</v>
       </c>
       <c r="D2284" t="s">
         <v>2286</v>
@@ -39862,7 +40438,7 @@
         <v>76</v>
       </c>
       <c r="C2285">
-        <v>5173.1</v>
+        <v>5977.7</v>
       </c>
       <c r="D2285" t="s">
         <v>2287</v>
@@ -39876,7 +40452,7 @@
         <v>77</v>
       </c>
       <c r="C2286">
-        <v>5100.3</v>
+        <v>5649.9</v>
       </c>
       <c r="D2286" t="s">
         <v>2288</v>
@@ -39890,7 +40466,7 @@
         <v>78</v>
       </c>
       <c r="C2287">
-        <v>4969.2</v>
+        <v>5568.7</v>
       </c>
       <c r="D2287" t="s">
         <v>2289</v>
@@ -39904,7 +40480,7 @@
         <v>79</v>
       </c>
       <c r="C2288">
-        <v>4856.6</v>
+        <v>5468.5</v>
       </c>
       <c r="D2288" t="s">
         <v>2290</v>
@@ -39918,7 +40494,7 @@
         <v>80</v>
       </c>
       <c r="C2289">
-        <v>4864.2</v>
+        <v>5396.1</v>
       </c>
       <c r="D2289" t="s">
         <v>2291</v>
@@ -39932,7 +40508,7 @@
         <v>81</v>
       </c>
       <c r="C2290">
-        <v>5263.7</v>
+        <v>5743.8</v>
       </c>
       <c r="D2290" t="s">
         <v>2292</v>
@@ -39946,7 +40522,7 @@
         <v>82</v>
       </c>
       <c r="C2291">
-        <v>5327.8</v>
+        <v>5791</v>
       </c>
       <c r="D2291" t="s">
         <v>2293</v>
@@ -39960,7 +40536,7 @@
         <v>83</v>
       </c>
       <c r="C2292">
-        <v>5346.2</v>
+        <v>5747.5</v>
       </c>
       <c r="D2292" t="s">
         <v>2294</v>
@@ -39974,7 +40550,7 @@
         <v>84</v>
       </c>
       <c r="C2293">
-        <v>5335.4</v>
+        <v>5702.4</v>
       </c>
       <c r="D2293" t="s">
         <v>2295</v>
@@ -39988,7 +40564,7 @@
         <v>85</v>
       </c>
       <c r="C2294">
-        <v>5278.2</v>
+        <v>5625.6</v>
       </c>
       <c r="D2294" t="s">
         <v>2296</v>
@@ -40002,7 +40578,7 @@
         <v>86</v>
       </c>
       <c r="C2295">
-        <v>5213.6</v>
+        <v>5593.1</v>
       </c>
       <c r="D2295" t="s">
         <v>2297</v>
@@ -40016,7 +40592,7 @@
         <v>87</v>
       </c>
       <c r="C2296">
-        <v>5187.7</v>
+        <v>5526.5</v>
       </c>
       <c r="D2296" t="s">
         <v>2298</v>
@@ -40030,7 +40606,7 @@
         <v>88</v>
       </c>
       <c r="C2297">
-        <v>5122.2</v>
+        <v>5502.9</v>
       </c>
       <c r="D2297" t="s">
         <v>2299</v>
@@ -40044,7 +40620,7 @@
         <v>89</v>
       </c>
       <c r="C2298">
-        <v>4784.4</v>
+        <v>5321</v>
       </c>
       <c r="D2298" t="s">
         <v>2300</v>
@@ -40058,7 +40634,7 @@
         <v>90</v>
       </c>
       <c r="C2299">
-        <v>4688.5</v>
+        <v>5286.5</v>
       </c>
       <c r="D2299" t="s">
         <v>2301</v>
@@ -40072,7 +40648,7 @@
         <v>91</v>
       </c>
       <c r="C2300">
-        <v>4602.5</v>
+        <v>5178.9</v>
       </c>
       <c r="D2300" t="s">
         <v>2302</v>
@@ -40086,7 +40662,7 @@
         <v>92</v>
       </c>
       <c r="C2301">
-        <v>4522.2</v>
+        <v>5168.2</v>
       </c>
       <c r="D2301" t="s">
         <v>2303</v>
@@ -40100,7 +40676,7 @@
         <v>93</v>
       </c>
       <c r="C2302">
-        <v>4281</v>
+        <v>5125.2</v>
       </c>
       <c r="D2302" t="s">
         <v>2304</v>
@@ -40114,7 +40690,7 @@
         <v>94</v>
       </c>
       <c r="C2303">
-        <v>4207.8</v>
+        <v>5042.4</v>
       </c>
       <c r="D2303" t="s">
         <v>2305</v>
@@ -40128,7 +40704,7 @@
         <v>95</v>
       </c>
       <c r="C2304">
-        <v>4184</v>
+        <v>5043.1</v>
       </c>
       <c r="D2304" t="s">
         <v>2306</v>
@@ -40142,7 +40718,7 @@
         <v>96</v>
       </c>
       <c r="C2305">
-        <v>4150.3</v>
+        <v>5052.2</v>
       </c>
       <c r="D2305" t="s">
         <v>2307</v>
@@ -40156,7 +40732,7 @@
         <v>1</v>
       </c>
       <c r="C2306">
-        <v>5621.1</v>
+        <v>5037.7</v>
       </c>
       <c r="D2306" t="s">
         <v>2308</v>
@@ -40170,7 +40746,7 @@
         <v>2</v>
       </c>
       <c r="C2307">
-        <v>5640.8</v>
+        <v>5064</v>
       </c>
       <c r="D2307" t="s">
         <v>2309</v>
@@ -40184,7 +40760,7 @@
         <v>3</v>
       </c>
       <c r="C2308">
-        <v>5650.1</v>
+        <v>5073.5</v>
       </c>
       <c r="D2308" t="s">
         <v>2310</v>
@@ -40198,7 +40774,7 @@
         <v>4</v>
       </c>
       <c r="C2309">
-        <v>5704.3</v>
+        <v>5011.2</v>
       </c>
       <c r="D2309" t="s">
         <v>2311</v>
@@ -40212,7 +40788,7 @@
         <v>5</v>
       </c>
       <c r="C2310">
-        <v>5725.1</v>
+        <v>5018.6</v>
       </c>
       <c r="D2310" t="s">
         <v>2312</v>
@@ -40226,7 +40802,7 @@
         <v>6</v>
       </c>
       <c r="C2311">
-        <v>5746.4</v>
+        <v>4999.4</v>
       </c>
       <c r="D2311" t="s">
         <v>2313</v>
@@ -40240,7 +40816,7 @@
         <v>7</v>
       </c>
       <c r="C2312">
-        <v>5759.5</v>
+        <v>4995.2</v>
       </c>
       <c r="D2312" t="s">
         <v>2314</v>
@@ -40254,7 +40830,7 @@
         <v>8</v>
       </c>
       <c r="C2313">
-        <v>5764.1</v>
+        <v>4971.8</v>
       </c>
       <c r="D2313" t="s">
         <v>2315</v>
@@ -40268,7 +40844,7 @@
         <v>9</v>
       </c>
       <c r="C2314">
-        <v>5779.1</v>
+        <v>4966.9</v>
       </c>
       <c r="D2314" t="s">
         <v>2316</v>
@@ -40282,7 +40858,7 @@
         <v>10</v>
       </c>
       <c r="C2315">
-        <v>5764.7</v>
+        <v>4969.8</v>
       </c>
       <c r="D2315" t="s">
         <v>2317</v>
@@ -40296,7 +40872,7 @@
         <v>11</v>
       </c>
       <c r="C2316">
-        <v>5748.5</v>
+        <v>4972.6</v>
       </c>
       <c r="D2316" t="s">
         <v>2318</v>
@@ -40310,7 +40886,7 @@
         <v>12</v>
       </c>
       <c r="C2317">
-        <v>5766.5</v>
+        <v>4907.4</v>
       </c>
       <c r="D2317" t="s">
         <v>2319</v>
@@ -40324,7 +40900,7 @@
         <v>13</v>
       </c>
       <c r="C2318">
-        <v>5643.5</v>
+        <v>4836.2</v>
       </c>
       <c r="D2318" t="s">
         <v>2320</v>
@@ -40338,7 +40914,7 @@
         <v>14</v>
       </c>
       <c r="C2319">
-        <v>5637.4</v>
+        <v>4713.9</v>
       </c>
       <c r="D2319" t="s">
         <v>2321</v>
@@ -40352,7 +40928,7 @@
         <v>15</v>
       </c>
       <c r="C2320">
-        <v>5656.4</v>
+        <v>4713.9</v>
       </c>
       <c r="D2320" t="s">
         <v>2322</v>
@@ -40366,7 +40942,7 @@
         <v>16</v>
       </c>
       <c r="C2321">
-        <v>5673.9</v>
+        <v>4663.9</v>
       </c>
       <c r="D2321" t="s">
         <v>2323</v>
@@ -40380,7 +40956,7 @@
         <v>17</v>
       </c>
       <c r="C2322">
-        <v>5690.5</v>
+        <v>4698.2</v>
       </c>
       <c r="D2322" t="s">
         <v>2324</v>
@@ -40394,7 +40970,7 @@
         <v>18</v>
       </c>
       <c r="C2323">
-        <v>5700</v>
+        <v>4689.3</v>
       </c>
       <c r="D2323" t="s">
         <v>2325</v>
@@ -40408,7 +40984,7 @@
         <v>19</v>
       </c>
       <c r="C2324">
-        <v>5683.5</v>
+        <v>4693.9</v>
       </c>
       <c r="D2324" t="s">
         <v>2326</v>
@@ -40422,7 +40998,7 @@
         <v>20</v>
       </c>
       <c r="C2325">
-        <v>5700.7</v>
+        <v>4693.8</v>
       </c>
       <c r="D2325" t="s">
         <v>2327</v>
@@ -40436,7 +41012,7 @@
         <v>21</v>
       </c>
       <c r="C2326">
-        <v>5734.2</v>
+        <v>4637.6</v>
       </c>
       <c r="D2326" t="s">
         <v>2328</v>
@@ -40450,7 +41026,7 @@
         <v>22</v>
       </c>
       <c r="C2327">
-        <v>5744.9</v>
+        <v>4696.1</v>
       </c>
       <c r="D2327" t="s">
         <v>2329</v>
@@ -40464,7 +41040,7 @@
         <v>23</v>
       </c>
       <c r="C2328">
-        <v>5796</v>
+        <v>4749.9</v>
       </c>
       <c r="D2328" t="s">
         <v>2330</v>
@@ -40478,7 +41054,7 @@
         <v>24</v>
       </c>
       <c r="C2329">
-        <v>5823.2</v>
+        <v>4734</v>
       </c>
       <c r="D2329" t="s">
         <v>2331</v>
@@ -40492,7 +41068,7 @@
         <v>25</v>
       </c>
       <c r="C2330">
-        <v>5794.8</v>
+        <v>4806</v>
       </c>
       <c r="D2330" t="s">
         <v>2332</v>
@@ -40506,7 +41082,7 @@
         <v>26</v>
       </c>
       <c r="C2331">
-        <v>5785.7</v>
+        <v>4856</v>
       </c>
       <c r="D2331" t="s">
         <v>2333</v>
@@ -40520,7 +41096,7 @@
         <v>27</v>
       </c>
       <c r="C2332">
-        <v>5851.8</v>
+        <v>4968.2</v>
       </c>
       <c r="D2332" t="s">
         <v>2334</v>
@@ -40534,7 +41110,7 @@
         <v>28</v>
       </c>
       <c r="C2333">
-        <v>5935.1</v>
+        <v>5003</v>
       </c>
       <c r="D2333" t="s">
         <v>2335</v>
@@ -40548,7 +41124,7 @@
         <v>29</v>
       </c>
       <c r="C2334">
-        <v>6226.9</v>
+        <v>5075.3</v>
       </c>
       <c r="D2334" t="s">
         <v>2336</v>
@@ -40562,7 +41138,7 @@
         <v>30</v>
       </c>
       <c r="C2335">
-        <v>6297.8</v>
+        <v>5135.2</v>
       </c>
       <c r="D2335" t="s">
         <v>2337</v>
@@ -40576,7 +41152,7 @@
         <v>31</v>
       </c>
       <c r="C2336">
-        <v>6362.2</v>
+        <v>5248.6</v>
       </c>
       <c r="D2336" t="s">
         <v>2338</v>
@@ -40590,7 +41166,7 @@
         <v>32</v>
       </c>
       <c r="C2337">
-        <v>6429</v>
+        <v>5340.7</v>
       </c>
       <c r="D2337" t="s">
         <v>2339</v>
@@ -40604,7 +41180,7 @@
         <v>33</v>
       </c>
       <c r="C2338">
-        <v>6425.9</v>
+        <v>5748.6</v>
       </c>
       <c r="D2338" t="s">
         <v>2340</v>
@@ -40618,7 +41194,7 @@
         <v>34</v>
       </c>
       <c r="C2339">
-        <v>6513.4</v>
+        <v>5879.2</v>
       </c>
       <c r="D2339" t="s">
         <v>2341</v>
@@ -40632,7 +41208,7 @@
         <v>35</v>
       </c>
       <c r="C2340">
-        <v>6605.8</v>
+        <v>5979.1</v>
       </c>
       <c r="D2340" t="s">
         <v>2342</v>
@@ -40646,7 +41222,7 @@
         <v>36</v>
       </c>
       <c r="C2341">
-        <v>6506.1</v>
+        <v>6081.7</v>
       </c>
       <c r="D2341" t="s">
         <v>2343</v>
@@ -40660,7 +41236,7 @@
         <v>37</v>
       </c>
       <c r="C2342">
-        <v>6203.5</v>
+        <v>5980.9</v>
       </c>
       <c r="D2342" t="s">
         <v>2344</v>
@@ -40674,7 +41250,7 @@
         <v>38</v>
       </c>
       <c r="C2343">
-        <v>6221.6</v>
+        <v>6063.1</v>
       </c>
       <c r="D2343" t="s">
         <v>2345</v>
@@ -40688,7 +41264,7 @@
         <v>39</v>
       </c>
       <c r="C2344">
-        <v>6283.8</v>
+        <v>6102.2</v>
       </c>
       <c r="D2344" t="s">
         <v>2346</v>
@@ -40702,7 +41278,7 @@
         <v>40</v>
       </c>
       <c r="C2345">
-        <v>6310.9</v>
+        <v>6168.6</v>
       </c>
       <c r="D2345" t="s">
         <v>2347</v>
@@ -40716,7 +41292,7 @@
         <v>41</v>
       </c>
       <c r="C2346">
-        <v>6243.4</v>
+        <v>6065.7</v>
       </c>
       <c r="D2346" t="s">
         <v>2348</v>
@@ -40730,7 +41306,7 @@
         <v>42</v>
       </c>
       <c r="C2347">
-        <v>6264.8</v>
+        <v>6148.6</v>
       </c>
       <c r="D2347" t="s">
         <v>2349</v>
@@ -40744,7 +41320,7 @@
         <v>43</v>
       </c>
       <c r="C2348">
-        <v>6332.9</v>
+        <v>6227.9</v>
       </c>
       <c r="D2348" t="s">
         <v>2350</v>
@@ -40758,7 +41334,7 @@
         <v>44</v>
       </c>
       <c r="C2349">
-        <v>6357.1</v>
+        <v>6328.8</v>
       </c>
       <c r="D2349" t="s">
         <v>2351</v>
@@ -40772,7 +41348,7 @@
         <v>45</v>
       </c>
       <c r="C2350">
-        <v>5542.5</v>
+        <v>6401.8</v>
       </c>
       <c r="D2350" t="s">
         <v>2352</v>
@@ -40786,7 +41362,7 @@
         <v>46</v>
       </c>
       <c r="C2351">
-        <v>5554.4</v>
+        <v>6498.2</v>
       </c>
       <c r="D2351" t="s">
         <v>2353</v>
@@ -40800,7 +41376,7 @@
         <v>47</v>
       </c>
       <c r="C2352">
-        <v>5545.1</v>
+        <v>6573.9</v>
       </c>
       <c r="D2352" t="s">
         <v>2354</v>
@@ -40814,7 +41390,7 @@
         <v>48</v>
       </c>
       <c r="C2353">
-        <v>5599.3</v>
+        <v>6627.3</v>
       </c>
       <c r="D2353" t="s">
         <v>2355</v>
@@ -40828,7 +41404,7 @@
         <v>49</v>
       </c>
       <c r="C2354">
-        <v>5442.3</v>
+        <v>6710.8</v>
       </c>
       <c r="D2354" t="s">
         <v>2356</v>
@@ -40842,7 +41418,7 @@
         <v>50</v>
       </c>
       <c r="C2355">
-        <v>5477.7</v>
+        <v>6743.7</v>
       </c>
       <c r="D2355" t="s">
         <v>2357</v>
@@ -40856,7 +41432,7 @@
         <v>51</v>
       </c>
       <c r="C2356">
-        <v>5388</v>
+        <v>6730.5</v>
       </c>
       <c r="D2356" t="s">
         <v>2358</v>
@@ -40870,7 +41446,7 @@
         <v>52</v>
       </c>
       <c r="C2357">
-        <v>5392.9</v>
+        <v>6855</v>
       </c>
       <c r="D2357" t="s">
         <v>2359</v>
@@ -40884,7 +41460,7 @@
         <v>53</v>
       </c>
       <c r="C2358">
-        <v>5515.8</v>
+        <v>6720</v>
       </c>
       <c r="D2358" t="s">
         <v>2360</v>
@@ -40898,7 +41474,7 @@
         <v>54</v>
       </c>
       <c r="C2359">
-        <v>5501.9</v>
+        <v>6722</v>
       </c>
       <c r="D2359" t="s">
         <v>2361</v>
@@ -40912,7 +41488,7 @@
         <v>55</v>
       </c>
       <c r="C2360">
-        <v>5517.6</v>
+        <v>6751.6</v>
       </c>
       <c r="D2360" t="s">
         <v>2362</v>
@@ -40926,7 +41502,7 @@
         <v>56</v>
       </c>
       <c r="C2361">
-        <v>5529.4</v>
+        <v>6721.1</v>
       </c>
       <c r="D2361" t="s">
         <v>2363</v>
@@ -40940,7 +41516,7 @@
         <v>57</v>
       </c>
       <c r="C2362">
-        <v>5513.4</v>
+        <v>6844.2</v>
       </c>
       <c r="D2362" t="s">
         <v>2364</v>
@@ -40954,7 +41530,7 @@
         <v>58</v>
       </c>
       <c r="C2363">
-        <v>5519.3</v>
+        <v>6869.4</v>
       </c>
       <c r="D2363" t="s">
         <v>2365</v>
@@ -40968,7 +41544,7 @@
         <v>59</v>
       </c>
       <c r="C2364">
-        <v>5532.4</v>
+        <v>6920.8</v>
       </c>
       <c r="D2364" t="s">
         <v>2366</v>
@@ -40982,7 +41558,7 @@
         <v>60</v>
       </c>
       <c r="C2365">
-        <v>5600.2</v>
+        <v>6970.5</v>
       </c>
       <c r="D2365" t="s">
         <v>2367</v>
@@ -40996,7 +41572,7 @@
         <v>61</v>
       </c>
       <c r="C2366">
-        <v>5820.9</v>
+        <v>7085.8</v>
       </c>
       <c r="D2366" t="s">
         <v>2368</v>
@@ -41010,7 +41586,7 @@
         <v>62</v>
       </c>
       <c r="C2367">
-        <v>5880.1</v>
+        <v>7077.5</v>
       </c>
       <c r="D2367" t="s">
         <v>2369</v>
@@ -41024,7 +41600,7 @@
         <v>63</v>
       </c>
       <c r="C2368">
-        <v>5935.6</v>
+        <v>7167.7</v>
       </c>
       <c r="D2368" t="s">
         <v>2370</v>
@@ -41038,7 +41614,7 @@
         <v>64</v>
       </c>
       <c r="C2369">
-        <v>5917.7</v>
+        <v>7210.6</v>
       </c>
       <c r="D2369" t="s">
         <v>2371</v>
@@ -41052,7 +41628,7 @@
         <v>65</v>
       </c>
       <c r="C2370">
-        <v>5763</v>
+        <v>7091.7</v>
       </c>
       <c r="D2370" t="s">
         <v>2372</v>
@@ -41066,7 +41642,7 @@
         <v>66</v>
       </c>
       <c r="C2371">
-        <v>5714.1</v>
+        <v>6997.8</v>
       </c>
       <c r="D2371" t="s">
         <v>2373</v>
@@ -41080,7 +41656,7 @@
         <v>67</v>
       </c>
       <c r="C2372">
-        <v>5651.6</v>
+        <v>6926.9</v>
       </c>
       <c r="D2372" t="s">
         <v>2374</v>
@@ -41094,7 +41670,7 @@
         <v>68</v>
       </c>
       <c r="C2373">
-        <v>5614.9</v>
+        <v>6847.9</v>
       </c>
       <c r="D2373" t="s">
         <v>2375</v>
@@ -41108,7 +41684,7 @@
         <v>69</v>
       </c>
       <c r="C2374">
-        <v>5996.3</v>
+        <v>6849.5</v>
       </c>
       <c r="D2374" t="s">
         <v>2376</v>
@@ -41122,7 +41698,7 @@
         <v>70</v>
       </c>
       <c r="C2375">
-        <v>5920</v>
+        <v>6714.8</v>
       </c>
       <c r="D2375" t="s">
         <v>2377</v>
@@ -41136,7 +41712,7 @@
         <v>71</v>
       </c>
       <c r="C2376">
-        <v>5808.5</v>
+        <v>6573.8</v>
       </c>
       <c r="D2376" t="s">
         <v>2378</v>
@@ -41150,7 +41726,7 @@
         <v>72</v>
       </c>
       <c r="C2377">
-        <v>5696.4</v>
+        <v>6466.1</v>
       </c>
       <c r="D2377" t="s">
         <v>2379</v>
@@ -41164,7 +41740,7 @@
         <v>73</v>
       </c>
       <c r="C2378">
-        <v>5719.2</v>
+        <v>6304.7</v>
       </c>
       <c r="D2378" t="s">
         <v>2380</v>
@@ -41178,7 +41754,7 @@
         <v>74</v>
       </c>
       <c r="C2379">
-        <v>5575.3</v>
+        <v>6145.4</v>
       </c>
       <c r="D2379" t="s">
         <v>2381</v>
@@ -41192,7 +41768,7 @@
         <v>75</v>
       </c>
       <c r="C2380">
-        <v>5366.7</v>
+        <v>6004.9</v>
       </c>
       <c r="D2380" t="s">
         <v>2382</v>
@@ -41206,7 +41782,7 @@
         <v>76</v>
       </c>
       <c r="C2381">
-        <v>5243.1</v>
+        <v>5897.7</v>
       </c>
       <c r="D2381" t="s">
         <v>2383</v>
@@ -41220,7 +41796,7 @@
         <v>77</v>
       </c>
       <c r="C2382">
-        <v>5160.3</v>
+        <v>5599.9</v>
       </c>
       <c r="D2382" t="s">
         <v>2384</v>
@@ -41234,7 +41810,7 @@
         <v>78</v>
       </c>
       <c r="C2383">
-        <v>5029.2</v>
+        <v>5558.7</v>
       </c>
       <c r="D2383" t="s">
         <v>2385</v>
@@ -41248,7 +41824,7 @@
         <v>79</v>
       </c>
       <c r="C2384">
-        <v>4906.6</v>
+        <v>5498.5</v>
       </c>
       <c r="D2384" t="s">
         <v>2386</v>
@@ -41262,7 +41838,7 @@
         <v>80</v>
       </c>
       <c r="C2385">
-        <v>4904.2</v>
+        <v>5446.1</v>
       </c>
       <c r="D2385" t="s">
         <v>2387</v>
@@ -41276,7 +41852,7 @@
         <v>81</v>
       </c>
       <c r="C2386">
-        <v>5293.7</v>
+        <v>5823.8</v>
       </c>
       <c r="D2386" t="s">
         <v>2388</v>
@@ -41290,7 +41866,7 @@
         <v>82</v>
       </c>
       <c r="C2387">
-        <v>5347.8</v>
+        <v>5871</v>
       </c>
       <c r="D2387" t="s">
         <v>2389</v>
@@ -41304,7 +41880,7 @@
         <v>83</v>
       </c>
       <c r="C2388">
-        <v>5356.2</v>
+        <v>5827.5</v>
       </c>
       <c r="D2388" t="s">
         <v>2390</v>
@@ -41318,7 +41894,7 @@
         <v>84</v>
       </c>
       <c r="C2389">
-        <v>5335.4</v>
+        <v>5802.4</v>
       </c>
       <c r="D2389" t="s">
         <v>2391</v>
@@ -41332,7 +41908,7 @@
         <v>85</v>
       </c>
       <c r="C2390">
-        <v>5268.2</v>
+        <v>5775.6</v>
       </c>
       <c r="D2390" t="s">
         <v>2392</v>
@@ -41346,7 +41922,7 @@
         <v>86</v>
       </c>
       <c r="C2391">
-        <v>5193.6</v>
+        <v>5793.1</v>
       </c>
       <c r="D2391" t="s">
         <v>2393</v>
@@ -41360,7 +41936,7 @@
         <v>87</v>
       </c>
       <c r="C2392">
-        <v>5167.7</v>
+        <v>5796.5</v>
       </c>
       <c r="D2392" t="s">
         <v>2394</v>
@@ -41374,7 +41950,7 @@
         <v>88</v>
       </c>
       <c r="C2393">
-        <v>5122.2</v>
+        <v>5792.9</v>
       </c>
       <c r="D2393" t="s">
         <v>2395</v>
@@ -41388,7 +41964,7 @@
         <v>89</v>
       </c>
       <c r="C2394">
-        <v>4794.4</v>
+        <v>5571</v>
       </c>
       <c r="D2394" t="s">
         <v>2396</v>
@@ -41402,7 +41978,7 @@
         <v>90</v>
       </c>
       <c r="C2395">
-        <v>4708.5</v>
+        <v>5546.5</v>
       </c>
       <c r="D2395" t="s">
         <v>2397</v>
@@ -41416,7 +41992,7 @@
         <v>91</v>
       </c>
       <c r="C2396">
-        <v>4632.5</v>
+        <v>5478.9</v>
       </c>
       <c r="D2396" t="s">
         <v>2398</v>
@@ -41430,7 +42006,7 @@
         <v>92</v>
       </c>
       <c r="C2397">
-        <v>4552.2</v>
+        <v>5418.2</v>
       </c>
       <c r="D2397" t="s">
         <v>2399</v>
@@ -41444,7 +42020,7 @@
         <v>93</v>
       </c>
       <c r="C2398">
-        <v>4311</v>
+        <v>5235.2</v>
       </c>
       <c r="D2398" t="s">
         <v>2400</v>
@@ -41458,7 +42034,7 @@
         <v>94</v>
       </c>
       <c r="C2399">
-        <v>4237.8</v>
+        <v>5142.4</v>
       </c>
       <c r="D2399" t="s">
         <v>2401</v>
@@ -41472,7 +42048,7 @@
         <v>95</v>
       </c>
       <c r="C2400">
-        <v>4204</v>
+        <v>5143.1</v>
       </c>
       <c r="D2400" t="s">
         <v>2402</v>
@@ -41486,7 +42062,7 @@
         <v>96</v>
       </c>
       <c r="C2401">
-        <v>4170.3</v>
+        <v>5152.2</v>
       </c>
       <c r="D2401" t="s">
         <v>2403</v>
@@ -41500,7 +42076,7 @@
         <v>1</v>
       </c>
       <c r="C2402">
-        <v>5077.7</v>
+        <v>4977.7</v>
       </c>
       <c r="D2402" t="s">
         <v>2404</v>
@@ -41514,7 +42090,7 @@
         <v>2</v>
       </c>
       <c r="C2403">
-        <v>5104</v>
+        <v>5004</v>
       </c>
       <c r="D2403" t="s">
         <v>2405</v>
@@ -41528,7 +42104,7 @@
         <v>3</v>
       </c>
       <c r="C2404">
-        <v>5123.5</v>
+        <v>5023.5</v>
       </c>
       <c r="D2404" t="s">
         <v>2406</v>
@@ -41542,7 +42118,7 @@
         <v>4</v>
       </c>
       <c r="C2405">
-        <v>5091.2</v>
+        <v>4991.2</v>
       </c>
       <c r="D2405" t="s">
         <v>2407</v>
@@ -41556,7 +42132,7 @@
         <v>5</v>
       </c>
       <c r="C2406">
-        <v>5108.6</v>
+        <v>5008.6</v>
       </c>
       <c r="D2406" t="s">
         <v>2408</v>
@@ -41570,7 +42146,7 @@
         <v>6</v>
       </c>
       <c r="C2407">
-        <v>5099.4</v>
+        <v>4999.4</v>
       </c>
       <c r="D2407" t="s">
         <v>2409</v>
@@ -41584,7 +42160,7 @@
         <v>7</v>
       </c>
       <c r="C2408">
-        <v>5085.2</v>
+        <v>4985.2</v>
       </c>
       <c r="D2408" t="s">
         <v>2410</v>
@@ -41598,7 +42174,7 @@
         <v>8</v>
       </c>
       <c r="C2409">
-        <v>5061.8</v>
+        <v>4961.8</v>
       </c>
       <c r="D2409" t="s">
         <v>2411</v>
@@ -41612,7 +42188,7 @@
         <v>9</v>
       </c>
       <c r="C2410">
-        <v>5056.9</v>
+        <v>4956.9</v>
       </c>
       <c r="D2410" t="s">
         <v>2412</v>
@@ -41626,7 +42202,7 @@
         <v>10</v>
       </c>
       <c r="C2411">
-        <v>5049.8</v>
+        <v>4949.8</v>
       </c>
       <c r="D2411" t="s">
         <v>2413</v>
@@ -41640,7 +42216,7 @@
         <v>11</v>
       </c>
       <c r="C2412">
-        <v>5042.6</v>
+        <v>4942.6</v>
       </c>
       <c r="D2412" t="s">
         <v>2414</v>
@@ -41654,7 +42230,7 @@
         <v>12</v>
       </c>
       <c r="C2413">
-        <v>4977.4</v>
+        <v>4877.4</v>
       </c>
       <c r="D2413" t="s">
         <v>2415</v>
@@ -41668,7 +42244,7 @@
         <v>13</v>
       </c>
       <c r="C2414">
-        <v>4916.2</v>
+        <v>4816.2</v>
       </c>
       <c r="D2414" t="s">
         <v>2416</v>
@@ -41682,7 +42258,7 @@
         <v>14</v>
       </c>
       <c r="C2415">
-        <v>4803.9</v>
+        <v>4703.9</v>
       </c>
       <c r="D2415" t="s">
         <v>2417</v>
@@ -41696,7 +42272,7 @@
         <v>15</v>
       </c>
       <c r="C2416">
-        <v>4803.9</v>
+        <v>4703.9</v>
       </c>
       <c r="D2416" t="s">
         <v>2418</v>
@@ -41710,7 +42286,7 @@
         <v>16</v>
       </c>
       <c r="C2417">
-        <v>4773.9</v>
+        <v>4673.9</v>
       </c>
       <c r="D2417" t="s">
         <v>2419</v>
@@ -41724,7 +42300,7 @@
         <v>17</v>
       </c>
       <c r="C2418">
-        <v>4798.2</v>
+        <v>4698.2</v>
       </c>
       <c r="D2418" t="s">
         <v>2420</v>
@@ -41738,7 +42314,7 @@
         <v>18</v>
       </c>
       <c r="C2419">
-        <v>4789.3</v>
+        <v>4689.3</v>
       </c>
       <c r="D2419" t="s">
         <v>2421</v>
@@ -41752,7 +42328,7 @@
         <v>19</v>
       </c>
       <c r="C2420">
-        <v>4793.9</v>
+        <v>4693.9</v>
       </c>
       <c r="D2420" t="s">
         <v>2422</v>
@@ -41766,7 +42342,7 @@
         <v>20</v>
       </c>
       <c r="C2421">
-        <v>4793.8</v>
+        <v>4693.8</v>
       </c>
       <c r="D2421" t="s">
         <v>2423</v>
@@ -41780,7 +42356,7 @@
         <v>21</v>
       </c>
       <c r="C2422">
-        <v>4727.6</v>
+        <v>4627.6</v>
       </c>
       <c r="D2422" t="s">
         <v>2424</v>
@@ -41794,7 +42370,7 @@
         <v>22</v>
       </c>
       <c r="C2423">
-        <v>4796.1</v>
+        <v>4696.1</v>
       </c>
       <c r="D2423" t="s">
         <v>2425</v>
@@ -41808,7 +42384,7 @@
         <v>23</v>
       </c>
       <c r="C2424">
-        <v>4849.9</v>
+        <v>4749.9</v>
       </c>
       <c r="D2424" t="s">
         <v>2426</v>
@@ -41822,7 +42398,7 @@
         <v>24</v>
       </c>
       <c r="C2425">
-        <v>4844</v>
+        <v>4744</v>
       </c>
       <c r="D2425" t="s">
         <v>2427</v>
@@ -41836,7 +42412,7 @@
         <v>25</v>
       </c>
       <c r="C2426">
-        <v>4936</v>
+        <v>4836</v>
       </c>
       <c r="D2426" t="s">
         <v>2428</v>
@@ -41850,7 +42426,7 @@
         <v>26</v>
       </c>
       <c r="C2427">
-        <v>4986</v>
+        <v>4886</v>
       </c>
       <c r="D2427" t="s">
         <v>2429</v>
@@ -41864,7 +42440,7 @@
         <v>27</v>
       </c>
       <c r="C2428">
-        <v>5128.2</v>
+        <v>5028.2</v>
       </c>
       <c r="D2428" t="s">
         <v>2430</v>
@@ -41878,7 +42454,7 @@
         <v>28</v>
       </c>
       <c r="C2429">
-        <v>5173</v>
+        <v>5073</v>
       </c>
       <c r="D2429" t="s">
         <v>2431</v>
@@ -41892,7 +42468,7 @@
         <v>29</v>
       </c>
       <c r="C2430">
-        <v>5265.3</v>
+        <v>5165.3</v>
       </c>
       <c r="D2430" t="s">
         <v>2432</v>
@@ -41906,7 +42482,7 @@
         <v>30</v>
       </c>
       <c r="C2431">
-        <v>5335.2</v>
+        <v>5235.2</v>
       </c>
       <c r="D2431" t="s">
         <v>2433</v>
@@ -41920,7 +42496,7 @@
         <v>31</v>
       </c>
       <c r="C2432">
-        <v>5458.6</v>
+        <v>5358.6</v>
       </c>
       <c r="D2432" t="s">
         <v>2434</v>
@@ -41934,7 +42510,7 @@
         <v>32</v>
       </c>
       <c r="C2433">
-        <v>5560.7</v>
+        <v>5460.7</v>
       </c>
       <c r="D2433" t="s">
         <v>2435</v>
@@ -41948,7 +42524,7 @@
         <v>33</v>
       </c>
       <c r="C2434">
-        <v>5958.6</v>
+        <v>5858.6</v>
       </c>
       <c r="D2434" t="s">
         <v>2436</v>
@@ -41962,7 +42538,7 @@
         <v>34</v>
       </c>
       <c r="C2435">
-        <v>6069.2</v>
+        <v>5969.2</v>
       </c>
       <c r="D2435" t="s">
         <v>2437</v>
@@ -41976,7 +42552,7 @@
         <v>35</v>
       </c>
       <c r="C2436">
-        <v>6149.1</v>
+        <v>6049.1</v>
       </c>
       <c r="D2436" t="s">
         <v>2438</v>
@@ -41990,7 +42566,7 @@
         <v>36</v>
       </c>
       <c r="C2437">
-        <v>6201.7</v>
+        <v>6101.7</v>
       </c>
       <c r="D2437" t="s">
         <v>2439</v>
@@ -42004,7 +42580,7 @@
         <v>37</v>
       </c>
       <c r="C2438">
-        <v>6060.9</v>
+        <v>5960.9</v>
       </c>
       <c r="D2438" t="s">
         <v>2440</v>
@@ -42018,7 +42594,7 @@
         <v>38</v>
       </c>
       <c r="C2439">
-        <v>6113.1</v>
+        <v>6013.1</v>
       </c>
       <c r="D2439" t="s">
         <v>2441</v>
@@ -42032,7 +42608,7 @@
         <v>39</v>
       </c>
       <c r="C2440">
-        <v>6102.2</v>
+        <v>6002.2</v>
       </c>
       <c r="D2440" t="s">
         <v>2442</v>
@@ -42046,7 +42622,7 @@
         <v>40</v>
       </c>
       <c r="C2441">
-        <v>6138.6</v>
+        <v>6038.6</v>
       </c>
       <c r="D2441" t="s">
         <v>2443</v>
@@ -42060,7 +42636,7 @@
         <v>41</v>
       </c>
       <c r="C2442">
-        <v>6005.7</v>
+        <v>5905.7</v>
       </c>
       <c r="D2442" t="s">
         <v>2444</v>
@@ -42074,7 +42650,7 @@
         <v>42</v>
       </c>
       <c r="C2443">
-        <v>6058.6</v>
+        <v>5958.6</v>
       </c>
       <c r="D2443" t="s">
         <v>2445</v>
@@ -42088,7 +42664,7 @@
         <v>43</v>
       </c>
       <c r="C2444">
-        <v>6117.9</v>
+        <v>6017.9</v>
       </c>
       <c r="D2444" t="s">
         <v>2446</v>
@@ -42102,7 +42678,7 @@
         <v>44</v>
       </c>
       <c r="C2445">
-        <v>6218.8</v>
+        <v>6118.8</v>
       </c>
       <c r="D2445" t="s">
         <v>2447</v>
@@ -42116,7 +42692,7 @@
         <v>45</v>
       </c>
       <c r="C2446">
-        <v>6281.8</v>
+        <v>6181.8</v>
       </c>
       <c r="D2446" t="s">
         <v>2448</v>
@@ -42130,7 +42706,7 @@
         <v>46</v>
       </c>
       <c r="C2447">
-        <v>6388.2</v>
+        <v>6288.2</v>
       </c>
       <c r="D2447" t="s">
         <v>2449</v>
@@ -42144,7 +42720,7 @@
         <v>47</v>
       </c>
       <c r="C2448">
-        <v>6473.9</v>
+        <v>6373.9</v>
       </c>
       <c r="D2448" t="s">
         <v>2450</v>
@@ -42158,7 +42734,7 @@
         <v>48</v>
       </c>
       <c r="C2449">
-        <v>6527.3</v>
+        <v>6427.3</v>
       </c>
       <c r="D2449" t="s">
         <v>2451</v>
@@ -42172,7 +42748,7 @@
         <v>49</v>
       </c>
       <c r="C2450">
-        <v>6620.8</v>
+        <v>6520.8</v>
       </c>
       <c r="D2450" t="s">
         <v>2452</v>
@@ -42186,7 +42762,7 @@
         <v>50</v>
       </c>
       <c r="C2451">
-        <v>6663.7</v>
+        <v>6563.7</v>
       </c>
       <c r="D2451" t="s">
         <v>2453</v>
@@ -42200,7 +42776,7 @@
         <v>51</v>
       </c>
       <c r="C2452">
-        <v>6660.5</v>
+        <v>6560.5</v>
       </c>
       <c r="D2452" t="s">
         <v>2454</v>
@@ -42214,7 +42790,7 @@
         <v>52</v>
       </c>
       <c r="C2453">
-        <v>6785</v>
+        <v>6685</v>
       </c>
       <c r="D2453" t="s">
         <v>2455</v>
@@ -42228,7 +42804,7 @@
         <v>53</v>
       </c>
       <c r="C2454">
-        <v>6660</v>
+        <v>6560</v>
       </c>
       <c r="D2454" t="s">
         <v>2456</v>
@@ -42242,7 +42818,7 @@
         <v>54</v>
       </c>
       <c r="C2455">
-        <v>6672</v>
+        <v>6572</v>
       </c>
       <c r="D2455" t="s">
         <v>2457</v>
@@ -42256,7 +42832,7 @@
         <v>55</v>
       </c>
       <c r="C2456">
-        <v>6701.6</v>
+        <v>6601.6</v>
       </c>
       <c r="D2456" t="s">
         <v>2458</v>
@@ -42270,7 +42846,7 @@
         <v>56</v>
       </c>
       <c r="C2457">
-        <v>6671.1</v>
+        <v>6571.1</v>
       </c>
       <c r="D2457" t="s">
         <v>2459</v>
@@ -42284,7 +42860,7 @@
         <v>57</v>
       </c>
       <c r="C2458">
-        <v>6804.2</v>
+        <v>6704.2</v>
       </c>
       <c r="D2458" t="s">
         <v>2460</v>
@@ -42298,7 +42874,7 @@
         <v>58</v>
       </c>
       <c r="C2459">
-        <v>6839.4</v>
+        <v>6739.4</v>
       </c>
       <c r="D2459" t="s">
         <v>2461</v>
@@ -42312,7 +42888,7 @@
         <v>59</v>
       </c>
       <c r="C2460">
-        <v>6900.8</v>
+        <v>6800.8</v>
       </c>
       <c r="D2460" t="s">
         <v>2462</v>
@@ -42326,7 +42902,7 @@
         <v>60</v>
       </c>
       <c r="C2461">
-        <v>6950.5</v>
+        <v>6850.5</v>
       </c>
       <c r="D2461" t="s">
         <v>2463</v>
@@ -42340,7 +42916,7 @@
         <v>61</v>
       </c>
       <c r="C2462">
-        <v>7065.8</v>
+        <v>6965.8</v>
       </c>
       <c r="D2462" t="s">
         <v>2464</v>
@@ -42354,7 +42930,7 @@
         <v>62</v>
       </c>
       <c r="C2463">
-        <v>7067.5</v>
+        <v>6967.5</v>
       </c>
       <c r="D2463" t="s">
         <v>2465</v>
@@ -42368,7 +42944,7 @@
         <v>63</v>
       </c>
       <c r="C2464">
-        <v>7157.7</v>
+        <v>7057.7</v>
       </c>
       <c r="D2464" t="s">
         <v>2466</v>
@@ -42382,7 +42958,7 @@
         <v>64</v>
       </c>
       <c r="C2465">
-        <v>7220.6</v>
+        <v>7120.6</v>
       </c>
       <c r="D2465" t="s">
         <v>2467</v>
@@ -42396,7 +42972,7 @@
         <v>65</v>
       </c>
       <c r="C2466">
-        <v>7111.7</v>
+        <v>7011.7</v>
       </c>
       <c r="D2466" t="s">
         <v>2468</v>
@@ -42410,7 +42986,7 @@
         <v>66</v>
       </c>
       <c r="C2467">
-        <v>7037.8</v>
+        <v>6937.8</v>
       </c>
       <c r="D2467" t="s">
         <v>2469</v>
@@ -42424,7 +43000,7 @@
         <v>67</v>
       </c>
       <c r="C2468">
-        <v>6996.9</v>
+        <v>6896.9</v>
       </c>
       <c r="D2468" t="s">
         <v>2470</v>
@@ -42438,7 +43014,7 @@
         <v>68</v>
       </c>
       <c r="C2469">
-        <v>6937.9</v>
+        <v>6837.9</v>
       </c>
       <c r="D2469" t="s">
         <v>2471</v>
@@ -42452,7 +43028,7 @@
         <v>69</v>
       </c>
       <c r="C2470">
-        <v>6959.5</v>
+        <v>6859.5</v>
       </c>
       <c r="D2470" t="s">
         <v>2472</v>
@@ -42466,7 +43042,7 @@
         <v>70</v>
       </c>
       <c r="C2471">
-        <v>6854.8</v>
+        <v>6754.8</v>
       </c>
       <c r="D2471" t="s">
         <v>2473</v>
@@ -42480,7 +43056,7 @@
         <v>71</v>
       </c>
       <c r="C2472">
-        <v>6733.8</v>
+        <v>6633.8</v>
       </c>
       <c r="D2472" t="s">
         <v>2474</v>
@@ -42494,7 +43070,7 @@
         <v>72</v>
       </c>
       <c r="C2473">
-        <v>6636.1</v>
+        <v>6536.1</v>
       </c>
       <c r="D2473" t="s">
         <v>2475</v>
@@ -42508,7 +43084,7 @@
         <v>73</v>
       </c>
       <c r="C2474">
-        <v>6484.7</v>
+        <v>6384.7</v>
       </c>
       <c r="D2474" t="s">
         <v>2476</v>
@@ -42522,7 +43098,7 @@
         <v>74</v>
       </c>
       <c r="C2475">
-        <v>6335.4</v>
+        <v>6235.4</v>
       </c>
       <c r="D2475" t="s">
         <v>2477</v>
@@ -42536,7 +43112,7 @@
         <v>75</v>
       </c>
       <c r="C2476">
-        <v>6204.9</v>
+        <v>6104.9</v>
       </c>
       <c r="D2476" t="s">
         <v>2478</v>
@@ -42550,7 +43126,7 @@
         <v>76</v>
       </c>
       <c r="C2477">
-        <v>6117.7</v>
+        <v>6017.7</v>
       </c>
       <c r="D2477" t="s">
         <v>2479</v>
@@ -42564,7 +43140,7 @@
         <v>77</v>
       </c>
       <c r="C2478">
-        <v>5829.9</v>
+        <v>5729.9</v>
       </c>
       <c r="D2478" t="s">
         <v>2480</v>
@@ -42578,7 +43154,7 @@
         <v>78</v>
       </c>
       <c r="C2479">
-        <v>5798.7</v>
+        <v>5698.7</v>
       </c>
       <c r="D2479" t="s">
         <v>2481</v>
@@ -42592,7 +43168,7 @@
         <v>79</v>
       </c>
       <c r="C2480">
-        <v>5758.5</v>
+        <v>5658.5</v>
       </c>
       <c r="D2480" t="s">
         <v>2482</v>
@@ -42606,7 +43182,7 @@
         <v>80</v>
       </c>
       <c r="C2481">
-        <v>5706.1</v>
+        <v>5606.1</v>
       </c>
       <c r="D2481" t="s">
         <v>2483</v>
@@ -42620,7 +43196,7 @@
         <v>81</v>
       </c>
       <c r="C2482">
-        <v>6073.8</v>
+        <v>5973.8</v>
       </c>
       <c r="D2482" t="s">
         <v>2484</v>
@@ -42634,7 +43210,7 @@
         <v>82</v>
       </c>
       <c r="C2483">
-        <v>6131</v>
+        <v>6031</v>
       </c>
       <c r="D2483" t="s">
         <v>2485</v>
@@ -42648,7 +43224,7 @@
         <v>83</v>
       </c>
       <c r="C2484">
-        <v>6107.5</v>
+        <v>6007.5</v>
       </c>
       <c r="D2484" t="s">
         <v>2486</v>
@@ -42662,7 +43238,7 @@
         <v>84</v>
       </c>
       <c r="C2485">
-        <v>6102.4</v>
+        <v>6002.4</v>
       </c>
       <c r="D2485" t="s">
         <v>2487</v>
@@ -42676,7 +43252,7 @@
         <v>85</v>
       </c>
       <c r="C2486">
-        <v>6065.6</v>
+        <v>5965.6</v>
       </c>
       <c r="D2486" t="s">
         <v>2488</v>
@@ -42690,7 +43266,7 @@
         <v>86</v>
       </c>
       <c r="C2487">
-        <v>6033.1</v>
+        <v>5933.1</v>
       </c>
       <c r="D2487" t="s">
         <v>2489</v>
@@ -42704,7 +43280,7 @@
         <v>87</v>
       </c>
       <c r="C2488">
-        <v>6006.5</v>
+        <v>5906.5</v>
       </c>
       <c r="D2488" t="s">
         <v>2490</v>
@@ -42718,7 +43294,7 @@
         <v>88</v>
       </c>
       <c r="C2489">
-        <v>5932.9</v>
+        <v>5832.9</v>
       </c>
       <c r="D2489" t="s">
         <v>2491</v>
@@ -42732,7 +43308,7 @@
         <v>89</v>
       </c>
       <c r="C2490">
-        <v>5631</v>
+        <v>5531</v>
       </c>
       <c r="D2490" t="s">
         <v>2492</v>
@@ -42746,7 +43322,7 @@
         <v>90</v>
       </c>
       <c r="C2491">
-        <v>5546.5</v>
+        <v>5446.5</v>
       </c>
       <c r="D2491" t="s">
         <v>2493</v>
@@ -42760,7 +43336,7 @@
         <v>91</v>
       </c>
       <c r="C2492">
-        <v>5458.9</v>
+        <v>5358.9</v>
       </c>
       <c r="D2492" t="s">
         <v>2494</v>
@@ -42774,7 +43350,7 @@
         <v>92</v>
       </c>
       <c r="C2493">
-        <v>5418.2</v>
+        <v>5318.2</v>
       </c>
       <c r="D2493" t="s">
         <v>2495</v>
@@ -42788,7 +43364,7 @@
         <v>93</v>
       </c>
       <c r="C2494">
-        <v>5245.2</v>
+        <v>5145.2</v>
       </c>
       <c r="D2494" t="s">
         <v>2496</v>
@@ -42802,7 +43378,7 @@
         <v>94</v>
       </c>
       <c r="C2495">
-        <v>5142.4</v>
+        <v>5042.4</v>
       </c>
       <c r="D2495" t="s">
         <v>2497</v>
@@ -42816,7 +43392,7 @@
         <v>95</v>
       </c>
       <c r="C2496">
-        <v>5143.1</v>
+        <v>5043.1</v>
       </c>
       <c r="D2496" t="s">
         <v>2498</v>
@@ -42830,10 +43406,2698 @@
         <v>96</v>
       </c>
       <c r="C2497">
-        <v>5152.2</v>
+        <v>5052.2</v>
       </c>
       <c r="D2497" t="s">
         <v>2499</v>
+      </c>
+    </row>
+    <row r="2498" spans="1:4">
+      <c r="A2498" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2498">
+        <v>1</v>
+      </c>
+      <c r="C2498">
+        <v>5037.7</v>
+      </c>
+      <c r="D2498" t="s">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="2499" spans="1:4">
+      <c r="A2499" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2499">
+        <v>2</v>
+      </c>
+      <c r="C2499">
+        <v>5054</v>
+      </c>
+      <c r="D2499" t="s">
+        <v>2501</v>
+      </c>
+    </row>
+    <row r="2500" spans="1:4">
+      <c r="A2500" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2500">
+        <v>3</v>
+      </c>
+      <c r="C2500">
+        <v>5073.5</v>
+      </c>
+      <c r="D2500" t="s">
+        <v>2502</v>
+      </c>
+    </row>
+    <row r="2501" spans="1:4">
+      <c r="A2501" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2501">
+        <v>4</v>
+      </c>
+      <c r="C2501">
+        <v>5041.2</v>
+      </c>
+      <c r="D2501" t="s">
+        <v>2503</v>
+      </c>
+    </row>
+    <row r="2502" spans="1:4">
+      <c r="A2502" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2502">
+        <v>5</v>
+      </c>
+      <c r="C2502">
+        <v>5058.6</v>
+      </c>
+      <c r="D2502" t="s">
+        <v>2504</v>
+      </c>
+    </row>
+    <row r="2503" spans="1:4">
+      <c r="A2503" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2503">
+        <v>6</v>
+      </c>
+      <c r="C2503">
+        <v>5049.4</v>
+      </c>
+      <c r="D2503" t="s">
+        <v>2505</v>
+      </c>
+    </row>
+    <row r="2504" spans="1:4">
+      <c r="A2504" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2504">
+        <v>7</v>
+      </c>
+      <c r="C2504">
+        <v>5035.2</v>
+      </c>
+      <c r="D2504" t="s">
+        <v>2506</v>
+      </c>
+    </row>
+    <row r="2505" spans="1:4">
+      <c r="A2505" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2505">
+        <v>8</v>
+      </c>
+      <c r="C2505">
+        <v>5011.8</v>
+      </c>
+      <c r="D2505" t="s">
+        <v>2507</v>
+      </c>
+    </row>
+    <row r="2506" spans="1:4">
+      <c r="A2506" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2506">
+        <v>9</v>
+      </c>
+      <c r="C2506">
+        <v>5006.9</v>
+      </c>
+      <c r="D2506" t="s">
+        <v>2508</v>
+      </c>
+    </row>
+    <row r="2507" spans="1:4">
+      <c r="A2507" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2507">
+        <v>10</v>
+      </c>
+      <c r="C2507">
+        <v>4999.8</v>
+      </c>
+      <c r="D2507" t="s">
+        <v>2509</v>
+      </c>
+    </row>
+    <row r="2508" spans="1:4">
+      <c r="A2508" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2508">
+        <v>11</v>
+      </c>
+      <c r="C2508">
+        <v>4992.6</v>
+      </c>
+      <c r="D2508" t="s">
+        <v>2510</v>
+      </c>
+    </row>
+    <row r="2509" spans="1:4">
+      <c r="A2509" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2509">
+        <v>12</v>
+      </c>
+      <c r="C2509">
+        <v>4927.4</v>
+      </c>
+      <c r="D2509" t="s">
+        <v>2511</v>
+      </c>
+    </row>
+    <row r="2510" spans="1:4">
+      <c r="A2510" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2510">
+        <v>13</v>
+      </c>
+      <c r="C2510">
+        <v>4866.2</v>
+      </c>
+      <c r="D2510" t="s">
+        <v>2512</v>
+      </c>
+    </row>
+    <row r="2511" spans="1:4">
+      <c r="A2511" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2511">
+        <v>14</v>
+      </c>
+      <c r="C2511">
+        <v>4753.9</v>
+      </c>
+      <c r="D2511" t="s">
+        <v>2513</v>
+      </c>
+    </row>
+    <row r="2512" spans="1:4">
+      <c r="A2512" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2512">
+        <v>15</v>
+      </c>
+      <c r="C2512">
+        <v>4753.9</v>
+      </c>
+      <c r="D2512" t="s">
+        <v>2514</v>
+      </c>
+    </row>
+    <row r="2513" spans="1:4">
+      <c r="A2513" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2513">
+        <v>16</v>
+      </c>
+      <c r="C2513">
+        <v>4723.9</v>
+      </c>
+      <c r="D2513" t="s">
+        <v>2515</v>
+      </c>
+    </row>
+    <row r="2514" spans="1:4">
+      <c r="A2514" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2514">
+        <v>17</v>
+      </c>
+      <c r="C2514">
+        <v>4748.2</v>
+      </c>
+      <c r="D2514" t="s">
+        <v>2516</v>
+      </c>
+    </row>
+    <row r="2515" spans="1:4">
+      <c r="A2515" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2515">
+        <v>18</v>
+      </c>
+      <c r="C2515">
+        <v>4739.3</v>
+      </c>
+      <c r="D2515" t="s">
+        <v>2517</v>
+      </c>
+    </row>
+    <row r="2516" spans="1:4">
+      <c r="A2516" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2516">
+        <v>19</v>
+      </c>
+      <c r="C2516">
+        <v>4743.9</v>
+      </c>
+      <c r="D2516" t="s">
+        <v>2518</v>
+      </c>
+    </row>
+    <row r="2517" spans="1:4">
+      <c r="A2517" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2517">
+        <v>20</v>
+      </c>
+      <c r="C2517">
+        <v>4743.8</v>
+      </c>
+      <c r="D2517" t="s">
+        <v>2519</v>
+      </c>
+    </row>
+    <row r="2518" spans="1:4">
+      <c r="A2518" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2518">
+        <v>21</v>
+      </c>
+      <c r="C2518">
+        <v>4677.6</v>
+      </c>
+      <c r="D2518" t="s">
+        <v>2520</v>
+      </c>
+    </row>
+    <row r="2519" spans="1:4">
+      <c r="A2519" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2519">
+        <v>22</v>
+      </c>
+      <c r="C2519">
+        <v>4746.1</v>
+      </c>
+      <c r="D2519" t="s">
+        <v>2521</v>
+      </c>
+    </row>
+    <row r="2520" spans="1:4">
+      <c r="A2520" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2520">
+        <v>23</v>
+      </c>
+      <c r="C2520">
+        <v>4799.9</v>
+      </c>
+      <c r="D2520" t="s">
+        <v>2522</v>
+      </c>
+    </row>
+    <row r="2521" spans="1:4">
+      <c r="A2521" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2521">
+        <v>24</v>
+      </c>
+      <c r="C2521">
+        <v>4794</v>
+      </c>
+      <c r="D2521" t="s">
+        <v>2523</v>
+      </c>
+    </row>
+    <row r="2522" spans="1:4">
+      <c r="A2522" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2522">
+        <v>25</v>
+      </c>
+      <c r="C2522">
+        <v>4886</v>
+      </c>
+      <c r="D2522" t="s">
+        <v>2524</v>
+      </c>
+    </row>
+    <row r="2523" spans="1:4">
+      <c r="A2523" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2523">
+        <v>26</v>
+      </c>
+      <c r="C2523">
+        <v>4936</v>
+      </c>
+      <c r="D2523" t="s">
+        <v>2525</v>
+      </c>
+    </row>
+    <row r="2524" spans="1:4">
+      <c r="A2524" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2524">
+        <v>27</v>
+      </c>
+      <c r="C2524">
+        <v>5078.2</v>
+      </c>
+      <c r="D2524" t="s">
+        <v>2526</v>
+      </c>
+    </row>
+    <row r="2525" spans="1:4">
+      <c r="A2525" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2525">
+        <v>28</v>
+      </c>
+      <c r="C2525">
+        <v>5123</v>
+      </c>
+      <c r="D2525" t="s">
+        <v>2527</v>
+      </c>
+    </row>
+    <row r="2526" spans="1:4">
+      <c r="A2526" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2526">
+        <v>29</v>
+      </c>
+      <c r="C2526">
+        <v>5215.3</v>
+      </c>
+      <c r="D2526" t="s">
+        <v>2528</v>
+      </c>
+    </row>
+    <row r="2527" spans="1:4">
+      <c r="A2527" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2527">
+        <v>30</v>
+      </c>
+      <c r="C2527">
+        <v>5285.2</v>
+      </c>
+      <c r="D2527" t="s">
+        <v>2529</v>
+      </c>
+    </row>
+    <row r="2528" spans="1:4">
+      <c r="A2528" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2528">
+        <v>31</v>
+      </c>
+      <c r="C2528">
+        <v>5408.6</v>
+      </c>
+      <c r="D2528" t="s">
+        <v>2530</v>
+      </c>
+    </row>
+    <row r="2529" spans="1:4">
+      <c r="A2529" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2529">
+        <v>32</v>
+      </c>
+      <c r="C2529">
+        <v>5510.7</v>
+      </c>
+      <c r="D2529" t="s">
+        <v>2531</v>
+      </c>
+    </row>
+    <row r="2530" spans="1:4">
+      <c r="A2530" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2530">
+        <v>33</v>
+      </c>
+      <c r="C2530">
+        <v>5908.6</v>
+      </c>
+      <c r="D2530" t="s">
+        <v>2532</v>
+      </c>
+    </row>
+    <row r="2531" spans="1:4">
+      <c r="A2531" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2531">
+        <v>34</v>
+      </c>
+      <c r="C2531">
+        <v>6019.2</v>
+      </c>
+      <c r="D2531" t="s">
+        <v>2533</v>
+      </c>
+    </row>
+    <row r="2532" spans="1:4">
+      <c r="A2532" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2532">
+        <v>35</v>
+      </c>
+      <c r="C2532">
+        <v>6099.1</v>
+      </c>
+      <c r="D2532" t="s">
+        <v>2534</v>
+      </c>
+    </row>
+    <row r="2533" spans="1:4">
+      <c r="A2533" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2533">
+        <v>36</v>
+      </c>
+      <c r="C2533">
+        <v>6151.7</v>
+      </c>
+      <c r="D2533" t="s">
+        <v>2535</v>
+      </c>
+    </row>
+    <row r="2534" spans="1:4">
+      <c r="A2534" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2534">
+        <v>37</v>
+      </c>
+      <c r="C2534">
+        <v>6010.9</v>
+      </c>
+      <c r="D2534" t="s">
+        <v>2536</v>
+      </c>
+    </row>
+    <row r="2535" spans="1:4">
+      <c r="A2535" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2535">
+        <v>38</v>
+      </c>
+      <c r="C2535">
+        <v>6063.1</v>
+      </c>
+      <c r="D2535" t="s">
+        <v>2537</v>
+      </c>
+    </row>
+    <row r="2536" spans="1:4">
+      <c r="A2536" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2536">
+        <v>39</v>
+      </c>
+      <c r="C2536">
+        <v>6052.2</v>
+      </c>
+      <c r="D2536" t="s">
+        <v>2538</v>
+      </c>
+    </row>
+    <row r="2537" spans="1:4">
+      <c r="A2537" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2537">
+        <v>40</v>
+      </c>
+      <c r="C2537">
+        <v>6088.6</v>
+      </c>
+      <c r="D2537" t="s">
+        <v>2539</v>
+      </c>
+    </row>
+    <row r="2538" spans="1:4">
+      <c r="A2538" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2538">
+        <v>41</v>
+      </c>
+      <c r="C2538">
+        <v>5955.7</v>
+      </c>
+      <c r="D2538" t="s">
+        <v>2540</v>
+      </c>
+    </row>
+    <row r="2539" spans="1:4">
+      <c r="A2539" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2539">
+        <v>42</v>
+      </c>
+      <c r="C2539">
+        <v>6008.6</v>
+      </c>
+      <c r="D2539" t="s">
+        <v>2541</v>
+      </c>
+    </row>
+    <row r="2540" spans="1:4">
+      <c r="A2540" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2540">
+        <v>43</v>
+      </c>
+      <c r="C2540">
+        <v>6067.9</v>
+      </c>
+      <c r="D2540" t="s">
+        <v>2542</v>
+      </c>
+    </row>
+    <row r="2541" spans="1:4">
+      <c r="A2541" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2541">
+        <v>44</v>
+      </c>
+      <c r="C2541">
+        <v>6168.8</v>
+      </c>
+      <c r="D2541" t="s">
+        <v>2543</v>
+      </c>
+    </row>
+    <row r="2542" spans="1:4">
+      <c r="A2542" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2542">
+        <v>45</v>
+      </c>
+      <c r="C2542">
+        <v>6231.8</v>
+      </c>
+      <c r="D2542" t="s">
+        <v>2544</v>
+      </c>
+    </row>
+    <row r="2543" spans="1:4">
+      <c r="A2543" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2543">
+        <v>46</v>
+      </c>
+      <c r="C2543">
+        <v>6338.2</v>
+      </c>
+      <c r="D2543" t="s">
+        <v>2545</v>
+      </c>
+    </row>
+    <row r="2544" spans="1:4">
+      <c r="A2544" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2544">
+        <v>47</v>
+      </c>
+      <c r="C2544">
+        <v>6423.9</v>
+      </c>
+      <c r="D2544" t="s">
+        <v>2546</v>
+      </c>
+    </row>
+    <row r="2545" spans="1:4">
+      <c r="A2545" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2545">
+        <v>48</v>
+      </c>
+      <c r="C2545">
+        <v>6477.3</v>
+      </c>
+      <c r="D2545" t="s">
+        <v>2547</v>
+      </c>
+    </row>
+    <row r="2546" spans="1:4">
+      <c r="A2546" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2546">
+        <v>49</v>
+      </c>
+      <c r="C2546">
+        <v>6570.8</v>
+      </c>
+      <c r="D2546" t="s">
+        <v>2548</v>
+      </c>
+    </row>
+    <row r="2547" spans="1:4">
+      <c r="A2547" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2547">
+        <v>50</v>
+      </c>
+      <c r="C2547">
+        <v>6613.7</v>
+      </c>
+      <c r="D2547" t="s">
+        <v>2549</v>
+      </c>
+    </row>
+    <row r="2548" spans="1:4">
+      <c r="A2548" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2548">
+        <v>51</v>
+      </c>
+      <c r="C2548">
+        <v>6610.5</v>
+      </c>
+      <c r="D2548" t="s">
+        <v>2550</v>
+      </c>
+    </row>
+    <row r="2549" spans="1:4">
+      <c r="A2549" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2549">
+        <v>52</v>
+      </c>
+      <c r="C2549">
+        <v>6735</v>
+      </c>
+      <c r="D2549" t="s">
+        <v>2551</v>
+      </c>
+    </row>
+    <row r="2550" spans="1:4">
+      <c r="A2550" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2550">
+        <v>53</v>
+      </c>
+      <c r="C2550">
+        <v>6610</v>
+      </c>
+      <c r="D2550" t="s">
+        <v>2552</v>
+      </c>
+    </row>
+    <row r="2551" spans="1:4">
+      <c r="A2551" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2551">
+        <v>54</v>
+      </c>
+      <c r="C2551">
+        <v>6622</v>
+      </c>
+      <c r="D2551" t="s">
+        <v>2553</v>
+      </c>
+    </row>
+    <row r="2552" spans="1:4">
+      <c r="A2552" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2552">
+        <v>55</v>
+      </c>
+      <c r="C2552">
+        <v>6651.6</v>
+      </c>
+      <c r="D2552" t="s">
+        <v>2554</v>
+      </c>
+    </row>
+    <row r="2553" spans="1:4">
+      <c r="A2553" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2553">
+        <v>56</v>
+      </c>
+      <c r="C2553">
+        <v>6621.1</v>
+      </c>
+      <c r="D2553" t="s">
+        <v>2555</v>
+      </c>
+    </row>
+    <row r="2554" spans="1:4">
+      <c r="A2554" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2554">
+        <v>57</v>
+      </c>
+      <c r="C2554">
+        <v>6754.2</v>
+      </c>
+      <c r="D2554" t="s">
+        <v>2556</v>
+      </c>
+    </row>
+    <row r="2555" spans="1:4">
+      <c r="A2555" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2555">
+        <v>58</v>
+      </c>
+      <c r="C2555">
+        <v>6789.4</v>
+      </c>
+      <c r="D2555" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="2556" spans="1:4">
+      <c r="A2556" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2556">
+        <v>59</v>
+      </c>
+      <c r="C2556">
+        <v>6850.8</v>
+      </c>
+      <c r="D2556" t="s">
+        <v>2558</v>
+      </c>
+    </row>
+    <row r="2557" spans="1:4">
+      <c r="A2557" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2557">
+        <v>60</v>
+      </c>
+      <c r="C2557">
+        <v>6900.5</v>
+      </c>
+      <c r="D2557" t="s">
+        <v>2559</v>
+      </c>
+    </row>
+    <row r="2558" spans="1:4">
+      <c r="A2558" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2558">
+        <v>61</v>
+      </c>
+      <c r="C2558">
+        <v>7015.8</v>
+      </c>
+      <c r="D2558" t="s">
+        <v>2560</v>
+      </c>
+    </row>
+    <row r="2559" spans="1:4">
+      <c r="A2559" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2559">
+        <v>62</v>
+      </c>
+      <c r="C2559">
+        <v>7017.5</v>
+      </c>
+      <c r="D2559" t="s">
+        <v>2561</v>
+      </c>
+    </row>
+    <row r="2560" spans="1:4">
+      <c r="A2560" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2560">
+        <v>63</v>
+      </c>
+      <c r="C2560">
+        <v>7107.7</v>
+      </c>
+      <c r="D2560" t="s">
+        <v>2562</v>
+      </c>
+    </row>
+    <row r="2561" spans="1:4">
+      <c r="A2561" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2561">
+        <v>64</v>
+      </c>
+      <c r="C2561">
+        <v>7170.6</v>
+      </c>
+      <c r="D2561" t="s">
+        <v>2563</v>
+      </c>
+    </row>
+    <row r="2562" spans="1:4">
+      <c r="A2562" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2562">
+        <v>65</v>
+      </c>
+      <c r="C2562">
+        <v>7061.7</v>
+      </c>
+      <c r="D2562" t="s">
+        <v>2564</v>
+      </c>
+    </row>
+    <row r="2563" spans="1:4">
+      <c r="A2563" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2563">
+        <v>66</v>
+      </c>
+      <c r="C2563">
+        <v>6987.8</v>
+      </c>
+      <c r="D2563" t="s">
+        <v>2565</v>
+      </c>
+    </row>
+    <row r="2564" spans="1:4">
+      <c r="A2564" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2564">
+        <v>67</v>
+      </c>
+      <c r="C2564">
+        <v>6946.9</v>
+      </c>
+      <c r="D2564" t="s">
+        <v>2566</v>
+      </c>
+    </row>
+    <row r="2565" spans="1:4">
+      <c r="A2565" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2565">
+        <v>68</v>
+      </c>
+      <c r="C2565">
+        <v>6887.9</v>
+      </c>
+      <c r="D2565" t="s">
+        <v>2567</v>
+      </c>
+    </row>
+    <row r="2566" spans="1:4">
+      <c r="A2566" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2566">
+        <v>69</v>
+      </c>
+      <c r="C2566">
+        <v>6909.5</v>
+      </c>
+      <c r="D2566" t="s">
+        <v>2568</v>
+      </c>
+    </row>
+    <row r="2567" spans="1:4">
+      <c r="A2567" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2567">
+        <v>70</v>
+      </c>
+      <c r="C2567">
+        <v>6804.8</v>
+      </c>
+      <c r="D2567" t="s">
+        <v>2569</v>
+      </c>
+    </row>
+    <row r="2568" spans="1:4">
+      <c r="A2568" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2568">
+        <v>71</v>
+      </c>
+      <c r="C2568">
+        <v>6683.8</v>
+      </c>
+      <c r="D2568" t="s">
+        <v>2570</v>
+      </c>
+    </row>
+    <row r="2569" spans="1:4">
+      <c r="A2569" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2569">
+        <v>72</v>
+      </c>
+      <c r="C2569">
+        <v>6586.1</v>
+      </c>
+      <c r="D2569" t="s">
+        <v>2571</v>
+      </c>
+    </row>
+    <row r="2570" spans="1:4">
+      <c r="A2570" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2570">
+        <v>73</v>
+      </c>
+      <c r="C2570">
+        <v>6434.7</v>
+      </c>
+      <c r="D2570" t="s">
+        <v>2572</v>
+      </c>
+    </row>
+    <row r="2571" spans="1:4">
+      <c r="A2571" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2571">
+        <v>74</v>
+      </c>
+      <c r="C2571">
+        <v>6285.4</v>
+      </c>
+      <c r="D2571" t="s">
+        <v>2573</v>
+      </c>
+    </row>
+    <row r="2572" spans="1:4">
+      <c r="A2572" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2572">
+        <v>75</v>
+      </c>
+      <c r="C2572">
+        <v>6154.9</v>
+      </c>
+      <c r="D2572" t="s">
+        <v>2574</v>
+      </c>
+    </row>
+    <row r="2573" spans="1:4">
+      <c r="A2573" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2573">
+        <v>76</v>
+      </c>
+      <c r="C2573">
+        <v>6067.7</v>
+      </c>
+      <c r="D2573" t="s">
+        <v>2575</v>
+      </c>
+    </row>
+    <row r="2574" spans="1:4">
+      <c r="A2574" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2574">
+        <v>77</v>
+      </c>
+      <c r="C2574">
+        <v>5779.9</v>
+      </c>
+      <c r="D2574" t="s">
+        <v>2576</v>
+      </c>
+    </row>
+    <row r="2575" spans="1:4">
+      <c r="A2575" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2575">
+        <v>78</v>
+      </c>
+      <c r="C2575">
+        <v>5748.7</v>
+      </c>
+      <c r="D2575" t="s">
+        <v>2577</v>
+      </c>
+    </row>
+    <row r="2576" spans="1:4">
+      <c r="A2576" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2576">
+        <v>79</v>
+      </c>
+      <c r="C2576">
+        <v>5708.5</v>
+      </c>
+      <c r="D2576" t="s">
+        <v>2578</v>
+      </c>
+    </row>
+    <row r="2577" spans="1:4">
+      <c r="A2577" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2577">
+        <v>80</v>
+      </c>
+      <c r="C2577">
+        <v>5656.1</v>
+      </c>
+      <c r="D2577" t="s">
+        <v>2579</v>
+      </c>
+    </row>
+    <row r="2578" spans="1:4">
+      <c r="A2578" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2578">
+        <v>81</v>
+      </c>
+      <c r="C2578">
+        <v>6023.8</v>
+      </c>
+      <c r="D2578" t="s">
+        <v>2580</v>
+      </c>
+    </row>
+    <row r="2579" spans="1:4">
+      <c r="A2579" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2579">
+        <v>82</v>
+      </c>
+      <c r="C2579">
+        <v>6081</v>
+      </c>
+      <c r="D2579" t="s">
+        <v>2581</v>
+      </c>
+    </row>
+    <row r="2580" spans="1:4">
+      <c r="A2580" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2580">
+        <v>83</v>
+      </c>
+      <c r="C2580">
+        <v>6057.5</v>
+      </c>
+      <c r="D2580" t="s">
+        <v>2582</v>
+      </c>
+    </row>
+    <row r="2581" spans="1:4">
+      <c r="A2581" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2581">
+        <v>84</v>
+      </c>
+      <c r="C2581">
+        <v>6052.4</v>
+      </c>
+      <c r="D2581" t="s">
+        <v>2583</v>
+      </c>
+    </row>
+    <row r="2582" spans="1:4">
+      <c r="A2582" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2582">
+        <v>85</v>
+      </c>
+      <c r="C2582">
+        <v>6015.6</v>
+      </c>
+      <c r="D2582" t="s">
+        <v>2584</v>
+      </c>
+    </row>
+    <row r="2583" spans="1:4">
+      <c r="A2583" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2583">
+        <v>86</v>
+      </c>
+      <c r="C2583">
+        <v>5983.1</v>
+      </c>
+      <c r="D2583" t="s">
+        <v>2585</v>
+      </c>
+    </row>
+    <row r="2584" spans="1:4">
+      <c r="A2584" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2584">
+        <v>87</v>
+      </c>
+      <c r="C2584">
+        <v>5956.5</v>
+      </c>
+      <c r="D2584" t="s">
+        <v>2586</v>
+      </c>
+    </row>
+    <row r="2585" spans="1:4">
+      <c r="A2585" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2585">
+        <v>88</v>
+      </c>
+      <c r="C2585">
+        <v>5882.9</v>
+      </c>
+      <c r="D2585" t="s">
+        <v>2587</v>
+      </c>
+    </row>
+    <row r="2586" spans="1:4">
+      <c r="A2586" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2586">
+        <v>89</v>
+      </c>
+      <c r="C2586">
+        <v>5581</v>
+      </c>
+      <c r="D2586" t="s">
+        <v>2588</v>
+      </c>
+    </row>
+    <row r="2587" spans="1:4">
+      <c r="A2587" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2587">
+        <v>90</v>
+      </c>
+      <c r="C2587">
+        <v>5496.5</v>
+      </c>
+      <c r="D2587" t="s">
+        <v>2589</v>
+      </c>
+    </row>
+    <row r="2588" spans="1:4">
+      <c r="A2588" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2588">
+        <v>91</v>
+      </c>
+      <c r="C2588">
+        <v>5408.9</v>
+      </c>
+      <c r="D2588" t="s">
+        <v>2590</v>
+      </c>
+    </row>
+    <row r="2589" spans="1:4">
+      <c r="A2589" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2589">
+        <v>92</v>
+      </c>
+      <c r="C2589">
+        <v>5368.2</v>
+      </c>
+      <c r="D2589" t="s">
+        <v>2591</v>
+      </c>
+    </row>
+    <row r="2590" spans="1:4">
+      <c r="A2590" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2590">
+        <v>93</v>
+      </c>
+      <c r="C2590">
+        <v>5195.2</v>
+      </c>
+      <c r="D2590" t="s">
+        <v>2592</v>
+      </c>
+    </row>
+    <row r="2591" spans="1:4">
+      <c r="A2591" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2591">
+        <v>94</v>
+      </c>
+      <c r="C2591">
+        <v>5092.4</v>
+      </c>
+      <c r="D2591" t="s">
+        <v>2593</v>
+      </c>
+    </row>
+    <row r="2592" spans="1:4">
+      <c r="A2592" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2592">
+        <v>95</v>
+      </c>
+      <c r="C2592">
+        <v>5093.1</v>
+      </c>
+      <c r="D2592" t="s">
+        <v>2594</v>
+      </c>
+    </row>
+    <row r="2593" spans="1:4">
+      <c r="A2593" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2593">
+        <v>96</v>
+      </c>
+      <c r="C2593">
+        <v>5102.2</v>
+      </c>
+      <c r="D2593" t="s">
+        <v>2595</v>
+      </c>
+    </row>
+    <row r="2594" spans="1:4">
+      <c r="A2594" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2594">
+        <v>1</v>
+      </c>
+      <c r="C2594">
+        <v>4957.7</v>
+      </c>
+      <c r="D2594" t="s">
+        <v>2596</v>
+      </c>
+    </row>
+    <row r="2595" spans="1:4">
+      <c r="A2595" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2595">
+        <v>2</v>
+      </c>
+      <c r="C2595">
+        <v>4974</v>
+      </c>
+      <c r="D2595" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="2596" spans="1:4">
+      <c r="A2596" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2596">
+        <v>3</v>
+      </c>
+      <c r="C2596">
+        <v>4993.5</v>
+      </c>
+      <c r="D2596" t="s">
+        <v>2598</v>
+      </c>
+    </row>
+    <row r="2597" spans="1:4">
+      <c r="A2597" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2597">
+        <v>4</v>
+      </c>
+      <c r="C2597">
+        <v>4961.2</v>
+      </c>
+      <c r="D2597" t="s">
+        <v>2599</v>
+      </c>
+    </row>
+    <row r="2598" spans="1:4">
+      <c r="A2598" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2598">
+        <v>5</v>
+      </c>
+      <c r="C2598">
+        <v>4978.6</v>
+      </c>
+      <c r="D2598" t="s">
+        <v>2600</v>
+      </c>
+    </row>
+    <row r="2599" spans="1:4">
+      <c r="A2599" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2599">
+        <v>6</v>
+      </c>
+      <c r="C2599">
+        <v>4969.4</v>
+      </c>
+      <c r="D2599" t="s">
+        <v>2601</v>
+      </c>
+    </row>
+    <row r="2600" spans="1:4">
+      <c r="A2600" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2600">
+        <v>7</v>
+      </c>
+      <c r="C2600">
+        <v>4955.2</v>
+      </c>
+      <c r="D2600" t="s">
+        <v>2602</v>
+      </c>
+    </row>
+    <row r="2601" spans="1:4">
+      <c r="A2601" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2601">
+        <v>8</v>
+      </c>
+      <c r="C2601">
+        <v>4931.8</v>
+      </c>
+      <c r="D2601" t="s">
+        <v>2603</v>
+      </c>
+    </row>
+    <row r="2602" spans="1:4">
+      <c r="A2602" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2602">
+        <v>9</v>
+      </c>
+      <c r="C2602">
+        <v>4926.9</v>
+      </c>
+      <c r="D2602" t="s">
+        <v>2604</v>
+      </c>
+    </row>
+    <row r="2603" spans="1:4">
+      <c r="A2603" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2603">
+        <v>10</v>
+      </c>
+      <c r="C2603">
+        <v>4919.8</v>
+      </c>
+      <c r="D2603" t="s">
+        <v>2605</v>
+      </c>
+    </row>
+    <row r="2604" spans="1:4">
+      <c r="A2604" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2604">
+        <v>11</v>
+      </c>
+      <c r="C2604">
+        <v>4912.6</v>
+      </c>
+      <c r="D2604" t="s">
+        <v>2606</v>
+      </c>
+    </row>
+    <row r="2605" spans="1:4">
+      <c r="A2605" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2605">
+        <v>12</v>
+      </c>
+      <c r="C2605">
+        <v>4847.4</v>
+      </c>
+      <c r="D2605" t="s">
+        <v>2607</v>
+      </c>
+    </row>
+    <row r="2606" spans="1:4">
+      <c r="A2606" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2606">
+        <v>13</v>
+      </c>
+      <c r="C2606">
+        <v>4786.2</v>
+      </c>
+      <c r="D2606" t="s">
+        <v>2608</v>
+      </c>
+    </row>
+    <row r="2607" spans="1:4">
+      <c r="A2607" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2607">
+        <v>14</v>
+      </c>
+      <c r="C2607">
+        <v>4673.9</v>
+      </c>
+      <c r="D2607" t="s">
+        <v>2609</v>
+      </c>
+    </row>
+    <row r="2608" spans="1:4">
+      <c r="A2608" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2608">
+        <v>15</v>
+      </c>
+      <c r="C2608">
+        <v>4673.9</v>
+      </c>
+      <c r="D2608" t="s">
+        <v>2610</v>
+      </c>
+    </row>
+    <row r="2609" spans="1:4">
+      <c r="A2609" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2609">
+        <v>16</v>
+      </c>
+      <c r="C2609">
+        <v>4643.9</v>
+      </c>
+      <c r="D2609" t="s">
+        <v>2611</v>
+      </c>
+    </row>
+    <row r="2610" spans="1:4">
+      <c r="A2610" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2610">
+        <v>17</v>
+      </c>
+      <c r="C2610">
+        <v>4668.2</v>
+      </c>
+      <c r="D2610" t="s">
+        <v>2612</v>
+      </c>
+    </row>
+    <row r="2611" spans="1:4">
+      <c r="A2611" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2611">
+        <v>18</v>
+      </c>
+      <c r="C2611">
+        <v>4659.3</v>
+      </c>
+      <c r="D2611" t="s">
+        <v>2613</v>
+      </c>
+    </row>
+    <row r="2612" spans="1:4">
+      <c r="A2612" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2612">
+        <v>19</v>
+      </c>
+      <c r="C2612">
+        <v>4663.9</v>
+      </c>
+      <c r="D2612" t="s">
+        <v>2614</v>
+      </c>
+    </row>
+    <row r="2613" spans="1:4">
+      <c r="A2613" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2613">
+        <v>20</v>
+      </c>
+      <c r="C2613">
+        <v>4663.8</v>
+      </c>
+      <c r="D2613" t="s">
+        <v>2615</v>
+      </c>
+    </row>
+    <row r="2614" spans="1:4">
+      <c r="A2614" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2614">
+        <v>21</v>
+      </c>
+      <c r="C2614">
+        <v>4597.6</v>
+      </c>
+      <c r="D2614" t="s">
+        <v>2616</v>
+      </c>
+    </row>
+    <row r="2615" spans="1:4">
+      <c r="A2615" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2615">
+        <v>22</v>
+      </c>
+      <c r="C2615">
+        <v>4666.1</v>
+      </c>
+      <c r="D2615" t="s">
+        <v>2617</v>
+      </c>
+    </row>
+    <row r="2616" spans="1:4">
+      <c r="A2616" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2616">
+        <v>23</v>
+      </c>
+      <c r="C2616">
+        <v>4719.9</v>
+      </c>
+      <c r="D2616" t="s">
+        <v>2618</v>
+      </c>
+    </row>
+    <row r="2617" spans="1:4">
+      <c r="A2617" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2617">
+        <v>24</v>
+      </c>
+      <c r="C2617">
+        <v>4714</v>
+      </c>
+      <c r="D2617" t="s">
+        <v>2619</v>
+      </c>
+    </row>
+    <row r="2618" spans="1:4">
+      <c r="A2618" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2618">
+        <v>25</v>
+      </c>
+      <c r="C2618">
+        <v>4806</v>
+      </c>
+      <c r="D2618" t="s">
+        <v>2620</v>
+      </c>
+    </row>
+    <row r="2619" spans="1:4">
+      <c r="A2619" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2619">
+        <v>26</v>
+      </c>
+      <c r="C2619">
+        <v>4856</v>
+      </c>
+      <c r="D2619" t="s">
+        <v>2621</v>
+      </c>
+    </row>
+    <row r="2620" spans="1:4">
+      <c r="A2620" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2620">
+        <v>27</v>
+      </c>
+      <c r="C2620">
+        <v>4998.2</v>
+      </c>
+      <c r="D2620" t="s">
+        <v>2622</v>
+      </c>
+    </row>
+    <row r="2621" spans="1:4">
+      <c r="A2621" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2621">
+        <v>28</v>
+      </c>
+      <c r="C2621">
+        <v>5043</v>
+      </c>
+      <c r="D2621" t="s">
+        <v>2623</v>
+      </c>
+    </row>
+    <row r="2622" spans="1:4">
+      <c r="A2622" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2622">
+        <v>29</v>
+      </c>
+      <c r="C2622">
+        <v>5135.3</v>
+      </c>
+      <c r="D2622" t="s">
+        <v>2624</v>
+      </c>
+    </row>
+    <row r="2623" spans="1:4">
+      <c r="A2623" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2623">
+        <v>30</v>
+      </c>
+      <c r="C2623">
+        <v>5205.2</v>
+      </c>
+      <c r="D2623" t="s">
+        <v>2625</v>
+      </c>
+    </row>
+    <row r="2624" spans="1:4">
+      <c r="A2624" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2624">
+        <v>31</v>
+      </c>
+      <c r="C2624">
+        <v>5328.6</v>
+      </c>
+      <c r="D2624" t="s">
+        <v>2626</v>
+      </c>
+    </row>
+    <row r="2625" spans="1:4">
+      <c r="A2625" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2625">
+        <v>32</v>
+      </c>
+      <c r="C2625">
+        <v>5430.7</v>
+      </c>
+      <c r="D2625" t="s">
+        <v>2627</v>
+      </c>
+    </row>
+    <row r="2626" spans="1:4">
+      <c r="A2626" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2626">
+        <v>33</v>
+      </c>
+      <c r="C2626">
+        <v>5828.6</v>
+      </c>
+      <c r="D2626" t="s">
+        <v>2628</v>
+      </c>
+    </row>
+    <row r="2627" spans="1:4">
+      <c r="A2627" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2627">
+        <v>34</v>
+      </c>
+      <c r="C2627">
+        <v>5939.2</v>
+      </c>
+      <c r="D2627" t="s">
+        <v>2629</v>
+      </c>
+    </row>
+    <row r="2628" spans="1:4">
+      <c r="A2628" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2628">
+        <v>35</v>
+      </c>
+      <c r="C2628">
+        <v>6019.1</v>
+      </c>
+      <c r="D2628" t="s">
+        <v>2630</v>
+      </c>
+    </row>
+    <row r="2629" spans="1:4">
+      <c r="A2629" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2629">
+        <v>36</v>
+      </c>
+      <c r="C2629">
+        <v>6071.7</v>
+      </c>
+      <c r="D2629" t="s">
+        <v>2631</v>
+      </c>
+    </row>
+    <row r="2630" spans="1:4">
+      <c r="A2630" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2630">
+        <v>37</v>
+      </c>
+      <c r="C2630">
+        <v>5930.9</v>
+      </c>
+      <c r="D2630" t="s">
+        <v>2632</v>
+      </c>
+    </row>
+    <row r="2631" spans="1:4">
+      <c r="A2631" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2631">
+        <v>38</v>
+      </c>
+      <c r="C2631">
+        <v>5983.1</v>
+      </c>
+      <c r="D2631" t="s">
+        <v>2633</v>
+      </c>
+    </row>
+    <row r="2632" spans="1:4">
+      <c r="A2632" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2632">
+        <v>39</v>
+      </c>
+      <c r="C2632">
+        <v>5972.2</v>
+      </c>
+      <c r="D2632" t="s">
+        <v>2634</v>
+      </c>
+    </row>
+    <row r="2633" spans="1:4">
+      <c r="A2633" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2633">
+        <v>40</v>
+      </c>
+      <c r="C2633">
+        <v>6008.6</v>
+      </c>
+      <c r="D2633" t="s">
+        <v>2635</v>
+      </c>
+    </row>
+    <row r="2634" spans="1:4">
+      <c r="A2634" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2634">
+        <v>41</v>
+      </c>
+      <c r="C2634">
+        <v>5875.7</v>
+      </c>
+      <c r="D2634" t="s">
+        <v>2636</v>
+      </c>
+    </row>
+    <row r="2635" spans="1:4">
+      <c r="A2635" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2635">
+        <v>42</v>
+      </c>
+      <c r="C2635">
+        <v>5928.6</v>
+      </c>
+      <c r="D2635" t="s">
+        <v>2637</v>
+      </c>
+    </row>
+    <row r="2636" spans="1:4">
+      <c r="A2636" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2636">
+        <v>43</v>
+      </c>
+      <c r="C2636">
+        <v>5987.9</v>
+      </c>
+      <c r="D2636" t="s">
+        <v>2638</v>
+      </c>
+    </row>
+    <row r="2637" spans="1:4">
+      <c r="A2637" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2637">
+        <v>44</v>
+      </c>
+      <c r="C2637">
+        <v>6088.8</v>
+      </c>
+      <c r="D2637" t="s">
+        <v>2639</v>
+      </c>
+    </row>
+    <row r="2638" spans="1:4">
+      <c r="A2638" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2638">
+        <v>45</v>
+      </c>
+      <c r="C2638">
+        <v>6151.8</v>
+      </c>
+      <c r="D2638" t="s">
+        <v>2640</v>
+      </c>
+    </row>
+    <row r="2639" spans="1:4">
+      <c r="A2639" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2639">
+        <v>46</v>
+      </c>
+      <c r="C2639">
+        <v>6258.2</v>
+      </c>
+      <c r="D2639" t="s">
+        <v>2641</v>
+      </c>
+    </row>
+    <row r="2640" spans="1:4">
+      <c r="A2640" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2640">
+        <v>47</v>
+      </c>
+      <c r="C2640">
+        <v>6343.9</v>
+      </c>
+      <c r="D2640" t="s">
+        <v>2642</v>
+      </c>
+    </row>
+    <row r="2641" spans="1:4">
+      <c r="A2641" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2641">
+        <v>48</v>
+      </c>
+      <c r="C2641">
+        <v>6397.3</v>
+      </c>
+      <c r="D2641" t="s">
+        <v>2643</v>
+      </c>
+    </row>
+    <row r="2642" spans="1:4">
+      <c r="A2642" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2642">
+        <v>49</v>
+      </c>
+      <c r="C2642">
+        <v>6490.8</v>
+      </c>
+      <c r="D2642" t="s">
+        <v>2644</v>
+      </c>
+    </row>
+    <row r="2643" spans="1:4">
+      <c r="A2643" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2643">
+        <v>50</v>
+      </c>
+      <c r="C2643">
+        <v>6533.7</v>
+      </c>
+      <c r="D2643" t="s">
+        <v>2645</v>
+      </c>
+    </row>
+    <row r="2644" spans="1:4">
+      <c r="A2644" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2644">
+        <v>51</v>
+      </c>
+      <c r="C2644">
+        <v>6530.5</v>
+      </c>
+      <c r="D2644" t="s">
+        <v>2646</v>
+      </c>
+    </row>
+    <row r="2645" spans="1:4">
+      <c r="A2645" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2645">
+        <v>52</v>
+      </c>
+      <c r="C2645">
+        <v>6655</v>
+      </c>
+      <c r="D2645" t="s">
+        <v>2647</v>
+      </c>
+    </row>
+    <row r="2646" spans="1:4">
+      <c r="A2646" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2646">
+        <v>53</v>
+      </c>
+      <c r="C2646">
+        <v>6530</v>
+      </c>
+      <c r="D2646" t="s">
+        <v>2648</v>
+      </c>
+    </row>
+    <row r="2647" spans="1:4">
+      <c r="A2647" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2647">
+        <v>54</v>
+      </c>
+      <c r="C2647">
+        <v>6542</v>
+      </c>
+      <c r="D2647" t="s">
+        <v>2649</v>
+      </c>
+    </row>
+    <row r="2648" spans="1:4">
+      <c r="A2648" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2648">
+        <v>55</v>
+      </c>
+      <c r="C2648">
+        <v>6571.6</v>
+      </c>
+      <c r="D2648" t="s">
+        <v>2650</v>
+      </c>
+    </row>
+    <row r="2649" spans="1:4">
+      <c r="A2649" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2649">
+        <v>56</v>
+      </c>
+      <c r="C2649">
+        <v>6541.1</v>
+      </c>
+      <c r="D2649" t="s">
+        <v>2651</v>
+      </c>
+    </row>
+    <row r="2650" spans="1:4">
+      <c r="A2650" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2650">
+        <v>57</v>
+      </c>
+      <c r="C2650">
+        <v>6674.2</v>
+      </c>
+      <c r="D2650" t="s">
+        <v>2652</v>
+      </c>
+    </row>
+    <row r="2651" spans="1:4">
+      <c r="A2651" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2651">
+        <v>58</v>
+      </c>
+      <c r="C2651">
+        <v>6709.4</v>
+      </c>
+      <c r="D2651" t="s">
+        <v>2653</v>
+      </c>
+    </row>
+    <row r="2652" spans="1:4">
+      <c r="A2652" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2652">
+        <v>59</v>
+      </c>
+      <c r="C2652">
+        <v>6770.8</v>
+      </c>
+      <c r="D2652" t="s">
+        <v>2654</v>
+      </c>
+    </row>
+    <row r="2653" spans="1:4">
+      <c r="A2653" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2653">
+        <v>60</v>
+      </c>
+      <c r="C2653">
+        <v>6820.5</v>
+      </c>
+      <c r="D2653" t="s">
+        <v>2655</v>
+      </c>
+    </row>
+    <row r="2654" spans="1:4">
+      <c r="A2654" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2654">
+        <v>61</v>
+      </c>
+      <c r="C2654">
+        <v>6935.8</v>
+      </c>
+      <c r="D2654" t="s">
+        <v>2656</v>
+      </c>
+    </row>
+    <row r="2655" spans="1:4">
+      <c r="A2655" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2655">
+        <v>62</v>
+      </c>
+      <c r="C2655">
+        <v>6937.5</v>
+      </c>
+      <c r="D2655" t="s">
+        <v>2657</v>
+      </c>
+    </row>
+    <row r="2656" spans="1:4">
+      <c r="A2656" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2656">
+        <v>63</v>
+      </c>
+      <c r="C2656">
+        <v>7027.7</v>
+      </c>
+      <c r="D2656" t="s">
+        <v>2658</v>
+      </c>
+    </row>
+    <row r="2657" spans="1:4">
+      <c r="A2657" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2657">
+        <v>64</v>
+      </c>
+      <c r="C2657">
+        <v>7090.6</v>
+      </c>
+      <c r="D2657" t="s">
+        <v>2659</v>
+      </c>
+    </row>
+    <row r="2658" spans="1:4">
+      <c r="A2658" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2658">
+        <v>65</v>
+      </c>
+      <c r="C2658">
+        <v>6981.7</v>
+      </c>
+      <c r="D2658" t="s">
+        <v>2660</v>
+      </c>
+    </row>
+    <row r="2659" spans="1:4">
+      <c r="A2659" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2659">
+        <v>66</v>
+      </c>
+      <c r="C2659">
+        <v>6907.8</v>
+      </c>
+      <c r="D2659" t="s">
+        <v>2661</v>
+      </c>
+    </row>
+    <row r="2660" spans="1:4">
+      <c r="A2660" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2660">
+        <v>67</v>
+      </c>
+      <c r="C2660">
+        <v>6866.9</v>
+      </c>
+      <c r="D2660" t="s">
+        <v>2662</v>
+      </c>
+    </row>
+    <row r="2661" spans="1:4">
+      <c r="A2661" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2661">
+        <v>68</v>
+      </c>
+      <c r="C2661">
+        <v>6807.9</v>
+      </c>
+      <c r="D2661" t="s">
+        <v>2663</v>
+      </c>
+    </row>
+    <row r="2662" spans="1:4">
+      <c r="A2662" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2662">
+        <v>69</v>
+      </c>
+      <c r="C2662">
+        <v>6829.5</v>
+      </c>
+      <c r="D2662" t="s">
+        <v>2664</v>
+      </c>
+    </row>
+    <row r="2663" spans="1:4">
+      <c r="A2663" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2663">
+        <v>70</v>
+      </c>
+      <c r="C2663">
+        <v>6724.8</v>
+      </c>
+      <c r="D2663" t="s">
+        <v>2665</v>
+      </c>
+    </row>
+    <row r="2664" spans="1:4">
+      <c r="A2664" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2664">
+        <v>71</v>
+      </c>
+      <c r="C2664">
+        <v>6603.8</v>
+      </c>
+      <c r="D2664" t="s">
+        <v>2666</v>
+      </c>
+    </row>
+    <row r="2665" spans="1:4">
+      <c r="A2665" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2665">
+        <v>72</v>
+      </c>
+      <c r="C2665">
+        <v>6506.1</v>
+      </c>
+      <c r="D2665" t="s">
+        <v>2667</v>
+      </c>
+    </row>
+    <row r="2666" spans="1:4">
+      <c r="A2666" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2666">
+        <v>73</v>
+      </c>
+      <c r="C2666">
+        <v>6354.7</v>
+      </c>
+      <c r="D2666" t="s">
+        <v>2668</v>
+      </c>
+    </row>
+    <row r="2667" spans="1:4">
+      <c r="A2667" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2667">
+        <v>74</v>
+      </c>
+      <c r="C2667">
+        <v>6205.4</v>
+      </c>
+      <c r="D2667" t="s">
+        <v>2669</v>
+      </c>
+    </row>
+    <row r="2668" spans="1:4">
+      <c r="A2668" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2668">
+        <v>75</v>
+      </c>
+      <c r="C2668">
+        <v>6074.9</v>
+      </c>
+      <c r="D2668" t="s">
+        <v>2670</v>
+      </c>
+    </row>
+    <row r="2669" spans="1:4">
+      <c r="A2669" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2669">
+        <v>76</v>
+      </c>
+      <c r="C2669">
+        <v>5987.7</v>
+      </c>
+      <c r="D2669" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="2670" spans="1:4">
+      <c r="A2670" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2670">
+        <v>77</v>
+      </c>
+      <c r="C2670">
+        <v>5699.9</v>
+      </c>
+      <c r="D2670" t="s">
+        <v>2672</v>
+      </c>
+    </row>
+    <row r="2671" spans="1:4">
+      <c r="A2671" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2671">
+        <v>78</v>
+      </c>
+      <c r="C2671">
+        <v>5668.7</v>
+      </c>
+      <c r="D2671" t="s">
+        <v>2673</v>
+      </c>
+    </row>
+    <row r="2672" spans="1:4">
+      <c r="A2672" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2672">
+        <v>79</v>
+      </c>
+      <c r="C2672">
+        <v>5628.5</v>
+      </c>
+      <c r="D2672" t="s">
+        <v>2674</v>
+      </c>
+    </row>
+    <row r="2673" spans="1:4">
+      <c r="A2673" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2673">
+        <v>80</v>
+      </c>
+      <c r="C2673">
+        <v>5576.1</v>
+      </c>
+      <c r="D2673" t="s">
+        <v>2675</v>
+      </c>
+    </row>
+    <row r="2674" spans="1:4">
+      <c r="A2674" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2674">
+        <v>81</v>
+      </c>
+      <c r="C2674">
+        <v>5943.8</v>
+      </c>
+      <c r="D2674" t="s">
+        <v>2676</v>
+      </c>
+    </row>
+    <row r="2675" spans="1:4">
+      <c r="A2675" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2675">
+        <v>82</v>
+      </c>
+      <c r="C2675">
+        <v>6001</v>
+      </c>
+      <c r="D2675" t="s">
+        <v>2677</v>
+      </c>
+    </row>
+    <row r="2676" spans="1:4">
+      <c r="A2676" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2676">
+        <v>83</v>
+      </c>
+      <c r="C2676">
+        <v>5977.5</v>
+      </c>
+      <c r="D2676" t="s">
+        <v>2678</v>
+      </c>
+    </row>
+    <row r="2677" spans="1:4">
+      <c r="A2677" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2677">
+        <v>84</v>
+      </c>
+      <c r="C2677">
+        <v>5972.4</v>
+      </c>
+      <c r="D2677" t="s">
+        <v>2679</v>
+      </c>
+    </row>
+    <row r="2678" spans="1:4">
+      <c r="A2678" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2678">
+        <v>85</v>
+      </c>
+      <c r="C2678">
+        <v>5935.6</v>
+      </c>
+      <c r="D2678" t="s">
+        <v>2680</v>
+      </c>
+    </row>
+    <row r="2679" spans="1:4">
+      <c r="A2679" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2679">
+        <v>86</v>
+      </c>
+      <c r="C2679">
+        <v>5903.1</v>
+      </c>
+      <c r="D2679" t="s">
+        <v>2681</v>
+      </c>
+    </row>
+    <row r="2680" spans="1:4">
+      <c r="A2680" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2680">
+        <v>87</v>
+      </c>
+      <c r="C2680">
+        <v>5876.5</v>
+      </c>
+      <c r="D2680" t="s">
+        <v>2682</v>
+      </c>
+    </row>
+    <row r="2681" spans="1:4">
+      <c r="A2681" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2681">
+        <v>88</v>
+      </c>
+      <c r="C2681">
+        <v>5802.9</v>
+      </c>
+      <c r="D2681" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="2682" spans="1:4">
+      <c r="A2682" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2682">
+        <v>89</v>
+      </c>
+      <c r="C2682">
+        <v>5501</v>
+      </c>
+      <c r="D2682" t="s">
+        <v>2684</v>
+      </c>
+    </row>
+    <row r="2683" spans="1:4">
+      <c r="A2683" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2683">
+        <v>90</v>
+      </c>
+      <c r="C2683">
+        <v>5416.5</v>
+      </c>
+      <c r="D2683" t="s">
+        <v>2685</v>
+      </c>
+    </row>
+    <row r="2684" spans="1:4">
+      <c r="A2684" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2684">
+        <v>91</v>
+      </c>
+      <c r="C2684">
+        <v>5328.9</v>
+      </c>
+      <c r="D2684" t="s">
+        <v>2686</v>
+      </c>
+    </row>
+    <row r="2685" spans="1:4">
+      <c r="A2685" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2685">
+        <v>92</v>
+      </c>
+      <c r="C2685">
+        <v>5288.2</v>
+      </c>
+      <c r="D2685" t="s">
+        <v>2687</v>
+      </c>
+    </row>
+    <row r="2686" spans="1:4">
+      <c r="A2686" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2686">
+        <v>93</v>
+      </c>
+      <c r="C2686">
+        <v>5115.2</v>
+      </c>
+      <c r="D2686" t="s">
+        <v>2688</v>
+      </c>
+    </row>
+    <row r="2687" spans="1:4">
+      <c r="A2687" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2687">
+        <v>94</v>
+      </c>
+      <c r="C2687">
+        <v>5012.4</v>
+      </c>
+      <c r="D2687" t="s">
+        <v>2689</v>
+      </c>
+    </row>
+    <row r="2688" spans="1:4">
+      <c r="A2688" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2688">
+        <v>95</v>
+      </c>
+      <c r="C2688">
+        <v>5013.1</v>
+      </c>
+      <c r="D2688" t="s">
+        <v>2690</v>
+      </c>
+    </row>
+    <row r="2689" spans="1:4">
+      <c r="A2689" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2689">
+        <v>96</v>
+      </c>
+      <c r="C2689">
+        <v>5022.2</v>
+      </c>
+      <c r="D2689" t="s">
+        <v>2691</v>
       </c>
     </row>
   </sheetData>
